--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-13 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-14 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -13645,7 +13645,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Raymond James</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (primary); Data Science Intern; Machine Learning / ML Research Intern (Valence Labs)  (3 of 5 tracks)</t>
+          <t>Information Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>recursion.com/open-positions</t>
+          <t>raymondjames.wd1.myworkdayjobs.com/RaymondJamesEarlyCareers</t>
         </is>
       </c>
       <c r="F236" s="7" t="inlineStr">
@@ -13675,30 +13675,34 @@
       </c>
       <c r="G236" s="6" t="inlineStr">
         <is>
-          <t>Recursion has no live intern hiring process right now, and the intern-specific loop is not fully documented. The realistic path today, based on the Talent Network form and prior-cycle evidence, is: 1. Submit to the Internship Talent Network. Complete the Greenhouse form at job-boards.greenhouse.io/r</t>
-        </is>
-      </c>
-      <c r="H236" s="6" t="inlineStr"/>
+          <t>Raymond James runs a five-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through the Raymond James Workday portal with your resume, cover letter, and transcripts. Raymond James posts separate listings per division, so choose your strongest</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr">
+        <is>
+          <t>No. Raymond James does not offer visa sponsorship for internships. Applicants must be legally authorized to work in the U.S. without visa sponsorship now or in the future, including beyond OPT/EAD. International students</t>
+        </is>
+      </c>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>Partially. Prior Data Science intern JD said the program "lasts 3 months and can start any time, depending on your availability," with summer as the primary coh</t>
+          <t>Yes. Raymond James reviews applications on a rolling basis; apply within the first 2–3 weeks</t>
         </is>
       </c>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>Recursion does not publish intern pay. Community estimates (Glassdoor, tiny samples) suggest ~$65–67/hr for SWE/DS interns; Indeed estimates ~$29/hr, a wide and</t>
+          <t>$72,000–$95,000 annualized by division (IB Summer Analyst ~$95,000; general intern ~$72,000)</t>
         </is>
       </c>
       <c r="K236" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Applications for summer 2027 are expected to open around fall 2026 IF the program restarts; prior Summer 2024 intern roles posted ~Oct–Nov 2023. The Summer 2026 program was explicitly paused, so 2027 timing is uncertain (CEO transition + layoffs)</t>
+          <t>Open now for summer 2027: IB Summer Analyst M&amp;A (St. Petersburg), Capital Markets Summer Analyst and Equity Research Summer Internship posted September 11, 2026 on the Raymond James Early Careers Workday portal, no deadline printed. Summer 2028 not yet posted</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Recursion</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -13708,17 +13712,17 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Machine Learning Intern; Information Security Engineering Intern; Data Science Intern; ML Engineering Intern - Ads Marketplace (PhD)  (5 of 6 tracks)</t>
+          <t>Software Engineering Intern (primary); Data Science Intern; Machine Learning / ML Research Intern (Valence Labs)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/reddit</t>
+          <t>recursion.com/open-positions</t>
         </is>
       </c>
       <c r="F237" s="7" t="inlineStr">
@@ -13728,34 +13732,30 @@
       </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>For SWE interns, the process averages 2 rounds and about 3 days: a recruiter screen followed by a technical interview covering coding and data structures. Glassdoor rates the experience 88% positive with a 2.6 out of 5 difficulty, significantly easier than the full-time loop. Some candidates may fac</t>
-        </is>
-      </c>
-      <c r="H237" s="6" t="inlineStr">
-        <is>
-          <t>Not available for interns. JDs state "sponsorship is not available" and require US work authorization</t>
-        </is>
-      </c>
+          <t>Recursion has no live intern hiring process right now, and the intern-specific loop is not fully documented. The realistic path today, based on the Talent Network form and prior-cycle evidence, is: 1. Submit to the Internship Talent Network. Complete the Greenhouse form at job-boards.greenhouse.io/r</t>
+        </is>
+      </c>
+      <c r="H237" s="6" t="inlineStr"/>
       <c r="I237" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling with a soft close. The PM intern 2025 posting was removed January 6, 2025, suggesting roles close once filled. Apply immediately when postings go</t>
+          <t>Partially. Prior Data Science intern JD said the program "lasts 3 months and can start any time, depending on your availability," with summer as the primary coh</t>
         </is>
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>Official JD range $50 to $60/hr (SWE, PM). Community-reported: $68/hr SWE SF 2026. Housing stipend $2,000 to $6,000</t>
+          <t>Recursion does not publish intern pay. Community estimates (Glassdoor, tiny samples) suggest ~$65–67/hr for SWE/DS interns; Indeed estimates ~$29/hr, a wide and</t>
         </is>
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>Expected September to October 2026 for summer 2027. Projected from prior cycles, not yet posted</t>
+          <t>Not confirmed. Applications for summer 2027 are expected to open around fall 2026 IF the program restarts; prior Summer 2024 intern roles posted ~Oct–Nov 2023. The Summer 2026 program was explicitly paused, so 2027 timing is uncertain (CEO transition + layoffs)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -13765,17 +13765,17 @@
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>Data Science &amp; Bioinformatics; Technology/IT (AI/ML); Supply Chain &amp; Engineering  (3 of 12 tracks)</t>
+          <t>Software Engineering Intern; Machine Learning Intern; Information Security Engineering Intern; Data Science Intern; ML Engineering Intern - Ads Marketplace (PhD)  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>careers.regeneron.com/en/career-pathways/early-careers/</t>
+          <t>job-boards.greenhouse.io/reddit</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
@@ -13785,34 +13785,34 @@
       </c>
       <c r="G238" s="6" t="inlineStr">
         <is>
-          <t>The standard process is: ATS resume screen, recruiter phone screen (20 to 30 minutes), HireVue on-demand video interview (AI-scored on transcript alignment), then a live hiring manager interview via MS Teams (45 to 60 minutes). Select roles add an in-person final round at Tarrytown with 3 to 5 inter</t>
+          <t>For SWE interns, the process averages 2 rounds and about 3 days: a recruiter screen followed by a technical interview covering coding and data structures. Glassdoor rates the experience 88% positive with a 2.6 out of 5 difficulty, significantly easier than the full-time loop. Some candidates may fac</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
         <is>
-          <t>No. Regeneron does not directly sponsor visas for interns. International students on F-1 visas must secure CPT (Curricular Practical Training) authorization through their university before the internship starts. You'll n</t>
+          <t>Not available for interns. JDs state "sponsorship is not available" and require US work authorization</t>
         </is>
       </c>
       <c r="I238" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified within the window</t>
+          <t>Likely rolling with a soft close. The PM intern 2025 posting was removed January 6, 2025, suggesting roles close once filled. Apply immediately when postings go</t>
         </is>
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>$17.90–$50.90/hr by degree level + $1,400/mo housing stipend + free meals and gym</t>
+          <t>Official JD range $50 to $60/hr (SWE, PM). Community-reported: $68/hr SWE SF 2026. Housing stipend $2,000 to $6,000</t>
         </is>
       </c>
       <c r="K238" s="6" t="inlineStr">
         <is>
-          <t>For summer 2027: expected early Sep 2026 to mid-Nov 2026; priority by mid-Oct 2026 (projected from prior cycle)</t>
+          <t>Expected September to October 2026 for summer 2027. Projected from prior cycles, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>Relativity Space</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -13822,17 +13822,17 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Test Engineering; Robotics Software  (4 of 6 tracks)</t>
+          <t>Data Science &amp; Bioinformatics; Technology/IT (AI/ML); Supply Chain &amp; Engineering  (3 of 12 tracks)</t>
         </is>
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>relativityspace.com/internships</t>
+          <t>careers.regeneron.com/en/career-pathways/early-careers/</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
@@ -13842,34 +13842,34 @@
       </c>
       <c r="G239" s="6" t="inlineStr">
         <is>
-          <t>The standard process has 2–3 stages: a 30-minute recruiter phone screen covering background, projects, and career goals; a 45–60-minute technical interview specific to your role (coding for SWE, materials analysis for manufacturing, thermodynamics for propulsion); and a behavioral interview assessin</t>
+          <t>The standard process is: ATS resume screen, recruiter phone screen (20 to 30 minutes), HireVue on-demand video interview (AI-scored on transcript alignment), then a live hiring manager interview via MS Teams (45 to 60 minutes). Select roles add an in-person final round at Tarrytown with 3 to 5 inter</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
         <is>
-          <t>Most engineering roles require U.S. Person status under ITAR regulations (U.S. citizen, permanent resident, refugee, or asylee). F-1 visa holders are generally ineligible for hardware roles involving flight software, pro</t>
+          <t>No. Regeneron does not directly sponsor visas for interns. International students on F-1 visas must secure CPT (Curricular Practical Training) authorization through their university before the internship starts. You'll n</t>
         </is>
       </c>
       <c r="I239" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified; earlier applications get more attention</t>
+          <t>Yes. Positions filled as qualified candidates are identified within the window</t>
         </is>
       </c>
       <c r="J239" s="6" t="inlineStr">
         <is>
-          <t>SWE: $38/hr (2025 actual), projected $44–52/hr for 2027; housing stipend provided</t>
+          <t>$17.90–$50.90/hr by degree level + $1,400/mo housing stipend + free meals and gym</t>
         </is>
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>Expected September 2026; rolling review, peak interviews October 2026 to February 2027</t>
+          <t>For summer 2027: expected early Sep 2026 to mid-Nov 2026; priority by mid-Oct 2026 (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Relativity Space</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -13884,12 +13884,12 @@
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Technical Game Design; Research Scientist (AI)  (3 of 6 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Test Engineering; Robotics Software  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>riotgames.com/en/work-with-us/jobs</t>
+          <t>relativityspace.com/internships</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
@@ -13899,30 +13899,34 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">For SWE: a HackerRank OA (2 hours, 4 to 5 medium LeetCode problems), then 3 to 4 remote interviews over about 3 weeks testing technical skills, behavioral alignment, and culture fit. Creative tracks get take-home craft tests instead of the OA. Average time from application to decision is roughly 70 </t>
-        </is>
-      </c>
-      <c r="H240" s="6" t="inlineStr"/>
+          <t>The standard process has 2–3 stages: a 30-minute recruiter phone screen covering background, projects, and career goals; a 45–60-minute technical interview specific to your role (coding for SWE, materials analysis for manufacturing, thermodynamics for propulsion); and a behavioral interview assessin</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>Most engineering roles require U.S. Person status under ITAR regulations (U.S. citizen, permanent resident, refugee, or asylee). F-1 visa holders are generally ineligible for hardware roles involving flight software, pro</t>
+        </is>
+      </c>
       <c r="I240" s="6" t="inlineStr">
         <is>
-          <t>Partially. Review is rolling within each deadline window; applying early is recommended</t>
+          <t>Yes. Positions filled as qualified candidates are identified; earlier applications get more attention</t>
         </is>
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>$56.59/hr SWE; $35–$43/hr non-engineering; ~$2K/mo housing stipend</t>
+          <t>SWE: $38/hr (2025 actual), projected $44–52/hr for 2027; housing stipend provided</t>
         </is>
       </c>
       <c r="K240" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open September 2026 (projected from prior cycle); SWE closes late October 2026, other tracks through January 2027</t>
+          <t>Expected September 2026; rolling review, peak interviews October 2026 to February 2027</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -13932,17 +13936,17 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Mechanical Engineering Intern; Manufacturing Engineering Intern; AI, ML &amp; Data Science Intern  (4 of 6 tracks)</t>
+          <t>Software Engineering; Technical Game Design; Research Scientist (AI)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>careers.rivian.com/students</t>
+          <t>riotgames.com/en/work-with-us/jobs</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
@@ -13952,34 +13956,30 @@
       </c>
       <c r="G241" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a 30- to 45-minute recruiter phone screen, then face 1 to 2 technical interview rounds (coding on HackerRank for SWE or engineering fundamentals for hardware) plus a behavioral round and a hiring-manager chat. Glassdoor rates difficulty at 2.8 out of 5.</t>
-        </is>
-      </c>
-      <c r="H241" s="6" t="inlineStr">
-        <is>
-          <t>Valid work authorization required. F-1 CPT supported; international students reviewed case-by-case. Some roles carry export-control restrictions</t>
-        </is>
-      </c>
+          <t xml:space="preserve">For SWE: a HackerRank OA (2 hours, 4 to 5 medium LeetCode problems), then 3 to 4 remote interviews over about 3 weeks testing technical skills, behavioral alignment, and culture fit. Creative tracks get take-home craft tests instead of the OA. Average time from application to decision is roughly 70 </t>
+        </is>
+      </c>
+      <c r="H241" s="6" t="inlineStr"/>
       <c r="I241" s="6" t="inlineStr">
         <is>
-          <t>Yes. Rivian reviews applications and schedules interviews on a rolling basis from October through March. Early applicants face the most open seats</t>
+          <t>Partially. Review is rolling within each deadline window; applying early is recommended</t>
         </is>
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>$25 to $51 per hour depending on role and location. Palo Alto SWE interns report $51/hr ($8,840/mo). Housing stipend of $2,000 to $2,500/mo plus relocation assi</t>
+          <t>$56.59/hr SWE; $35–$43/hr non-engineering; ~$2K/mo housing stipend</t>
         </is>
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>Expected September to October 2026 for summer 2027 roles. Interviews run October 2026 through March 2027. Projected from prior-cycle timing</t>
+          <t>Applications for summer 2027 expected to open September 2026 (projected from prior cycle); SWE closes late October 2026, other tracks through January 2027</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -13989,17 +13989,17 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (Backend); Software Engineering (Web/Frontend); Software Engineering (iOS/Android); Machine Learning Engineering  (4 of 6 tracks)</t>
+          <t>Software Engineering Intern; Mechanical Engineering Intern; Manufacturing Engineering Intern; AI, ML &amp; Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>robinhood.com/us/en/careers/early-talent/</t>
+          <t>careers.rivian.com/students</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
@@ -14009,30 +14009,34 @@
       </c>
       <c r="G242" s="6" t="inlineStr">
         <is>
-          <t>SWE interns face a CodeSignal coding assessment (4 questions, 70 minutes, LeetCode Medium-Hard), then a recruiter phone screen, a technical phone interview via Karat or CoderPad, and a virtual onsite with two technical rounds and one behavioral round lasting about two hours total.</t>
-        </is>
-      </c>
-      <c r="H242" s="6" t="inlineStr"/>
+          <t>You apply online, complete a 30- to 45-minute recruiter phone screen, then face 1 to 2 technical interview rounds (coding on HackerRank for SWE or engineering fundamentals for hardware) plus a behavioral round and a hiring-manager chat. Glassdoor rates difficulty at 2.8 out of 5.</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>Valid work authorization required. F-1 CPT supported; international students reviewed case-by-case. Some roles carry export-control restrictions</t>
+        </is>
+      </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed "on a rolling basis" with most hiring completed by March</t>
+          <t>Yes. Rivian reviews applications and schedules interviews on a rolling basis from October through March. Early applicants face the most open seats</t>
         </is>
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>SWE: ~$48/hr + $6,000/mo housing stipend (Levels.fyi); Finance: $25–32/hr by zone</t>
+          <t>$25 to $51 per hour depending on role and location. Palo Alto SWE interns report $51/hr ($8,840/mo). Housing stipend of $2,000 to $2,500/mo plus relocation assi</t>
         </is>
       </c>
       <c r="K242" s="6" t="inlineStr">
         <is>
-          <t>Expected mid-September 2026, rolling through March 2027 (documented pattern; not yet posted)</t>
+          <t>Expected September to October 2026 for summer 2027 roles. Interviews run October 2026 through March 2027. Projected from prior-cycle timing</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>SambaNova</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -14042,17 +14046,17 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; ML/AI Compiler Intern; Hardware Engineering Intern; ML Software Engineer Intern</t>
+          <t>Software Engineering (Backend); Software Engineering (Web/Frontend); Software Engineering (iOS/Android); Machine Learning Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>sambanova.ai/company/careers/job-openings</t>
+          <t>robinhood.com/us/en/careers/early-talent/</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
@@ -14062,34 +14066,30 @@
       </c>
       <c r="G243" s="6" t="inlineStr">
         <is>
-          <t>SambaNova's interview process spans 22 to 35 days depending on role, with 58.6% of candidates reporting a positive experience on Glassdoor. The typical loop for intern candidates: 1. Apply online via sambanova.ai/company/careers . Submit your resume through the Greenhouse ATS. Online applications ac</t>
-        </is>
-      </c>
-      <c r="H243" s="6" t="inlineStr">
-        <is>
-          <t>H-1B sponsored (12 to 31 LCAs filed per year). F-1 students eligible via CPT. Full-time conversion sponsorship track record is established</t>
-        </is>
-      </c>
+          <t>SWE interns face a CodeSignal coding assessment (4 questions, 70 minutes, LeetCode Medium-Hard), then a recruiter phone screen, a technical phone interview via Karat or CoderPad, and a virtual onsite with two technical rounds and one behavioral round lasting about two hours total.</t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr"/>
       <c r="I243" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling. Online applications account for 54% of interview candidates, campus recruiting 27%, employee referrals 10%</t>
+          <t>Yes. Applications reviewed "on a rolling basis" with most hiring completed by March</t>
         </is>
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>Estimated $45 to $60/hr based on comparable AI chip startups and new grad offer data ($135K base). Housing and relocation support likely provided given Bay Area</t>
+          <t>SWE: ~$48/hr + $6,000/mo housing stipend (Levels.fyi); Finance: $25–32/hr by zone</t>
         </is>
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>Expected September to November 2026 for summer 2027 roles. Positions filled as suitable candidates are found. Some years postings appear as late as January to February</t>
+          <t>Expected mid-September 2026, rolling through March 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>Schlumberger (SLB)</t>
+          <t>SambaNova</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -14099,17 +14099,17 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>Field Engineer Intern (Operations); Technology (Digital Technology Intern; Technology) Engineering &amp; Manufacturing Intern  (3 of 5 tracks)</t>
+          <t>Software Engineer Intern; ML/AI Compiler Intern; Hardware Engineering Intern; ML Software Engineer Intern</t>
         </is>
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>careers.slb.com/early-careers/internships</t>
+          <t>sambanova.ai/company/careers/job-openings</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
@@ -14119,34 +14119,34 @@
       </c>
       <c r="G244" s="6" t="inlineStr">
         <is>
-          <t>Depending on track: an online or aptitude assessment (Java coding for digital roles; logic, math, and mechanics for field roles), a recruiter screen, a group-discussion round in sets of about 10, a technical interview with a field-topic presentation, and a hiring-manager round. Glassdoor rates the F</t>
+          <t>SambaNova's interview process spans 22 to 35 days depending on role, with 58.6% of candidates reporting a positive experience on Glassdoor. The typical loop for intern candidates: 1. Apply online via sambanova.ai/company/careers . Submit your resume through the Greenhouse ATS. Online applications ac</t>
         </is>
       </c>
       <c r="H244" s="6" t="inlineStr">
         <is>
-          <t>NOT FOUND for interns. Official pages don't state US sponsorship terms, and some branded postings are region-restricted (the STEM 2026 requisition required Pakistani student status). Confirm work-authorization requiremen</t>
+          <t>H-1B sponsored (12 to 31 LCAs filed per year). F-1 students eligible via CPT. Full-time conversion sponsorship track record is established</t>
         </is>
       </c>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively continuous. Early-careers postings feed a talent pool matched to vacancies as they open, though individual regional requisitions carry hard dea</t>
+          <t>Yes, effectively rolling. Online applications account for 54% of interview candidates, campus recruiting 27%, employee referrals 10%</t>
         </is>
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>All internships are paid, but SLB publishes no rate. Community data (Glassdoor/Levels.fyi, community-labeled): Field Engineer interns ~$27–$43/hr; Software Engi</t>
+          <t>Estimated $45 to $60/hr based on comparable AI chip startups and new grad offer data ($135K base). Housing and relocation support likely provided given Bay Area</t>
         </is>
       </c>
       <c r="K244" s="6" t="inlineStr">
         <is>
-          <t>Not yet published for Summer 2027. Projected from the documented Summer 2026 cycle: postings open on a rolling basis around Fall 2026 (expected), with a deadline near mid-May 2027 (expected (the STEM 2026 posting closed 18 May 2026)</t>
+          <t>Expected September to November 2026 for summer 2027 roles. Positions filled as suitable candidates are found. Some years postings appear as late as January to February</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Schlumberger (SLB)</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -14161,12 +14161,12 @@
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>Digital / Technology; Data Analytics  (2 of 6 tracks)</t>
+          <t>Field Engineer Intern (Operations); Technology (Digital Technology Intern; Technology) Engineering &amp; Manufacturing Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>join.sephora.com/careers?query=intern</t>
+          <t>careers.slb.com/early-careers/internships</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
@@ -14176,34 +14176,34 @@
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 stages over roughly 22 days: an on-demand video interview with behavioral and beauty-passion questions, a recruiter phone screen, a hiring manager interview, and for competitive tracks a final panel or Superday with senior leaders. Some roles include a 60 to 90 minute online assessm</t>
+          <t>Depending on track: an online or aptitude assessment (Java coding for digital roles; logic, math, and mechanics for field roles), a recruiter screen, a group-discussion round in sets of about 10, a technical interview with a field-topic presentation, and a hiring-manager round. Glassdoor rates the F</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
         <is>
-          <t>No. Sephora does not sponsor H-1B visas for internships. International students must have independent work authorization through CPT or OPT. You must be authorized to work in the U.S. without employer sponsorship.</t>
+          <t>NOT FOUND for interns. Official pages don't state US sponsorship terms, and some branded postings are region-restricted (the STEM 2026 requisition required Pakistani student status). Confirm work-authorization requiremen</t>
         </is>
       </c>
       <c r="I245" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; priority consideration by mid-October</t>
+          <t>Yes, effectively continuous. Early-careers postings feed a talent pool matched to vacancies as they open, though individual regional requisitions carry hard dea</t>
         </is>
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
-          <t>$22–$25/hr depending on role (~$9,000 total at top rate)</t>
+          <t>All internships are paid, but SLB publishes no rate. Community data (Glassdoor/Levels.fyi, community-labeled): Field Engineer interns ~$27–$43/hr; Software Engi</t>
         </is>
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open September 2026, closing by mid-November 2026 (rolling; documented pattern)</t>
+          <t>Not yet published for Summer 2027. Projected from the documented Summer 2026 cycle: postings open on a rolling basis around Fall 2026 (expected), with a deadline near mid-May 2027 (expected (the STEM 2026 posting closed 18 May 2026)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -14218,12 +14218,12 @@
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineer Intern; Mechanical Engineer Intern; Propulsion Engineer Intern; Systems Engineer Intern; Electrical Engineer Intern; Software Engineer Intern</t>
+          <t>Digital / Technology; Data Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>sierraspace.com/careers/internship/</t>
+          <t>join.sephora.com/careers?query=intern</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
@@ -14233,34 +14233,34 @@
       </c>
       <c r="G246" s="6" t="inlineStr">
         <is>
-          <t>Sierra Space does not publish a formal, round-by-round intern interview structure, so the steps below combine the official application flow with community-reported interview signal (Reddit r/aerospace): treat the interview specifics as directional, not official: 1. Monitor the internship page (start</t>
+          <t>Typically 3 to 4 stages over roughly 22 days: an on-demand video interview with behavioral and beauty-passion questions, a recruiter phone screen, a hiring manager interview, and for competitive tracks a final panel or Superday with senior leaders. Some roles include a 60 to 90 minute online assessm</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
         <is>
-          <t>Not available. Because of ITAR / export-control work, F-1 visa sponsorship is not offered for internships, and non-US-persons are effectively screened out. Security-clearance eligibility is also required</t>
+          <t>No. Sephora does not sponsor H-1B visas for internships. International students must have independent work authorization through CPT or OPT. You must be authorized to work in the U.S. without employer sponsorship.</t>
         </is>
       </c>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>Partially. Individual postings state the deadline stays open "until a qualified pool of candidates is identified," so roles close once filled. Apply early (as s</t>
+          <t>Yes. Applications reviewed on a rolling basis; priority consideration by mid-October</t>
         </is>
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>$30.00/hour on the official 2026 Colorado "Engineering Intern" posting. Community sources vary: Glassdoor ~$34/hr average (~$26–$47 range, 5 reports), Indeed ~$</t>
+          <t>$22–$25/hr depending on role (~$9,000 total at top rate)</t>
         </is>
       </c>
       <c r="K246" s="6" t="inlineStr">
         <is>
-          <t>Not yet published. Based on the documented annual cycle, applications for summer 2027 are expected to open around September 2026, with a deadline around December 2026 (expected, not confirmed)</t>
+          <t>Applications for summer 2027 expected to open September 2026, closing by mid-November 2026 (rolling; documented pattern)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Software Engineer Intern (AI/ML); Data Engineer Intern; Data Science Intern  (4 of 6 tracks)</t>
+          <t>Aerospace Engineer Intern; Mechanical Engineer Intern; Propulsion Engineer Intern; Systems Engineer Intern; Electrical Engineer Intern; Software Engineer Intern</t>
         </is>
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>careers.snowflake.com/us/en/university</t>
+          <t>sierraspace.com/careers/internship/</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
@@ -14290,34 +14290,34 @@
       </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a 30-minute recruiter phone screen, take a 90- to 120-minute HackerRank OA with 2 to 3 medium-to-hard problems, then two technical coding interviews plus a behavioral round. Offers come within 3 to 5 business days of the final interview. Total timeline: 6 to 10 weeks.</t>
+          <t>Sierra Space does not publish a formal, round-by-round intern interview structure, so the steps below combine the official application flow with community-reported interview signal (Reddit r/aerospace): treat the interview specifics as directional, not official: 1. Monitor the internship page (start</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for internships, OPT for new graduates. STEM-designated employer (24-month OPT extension eligible). No J-1 sponsorship</t>
+          <t>Not available. Because of ITAR / export-control work, F-1 visa sponsorship is not offered for internships, and non-US-persons are effectively screened out. Security-clearance eligibility is also required</t>
         </is>
       </c>
       <c r="I247" s="6" t="inlineStr">
         <is>
-          <t>Yes. Snowflake reviews applications on a rolling basis and extends offers as seats fill. Apply in September for the best response rates</t>
+          <t>Partially. Individual postings state the deadline stays open "until a qualified pool of candidates is identified," so roles close once filled. Apply early (as s</t>
         </is>
       </c>
       <c r="J247" s="6" t="inlineStr">
         <is>
-          <t>$55 per hour ($9,533 per month) for SWE interns per Levels.fyi. Housing stipend of $2,000 to $2,500 per month. Some offers include a relocation bonus of $500 to</t>
+          <t>$30.00/hour on the official 2026 Colorado "Engineering Intern" posting. Community sources vary: Glassdoor ~$34/hr average (~$26–$47 range, 5 reports), Indeed ~$</t>
         </is>
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>Expected early September 2026 for summer 2027 roles. Priority screening within the first two to three weeks; many positions fill by late October. Projected from prior cycle</t>
+          <t>Not yet published. Based on the documented annual cycle, applications for summer 2027 are expected to open around September 2026, with a deadline around December 2026 (expected, not confirmed)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>Snyk</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -14327,17 +14327,17 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – March 2027</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer / R&amp;D Engineer Intern (primary); Software Engineer Intern: Container; Co-op (Engineering / other); Marketing / Social Media Intern (non-engineering)  (4 of 5 tracks)</t>
+          <t>Software Engineer Intern; Software Engineer Intern (AI/ML); Data Engineer Intern; Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>snyk.io/careers/all-jobs/</t>
+          <t>careers.snowflake.com/us/en/university</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
@@ -14347,34 +14347,34 @@
       </c>
       <c r="G248" s="6" t="inlineStr">
         <is>
-          <t>Typically a recruiter screen, a hiring-manager conversation, and a technical PR-review round where you review a pull request sent in advance and present your findings, sometimes with a small coding problem. Average difficulty is about 2.9 out of 5, and the process runs roughly 21 to 24 days end to e</t>
+          <t>You apply, complete a 30-minute recruiter phone screen, take a 90- to 120-minute HackerRank OA with 2 to 3 medium-to-hard problems, then two technical coding interviews plus a behavioral round. Offers come within 3 to 5 business days of the final interview. Total timeline: 6 to 10 weeks.</t>
         </is>
       </c>
       <c r="H248" s="6" t="inlineStr">
         <is>
-          <t>Snyk sponsors H-1B for full-time roles (H1BGrader lists LCA/approval history for "Snyk LTD"). Intern-specific CPT/OPT/visa policy is not published, so confirm with the recruiter</t>
+          <t>F-1 CPT supported for internships, OPT for new graduates. STEM-designated employer (24-month OPT extension eligible). No J-1 sponsorship</t>
         </is>
       </c>
       <c r="I248" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Snyk posts discrete intern and co-op requisitions on Workday and removes them when filled, so treat it as cohort-based with rolling review and apply </t>
+          <t>Yes. Snowflake reviews applications on a rolling basis and extends offers as seats fill. Apply in September for the best response rates</t>
         </is>
       </c>
       <c r="J248" s="6" t="inlineStr">
         <is>
-          <t>No official Snyk intern rate is published (Levels.fyi's Snyk intern page has zero data points). Glassdoor estimates the Boston Co-op at about $43K to $73K per y</t>
+          <t>$55 per hour ($9,533 per month) for SWE interns per Levels.fyi. Housing stipend of $2,000 to $2,500 per month. Some offers include a relocation bonus of $500 to</t>
         </is>
       </c>
       <c r="K248" s="6" t="inlineStr">
         <is>
-          <t>Expected fall 2026 through winter/early spring 2027 for summer 2027 roles. The summer 2026 Software Engineer Intern posting (JR100489) was removed around May 8, 2026, so this mirrors the documented prior cycle. Snyk has not published a 2027 window (expected)</t>
+          <t>Expected early September 2026 for summer 2027 roles. Priority screening within the first two to three weeks; many positions fill by late October. Projected from prior cycle</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Snyk</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -14389,12 +14389,12 @@
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>Power Generation Engineering (Nuclear / Hydro / Fossil); Corporate Support) Engineering / System Planning; Technology Organization (IT / Cyber / AI)  (3 of 6 tracks)</t>
+          <t>Software Engineer / R&amp;D Engineer Intern (primary); Software Engineer Intern: Container; Co-op (Engineering / other); Marketing / Social Media Intern (non-engineering)  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>southerncompany-campus.jobs/</t>
+          <t>snyk.io/careers/all-jobs/</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
@@ -14404,34 +14404,34 @@
       </c>
       <c r="G249" s="6" t="inlineStr">
         <is>
-          <t>Largely career-fair and behavioral driven, with a scheduled final round. The Technology Organization and engineering tracks can include technical questions, while most other tracks are behavioral. Timelines are rolling and can run several weeks, in some cases roughly a month to six weeks, from inter</t>
+          <t>Typically a recruiter screen, a hiring-manager conversation, and a technical PR-review round where you review a pull request sent in advance and present your findings, sometimes with a small coding problem. Average difficulty is about 2.9 out of 5, and the process runs roughly 21 to 24 days end to e</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
         <is>
-          <t>No visa sponsorship is indicated for student roles; current US work authorization is required. Return: co-ops are officially described as "direct pipelines into full-time careers," though no conversion percentage is publ</t>
+          <t>Snyk sponsors H-1B for full-time roles (H1BGrader lists LCA/approval history for "Snyk LTD"). Intern-specific CPT/OPT/visa policy is not published, so confirm with the recruiter</t>
         </is>
       </c>
       <c r="I249" s="6" t="inlineStr">
         <is>
-          <t>Partially. Positions are posted per term (Spring/Summer/Fall) and filled as campus recruiting progresses, so effectively rolling within each recruiting season r</t>
+          <t xml:space="preserve">Partially. Snyk posts discrete intern and co-op requisitions on Workday and removes them when filled, so treat it as cohort-based with rolling review and apply </t>
         </is>
       </c>
       <c r="J249" s="6" t="inlineStr">
         <is>
-          <t>Official pages do not publish rates but confirm some positions include a housing stipend. Community data (Levels.fyi/Indeed) puts tech/engineering interns aroun</t>
+          <t>No official Snyk intern rate is published (Levels.fyi's Snyk intern page has zero data points). Glassdoor estimates the Boston Co-op at about $43K to $73K per y</t>
         </is>
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>No single national deadline. For Summer 2027, postings are expected to open ~fall 2026, with the main recruiting push via career fairs January–March 2027 (projected from the documented Spring 2026 cycle). Label: expected</t>
+          <t>Expected fall 2026 through winter/early spring 2027 for summer 2027 roles. The summer 2026 Software Engineer Intern posting (JR100489) was removed around May 8, 2026, so this mirrors the documented prior cycle. Snyk has not published a 2027 window (expected)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September 2026 – March 2027</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Backend/Full-Stack); C++ Software Engineer Intern; Solutions Engineer Intern; Security Engineering Intern; Data Science Intern  (5 of 6 tracks)</t>
+          <t>Power Generation Engineering (Nuclear / Hydro / Fossil); Corporate Support) Engineering / System Planning; Technology Organization (IT / Cyber / AI)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>careers.cisco.com/global/en/splunk</t>
+          <t>southerncompany-campus.jobs/</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
@@ -14461,34 +14461,34 @@
       </c>
       <c r="G250" s="6" t="inlineStr">
         <is>
-          <t>A recruiter phone screen (15 to 30 minutes), then a Karat technical assessment (15-minute MCQ quiz plus 60-minute live coding), then a hiring manager behavioral interview (45 to 60 minutes). Some roles add a virtual onsite with 2 to 4 additional rounds. Total timeline is 3 to 5 weeks from first cont</t>
+          <t>Largely career-fair and behavioral driven, with a scheduled final round. The Technology Organization and engineering tracks can include technical questions, while most other tracks are behavioral. Timelines are rolling and can run several weeks, in some cases roughly a month to six weeks, from inter</t>
         </is>
       </c>
       <c r="H250" s="6" t="inlineStr">
         <is>
-          <t>Roles available in US, Canada, UK, Germany, Poland, Australia, Japan, Singapore. US roles likely require valid work authorization (CPT for F-1 students)</t>
+          <t>No visa sponsorship is indicated for student roles; current US work authorization is required. Return: co-ops are officially described as "direct pipelines into full-time careers," though no conversion percentage is publ</t>
         </is>
       </c>
       <c r="I250" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Splunk posts roles in early September and fills them progressively through February. Apply in the first weeks</t>
+          <t>Partially. Positions are posted per term (Spring/Summer/Fall) and filled as campus recruiting progresses, so effectively rolling within each recruiting season r</t>
         </is>
       </c>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>SWE intern $42 to $60/hr ($7,280 to $10,400/mo) depending on location. Housing stipends $2,000 to $6,000 for select offices</t>
+          <t>Official pages do not publish rates but confirm some positions include a housing stipend. Community data (Levels.fyi/Indeed) puts tech/engineering interns aroun</t>
         </is>
       </c>
       <c r="K250" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open early September 2026, rolling through February 2027. Projected from prior cycles, not yet posted</t>
+          <t>No single national deadline. For Summer 2027, postings are expected to open ~fall 2026, with the main recruiting push via career fairs January–March 2027 (projected from the documented Spring 2026 cycle). Label: expected</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>Sprout Social</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -14498,17 +14498,17 @@
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Associate Software Engineer (New Grad); Data Science / Analytics Program  (3 of 5 tracks)</t>
+          <t>Software Engineering Intern (Backend/Full-Stack); C++ Software Engineer Intern; Solutions Engineer Intern; Security Engineering Intern; Data Science Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/sproutsocialcollege</t>
+          <t>careers.cisco.com/global/en/splunk</t>
         </is>
       </c>
       <c r="F251" s="7" t="inlineStr">
@@ -14518,34 +14518,34 @@
       </c>
       <c r="G251" s="6" t="inlineStr">
         <is>
-          <t>Typically 4 to 5 rounds over approximately 17 days for SWE: recruiter screen, hiring manager call, 1 to 2 technical interviews with whiteboarding and pseudocoding, and an optional CRG coffee chat. Difficulty is rated 2.9 out of 5 on Glassdoor with 59% positive SWE experience.</t>
+          <t>A recruiter phone screen (15 to 30 minutes), then a Karat technical assessment (15-minute MCQ quiz plus 60-minute live coding), then a hiring manager behavioral interview (45 to 60 minutes). Some roles add a virtual onsite with 2 to 4 additional rounds. Total timeline is 3 to 5 weeks from first cont</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
         <is>
-          <t>Limited. Sprout Social filed 2 H-1B LCAs between 2021–2023 (100% approval rate). F-1 students can typically use CPT for internships without employer H-1B sponsorship. Confirm directly with recruiting</t>
+          <t>Roles available in US, Canada, UK, Germany, Poland, Australia, Japan, Singapore. US roles likely require valid work authorization (CPT for F-1 students)</t>
         </is>
       </c>
       <c r="I251" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling within an application window. Sprout Social uses Greenhouse ATS and accepts applications as positions are posted. No official confirmation of rol</t>
+          <t>Yes, confirmed. Splunk posts roles in early September and fills them progressively through February. Apply in the first weeks</t>
         </is>
       </c>
       <c r="J251" s="6" t="inlineStr">
         <is>
-          <t>$24/hr median base pay, $27/hr median total compensation (Glassdoor). Range of $23 to $35/hr depending on role and bonus component. Full-time Associate SWE earn</t>
+          <t>SWE intern $42 to $60/hr ($7,280 to $10,400/mo) depending on location. Housing stipends $2,000 to $6,000 for select offices</t>
         </is>
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>Expected September–November 2026 for summer 2027 roles. Interviews October–January, offers December–February. No active college postings as of July 2026, consistent with a fall recruiting cycle</t>
+          <t>Applications for summer 2027 expected to open early September 2026, rolling through February 2027. Projected from prior cycles, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Sprout Social</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -14555,17 +14555,17 @@
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>Vehicle Engineering Summer Internship (primary); Technical Software Summer Internship; Chrysler Institute of Engineering (CIE): new-grad  (3 of 5 tracks)</t>
+          <t>Software Engineering Intern; Associate Software Engineer (New Grad); Data Science / Analytics Program  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>careers.stellantis.com/early-careers/students-north-america/</t>
+          <t>job-boards.greenhouse.io/sproutsocialcollege</t>
         </is>
       </c>
       <c r="F252" s="7" t="inlineStr">
@@ -14575,34 +14575,34 @@
       </c>
       <c r="G252" s="6" t="inlineStr">
         <is>
-          <t>Mostly behavioral and conversational: a recruiter or HR screen, then a hiring-manager round with "tell me about yourself," STAR questions, a resume walkthrough, and role-specific technical questions (for IT/software, digital electronics and basic control theory). Interns rate the difficulty just 2.4</t>
+          <t>Typically 4 to 5 rounds over approximately 17 days for SWE: recruiter screen, hiring manager call, 1 to 2 technical interviews with whiteboarding and pseudocoding, and an optional CRG coffee chat. Difficulty is rated 2.9 out of 5 on Glassdoor with 59% positive SWE experience.</t>
         </is>
       </c>
       <c r="H252" s="6" t="inlineStr">
         <is>
-          <t>None. Every intern JD states Stellantis "does not provide immigration-related sponsorship for this role." Eligible work rights: US Citizen, US Permanent Resident, or US Student Visa (e.g., F-1 with valid authorization)</t>
+          <t>Limited. Sprout Social filed 2 H-1B LCAs between 2021–2023 (100% approval rate). F-1 students can typically use CPT for internships without employer H-1B sponsorship. Confirm directly with recruiting</t>
         </is>
       </c>
       <c r="I252" s="6" t="inlineStr">
         <is>
-          <t>Not strictly rolling, but apply early. Each posting has a fixed apply-by date, yet every JD warns it "may close before the stated closing date." Interns average</t>
+          <t>Likely rolling within an application window. Sprout Social uses Greenhouse ATS and accepts applications as positions are posted. No official confirmation of rol</t>
         </is>
       </c>
       <c r="J252" s="6" t="inlineStr">
         <is>
-          <t>"Competitive salary" (no official number). Community self-reports: engineering interns ~$24–$25/hr (Indeed); all-intern average ~$33/hr, ~$68K/yr (Glassdoor). P</t>
+          <t>$24/hr median base pay, $27/hr median total compensation (Glassdoor). Range of $23 to $35/hr depending on role and bonus component. Full-time Associate SWE earn</t>
         </is>
       </c>
       <c r="K252" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: postings went live September 3, 2026 (50+ US roles across Purchasing, Manufacturing, HR, Engineering, Communications, Planning); no close dates published yet. The 2026 cycle closed in November (Technical Software Nov 8, Vehicle Engineering Nov 22, 2025), so treat that as the outer limit</t>
+          <t>Expected September–November 2026 for summer 2027 roles. Interviews October–January, offers December–February. No active college postings as of July 2026, consistent with a fall recruiting cycle</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>Suno</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -14612,17 +14612,17 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (confirmed); ML / AI Research Intern (plausible); ML Infrastructure Intern (plausible)  (3 of 4 tracks)</t>
+          <t>Vehicle Engineering Summer Internship (primary); Technical Software Summer Internship; Chrysler Institute of Engineering (CIE): new-grad  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/suno</t>
+          <t>careers.stellantis.com/early-careers/students-north-america/</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
@@ -14632,34 +14632,34 @@
       </c>
       <c r="G253" s="6" t="inlineStr">
         <is>
-          <t>The process averages 17 days and is rated 2.91 out of 5.0 difficulty on Glassdoor. It typically includes a recruiter phone screen (15 to 30 minutes), a technical screen (coding challenge or take-home), technical interviews (system design and coding), a behavioral and culture fit round, and a final t</t>
+          <t>Mostly behavioral and conversational: a recruiter or HR screen, then a hiring-manager round with "tell me about yourself," STAR questions, a resume walkthrough, and role-specific technical questions (for IT/software, digital electronics and basic control theory). Interns rate the difficulty just 2.4</t>
         </is>
       </c>
       <c r="H253" s="6" t="inlineStr">
         <is>
-          <t>US work eligibility required. F-1 students with CPT authorization qualify. H-1B sponsorship confirmed for full-time roles on a selective basis (MigrateMate, MyVisaJobs). Intern-specific visa sponsorship is not confirmed</t>
+          <t>None. Every intern JD states Stellantis "does not provide immigration-related sponsorship for this role." Eligible work rights: US Citizen, US Permanent Resident, or US Student Visa (e.g., F-1 with valid authorization)</t>
         </is>
       </c>
       <c r="I253" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Suno uses Ashby as its ATS and postings stay open until filled. Glassdoor shows an average of 17 days from application to decision. Apply early (Sep</t>
+          <t>Not strictly rolling, but apply early. Each posting has a fixed apply-by date, yet every JD warns it "may close before the stated closing date." Interns average</t>
         </is>
       </c>
       <c r="J253" s="6" t="inlineStr">
         <is>
-          <t>$73.56/hr (~$12,750/month, ~$153K annualized) per Levels.fyi user-reported data for Summer 2026 in Cambridge, MA. One of the highest-paying AI startup internshi</t>
+          <t>"Competitive salary" (no official number). Community self-reports: engineering interns ~$24–$25/hr (Indeed); all-intern average ~$33/hr, ~$68K/yr (Glassdoor). P</t>
         </is>
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>Expected September to November 2026 for summer 2027 roles. No fixed public deadline; roles appear to fill on a rolling basis. Projected from the Summer 2026 intern cycle</t>
+          <t>Open now for summer 2027: postings went live September 3, 2026 (50+ US roles across Purchasing, Manufacturing, HR, Engineering, Communications, Planning); no close dates published yet. The 2026 cycle closed in November (Technical Software Nov 8, Vehicle Engineering Nov 22, 2025), so treat that as the outer limit</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>Suno</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -14669,17 +14669,17 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data / Analytics; Cybersecurity  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern (confirmed); ML / AI Research Intern (plausible); ML Infrastructure Intern (plausible)  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>careers.t-mobile.com/internship</t>
+          <t>jobs.ashbyhq.com/suno</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
@@ -14689,34 +14689,34 @@
       </c>
       <c r="G254" s="6" t="inlineStr">
         <is>
-          <t>Typically a recruiter phone screen, then a behavioral or hiring-manager round (sometimes a group interview), with an online assessment added for some technology roles. After interviews, candidates often fill out a form to rank project teams. Glassdoor rates interview difficulty a moderate 2.7/5, and</t>
+          <t>The process averages 17 days and is rated 2.91 out of 5.0 difficulty on Glassdoor. It typically includes a recruiter phone screen (15 to 30 minutes), a technical screen (coding challenge or take-home), technical interviews (system design and coding), a behavioral and culture fit round, and a final t</t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr">
         <is>
-          <t>None. Both JDs state T-Mobile does not sponsor work visas, and note this also applies to F-1 students seeking sponsorship after graduation</t>
+          <t>US work eligibility required. F-1 students with CPT authorization qualify. H-1B sponsorship confirmed for full-time roles on a selective basis (MigrateMate, MyVisaJobs). Intern-specific visa sponsorship is not confirmed</t>
         </is>
       </c>
       <c r="I254" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively. Roles are posted on a 1:1 basis and close once the position is filled, so apply the week a req opens</t>
+          <t>Likely yes. Suno uses Ashby as its ATS and postings stay open until filled. Glassdoor shows an average of 17 days from application to decision. Apply early (Sep</t>
         </is>
       </c>
       <c r="J254" s="6" t="inlineStr">
         <is>
-          <t>Official JD ranges: $26–$47/hr for Software Engineering (higher with a STEM designation), $20–$40/hr for Finance. Community sites report a ~$39–$47/hr median fo</t>
+          <t>$73.56/hr (~$12,750/month, ~$153K annualized) per Levels.fyi user-reported data for Summer 2026 in Cambridge, MA. One of the highest-paying AI startup internshi</t>
         </is>
       </c>
       <c r="K254" s="6" t="inlineStr">
         <is>
-          <t>Not yet published. Projected from the 2026 cycle: postings open ~late summer / early fall 2026 (expected), deadlines land on a rolling basis around April 2027 (expected)</t>
+          <t>Expected September to November 2026 for summer 2027 roles. No fixed public deadline; roles appear to fill on a rolling basis. Projected from the Summer 2026 intern cycle</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -14726,17 +14726,17 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>September–December 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer / Game Programming (2K Engineering Graduate Program; Rockstar ; Data Science / Analytics Intern (Take-Two, NYC); Art / Technical Art (2K &amp; Rockstar)  (4 of 5 tracks)</t>
+          <t>Software Engineering; Data / Analytics; Cybersecurity  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>careers.take2games.com/jobs</t>
+          <t>careers.t-mobile.com/internship</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
@@ -14746,30 +14746,34 @@
       </c>
       <c r="G255" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The 2K Engineering Graduate Program runs four stages: application and CV review, a mandatory group scoping call, a C++ task stage, and an interview stage. 2K and Rockstar studio roles commonly add a coding test (a HackerRank test in C++, or C# for some Rockstar roles). Some Take-Two corporate roles </t>
-        </is>
-      </c>
-      <c r="H255" s="6" t="inlineStr"/>
+          <t>Typically a recruiter phone screen, then a behavioral or hiring-manager round (sometimes a group interview), with an online assessment added for some technology roles. After interviews, candidates often fill out a form to rank project teams. Glassdoor rates interview difficulty a moderate 2.7/5, and</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t>None. Both JDs state T-Mobile does not sponsor work visas, and note this also applies to F-1 students seeking sponsorship after graduation</t>
+        </is>
+      </c>
       <c r="I255" s="6" t="inlineStr">
         <is>
-          <t>2K Engineering Graduate Program: yes, applications are processed as they are received (apply early). Take-Two Summer Internship: not explicitly stated, but post</t>
+          <t>Yes, effectively. Roles are posted on a 1:1 basis and close once the position is filled, so apply the week a req opens</t>
         </is>
       </c>
       <c r="J255" s="6" t="inlineStr">
         <is>
-          <t>Take-Two Summer Internship, NYC: $30/hour (Data Science and IT Support intern JDs). 2K Engineering Graduate Program: "highly competitive salary" plus benefits (</t>
+          <t>Official JD ranges: $26–$47/hr for Software Engineering (higher with a STEM designation), $20–$40/hr for Finance. Community sites report a ~$39–$47/hr median fo</t>
         </is>
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2K Engineering Graduate Program: applications re-open September 2026 for the Summer 2027 intake (official). Take-Two Summer Internship reqs are expected to open ~fall 2026 (roughly Oct–Dec) and close early 2027, based on the prior cycle being removed in early January 2026</t>
+          <t>Not yet published. Projected from the 2026 cycle: postings open ~late summer / early fall 2026 (expected), deadlines land on a rolling basis around April 2027 (expected)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>Tempus AI</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -14779,17 +14783,17 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – March 2027</t>
+          <t>September–December 2026</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>AI Data Science Summer Analyst (undergrad, primary); Machine Learning Summer Associate, Applied AI &amp; Research (Master's/PhD); Software Engineering (Security) Summer Analyst (undergrad); Generative AI Summer Analyst (undergrad, bio/MD-PhD interest)</t>
+          <t>Software Engineer / Game Programming (2K Engineering Graduate Program; Rockstar ; Data Science / Analytics Intern (Take-Two, NYC); Art / Technical Art (2K &amp; Rockstar)  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>tempus.wd5.myworkdayjobs.com/Tempus_Careers</t>
+          <t>careers.take2games.com/jobs</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
@@ -14799,34 +14803,30 @@
       </c>
       <c r="G256" s="6" t="inlineStr">
         <is>
-          <t>Tempus does not officially publish its intern interview sequence, so the steps below synthesize the documented application flow with community reports and standard summer-analyst norms. Steps 4 through 6 are inferred: 1. Fall 2026: watch and apply. Monitor the Tempus Workday careers site (tempus.wd5</t>
-        </is>
-      </c>
-      <c r="H256" s="6" t="inlineStr">
-        <is>
-          <t>Tempus AI/Tempus Labs is an active H-1B sponsor (200+ LCAs historically; recent 2026 filings include a Senior Software Engineer in Chicago at $140K). Intern-specific CPT/OPT sponsorship is not explicitly confirmed in the</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The 2K Engineering Graduate Program runs four stages: application and CV review, a mandatory group scoping call, a C++ task stage, and an interview stage. 2K and Rockstar studio roles commonly add a coding test (a HackerRank test in C++, or C# for some Rockstar roles). Some Take-Two corporate roles </t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="inlineStr"/>
       <c r="I256" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Tempus runs a structured summer program with defined start waves, but individual reqs are reviewed on a rolling basis until filled. Levels.fyi notes </t>
+          <t>2K Engineering Graduate Program: yes, applications are processed as they are received (apply early). Take-Two Summer Internship: not explicitly stated, but post</t>
         </is>
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>Official JD pay ranges (Illinois): $25/hr for undergraduate summer analysts, $35/hr for advanced-degree (Master's/PhD) ML summer associates, plus a relocation b</t>
+          <t>Take-Two Summer Internship, NYC: $30/hour (Data Science and IT Support intern JDs). 2K Engineering Graduate Program: "highly competitive salary" plus benefits (</t>
         </is>
       </c>
       <c r="K256" s="6" t="inlineStr">
         <is>
-          <t>Expected to open ~Fall 2026 (roughly Sept–Nov) and run through spring 2027, projected from the Summer 2026 cycle whose AI Data Science role stayed live until May 21, 2026. As of August 2026 no Summer 2027 intern reqs are live yet (160 open roles on Workday, none intern)</t>
+          <t>2K Engineering Graduate Program: applications re-open September 2026 for the Summer 2027 intake (official). Take-Two Summer Internship reqs are expected to open ~fall 2026 (roughly Oct–Dec) and close early 2027, based on the prior cycle being removed in early January 2026</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Tempus AI</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -14836,17 +14836,17 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – February 2027</t>
+          <t>September 2026 – March 2027</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>AI / Self-Driving (Autopilot); Software Engineering (Vehicle); Battery / Cell Engineering; Supply Chain Analytics  (4 of 6 tracks)</t>
+          <t>AI Data Science Summer Analyst (undergrad, primary); Machine Learning Summer Associate, Applied AI &amp; Research (Master's/PhD); Software Engineering (Security) Summer Analyst (undergrad); Generative AI Summer Analyst (undergrad, bio/MD-PhD interest)</t>
         </is>
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>tesla.com/careers/internships</t>
+          <t>tempus.wd5.myworkdayjobs.com/Tempus_Careers</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
@@ -14856,34 +14856,34 @@
       </c>
       <c r="G257" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 rounds: a recruiter phone screen (15 to 30 minutes), an online coding assessment via Codility (about 85 minutes, 2 to 3 LeetCode-Medium problems), a live technical interview (45 to 60 minutes), and a manager or final round. Non-SWE roles may replace the coding assessment with a proj</t>
+          <t>Tempus does not officially publish its intern interview sequence, so the steps below synthesize the documented application flow with community reports and standard summer-analyst norms. Steps 4 through 6 are inferred: 1. Fall 2026: watch and apply. Monitor the Tempus Workday careers site (tempus.wd5</t>
         </is>
       </c>
       <c r="H257" s="6" t="inlineStr">
         <is>
-          <t>Tesla accepts F-1 CPT and OPT for internships. You'll need to verify 40-hour-per-week work authorization for the on-site requirement. H-1B sponsorship for full-time roles after internship conversion is handled case by ca</t>
+          <t>Tempus AI/Tempus Labs is an active H-1B sponsor (200+ LCAs historically; recent 2026 filings include a Senior Software Engineer in Chicago at $140K). Intern-specific CPT/OPT sponsorship is not explicitly confirmed in the</t>
         </is>
       </c>
       <c r="I257" s="6" t="inlineStr">
         <is>
-          <t>Yes. Tesla reviews applications immediately upon submission and may recruit up to 4 months after posting</t>
+          <t xml:space="preserve">Partially. Tempus runs a structured summer program with defined start waves, but individual reqs are reviewed on a rolling basis until filled. Levels.fyi notes </t>
         </is>
       </c>
       <c r="J257" s="6" t="inlineStr">
         <is>
-          <t>SWE $58.80/hr (Levels.fyi); AI/Self-Driving $48–$72/hr; manufacturing $20–$50/hr + housing $700–$3,000/mo</t>
+          <t>Official JD pay ranges (Illinois): $25/hr for undergraduate summer analysts, $35/hr for advanced-degree (Master's/PhD) ML summer associates, plus a relocation b</t>
         </is>
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>Rolling year-round; applications for summer 2027 expected to open September–November 2026, with peak hiring November 2026 through February 2027 (projected from prior cycle)</t>
+          <t>Expected to open ~Fall 2026 (roughly Sept–Nov) and run through spring 2027, projected from the Summer 2026 cycle whose AI Data Science role stayed live until May 21, 2026. As of August 2026 no Summer 2027 intern reqs are live yet (160 open roles on Workday, none intern)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -14893,17 +14893,17 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026 – February 2027</t>
         </is>
       </c>
       <c r="D258" s="6" t="inlineStr">
         <is>
-          <t>Textron Aviation Engineering (Wichita, KS); Textron Systems Engineering &amp; IT (Hunt Valley, MD)  (2 of 6 tracks)</t>
+          <t>AI / Self-Driving (Autopilot); Software Engineering (Vehicle); Battery / Cell Engineering; Supply Chain Analytics  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>careers.textron.com/interns/</t>
+          <t>tesla.com/careers/internships</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
@@ -14913,30 +14913,34 @@
       </c>
       <c r="G258" s="6" t="inlineStr">
         <is>
-          <t>A straightforward 2-step process: a recruiter phone screen (15-30 min) covering your background and motivation, followed by a virtual interview with the hiring manager via Microsoft Teams (30-60 min) using STAR behavioral questions. Bell may add an in-person component with a technical competency lea</t>
-        </is>
-      </c>
-      <c r="H258" s="6" t="inlineStr"/>
+          <t>Typically 3 to 4 rounds: a recruiter phone screen (15 to 30 minutes), an online coding assessment via Codility (about 85 minutes, 2 to 3 LeetCode-Medium problems), a live technical interview (45 to 60 minutes), and a manager or final round. Non-SWE roles may replace the coding assessment with a proj</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>Tesla accepts F-1 CPT and OPT for internships. You'll need to verify 40-hour-per-week work authorization for the on-site requirement. H-1B sponsorship for full-time roles after internship conversion is handled case by ca</t>
+        </is>
+      </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Applications reviewed in order of submission; window may shorten based on candidate flow</t>
+          <t>Yes. Tesla reviews applications immediately upon submission and may recruit up to 4 months after posting</t>
         </is>
       </c>
       <c r="J258" s="6" t="inlineStr">
         <is>
-          <t>$24 to $43/hr depending on role and division; housing/relocation stipends of $800/mo to $2,750</t>
+          <t>SWE $58.80/hr (Levels.fyi); AI/Self-Driving $48–$72/hr; manufacturing $20–$50/hr + housing $700–$3,000/mo</t>
         </is>
       </c>
       <c r="K258" s="6" t="inlineStr">
         <is>
-          <t>September 1 to October 31, 2026 for summer 2027 (documented annual pattern)</t>
+          <t>Rolling year-round; applications for summer 2027 expected to open September–November 2026, with peak hiring November 2026 through February 2027 (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -14946,17 +14950,17 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science &amp; Analytics Intern  (2 of 8 tracks)</t>
+          <t>Textron Aviation Engineering (Wichita, KS); Textron Systems Engineering &amp; IT (Hunt Valley, MD)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>jobs.thermofisher.com/global/en/c/students-internships-jobs</t>
+          <t>careers.textron.com/interns/</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
@@ -14966,34 +14970,30 @@
       </c>
       <c r="G259" s="6" t="inlineStr">
         <is>
-          <t>The process typically includes a 15-to-30-minute recruiter phone screen with STAR-format behavioral questions, followed by one to two rounds of interviews with hiring managers covering role-specific skills and 4i Values alignment. Glassdoor rates interview difficulty at 2.4 out of 5.</t>
-        </is>
-      </c>
-      <c r="H259" s="6" t="inlineStr">
-        <is>
-          <t>Not available. Thermo Fisher does not sponsor F-1, J-1, H-1, OPT, or CPT visas for internships. Applicants must be legally authorized to work in the U.S. without sponsorship</t>
-        </is>
-      </c>
+          <t>A straightforward 2-step process: a recruiter phone screen (15-30 min) covering your background and motivation, followed by a virtual interview with the hiring manager via Microsoft Teams (30-60 min) using STAR behavioral questions. Bell may add an in-person component with a technical competency lea</t>
+        </is>
+      </c>
+      <c r="H259" s="6" t="inlineStr"/>
       <c r="I259" s="6" t="inlineStr">
         <is>
-          <t>Yes. Thermo Fisher reviews applications on a rolling basis and extends offers as seats fill. Apply within the first few weeks of a posting for the best response</t>
+          <t>Effectively yes. Applications reviewed in order of submission; window may shorten based on candidate flow</t>
         </is>
       </c>
       <c r="J259" s="6" t="inlineStr">
         <is>
-          <t>$21.50–$38.00 per hour depending on role and location. Software engineering interns at the higher end (~$38/hr per Levels.fyi). $5,000 relocation stipend for st</t>
+          <t>$24 to $43/hr depending on role and division; housing/relocation stipends of $800/mo to $2,750</t>
         </is>
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>Expected September to November 2026 for summer 2027 roles, projected from the 2025–26 cycle. Some postings appear as early as August</t>
+          <t>September 1 to October 31, 2026 for summer 2027 (documented annual pattern)</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>Thinking Machines Lab</t>
+          <t>Thermo Fisher</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -15003,17 +15003,17 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D260" s="6" t="inlineStr">
         <is>
-          <t>AI Research Intern (Post-Training); AI Research Intern (Multimodal); Software Engineering Intern; AI Safety Research Intern; Product Engineering Intern</t>
+          <t>Software Engineering Intern; Data Science &amp; Analytics Intern  (2 of 8 tracks)</t>
         </is>
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/thinkingmachines</t>
+          <t>jobs.thermofisher.com/global/en/c/students-internships-jobs</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr">
@@ -15023,34 +15023,34 @@
       </c>
       <c r="G260" s="6" t="inlineStr">
         <is>
-          <t>No intern-specific data exists. The full-time interview process averages 19 days, has a difficulty rating of 3.41 out of 5.0, and an 88% positive experience rate. It typically includes a recruiter screen, a technical interview weighted toward your deepest expertise, and a behavioral interview focuse</t>
+          <t>The process typically includes a 15-to-30-minute recruiter phone screen with STAR-format behavioral questions, followed by one to two rounds of interviews with hiring managers covering role-specific skills and 4i Values alignment. Glassdoor rates interview difficulty at 2.4 out of 5.</t>
         </is>
       </c>
       <c r="H260" s="6" t="inlineStr">
         <is>
-          <t>H-1B confirmed for full-time hires (4 technical hires on H-1B in Q1 2025). Intern visa sponsorship not confirmed</t>
+          <t>Not available. Thermo Fisher does not sponsor F-1, J-1, H-1, OPT, or CPT visas for internships. Applicants must be legally authorized to work in the U.S. without sponsorship</t>
         </is>
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>NOT CONFIRMED. Peer AI labs typically use deadline-based windows rather than rolling admissions</t>
+          <t>Yes. Thermo Fisher reviews applications on a rolling basis and extends offers as seats fill. Apply within the first few weeks of a posting for the best response</t>
         </is>
       </c>
       <c r="J260" s="6" t="inlineStr">
         <is>
-          <t>No intern pay data. Based on peer labs (Anthropic, OpenAI), estimated at $9,000 to $12,000/month plus a housing stipend. Full-time technical base: $450,000 to $</t>
+          <t>$21.50–$38.00 per hour depending on role and location. Software engineering interns at the higher end (~$38/hr per Levels.fyi). $5,000 relocation stipend for st</t>
         </is>
       </c>
       <c r="K260" s="6" t="inlineStr">
         <is>
-          <t>NOT CONFIRMED. If a program launches, expect applications to open Fall 2026 to Winter 2027, based on peer AI lab patterns (Anthropic, OpenAI, DeepMind)</t>
+          <t>Expected September to November 2026 for summer 2027 roles, projected from the 2025–26 cycle. Some postings appear as early as August</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Thinking Machines Lab</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -15060,17 +15060,17 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D261" s="6" t="inlineStr">
         <is>
-          <t>Information Technology Internship  (1 of 6 tracks)</t>
+          <t>AI Research Intern (Post-Training); AI Research Intern (Multimodal); Software Engineering Intern; AI Safety Research Intern; Product Engineering Intern</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>jobs.tjx.com/global/en/studentsus</t>
+          <t>job-boards.greenhouse.io/thinkingmachines</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr">
@@ -15080,30 +15080,34 @@
       </c>
       <c r="G261" s="6" t="inlineStr">
         <is>
-          <t>Officially: a HireVue one-way video interview, then a case study, then behavioral interviews. The HireVue is about five recorded questions with roughly a minute to prep each, including an allocate-the-product scenario. The case study tests retail math, and the final round is often two interviewers f</t>
-        </is>
-      </c>
-      <c r="H261" s="6" t="inlineStr"/>
+          <t>No intern-specific data exists. The full-time interview process averages 19 days, has a difficulty rating of 3.41 out of 5.0, and an 88% positive experience rate. It typically includes a recruiter screen, a technical interview weighted toward your deepest expertise, and a behavioral interview focuse</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="inlineStr">
+        <is>
+          <t>H-1B confirmed for full-time hires (4 technical hires on H-1B in Q1 2025). Intern visa sponsorship not confirmed</t>
+        </is>
+      </c>
       <c r="I261" s="6" t="inlineStr">
         <is>
-          <t>Yes (community-reported). TJX interviews merchandising interns as applications arrive, and many roles fill before the formal deadline. Apply the first week post</t>
+          <t>NOT CONFIRMED. Peer AI labs typically use deadline-based windows rather than rolling admissions</t>
         </is>
       </c>
       <c r="J261" s="6" t="inlineStr">
         <is>
-          <t>No official rate published. Community and Levels.fyi data: merchandising interns ~$21–$26/hr; software-engineer interns ~$22/hr. Housing and relocation are unre</t>
+          <t>No intern pay data. Based on peer labs (Anthropic, OpenAI), estimated at $9,000 to $12,000/month plus a housing stipend. Full-time technical base: $450,000 to $</t>
         </is>
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>Not officially published. Expected to open around September 2026 for summer 2027, with a priority window of roughly mid-September through October (community-sourced from the previous cycle)</t>
+          <t>NOT CONFIRMED. If a program launches, expect applications to open Fall 2026 to Winter 2027, based on peer AI lab patterns (Anthropic, OpenAI, DeepMind)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -15113,17 +15117,17 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D262" s="6" t="inlineStr">
         <is>
-          <t>Refining &amp; Petrochemical Site Engineering Intern (primary); Cross-Segment Business &amp; Technical Intern  (2 of 6 tracks)</t>
+          <t>Information Technology Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E262" s="7" t="inlineStr">
         <is>
-          <t>jobs.totalenergies.com/en_US/careers/</t>
+          <t>jobs.tjx.com/global/en/studentsus</t>
         </is>
       </c>
       <c r="F262" s="7" t="inlineStr">
@@ -15133,30 +15137,30 @@
       </c>
       <c r="G262" s="6" t="inlineStr">
         <is>
-          <t>TotalEnergies' intern hiring is short and friendly relative to many peers: Glassdoor rates intern interview difficulty Average (3 of 5) with 75% positive experiences and an average of about 29 days start to finish. Here is the typical path: 1. Apply online via the TotalEnergies careers portal, filte</t>
+          <t>Officially: a HireVue one-way video interview, then a case study, then behavioral interviews. The HireVue is about five recorded questions with roughly a minute to prep each, including an allocate-the-product scenario. The case study tests retail math, and the final round is often two interviewers f</t>
         </is>
       </c>
       <c r="H262" s="6" t="inlineStr"/>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>Partially. TotalEnergies says internships are "offered throughout the year in all fields and in all countries," but the flagship US summer site engineering inte</t>
+          <t>Yes (community-reported). TJX interviews merchandising interns as applications arrive, and many roles fill before the formal deadline. Apply the first week post</t>
         </is>
       </c>
       <c r="J262" s="6" t="inlineStr">
         <is>
-          <t>Community-reported only (not official). US Glassdoor intern reports (17 salaries) cluster around $5,000/month median, with a $4,000–$7,000 typical band and indi</t>
+          <t>No official rate published. Community and Levels.fyi data: merchandising interns ~$21–$26/hr; software-engineer interns ~$22/hr. Housing and relocation are unre</t>
         </is>
       </c>
       <c r="K262" s="6" t="inlineStr">
         <is>
-          <t>Not published for Summer 2027 as of August 2026. US roles are expected to open around September to November 2026 for the following summer, aligned with fall career fairs (dates expected, not confirmed). Monitor from Sept 2026.</t>
+          <t>Not officially published. Expected to open around September 2026 for summer 2027, with a priority window of roughly mid-September through October (community-sourced from the previous cycle)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -15166,17 +15170,17 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D263" s="6" t="inlineStr">
         <is>
-          <t>TFS D&amp;T Software Engineering  (1 of 6 tracks)</t>
+          <t>Refining &amp; Petrochemical Site Engineering Intern (primary); Cross-Segment Business &amp; Technical Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>careers.toyota.com/us/en/students</t>
+          <t>jobs.totalenergies.com/en_US/careers/</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
@@ -15186,34 +15190,30 @@
       </c>
       <c r="G263" s="6" t="inlineStr">
         <is>
-          <t>Toyota's funnel runs faster than most manufacturing giants once it starts: Glassdoor data puts the average time from first contact to hire at about 17 days for interns, and the interview difficulty is rated 3.0 out of 5.0 (moderate). Here's the full pipeline: 1. Apply at careers.toyota.com or throug</t>
-        </is>
-      </c>
-      <c r="H263" s="6" t="inlineStr">
-        <is>
-          <t>No. Toyota explicitly states: "Must have the right to work in the United States and not require Toyota sponsorship for immigration-related employment (e.g., H-1B, O-1, E-3, TN, or F-1 OPT extension) now or in the future.</t>
-        </is>
-      </c>
+          <t>TotalEnergies' intern hiring is short and friendly relative to many peers: Glassdoor rates intern interview difficulty Average (3 of 5) with 75% positive experiences and an average of about 29 days start to finish. Here is the typical path: 1. Apply online via the TotalEnergies careers portal, filte</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr"/>
       <c r="I263" s="6" t="inlineStr">
         <is>
-          <t>Yes. Toyota reviews on a rolling basis; early submission is advantageous as positions fill continuously</t>
+          <t>Partially. TotalEnergies says internships are "offered throughout the year in all fields and in all countries," but the flagship US summer site engineering inte</t>
         </is>
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
-          <t>SWE $29–$32/hr; Toyota Research Institute $65/hr; general intern ~$24/hr + housing/relocation support</t>
+          <t>Community-reported only (not official). US Glassdoor intern reports (17 salaries) cluster around $5,000/month median, with a $4,000–$7,000 typical band and indi</t>
         </is>
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>Expected September to October 2026 for summer 2027 (projected from the summer 2026 cycle); most postings close by November or December 2026</t>
+          <t>Not published for Summer 2027 as of August 2026. US roles are expected to open around September to November 2026 for the following summer, aligned with fall career fairs (dates expected, not confirmed). Monitor from Sept 2026.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -15223,17 +15223,17 @@
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – February 2027</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D264" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (US Summer, primary); Software Engineer Intern (January start); Software Engineer Intern (International)  (3 of 5 tracks)</t>
+          <t>TFS D&amp;T Software Engineering  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>twilio.com/en-us/company/jobs</t>
+          <t>careers.toyota.com/us/en/students</t>
         </is>
       </c>
       <c r="F264" s="7" t="inlineStr">
@@ -15243,34 +15243,34 @@
       </c>
       <c r="G264" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen (15 to 30 minutes), then a HackerRank online assessment (interns report 1 Easy + 1 Medium in about 1.5 hours), a live coding interview (~2 LeetCode-medium problems in an hour), sometimes a design round, and a hiring-manager plus "Twilio Magic" values behavioral round. The full loo</t>
+          <t>Toyota's funnel runs faster than most manufacturing giants once it starts: Glassdoor data puts the average time from first contact to hire at about 17 days for interns, and the interview difficulty is rated 3.0 out of 5.0 (moderate). Here's the full pipeline: 1. Apply at careers.toyota.com or throug</t>
         </is>
       </c>
       <c r="H264" s="6" t="inlineStr">
         <is>
-          <t>NOT FOUND on both. No official or Twilio-specific community conversion rate was located; offers are extended (one Reddit intern reported receiving one), but no rate is published. Intern visa sponsorship is likewise not s</t>
+          <t>No. Toyota explicitly states: "Must have the right to work in the United States and not require Toyota sponsorship for immigration-related employment (e.g., H-1B, O-1, E-3, TN, or F-1 OPT extension) now or in the future.</t>
         </is>
       </c>
       <c r="I264" s="6" t="inlineStr">
         <is>
-          <t>Likely yes (expected). Twilio publishes no fixed hard deadline; the Social Impact posting notes applications "may close earlier depending on business needs," an</t>
+          <t>Yes. Toyota reviews on a rolling basis; early submission is advantageous as positions fill continuously</t>
         </is>
       </c>
       <c r="J264" s="6" t="inlineStr">
         <is>
-          <t>Community-reported (Levels.fyi, 10 data points): ~$47/hour (~$8,147/month) for Summer 2026 remote US, historical range $35–$53/hour. Not an official Twilio figu</t>
+          <t>SWE $29–$32/hr; Toyota Research Institute $65/hr; general intern ~$24/hr + housing/relocation support</t>
         </is>
       </c>
       <c r="K264" s="6" t="inlineStr">
         <is>
-          <t>Not yet posted. Applications for summer 2027 are expected to open ~Fall 2026 and run rolling into winter/early 2027, projected from the Summer 2026 cycle. No official 2027 date is published yet.</t>
+          <t>Expected September to October 2026 for summer 2027 (projected from the summer 2026 cycle); most postings close by November or December 2026</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -15280,17 +15280,17 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September 2026 – February 2027</t>
         </is>
       </c>
       <c r="D265" s="6" t="inlineStr">
         <is>
-          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern (US Summer, primary); Software Engineer Intern (January start); Software Engineer Intern (International)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>careers.ulta.com/internships</t>
+          <t>twilio.com/en-us/company/jobs</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr">
@@ -15300,30 +15300,34 @@
       </c>
       <c r="G265" s="6" t="inlineStr">
         <is>
-          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
-        </is>
-      </c>
-      <c r="H265" s="6" t="inlineStr"/>
+          <t>A recruiter screen (15 to 30 minutes), then a HackerRank online assessment (interns report 1 Easy + 1 Medium in about 1.5 hours), a live coding interview (~2 LeetCode-medium problems in an hour), sometimes a design round, and a hiring-manager plus "Twilio Magic" values behavioral round. The full loo</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="inlineStr">
+        <is>
+          <t>NOT FOUND on both. No official or Twilio-specific community conversion rate was located; offers are extended (one Reddit intern reported receiving one), but no rate is published. Intern visa sponsorship is likewise not s</t>
+        </is>
+      </c>
       <c r="I265" s="6" t="inlineStr">
         <is>
-          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
+          <t>Likely yes (expected). Twilio publishes no fixed hard deadline; the Social Impact posting notes applications "may close earlier depending on business needs," an</t>
         </is>
       </c>
       <c r="J265" s="6" t="inlineStr">
         <is>
-          <t>$14.00–$25.00 per hour for corporate interns (official 2026-cycle Ulta JDs, Bolingbrook), roughly $5,600–$10,000 over a 10-week summer at 40 hrs/week. Higher Gl</t>
+          <t>Community-reported (Levels.fyi, 10 data points): ~$47/hour (~$8,147/month) for Summer 2026 remote US, historical range $35–$53/hour. Not an official Twilio figu</t>
         </is>
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>Not yet published for Summer 2027. Projected from the 2026 cycle: postings expected ~fall 2026 with an application deadline around January 1, 2027 (expected). Apply early (Sept–Oct) for priority</t>
+          <t>Not yet posted. Applications for summer 2027 are expected to open ~Fall 2026 and run rolling into winter/early 2027, projected from the Summer 2026 cycle. No official 2027 date is published yet.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -15333,17 +15337,17 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D266" s="6" t="inlineStr">
         <is>
-          <t>Digital Technology; Technical Operations  (2 of 6 tracks)</t>
+          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>careers.united.com/us/en/students</t>
+          <t>careers.ulta.com/internships</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
@@ -15353,30 +15357,30 @@
       </c>
       <c r="G266" s="6" t="inlineStr">
         <is>
-          <t>After application review, most candidates face one to two behavioral interviews in STAR format. Digital Technology roles include a two-interviewer panel. Some tracks add an online assessment: a values-fit quiz for general roles or a proctored 55-minute exam for analytical positions. The overall proc</t>
+          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr"/>
       <c r="I266" s="6" t="inlineStr">
         <is>
-          <t>Yes. Offers extended on a rolling basis; timelines may vary</t>
+          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
         </is>
       </c>
       <c r="J266" s="6" t="inlineStr">
         <is>
-          <t>$20 to $31/hr depending on track; some DT roles include a $2,000 relocation stipend; plus unlimited standby flights</t>
+          <t>$14.00–$25.00 per hour for corporate interns (official 2026-cycle Ulta JDs, Bolingbrook), roughly $5,600–$10,000 over a 10-week summer at 40 hrs/week. Higher Gl</t>
         </is>
       </c>
       <c r="K266" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open September to November 2026 (documented pattern across multiple cycles; not yet posted)</t>
+          <t>Not yet published for Summer 2027. Projected from the 2026 cycle: postings expected ~fall 2026 with an application deadline around January 1, 2027 (expected). Apply early (Sept–Oct) for priority</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -15391,12 +15395,12 @@
       </c>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>Technology Development Program (TDP); Analytics  (2 of 6 tracks)</t>
+          <t>Digital Technology; Technical Operations  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>careers.unitedhealthgroup.com/</t>
+          <t>careers.united.com/us/en/students</t>
         </is>
       </c>
       <c r="F267" s="7" t="inlineStr">
@@ -15406,34 +15410,30 @@
       </c>
       <c r="G267" s="6" t="inlineStr">
         <is>
-          <t>After applying online, most candidates receive a HireVue or Modern Hire asynchronous video interview with behavioral prompts within 24–48 hours. Next comes a 20–30 minute recruiter phone screen, followed by a "Super Day" panel of 2–3 hours with back-to-back interviews. The whole process averages abo</t>
-        </is>
-      </c>
-      <c r="H267" s="6" t="inlineStr">
-        <is>
-          <t>CPT and OPT are available for F-1 students on internships. However, TDP generally requires unrestricted US work authorization for full-time conversion. Actuarial programs tend to be more flexible on sponsorship. Check th</t>
-        </is>
-      </c>
+          <t>After application review, most candidates face one to two behavioral interviews in STAR format. Digital Technology roles include a two-interviewer panel. Some tracks add an online assessment: a values-fit quiz for general roles or a proctored 55-minute exam for analytical positions. The overall proc</t>
+        </is>
+      </c>
+      <c r="H267" s="6" t="inlineStr"/>
       <c r="I267" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Rolling admissions with priority to early applicants; referrals are 3–4x more likely to reach a digital interview</t>
+          <t>Yes. Offers extended on a rolling basis; timelines may vary</t>
         </is>
       </c>
       <c r="J267" s="6" t="inlineStr">
         <is>
-          <t>~$22.72/hr average (Indeed); Optum SWE interns up to $33/hr in Boston (Levels.fyi); ~$2,500 housing stipend available</t>
+          <t>$20 to $31/hr depending on track; some DT roles include a $2,000 relocation stipend; plus unlimited standby flights</t>
         </is>
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>Expected mid-September to mid-November 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Applications for summer 2027 expected to open September to November 2026 (documented pattern across multiple cycles; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -15448,12 +15448,12 @@
       </c>
       <c r="D268" s="6" t="inlineStr">
         <is>
-          <t>Chemical Engineering Intern; Mechanical Engineering Intern; Safety Engineering Intern  (3 of 6 tracks)</t>
+          <t>Technology Development Program (TDP); Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>valero.com/careers</t>
+          <t>careers.unitedhealthgroup.com/</t>
         </is>
       </c>
       <c r="F268" s="7" t="inlineStr">
@@ -15463,30 +15463,34 @@
       </c>
       <c r="G268" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Glassdoor rates the interview difficulty at 2.3 out of 5 (easy), with 78% of candidates reporting a positive experience. Expect behavioral questions like “tell me about yourself,” “why Valero,” and questions about your coursework and past experiences. Multiple candidates confirm there are typically </t>
-        </is>
-      </c>
-      <c r="H268" s="6" t="inlineStr"/>
+          <t>After applying online, most candidates receive a HireVue or Modern Hire asynchronous video interview with behavioral prompts within 24–48 hours. Next comes a 20–30 minute recruiter phone screen, followed by a "Super Day" panel of 2–3 hours with back-to-back interviews. The whole process averages abo</t>
+        </is>
+      </c>
+      <c r="H268" s="6" t="inlineStr">
+        <is>
+          <t>CPT and OPT are available for F-1 students on internships. However, TDP generally requires unrestricted US work authorization for full-time conversion. Actuarial programs tend to be more flexible on sponsorship. Check th</t>
+        </is>
+      </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions may be listed for as few as 3 days; recruiters contact candidates within 30 days</t>
+          <t>Effectively yes. Rolling admissions with priority to early applicants; referrals are 3–4x more likely to reach a digital interview</t>
         </is>
       </c>
       <c r="J268" s="6" t="inlineStr">
         <is>
-          <t>$34.50–$41.50/hr for engineering interns (2026 JDs); overtime eligible; relocation assistance included</t>
+          <t>~$22.72/hr average (Indeed); Optum SWE interns up to $33/hr in Boston (Levels.fyi); ~$2,500 housing stipend available</t>
         </is>
       </c>
       <c r="K268" s="6" t="inlineStr">
         <is>
-          <t>Expected fall 2026 (Sep–Nov) for summer 2027; no official 2027 dates posted yet</t>
+          <t>Expected mid-September to mid-November 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>Vanta</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -15496,17 +15500,17 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – February 2027</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern / New Grad SWE (primary); Backend / Platform Engineering; GRC Product Engineering  (3 of 4 tracks)</t>
+          <t>Chemical Engineering Intern; Mechanical Engineering Intern; Safety Engineering Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/vanta</t>
+          <t>valero.com/careers</t>
         </is>
       </c>
       <c r="F269" s="7" t="inlineStr">
@@ -15516,30 +15520,30 @@
       </c>
       <c r="G269" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three stages over roughly 3 to 5 weeks: a recruiter screen (30 to 45 minutes on background, goals, and comp), a technical screening (an online assessment or a live one-hour CoderPad coding round over Zoom), and a virtual onsite loop covering practical coding (~1.5 hours), algorithmic coding, system </t>
+          <t xml:space="preserve">Glassdoor rates the interview difficulty at 2.3 out of 5 (easy), with 78% of candidates reporting a positive experience. Expect behavioral questions like “tell me about yourself,” “why Valero,” and questions about your coursework and past experiences. Multiple candidates confirm there are typically </t>
         </is>
       </c>
       <c r="H269" s="6" t="inlineStr"/>
       <c r="I269" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling and continuous, not a fixed cohort deadline. Vanta posts individual roles on Ashby and fills them as strong candidates appear. Apply the week a p</t>
+          <t>Effectively yes. Positions may be listed for as few as 3 days; recruiters contact candidates within 30 days</t>
         </is>
       </c>
       <c r="J269" s="6" t="inlineStr">
         <is>
-          <t>No official intern rate is published (NOT FOUND on Levels.fyi's single Summer 2023 data point). For context only, entry-level SWE base is about $140K to $180K (</t>
+          <t>$34.50–$41.50/hr for engineering interns (2026 JDs); overtime eligible; relocation assistance included</t>
         </is>
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>No formal intern posting is live as of August 2026. Based on the early-career calendar and Vanta's new-grad hiring, applications for summer 2027 are expected to open on Ashby around Fall 2026 (roughly Sept–Nov 2026), reviewed on a rolling basis into early 2027 (expected, not officially confirmed)</t>
+          <t>Expected fall 2026 (Sep–Nov) for summer 2027; no official 2027 dates posted yet</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>VaynerMedia</t>
+          <t>Vanta</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -15549,17 +15553,17 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – April 2027</t>
+          <t>September 2026 – February 2027</t>
         </is>
       </c>
       <c r="D270" s="6" t="inlineStr">
         <is>
-          <t>Analytics / Integrated Research &amp; Insights  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern / New Grad SWE (primary); Backend / Platform Engineering; GRC Product Engineering  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E270" s="7" t="inlineStr">
         <is>
-          <t>vaynermedia.com/careers/</t>
+          <t>jobs.ashbyhq.com/vanta</t>
         </is>
       </c>
       <c r="F270" s="7" t="inlineStr">
@@ -15569,30 +15573,30 @@
       </c>
       <c r="G270" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, then role-specific hiring-manager and team interviews. One strategist candidate reported four rounds. Expect questions about high-volume social content (the "Vayner Volume Model") and platform-native creative, and be ready for a supplemental or creative prompt rather than a forma</t>
+          <t xml:space="preserve">Three stages over roughly 3 to 5 weeks: a recruiter screen (30 to 45 minutes on background, goals, and comp), a technical screening (an online assessment or a live one-hour CoderPad coding round over Zoom), and a virtual onsite loop covering practical coding (~1.5 hours), algorithmic coding, system </t>
         </is>
       </c>
       <c r="H270" s="6" t="inlineStr"/>
       <c r="I270" s="6" t="inlineStr">
         <is>
-          <t>Partially. The cohort is a fixed summer program, but hiring runs on a rolling basis until filled (the 2018 cycle expected all interns hired by early April). App</t>
+          <t>Likely rolling and continuous, not a fixed cohort deadline. Vanta posts individual roles on Ashby and fills them as strong candidates appear. Apply the week a p</t>
         </is>
       </c>
       <c r="J270" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advertised as PAID. Community estimates (Glassdoor/Indeed) run ~$25-42/hr; the reliable range for advertising interns is closer to ~$20-35/hr. No official rate </t>
+          <t>No official intern rate is published (NOT FOUND on Levels.fyi's single Summer 2023 data point). For context only, entry-level SWE base is about $140K to $180K (</t>
         </is>
       </c>
       <c r="K270" s="6" t="inlineStr">
         <is>
-          <t>Not yet published. Projected from documented cycles: applications for summer 2027 expected to open ~fall 2026 through early 2027, with all interns hired by ~early April 2027 (expected)</t>
+          <t>No formal intern posting is live as of August 2026. Based on the early-career calendar and Vanta's new-grad hiring, applications for summer 2027 are expected to open on Ashby around Fall 2026 (roughly Sept–Nov 2026), reviewed on a rolling basis into early 2027 (expected, not officially confirmed)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>VaynerMedia</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -15602,17 +15606,17 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September 2026 – April 2027</t>
         </is>
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>1 formal track: "Engineering Summer Intern" (Software Engineer Intern). Interns are placed across teams and codebases (website monorepo, v0, support tooling) rather than into fixed named sub-tracks</t>
+          <t>Analytics / Integrated Research &amp; Insights  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr">
         <is>
-          <t>vercel.com/careers</t>
+          <t>vaynermedia.com/careers/</t>
         </is>
       </c>
       <c r="F271" s="7" t="inlineStr">
@@ -15622,30 +15626,30 @@
       </c>
       <c r="G271" s="6" t="inlineStr">
         <is>
-          <t>A practical, project/problem-based interview that mimics real work. You break down a problem and reason aloud about possible solutions, and using Google and asking clarifying questions is explicitly encouraged. It is not a LeetCode-style interview. Community reports suggest a frontend-leaning practi</t>
+          <t>A recruiter screen, then role-specific hiring-manager and team interviews. One strategist candidate reported four rounds. Expect questions about high-volume social content (the "Vayner Volume Model") and platform-native creative, and be ready for a supplemental or creative prompt rather than a forma</t>
         </is>
       </c>
       <c r="H271" s="6" t="inlineStr"/>
       <c r="I271" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated. Vercel posts a single intern req per summer cycle and the summer 2026 listing came down in late September 2025. Treat it as early-close /</t>
+          <t>Partially. The cohort is a fixed summer program, but hiring runs on a rolling basis until filled (the 2018 cycle expected all interns hired by early April). App</t>
         </is>
       </c>
       <c r="J271" s="6" t="inlineStr">
         <is>
-          <t>$9,500 to $11,000 per month (official JD). Levels.fyi community data lists $70.00/hr. Benefits: mentorship and events, Flexible Time Off plus paid holidays, rem</t>
+          <t xml:space="preserve">Advertised as PAID. Community estimates (Glassdoor/Indeed) run ~$25-42/hr; the reliable range for advertising interns is closer to ~$20-35/hr. No official rate </t>
         </is>
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>Not yet open as of August 2026. For the summer 2027 cycle, expect the intern req to appear ~summer to fall 2026 and to close by early fall. The summer 2026 listing was removed Sep 26, 2025 (expected timing)</t>
+          <t>Not yet published. Projected from documented cycles: applications for summer 2027 expected to open ~fall 2026 through early 2027, with all interns hired by ~early April 2027 (expected)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -15655,17 +15659,17 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>Global Solutions Technology; Cybersecurity / AI Risk; AI/ML Engineering; Data Science &amp; Analytics  (4 of 6 tracks)</t>
+          <t>1 formal track: "Engineering Summer Intern" (Software Engineer Intern). Interns are placed across teams and codebases (website monorepo, v0, support tooling) rather than into fixed named sub-tracks</t>
         </is>
       </c>
       <c r="E272" s="7" t="inlineStr">
         <is>
-          <t>mycareer.verizon.com/life-at-verizon/students-internships/</t>
+          <t>vercel.com/careers</t>
         </is>
       </c>
       <c r="F272" s="7" t="inlineStr">
@@ -15675,34 +15679,30 @@
       </c>
       <c r="G272" s="6" t="inlineStr">
         <is>
-          <t>After applying online, most candidates complete a Candidates Assessment on Workday (the ADEPT-15 personality test, about 25–30 minutes), followed by a self-recorded video interview with 6 behavioral questions and 2 attempts each. Strong candidates advance to a phone or virtual interview, and some ro</t>
-        </is>
-      </c>
-      <c r="H272" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No. All Verizon internship postings require "authorization to work in the U.S. without restrictions or need for future sponsorship." International students on F-1 visas may qualify through CPT or OPT work authorization, </t>
-        </is>
-      </c>
+          <t>A practical, project/problem-based interview that mimics real work. You break down a problem and reason aloud about possible solutions, and using Google and asking clarifying questions is explicitly encouraged. It is not a LeetCode-style interview. Community reports suggest a frontend-leaning practi</t>
+        </is>
+      </c>
+      <c r="H272" s="6" t="inlineStr"/>
       <c r="I272" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Postings "may close before the stated closing date"; applicants encouraged to apply as soon as possible</t>
+          <t>Not explicitly stated. Vercel posts a single intern req per summer cycle and the summer 2026 listing came down in late September 2025. Treat it as early-close /</t>
         </is>
       </c>
       <c r="J272" s="6" t="inlineStr">
         <is>
-          <t>$23–$36/hr depending on role; 401(k) match on first 6%, full benefits from day one</t>
+          <t>$9,500 to $11,000 per month (official JD). Levels.fyi community data lists $70.00/hr. Benefits: mentorship and events, Flexible Time Off plus paid holidays, rem</t>
         </is>
       </c>
       <c r="K272" s="6" t="inlineStr">
         <is>
-          <t>Expected September–November 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Not yet open as of August 2026. For the summer 2027 cycle, expect the intern req to appear ~summer to fall 2026 and to close by early fall. The summer 2026 listing was removed Sep 26, 2025 (expected timing)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>VMware</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -15712,17 +15712,17 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure Software (vSphere/VCF); Networking Software (NSX); Cloud-Native / Tanzu; Software Engineering (General)  (4 of 5 tracks)</t>
+          <t>Global Solutions Technology; Cybersecurity / AI Risk; AI/ML Engineering; Data Science &amp; Analytics  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E273" s="7" t="inlineStr">
         <is>
-          <t>broadcom.wd1.myworkdayjobs.com/External_Career</t>
+          <t>mycareer.verizon.com/life-at-verizon/students-internships/</t>
         </is>
       </c>
       <c r="F273" s="7" t="inlineStr">
@@ -15732,30 +15732,34 @@
       </c>
       <c r="G273" s="6" t="inlineStr">
         <is>
-          <t>Expect a recruiter phone screen (30 minutes), a coding assessment on HackerRank or CoderPad testing data structures and systems programming, then a virtual onsite of three to four rounds covering technical coding, systems design, behavioral fit using STAR, and a hiring manager conversation. Intervie</t>
-        </is>
-      </c>
-      <c r="H273" s="6" t="inlineStr"/>
+          <t>After applying online, most candidates complete a Candidates Assessment on Workday (the ADEPT-15 personality test, about 25–30 minutes), followed by a self-recorded video interview with 6 behavioral questions and 2 attempts each. Strong candidates advance to a phone or virtual interview, and some ro</t>
+        </is>
+      </c>
+      <c r="H273" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. All Verizon internship postings require "authorization to work in the U.S. without restrictions or need for future sponsorship." International students on F-1 visas may qualify through CPT or OPT work authorization, </t>
+        </is>
+      </c>
       <c r="I273" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Broadcom contacts candidates November to January, implying window-based rolling review</t>
+          <t>Effectively yes. Postings "may close before the stated closing date"; applicants encouraged to apply as soon as possible</t>
         </is>
       </c>
       <c r="J273" s="6" t="inlineStr">
         <is>
-          <t>$40–$55/hr estimated for SWE interns (Levels.fyi historical average ~$42/hr); $1,500–$8,500 housing stipend</t>
+          <t>$23–$36/hr depending on role; 401(k) match on first 6%, full benefits from day one</t>
         </is>
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>Expected September–October 2026 for summer 2027 (documented pattern from the 2026 cycle; not yet posted)</t>
+          <t>Expected September–November 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>VMware</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -15765,17 +15769,17 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>Technology / IT Internship  (1 of 7 tracks)</t>
+          <t>Infrastructure Software (vSphere/VCF); Networking Software (NSX); Cloud-Native / Tanzu; Software Engineering (General)  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E274" s="7" t="inlineStr">
         <is>
-          <t>jobs.walgreens.com/en/students</t>
+          <t>broadcom.wd1.myworkdayjobs.com/External_Career</t>
         </is>
       </c>
       <c r="F274" s="7" t="inlineStr">
@@ -15785,30 +15789,30 @@
       </c>
       <c r="G274" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves 2–4 rounds: an online application, possibly an online assessment or HireVue pre-recorded video interview, a phone or video screen with a recruiter, and a final interview with the hiring manager. Expect a mix of behavioral and situational questions. Glassdoor rates inte</t>
+          <t>Expect a recruiter phone screen (30 minutes), a coding assessment on HackerRank or CoderPad testing data structures and systems programming, then a virtual onsite of three to four rounds covering technical coding, systems design, behavioral fit using STAR, and a hiring manager conversation. Intervie</t>
         </is>
       </c>
       <c r="H274" s="6" t="inlineStr"/>
       <c r="I274" s="6" t="inlineStr">
         <is>
-          <t>No explicit rolling statement for corporate programs. Community pharmacy intern positions are posted and filled continuously across 50 states</t>
+          <t>Likely yes. Broadcom contacts candidates November to January, implying window-based rolling review</t>
         </is>
       </c>
       <c r="J274" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$16.50–$25.00/hr corporate; $17–$19/hr community management; $18–$31/hr pharmacy intern (Indeed avg $21.53/hr). Housing provided for corporate pharmacy interns </t>
+          <t>$40–$55/hr estimated for SWE interns (Levels.fyi historical average ~$42/hr); $1,500–$8,500 housing stipend</t>
         </is>
       </c>
       <c r="K274" s="6" t="inlineStr">
         <is>
-          <t>Expected fall 2026 for corporate and community management; community pharmacy intern roles post year-round (documented pattern; not yet posted)</t>
+          <t>Expected September–October 2026 for summer 2027 (documented pattern from the 2026 cycle; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros Discovery</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -15818,17 +15822,17 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science Intern  (2 of 6 tracks)</t>
+          <t>Technology / IT Internship  (1 of 7 tracks)</t>
         </is>
       </c>
       <c r="E275" s="7" t="inlineStr">
         <is>
-          <t>careers.wbd.com/global/en/us-internship-opportunities</t>
+          <t>jobs.walgreens.com/en/students</t>
         </is>
       </c>
       <c r="F275" s="7" t="inlineStr">
@@ -15838,34 +15842,30 @@
       </c>
       <c r="G275" s="6" t="inlineStr">
         <is>
-          <t>For tech: HireVue video (5 behavioral questions plus 20 technical MCQs), recruiter phone screen, technical Zoom interview, managerial round, and a People and Culture round. For non-tech: HireVue video (behavioral only), then one or two Zoom interviews with the hiring manager.</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>No. WBD requires current US work authorization and explicitly lists F-1 CPT, F-1 OPT, J-1, and M-1 visas as ineligible categories. This applies to all internship tracks regardless of division.</t>
-        </is>
-      </c>
+          <t>The process typically involves 2–4 rounds: an online application, possibly an online assessment or HireVue pre-recorded video interview, a phone or video screen with a recruiter, and a final interview with the hiring manager. Expect a mix of behavioral and situational questions. Glassdoor rates inte</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr"/>
       <c r="I275" s="6" t="inlineStr">
         <is>
-          <t>Yes for Tech/Games. HireVue and offers sent on a rolling basis September through December. Non-tech uses batch review with interviews February through April</t>
+          <t>No explicit rolling statement for corporate programs. Community pharmacy intern positions are posted and filled continuously across 50 states</t>
         </is>
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
-          <t>$19/hr (media/marketing undergrad) to $47/hr (software engineering). Graduate non-tech: $23–$25/hr</t>
+          <t xml:space="preserve">$16.50–$25.00/hr corporate; $17–$19/hr community management; $18–$31/hr pharmacy intern (Indeed avg $21.53/hr). Housing provided for corporate pharmacy interns </t>
         </is>
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 — Tech/Games: expected to open mid-September to end-October 2026. Non-tech/media: expected January to February 2027 (projected from prior cycle; not yet posted)</t>
+          <t>Expected fall 2026 for corporate and community management; community pharmacy intern roles post year-round (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Warner Bros Discovery</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -15875,17 +15875,17 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – February 2027</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science Intern (Operations); Machine Learning Intern  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern; Data Science Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E276" s="7" t="inlineStr">
         <is>
-          <t>wayfair.com/careers/jobs</t>
+          <t>careers.wbd.com/global/en/us-internship-opportunities</t>
         </is>
       </c>
       <c r="F276" s="7" t="inlineStr">
@@ -15895,34 +15895,34 @@
       </c>
       <c r="G276" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a HackerRank online assessment, a roughly 45-minute technical phone screen (LeetCode easy-to-medium), and a virtual onsite with technical and behavioral rounds, sometimes several back-to-back the same day. Behavioral questions follow Wayfair's three People Principles using the ST</t>
+          <t>For tech: HireVue video (5 behavioral questions plus 20 technical MCQs), recruiter phone screen, technical Zoom interview, managerial round, and a People and Culture round. For non-tech: HireVue video (behavioral only), then one or two Zoom interviews with the hiring manager.</t>
         </is>
       </c>
       <c r="H276" s="6" t="inlineStr">
         <is>
-          <t>Varies by role. The Data Science (Operations) intern JD explicitly does NOT sponsor (no STEM OPT EAD, H-1B, H-1B1, E-3, O-1, J-1, or TN). The SWE Intern JD states no sponsorship restriction. Confirm per posting</t>
+          <t>No. WBD requires current US work authorization and explicitly lists F-1 CPT, F-1 OPT, J-1, and M-1 visas as ineligible categories. This applies to all internship tracks regardless of division.</t>
         </is>
       </c>
       <c r="I276" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly. Early-talent applications are reviewed on a rolling basis with an "initial update within 3 weeks," but the flagship summer internship is a fixed, dated </t>
+          <t>Yes for Tech/Games. HireVue and offers sent on a rolling basis September through December. Non-tech uses batch review with interviews February through April</t>
         </is>
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern: $40/hour (~$6,933/month in Boston, Summer 2025, with a $600/month housing stipend on some offers). Data Science Intern: $35/hour. Full-time SWE tota</t>
+          <t>$19/hr (media/marketing undergrad) to $47/hr (software engineering). Graduate non-tech: $23–$25/hr</t>
         </is>
       </c>
       <c r="K276" s="6" t="inlineStr">
         <is>
-          <t>Not yet published. Based on the Summer 2026 cycle (posted ~Sep 17, 2025), applications for summer 2027 are expected to open ~Sep–Oct 2026 and run through late 2026 / early 2027. Exact 2027 open/close dates NOT FOUND as of August 2026. Monitor wayfair.com/careers starting Fall 2026</t>
+          <t>Applications for summer 2027 — Tech/Games: expected to open mid-September to end-October 2026. Non-tech/media: expected January to February 2027 (projected from prior cycle; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -15932,17 +15932,17 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026 – February 2027</t>
         </is>
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>Technology Undergraduate Summer Internship  (1 of 3 tracks)</t>
+          <t>Software Engineering Intern; Data Science Intern (Operations); Machine Learning Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E277" s="7" t="inlineStr">
         <is>
-          <t>wellington.wd5.myworkdayjobs.com/Campus</t>
+          <t>wayfair.com/careers/jobs</t>
         </is>
       </c>
       <c r="F277" s="7" t="inlineStr">
@@ -15952,34 +15952,34 @@
       </c>
       <c r="G277" s="6" t="inlineStr">
         <is>
-          <t>You apply on the Workday Campus Portal with a resume, Statement of Interest (2 pages), and transcript. Then a conversational phone screen, followed by multiple virtual one-to-one interviews via Microsoft Teams. Questions are primarily behavioral, focused on cultural fit, collaboration, and why Welli</t>
+          <t>A recruiter screen, a HackerRank online assessment, a roughly 45-minute technical phone screen (LeetCode easy-to-medium), and a virtual onsite with technical and behavioral rounds, sometimes several back-to-back the same day. Behavioral questions follow Wayfair's three People Principles using the ST</t>
         </is>
       </c>
       <c r="H277" s="6" t="inlineStr">
         <is>
-          <t>No visa sponsorship for undergraduate internships. Must be authorized to work in the respective country</t>
+          <t>Varies by role. The Data Science (Operations) intern JD explicitly does NOT sponsor (no STEM OPT EAD, H-1B, H-1B1, E-3, O-1, J-1, or TN). The SWE Intern JD states no sponsorship restriction. Confirm per posting</t>
         </is>
       </c>
       <c r="I277" s="6" t="inlineStr">
         <is>
-          <t>No. Firm deadline; the 2026 cycle closed October 21 at 12:00 PM ET with no rolling review</t>
+          <t xml:space="preserve">Partly. Early-talent applications are reviewed on a rolling basis with an "initial update within 3 weeks," but the flagship summer internship is a fixed, dated </t>
         </is>
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
-          <t>~$32/hr average (~$67,337 annualized). Monthly range $4,217 to $7,568. Housing stipend for out-of-area interns</t>
+          <t>SWE Intern: $40/hour (~$6,933/month in Boston, Summer 2025, with a $600/month housing stipend on some offers). Data Science Intern: $35/hour. Full-time SWE tota</t>
         </is>
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>Expected September to late October 2026 (prior cycle: September 10 to October 21, 2025). Projected from the 2026 cohort</t>
+          <t>Not yet published. Based on the Summer 2026 cycle (posted ~Sep 17, 2025), applications for summer 2027 are expected to open ~Sep–Oct 2026 and run through late 2026 / early 2027. Exact 2027 open/close dates NOT FOUND as of August 2026. Monitor wayfair.com/careers starting Fall 2026</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>Windsurf (Codeium)</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -15989,17 +15989,17 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Research Engineer Intern (projected); Applied AI Engineer Intern (projected); Product Engineer Intern (projected)</t>
+          <t>Technology Undergraduate Summer Internship  (1 of 3 tracks)</t>
         </is>
       </c>
       <c r="E278" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/cognition</t>
+          <t>wellington.wd5.myworkdayjobs.com/Campus</t>
         </is>
       </c>
       <c r="F278" s="7" t="inlineStr">
@@ -16009,34 +16009,34 @@
       </c>
       <c r="G278" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The process includes an online assessment where AI tools are allowed, two technical interviews focused on data structures and algorithms at medium to medium-hard LeetCode difficulty, and a behavioral round. Some candidates also receive a take-home project or open-source debugging round. The average </t>
+          <t>You apply on the Workday Campus Portal with a resume, Statement of Interest (2 pages), and transcript. Then a conversational phone screen, followed by multiple virtual one-to-one interviews via Microsoft Teams. Questions are primarily behavioral, focused on cultural fit, collaboration, and why Welli</t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed for interns. As a well-funded US tech company, CPT/OPT support is likely but not officially stated</t>
+          <t>No visa sponsorship for undergraduate internships. Must be authorized to work in the respective country</t>
         </is>
       </c>
       <c r="I278" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. As a startup with fewer than 300 employees pre-acquisition, the program was likely informal and rolling. Monitor the Cognition Ashby board for po</t>
+          <t>No. Firm deadline; the 2026 cycle closed October 21 at 12:00 PM ET with no rolling review</t>
         </is>
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
-          <t>$54.81/hr (~$9,500/month) in Summer 2025, per Levels.fyi. Housing and transportation tags appeared on Levels.fyi but specific stipend amounts are unconfirmed</t>
+          <t>~$32/hr average (~$67,337 annualized). Monthly range $4,217 to $7,568. Housing stipend for out-of-area interns</t>
         </is>
       </c>
       <c r="K278" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Historically, Windsurf (as Codeium) posted intern listings in fall for spring/summer terms. Expect Cognition to follow a similar pattern starting fall 2026 for summer 2027</t>
+          <t>Expected September to late October 2026 (prior cycle: September 10 to October 21, 2025). Projected from the 2026 cohort</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>WPP</t>
+          <t>Windsurf (Codeium)</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -16046,17 +16046,17 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>AKQA Design / Technology Intern  (1 of 5 tracks)</t>
+          <t>Software Engineer Intern; Research Engineer Intern (projected); Applied AI Engineer Intern (projected); Product Engineer Intern (projected)</t>
         </is>
       </c>
       <c r="E279" s="7" t="inlineStr">
         <is>
-          <t>wpp.com/careers</t>
+          <t>jobs.ashbyhq.com/cognition</t>
         </is>
       </c>
       <c r="F279" s="7" t="inlineStr">
@@ -16066,34 +16066,34 @@
       </c>
       <c r="G279" s="6" t="inlineStr">
         <is>
-          <t>Interview-driven, with no coding assessment. Expect a short (~20-minute) first interview, then team or hiring-manager rounds; some offices run an onsite with a brief-and-pitch or role-play exercise. Offers reportedly land within about a week of the final round. WPP's summer 2027 seats will be decide</t>
+          <t xml:space="preserve">The process includes an online assessment where AI tools are allowed, two technical interviews focused on data structures and algorithms at medium to medium-hard LeetCode difficulty, and a behavioral round. Some candidates also receive a take-home project or open-source debugging round. The average </t>
         </is>
       </c>
       <c r="H279" s="6" t="inlineStr">
         <is>
-          <t>Interns are generally not visa-sponsored: agencies require U.S. work authorization now and in the future. No official intern-to-full-time conversion rate is published by WPP or its agencies</t>
+          <t>Not confirmed for interns. As a well-funded US tech company, CPT/OPT support is likely but not officially stated</t>
         </is>
       </c>
       <c r="I279" s="6" t="inlineStr">
         <is>
-          <t>Partially. Ogilvy sets a fixed deadline but warns popular roles "fill up quickly" and close once filled; WPP Media posts reqs on Greenhouse and removes them whe</t>
+          <t>Not confirmed. As a startup with fewer than 300 employees pre-acquisition, the program was likely informal and rolling. Monitor the Cognition Ashby board for po</t>
         </is>
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>Paid, hourly. Ogilvy Summer 2026: $20–$25/hour; WPP Media: $20/hour. Peer benchmarks: Havas $18–$22/hr, Publicis ~$14–$21/hr (community-reported). No housing or</t>
+          <t>$54.81/hr (~$9,500/month) in Summer 2025, per Levels.fyi. Housing and transportation tags appeared on Levels.fyi but specific stipend amounts are unconfirmed</t>
         </is>
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>No 2027-cycle dates published yet (expected). Based on the Summer 2026 cycle, applications for summer 2027 are expected to open ~September–October 2026 and close in early-to-mid January 2027 (Ogilvy's Summer 2026 deadline was January 5, 2026)</t>
+          <t>Not confirmed. Historically, Windsurf (as Codeium) posted intern listings in fall for spring/summer terms. Expect Cognition to follow a similar pattern starting fall 2026 for summer 2027</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>WPP</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -16103,17 +16103,17 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>September–November 2026</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering, Agents; Software Engineering, Generative AI; Software Engineering, Connectors &amp; MCP; AI/ML Research; AI Engineering; Infrastructure/Platform Engineering</t>
+          <t>AKQA Design / Technology Intern  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/writer</t>
+          <t>wpp.com/careers</t>
         </is>
       </c>
       <c r="F280" s="7" t="inlineStr">
@@ -16123,34 +16123,34 @@
       </c>
       <c r="G280" s="6" t="inlineStr">
         <is>
-          <t>Full-time engineering interviews involve 5 rounds: recruiter screen, hiring manager screen, live coding with a real GitHub repo, peer-to-peer assessment, and a CTO round. Average difficulty is 3.1 out of 5 on Glassdoor and hiring takes about 30 days. An intern process would likely be shorter.</t>
+          <t>Interview-driven, with no coding assessment. Expect a short (~20-minute) first interview, then team or hiring-manager rounds; some offices run an onsite with a brief-and-pitch or role-play exercise. Offers reportedly land within about a week of the final round. WPP's summer 2027 seats will be decide</t>
         </is>
       </c>
       <c r="H280" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. London office suggests international hiring capability, but no policy is published</t>
+          <t>Interns are generally not visa-sponsored: agencies require U.S. work authorization now and in the future. No official intern-to-full-time conversion rate is published by WPP or its agencies</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>Unknown. Most AI startups of similar size use a hybrid approach with a fixed window and rolling review</t>
+          <t>Partially. Ogilvy sets a fixed deadline but warns popular roles "fill up quickly" and close once filled; WPP Media posts reqs on Greenhouse and removes them whe</t>
         </is>
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Full-time SWE base ranges from $111.7K–$304.1K; intern pay would differ substantially</t>
+          <t>Paid, hourly. Ogilvy Summer 2026: $20–$25/hour; WPP Media: $20/hour. Peer benchmarks: Havas $18–$22/hr, Publicis ~$14–$21/hr (community-reported). No housing or</t>
         </is>
       </c>
       <c r="K280" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. If launched, expect postings September–November 2026 for Summer 2027 (based on comparable AI startups)</t>
+          <t>No 2027-cycle dates published yet (expected). Based on the Summer 2026 cycle, applications for summer 2027 are expected to open ~September–October 2026 and close in early-to-mid January 2027 (Ogilvy's Summer 2026 deadline was January 5, 2026)</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -16165,12 +16165,12 @@
       </c>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; AI / Machine Learning; Data / Analytics  (3 of 6 tracks)</t>
+          <t>Software Engineering, Agents; Software Engineering, Generative AI; Software Engineering, Connectors &amp; MCP; AI/ML Research; AI Engineering; Infrastructure/Platform Engineering</t>
         </is>
       </c>
       <c r="E281" s="7" t="inlineStr">
         <is>
-          <t>jobs.lever.co/zoox?department=Zoox+Internships</t>
+          <t>jobs.ashbyhq.com/writer</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
@@ -16180,30 +16180,34 @@
       </c>
       <c r="G281" s="6" t="inlineStr">
         <is>
-          <t>After applying, expect an online assessment (2 LeetCode-medium questions, 90 minutes, typically Python), a recruiter phone screen, and then a technical interview loop of 2 to 3 back-to-back rounds totaling about 3 hours. Topics include coding, low-level design, and system design. A team-matching con</t>
-        </is>
-      </c>
-      <c r="H281" s="6" t="inlineStr"/>
+          <t>Full-time engineering interviews involve 5 rounds: recruiter screen, hiring manager screen, live coding with a real GitHub repo, peer-to-peer assessment, and a CTO round. Average difficulty is 3.1 out of 5 on Glassdoor and hiring takes about 30 days. An intern process would likely be shorter.</t>
+        </is>
+      </c>
+      <c r="H281" s="6" t="inlineStr">
+        <is>
+          <t>Not confirmed. London office suggests international hiring capability, but no policy is published</t>
+        </is>
+      </c>
       <c r="I281" s="6" t="inlineStr">
         <is>
-          <t>Yes (implied). Positions close when filled; Reddit confirms varied offer timelines with rolling team matching</t>
+          <t>Unknown. Most AI startups of similar size use a hybrid approach with a fixed window and rolling review</t>
         </is>
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>$40–$55/hr for SWE ($7,500–$9,500/mo) + $1,000/mo housing stipend + free meals + medical insurance</t>
+          <t>Not confirmed. Full-time SWE base ranges from $111.7K–$304.1K; intern pay would differ substantially</t>
         </is>
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>Expected September to November 2026 for summer 2027 (prior-cycle pattern; not yet posted)</t>
+          <t>Not confirmed. If launched, expect postings September–November 2026 for Summer 2027 (based on comparable AI startups)</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -16213,17 +16217,17 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September–November 2026</t>
         </is>
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer / SDE Intern (primary); AI / ML / Data Science Engineering Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering; AI / Machine Learning; Data / Analytics  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>zscaler.com/careers</t>
+          <t>jobs.lever.co/zoox?department=Zoox+Internships</t>
         </is>
       </c>
       <c r="F282" s="7" t="inlineStr">
@@ -16233,34 +16237,30 @@
       </c>
       <c r="G282" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a HackerRank online assessment (coding plus CS-fundamentals MCQs, front-end and/or back-end tracks), then a technical interview that mixes live coding with a networking deep-dive, followed by team matching and an offer. Full-time-style candidates may face a four-round onsite (DSA</t>
-        </is>
-      </c>
-      <c r="H282" s="6" t="inlineStr">
-        <is>
-          <t>NOT stated for interns) the US JD is silent on intern visa sponsorship. Confirm F-1/CPT/OPT support with the recruiter</t>
-        </is>
-      </c>
+          <t>After applying, expect an online assessment (2 LeetCode-medium questions, 90 minutes, typically Python), a recruiter phone screen, and then a technical interview loop of 2 to 3 back-to-back rounds totaling about 3 hours. Topics include coding, low-level design, and system design. A team-matching con</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr"/>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly. The US cohort is recruited seasonally (fall postings) but individual reqs fill on a rolling, first-qualified basis. India Skybound runs as a structured </t>
+          <t>Yes (implied). Positions close when filled; Reddit confirms varied offer timelines with rolling team matching</t>
         </is>
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>Official US base: $45–65/hour (bonus/equity excluded). Levels.fyi (community) shows US SWE interns ~$45–50/hr ($7,800–8,667/mo), with a $3,000 relocation report</t>
+          <t>$40–$55/hr for SWE ($7,500–$9,500/mo) + $1,000/mo housing stipend + free meals + medical insurance</t>
         </is>
       </c>
       <c r="K282" s="6" t="inlineStr">
         <is>
-          <t>Unpublished for 2027. Expected to open ~September–October 2026 and primarily close ~December 2026 (the Summer 2026 posting was removed Dec 20, 2025), with some reqs lingering into early 2027. Apply early) the posting flags "Be an Early Applicant"</t>
+          <t>Expected September to November 2026 for summer 2027 (prior-cycle pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -16270,17 +16270,17 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
+          <t>Software Engineer / SDE Intern (primary); AI / ML / Data Science Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E283" s="7" t="inlineStr">
         <is>
-          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
+          <t>zscaler.com/careers</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -16290,30 +16290,34 @@
       </c>
       <c r="G283" s="6" t="inlineStr">
         <is>
-          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
-        </is>
-      </c>
-      <c r="H283" s="6" t="inlineStr"/>
+          <t>A recruiter screen, a HackerRank online assessment (coding plus CS-fundamentals MCQs, front-end and/or back-end tracks), then a technical interview that mixes live coding with a networking deep-dive, followed by team matching and an offer. Full-time-style candidates may face a four-round onsite (DSA</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="inlineStr">
+        <is>
+          <t>NOT stated for interns) the US JD is silent on intern visa sponsorship. Confirm F-1/CPT/OPT support with the recruiter</t>
+        </is>
+      </c>
       <c r="I283" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
+          <t xml:space="preserve">Partly. The US cohort is recruited seasonally (fall postings) but individual reqs fill on a rolling, first-qualified basis. India Skybound runs as a structured </t>
         </is>
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
+          <t>Official US base: $45–65/hour (bonus/equity excluded). Levels.fyi (community) shows US SWE interns ~$45–50/hr ($7,800–8,667/mo), with a $3,000 relocation report</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
+          <t>Unpublished for 2027. Expected to open ~September–October 2026 and primarily close ~December 2026 (the Summer 2026 posting was removed Dec 20, 2025), with some reqs lingering into early 2027. Apply early) the posting flags "Be an Early Applicant"</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -16323,17 +16327,17 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>Engineering / Developer  (1 of 6 tracks)</t>
+          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
+          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
         </is>
       </c>
       <c r="F284" s="7" t="inlineStr">
@@ -16343,34 +16347,30 @@
       </c>
       <c r="G284" s="6" t="inlineStr">
         <is>
-          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
-        </is>
-      </c>
-      <c r="H284" s="6" t="inlineStr">
-        <is>
-          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
-        </is>
-      </c>
+          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
+        </is>
+      </c>
+      <c r="H284" s="6" t="inlineStr"/>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
+          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
         </is>
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
+          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
+          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -16380,17 +16380,17 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>March–September 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
+          <t>Engineering / Developer  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E285" s="7" t="inlineStr">
         <is>
-          <t>careers.l3harris.com/en/new-grads-and-interns</t>
+          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
         </is>
       </c>
       <c r="F285" s="7" t="inlineStr">
@@ -16400,34 +16400,34 @@
       </c>
       <c r="G285" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
+          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
         </is>
       </c>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
+          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
         <is>
-          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
+          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
         </is>
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
+          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
+          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>March–September 2027</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>SDE Intern; Applied Scientist Intern; Data Scientist Intern; Business Intelligence Engineer Intern; Data Engineer Intern  (5 of 6 tracks)</t>
+          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>amazon.jobs/en/teams/internships-for-students</t>
+          <t>careers.l3harris.com/en/new-grads-and-interns</t>
         </is>
       </c>
       <c r="F286" s="7" t="inlineStr">
@@ -16457,34 +16457,34 @@
       </c>
       <c r="G286" s="6" t="inlineStr">
         <is>
-          <t>You apply, take a two-hour online assessment (two coding problems, a debugging section, a Work Simulation, and a Work Styles questionnaire), then one to five virtual rounds blending behavioral questions with live coding. Then offers come within five business days.</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>Varies by role. Engineering and science commonly sponsor; the 2027 Finance and Operations JDs state they cannot</t>
+          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Roles are reviewed and filled rolling; apply within the first 1 to 2 weeks of a posting</t>
+          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
         </is>
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>SDE Seattle $110,500 to $160,000 annualized base, about $53 to $77/hr (official JD). Return-offer TC ~$178k to $185k (community, Blind)</t>
+          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
         </is>
       </c>
       <c r="K286" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 29 US intern roles live at amazon.jobs, including SDE, Finance Rotation 2027, PMT Summer 2027, Area Manager Summer 2027, and WHS Specialist. Rolling review. Projected from the prior cycle where not yet posted</t>
+          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -16494,17 +16494,17 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern; Software Engineering Intern; Electrical Engineering Intern; Cybersecurity Intern; IT / PTECH Intern  (5 of 6 tracks)</t>
+          <t>SDE Intern; Applied Scientist Intern; Data Scientist Intern; Business Intelligence Engineer Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E287" s="7" t="inlineStr">
         <is>
-          <t>jobs.baesystems.com/global/en/leap</t>
+          <t>amazon.jobs/en/teams/internships-for-students</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
@@ -16514,34 +16514,34 @@
       </c>
       <c r="G287" s="6" t="inlineStr">
         <is>
-          <t>You apply online, may complete a gamified online assessment, then a 30-minute recruiter phone screen, a non-technical behavioral interview with a hiring manager using STAR+R format, and for engineering roles a technical or in-person interview. Average time to hire is about 17 days (Glassdoor).</t>
+          <t>You apply, take a two-hour online assessment (two coding problems, a debugging section, a Work Simulation, and a Work Styles questionnaire), then one to five virtual rounds blending behavioral questions with live coding. Then offers come within five business days.</t>
         </is>
       </c>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>Very rare. The vast majority of positions require U.S. citizenship or U.S. Person status (citizen, permanent resident, refugee, or asylee). Security-clearance roles require U.S. citizenship specifically</t>
+          <t>Varies by role. Engineering and science commonly sponsor; the 2027 Finance and Operations JDs state they cannot</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
         <is>
-          <t>Yes. BAE Systems reviews applications as they arrive and fills seats on a rolling basis. Apply within the first few weeks of a posting for the best response rat</t>
+          <t>Yes, confirmed. Roles are reviewed and filled rolling; apply within the first 1 to 2 weeks of a posting</t>
         </is>
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>$20 to $37 per hour depending on role level and location. Technical Intern I (freshman-level) starts around $14 to $20/hr; senior technical interns reach $30 to</t>
+          <t>SDE Seattle $110,500 to $160,000 annualized base, about $53 to $77/hr (official JD). Return-offer TC ~$178k to $185k (community, Blind)</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027. 44 US internship-level Summer 2027 reqs posted on jobs.baesystems.com on September 3, 2026 (one more September 10), across software, systems, electrical, mechanical, RF and microelectronics engineering in New Hampshire, Iowa, New York and San Diego. No deadline is printed on the requisitions</t>
+          <t>OPEN NOW. 29 US intern roles live at amazon.jobs, including SDE, Finance Rotation 2027, PMT Summer 2027, Area Manager Summer 2027, and WHS Specialist. Rolling review. Projected from the prior cycle where not yet posted</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -16556,12 +16556,12 @@
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>InnoTech Software Engineering Intern; InnoTech Data Science &amp; Analytics Intern  (2 of 6 tracks)</t>
+          <t>Systems Engineering Intern; Software Engineering Intern; Electrical Engineering Intern; Cybersecurity Intern; IT / PTECH Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>jobs.cvshealth.com/us/en/students-internship-jobs</t>
+          <t>jobs.baesystems.com/global/en/leap</t>
         </is>
       </c>
       <c r="F288" s="7" t="inlineStr">
@@ -16571,34 +16571,34 @@
       </c>
       <c r="G288" s="6" t="inlineStr">
         <is>
-          <t>You apply through Workday, complete a HireVue on-demand video assessment with behavioral questions, then have one or two live virtual interviews with hiring managers. Some tracks include a Superday with four to five 30-minute interviews. Decisions come within one to two weeks.</t>
+          <t>You apply online, may complete a gamified online assessment, then a 30-minute recruiter phone screen, a non-technical behavioral interview with a hiring manager using STAR+R format, and for engineering roles a technical or in-person interview. Average time to hire is about 17 days (Glassdoor).</t>
         </is>
       </c>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>Limited. Select post-graduation Analytics, Data Science, and MBA roles may offer sponsorship. PharmD and niche cybersecurity roles may also qualify. Most internship tracks do not sponsor</t>
+          <t>Very rare. The vast majority of positions require U.S. citizenship or U.S. Person status (citizen, permanent resident, refugee, or asylee). Security-clearance roles require U.S. citizenship specifically</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>Yes. CVS Health reviews applications on a rolling basis. Apply in September or October for the best response rates</t>
+          <t>Yes. BAE Systems reviews applications as they arrive and fills seats on a rolling basis. Apply within the first few weeks of a posting for the best response rat</t>
         </is>
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>$20 to $55 per hour depending on track. Undergraduate corporate roles around $23 to $28/hr; graduate and software engineering roles $45 to $55/hr. Housing stipe</t>
+          <t>$20 to $37 per hour depending on role level and location. Technical Intern I (freshman-level) starts around $14 to $20/hr; senior technical interns reach $30 to</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 37 Summer 2027 reqs posted September 2 to 9, 2026 (corporate Finance, Supply Chain &amp; Logistics, General Management, plus Retail Store Management in ~30 metros). No deadline: CVS accepts applications "on an ongoing basis" (one Finance req shows an October 31, 2026 end date). Prior cycles ran to March or until filled</t>
+          <t>OPEN NOW for summer 2027. 44 US internship-level Summer 2027 reqs posted on jobs.baesystems.com on September 3, 2026 (one more September 10), across software, systems, electrical, mechanical, RF and microelectronics engineering in New Hampshire, Iowa, New York and San Diego. No deadline is printed on the requisitions</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -16613,12 +16613,12 @@
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>Wind Engineering; Gas Power Engineering; Digital Technology; Nuclear Engineering  (4 of 6 tracks)</t>
+          <t>InnoTech Software Engineering Intern; InnoTech Data Science &amp; Analytics Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr">
         <is>
-          <t>careers.gevernova.com/early-careers</t>
+          <t>jobs.cvshealth.com/us/en/students-internship-jobs</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
@@ -16628,34 +16628,34 @@
       </c>
       <c r="G289" s="6" t="inlineStr">
         <is>
-          <t>Expect 2 rounds over about 26 days total. The interview is a mix of behavioral and technical questions, though Glassdoor rates the difficulty at only 2.4 out of 5. You will likely meet with an HR representative and a team member on Zoom or Teams. Behavioral questions focus on leadership, teamwork, a</t>
+          <t>You apply through Workday, complete a HireVue on-demand video assessment with behavioral questions, then have one or two live virtual interviews with hiring managers. Some tracks include a Superday with four to five 30-minute interviews. Decisions come within one to two weeks.</t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>No. All US internship postings state applicants must have "the ability to work in the United States for an unlimited amount of time without sponsorship." This language is stricter than many other companies and likely exc</t>
+          <t>Limited. Select post-graduation Analytics, Data Science, and MBA roles may offer sponsorship. PharmD and niche cybersecurity roles may also qualify. Most internship tracks do not sponsor</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
         <is>
-          <t>Yes. Postings are "expected to remain open for at least seven days" and close once filled. Apply within two weeks of a posting going live</t>
+          <t>Yes. CVS Health reviews applications on a rolling basis. Apply in September or October for the best response rates</t>
         </is>
       </c>
       <c r="J289" s="6" t="inlineStr">
         <is>
-          <t>$21–$50/hr depending on role and year of study; housing allowance and relocation reimbursement for 50+ mile commutes</t>
+          <t>$20 to $55 per hour depending on track. Undergraduate corporate roles around $23 to $28/hr; graduate and software engineering roles $45 to $55/hr. Housing stipe</t>
         </is>
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>Open now: 44 US 2027-titled reqs (29 Summer 2027, plus Spring and Fall 2027 co-ops) posted September 4 to 11, 2026. No closing language; where an end date is printed it runs September 30 to November 13, 2026, so check each req</t>
+          <t>Open now for summer 2027: 37 Summer 2027 reqs posted September 2 to 9, 2026 (corporate Finance, Supply Chain &amp; Logistics, General Management, plus Retail Store Management in ~30 metros). No deadline: CVS accepts applications "on an ongoing basis" (one Finance req shows an October 31, 2026 end date). Prior cycles ran to March or until filled</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -16665,17 +16665,17 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>Refining Chemical Engineering; Midstream Engineering (MPLX)  (2 of 6 tracks)</t>
+          <t>Wind Engineering; Gas Power Engineering; Digital Technology; Nuclear Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>mpc.wd1.myworkdayjobs.com/MPCCareers?workerSubType=762d3bc56</t>
+          <t>careers.gevernova.com/early-careers</t>
         </is>
       </c>
       <c r="F290" s="7" t="inlineStr">
@@ -16685,34 +16685,34 @@
       </c>
       <c r="G290" s="6" t="inlineStr">
         <is>
-          <t>After applying online, you may complete aptitude and personality assessments. If shortlisted, expect a phone screen with a recruiter followed by one or two interviews with the hiring manager and team members. Questions are primarily behavioral using the STAR method, with some technical questions for</t>
+          <t>Expect 2 rounds over about 26 days total. The interview is a mix of behavioral and technical questions, though Glassdoor rates the difficulty at only 2.4 out of 5. You will likely meet with an HR representative and a team member on Zoom or Teams. Behavioral questions focus on leadership, teamwork, a</t>
         </is>
       </c>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>No. Every MPC intern and co-op posting states that candidates must be authorized to work in the US on a full-time indefinite basis without the need for employment visa sponsorship now or in the future. This means interna</t>
+          <t>No. All US internship postings state applicants must have "the ability to work in the United States for an unlimited amount of time without sponsorship." This language is stricter than many other companies and likely exc</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>Not officially, but postings warn they "may close before the stated closing date" and encourage applying "as soon as possible"</t>
+          <t>Yes. Postings are "expected to remain open for at least seven days" and close once filled. Apply within two weeks of a posting going live</t>
         </is>
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>$20 to $42/hr depending on role; engineering interns $32-$42/hr; $4,500 relocation allowance</t>
+          <t>$21–$50/hr depending on role and year of study; housing allowance and relocation reimbursement for 50+ mile commutes</t>
         </is>
       </c>
       <c r="K290" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027, Spring 2027, and Fall 2026 intern/co-op roles are live on MPC's Workday portal as of August 2026, including Finance, Accounting, and Supply Chain. Rolling review</t>
+          <t>Open now: 44 US 2027-titled reqs (29 Summer 2027, plus Spring and Fall 2027 co-ops) posted September 4 to 11, 2026. No closing language; where an end date is printed it runs September 30 to November 13, 2026, so check each req</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -16727,12 +16727,12 @@
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Community Apprenticeship (SWE); Data Scientist PhD Intern; Applied Scientist PhD Intern  (4 of 6 tracks)</t>
+          <t>Refining Chemical Engineering; Midstream Engineering (MPLX)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr">
         <is>
-          <t>careers.roblox.com/early-career</t>
+          <t>mpc.wd1.myworkdayjobs.com/MPCCareers?workerSubType=762d3bc56</t>
         </is>
       </c>
       <c r="F291" s="7" t="inlineStr">
@@ -16742,34 +16742,34 @@
       </c>
       <c r="G291" s="6" t="inlineStr">
         <is>
-          <t>Expect 2 to 4 months total. The typical flow: resume screen (1-2 weeks), OA invitation (1-3 weeks after), technical screen scheduling (1-3 weeks), virtual onsite (1-2 weeks after screen), and offer (1-2 weeks after onsite). Community reports indicate some candidates experience significant delays and</t>
+          <t>After applying online, you may complete aptitude and personality assessments. If shortlisted, expect a phone screen with a recruiter followed by one or two interviews with the hiring manager and team members. Questions are primarily behavioral using the STAR method, with some technical questions for</t>
         </is>
       </c>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>No. Roblox does not sponsor H-1B or other visas for intern positions. However, international students with existing US work authorization (F-1 CPT, OPT, or STEM OPT) are eligible. Roblox does sponsor H-1B for full-time r</t>
+          <t>No. Every MPC intern and co-op posting states that candidates must be authorized to work in the US on a full-time indefinite basis without the need for employment visa sponsorship now or in the future. This means interna</t>
         </is>
       </c>
       <c r="I291" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions fill continuously until closed; no fixed deadline published</t>
+          <t>Not officially, but postings warn they "may close before the stated closing date" and encourage applying "as soon as possible"</t>
         </is>
       </c>
       <c r="J291" s="6" t="inlineStr">
         <is>
-          <t>SWE/PM $62/hr, Research $72/hr, Design $58/hr + $10,000 housing stipend + free meals</t>
+          <t>$20 to $42/hr depending on role; engineering interns $32-$42/hr; $4,500 relocation allowance</t>
         </is>
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 OPEN NOW. Software Engineer Intern (Summer 2027) is live on careers.roblox.com as of August 2026. Rolling review, no fixed deadline</t>
+          <t>OPEN NOW. Summer 2027, Spring 2027, and Fall 2026 intern/co-op roles are live on MPC's Workday portal as of August 2026, including Finance, Accounting, and Supply Chain. Rolling review</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -16779,17 +16779,17 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical / Multi-Disciplined Engineer Intern; Systems Engineering Intern / Co-op; Digital Technology / Cyber, Finance &amp; Supply Chain</t>
+          <t>Software Engineer Intern; Community Apprenticeship (SWE); Data Scientist PhD Intern; Applied Scientist PhD Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>careers.rtx.com/global/en/campus</t>
+          <t>careers.roblox.com/early-career</t>
         </is>
       </c>
       <c r="F292" s="7" t="inlineStr">
@@ -16799,34 +16799,34 @@
       </c>
       <c r="G292" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, often a HireVue recorded video, then a behavioral hiring-manager or Zoom interview (sometimes a panel or a single director), a possible in-person step, and an offer. It is behavioral-heavy (conflict, leadership, teamwork, datasets) with no documented timed coding assessment. Turn</t>
+          <t>Expect 2 to 4 months total. The typical flow: resume screen (1-2 weeks), OA invitation (1-3 weeks after), technical screen scheduling (1-3 weeks), virtual onsite (1-2 weeks after screen), and offer (1-2 weeks after onsite). Community reports indicate some candidates experience significant delays and</t>
         </is>
       </c>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>No) US citizenship is required for nearly all US roles (ITAR-controlled defense work); software reqs are tagged "No H1B Sponsorship." A minority of roles require an active SECRET clearance on day one</t>
+          <t>No. Roblox does not sponsor H-1B or other visas for intern positions. However, international students with existing US work authorization (F-1 CPT, OPT, or STEM OPT) are eligible. Roblox does sponsor H-1B for full-time r</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Each req states the window closes "approximately 40 days from the date the notice was posted," subject to candidate flow and business need</t>
+          <t>Yes. Positions fill continuously until closed; no fixed deadline published</t>
         </is>
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>No single official hourly figure; Levels.fyi (community) shows roughly $27–43/hr by business unit, role, location, and class standing (RTX SWE interns average ~</t>
+          <t>SWE/PM $62/hr, Research $72/hr, Design $58/hr + $10,000 housing stipend + free meals</t>
         </is>
       </c>
       <c r="K292" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW, short windows. 148 US 2027-cycle intern and co-op reqs live (39 titled Summer 2027), the bulk posted September 2 to 11, 2026; half of a 30-req sample carried a Workday end date only 5 to 6 days after posting, the rest 3 to 7 weeks. There is no company-wide deadline. Apply the day a matching role appears</t>
+          <t>Applications for summer 2027 OPEN NOW. Software Engineer Intern (Summer 2027) is live on careers.roblox.com as of August 2026. Rolling review, no fixed deadline</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -16836,17 +16836,17 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>December 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Product); SWE Intern (Developer Tools); SWE Intern (Infrastructure); Data Engineer / Data Scientist Intern  (4 of 5 tracks)</t>
+          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical / Multi-Disciplined Engineer Intern; Systems Engineering Intern / Co-op; Digital Technology / Cyber, Finance &amp; Supply Chain</t>
         </is>
       </c>
       <c r="E293" s="7" t="inlineStr">
         <is>
-          <t>figma.com/careers/</t>
+          <t>careers.rtx.com/global/en/campus</t>
         </is>
       </c>
       <c r="F293" s="7" t="inlineStr">
@@ -16856,34 +16856,34 @@
       </c>
       <c r="G293" s="6" t="inlineStr">
         <is>
-          <t>Figma's interview process spans 3 to 5 weeks with 4 to 6 rounds: a recruiter screen, a Byteboard technical assessment, a hiring manager interview, and a multi-session virtual onsite covering applied coding, system design, behavioral questions, and project deep-dives. For Product Design interns, a Ja</t>
+          <t>A recruiter screen, often a HireVue recorded video, then a behavioral hiring-manager or Zoom interview (sometimes a panel or a single director), a possible in-person step, and an offer. It is behavioral-heavy (conflict, leadership, teamwork, datasets) with no documented timed coding assessment. Turn</t>
         </is>
       </c>
       <c r="H293" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated in job descriptions. Figma is an equal opportunity employer with global offices in 12+ cities</t>
+          <t>No) US citizenship is required for nearly all US roles (ITAR-controlled defense work); software reqs are tagged "No H1B Sponsorship." A minority of roles require an active SECRET clearance on day one</t>
         </is>
       </c>
       <c r="I293" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling with batch review. The SWE Intern (2026) listing was live Aug 29, 2025 to Jan 29, 2026, closing once filled</t>
+          <t>Yes, confirmed. Each req states the window closes "approximately 40 days from the date the notice was posted," subject to candidate flow and business need</t>
         </is>
       </c>
       <c r="J293" s="6" t="inlineStr">
         <is>
-          <t>SWE intern NYC $60/hr ($10,400/mo), SF $51.06/hr ($8,850/mo). Plus $2,000/mo housing stipend, meals, travel reimbursement</t>
+          <t>No single official hourly figure; Levels.fyi (community) shows roughly $27–43/hr by business unit, role, location, and class standing (RTX SWE interns average ~</t>
         </is>
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Software Engineer Intern (Winter 2027) is live at figma.com/careers. Rolling; rolling review through early 2027. Projected from 2025–26 cycle, not yet posted</t>
+          <t>OPEN NOW, short windows. 148 US 2027-cycle intern and co-op reqs live (39 titled Summer 2027), the bulk posted September 2 to 11, 2026; half of a 30-req sample carried a Workday end date only 5 to 6 days after posting, the rest 3 to 7 weeks. There is no company-wide deadline. Apply the day a matching role appears</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -16898,12 +16898,12 @@
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
+          <t>SWE Intern (Product); SWE Intern (Developer Tools); SWE Intern (Infrastructure); Data Engineer / Data Scientist Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E294" s="7" t="inlineStr">
         <is>
-          <t>pepsicojobs.com/internshipsprograms</t>
+          <t>figma.com/careers/</t>
         </is>
       </c>
       <c r="F294" s="7" t="inlineStr">
@@ -16913,30 +16913,34 @@
       </c>
       <c r="G294" s="6" t="inlineStr">
         <is>
-          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
-        </is>
-      </c>
-      <c r="H294" s="6" t="inlineStr"/>
+          <t>Figma's interview process spans 3 to 5 weeks with 4 to 6 rounds: a recruiter screen, a Byteboard technical assessment, a hiring manager interview, and a multi-session virtual onsite covering applied coding, system design, behavioral questions, and project deep-dives. For Product Design interns, a Ja</t>
+        </is>
+      </c>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated in job descriptions. Figma is an equal opportunity employer with global offices in 12+ cities</t>
+        </is>
+      </c>
       <c r="I294" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
+          <t>Likely rolling with batch review. The SWE Intern (2026) listing was live Aug 29, 2025 to Jan 29, 2026, closing once filled</t>
         </is>
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
-          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
+          <t>SWE intern NYC $60/hr ($10,400/mo), SF $51.06/hr ($8,850/mo). Plus $2,000/mo housing stipend, meals, travel reimbursement</t>
         </is>
       </c>
       <c r="K294" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
+          <t>OPEN NOW. Software Engineer Intern (Winter 2027) is live at figma.com/careers. Rolling; rolling review through early 2027. Projected from 2025–26 cycle, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -16946,17 +16950,17 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>December 2027</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
+          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E295" s="7" t="inlineStr">
         <is>
-          <t>search.jobs.barclays/internships</t>
+          <t>pepsicojobs.com/internshipsprograms</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
@@ -16966,54 +16970,50 @@
       </c>
       <c r="G295" s="6" t="inlineStr">
         <is>
-          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
-        </is>
-      </c>
-      <c r="H295" s="6" t="inlineStr">
-        <is>
-          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
-        </is>
-      </c>
+          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
+        </is>
+      </c>
+      <c r="H295" s="6" t="inlineStr"/>
       <c r="I295" s="6" t="inlineStr">
         <is>
-          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
+          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
         </is>
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
+          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
         </is>
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Quantitative Finance Associate Summer Internship Program 2027 (New York) is live on Workday. Most other Summer 2027 postings are international or off-cycle. Rolling review. Confirm on the official careers portal</t>
+          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Addepar</t>
-        </is>
-      </c>
-      <c r="B296" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Window open - check now</t>
         </is>
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern - Platform Services; SWE Intern - Research; SWE Intern - ADM (Automated Data Management); SWE Intern - Core Applications  (4 of 6 tracks)</t>
+          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
         <is>
-          <t>addepar.com/careers</t>
+          <t>search.jobs.barclays/internships</t>
         </is>
       </c>
       <c r="F296" s="7" t="inlineStr">
@@ -17023,34 +17023,34 @@
       </c>
       <c r="G296" s="6" t="inlineStr">
         <is>
-          <t>Candidates report 4 to 7 rounds: a recruiter screen, hiring manager call, 1 to 2 live coding interviews with domain-specific problems (portfolio reconciliation, transaction processing), and a behavioral round. Glassdoor rates the difficulty at 3 out of 5, with an average time to offer of approximate</t>
+          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
         </is>
       </c>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>Must be enrolled at a US or Canadian institution. Specific visa sponsorship details not confirmed in job postings</t>
+          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No published deadlines; job postings remain open until filled. Community data shows candidates hearing back at varying timelines</t>
+          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
         </is>
       </c>
       <c r="J296" s="6" t="inlineStr">
         <is>
-          <t>$51/hr (~$8,840/month) for US-based roles in 2025 (Levels.fyi). JD range: $34 to $53/hr depending on state. Historical rates: $43 to $60/hr (2021 to 2023)</t>
+          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
         </is>
       </c>
       <c r="K296" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles, with rolling review through January to February 2027. Projected from 2022 to 2025 cycles</t>
+          <t>OPEN NOW. Quantitative Finance Associate Summer Internship Program 2027 (New York) is live on Workday. Most other Summer 2027 postings are international or off-cycle. Rolling review. Confirm on the official careers portal</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Addepar</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
@@ -17065,12 +17065,12 @@
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>Perception SWE Intern (primary autonomy track); Machine Learning / ML Data Engine Intern; Motion Planning SWE Intern; Maps / General SWE Intern  (4 of 5 tracks)</t>
+          <t>SWE Intern - Platform Services; SWE Intern - Research; SWE Intern - ADM (Automated Data Management); SWE Intern - Core Applications  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E297" s="7" t="inlineStr">
         <is>
-          <t>aurora.tech/careers</t>
+          <t>addepar.com/careers</t>
         </is>
       </c>
       <c r="F297" s="7" t="inlineStr">
@@ -17080,34 +17080,34 @@
       </c>
       <c r="G297" s="6" t="inlineStr">
         <is>
-          <t>Community-reported (not officially published): a recruiter screen (~20–30 min), a hiring-manager behavioral round (~30 min), a ~60-minute technical/coding round covering LeetCode medium-to-hard plus some system design and role-specific depth, and an onsite loop of about 2 to 2.5 hours across three i</t>
+          <t>Candidates report 4 to 7 rounds: a recruiter screen, hiring manager call, 1 to 2 live coding interviews with domain-specific problems (portfolio reconciliation, transaction processing), and a behavioral round. Glassdoor rates the difficulty at 3 out of 5, with an average time to offer of approximate</t>
         </is>
       </c>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>No J-1 visa sponsorship for interns. You must already be authorized to work in the US for the full internship (e.g., F-1 CPT/OPT)</t>
+          <t>Must be enrolled at a US or Canadian institution. Specific visa sponsorship details not confirmed in job postings</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Likely rolling within each cycle. Aurora reviews applications on an ongoing basis once postings go live, with no single published hard deadline, so apply early </t>
+          <t>Likely yes. No published deadlines; job postings remain open until filled. Community data shows candidates hearing back at varying timelines</t>
         </is>
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>Official 2025 intern JD rates: $47/hr (undergrad), $52/hr (master's), $58/hr (PhD), roughly $8,100/month for undergrads at 40 hrs/week. One JD variant lists $51</t>
+          <t>$51/hr (~$8,840/month) for US-based roles in 2025 (Levels.fyi). JD range: $34 to $53/hr depending on state. Historical rates: $43 to $60/hr (2021 to 2023)</t>
         </is>
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>Not yet published. Based on the prior cycle (the summer 2025 posting went live Oct 31, 2024), applications for summer 2027 are expected to open ~October–November 2026 and run through winter/early 2027</t>
+          <t>Expected October to December 2026 for summer 2027 roles, with rolling review through January to February 2027. Projected from 2022 to 2025 cycles</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B298" s="8" t="inlineStr">
@@ -17117,17 +17117,17 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
-          <t>Engineering (Mechanical / Electrical); Software / IT; Data &amp; Analytics  (3 of 6 tracks)</t>
+          <t>Perception SWE Intern (primary autonomy track); Machine Learning / ML Data Engine Intern; Motion Planning SWE Intern; Maps / General SWE Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E298" s="7" t="inlineStr">
         <is>
-          <t>bosch.us/careers/start-your-career/students/</t>
+          <t>aurora.tech/careers</t>
         </is>
       </c>
       <c r="F298" s="7" t="inlineStr">
@@ -17137,34 +17137,34 @@
       </c>
       <c r="G298" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves two to three rounds: an initial HR phone screen confirming your background and motivation, followed by a technical or behavioral interview with the hiring manager discussing your projects and problem-solving approach. Glassdoor rates the difficulty at 2.6 out of 5, and</t>
+          <t>Community-reported (not officially published): a recruiter screen (~20–30 min), a hiring-manager behavioral round (~30 min), a ~60-minute technical/coding round covering LeetCode medium-to-hard plus some system design and role-specific depth, and an onsite loop of about 2 to 2.5 hours across three i</t>
         </is>
       </c>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>Bosch US internship postings require "indefinite U.S. work authorized individuals only" and state that future sponsorship for work authorization is unavailable. International students may qualify if they have independent</t>
+          <t>No J-1 visa sponsorship for interns. You must already be authorized to work in the US for the full internship (e.g., F-1 CPT/OPT)</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">
         <is>
-          <t>Yes. Rolling review begins as soon as postings go live; some positions closed as early as January in the previous cycle</t>
+          <t xml:space="preserve">Likely rolling within each cycle. Aurora reviews applications on an ongoing basis once postings go live, with no single published hard deadline, so apply early </t>
         </is>
       </c>
       <c r="J298" s="6" t="inlineStr">
         <is>
-          <t>$22–$30/hr for engineering and software interns; Indeed average $26.03/hr for engineering</t>
+          <t>Official 2025 intern JD rates: $47/hr (undergrad), $52/hr (master's), $58/hr (PhD), roughly $8,100/month for undergrads at 40 hrs/week. One JD variant lists $51</t>
         </is>
       </c>
       <c r="K298" s="6" t="inlineStr">
         <is>
-          <t>In progress: 6 Spring 2027 co-ops (Charleston SC, posted August 2026) and 6 Summer 2027 interns (HydraForce/Bosch Rexroth, Lincolnshire IL, posted September 9, 2026) live now; main Bosch NA summer 2027 engineering wave expected October–November 2026; rolling review, positions close as filled</t>
+          <t>Not yet published. Based on the prior cycle (the summer 2025 posting went live Oct 31, 2024), applications for summer 2027 are expected to open ~October–November 2026 and run through winter/early 2027</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
@@ -17174,17 +17174,17 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern, Core Banking; SWE Intern, Design Systems; SWE Intern, Growth/Referrals; SWE Intern, FinPlat; AI Automation Intern; Data Science Intern</t>
+          <t>Engineering (Mechanical / Electrical); Software / IT; Data &amp; Analytics  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E299" s="7" t="inlineStr">
         <is>
-          <t>careers.chime.com/early-talent/</t>
+          <t>bosch.us/careers/start-your-career/students/</t>
         </is>
       </c>
       <c r="F299" s="7" t="inlineStr">
@@ -17194,34 +17194,34 @@
       </c>
       <c r="G299" s="6" t="inlineStr">
         <is>
-          <t>Chime's interview has 3 to 4 rounds: a technical phone screen with algorithms and data structures at easy-to-medium LeetCode difficulty, a deeper coding round, a system design round focused on transaction processing or fraud detection, and a behavioral round emphasizing mission alignment with financ</t>
+          <t>The process typically involves two to three rounds: an initial HR phone screen confirming your background and motivation, followed by a technical or behavioral interview with the hiring manager discussing your projects and problem-solving approach. Glassdoor rates the difficulty at 2.6 out of 5, and</t>
         </is>
       </c>
       <c r="H299" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. OPT/STEM OPT for full-time conversion. H-1B handled case-by-case for exceptional full-time hires</t>
+          <t>Bosch US internship postings require "indefinite U.S. work authorized individuals only" and state that future sponsorship for work authorization is unavailable. International students may qualify if they have independent</t>
         </is>
       </c>
       <c r="I299" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Roles are posted October to November and filled rolling; apply before January for broadest team placement options</t>
+          <t>Yes. Rolling review begins as soon as postings go live; some positions closed as early as January in the previous cycle</t>
         </is>
       </c>
       <c r="J299" s="6" t="inlineStr">
         <is>
-          <t>SWE intern $50/hr (~$8,667/month) plus ~$3,000 housing stipend for relocators. Data science intern $42–$52/hr</t>
+          <t>$22–$30/hr for engineering and software interns; Indeed average $26.03/hr for engineering</t>
         </is>
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>Expected October 2026 for Summer 2027; October 2027 for Summer 2028. Projected from prior cycles, not yet posted</t>
+          <t>In progress: 6 Spring 2027 co-ops (Charleston SC, posted August 2026) and 6 Summer 2027 interns (HydraForce/Bosch Rexroth, Lincolnshire IL, posted September 9, 2026) live now; main Bosch NA summer 2027 engineering wave expected October–November 2026; rolling review, positions close as filled</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B300" s="8" t="inlineStr">
@@ -17236,12 +17236,12 @@
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Undergrad); SWE Intern (Graduate); Data &amp; Tech Ops Intern  (3 of 6 tracks)</t>
+          <t>SWE Intern, Core Banking; SWE Intern, Design Systems; SWE Intern, Growth/Referrals; SWE Intern, FinPlat; AI Automation Intern; Data Science Intern</t>
         </is>
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>cloudflare.com/careers/jobs/</t>
+          <t>careers.chime.com/early-talent/</t>
         </is>
       </c>
       <c r="F300" s="7" t="inlineStr">
@@ -17251,34 +17251,34 @@
       </c>
       <c r="G300" s="6" t="inlineStr">
         <is>
-          <t>You apply, optionally fast-track with an AI project on Cloudflare, take a HackerRank OA (2 to 3 medium problems, 60 to 90 minutes), then a recruiter screen and 2 to 3 technical interviews via video call. Decisions come within 1 to 2 weeks of the final round.</t>
+          <t>Chime's interview has 3 to 4 rounds: a technical phone screen with algorithms and data structures at easy-to-medium LeetCode difficulty, a deeper coding round, a system design round focused on transaction processing or fraud detection, and a behavioral round emphasizing mission alignment with financ</t>
         </is>
       </c>
       <c r="H300" s="6" t="inlineStr">
         <is>
-          <t>F-1 students supported via CPT in the US. International candidates welcome at London, Lisbon, and Bengaluru hubs</t>
+          <t>CPT supported for F-1 students. OPT/STEM OPT for full-time conversion. H-1B handled case-by-case for exceptional full-time hires</t>
         </is>
       </c>
       <c r="I300" s="6" t="inlineStr">
         <is>
-          <t>Yes, reviewed in batches. Early applicants have an advantage as positions fill on a rolling basis</t>
+          <t>Yes, confirmed. Roles are posted October to November and filled rolling; apply before January for broadest team placement options</t>
         </is>
       </c>
       <c r="J300" s="6" t="inlineStr">
         <is>
-          <t>US engineering interns: $45–53/hr ($7,800–9,200/mo) plus housing and relocation stipends</t>
+          <t>SWE intern $50/hr (~$8,667/month) plus ~$3,000 housing stipend for relocators. Data science intern $42–$52/hr</t>
         </is>
       </c>
       <c r="K300" s="6" t="inlineStr">
         <is>
-          <t>Expected mid-October 2026 for summer 2027. Priority window: October through early November. Practical deadline: late January to early February 2027</t>
+          <t>Expected October 2026 for Summer 2027; October 2027 for Summer 2028. Projected from prior cycles, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
@@ -17288,17 +17288,17 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>Agent Software Engineer Intern; Agent Software Engineer – New Grad (adjacent pipeline)  (2 of 3 tracks)</t>
+          <t>SWE Intern (Undergrad); SWE Intern (Graduate); Data &amp; Tech Ops Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E301" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/decagon</t>
+          <t>cloudflare.com/careers/jobs/</t>
         </is>
       </c>
       <c r="F301" s="7" t="inlineStr">
@@ -17308,34 +17308,34 @@
       </c>
       <c r="G301" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a 45- to 60-minute technical phone screen in TypeScript or Python, then a full-day on-site with coding pair, system design, project deep dive, and behavioral rounds. The entire process averages 13 days. Expect AI-agent-specific system design questions.</t>
+          <t>You apply, optionally fast-track with an AI project on Cloudflare, take a HackerRank OA (2 to 3 medium problems, 60 to 90 minutes), then a recruiter screen and 2 to 3 technical interviews via video call. Decisions come within 1 to 2 weeks of the final round.</t>
         </is>
       </c>
       <c r="H301" s="6" t="inlineStr">
         <is>
-          <t>Full-time H-1B confirmed (11 LCAs in FY2026). Intern CPT/OPT not explicitly confirmed; likely supported given the University department classification</t>
+          <t>F-1 students supported via CPT in the US. International candidates welcome at London, Lisbon, and Bengaluru hubs</t>
         </is>
       </c>
       <c r="I301" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Likely yes. The Summer 2026 listing remained open for several months. Glassdoor reports a 13-day average hiring process, suggesting quick turnaround consistent </t>
+          <t>Yes, reviewed in batches. Early applicants have an advantage as positions fill on a rolling basis</t>
         </is>
       </c>
       <c r="J301" s="6" t="inlineStr">
         <is>
-          <t>$2,400/week (~$60/hr) plus a $10,000 housing stipend for the internship. Free daily meals, medical/dental/vision, commuter benefits</t>
+          <t>US engineering interns: $45–53/hr ($7,800–9,200/mo) plus housing and relocation stipends</t>
         </is>
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>Expected October to November 2026 for Summer 2027, based on Summer 2026 posting cadence. Likely rolling</t>
+          <t>Expected mid-October 2026 for summer 2027. Priority window: October through early November. Practical deadline: late January to early February 2027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="B302" s="8" t="inlineStr">
@@ -17345,17 +17345,17 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern - Perks; SWE Intern - Data Products; SWE Intern - Native Framework &amp; Tools; SWE Intern - Platform Ecosystems; ML Platform Intern  (5 of 6 tracks)</t>
+          <t>Agent Software Engineer Intern; Agent Software Engineer – New Grad (adjacent pipeline)  (2 of 3 tracks)</t>
         </is>
       </c>
       <c r="E302" s="7" t="inlineStr">
         <is>
-          <t>discord.com/careers</t>
+          <t>jobs.ashbyhq.com/decagon</t>
         </is>
       </c>
       <c r="F302" s="7" t="inlineStr">
@@ -17365,34 +17365,34 @@
       </c>
       <c r="G302" s="6" t="inlineStr">
         <is>
-          <t>Recruiter screen (about 30 minutes), then a 1-hour coding interview with a practical, real-world problem. You can use Google, Stack Overflow, and documentation. No automated OA. Interns likely face 2 to 3 rounds total, completed in roughly 2 to 4 weeks.</t>
+          <t>A recruiter screen, a 45- to 60-minute technical phone screen in TypeScript or Python, then a full-day on-site with coding pair, system design, project deep dive, and behavioral rounds. The entire process averages 13 days. Expect AI-agent-specific system design questions.</t>
         </is>
       </c>
       <c r="H302" s="6" t="inlineStr">
         <is>
-          <t>Discord sponsors O-1, TN, E-3, H-1B1, H-1B and Green Card for full-time employees. Intern-specific visa sponsorship is not explicitly stated; confirm per role</t>
+          <t>Full-time H-1B confirmed (11 LCAs in FY2026). Intern CPT/OPT not explicitly confirmed; likely supported given the University department classification</t>
         </is>
       </c>
       <c r="I302" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No hard deadline language in any JD; postings stay open until filled. Discord states they respond within two weeks of applying</t>
+          <t xml:space="preserve">Likely yes. The Summer 2026 listing remained open for several months. Glassdoor reports a 13-day average hiring process, suggesting quick turnaround consistent </t>
         </is>
       </c>
       <c r="J302" s="6" t="inlineStr">
         <is>
-          <t>SWE intern (Bachelor's) $63/hr (~$10,920/mo); Master's $73/hr; PhD $83/hr. Creative intern $59/hr. Housing and transportation benefits included</t>
+          <t>$2,400/week (~$60/hr) plus a $10,000 housing stipend for the internship. Free daily meals, medical/dental/vision, commuter benefits</t>
         </is>
       </c>
       <c r="K302" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027. Projected from the past two cycles (Nov 2023 for Summer 2024, late 2024 for Summer 2025); not yet posted</t>
+          <t>Expected October to November 2026 for Summer 2027, based on Summer 2026 posting cadence. Likely rolling</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>Fireworks AI</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
@@ -17402,17 +17402,17 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>0 confirmed intern tracks. 6 potential tracks inferred from full-time team structure: AI Training Infrastructure, Cloud Infrastructure, Performance Optimization, ML Research, Full Stack/Platform, Applied ML</t>
+          <t>SWE Intern - Perks; SWE Intern - Data Products; SWE Intern - Native Framework &amp; Tools; SWE Intern - Platform Ecosystems; ML Platform Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E303" s="7" t="inlineStr">
         <is>
-          <t>fireworks.ai/careers</t>
+          <t>discord.com/careers</t>
         </is>
       </c>
       <c r="F303" s="7" t="inlineStr">
@@ -17422,34 +17422,34 @@
       </c>
       <c r="G303" s="6" t="inlineStr">
         <is>
-          <t>No intern interview process exists. The following is the full-time engineering process, which would likely serve as the template for any future intern loop: 1. Monitor fireworks.ai/careers and Greenhouse ATS . Check weekly starting fall 2026. Also monitor the Sequoia Jobs portal . If no intern roles</t>
+          <t>Recruiter screen (about 30 minutes), then a 1-hour coding interview with a practical, real-world problem. You can use Google, Stack Overflow, and documentation. No automated OA. Interns likely face 2 to 3 rounds total, completed in roughly 2 to 4 weeks.</t>
         </is>
       </c>
       <c r="H303" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsored for full-time roles (19 LCAs filed in 2025, 7 in 2026, median salary $220K). Listed among startups sponsoring H-1B for CS new graduates</t>
+          <t>Discord sponsors O-1, TN, E-3, H-1B1, H-1B and Green Card for full-time employees. Intern-specific visa sponsorship is not explicitly stated; confirm per role</t>
         </is>
       </c>
       <c r="I303" s="6" t="inlineStr">
         <is>
-          <t>Not applicable yet. Full-time roles hire on a continuous/rolling basis through Greenhouse. A future intern program would likely follow the same model</t>
+          <t>Likely yes. No hard deadline language in any JD; postings stay open until filled. Discord states they respond within two weeks of applying</t>
         </is>
       </c>
       <c r="J303" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No intern salary data exists. Estimated $55 to $75 per hour ($9,200 to $12,500/month) based on comparable AI infrastructure startups and Fireworks AI full-time </t>
+          <t>SWE intern (Bachelor's) $63/hr (~$10,920/mo); Master's $73/hr; PhD $83/hr. Creative intern $59/hr. Housing and transportation benefits included</t>
         </is>
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>No confirmed timeline. If an intern program launches, postings would likely appear October 2026 to February 2027 (estimated from industry norms)</t>
+          <t>Expected October to December 2026 for summer 2027. Projected from the past two cycles (Nov 2023 for Summer 2024, late 2024 for Summer 2025); not yet posted</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>Groq</t>
+          <t>Fireworks AI</t>
         </is>
       </c>
       <c r="B304" s="8" t="inlineStr">
@@ -17459,17 +17459,17 @@
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering, Distributed Systems Intern; Software Engineer, Model Evaluation Systems Intern; Compound AI Engineering Intern; AI Application Engineering Intern  (4 of 5 tracks)</t>
+          <t>0 confirmed intern tracks. 6 potential tracks inferred from full-time team structure: AI Training Infrastructure, Cloud Infrastructure, Performance Optimization, ML Research, Full Stack/Platform, Applied ML</t>
         </is>
       </c>
       <c r="E304" s="7" t="inlineStr">
         <is>
-          <t>groq.com/careers-at-groq</t>
+          <t>fireworks.ai/careers</t>
         </is>
       </c>
       <c r="F304" s="7" t="inlineStr">
@@ -17479,34 +17479,34 @@
       </c>
       <c r="G304" s="6" t="inlineStr">
         <is>
-          <t>Groq's interview process was deliberately different from the industry standard, emphasizing project work and practical skill over algorithmic puzzles: 1. Find open roles at groq.com/careers-at-groq or jobs.gem.com/groq . If no internship roles are posted, you can share your resume on the gem.com por</t>
+          <t>No intern interview process exists. The following is the full-time engineering process, which would likely serve as the template for any future intern loop: 1. Monitor fireworks.ai/careers and Greenhouse ATS . Check weekly starting fall 2026. Also monitor the Sequoia Jobs portal . If no intern roles</t>
         </is>
       </c>
       <c r="H304" s="6" t="inlineStr">
         <is>
-          <t>Must be authorized to work in the US or Canada. Interns typically use CPT or co-op authorization. Groq has filed 11 H-1B petitions historically for full-time roles. No explicit intern visa sponsorship statement</t>
+          <t>H-1B sponsored for full-time roles (19 LCAs filed in 2025, 7 in 2026, median salary $220K). Listed among startups sponsoring H-1B for CS new graduates</t>
         </is>
       </c>
       <c r="I304" s="6" t="inlineStr">
         <is>
-          <t>Yes, historically. Groq did not publish fixed deadlines. Positions filled on a rolling basis once postings opened</t>
+          <t>Not applicable yet. Full-time roles hire on a continuous/rolling basis through Greenhouse. A future intern program would likely follow the same model</t>
         </is>
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$30 to $50 per hour for US technical internships. Glassdoor reports an average of $52 per hour (range $40 to $69). Housing and transportation support provided. </t>
+          <t xml:space="preserve">No intern salary data exists. Estimated $55 to $75 per hour ($9,200 to $12,500/month) based on comparable AI infrastructure startups and Fireworks AI full-time </t>
         </is>
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>Historically October to November for Summer roles. Confidence is low given the Nvidia deal. Monitor both Groq and Nvidia portals starting fall 2026</t>
+          <t>No confirmed timeline. If an intern program launches, postings would likely appear October 2026 to February 2027 (estimated from industry norms)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>Ideogram</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
@@ -17516,17 +17516,17 @@
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; ML Data Infrastructure Intern (projected); Applied AI Intern (projected); Research Engineer Intern (projected)</t>
+          <t>Software Engineering, Distributed Systems Intern; Software Engineer, Model Evaluation Systems Intern; Compound AI Engineering Intern; AI Application Engineering Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E305" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/ideogram</t>
+          <t>groq.com/careers-at-groq</t>
         </is>
       </c>
       <c r="F305" s="7" t="inlineStr">
@@ -17536,34 +17536,34 @@
       </c>
       <c r="G305" s="6" t="inlineStr">
         <is>
-          <t>Four stages: HR screen, a technical interview on ML fundamentals (attention mechanisms, diffusion models, backpropagation derivations), a coding round, and an on-site day in Toronto concluding with a meeting with CEO Mohammad Norouzi. The full process takes approximately 2 weeks.</t>
+          <t>Groq's interview process was deliberately different from the industry standard, emphasizing project work and practical skill over algorithmic puzzles: 1. Find open roles at groq.com/careers-at-groq or jobs.gem.com/groq . If no internship roles are posted, you can share your resume on the gem.com por</t>
         </is>
       </c>
       <c r="H305" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Canadian study-permit holders can obtain co-op work permits. US-based applicants need existing work authorization or CPT/OPT</t>
+          <t>Must be authorized to work in the US or Canada. Interns typically use CPT or co-op authorization. Groq has filed 11 H-1B petitions historically for full-time roles. No explicit intern visa sponsorship statement</t>
         </is>
       </c>
       <c r="I305" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes, ad hoc. The Summer 2026 ML Research Intern listing was open approximately 268 days (October 2025 to July 2026). Postings appear based on team needs rather </t>
+          <t>Yes, historically. Groq did not publish fixed deadlines. Positions filled on a rolling basis once postings opened</t>
         </is>
       </c>
       <c r="J305" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed. Estimated $6,000 to $10,000 CAD/month (Toronto) or $8,000 to $12,000 USD/month (NYC) based on comparable AI startups. Equity component n</t>
+          <t xml:space="preserve">$30 to $50 per hour for US technical internships. Glassdoor reports an average of $52 per hour (range $40 to $69). Housing and transportation support provided. </t>
         </is>
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>Expected Q4 2026 (October to December 2026) for summer 2027 roles. Projected from the Summer 2026 cycle, where the listing appeared in October 2025</t>
+          <t>Historically October to November for Summer roles. Confidence is low given the Nvidia deal. Monitor both Groq and Nvidia portals starting fall 2026</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Inflection AI</t>
+          <t>Ideogram</t>
         </is>
       </c>
       <c r="B306" s="8" t="inlineStr">
@@ -17578,12 +17578,12 @@
       </c>
       <c r="D306" s="6" t="inlineStr">
         <is>
-          <t>ML Engineering Intern; Data Science Intern; Voice AI Intern; AI Systems Intern  (4 of 5 tracks)</t>
+          <t>ML Research Intern; ML Data Infrastructure Intern (projected); Applied AI Intern (projected); Research Engineer Intern (projected)</t>
         </is>
       </c>
       <c r="E306" s="7" t="inlineStr">
         <is>
-          <t>inflection.ai/about</t>
+          <t>jobs.ashbyhq.com/ideogram</t>
         </is>
       </c>
       <c r="F306" s="7" t="inlineStr">
@@ -17593,34 +17593,34 @@
       </c>
       <c r="G306" s="6" t="inlineStr">
         <is>
-          <t>Three stages, all virtual: a 30-minute recruiter conversation, 90 minutes of technical interviews covering coding, ML domain questions, and systems design, and a 30-minute mentor or team conversation. The full process takes about three weeks, with decisions typically within one week of the final rou</t>
+          <t>Four stages: HR screen, a technical interview on ML fundamentals (attention mechanisms, diffusion models, backpropagation derivations), a coding round, and an on-site day in Toronto concluding with a meeting with CEO Mohammad Norouzi. The full process takes approximately 2 weeks.</t>
         </is>
       </c>
       <c r="H306" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed for interns. Inflection AI has filed a small number of H-1B petitions for full-time roles; CPT would typically apply for enrolled international students</t>
+          <t>Not confirmed. Canadian study-permit holders can obtain co-op work permits. US-based applicants need existing work authorization or CPT/OPT</t>
         </is>
       </c>
       <c r="I306" s="6" t="inlineStr">
         <is>
-          <t>Not officially confirmed, but positions fill quickly, suggesting first-come review. Apply as soon as listings appear</t>
+          <t xml:space="preserve">Yes, ad hoc. The Summer 2026 ML Research Intern listing was open approximately 268 days (October 2025 to July 2026). Postings appear based on team needs rather </t>
         </is>
       </c>
       <c r="J306" s="6" t="inlineStr">
         <is>
-          <t>Technical: $50 to $65/hr ($8,700 to $11,300/month). Nontechnical: $25 to $40/hr. Rate scales with education level and experience. Housing stipend not confirmed</t>
+          <t>Not publicly disclosed. Estimated $6,000 to $10,000 CAD/month (Toronto) or $8,000 to $12,000 USD/month (NYC) based on comparable AI startups. Equity component n</t>
         </is>
       </c>
       <c r="K306" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles, based on the Summer 2026 cycle pattern. Listings close once positions are filled</t>
+          <t>Expected Q4 2026 (October to December 2026) for summer 2027 roles. Projected from the Summer 2026 cycle, where the listing appeared in October 2025</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Inflection AI</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
@@ -17630,17 +17630,17 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>GPU Optimization &amp; AI Infrastructure  (1 of 4 tracks)</t>
+          <t>ML Engineering Intern; Data Science Intern; Voice AI Intern; AI Systems Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E307" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/modal</t>
+          <t>inflection.ai/about</t>
         </is>
       </c>
       <c r="F307" s="7" t="inlineStr">
@@ -17650,34 +17650,34 @@
       </c>
       <c r="G307" s="6" t="inlineStr">
         <is>
-          <t>The intern interview likely consists of a recruiter screen (30 minutes), one to two technical coding rounds in Python, Rust, or Go focusing on systems fundamentals, and a behavioral round. The full-time process is rated 8 out of 10 difficulty, comparable to Stripe and HashiCorp. Modal does not use K</t>
+          <t>Three stages, all virtual: a 30-minute recruiter conversation, 90 minutes of technical interviews covering coding, ML domain questions, and systems design, and a 30-minute mentor or team conversation. The full process takes about three weeks, with decisions typically within one week of the final rou</t>
         </is>
       </c>
       <c r="H307" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsorship confirmed for full-time roles. CPT-eligible international students likely accepted for internships. Verify directly with Modal's recruiter</t>
+          <t>Not confirmed for interns. Inflection AI has filed a small number of H-1B petitions for full-time roles; CPT would typically apply for enrolled international students</t>
         </is>
       </c>
       <c r="I307" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling. With only seven to eight intern spots per cohort, positions probably fill quickly once posted. Apply the day the listing appears</t>
+          <t>Not officially confirmed, but positions fill quickly, suggesting first-come review. Apply as soon as listings appear</t>
         </is>
       </c>
       <c r="J307" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed. Estimated $60 to $85 per hour based on comparable AI infrastructure startups. Full-time SWE total comp ranges from $300K to $470K. Housi</t>
+          <t>Technical: $50 to $65/hr ($8,700 to $11,300/month). Nontechnical: $25 to $40/hr. Rate scales with education level and experience. Housing stipend not confirmed</t>
         </is>
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>Expected October to November 2026 for Summer 2027 roles. No confirmed dates. Projected from industry patterns and past cohort timing</t>
+          <t>Expected October to December 2026 for summer 2027 roles, based on the Summer 2026 cycle pattern. Listings close once positions are filled</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>Nintendo</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="B308" s="8" t="inlineStr">
@@ -17687,17 +17687,17 @@
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (NTD)  (1 of 6 tracks)</t>
+          <t>GPU Optimization &amp; AI Infrastructure  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E308" s="7" t="inlineStr">
         <is>
-          <t>careers.nintendo.com/</t>
+          <t>jobs.ashbyhq.com/modal</t>
         </is>
       </c>
       <c r="F308" s="7" t="inlineStr">
@@ -17707,34 +17707,34 @@
       </c>
       <c r="G308" s="6" t="inlineStr">
         <is>
-          <t>Nintendo’s funnel is structured and predictable, running roughly 3 to 4 months from application to offer: 1. Apply at careers.nintendo.com with a resume, cover letter showing Nintendo brand knowledge, and the Internship Questionnaire. Design roles require a portfolio. Submit before December 1. 2. Re</t>
+          <t>The intern interview likely consists of a recruiter screen (30 minutes), one to two technical coding rounds in Python, Rust, or Go focusing on systems fundamentals, and a behavioral round. The full-time process is rated 8 out of 10 difficulty, comparable to Stripe and HashiCorp. Modal does not use K</t>
         </is>
       </c>
       <c r="H308" s="6" t="inlineStr">
         <is>
-          <t>No. Nintendo of America requires applicants to be legally authorized to work in the United States and states that visa sponsorship is not available for internship positions. International students with valid CPT authoriz</t>
+          <t>H-1B sponsorship confirmed for full-time roles. CPT-eligible international students likely accepted for internships. Verify directly with Modal's recruiter</t>
         </is>
       </c>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>No. Hard December 1 deadline with batch review. Offers in January, all candidates notified by February</t>
+          <t>Likely rolling. With only seven to eight intern spots per cohort, positions probably fill quickly once posted. Apply the day the listing appears</t>
         </is>
       </c>
       <c r="J308" s="6" t="inlineStr">
         <is>
-          <t>$25/hr (marketing, UX, CSR) to $40/hr (NTD software engineering) + housing/travel support</t>
+          <t>Not publicly disclosed. Estimated $60 to $85 per hour based on comparable AI infrastructure startups. Full-time SWE total comp ranges from $300K to $470K. Housi</t>
         </is>
       </c>
       <c r="K308" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open ~October 2026, closing December 1, 2026 (documented pattern; not yet posted)</t>
+          <t>Expected October to November 2026 for Summer 2027 roles. No confirmed dates. Projected from industry patterns and past cohort timing</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Nintendo</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
@@ -17744,17 +17744,17 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – January 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D309" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data / Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineering (NTD)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E309" s="7" t="inlineStr">
         <is>
-          <t>careers.paramount.com/go/Interns/8710100/</t>
+          <t>careers.nintendo.com/</t>
         </is>
       </c>
       <c r="F309" s="7" t="inlineStr">
@@ -17764,30 +17764,34 @@
       </c>
       <c r="G309" s="6" t="inlineStr">
         <is>
-          <t>Most roles follow a two-round process. Round one is a recruiter phone screen lasting 15-30 minutes covering your background, interest in entertainment, and availability. Round two is a Zoom interview with the hiring team, often including behavioral questions like "What media do you consume?" and "Wh</t>
-        </is>
-      </c>
-      <c r="H309" s="6" t="inlineStr"/>
+          <t>Nintendo’s funnel is structured and predictable, running roughly 3 to 4 months from application to offer: 1. Apply at careers.nintendo.com with a resume, cover letter showing Nintendo brand knowledge, and the Internship Questionnaire. Design roles require a portfolio. Submit before December 1. 2. Re</t>
+        </is>
+      </c>
+      <c r="H309" s="6" t="inlineStr">
+        <is>
+          <t>No. Nintendo of America requires applicants to be legally authorized to work in the United States and states that visa sponsorship is not available for internship positions. International students with valid CPT authoriz</t>
+        </is>
+      </c>
       <c r="I309" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as qualified candidates apply; no individual status feedback provided</t>
+          <t>No. Hard December 1 deadline with batch review. Offers in January, all candidates notified by February</t>
         </is>
       </c>
       <c r="J309" s="6" t="inlineStr">
         <is>
-          <t>$23/hr median (Glassdoor, 266 reports); $19-$23/hr business roles, $34-$45/hr engineering roles</t>
+          <t>$25/hr (marketing, UX, CSR) to $40/hr (NTD software engineering) + housing/travel support</t>
         </is>
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>Expected October-November 2026 through late December 2026 / early January 2027 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Applications for summer 2027 expected to open ~October 2026, closing December 1, 2026 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="B310" s="8" t="inlineStr">
@@ -17797,17 +17801,17 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – January 2027</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Digital / Technology  (1 of 6 tracks)</t>
+          <t>Software Engineering; Data / Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E310" s="7" t="inlineStr">
         <is>
-          <t>pfizer.com/en/about/careers/pfizer-futures</t>
+          <t>careers.paramount.com/go/Interns/8710100/</t>
         </is>
       </c>
       <c r="F310" s="7" t="inlineStr">
@@ -17817,30 +17821,30 @@
       </c>
       <c r="G310" s="6" t="inlineStr">
         <is>
-          <t>Pfizer's funnel has two to three interview levels, and the process typically runs 4 to 8 weeks from application to final decision: 1. Create a profile on Pfizer's Workday portal or apply through the Pfizer Futures page . Select 2–3 areas of interest (community advice: do not select all, as it signal</t>
+          <t>Most roles follow a two-round process. Round one is a recruiter phone screen lasting 15-30 minutes covering your background, interest in entertainment, and availability. Round two is a Zoom interview with the hiring team, often including behavioral questions like "What media do you consume?" and "Wh</t>
         </is>
       </c>
       <c r="H310" s="6" t="inlineStr"/>
       <c r="I310" s="6" t="inlineStr">
         <is>
-          <t>Yes. "Applications reviewed on a rolling basis" (all JD postings). Community reports 70% of top-track slots go within first 45 days</t>
+          <t>Effectively yes. Positions fill as qualified candidates apply; no individual status feedback provided</t>
         </is>
       </c>
       <c r="J310" s="6" t="inlineStr">
         <is>
-          <t>$26–$29/hr undergrad (official); $45–$52/hr PhD (community-reported). Housing stipend available for relocated interns</t>
+          <t>$23/hr median (Glassdoor, 266 reports); $19-$23/hr business roles, $34-$45/hr engineering roles</t>
         </is>
       </c>
       <c r="K310" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open ~Oct 1 to Oct 31, 2026 (documented Oct pattern in prior cycles, projected from the summer 2026 cycle)</t>
+          <t>Expected October-November 2026 through late December 2026 / early January 2027 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Physical Intelligence</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
@@ -17850,17 +17854,17 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D311" s="6" t="inlineStr">
         <is>
-          <t>Research Intern (Robotics/AI); ML Infra Intern; Robotics SWE Intern  (3 of 5 tracks)</t>
+          <t>Digital / Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E311" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/physicalintelligence</t>
+          <t>pfizer.com/en/about/careers/pfizer-futures</t>
         </is>
       </c>
       <c r="F311" s="7" t="inlineStr">
@@ -17870,34 +17874,30 @@
       </c>
       <c r="G311" s="6" t="inlineStr">
         <is>
-          <t>Physical Intelligence does not publish its interview process, but recruiter job descriptions mention structured interviewer calibration, and the loop for comparable robotics AI research roles follows a predictable pattern: 1. Apply on the Ashby ATS or pi.website/join-us . Upload your resume, publica</t>
-        </is>
-      </c>
-      <c r="H311" s="6" t="inlineStr">
-        <is>
-          <t>Likely supported for qualified candidates. CPT standard for F-1 students. Not explicitly confirmed on PI's website; verify during application</t>
-        </is>
-      </c>
+          <t>Pfizer's funnel has two to three interview levels, and the process typically runs 4 to 8 weeks from application to final decision: 1. Create a profile on Pfizer's Workday portal or apply through the Pfizer Futures page . Select 2–3 areas of interest (community advice: do not select all, as it signal</t>
+        </is>
+      </c>
+      <c r="H311" s="6" t="inlineStr"/>
       <c r="I311" s="6" t="inlineStr">
         <is>
-          <t>Yes (DEFAULT tier). No publicly documented rigid cycle. Positions are posted when research teams identify needs. Apply as soon as you see a listing</t>
+          <t>Yes. "Applications reviewed on a rolling basis" (all JD postings). Community reports 70% of top-track slots go within first 45 days</t>
         </is>
       </c>
       <c r="J311" s="6" t="inlineStr">
         <is>
-          <t>Estimated $8,000 to $12,000/month for PhD research interns; $5,000 to $7,000/month for MS. Robot Operator roles approximately $25/hr. Based on comparable SF rob</t>
+          <t>$26–$29/hr undergrad (official); $45–$52/hr PhD (community-reported). Housing stipend available for relocated interns</t>
         </is>
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. Rolling review; likely closes January to February 2027. Projected from company growth trajectory and industry norms</t>
+          <t>Applications for summer 2027 expected to open ~Oct 1 to Oct 31, 2026 (documented Oct pattern in prior cycles, projected from the summer 2026 cycle)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Physical Intelligence</t>
         </is>
       </c>
       <c r="B312" s="8" t="inlineStr">
@@ -17912,12 +17912,12 @@
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>Summer Research Internship: Generative AI Features (prior cycle)  (1 of 4 tracks)</t>
+          <t>Research Intern (Robotics/AI); ML Infra Intern; Robotics SWE Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E312" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/pika</t>
+          <t>jobs.ashbyhq.com/physicalintelligence</t>
         </is>
       </c>
       <c r="F312" s="7" t="inlineStr">
@@ -17927,34 +17927,34 @@
       </c>
       <c r="G312" s="6" t="inlineStr">
         <is>
-          <t>Based on TechPrep candidate reports, the process takes 3 to 5 weeks and includes a recruiter screen (15 to 30 minutes), a technical phone screen with live Python coding (about 60 minutes), and a virtual onsite with 4 to 5 rounds covering DSA, system design for GPU inference and video pipelines, a cr</t>
+          <t>Physical Intelligence does not publish its interview process, but recruiter job descriptions mention structured interviewer calibration, and the loop for comparable robotics AI research roles follows a predictable pattern: 1. Apply on the Ashby ATS or pi.website/join-us . Upload your resume, publica</t>
         </is>
       </c>
       <c r="H312" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed. Likely supports OPT/CPT for F-1 students given Palo Alto location and funding level. Verify during recruiter screen</t>
+          <t>Likely supported for qualified candidates. CPT standard for F-1 students. Not explicitly confirmed on PI's website; verify during application</t>
         </is>
       </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t>Yes. The current Research Intern listing offers flexible part-time and full-time terms with no fixed deadline, suggesting continuous hiring. Apply as soon as th</t>
+          <t>Yes (DEFAULT tier). No publicly documented rigid cycle. Positions are posted when research teams identify needs. Apply as soon as you see a listing</t>
         </is>
       </c>
       <c r="J312" s="6" t="inlineStr">
         <is>
-          <t>$10,000/month (from prior BuiltInSF listing). Catered lunch and dinner in office. Weekly team events. Housing and transportation not included</t>
+          <t>Estimated $8,000 to $12,000/month for PhD research interns; $5,000 to $7,000/month for MS. Robot Operator roles approximately $25/hr. Based on comparable SF rob</t>
         </is>
       </c>
       <c r="K312" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. Rolling intake; the previous summer listing was removed September 2025, suggesting a similar rhythm</t>
+          <t>Expected October to December 2026 for summer 2027 roles. Rolling review; likely closes January to February 2027. Projected from company growth trajectory and industry norms</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
@@ -17964,17 +17964,17 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D313" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern — Workers AI / AI Platform; SWE Intern — Cloudflare Workers; ML Engineering Intern; SWE Intern — Infrastructure / Systems</t>
+          <t>Summer Research Internship: Generative AI Features (prior cycle)  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E313" s="7" t="inlineStr">
         <is>
-          <t>cloudflare.com/careers/early-talent/</t>
+          <t>jobs.ashbyhq.com/pika</t>
         </is>
       </c>
       <c r="F313" s="7" t="inlineStr">
@@ -17984,34 +17984,34 @@
       </c>
       <c r="G313" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">All applications go through Cloudflare's 1111 Interns program. The funnel spans 3 to 4 weeks from application to decision: 1. Apply on cloudflare.com/careers/early-talent . Search for internship roles mentioning Workers AI, AI Platform, or Machine Learning. Postings typically go live around October </t>
+          <t>Based on TechPrep candidate reports, the process takes 3 to 5 weeks and includes a recruiter screen (15 to 30 minutes), a technical phone screen with live Python coding (about 60 minutes), and a virtual onsite with 4 to 5 rounds covering DSA, system design for GPU inference and video pipelines, a cr</t>
         </is>
       </c>
       <c r="H313" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for US intern positions. International hub offices in London, Lisbon, and Bengaluru available for non-US students</t>
+          <t>Not explicitly confirmed. Likely supports OPT/CPT for F-1 students given Palo Alto location and funding level. Verify during recruiter screen</t>
         </is>
       </c>
       <c r="I313" s="6" t="inlineStr">
         <is>
-          <t>Yes. Cloudflare reviews applications on a rolling basis. Interviews run November through February with offers December through March. Apply as early as possible</t>
+          <t>Yes. The current Research Intern listing offers flexible part-time and full-time terms with no fixed deadline, suggesting continuous hiring. Apply as soon as th</t>
         </is>
       </c>
       <c r="J313" s="6" t="inlineStr">
         <is>
-          <t>$45 to $53 per hour (~$7,800 to $9,200/month) for US engineering interns. $1,000/month housing stipend plus relocation support. No Replicate-specific data exist</t>
+          <t>$10,000/month (from prior BuiltInSF listing). Catered lunch and dinner in office. Weekly team events. Housing and transportation not included</t>
         </is>
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>Expected mid-October 2026 for summer 2027 roles. Rolling review through February 2027. Projected from the 2026 cycle</t>
+          <t>Expected October to December 2026 for summer 2027 roles. Rolling intake; the previous summer listing was removed September 2025, suggesting a similar rhythm</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B314" s="8" t="inlineStr">
@@ -18021,17 +18021,17 @@
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – January 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
+          <t>SWE Intern — Workers AI / AI Platform; SWE Intern — Cloudflare Workers; ML Engineering Intern; SWE Intern — Infrastructure / Systems</t>
         </is>
       </c>
       <c r="E314" s="7" t="inlineStr">
         <is>
-          <t>rocketlabcorp.com/careers/internships/</t>
+          <t>cloudflare.com/careers/early-talent/</t>
         </is>
       </c>
       <c r="F314" s="7" t="inlineStr">
@@ -18041,34 +18041,34 @@
       </c>
       <c r="G314" s="6" t="inlineStr">
         <is>
-          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
+          <t xml:space="preserve">All applications go through Cloudflare's 1111 Interns program. The funnel spans 3 to 4 weeks from application to decision: 1. Apply on cloudflare.com/careers/early-talent . Search for internship roles mentioning Workers AI, AI Platform, or Machine Learning. Postings typically go live around October </t>
         </is>
       </c>
       <c r="H314" s="6" t="inlineStr">
         <is>
-          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
+          <t>F-1 CPT supported for US intern positions. International hub offices in London, Lisbon, and Bengaluru available for non-US students</t>
         </is>
       </c>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
+          <t>Yes. Cloudflare reviews applications on a rolling basis. Interviews run November through February with offers December through March. Apply as early as possible</t>
         </is>
       </c>
       <c r="J314" s="6" t="inlineStr">
         <is>
-          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
+          <t>$45 to $53 per hour (~$7,800 to $9,200/month) for US engineering interns. $1,000/month housing stipend plus relocation support. No Replicate-specific data exist</t>
         </is>
       </c>
       <c r="K314" s="6" t="inlineStr">
         <is>
-          <t>Expected October 2026 to January 2027 (projected from prior cycles; not yet posted)</t>
+          <t>Expected mid-October 2026 for summer 2027 roles. Rolling review through February 2027. Projected from the 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
@@ -18078,17 +18078,17 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026 – January 2027</t>
         </is>
       </c>
       <c r="D315" s="6" t="inlineStr">
         <is>
-          <t>Data Analytics / Data Science; Hardware Engineering  (2 of 6 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E315" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/rsgur</t>
+          <t>rocketlabcorp.com/careers/internships/</t>
         </is>
       </c>
       <c r="F315" s="7" t="inlineStr">
@@ -18098,34 +18098,34 @@
       </c>
       <c r="G315" s="6" t="inlineStr">
         <is>
-          <t>The process varies by role but typically spans 3 to 5 rounds over approximately 60 days. For Data Science interns, expect an initial 30-minute Zoom screening, a multi-day take-home data analysis project, follow-up technical discussions, and a final 60-minute panel interview. Game Design roles includ</t>
+          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
         </is>
       </c>
       <c r="H315" s="6" t="inlineStr">
         <is>
-          <t>US-based listings require eligibility to work in the US, which typically means US citizens, permanent residents, or students with valid work authorization such as CPT or OPT for F-1 visa holders. Rockstar doesn't confirm</t>
+          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
         </is>
       </c>
       <c r="I315" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Some roles close within weeks of posting; others stay open until spring. Early application is strongly recommended</t>
+          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
         </is>
       </c>
       <c r="J315" s="6" t="inlineStr">
         <is>
-          <t>$34/hr confirmed for NYC Data Science (Greenhouse listing); Glassdoor range $26–$47/hr across roles</t>
+          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
         </is>
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>Expected October–November 2026 for summer 2027 (based on documented Summer 2026 cycle; not yet posted)</t>
+          <t>Expected October 2026 to January 2027 (projected from prior cycles; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Rockstar Games</t>
         </is>
       </c>
       <c r="B316" s="8" t="inlineStr">
@@ -18135,17 +18135,17 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; Software Engineering Intern (inferred); Applied ML / Computer Vision Intern (inferred)  (3 of 4 tracks)</t>
+          <t>Data Analytics / Data Science; Hardware Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>runway.com/careers</t>
+          <t>job-boards.greenhouse.io/rsgur</t>
         </is>
       </c>
       <c r="F316" s="7" t="inlineStr">
@@ -18155,34 +18155,34 @@
       </c>
       <c r="G316" s="6" t="inlineStr">
         <is>
-          <t>The process typically takes 2 to 4 weeks (average 20 days on Glassdoor) and includes a recruiter screen (30 minutes), technical assessment (45 to 60 minutes of coding in Python and TypeScript), virtual onsite (pair programming, code review, systems design), and leadership meetings with senior leader</t>
+          <t>The process varies by role but typically spans 3 to 5 rounds over approximately 60 days. For Data Science interns, expect an initial 30-minute Zoom screening, a multi-day take-home data analysis project, follow-up technical discussions, and a final 60-minute panel interview. Game Design roles includ</t>
         </is>
       </c>
       <c r="H316" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsorship confirmed for full-time roles. CPT/OPT likely supported for international students (standard for AI companies at this tier). No explicit visa restriction stated</t>
+          <t>US-based listings require eligibility to work in the US, which typically means US citizens, permanent residents, or students with valid work authorization such as CPT or OPT for F-1 visa holders. Rockstar doesn't confirm</t>
         </is>
       </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No fixed deadline exists. Glassdoor data (80 interviews) shows an average of 20 days from application to decision. Apply as soon as a posting appear</t>
+          <t>Not confirmed. Some roles close within weeks of posting; others stay open until spring. Early application is strongly recommended</t>
         </is>
       </c>
       <c r="J316" s="6" t="inlineStr">
         <is>
-          <t>Indeed estimates approximately $4,015/month ($3,734 to $4,497 range), though this is based on limited data. Full-time research roles pay $320K+ median, suggesti</t>
+          <t>$34/hr confirmed for NYC Data Science (Greenhouse listing); Glassdoor range $26–$47/hr across roles</t>
         </is>
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed public deadline; roles fill on a rolling basis. Projected from general AI startup hiring patterns</t>
+          <t>Expected October–November 2026 for summer 2027 (based on documented Summer 2026 cycle; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
@@ -18192,17 +18192,17 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D317" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE / Data Engineering); Technology Analyst  (2 of 6 tracks)</t>
+          <t>ML Research Intern; Software Engineering Intern (inferred); Applied ML / Computer Vision Intern (inferred)  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E317" s="7" t="inlineStr">
         <is>
-          <t>careers.southwestair.com/us/en/campus-reach</t>
+          <t>runway.com/careers</t>
         </is>
       </c>
       <c r="F317" s="7" t="inlineStr">
@@ -18212,34 +18212,34 @@
       </c>
       <c r="G317" s="6" t="inlineStr">
         <is>
-          <t>It is an on-demand video interview with pre-set behavioral prompts and timed responses. The focus is entirely on culture fit, not technical skills. Southwest assesses alignment with their three core values: Warrior Spirit (resilience), Servant's Heart (service), and Fun-LUVing Attitude (positivity).</t>
+          <t>The process typically takes 2 to 4 weeks (average 20 days on Glassdoor) and includes a recruiter screen (30 minutes), technical assessment (45 to 60 minutes of coding in Python and TypeScript), virtual onsite (pair programming, code review, systems design), and leadership meetings with senior leader</t>
         </is>
       </c>
       <c r="H317" s="6" t="inlineStr">
         <is>
-          <t>Effectively no. Southwest requires unrestricted US work authorization without sponsorship. International students on F-1 visas using CPT or OPT are generally ineligible unless they hold separate permanent work authorizat</t>
+          <t>H-1B sponsorship confirmed for full-time roles. CPT/OPT likely supported for international students (standard for AI companies at this tier). No explicit visa restriction stated</t>
         </is>
       </c>
       <c r="I317" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling inside each fixed window. Southwest reviews on a rolling basis and may close early once the candidate pool is full</t>
+          <t>Likely yes. No fixed deadline exists. Glassdoor data (80 interviews) shows an average of 20 days from application to decision. Apply as soon as a posting appear</t>
         </is>
       </c>
       <c r="J317" s="6" t="inlineStr">
         <is>
-          <t>$20–$30/hr + up to $2,000 housing stipend + free unlimited standby flights on all Southwest routes</t>
+          <t>Indeed estimates approximately $4,015/month ($3,734 to $4,497 range), though this is based on limited data. Full-time research roles pay $320K+ median, suggesti</t>
         </is>
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>For summer 2027 — Tech &amp; Revenue Mgmt: expected ~October 2026 (8 days). All others: expected ~January 2027 (14 days). Both projected from the documented summer 2026 cycle</t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed public deadline; roles fill on a rolling basis. Projected from general AI startup hiring patterns</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="B318" s="8" t="inlineStr">
@@ -18249,17 +18249,17 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Security Engineer Intern  (2 of 7 tracks)</t>
+          <t>Technology (SWE / Data Engineering); Technology Analyst  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E318" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/togetherai</t>
+          <t>careers.southwestair.com/us/en/campus-reach</t>
         </is>
       </c>
       <c r="F318" s="7" t="inlineStr">
@@ -18269,30 +18269,34 @@
       </c>
       <c r="G318" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">For research interns, expect a PyTorch-based coding screen focused on ML-systems problems rather than traditional LeetCode. For engineering interns, expect coding interviews on distributed systems and full-stack development. The overall difficulty is rated 8 out of 10, comparable to Nvidia core GPU </t>
-        </is>
-      </c>
-      <c r="H318" s="6" t="inlineStr"/>
+          <t>It is an on-demand video interview with pre-set behavioral prompts and timed responses. The focus is entirely on culture fit, not technical skills. Southwest assesses alignment with their three core values: Warrior Spirit (resilience), Servant's Heart (service), and Fun-LUVing Attitude (positivity).</t>
+        </is>
+      </c>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>Effectively no. Southwest requires unrestricted US work authorization without sponsorship. International students on F-1 visas using CPT or OPT are generally ineligible unless they hold separate permanent work authorizat</t>
+        </is>
+      </c>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>Not stated. Positions close once filled; no fixed deadline published for most roles</t>
+          <t>Semi-rolling inside each fixed window. Southwest reviews on a rolling basis and may close early once the candidate pool is full</t>
         </is>
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
-          <t>$58–63/hr engineering/research; $43/hr marketing; $35/hr operations, plus housing stipend</t>
+          <t>$20–$30/hr + up to $2,000 housing stipend + free unlimited standby flights on all Southwest routes</t>
         </is>
       </c>
       <c r="K318" s="6" t="inlineStr">
         <is>
-          <t>Expected October–December 2026, based on 2026-cycle cadence (not yet posted)</t>
+          <t>For summer 2027 — Tech &amp; Revenue Mgmt: expected ~October 2026 (8 days). All others: expected ~January 2027 (14 days). Both projected from the documented summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Together AI</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
@@ -18307,12 +18311,12 @@
       </c>
       <c r="D319" s="6" t="inlineStr">
         <is>
-          <t>Software / IT (Phoenix)  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Security Engineer Intern  (2 of 7 tracks)</t>
         </is>
       </c>
       <c r="E319" s="7" t="inlineStr">
         <is>
-          <t>careers.tsmc.com/en_US/</t>
+          <t>job-boards.greenhouse.io/togetherai</t>
         </is>
       </c>
       <c r="F319" s="7" t="inlineStr">
@@ -18322,34 +18326,30 @@
       </c>
       <c r="G319" s="6" t="inlineStr">
         <is>
-          <t>TSMC's hiring funnel depends on whether you are applying for an engineering or software role, and the split matters: 1. Find your track at careers.tsmc.com and filter by US locations plus "intern." Arizona alone has 12+ engineering tracks, so read the specific JD carefully before applying. 2. Submit</t>
-        </is>
-      </c>
-      <c r="H319" s="6" t="inlineStr">
-        <is>
-          <t>No. TSMC explicitly excludes H-1B, OPT, O-1, and TN visa holders from US internship positions. Applicants must have long-term work authorization without any current or future employer sponsorship. Arizona postings use sl</t>
-        </is>
-      </c>
+          <t xml:space="preserve">For research interns, expect a PyTorch-based coding screen focused on ML-systems problems rather than traditional LeetCode. For engineering interns, expect coding interviews on distributed systems and full-stack development. The overall difficulty is rated 8 out of 10, comparable to Nvidia core GPU </t>
+        </is>
+      </c>
+      <c r="H319" s="6" t="inlineStr"/>
       <c r="I319" s="6" t="inlineStr">
         <is>
-          <t>Partially. Window is defined but review within it is rolling; apply early</t>
+          <t>Not stated. Positions close once filled; no fixed deadline published for most roles</t>
         </is>
       </c>
       <c r="J319" s="6" t="inlineStr">
         <is>
-          <t>$23 to $48/hr depending on location, role, and degree (Camas WA entry to San Jose PhD research)</t>
+          <t>$58–63/hr engineering/research; $43/hr marketing; $35/hr operations, plus housing stipend</t>
         </is>
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open October to December 2026 and close by March 2027 (earliest AZ postings live as of July 2026; projected from prior cycles)</t>
+          <t>Expected October–December 2026, based on 2026-cycle cadence (not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Ubisoft</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="B320" s="8" t="inlineStr">
@@ -18359,17 +18359,17 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics  (1 of 6 tracks)</t>
+          <t>Software / IT (Phoenix)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E320" s="7" t="inlineStr">
         <is>
-          <t>ubisoft.com/en-us/company/careers/search</t>
+          <t>careers.tsmc.com/en_US/</t>
         </is>
       </c>
       <c r="F320" s="7" t="inlineStr">
@@ -18379,30 +18379,34 @@
       </c>
       <c r="G320" s="6" t="inlineStr">
         <is>
-          <t>For programming roles, expect 4 rounds: an online MCQ assessment covering OOP, OS, C++, and data structures; two technical interviews testing CS fundamentals and game-specific knowledge like 3D math and engine concepts; and a short HR round. For other roles, expect 2 to 3 rounds including a recruite</t>
-        </is>
-      </c>
-      <c r="H320" s="6" t="inlineStr"/>
+          <t>TSMC's hiring funnel depends on whether you are applying for an engineering or software role, and the split matters: 1. Find your track at careers.tsmc.com and filter by US locations plus "intern." Arizona alone has 12+ engineering tracks, so read the specific JD carefully before applying. 2. Submit</t>
+        </is>
+      </c>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t>No. TSMC explicitly excludes H-1B, OPT, O-1, and TN visa holders from US internship positions. Applicants must have long-term work authorization without any current or future employer sponsorship. Arizona postings use sl</t>
+        </is>
+      </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Each studio reviews applications as they come in; positions close once filled. Structured programs (Develop at Ubisoft, Graduate Program, NEXT)</t>
+          <t>Partially. Window is defined but review within it is rolling; apply early</t>
         </is>
       </c>
       <c r="J320" s="6" t="inlineStr">
         <is>
-          <t>$23 to $33/hr for US interns (Indeed and Glassdoor ranges); ~$18 to $22 CAD/hr for Montreal co-ops</t>
+          <t>$23 to $48/hr depending on location, role, and degree (Camas WA entry to San Jose PhD research)</t>
         </is>
       </c>
       <c r="K320" s="6" t="inlineStr">
         <is>
-          <t>Studio postings expected December 2026 through March 2027; Develop at Ubisoft mentorship opens October 2026</t>
+          <t>Applications for summer 2027 expected to open October to December 2026 and close by March 2027 (earliest AZ postings live as of July 2026; projected from prior cycles)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Ubisoft</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
@@ -18417,12 +18421,12 @@
       </c>
       <c r="D321" s="6" t="inlineStr">
         <is>
-          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
+          <t>Data &amp; Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E321" s="7" t="inlineStr">
         <is>
-          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
+          <t>ubisoft.com/en-us/company/careers/search</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
@@ -18432,34 +18436,30 @@
       </c>
       <c r="G321" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
-        </is>
-      </c>
-      <c r="H321" s="6" t="inlineStr">
-        <is>
-          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
-        </is>
-      </c>
+          <t>For programming roles, expect 4 rounds: an online MCQ assessment covering OOP, OS, C++, and data structures; two technical interviews testing CS fundamentals and game-specific knowledge like 3D math and engine concepts; and a short HR round. For other roles, expect 2 to 3 rounds including a recruite</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr"/>
       <c r="I321" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
+          <t>Effectively yes. Each studio reviews applications as they come in; positions close once filled. Structured programs (Develop at Ubisoft, Graduate Program, NEXT)</t>
         </is>
       </c>
       <c r="J321" s="6" t="inlineStr">
         <is>
-          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
+          <t>$23 to $33/hr for US interns (Indeed and Glassdoor ranges); ~$18 to $22 CAD/hr for Montreal co-ops</t>
         </is>
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Studio postings expected December 2026 through March 2027; Develop at Ubisoft mentorship opens October 2026</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Waymo</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
@@ -18469,17 +18469,17 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – January 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; ML/Perception Research; Product Data Science  (3 of 6 tracks)</t>
+          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E322" s="7" t="inlineStr">
         <is>
-          <t>careers.withwaymo.com/early-careers</t>
+          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
         </is>
       </c>
       <c r="F322" s="7" t="inlineStr">
@@ -18489,30 +18489,34 @@
       </c>
       <c r="G322" s="6" t="inlineStr">
         <is>
-          <t>Expect a four-stage pipeline spanning 4 to 8 weeks: resume screen, 30-minute recruiter call, 45-60 minute live coding phone screen with medium-to-hard problems, and a 2 to 5 round virtual onsite covering coding, system design, a technical deep dive, and behavioral questions. There is no separate onl</t>
-        </is>
-      </c>
-      <c r="H322" s="6" t="inlineStr"/>
+          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
+        </is>
+      </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>Yes. Waymo explicitly accepts resumes on a rolling basis until roles are filled</t>
+          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
         </is>
       </c>
       <c r="J322" s="6" t="inlineStr">
         <is>
-          <t>$48 to $85/hr depending on role and education level; housing stipend provided for Mountain View campus</t>
+          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
         </is>
       </c>
       <c r="K322" s="6" t="inlineStr">
         <is>
-          <t>Expected October 2026 to January 2027 for summer 2027 (projected from the documented 2026 cycle; not yet posted)</t>
+          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Waymo</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -18522,17 +18526,17 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026 – January 2027</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern  (1 of 3 tracks)</t>
+          <t>Software Engineering; ML/Perception Research; Product Data Science  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E323" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/weaviate</t>
+          <t>careers.withwaymo.com/early-careers</t>
         </is>
       </c>
       <c r="F323" s="7" t="inlineStr">
@@ -18542,34 +18546,30 @@
       </c>
       <c r="G323" s="6" t="inlineStr">
         <is>
-          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
-        </is>
-      </c>
-      <c r="H323" s="6" t="inlineStr">
-        <is>
-          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
-        </is>
-      </c>
+          <t>Expect a four-stage pipeline spanning 4 to 8 weeks: resume screen, 30-minute recruiter call, 45-60 minute live coding phone screen with medium-to-hard problems, and a 2 to 5 round virtual onsite covering coding, system design, a technical deep dive, and behavioral questions. There is no separate onl</t>
+        </is>
+      </c>
+      <c r="H323" s="6" t="inlineStr"/>
       <c r="I323" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
+          <t>Yes. Waymo explicitly accepts resumes on a rolling basis until roles are filled</t>
         </is>
       </c>
       <c r="J323" s="6" t="inlineStr">
         <is>
-          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
+          <t>$48 to $85/hr depending on role and education level; housing stipend provided for Mountain View campus</t>
         </is>
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
+          <t>Expected October 2026 to January 2027 for summer 2027 (projected from the documented 2026 cycle; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
@@ -18579,17 +18579,17 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – March 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
+          <t>Software Engineer Intern  (1 of 3 tracks)</t>
         </is>
       </c>
       <c r="E324" s="7" t="inlineStr">
         <is>
-          <t>coreweave.com/careers/weights-biases</t>
+          <t>jobs.ashbyhq.com/weaviate</t>
         </is>
       </c>
       <c r="F324" s="7" t="inlineStr">
@@ -18599,34 +18599,34 @@
       </c>
       <c r="G324" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
+          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
         </is>
       </c>
       <c r="H324" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
+          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
         </is>
       </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
+          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
         </is>
       </c>
       <c r="J324" s="6" t="inlineStr">
         <is>
-          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
+          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
         </is>
       </c>
       <c r="K324" s="6" t="inlineStr">
         <is>
-          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -18636,17 +18636,17 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>October 2026 – March 2027</t>
         </is>
       </c>
       <c r="D325" s="6" t="inlineStr">
         <is>
-          <t>Media Tech Internship  (1 of 6 tracks)</t>
+          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E325" s="7" t="inlineStr">
         <is>
-          <t>jobs.comcast.com/early-career</t>
+          <t>coreweave.com/careers/weights-biases</t>
         </is>
       </c>
       <c r="F325" s="7" t="inlineStr">
@@ -18656,34 +18656,34 @@
       </c>
       <c r="G325" s="6" t="inlineStr">
         <is>
-          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
+          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
         </is>
       </c>
       <c r="H325" s="6" t="inlineStr">
         <is>
-          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
+          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
         </is>
       </c>
       <c r="I325" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
+          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
         </is>
       </c>
       <c r="J325" s="6" t="inlineStr">
         <is>
-          <t>Comcast SWE: $40/hr; NBCUniversal: $25/hr; sign-on bonus possible but not guaranteed</t>
+          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
         </is>
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
+          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
@@ -18693,17 +18693,17 @@
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – March 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>AI / ML Development Intern; Engineering &amp; Manufacturing Intern  (2 of 6 tracks)</t>
+          <t>Media Tech Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E326" s="7" t="inlineStr">
         <is>
-          <t>careers.gene.com/us/en/internship-opportunities</t>
+          <t>jobs.comcast.com/early-career</t>
         </is>
       </c>
       <c r="F326" s="7" t="inlineStr">
@@ -18713,34 +18713,34 @@
       </c>
       <c r="G326" s="6" t="inlineStr">
         <is>
-          <t>You apply with a resume, cover letter, and letters of recommendation. Then a phone screen with HR, a call with the hiring manager (sometimes including a short research presentation), a knowledge interview on your field, and a behavioral round using the STAR method. The average time to offer is 37 da</t>
+          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
         </is>
       </c>
       <c r="H326" s="6" t="inlineStr">
         <is>
-          <t>International students may apply. Visa sponsorship availability varies by position and department. You must be legally authorized to work in the US during the internship</t>
+          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
         </is>
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>Yes. Genentech posts positions on an ongoing basis from November through March and reviews applications as they arrive. Applying early maximizes your chances</t>
+          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
         </is>
       </c>
       <c r="J326" s="6" t="inlineStr">
         <is>
-          <t>$22 to $50 per hour depending on role, degree level, and year in school. Software engineer interns: $45/hr (Levels.fyi). Data science interns: $50/hr (Levels.fy</t>
+          <t>Comcast SWE: $40/hr; NBCUniversal: $25/hr; sign-on bonus possible but not guaranteed</t>
         </is>
       </c>
       <c r="K326" s="6" t="inlineStr">
         <is>
-          <t>Expected November 2026 through March 2027 for summer 2027 roles. Most hiring decisions made by end of March. Projected from prior cycles</t>
+          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -18750,17 +18750,17 @@
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November 2026 – March 2027</t>
         </is>
       </c>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
+          <t>AI / ML Development Intern; Engineering &amp; Manufacturing Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E327" s="7" t="inlineStr">
         <is>
-          <t>deepmind.google/student-researcher-program/</t>
+          <t>careers.gene.com/us/en/internship-opportunities</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
@@ -18770,30 +18770,34 @@
       </c>
       <c r="G327" s="6" t="inlineStr">
         <is>
-          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
-        </is>
-      </c>
-      <c r="H327" s="6" t="inlineStr"/>
+          <t>You apply with a resume, cover letter, and letters of recommendation. Then a phone screen with HR, a call with the hiring manager (sometimes including a short research presentation), a knowledge interview on your field, and a behavioral round using the STAR method. The average time to offer is 37 da</t>
+        </is>
+      </c>
+      <c r="H327" s="6" t="inlineStr">
+        <is>
+          <t>International students may apply. Visa sponsorship availability varies by position and department. You must be legally authorized to work in the US during the internship</t>
+        </is>
+      </c>
       <c r="I327" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
+          <t>Yes. Genentech posts positions on an ongoing basis from November through March and reviews applications as they arrive. Applying early maximizes your chances</t>
         </is>
       </c>
       <c r="J327" s="6" t="inlineStr">
         <is>
-          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
+          <t>$22 to $50 per hour depending on role, degree level, and year in school. Software engineer interns: $45/hr (Levels.fyi). Data science interns: $50/hr (Levels.fy</t>
         </is>
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
+          <t>Expected November 2026 through March 2027 for summer 2027 roles. Most hiring decisions made by end of March. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -18803,17 +18807,17 @@
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
+          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E328" s="7" t="inlineStr">
         <is>
-          <t>apply.workable.com/huggingface</t>
+          <t>deepmind.google/student-researcher-program/</t>
         </is>
       </c>
       <c r="F328" s="7" t="inlineStr">
@@ -18823,34 +18827,30 @@
       </c>
       <c r="G328" s="6" t="inlineStr">
         <is>
-          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
-        </is>
-      </c>
-      <c r="H328" s="6" t="inlineStr">
-        <is>
-          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
-        </is>
-      </c>
+          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr"/>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
+          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
+          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
         </is>
       </c>
       <c r="K328" s="6" t="inlineStr">
         <is>
-          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
+          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -18860,17 +18860,17 @@
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – June 2027</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E329" s="7" t="inlineStr">
         <is>
-          <t>jefferies.tal.net</t>
+          <t>apply.workable.com/huggingface</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
@@ -18880,34 +18880,34 @@
       </c>
       <c r="G329" s="6" t="inlineStr">
         <is>
-          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
+          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
         </is>
       </c>
       <c r="H329" s="6" t="inlineStr">
         <is>
-          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
+          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
         </is>
       </c>
       <c r="I329" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
+          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
         </is>
       </c>
       <c r="J329" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
+          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
         </is>
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted</t>
+          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -18917,17 +18917,17 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – June 2027</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern  (1 of 5 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E330" s="7" t="inlineStr">
         <is>
-          <t>marqeta.com/company/careers</t>
+          <t>jefferies.tal.net</t>
         </is>
       </c>
       <c r="F330" s="7" t="inlineStr">
@@ -18937,34 +18937,34 @@
       </c>
       <c r="G330" s="6" t="inlineStr">
         <is>
-          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
+          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
         </is>
       </c>
       <c r="H330" s="6" t="inlineStr">
         <is>
-          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
+          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
         </is>
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
+          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
         </is>
       </c>
       <c r="J330" s="6" t="inlineStr">
         <is>
-          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
+          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
         </is>
       </c>
       <c r="K330" s="6" t="inlineStr">
         <is>
-          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
+          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -18974,17 +18974,17 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – January 2027</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>Business — Analytics  (1 of 7 tracks)</t>
+          <t>Software Engineering Intern  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E331" s="7" t="inlineStr">
         <is>
-          <t>ogilvyearlycareers.com/the-summer-internship</t>
+          <t>marqeta.com/company/careers</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -18994,30 +18994,34 @@
       </c>
       <c r="G331" s="6" t="inlineStr">
         <is>
-          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
-        </is>
-      </c>
-      <c r="H331" s="6" t="inlineStr"/>
+          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
+        </is>
+      </c>
+      <c r="H331" s="6" t="inlineStr">
+        <is>
+          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
+        </is>
+      </c>
       <c r="I331" s="6" t="inlineStr">
         <is>
-          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
+          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
         </is>
       </c>
       <c r="J331" s="6" t="inlineStr">
         <is>
-          <t>$20 to $25/hr posted range (2026 cycle)</t>
+          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
         </is>
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
+          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -19027,17 +19031,17 @@
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – January 2027</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
+          <t>Business — Analytics  (1 of 7 tracks)</t>
         </is>
       </c>
       <c r="E332" s="7" t="inlineStr">
         <is>
-          <t>ouraring.com/careers</t>
+          <t>ogilvyearlycareers.com/the-summer-internship</t>
         </is>
       </c>
       <c r="F332" s="7" t="inlineStr">
@@ -19047,34 +19051,30 @@
       </c>
       <c r="G332" s="6" t="inlineStr">
         <is>
-          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
-        </is>
-      </c>
-      <c r="H332" s="6" t="inlineStr">
-        <is>
-          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
-        </is>
-      </c>
+          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
+        </is>
+      </c>
+      <c r="H332" s="6" t="inlineStr"/>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
+          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
         </is>
       </c>
       <c r="J332" s="6" t="inlineStr">
         <is>
-          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
+          <t>$20 to $25/hr posted range (2026 cycle)</t>
         </is>
       </c>
       <c r="K332" s="6" t="inlineStr">
         <is>
-          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
+          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -19084,17 +19084,17 @@
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>Process / Chemical Engineering Intern; Mechanical / Project Engineering Intern; Petroleum / Well Engineering Intern; Information Digital Technology (IDT) Intern  (4 of 6 tracks)</t>
+          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E333" s="7" t="inlineStr">
         <is>
-          <t>shell.com/careers/about-careers-at-shell/assessed-internship</t>
+          <t>ouraring.com/careers</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
@@ -19104,34 +19104,34 @@
       </c>
       <c r="G333" s="6" t="inlineStr">
         <is>
-          <t>You apply online (5 to 10 minutes), complete four HireVue game-based assessments (20 minutes), then a Virtual Job Tryout plus On-Demand Video Interview (40 minutes), and finally a live case-study presentation with two Shell professionals. Average time from application to hire is about 120 days.</t>
+          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
         </is>
       </c>
       <c r="H333" s="6" t="inlineStr">
         <is>
-          <t>Limited. US positions require US citizenship, permanent residency, or valid work authorization. Candidates on temporary visas (H-1, F-1, J-1) are generally not eligible. Limited PhD sponsorship in certain disciplines</t>
+          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
         </is>
       </c>
       <c r="I333" s="6" t="inlineStr">
         <is>
-          <t>Yes. Shell states that positions may close before the stated deadline and encourages applicants to apply as soon as possible</t>
+          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
         </is>
       </c>
       <c r="J333" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$25 to $45 per hour for general interns, $35 to $61 per hour for engineering interns (Glassdoor, 6,335 salary submissions). Business Analyst Intern: $22.50 per </t>
+          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
         </is>
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 to early 2027 for US summer 2027 roles. The 2026 US program posted in January 2026; the 2027 cycle is already appearing globally as of July 2026. Projected from prior cycles</t>
+          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -19141,17 +19141,17 @@
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – June 2027</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering; Digital IC Design; Product/Test Engineering; Manufacturing/Process Engineering; Applications Engineering  (5 of 6 tracks)</t>
+          <t>Process / Chemical Engineering Intern; Mechanical / Project Engineering Intern; Petroleum / Well Engineering Intern; Information Digital Technology (IDT) Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t>careers.ti.com/en/sites/CX/jobs?keyword=intern</t>
+          <t>shell.com/careers/about-careers-at-shell/assessed-internship</t>
         </is>
       </c>
       <c r="F334" s="7" t="inlineStr">
@@ -19161,34 +19161,34 @@
       </c>
       <c r="G334" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TI's interview funnel is shorter than most tech companies, averaging 22 days from application to offer. But the technical content is domain-specific rather than algorithm-focused, so generic LeetCode prep will not help you here: 1. Apply at careers.ti.com with a resume. No cover letter is required. </t>
+          <t>You apply online (5 to 10 minutes), complete four HireVue game-based assessments (20 minutes), then a Virtual Job Tryout plus On-Demand Video Interview (40 minutes), and finally a live case-study presentation with two Shell professionals. Average time from application to hire is about 120 days.</t>
         </is>
       </c>
       <c r="H334" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. For internships: CPT authorization from your school is sufficient (no employer petition needed). For full-time: TI actively sponsors H-1B visas and filed 122 petitions with 122 approved in FY2025. TN visas are also </t>
+          <t>Limited. US positions require US citizenship, permanent residency, or valid work authorization. Candidates on temporary visas (H-1, F-1, J-1) are generally not eligible. Limited PhD sponsorship in certain disciplines</t>
         </is>
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis. First-come advantage is real; positions may fill before the soft November close</t>
+          <t>Yes. Shell states that positions may close before the stated deadline and encourages applicants to apply as soon as possible</t>
         </is>
       </c>
       <c r="J334" s="6" t="inlineStr">
         <is>
-          <t>$28 to $47/hr depending on degree, role, and location, plus $2,300–$8,000 housing stipend</t>
+          <t xml:space="preserve">$25 to $45 per hour for general interns, $35 to $61 per hour for engineering interns (Glassdoor, 6,335 salary submissions). Business Analyst Intern: $22.50 per </t>
         </is>
       </c>
       <c r="K334" s="6" t="inlineStr">
         <is>
-          <t>Rolling, in progress: ~60 US intern reqs live with no year in the title (posting continuously since January 2026); the two 2027-titled reqs are Manufacturing Technician (AAS/certificate) roles with Apply Before November 30, 2026. Degree-track summer 2027 engineering reqs expected to be year-titled this fall</t>
+          <t>Expected late 2026 to early 2027 for US summer 2027 roles. The 2026 US program posted in January 2026; the 2027 cycle is already appearing globally as of July 2026. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -19198,17 +19198,17 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November 2026 – June 2027</t>
         </is>
       </c>
       <c r="D335" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
+          <t>Embedded Software Engineering; Digital IC Design; Product/Test Engineering; Manufacturing/Process Engineering; Applications Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/xai</t>
+          <t>careers.ti.com/en/sites/CX/jobs?keyword=intern</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
@@ -19218,54 +19218,54 @@
       </c>
       <c r="G335" s="6" t="inlineStr">
         <is>
-          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
+          <t xml:space="preserve">TI's interview funnel is shorter than most tech companies, averaging 22 days from application to offer. But the technical content is domain-specific rather than algorithm-focused, so generic LeetCode prep will not help you here: 1. Apply at careers.ti.com with a resume. No cover letter is required. </t>
         </is>
       </c>
       <c r="H335" s="6" t="inlineStr">
         <is>
-          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
+          <t xml:space="preserve">Yes. For internships: CPT authorization from your school is sufficient (no employer petition needed). For full-time: TI actively sponsors H-1B visas and filed 122 petitions with 122 approved in FY2025. TN visas are also </t>
         </is>
       </c>
       <c r="I335" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
+          <t>Yes. Applications reviewed on a rolling basis. First-come advantage is real; positions may fill before the soft November close</t>
         </is>
       </c>
       <c r="J335" s="6" t="inlineStr">
         <is>
-          <t>$10,000–$14,000/month (estimated; no first-party confirmation)</t>
+          <t>$28 to $47/hr depending on degree, role, and location, plus $2,300–$8,000 housing stipend</t>
         </is>
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 through early 2027 for Summer 2027; no fixed deadlines published</t>
+          <t>Rolling, in progress: ~60 US intern reqs live with no year in the title (posting continuously since January 2026); the two 2027-titled reqs are Manufacturing Technician (AAS/certificate) roles with Apply Before November 30, 2026. Degree-track summer 2027 engineering reqs expected to be year-titled this fall</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
-        </is>
-      </c>
-      <c r="B336" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B336" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E336" s="7" t="inlineStr">
         <is>
-          <t>biibhr.wd3.myworkdayjobs.com/external</t>
+          <t>job-boards.greenhouse.io/xai</t>
         </is>
       </c>
       <c r="F336" s="7" t="inlineStr">
@@ -19275,34 +19275,34 @@
       </c>
       <c r="G336" s="6" t="inlineStr">
         <is>
-          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
+          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
         </is>
       </c>
       <c r="H336" s="6" t="inlineStr">
         <is>
-          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
+          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
         </is>
       </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
+          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
         </is>
       </c>
       <c r="J336" s="6" t="inlineStr">
         <is>
-          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
+          <t>$10,000–$14,000/month (estimated; no first-party confirmation)</t>
         </is>
       </c>
       <c r="K336" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Expected late 2026 through early 2027 for Summer 2027; no fixed deadlines published</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19312,17 +19312,17 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – January 2027</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
         <is>
-          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
+          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E337" s="7" t="inlineStr">
         <is>
-          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
+          <t>biibhr.wd3.myworkdayjobs.com/external</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
@@ -19332,30 +19332,34 @@
       </c>
       <c r="G337" s="6" t="inlineStr">
         <is>
-          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
-        </is>
-      </c>
-      <c r="H337" s="6" t="inlineStr"/>
+          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
+        </is>
+      </c>
+      <c r="H337" s="6" t="inlineStr">
+        <is>
+          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
+        </is>
+      </c>
       <c r="I337" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
+          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
         </is>
       </c>
       <c r="J337" s="6" t="inlineStr">
         <is>
-          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
+          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
         </is>
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to January 2027 for summer 2028; Corporate Functions deadlines extend through mid-2027 (documented pattern; not yet posted)</t>
+          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19370,12 +19374,12 @@
       </c>
       <c r="D338" s="6" t="inlineStr">
         <is>
-          <t>Investment Engineer Intern; Software Engineer Intern; AI Innovation Hackathon  (3 of 5 tracks)</t>
+          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E338" s="7" t="inlineStr">
         <is>
-          <t>bridgewater.com/working-at-bridgewater/job-openings</t>
+          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
         </is>
       </c>
       <c r="F338" s="7" t="inlineStr">
@@ -19385,34 +19389,30 @@
       </c>
       <c r="G338" s="6" t="inlineStr">
         <is>
-          <t>The process takes an average of 33 days and includes a blind cognitive assessment, a 45-to-60-minute personal-development interview probing self-awareness and ego management, a macro case study or coding assessment depending on track, and a Super Day with 3 to 4 rounds including principled-disagreem</t>
-        </is>
-      </c>
-      <c r="H338" s="6" t="inlineStr">
-        <is>
-          <t>Bridgewater sponsors CPT, OPT, and H-1B visas. Investment Engineer roles require eligibility to work in the US for a minimum of 3 years; STEM degree required for H-1B/OPT sponsorship</t>
-        </is>
-      </c>
+          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
+        </is>
+      </c>
+      <c r="H338" s="6" t="inlineStr"/>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>Yes, rolling consideration once the window opens. Community advice: submit within the first wave once your resume and macro prep are ready</t>
+          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
         </is>
       </c>
       <c r="J338" s="6" t="inlineStr">
         <is>
-          <t>Investment Associate Intern: $71,000 total for 8 weeks including sign-on bonus, plus housing and travel (official). Investment Engineer Intern: $51,000 total fo</t>
+          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
         </is>
       </c>
       <c r="K338" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to January 2027, based on the documented December 1 to January 31 pattern from the current cycle. Projected, not yet posted</t>
+          <t>Expected December 2026 to January 2027 for summer 2028; Corporate Functions deadlines extend through mid-2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Bridgewater</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19427,12 +19427,12 @@
       </c>
       <c r="D339" s="6" t="inlineStr">
         <is>
-          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
+          <t>Investment Engineer Intern; Software Engineer Intern; AI Innovation Hackathon  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E339" s="7" t="inlineStr">
         <is>
-          <t>jobs.citi.com/</t>
+          <t>bridgewater.com/working-at-bridgewater/job-openings</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
@@ -19442,34 +19442,34 @@
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
+          <t>The process takes an average of 33 days and includes a blind cognitive assessment, a 45-to-60-minute personal-development interview probing self-awareness and ego management, a macro case study or coding assessment depending on track, and a Super Day with 3 to 4 rounds including principled-disagreem</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
+          <t>Bridgewater sponsors CPT, OPT, and H-1B visas. Investment Engineer roles require eligibility to work in the US for a minimum of 3 years; STEM degree required for H-1B/OPT sponsorship</t>
         </is>
       </c>
       <c r="I339" s="6" t="inlineStr">
         <is>
-          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
+          <t>Yes, rolling consideration once the window opens. Community advice: submit within the first wave once your resume and macro prep are ready</t>
         </is>
       </c>
       <c r="J339" s="6" t="inlineStr">
         <is>
-          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
+          <t>Investment Associate Intern: $71,000 total for 8 weeks including sign-on bonus, plus housing and travel (official). Investment Engineer Intern: $51,000 total fo</t>
         </is>
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>IB expected December 2026 to January 2027; Tech/Markets/Services expected August to December 2027 for summer 2028 (rolling; not yet posted as of July 2026 — check jobs.citi.com )</t>
+          <t>Expected December 2026 to January 2027, based on the documented December 1 to January 31 pattern from the current cycle. Projected, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19479,17 +19479,17 @@
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>December 2026 – January 2027</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
+          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E340" s="7" t="inlineStr">
         <is>
-          <t>careers.db.com/students-graduates/internship-programme/</t>
+          <t>jobs.citi.com/</t>
         </is>
       </c>
       <c r="F340" s="7" t="inlineStr">
@@ -19499,34 +19499,34 @@
       </c>
       <c r="G340" s="6" t="inlineStr">
         <is>
-          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
+          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
         </is>
       </c>
       <c r="H340" s="6" t="inlineStr">
         <is>
-          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
+          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
         </is>
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
+          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
         </is>
       </c>
       <c r="J340" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
+          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
         </is>
       </c>
       <c r="K340" s="6" t="inlineStr">
         <is>
-          <t>Partly open. Technology, Data and Innovation internship roles for 2027 are live as of August 2026. IB (summer 2028) still expected ~Dec 2026 through spring 2027 (UK/EMEA as early as Dec 2026). Rolling review</t>
+          <t>IB expected December 2026 to January 2027; Tech/Markets/Services expected August to December 2027 for summer 2028 (rolling; not yet posted as of July 2026 — check jobs.citi.com )</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>Raymond James</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19541,12 +19541,12 @@
       </c>
       <c r="D341" s="6" t="inlineStr">
         <is>
-          <t>Information Technology  (1 of 6 tracks)</t>
+          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E341" s="7" t="inlineStr">
         <is>
-          <t>raymondjames.wd1.myworkdayjobs.com/RaymondJamesEarlyCareers</t>
+          <t>careers.db.com/students-graduates/internship-programme/</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
@@ -19556,27 +19556,27 @@
       </c>
       <c r="G341" s="6" t="inlineStr">
         <is>
-          <t>Raymond James runs a five-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through the Raymond James Workday portal with your resume, cover letter, and transcripts. Raymond James posts separate listings per division, so choose your strongest</t>
+          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
         </is>
       </c>
       <c r="H341" s="6" t="inlineStr">
         <is>
-          <t>No. Raymond James does not offer visa sponsorship for internships. Applicants must be legally authorized to work in the U.S. without visa sponsorship now or in the future, including beyond OPT/EAD. International students</t>
+          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
         </is>
       </c>
       <c r="I341" s="6" t="inlineStr">
         <is>
-          <t>Yes. Raymond James reviews applications on a rolling basis; apply within the first 2–3 weeks</t>
+          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
         </is>
       </c>
       <c r="J341" s="6" t="inlineStr">
         <is>
-          <t>$72,000–$95,000 annualized by division (IB Summer Analyst ~$95,000; general intern ~$72,000)</t>
+          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
         </is>
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>Flagship IB expected Dec 2026 to spring 2027 for summer 2028 (rolling); broader corporate/HQ roles later into 2027. As of July 2026, not yet posted — watch the Workday portal</t>
+          <t>Partly open. Technology, Data and Innovation internship roles for 2027 are live as of August 2026. IB (summer 2028) still expected ~Dec 2026 through spring 2027 (UK/EMEA as early as Dec 2026). Rolling review</t>
         </is>
       </c>
     </row>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="K396" s="6" t="inlineStr">
         <is>
-          <t>Expected August to October 2027 for Summer 2028 U.S. roles. Some divisions open as early as spring of sophomore year. Rolling interviews run February through March. Projected from Summer 2026 and 2027 cycle patterns</t>
+          <t>IB Summer Analyst (summer 2028): expected August to October 2027, not yet posted. Live now: US 2027 Summer Internship Program, non-IB (Finance, Charlotte; Commercial Banking, New York, Boston, Charlotte), posted August 31, closes October 2, 2026</t>
         </is>
       </c>
     </row>
@@ -30262,7 +30262,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Raymond James</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -30284,7 +30284,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Recursion</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -30306,7 +30306,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -30328,7 +30328,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>Relativity Space</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -30350,7 +30350,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Relativity Space</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -30372,7 +30372,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -30394,7 +30394,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -30416,7 +30416,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>SambaNova</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -30438,7 +30438,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>Schlumberger (SLB)</t>
+          <t>SambaNova</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -30460,7 +30460,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Schlumberger (SLB)</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -30504,7 +30504,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -30526,7 +30526,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>Snyk</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -30548,7 +30548,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Snyk</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -30570,7 +30570,7 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -30592,7 +30592,7 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>Sprout Social</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -30614,7 +30614,7 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Sprout Social</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -30636,7 +30636,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>Suno</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -30658,7 +30658,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>Suno</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -30680,7 +30680,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -30702,7 +30702,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>Tempus AI</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -30724,7 +30724,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Tempus AI</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -30746,7 +30746,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -30768,7 +30768,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>Thermo Fisher</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -30790,7 +30790,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>Thinking Machines Lab</t>
+          <t>Thermo Fisher</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -30812,7 +30812,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Thinking Machines Lab</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -30834,7 +30834,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>TotalEnergies</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -30856,7 +30856,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>TotalEnergies</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -30878,7 +30878,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -30900,7 +30900,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -30922,7 +30922,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -30966,7 +30966,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -30988,7 +30988,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>Vanta</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -31010,7 +31010,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>VaynerMedia</t>
+          <t>Vanta</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -31032,7 +31032,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>VaynerMedia</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -31054,7 +31054,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -31076,7 +31076,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>VMware</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -31098,7 +31098,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>VMware</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -31120,7 +31120,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>Warner Bros Discovery</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -31142,7 +31142,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Warner Bros Discovery</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -31164,7 +31164,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>Wellington</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -31186,7 +31186,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>Windsurf (Codeium)</t>
+          <t>Wellington</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -31208,7 +31208,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>WPP</t>
+          <t>Windsurf (Codeium)</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -31230,7 +31230,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>Writer</t>
+          <t>WPP</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -31252,7 +31252,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Writer</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -31274,7 +31274,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>Zscaler</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -31296,7 +31296,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -31318,7 +31318,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -31340,7 +31340,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -31362,7 +31362,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -31384,7 +31384,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -31428,7 +31428,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -31450,7 +31450,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -31472,7 +31472,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -31494,7 +31494,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -31516,7 +31516,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -31538,7 +31538,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -31560,7 +31560,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -31582,12 +31582,12 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Addepar</t>
-        </is>
-      </c>
-      <c r="B296" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>Barclays</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Window open - check now</t>
         </is>
       </c>
       <c r="C296" s="7" t="inlineStr">
@@ -31604,7 +31604,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Addepar</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
@@ -31626,7 +31626,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B298" s="8" t="inlineStr">
@@ -31648,7 +31648,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
@@ -31670,7 +31670,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="B300" s="8" t="inlineStr">
@@ -31692,7 +31692,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
@@ -31714,7 +31714,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="B302" s="8" t="inlineStr">
@@ -31736,7 +31736,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>Fireworks AI</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
@@ -31758,7 +31758,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>Groq</t>
+          <t>Fireworks AI</t>
         </is>
       </c>
       <c r="B304" s="8" t="inlineStr">
@@ -31780,7 +31780,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>Ideogram</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
@@ -31802,7 +31802,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Inflection AI</t>
+          <t>Ideogram</t>
         </is>
       </c>
       <c r="B306" s="8" t="inlineStr">
@@ -31824,7 +31824,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Inflection AI</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
@@ -31846,7 +31846,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>Nintendo</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="B308" s="8" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Nintendo</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
@@ -31890,7 +31890,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="B310" s="8" t="inlineStr">
@@ -31912,7 +31912,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Physical Intelligence</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
@@ -31934,7 +31934,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Physical Intelligence</t>
         </is>
       </c>
       <c r="B312" s="8" t="inlineStr">
@@ -31956,7 +31956,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
@@ -31978,7 +31978,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B314" s="8" t="inlineStr">
@@ -32000,7 +32000,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
@@ -32022,7 +32022,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Rockstar Games</t>
         </is>
       </c>
       <c r="B316" s="8" t="inlineStr">
@@ -32044,7 +32044,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
@@ -32066,7 +32066,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="B318" s="8" t="inlineStr">
@@ -32088,7 +32088,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Together AI</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
@@ -32110,7 +32110,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Ubisoft</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="B320" s="8" t="inlineStr">
@@ -32132,7 +32132,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Ubisoft</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
@@ -32154,7 +32154,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Waymo</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
@@ -32176,7 +32176,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Waymo</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -32198,7 +32198,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
@@ -32220,7 +32220,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -32242,7 +32242,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
@@ -32264,7 +32264,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -32286,7 +32286,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -32308,7 +32308,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -32352,7 +32352,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -32374,7 +32374,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -32396,7 +32396,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -32418,7 +32418,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -32440,7 +32440,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -32462,12 +32462,12 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
-        </is>
-      </c>
-      <c r="B336" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="B336" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C336" s="7" t="inlineStr">
@@ -32484,7 +32484,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -32506,7 +32506,7 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>Bridgewater</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -32528,7 +32528,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Bridgewater</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -32550,7 +32550,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -32572,7 +32572,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>Raymond James</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -34965,7 +34965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -37834,17 +37834,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>⏳ OPENS SOON]</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Base44</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Campus Impact Leaders (Founding Class) — Deadline: Rolling</t>
+          <t>Campus Expert — Deadline: Annual Window (Applications Open Each July; Next: July 2027)</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr"/>
@@ -37867,12 +37867,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Canva</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Campus Canvassadors (Founding Cohort, Aug–Dec 2026) — Deadline: Rolling</t>
+          <t>Google Student Influencer Program (2026) — Deadline: Check site</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
@@ -37890,17 +37890,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>⏳ OPENS SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Campus Expert — Deadline: Annual Window (Applications Open Each July; Next: July 2027)</t>
+          <t>Microsoft Learn Student Ambassadors — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
@@ -37923,12 +37923,12 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Monster Energy</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Google Student Influencer Program (2026) — Deadline: Check site</t>
+          <t>College Ambassador Team (CAT) — Deadline: Check site</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr"/>
@@ -37951,12 +37951,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Microsoft Learn Student Ambassadors — Deadline: Rolling</t>
+          <t>Pearson Campus Ambassador — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr"/>
@@ -37979,12 +37979,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Monster Energy</t>
+          <t>Princess Polly</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>College Ambassador Team (CAT) — Deadline: Check site</t>
+          <t>College Ambassador — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr"/>
@@ -38007,12 +38007,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Pearson Campus Ambassador — Deadline: Rolling</t>
+          <t>Student Marketeer — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr"/>
@@ -38030,17 +38030,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Summer of Code</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Princess Polly</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>College Ambassador — Deadline: Rolling</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr"/>
@@ -38051,24 +38051,24 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>Student Marketeer — Deadline: Rolling</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr"/>
@@ -38079,27 +38079,31 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Summer of Code</t>
+          <t>Software Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr"/>
+          <t>SWE intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38107,27 +38111,31 @@
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Machine Learning &amp; AI Undergrad Internship</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr"/>
+          <t>ML / AI intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38135,14 +38143,14 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Software Undergrad Engineering Internship</t>
+          <t>Hardware Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
@@ -38152,7 +38160,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>SWE intern (undergrad)</t>
+          <t>hardware intern (undergrad)</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -38174,22 +38182,22 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; AI Undergrad Internship</t>
+          <t>Student Fellows Program</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>ML / AI intern (undergrad)</t>
+          <t>data and AI fellowship</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -38206,17 +38214,17 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Hardware Undergrad Engineering Internship</t>
+          <t>2027 US Summer Internship, Early Interest</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>hardware intern (undergrad)</t>
+          <t>early interest pipeline</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -38238,22 +38246,22 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Student Fellows Program</t>
+          <t>Learn Student Ambassadors</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>data and AI fellowship</t>
+          <t>ambassador program</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>check site</t>
+          <t>rolling</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
@@ -38270,17 +38278,17 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>2027 US Summer Internship, Early Interest</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>MLH</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>early interest pipeline</t>
+          <t>remote SWE fellowship, stipend</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -38302,22 +38310,22 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Learn Student Ambassadors</t>
+          <t>Neo Scholars</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>ambassador program</t>
+          <t>CS undergrad fellowship</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>approx June 14 to 30, 2026</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -38334,22 +38342,22 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>MLH Fellowship</t>
+          <t>AI Builder, Emerging Talent</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>MLH</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>remote SWE fellowship, stipend</t>
+          <t>emerging talent program</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E116" s="7" t="inlineStr">
@@ -38366,22 +38374,22 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Neo Scholars</t>
+          <t>2027 Summer Internships, Express Your Interest</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>Schonfeld</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>CS undergrad fellowship</t>
+          <t>express interest pipeline, full roles open Aug 2026</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>approx June 14 to 30, 2026</t>
+          <t>rolling</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
@@ -38398,24 +38406,20 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>AI Builder, Emerging Talent</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Coca-Cola Scholars Foundation</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>emerging talent program</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>check site</t>
-        </is>
-      </c>
+          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr"/>
       <c r="E118" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38423,31 +38427,27 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>2027 Summer Internships, Express Your Interest</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Schonfeld</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>express interest pipeline, full roles open Aug 2026</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr"/>
       <c r="E119" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38455,24 +38455,24 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>⏳ OPENS SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Ayn Rand Institute</t>
+          <t>Hagan Scholarship Foundation</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>Fountainhead Essay Contest (Grades 11–12) — Deadline: Sep 13, 2026 (Anthem contest closed May 31, 2026)</t>
+          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
@@ -38495,12 +38495,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Coca-Cola Scholars Foundation</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Coca-Cola Scholars Program (HS Senior; 3.0+ GPA)</t>
+          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
@@ -38518,17 +38518,17 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Gates Foundation</t>
+          <t>National Merit Scholarship Corporation</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>The Gates Scholarship (Low-Income Minority HS Seniors)</t>
+          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr"/>
@@ -38551,12 +38551,12 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Hagan Scholarship Foundation</t>
+          <t>Optimist International</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
+          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr"/>
@@ -38579,12 +38579,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Posse Foundation</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
+          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr"/>
@@ -38607,12 +38607,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>National Merit Scholarship Corporation</t>
+          <t>QuestBridge</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
+          <t>National College Match (HS Senior; Low-Income)</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr"/>
@@ -38635,12 +38635,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Optimist International</t>
+          <t>Regeneron / Society for Science</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
+          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr"/>
@@ -38663,12 +38663,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Posse Foundation</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
+          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr"/>
@@ -38679,7 +38679,7 @@
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
@@ -38691,12 +38691,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>QuestBridge</t>
+          <t>Career Pathways Initiative</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>National College Match (HS Senior; Low-Income)</t>
+          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr"/>
@@ -38707,7 +38707,7 @@
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
@@ -38719,12 +38719,12 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Regeneron / Society for Science</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
+          <t>Databricks Student Fellows Program — Deadline: Check site</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr"/>
@@ -38735,7 +38735,7 @@
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
         </is>
       </c>
     </row>
@@ -38747,12 +38747,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
+          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr"/>
@@ -38775,12 +38775,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative</t>
+          <t>GirlsWhoML</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
+          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr"/>
@@ -38803,12 +38803,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows Program — Deadline: Check site</t>
+          <t>AI Fellowship Program — Deadline: Check site</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr"/>
@@ -38831,12 +38831,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>IOScholarships</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
+          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr"/>
@@ -38854,17 +38854,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>GirlsWhoML</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
+          <t>Bridge — Deadline: Sep 27, 2026 (New York) / Jan 3, 2027 (London)</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr"/>
@@ -38887,12 +38887,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>AI Fellowship Program — Deadline: Check site</t>
+          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr"/>
@@ -38915,12 +38915,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>IOScholarships</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
+          <t>FOCUS — Deadline: Rolling (Sign Up to Be Notified)</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr"/>
@@ -38943,12 +38943,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Lime Connect</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>Lime Connect Network Membership — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr"/>
@@ -38971,12 +38971,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>MLT (Management Leadership for Tomorrow)</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>Bridge — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr"/>
@@ -38999,12 +38999,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>OpenTrade</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>FOCUS — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr"/>
@@ -39027,12 +39027,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Lime Connect</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Lime Connect Network Membership — Deadline: Rolling</t>
+          <t>PwC AI Externships — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr"/>
@@ -39055,12 +39055,12 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>MLT (Management Leadership for Tomorrow)</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
+          <t>Campus Leaders — Deadline: Rolling</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr"/>
@@ -39078,17 +39078,17 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>NSN (National Sales Network)</t>
+          <t>SHPE</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>2026 NSN Student Sales &amp; Marketing Conference — Deadline: Rolling (Event: Sep 12–14, 2026)</t>
+          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr"/>
@@ -39111,12 +39111,12 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>OpenTrade</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>OpenTrade Fellowship — Deadline: Rolling (Limited Spots)</t>
+          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr"/>
@@ -39139,12 +39139,12 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>WomenHack</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>PwC AI Externships — Deadline: Rolling</t>
+          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr"/>
@@ -39167,12 +39167,12 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>Campus Leaders — Deadline: Rolling</t>
+          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr"/>
@@ -39183,124 +39183,12 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>SHPE</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr"/>
-      <c r="E146" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>The Home Depot Externships (Multiple Tracks) — Deadline: Varies by Externship (Check Hub for Open Tracks)</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr"/>
-      <c r="E147" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>WomenHack</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr"/>
-      <c r="E148" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F148" s="5" t="inlineStr">
-        <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>✅ OPEN]</t>
-        </is>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr"/>
-      <c r="E149" s="7" t="inlineStr">
-        <is>
-          <t>apply</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
           <t>Underclassmen Research Programs</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F149"/>
+  <autoFilter ref="A2:F145"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -39448,10 +39336,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-14 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-15 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-16 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-17 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38406,7 +38406,7 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-17 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-18 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38602,7 +38602,7 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-18 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-19 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The process runs four stages for the Summer Internship: Finance · 5-minute preview See what this job actually feels like Try a quick task based on the kind of work you'd do in a real role. A company's revenue keeps growing, but its profit doesn't. Can you figure out why from the numbers? Try it Not </t>
+          <t>The process runs four stages for the Summer Internship: #extern-lab-finance .xl-stage{display:block;width:100%;overflow:hidden;margin:18px 0 22px;padding:0 0 16px}#extern-lab-finance .xl-deck{display:block;margin:0 auto;width:236px;height:272px;position:relative;cursor:pointer}#extern-lab-finance .x</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr"/>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-19 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-20 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-21 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-22 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-22 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-23 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-23 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-24 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>The process runs four stages for the Summer Internship: #extern-lab-finance .xl-stage{display:block;width:100%;overflow:hidden;margin:18px 0 22px;padding:0 0 16px}#extern-lab-finance .xl-deck{display:block;margin:0 auto;width:236px;height:272px;position:relative;cursor:pointer}#extern-lab-finance .x</t>
+          <t>The process runs four stages for the Summer Internship: #xi-blackrock-internship-guide{position:relative;max-width:680px;margin:36px auto;border:1px solid #e6e7ea;border-radius:22px;background:#fff;font-family:Inter,system-ui,-apple-system,"Segoe UI",sans-serif;color:#0c1117;overflow:hidden;text-ali</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-24 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-25 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>The process runs four stages for the Summer Internship: #xi-blackrock-internship-guide{position:relative;max-width:680px;margin:36px auto;border:1px solid #e6e7ea;border-radius:22px;background:#fff;font-family:Inter,system-ui,-apple-system,"Segoe UI",sans-serif;color:#0c1117;overflow:hidden;text-ali</t>
+          <t xml:space="preserve">The process runs four stages for the Summer Internship: 1. Online application at careers.blackrock.com: one program, up to two functions, resume. Choose your two functions deliberately, because withdrawing bars you from reapplying to the program that year. 2. Pre-interview assessment. An email link </t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-25 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-26 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-28 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-29 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38804,7 +38804,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-29 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-09-30 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -19244,9 +19244,9 @@
           <t>Biogen</t>
         </is>
       </c>
-      <c r="B336" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B336" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C336" s="5" t="inlineStr">
@@ -19301,9 +19301,9 @@
           <t>BNP Paribas</t>
         </is>
       </c>
-      <c r="B337" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C337" s="5" t="inlineStr">
@@ -19354,9 +19354,9 @@
           <t>Bridgewater</t>
         </is>
       </c>
-      <c r="B338" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B338" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
@@ -19411,9 +19411,9 @@
           <t>Citi</t>
         </is>
       </c>
-      <c r="B339" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
@@ -19468,9 +19468,9 @@
           <t>Deutsche Bank</t>
         </is>
       </c>
-      <c r="B340" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B340" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
@@ -19525,9 +19525,9 @@
           <t>Starbucks</t>
         </is>
       </c>
-      <c r="B341" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
@@ -19582,9 +19582,9 @@
           <t>Strava</t>
         </is>
       </c>
-      <c r="B342" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B342" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C342" s="5" t="inlineStr">
@@ -19635,9 +19635,9 @@
           <t>UBS</t>
         </is>
       </c>
-      <c r="B343" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
@@ -19692,9 +19692,9 @@
           <t>Volkswagen</t>
         </is>
       </c>
-      <c r="B344" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B344" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
@@ -32443,9 +32443,9 @@
           <t>Biogen</t>
         </is>
       </c>
-      <c r="B336" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B336" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C336" s="7" t="inlineStr">
@@ -32465,9 +32465,9 @@
           <t>BNP Paribas</t>
         </is>
       </c>
-      <c r="B337" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B337" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -32487,9 +32487,9 @@
           <t>Bridgewater</t>
         </is>
       </c>
-      <c r="B338" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B338" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C338" s="7" t="inlineStr">
@@ -32509,9 +32509,9 @@
           <t>Citi</t>
         </is>
       </c>
-      <c r="B339" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -32531,9 +32531,9 @@
           <t>Deutsche Bank</t>
         </is>
       </c>
-      <c r="B340" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B340" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C340" s="7" t="inlineStr">
@@ -32553,9 +32553,9 @@
           <t>Starbucks</t>
         </is>
       </c>
-      <c r="B341" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -32575,9 +32575,9 @@
           <t>Strava</t>
         </is>
       </c>
-      <c r="B342" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B342" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C342" s="7" t="inlineStr">
@@ -32597,9 +32597,9 @@
           <t>UBS</t>
         </is>
       </c>
-      <c r="B343" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -32619,9 +32619,9 @@
           <t>Volkswagen</t>
         </is>
       </c>
-      <c r="B344" s="9" t="inlineStr">
-        <is>
-          <t>Later this cycle</t>
+      <c r="B344" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C344" s="7" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-01 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-02 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>OPEN for summer 2027 on the Software Engineer track: Software Engineer Intern posted Aug 31, 2026 (San Francisco, Palo Alto, New York, Seattle, Bellevue, Burlington, Atlanta, Indianapolis), no end date printed, still live Oct 2. CLOSED: Sales Development Nonprofit and Public Sector and Recruiting Data Intelligence (pulled before Oct 2); Finance Operations Associate repost closes Oct 2</t>
+          <t>OPEN for summer 2027 on the Software Engineer track: Software Engineer Intern posted Aug 31, 2026 (San Francisco, Palo Alto, New York, Seattle, Bellevue, Burlington, Atlanta, Indianapolis), no end date printed, still live Oct 2. CLOSED: Sales Development Nonprofit and Public Sector and Recruiting Data Intelligence (pulled before Oct 2). Finance Operations Associate repost: last day Oct 2, 2026</t>
         </is>
       </c>
     </row>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>$35/hr standard undergraduate rate (official JD). Graduate-level quant roles pay $60 to $65/hr. 401(k) match included, no housing stipend</t>
+          <t>$37/hr on the summer 2027 postings we read, $40/hr on the two New York roles (prior cycle: $35/hr standard undergraduate rate). Graduate-level quant roles pay $</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="K374" s="6" t="inlineStr">
         <is>
-          <t>Mostly closed for summer 2027: the main US wave posted rolling from ~June 2026 and was gone by Sep 21, 2026. Two late Product Management Intern, Summer 2027 reqs are live as of Sep 27, 2026: Purchase, NY and Arlington, VA (R-287624-1, closes Sep 28) and St. Louis (R-287625-1, closes Oct 6). Summer 2028 roles expected to start posting ~June 2027. Mastercard posts and fills on a rolling, as-needed b</t>
+          <t xml:space="preserve">Mostly closed for summer 2027: the main US wave posted rolling from ~June 2026 and was gone by Sep 21, 2026. Of two late Product Management Intern, Summer 2027 reqs, one is still live as of Oct 1, 2026: St. Louis (R-287625-1, closes Oct 6, 2026). The Purchase, NY and Arlington, VA req (R-287624-1) closed Sep 28. Summer 2028 roles expected to start posting ~June 2027. Mastercard posts and fills on </t>
         </is>
       </c>
     </row>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="K392" s="6" t="inlineStr">
         <is>
-          <t>IB Summer Analyst (summer 2028): expected August to October 2027, not yet posted. Live as of Oct 1, 2026: one late 2027 IB Summer Analyst role (TD Cowen Healthcare, San Francisco), posted September 29, closes October 11, 2026; US 2027 Summer Internship Program, non-IB (Finance, Charlotte; Commercial Banking, New York, Boston, Charlotte; Risk), posted August 31, closes October 2, 2026</t>
+          <t>IB Summer Analyst (summer 2028): expected August to October 2027, not yet posted. On the board as of October 2, 2026: one late 2027 IB Summer Analyst role (TD Cowen Healthcare, San Francisco), posted September 29, end date October 11, 2026; US 2027 Summer Internship Program, non-IB (Finance, Commercial Banking, Risk, Audit and others), posted from August 31, end date October 2, 2026 on most; Globa</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-03 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-04 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live from September 14. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
+          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-06 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-07 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-08 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-09 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -23144,7 +23144,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 opened August 13 and close September 30, 2026 (rolling review from day one)</t>
+          <t>Summer 2027: opened August 13, 2026; the stated review window ended September 30, 2026, and on October 9, 2026, only the IT (Berkeley Heights, NJ) and Research and Innovation (Clark, NJ) postings were still listed. Summer 2028: expected around mid-August 2027 (projected from the 2025 and 2026 cycles)</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-09 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-10 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August 2026 – May 2027</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>IT &amp; Digital Technology Intern  (1 of 6 tracks)</t>
+          <t>Technology / Software Engineering; Data Science &amp; Analytics  (2 of 8 tracks)</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>jobs.aa.com/go/Interns-&amp;-Grads/9297200/</t>
+          <t>americanexpress.com/en-us/careers/student-programs/us/</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1946,34 +1946,30 @@
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>You apply online, pass ATS screening, complete a recruiter phone screen (20 to 30 minutes), potentially record a HireVue video assessment, then do 1 to 2 behavioral and technical interviews (45 to 60 minutes each). Glassdoor rates interview difficulty at 2.9 out of 5.</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>CPT supported for F-1 students during internships. H-1B sponsorship is limited for entry-level programs; most postings require existing U.S. work authorization</t>
-        </is>
-      </c>
+          <t>From application to offer, the process averages 21 to 25 days. Some candidates report receiving offers within 48 hours of their final interview. The process includes online assessments (within days of applying), a HireVue video interview, live interviews, and for some tracks a Superday.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Yes. American Airlines reviews applications on a rolling basis and extends offers through November to early February. Early applicants see roughly 40% higher in</t>
+          <t>Yes. AmEx reviews on a rolling basis and may fill all available spaces before the deadline</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Undergraduate: $28–$35/hr; Graduate: $40–$52/hr. SWE interns reported $33.75/hr (Levels.fyi, Summer 2025). Relocation stipend of $2,000–$3,000. No company-provi</t>
+          <t>UG $24–$63/hr (SWE NYC $54.40 + $5K housing); Grad $38–$87/hr + sign-on bonus</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Expected late August to early September 2026 for summer 2027 roles. Priority deadline around late October, final deadline mid-November 2026. Projected from prior cycle</t>
+          <t>OPEN NOW. Summer 2027 roles are live on careers.americanexpress.com as of August 2026, including AI Engineer, Cybersecurity Analyst, and other Enterprise Technology tracks. Rolling review; AmEx may fill positions before the posted deadline</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -1983,17 +1979,17 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – May 2027</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Technology / Software Engineering; Data Science &amp; Analytics  (2 of 8 tracks)</t>
+          <t>Software Engineer Intern; Data Science Intern  (2 of 3 tracks)</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>americanexpress.com/en-us/careers/student-programs/us/</t>
+          <t>asana.com/jobs/university-recruiting</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2003,30 +1999,34 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>From application to offer, the process averages 21 to 25 days. Some candidates report receiving offers within 48 hours of their final interview. The process includes online assessments (within days of applying), a HireVue video interview, live interviews, and for some tracks a Superday.</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
+          <t>Four stages: resume screen, 1 to 2 online coding assessments, a phone interview with a senior engineer, then 3 to 4 onsite or virtual rounds covering coding, algorithms, and design. The process averages about 25 days and is deliberately collaborative, with interviewers acting as partners rather than</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated in available postings. Check the specific role listing for sponsorship details</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Yes. AmEx reviews on a rolling basis and may fill all available spaces before the deadline</t>
+          <t>Yes. Rolling admissions confirmed. Interview slots fill by Oct/Nov for engineering, so early applicants get the most open seats</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>UG $24–$63/hr (SWE NYC $54.40 + $5K housing); Grad $38–$87/hr + sign-on bonus</t>
+          <t>SWE intern SF: $54–$81/hr ($9,352–$13,989/mo). Plus $1,500 relocation, free daily meals, $500 WFH stipend, $70/mo gym stipend</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 roles are live on careers.americanexpress.com as of August 2026, including AI Engineer, Cybersecurity Analyst, and other Enterprise Technology tracks. Rolling review; AmEx may fill positions before the posted deadline</t>
+          <t>Expected late Aug to early Sep 2026 for summer 2027; peak recruiting Sep to Nov. Projected from prior cycles, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Data Science Intern  (2 of 3 tracks)</t>
+          <t>TDP Software Engineer Intern; TDP Data Science Engineer Intern; TDP Systems Engineer Intern; TDP Network Engineer Intern; Cybersecurity Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>asana.com/jobs/university-recruiting</t>
+          <t>att.jobs/early-careers</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2056,34 +2056,34 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Four stages: resume screen, 1 to 2 online coding assessments, a phone interview with a senior engineer, then 3 to 4 onsite or virtual rounds covering coding, algorithms, and design. The process averages about 25 days and is deliberately collaborative, with interviewers acting as partners rather than</t>
+          <t>Six stages: online application, technical assessment (about four questions covering math, programming, and SQL), initial recruiter interview, technical interview (one LeetCode easy-to-medium problem plus debugging), behavioral interview (STAR format), and offer. The process averages about 51 days fo</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated in available postings. Check the specific role listing for sponsorship details</t>
+          <t>AT&amp;T has a history of H-1B sponsorship for full-time technology roles through AT&amp;T Services Inc. CPT is the standard mechanism for F-1 intern students. Check individual postings for specific work authorization requiremen</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>Yes. Rolling admissions confirmed. Interview slots fill by Oct/Nov for engineering, so early applicants get the most open seats</t>
+          <t xml:space="preserve">Semi-rolling within a defined window. Applications open August to September, interviews run September through February, and offers are extended October through </t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>SWE intern SF: $54–$81/hr ($9,352–$13,989/mo). Plus $1,500 relocation, free daily meals, $500 WFH stipend, $70/mo gym stipend</t>
+          <t>TDP Software Engineer Intern: approximately $39 per hour plus a $2,500 sign-on bonus (Levels.fyi and community reports). General intern roles: $25 to $44 per ho</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Expected late Aug to early Sep 2026 for summer 2027; peak recruiting Sep to Nov. Projected from prior cycles, not yet posted</t>
+          <t>Expected August to September 2026 for summer 2027 technology roles. Some positions reopen January through April 2027. Projected from AT&amp;T's published technology program timeline</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TDP Software Engineer Intern; TDP Data Science Engineer Intern; TDP Systems Engineer Intern; TDP Network Engineer Intern; Cybersecurity Intern  (5 of 6 tracks)</t>
+          <t>Software Engineering Internship; Data, Analytics &amp; ML Internship; Site Reliability Engineering Internship  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>att.jobs/early-careers</t>
+          <t>atlassian.com/company/careers/earlycareers</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2113,34 +2113,34 @@
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>Six stages: online application, technical assessment (about four questions covering math, programming, and SQL), initial recruiter interview, technical interview (one LeetCode easy-to-medium problem plus debugging), behavioral interview (STAR format), and offer. The process averages about 51 days fo</t>
+          <t>Typically 4 to 5 stages: online assessment (HackerRank, 2 to 4 problems, 60 to 90 minutes), recruiter phone screen (30 minutes), technical coding interview (code on your own laptop, 1 DSA problem with follow-ups, 45 to 60 minutes), values interview (behavioral, 45 to 60 minutes), and hiring committe</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>AT&amp;T has a history of H-1B sponsorship for full-time technology roles through AT&amp;T Services Inc. CPT is the standard mechanism for F-1 intern students. Check individual postings for specific work authorization requiremen</t>
+          <t>US internships are not available for any work sponsorship including F-1 OPT/CPT and J-1 status. Must have eligible US work authorization</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi-rolling within a defined window. Applications open August to September, interviews run September through February, and offers are extended October through </t>
+          <t>Yes, explicitly confirmed. Atlassian recruits on a rolling basis and strongly encourages early applications within the first 2 to 3 weeks</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>TDP Software Engineer Intern: approximately $39 per hour plus a $2,500 sign-on bonus (Levels.fyi and community reports). General intern roles: $25 to $44 per ho</t>
+          <t>Zone A (SF/NYC) $59 to $75/hr, Zone B (Seattle/Austin) $53 to $68/hr, Zone C (other US) $49 to $62/hr. Plus housing stipend of $1,000 to $3,000/month</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Expected August to September 2026 for summer 2027 technology roles. Some positions reopen January through April 2027. Projected from AT&amp;T's published technology program timeline</t>
+          <t>Applications for summer 2027 expected to open late Aug to early Sep 2026 for SWE and tech (US). Projected from prior cycles, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Internship; Data, Analytics &amp; ML Internship; Site Reliability Engineering Internship  (3 of 6 tracks)</t>
+          <t>SWE Intern (Core); Data Science Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>atlassian.com/company/careers/earlycareers</t>
+          <t>block.xyz/careers/jobs</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2170,34 +2170,34 @@
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Typically 4 to 5 stages: online assessment (HackerRank, 2 to 4 problems, 60 to 90 minutes), recruiter phone screen (30 minutes), technical coding interview (code on your own laptop, 1 DSA problem with follow-ups, 45 to 60 minutes), values interview (behavioral, 45 to 60 minutes), and hiring committe</t>
+          <t>Block's interview starts with a CodeSignal or Byteboard online assessment (60–70 minutes, LeetCode Easy to Medium), followed by a recruiter screen and a virtual onsite Superday with four 45-minute sessions. The format emphasizes pair programming, system design (often fintech-specific like payment pi</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>US internships are not available for any work sponsorship including F-1 OPT/CPT and J-1 status. Must have eligible US work authorization</t>
+          <t>CPT supported for F-1 students. OPT/STEM OPT for new grads. H-1B available but not guaranteed. Toronto and Melbourne locations for international candidates</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Yes, explicitly confirmed. Atlassian recruits on a rolling basis and strongly encourages early applications within the first 2 to 3 weeks</t>
+          <t>Yes, confirmed. Applications reviewed continuously; 70–80% of interview invitations go out September through October. Referred candidates are 3–4x more likely t</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Zone A (SF/NYC) $59 to $75/hr, Zone B (Seattle/Austin) $53 to $68/hr, Zone C (other US) $49 to $62/hr. Plus housing stipend of $1,000 to $3,000/month</t>
+          <t>SWE intern SF $48/hr (~$8,320/mo); NYC $50–60/hr. Plus $1,000–1,500/mo housing stipend. Total 12-week comp roughly $25,000–35,000</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open late Aug to early Sep 2026 for SWE and tech (US). Projected from prior cycles, not yet posted</t>
+          <t>Expected late Aug to early Sep 2026 for summer 2027; practical deadline mid-November 2026. Projected from prior cycle, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Core); Data Science Intern  (2 of 6 tracks)</t>
+          <t>Petroleum Engineer Intern; Reservoir Engineer Intern; Digital/Technology Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>block.xyz/careers/jobs</t>
+          <t>careers.bp.com/early-careers/internships</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2227,34 +2227,30 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Block's interview starts with a CodeSignal or Byteboard online assessment (60–70 minutes, LeetCode Easy to Medium), followed by a recruiter screen and a virtual onsite Superday with four 45-minute sessions. The format emphasizes pair programming, system design (often fintech-specific like payment pi</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>CPT supported for F-1 students. OPT/STEM OPT for new grads. H-1B available but not guaranteed. Toronto and Melbourne locations for international candidates</t>
-        </is>
-      </c>
+          <t xml:space="preserve">After applying online, candidates complete a situational judgement questionnaire plus verbal and numerical reasoning tests. If you advance, you record a HireVue video interview with competency-based questions. Finalists get a live technical interview and may attend an assessment centre. The average </t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed continuously; 70–80% of interview invitations go out September through October. Referred candidates are 3–4x more likely t</t>
+          <t>Yes. BP fills vacancies "on an ongoing basis" and may close applications before the stated deadline</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>SWE intern SF $48/hr (~$8,320/mo); NYC $50–60/hr. Plus $1,000–1,500/mo housing stipend. Total 12-week comp roughly $25,000–35,000</t>
+          <t>$5,171–$5,700/month plus corporate housing with furnished apartments and relocation assistance</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Expected late Aug to early Sep 2026 for summer 2027; practical deadline mid-November 2026. Projected from prior cycle, not yet posted</t>
+          <t>Expected August–October 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2264,17 +2260,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Petroleum Engineer Intern; Reservoir Engineer Intern; Digital/Technology Intern  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern; Data Science Intern  (2 of 5 tracks)</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>careers.bp.com/early-careers/internships</t>
+          <t>brex.com/careers</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2284,30 +2280,34 @@
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">After applying online, candidates complete a situational judgement questionnaire plus verbal and numerical reasoning tests. If you advance, you record a HireVue video interview with competency-based questions. Finalists get a live technical interview and may attend an assessment centre. The average </t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
+          <t>A recruiter phone screen (30 minutes), a technical phone screen with live coding (45 to 60 minutes), and a 2- to 3-round virtual onsite covering a complex coding problem with live endpoint implementation, system or financial system design, and a behavioral values round. Brex emphasizes debugging exi</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>F-1 CPT and OPT supported. STEM OPT Extension (24 months) supported. H-1B verified but increasingly restricted for new filings. Post-acquisition policies may align with Capital One</t>
+        </is>
+      </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Yes. BP fills vacancies "on an ongoing basis" and may close applications before the stated deadline</t>
+          <t>Yes, with caveats. Earlier applications receive faster review and internal referrals get priority screening. 60 to 70% of offers are extended by mid-October</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>$5,171–$5,700/month plus corporate housing with furnished apartments and relocation assistance</t>
+          <t>$48 to $58 per hour ($8,300 to $10,100/month) for SWE interns. Housing or relocation stipend of $3,000 to $6,000. BuiltInSF lists $55/hr for Summer 2026</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Expected August–October 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Expected late August to early September 2026 for summer 2027 roles. Priority window closes mid-October 2026. Final deadline projected late October to early November 2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -2317,17 +2317,17 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science Intern  (2 of 5 tracks)</t>
+          <t>ALDP) Analytics Leadership Development Program; TECDP: Technology Development Program  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>brex.com/careers</t>
+          <t>jobs.thecignagroup.com/us/en/studentandgraduates</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2337,34 +2337,34 @@
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>A recruiter phone screen (30 minutes), a technical phone screen with live coding (45 to 60 minutes), and a 2- to 3-round virtual onsite covering a complex coding problem with live endpoint implementation, system or financial system design, and a behavioral values round. Brex emphasizes debugging exi</t>
+          <t>Cigna's actuarial internship hiring is fit-forward, not a technical gauntlet. There is no documented coding online assessment for AEDP; the exam transcript functions as the de facto technical screen. Here is the path from posting to offer: 1. Find the posting. Browse jobs.thecignagroup.com (Students</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT and OPT supported. STEM OPT Extension (24 months) supported. H-1B verified but increasingly restricted for new filings. Post-acquisition policies may align with Capital One</t>
+          <t>No. AEDP is "open only to individuals... who would not require visa support including H-1B, CPT/OPT/STEM, etc., now or in the future." International students requiring OPT/CPT are effectively excluded</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Yes, with caveats. Earlier applications receive faster review and internal referrals get priority screening. 60 to 70% of offers are extended by mid-October</t>
+          <t>Fixed seasonal window with rolling review. Postings note they "may close before the stated closing date," so apply the week you see the role, not at the deadlin</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>$48 to $58 per hour ($8,300 to $10,100/month) for SWE interns. Housing or relocation stipend of $3,000 to $6,000. BuiltInSF lists $55/hr for Summer 2026</t>
+          <t>Official: a "competitive hourly rate" that scales with actuarial exam progress, plus paid travel, fully furnished shared housing, and paid exam study materials.</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Expected late August to early September 2026 for summer 2027 roles. Priority window closes mid-October 2026. Final deadline projected late October to early November 2026</t>
+          <t>AEDP recruiting runs August–October and has already begun for the 2026–2027 season, so applications for summer 2027 are open now and expected to close ~late October 2026 (projected from the documented 29 Oct 2025 close for the prior cohort). ALDP (posted September 8, 2026) and all five TECDP tracks (posted September 9 and 10, 2026) are also live, along with AIIDP, Risk &amp; Underwriting (closes mid-O</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August 2026 – February 2027</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>ALDP) Analytics Leadership Development Program; TECDP: Technology Development Program  (2 of 4 tracks)</t>
+          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical Engineering Intern; Systems Engineering Intern; SEPP (Summer Engineering Project Program)</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>jobs.thecignagroup.com/us/en/studentandgraduates</t>
+          <t>careers.rtx.com/global/en/campus</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2394,34 +2394,34 @@
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Cigna's actuarial internship hiring is fit-forward, not a technical gauntlet. There is no documented coding online assessment for AEDP; the exam transcript functions as the de facto technical screen. Here is the path from posting to offer: 1. Find the posting. Browse jobs.thecignagroup.com (Students</t>
+          <t>The documented flow is recruiter review, then a virtual behavioral interview, then a possible onsite interview and facility tour, then an offer. It is behavioral-heavy ("tell me about yourself," strengths and weaknesses, career goals) with no timed coding assessment on record. Panels are described a</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>No. AEDP is "open only to individuals... who would not require visa support including H-1B, CPT/OPT/STEM, etc., now or in the future." International students requiring OPT/CPT are effectively excluded</t>
+          <t xml:space="preserve">Effectively none for engineering interns. Collins JDs state US citizenship is required because only US citizens are eligible for the security clearance these roles need. International students are generally not eligible </t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Fixed seasonal window with rolling review. Postings note they "may close before the stated closing date," so apply the week you see the role, not at the deadlin</t>
+          <t>Effectively yes. Collins and RTX post individual role reqs and close each once its applicant pool is full. The two documented JDs had different close dates (Sep</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Official: a "competitive hourly rate" that scales with actuarial exam progress, plus paid travel, fully furnished shared housing, and paid exam study materials.</t>
+          <t>No official hourly rate is published. Self-reported Levels.fyi data shows roughly $27 to $37/hr depending on role, location, and class standing (Cedar Rapids, I</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>AEDP recruiting runs August–October and has already begun for the 2026–2027 season, so applications for summer 2027 are open now and expected to close ~late October 2026 (projected from the documented 29 Oct 2025 close for the prior cohort). ALDP (posted September 8, 2026) and all five TECDP tracks (posted September 9 and 10, 2026) are also live, along with AIIDP, Risk &amp; Underwriting (closes mid-O</t>
+          <t>Not yet posted for summer 2027 (expected). Based on documented 2024 and 2025 cycles, where deadlines ranged from September to March, applications for summer 2027 are expected to open around August to September 2026 and fill on a rolling basis into early 2027.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Collins Aerospace</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -2431,17 +2431,17 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – February 2027</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical Engineering Intern; Systems Engineering Intern; SEPP (Summer Engineering Project Program)</t>
+          <t>Information Technology (CDS)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>careers.rtx.com/global/en/campus</t>
+          <t>costco.com/career-opportunities.html</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2451,34 +2451,30 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>The documented flow is recruiter review, then a virtual behavioral interview, then a possible onsite interview and facility tour, then an offer. It is behavioral-heavy ("tell me about yourself," strengths and weaknesses, career goals) with no timed coding assessment on record. Panels are described a</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Effectively none for engineering interns. Collins JDs state US citizenship is required because only US citizens are eligible for the security clearance these roles need. International students are generally not eligible </t>
-        </is>
-      </c>
+          <t>For IT roles, expect a phone screen with HR, followed by an online coding assessment on cyberByte (3 coding problems plus 1 theory question), and a final interview with the hiring manager covering both technical and behavioral questions. Non-technical tracks typically involve two interview rounds: o</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Collins and RTX post individual role reqs and close each once its applicant pool is full. The two documented JDs had different close dates (Sep</t>
+          <t>Effectively yes. Postings may close before stated deadline as positions fill; applying within the first three weeks correlates with higher interview rates</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>No official hourly rate is published. Self-reported Levels.fyi data shows roughly $27 to $37/hr depending on role, location, and class standing (Cedar Rapids, I</t>
+          <t>$31.90/hr for IT (confirmed 2025 cycle); $25–$40/hr range across all tracks; housing not provided</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Not yet posted for summer 2027 (expected). Based on documented 2024 and 2025 cycles, where deadlines ranged from September to March, applications for summer 2027 are expected to open around August to September 2026 and fill on a rolling basis into early 2027.</t>
+          <t>IT/CDS: expected August–September 2026 for summer 2027 (documented pattern; not yet posted). Accounting: January–March 2027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -2488,17 +2484,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August 2026 – June 2027</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Information Technology (CDS)  (1 of 6 tracks)</t>
+          <t>Cyber &amp; Forensic Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>costco.com/career-opportunities.html</t>
+          <t>crai.com/cra-careers/jobs/?level=Students/Recent+Graduates</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2508,30 +2504,34 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>For IT roles, expect a phone screen with HR, followed by an online coding assessment on cyberByte (3 coding problems plus 1 theory question), and a final interview with the hiring manager covering both technical and behavioral questions. Non-technical tracks typically involve two interview rounds: o</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr"/>
+          <t>CRA’s funnel blends behavioral, case, and technical evaluation, with offers communicated within days of the final round: 1. Find open positions on crai.com/cra-careers/jobs . Filter by Students/Recent Graduates, select up to two geographic and practice preferences, and submit via Greenhouse ATS with</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated in JDs. International offices (London, Brussels, Munich) hire locally</t>
+        </is>
+      </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Postings may close before stated deadline as positions fill; applying within the first three weeks correlates with higher interview rates</t>
+          <t>Yes. CRA reviews on a rolling basis; positions may fill before March</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>$31.90/hr for IT (confirmed 2025 cycle); $25–$40/hr range across all tracks; housing not provided</t>
+          <t>$30–$36/hr for NYC/DC offices (official JD). Glassdoor average: ~$57K annualized</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>IT/CDS: expected August–September 2026 for summer 2027 (documented pattern; not yet posted). Accounting: January–March 2027</t>
+          <t>Open since August 28, 2026 (summer 2027); résumé review from October 15, rolling until positions fill, historically through March 2027. Rising First-Year deadline ~January 2027</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – June 2027</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Cyber &amp; Forensic Technology Intern  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Data Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>crai.com/cra-careers/jobs/?level=Students/Recent+Graduates</t>
+          <t>careers.datadoghq.com/early-careers/</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2561,34 +2561,34 @@
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CRA’s funnel blends behavioral, case, and technical evaluation, with offers communicated within days of the final round: 1. Find open positions on crai.com/cra-careers/jobs . Filter by Students/Recent Graduates, select up to two geographic and practice preferences, and submit via Greenhouse ATS with</t>
+          <t>You apply, complete a 90-minute HackerRank OA with 2 to 3 LeetCode-medium problems, then a 45- to 60-minute technical phone screen via CoderPad, followed by a final round of 3 to 4 interviews covering coding, systems design, a project deep dive, and behavioral assessment.</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated in JDs. International offices (London, Brussels, Munich) hire locally</t>
+          <t>F-1 CPT fully supported for internships. OPT and STEM OPT extension (36 months) for new graduates. H-1B sponsorship available. TN visa supported for Canada and Mexico citizens</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Yes. CRA reviews on a rolling basis; positions may fill before March</t>
+          <t>Yes. Datadog reviews applications on a rolling basis and interviews September through March. Apply within the first week for the highest callback rates</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>$30–$36/hr for NYC/DC offices (official JD). Glassdoor average: ~$57K annualized</t>
+          <t>$48 to $57 per hour for SWE interns ($8,300 to $9,931 per month) depending on location. Housing stipend of $6,000 to $7,500 for NYC and Boston. PM interns at $5</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Open since August 28, 2026 (summer 2027); résumé review from October 15, rolling until positions fill, historically through March 2027. Rising First-Year deadline ~January 2027</t>
+          <t>Open now for summer 2027: Product Management Intern (posted August 17, 2026), Software Engineering Intern (Summer, posted September 8) and Research Science Intern (PhD, posted September 15). No deadline printed; rolling until positions are filled, with a priority deadline around late October in the prior cycle</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -2598,17 +2598,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August 2026 – May 2027</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Data Engineering Intern  (2 of 6 tracks)</t>
+          <t>Technology: IT SWE / Innovation-AI Engineering / InfoSec; Analytics: Operations Analytics Co-Op  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>careers.datadoghq.com/early-careers/</t>
+          <t>delta.com/us/en/careers/students-and-early-careers</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2618,34 +2618,34 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a 90-minute HackerRank OA with 2 to 3 LeetCode-medium problems, then a 45- to 60-minute technical phone screen via CoderPad, followed by a final round of 3 to 4 interviews covering coding, systems design, a project deep dive, and behavioral assessment.</t>
+          <t>Typically a digital assessment (Virtual Job Tryout / HireVue on-demand video), then a recruiter or live virtual interview, then a behavioral plus (for tech) technical round, and sometimes a final interview or Event Day at Atlanta HQ. Delta uses STAR behavioral questions tied to its "Rules of the Roa</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT fully supported for internships. OPT and STEM OPT extension (36 months) for new graduates. H-1B sponsorship available. TN visa supported for Canada and Mexico citizens</t>
+          <t>The IT SWE posting accepts US Citizen, Permanent Resident, or US Student Visa. Work authorization is required; confirm sponsorship per posting: it is not broadly advertised</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Yes. Datadog reviews applications on a rolling basis and interviews September through March. Apply within the first week for the highest callback rates</t>
+          <t>Yes. Delta's FAQ says Internship and MBA opportunities are "consistently hiring" and Co-Ops are "hired year round" for spring, summer, and fall rotations. Revie</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>$48 to $57 per hour for SWE interns ($8,300 to $9,931 per month) depending on location. Housing stipend of $6,000 to $7,500 for NYC and Boston. PM interns at $5</t>
+          <t>MBA Supply Chain intern: $9,493/month (official). Undergrad interns ~$22–23/hr in official/community postings (a Minneapolis SWE role listed $22.56/hr); Glassdo</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Product Management Intern (posted August 17, 2026), Software Engineering Intern (Summer, posted September 8) and Research Science Intern (PhD, posted September 15). No deadline printed; rolling until positions are filled, with a priority deadline around late October in the prior cycle</t>
+          <t xml:space="preserve">OPEN NOW. Summer 2027 roles live on Delta's own Avature careers site include Finance, Commercial Strategy (both the intern and MBA versions), MBA Supply Chain Management, MBA Financial Strategy and Network Scheduling. We confirmed the Commercial Strategy intern requisition (job 33352, created August 5, 2026) was still open on August 15, 2026. Delta hires on a rolling basis and warns postings "may </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -2655,17 +2655,17 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – May 2027</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Technology: IT SWE / Innovation-AI Engineering / InfoSec; Analytics: Operations Analytics Co-Op  (2 of 6 tracks)</t>
+          <t>Engineering Intern &amp; Co-op  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>delta.com/us/en/careers/students-and-early-careers</t>
+          <t>dukeenergy.wd1.myworkdayjobs.com/en-US/Search</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2675,34 +2675,30 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Typically a digital assessment (Virtual Job Tryout / HireVue on-demand video), then a recruiter or live virtual interview, then a behavioral plus (for tech) technical round, and sometimes a final interview or Event Day at Atlanta HQ. Delta uses STAR behavioral questions tied to its "Rules of the Roa</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>The IT SWE posting accepts US Citizen, Permanent Resident, or US Student Visa. Work authorization is required; confirm sponsorship per posting: it is not broadly advertised</t>
-        </is>
-      </c>
+          <t>Expect 2–3 rounds: a phone screen with a recruiter, a panel interview with 2–4 interviewers using STAR-method behavioral questions, and an optional follow-up. The process takes an average of 54 days from application to offer. Glassdoor rates difficulty at 3.1 out of 5 (medium).</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Yes. Delta's FAQ says Internship and MBA opportunities are "consistently hiring" and Co-Ops are "hired year round" for spring, summer, and fall rotations. Revie</t>
+          <t>No. Each function has its own posting and end date; for summer 2027 the live postings end October 12 to 17, 2026</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>MBA Supply Chain intern: $9,493/month (official). Undergrad interns ~$22–23/hr in official/community postings (a Minneapolis SWE role listed $22.56/hr); Glassdo</t>
+          <t>$21–$36/hr depending on role; housing stipend available for interns placed 50+ miles from home</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN NOW. Summer 2027 roles live on Delta's own Avature careers site include Finance, Commercial Strategy (both the intern and MBA versions), MBA Supply Chain Management, MBA Financial Strategy and Network Scheduling. We confirmed the Commercial Strategy intern requisition (job 33352, created August 5, 2026) was still open on August 15, 2026. Delta hires on a rolling basis and warns postings "may </t>
+          <t>Open now for summer 2027: IT and Telecommunications posted August 31, 2026; Engineering Internship &amp; Co-op Program, UX Design and others posted October 2. Posting end dates on the live reqs: UX Design October 12, IT and Telecommunications October 14, Engineering October 17, 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -2712,17 +2708,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern &amp; Co-op  (1 of 6 tracks)</t>
+          <t>Engineering &amp; Technology; Information Technology; Technical Sales; Engineering Services  (4 of 7 tracks)</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>dukeenergy.wd1.myworkdayjobs.com/en-US/Search</t>
+          <t>eaton.eightfold.ai/careers?query=%23EarlyTalent&amp;location=Uni</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2732,30 +2728,30 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Expect 2–3 rounds: a phone screen with a recruiter, a panel interview with 2–4 interviewers using STAR-method behavioral questions, and an optional follow-up. The process takes an average of 54 days from application to offer. Glassdoor rates difficulty at 3.1 out of 5 (medium).</t>
+          <t>For internships, Eaton uses a single interview experience lasting about one hour with two interviewers. It can be virtual (Microsoft Teams) or on campus. Expect a mix of behavioral questions using the STAR method and role-specific technical questions. Glassdoor rates the difficulty at 2.8–3.0 out of</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>No. Each function has its own posting and end date; for summer 2027 the live postings end October 12 to 17, 2026</t>
+          <t>No official statement; positions fill as posted. Average time from application to offer: 16 days</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>$21–$36/hr depending on role; housing stipend available for interns placed 50+ miles from home</t>
+          <t>$26–$47/hr across intern roles (Glassdoor); the live Summer 2027 Electrical role we checked posts $22.15–$27.69/hr; SWE interns up to $37/hr; plus lump-sum relo</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: IT and Telecommunications posted August 31, 2026; Engineering Internship &amp; Co-op Program, UX Design and others posted October 2. Posting end dates on the live reqs: UX Design October 12, IT and Telecommunications October 14, Engineering October 17, 2026</t>
+          <t>Open now: postings live since Aug 31, 2026 (about 30 US intern and co-op roles as of Oct 1); positions fill as they post</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -2765,17 +2761,17 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August 2026 – May 2027</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology; Information Technology; Technical Sales; Engineering Services  (4 of 7 tracks)</t>
+          <t>Data Science &amp; Analytics Intern; Digital Platforms &amp; AI Intern (DPAIO)  (2 of 5 tracks)</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>eaton.eightfold.ai/careers?query=%23EarlyTalent&amp;location=Uni</t>
+          <t>careers.elevancehealth.com/programs</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2785,30 +2781,30 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>For internships, Eaton uses a single interview experience lasting about one hour with two interviewers. It can be virtual (Microsoft Teams) or on campus. Expect a mix of behavioral questions using the STAR method and role-specific technical questions. Glassdoor rates the difficulty at 2.8–3.0 out of</t>
+          <t>Typically three to four stages: a resume/ATS screen, an asynchronous HireVue video interview with roughly three to five mostly-behavioral questions, a recruiter screen, and two to three panel or hiring-manager rounds via Microsoft Teams. Actuarial interviews lean heavily behavioral with lighter tech</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>No official statement; positions fill as posted. Average time from application to offer: 16 days</t>
+          <t>Effectively yes (community-labeled). Official postings warn "this job may close before the stated closing date, you are encouraged to apply as soon as possible.</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>$26–$47/hr across intern roles (Glassdoor); the live Summer 2027 Electrical role we checked posts $22.15–$27.69/hr; SWE interns up to $37/hr; plus lump-sum relo</t>
+          <t>Official rates not published. Community/aggregator data suggests ~$22 to $41 per hour by track (getsmartresume); Levels.fyi reports $33.33/hr for SWE interns. H</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Open now: postings live since Aug 31, 2026 (about 30 US intern and co-op roles as of Oct 1); positions fill as they post</t>
+          <t>OPEN NOW for Summer 2027: Actuarial Intern (posted Aug 27), Tax Intern (Sep 2), Finance Intern (Sep 17) and Information Security Co-Op 2027, all on the Workday portal with an anticipated end date of Nov 7, 2026 (may close earlier). Offers expected November 2026 to January 2027</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Etsy</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -2818,17 +2814,17 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – May 2027</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Data Science &amp; Analytics Intern; Digital Platforms &amp; AI Intern (DPAIO)  (2 of 5 tracks)</t>
+          <t>Software Engineering; Data Science / ML (periodic)  (2 of 3 tracks)</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>careers.elevancehealth.com/programs</t>
+          <t>etsy.wd5.myworkdayjobs.com/Etsy_Careers</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2838,30 +2834,30 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Typically three to four stages: a resume/ATS screen, an asynchronous HireVue video interview with roughly three to five mostly-behavioral questions, a recruiter screen, and two to three panel or hiring-manager rounds via Microsoft Teams. Actuarial interviews lean heavily behavioral with lighter tech</t>
+          <t>After applying, expect a recruiter phone screen followed by a HackerRank coding assessment (debugging or algorithm problems, 60 to 90 minutes). Finalists advance to a virtual onsite with two rounds: a live technical interview with screen-sharing and a behavioral interview with an engineering manager</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes (community-labeled). Official postings warn "this job may close before the stated closing date, you are encouraged to apply as soon as possible.</t>
+          <t>Yes, effectively. The 2026 posting was open roughly 2 months (September–November), and the most competitive candidates applied within the first 4 weeks</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Official rates not published. Community/aggregator data suggests ~$22 to $41 per hour by track (getsmartresume); Levels.fyi reports $33.33/hr for SWE interns. H</t>
+          <t>Estimated $50–$65/hr (~$8,000–$10,400/month) for SWE interns; housing/relocation stipend reportedly $3,000–$5,000</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for Summer 2027: Actuarial Intern (posted Aug 27), Tax Intern (Sep 2), Finance Intern (Sep 17) and Information Security Co-Op 2027, all on the Workday portal with an anticipated end date of Nov 7, 2026 (may close earlier). Offers expected November 2026 to January 2027</t>
+          <t>Expected August–September 2026 for summer 2027; August–September 2027 for summer 2028 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Etsy</t>
+          <t>Expedia</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -2871,17 +2867,17 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Science / ML (periodic)  (2 of 3 tracks)</t>
+          <t>Software Development Engineering; Cloud Engineering; Data Science &amp; Analytics; Machine Learning Science  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>etsy.wd5.myworkdayjobs.com/Etsy_Careers</t>
+          <t>careers.expediagroup.com/emerging-talent-and-careers/</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2891,30 +2887,30 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>After applying, expect a recruiter phone screen followed by a HackerRank coding assessment (debugging or algorithm problems, 60 to 90 minutes). Finalists advance to a virtual onsite with two rounds: a live technical interview with screen-sharing and a behavioral interview with an engineering manager</t>
+          <t xml:space="preserve">The process spans 4–8 weeks with 4–5 stages: a recruiter screen, a strength-based behavioral assessment, a HackerRank online assessment with 2 coding problems and MCQs, and then 2 back-to-back 60-minute technical interviews with LeetCode-style questions. Difficulty is Easy to Medium, notably easier </t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively. The 2026 posting was open roughly 2 months (September–November), and the most competitive candidates applied within the first 4 weeks</t>
+          <t>Yes. Most interview slots fill by mid-October; positions close once enough qualified candidates are received</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Estimated $50–$65/hr (~$8,000–$10,400/month) for SWE interns; housing/relocation stipend reportedly $3,000–$5,000</t>
+          <t>$45/hr for SWE ($7,800/month) + $2,000/mo housing or $6,000 lump sum; PM ~$35/hr + corporate housing</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Expected August–September 2026 for summer 2027; August–September 2027 for summer 2028 (documented pattern; not yet posted)</t>
+          <t>Expected August–October 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -2924,17 +2920,17 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Software Development Engineering; Cloud Engineering; Data Science &amp; Analytics; Machine Learning Science  (4 of 6 tracks)</t>
+          <t>Cybersecurity Intern; Data Engineering Intern; Data Science / Database Management Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>careers.expediagroup.com/emerging-talent-and-careers/</t>
+          <t>careers.fiserv.com/us/en/summer-internships</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -2944,30 +2940,34 @@
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The process spans 4–8 weeks with 4–5 stages: a recruiter screen, a strength-based behavioral assessment, a HackerRank online assessment with 2 coding problems and MCQs, and then 2 back-to-back 60-minute technical interviews with LeetCode-style questions. Difficulty is Easy to Medium, notably easier </t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
+          <t>Fiserv's funnel runs 3 to 4 rounds, with an average of about 25 days from application to hire and an interview difficulty of 2.6 out of 5: 1. Apply on careers.fiserv.com or the Workday portal . Create a profile, submit a one-page ATS-friendly resume highlighting projects, coursework, and internships</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>No. All positions require legal US work authorization. F-1 students may use CPT but Fiserv does not sponsor</t>
+        </is>
+      </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Yes. Most interview slots fill by mid-October; positions close once enough qualified candidates are received</t>
+          <t>Yes for technology tracks. Positions reviewed and filled rolling Sep through Dec. Finance track uses a shorter batch window</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>$45/hr for SWE ($7,800/month) + $2,000/mo housing or $6,000 lump sum; PM ~$35/hr + corporate housing</t>
+          <t>Tech intern $25–$30/hr at Berkeley Heights NJ ( Levels.fyi ). JD salary disclosure: $45,900–$62,100/year annualized</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Expected August–October 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Applications for summer 2027 expected to open Aug to Sep 2026 for tech tracks; finance may open with a very short window (as few as 6 days in past cycles). Projected pattern, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -2977,17 +2977,17 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Cybersecurity Intern; Data Engineering Intern; Data Science / Database Management Intern  (3 of 6 tracks)</t>
+          <t>R&amp;D / Engineering Intern; Digital &amp; Technology Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>careers.fiserv.com/us/en/summer-internships</t>
+          <t>careers.generalmills.com/campus</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2997,34 +2997,34 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Fiserv's funnel runs 3 to 4 rounds, with an average of about 25 days from application to hire and an interview difficulty of 2.6 out of 5: 1. Apply on careers.fiserv.com or the Workday portal . Create a profile, submit a one-page ATS-friendly resume highlighting projects, coursework, and internships</t>
+          <t>Resume review, a recruiter or campus screen, then one to two behavioral interviews explicitly scored in STAR format: situation, task, action, result. Some tracks add a case or technical exercise, like a business case for brand and finance or a coding conversation for Digital &amp; Technology. Offers fol</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>No. All positions require legal US work authorization. F-1 students may use CPT but Fiserv does not sponsor</t>
+          <t>Most US intern postings expect ongoing US work authorization without sponsorship. Community reports say brand and marketing intern roles are not sponsored, so read the sponsorship line on each posting</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Yes for technology tracks. Positions reviewed and filled rolling Sep through Dec. Finance track uses a shorter batch window</t>
+          <t>Effectively yes. Roles fill as fall campus recruiting proceeds, so apply when a posting opens and attend info sessions early</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Tech intern $25–$30/hr at Berkeley Heights NJ ( Levels.fyi ). JD salary disclosure: $45,900–$62,100/year annualized</t>
+          <t>Glassdoor pegs General Mills interns at roughly $26 to $47 per hour (about $35/hr average); community reports put MBA brand interns near $35 to $40/hr, with sub</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open Aug to Sep 2026 for tech tracks; finance may open with a very short window (as few as 6 days in past cycles). Projected pattern, not yet posted</t>
+          <t>Open now for summer 2027: the 14 internship requisitions went live in early August 2026 (Workday posting dates August 6 to 10) and were all still open on October 6, 2026. No closing date is posted; unfilled roles have reposted into winter and spring in past cycles</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>R&amp;D / Engineering Intern; Digital &amp; Technology Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering (Autonomous Driving); AI/ML Engineering; Manufacturing Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>careers.generalmills.com/campus</t>
+          <t>search-careers.gm.com/en/early-careers/internship-program/</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3054,34 +3054,30 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Resume review, a recruiter or campus screen, then one to two behavioral interviews explicitly scored in STAR format: situation, task, action, result. Some tracks add a case or technical exercise, like a business case for brand and finance or a coding conversation for Digital &amp; Technology. Offers fol</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>Most US intern postings expect ongoing US work authorization without sponsorship. Community reports say brand and marketing intern roles are not sponsored, so read the sponsorship line on each posting</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GM's hiring funnel averages 24 days from application to offer per Indeed data, though the full timeline spans 6–8 weeks when you count the rolling wait for assessment invitations: 1. Find and apply at search-careers.gm.com through the Workday portal. Upload your resume, use a permanent address (for </t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Roles fill as fall campus recruiting proceeds, so apply when a posting opens and attend info sessions early</t>
+          <t>Yes. No fixed deadlines; postings remain open until the applicant pool is sufficient</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Glassdoor pegs General Mills interns at roughly $26 to $47 per hour (about $35/hr average); community reports put MBA brand interns near $35 to $40/hr, with sub</t>
+          <t>$5,300–$10,600/mo by degree level + housing stipend for CA placements</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: the 14 internship requisitions went live in early August 2026 (Workday posting dates August 6 to 10) and were all still open on October 6, 2026. No closing date is posted; unfilled roles have reposted into winter and spring in past cycles</t>
+          <t>Open now for summer 2027: about 40 US requisitions posted August 17 to September 14, 2026; each req prints its own close date (Sales Intern closes October 9, 2026); start dates May 24 or June 14, 2027</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -3091,17 +3087,17 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (Autonomous Driving); AI/ML Engineering; Manufacturing Engineering  (3 of 6 tracks)</t>
+          <t>STEP (not posted for 2027); Software Engineering Intern; Student Researcher; Research Scientist Intern (PhD); Silicon / Hardware Engineering Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>search-careers.gm.com/en/early-careers/internship-program/</t>
+          <t>google.com/about/careers/applications/students/</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3111,30 +3107,34 @@
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GM's hiring funnel averages 24 days from application to offer per Indeed data, though the full timeline spans 6–8 weeks when you count the rolling wait for assessment invitations: 1. Find and apply at search-careers.gm.com through the Workday portal. Upload your resume, use a permanent address (for </t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+          <t>Google's funnel runs about 8 to 10 weeks from resume screen to decision, though recruiter contact alone can take 60-plus days: 1. Apply at careers.google.com with a resume that shows your graduation date in MM/YY plus a transcript or course list. You can submit up to 3 applications every 30 days, an</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>It depends on the role. Visa requirements differ across internships and are noted in each job description; your recruiter shares details after the initial screening. Google gives no blanket sponsorship promise on its off</t>
+        </is>
+      </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Yes. No fixed deadlines; postings remain open until the applicant pool is sufficient</t>
+          <t>Yes. Official JD: reviewed "on a rolling basis," and a posting "may close earlier if all available projects are full"</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>$5,300–$10,600/mo by degree level + housing stipend for CA placements</t>
+          <t>SWE intern median $62.98/hr plus ~$3,000/mo housing stipend (Levels.fyi, crowdsourced)</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: about 40 US requisitions posted August 17 to September 14, 2026; each req prints its own close date (Sales Intern closes October 9, 2026); start dates May 24 or June 14, 2027</t>
+          <t>OPEN NOW. August to October 2026, rolling, for summer 2027. SWE PhD and Research PhD Summer 2027 roles are live now</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>HashiCorp</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–November 2026</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>STEP (not posted for 2027); Software Engineering Intern; Student Researcher; Research Scientist Intern (PhD); Silicon / Hardware Engineering Intern  (5 of 6 tracks)</t>
+          <t>SWE Intern (Vault (primary); SWE Intern) Terraform; SWE Intern (Consul / Networking; SWE Intern) Cloud (HCP)  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>google.com/about/careers/applications/students/</t>
+          <t>hashicorp.com/en/careers</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3164,34 +3164,34 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>Google's funnel runs about 8 to 10 weeks from resume screen to decision, though recruiter contact alone can take 60-plus days: 1. Apply at careers.google.com with a resume that shows your graduation date in MM/YY plus a transcript or course list. You can submit up to 3 applications every 30 days, an</t>
+          <t>Five to six practical stages, not LeetCode: a recruiter screen, a hiring-manager/Principles screen, a technical assessment (async OA or live coding), a pair-programming round where you make failing tests pass, a distinctive code-review round where you review a PR as a teammate, and a system-design p</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>It depends on the role. Visa requirements differ across internships and are noted in each job description; your recruiter shares details after the initial screening. Google gives no blanket sponsorship promise on its off</t>
+          <t>Varies by req) IBM states some postings sponsor and some do not, and it is not guaranteed for interns. Check each posting's fine print</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official JD: reviewed "on a rolling basis," and a posting "may close earlier if all available projects are full"</t>
+          <t>Partly. IBM works through applications on a rolling basis and reaches out after you apply; HashiCorp loops have run from ~1 week to ~2 months. Apply early in th</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>SWE intern median $62.98/hr plus ~$3,000/mo housing stipend (Levels.fyi, crowdsourced)</t>
+          <t>~$46/hour (about $7,973/month) plus up to $7,000 relocation for recent US cycles (community levels.fyi, not official). IBM guarantees all internships are paid</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. August to October 2026, rolling, for summer 2027. SWE PhD and Research PhD Summer 2027 roles are live now</t>
+          <t>Expected ~August–November 2026 for a Summer 2027 start. IBM runs US intern hiring August to November each year; no firm 2027 date is published yet</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>HashiCorp</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>August–November 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Vault (primary); SWE Intern) Terraform; SWE Intern (Consul / Networking; SWE Intern) Cloud (HCP)  (4 of 5 tracks)</t>
+          <t>Corporate Internship, Technology; Corporate Internship, Data Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>hashicorp.com/en/careers</t>
+          <t>jobs.hilton.com/us/en/corpinternship</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -3221,34 +3221,30 @@
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Five to six practical stages, not LeetCode: a recruiter screen, a hiring-manager/Principles screen, a technical assessment (async OA or live coding), a pair-programming round where you make failing tests pass, a distinctive code-review round where you review a PR as a teammate, and a system-design p</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>Varies by req) IBM states some postings sponsor and some do not, and it is not guaranteed for interns. Check each posting's fine print</t>
-        </is>
-      </c>
+          <t>After applying, most candidates receive a HireVue one-way video interview with 5–7 behavioral questions (30 seconds prep, 3 minutes per answer). This is followed by a phone screen, one or two behavioral interviews using the STAR method, and a final round with senior leaders. The process takes roughl</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Partly. IBM works through applications on a rolling basis and reaches out after you apply; HashiCorp loops have run from ~1 week to ~2 months. Apply early in th</t>
+          <t xml:space="preserve">Yes. In earlier cycles nearly half of spots were allocated by November 1 and 60–80% were filled by a January deadline; the 2027 corporate postings came down by </t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>~$46/hour (about $7,973/month) plus up to $7,000 relocation for recent US cycles (community levels.fyi, not official). IBM guarantees all internships are paid</t>
+          <t>$22–$29/hr depending on track and location; Indeed average $22.83/hr; plus Go Hilton travel discounts</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Expected ~August–November 2026 for a Summer 2027 start. IBM runs US intern hiring August to November each year; no firm 2027 date is published yet</t>
+          <t>CORPORATE WINDOW CLOSED. The 2027 Corporate Summer Internship postings (about 18 US tracks across McLean, Dallas and Memphis) went live in mid-August 2026 and were no longer on Hilton's careers system as of September 27, 2026; one late Memphis posting, the 2027 Corporate 12-month Internship in Accounting and Financial Services, went up September 28 with a listing end date of October 2, 2026, so tr</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -3258,17 +3254,17 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Corporate Internship, Technology; Corporate Internship, Data Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineering; Cybersecurity; Data Science (UG)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>jobs.hilton.com/us/en/corpinternship</t>
+          <t>careers.homedepot.com/students-internships/</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3278,30 +3274,34 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>After applying, most candidates receive a HireVue one-way video interview with 5–7 behavioral questions (30 seconds prep, 3 minutes per answer). This is followed by a phone screen, one or two behavioral interviews using the STAR method, and a final round with senior leaders. The process takes roughl</t>
-        </is>
-      </c>
-      <c r="H51" s="6" t="inlineStr"/>
+          <t>Home Depot's funnel runs 2–4 weeks from first interview to offer, faster than most Fortune 50 programs: 1. Create a profile at careers.homedepot.com and upload your resume (PDF or Word, under 5MB). A cover letter is optional but recommended for business tracks. Complete the 3–5 role-specific screeni</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>F-1 students on CPT are explicitly accepted. OPT is also eligible. H-1B sponsorship for interns is described as "case-by-case" and isn't guaranteed. Full-time H-1B sponsorship is more common after conversion.</t>
+        </is>
+      </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. In earlier cycles nearly half of spots were allocated by November 1 and 60–80% were filled by a January deadline; the 2027 corporate postings came down by </t>
+          <t>Yes. Tech roles fill by mid-October; business roles extend into January</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>$22–$29/hr depending on track and location; Indeed average $22.83/hr; plus Go Hilton travel discounts</t>
+          <t>$24–$27/hr SWE and Cybersecurity (official); $22–$35/hr across all tracks</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>CORPORATE WINDOW CLOSED. The 2027 Corporate Summer Internship postings (about 18 US tracks across McLean, Dallas and Memphis) went live in mid-August 2026 and were no longer on Hilton's careers system as of September 27, 2026; one late Memphis posting, the 2027 Corporate 12-month Internship in Accounting and Financial Services, went up September 28 with a listing end date of October 2, 2026, so tr</t>
+          <t>Open now for summer 2027: 11 requisitions live since August 31, 2026; "Applications are accepted on an ongoing basis" (employer header); program May 17 to July 30, 2027</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Cybersecurity; Data Science (UG)  (3 of 6 tracks)</t>
+          <t>Engineering; IT / Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>careers.homedepot.com/students-internships/</t>
+          <t>careers.honeywell.com/us/en/students-graduates</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3331,34 +3331,34 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Home Depot's funnel runs 2–4 weeks from first interview to offer, faster than most Fortune 50 programs: 1. Create a profile at careers.homedepot.com and upload your resume (PDF or Word, under 5MB). A cover letter is optional but recommended for business tracks. Complete the 3–5 role-specific screeni</t>
+          <t>Two to three stages: an online coding assessment on HackerRank or HackerEarth with 3 medium-to-hard questions and a 90-minute time limit (for technical roles), followed by a combined technical and HR interview lasting 20–45 minutes. Some roles add a panel interview with the hiring manager and future</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>F-1 students on CPT are explicitly accepted. OPT is also eligible. H-1B sponsorship for interns is described as "case-by-case" and isn't guaranteed. Full-time H-1B sponsorship is more common after conversion.</t>
+          <t>No. Honeywell doesn't sponsor employment visas for interns. You must be authorized to work in the United States without current or future sponsorship. International students on valid CPT or OPT authorization are generall</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Yes. Tech roles fill by mid-October; business roles extend into January</t>
+          <t>Yes. Applications are reviewed from day one and roles close when filled</t>
         </is>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>$24–$27/hr SWE and Cybersecurity (official); $22–$35/hr across all tracks</t>
+          <t>$19–$42/hr depending on role; SWE interns average ~$36.50/hr, engineering interns ~$24–$27/hr</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 11 requisitions live since August 31, 2026; "Applications are accepted on an ongoing basis" (employer header); program May 17 to July 30, 2027</t>
+          <t>Open now for summer 2027: 26 US intern requisitions posted August 25 to 27, 2026. Apply Before March 31, 2027 (printed on each requisition; Honeywell says the period may be shortened)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Honeywell Aerospace</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -3368,17 +3368,17 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Engineering; IT / Technology  (2 of 6 tracks)</t>
+          <t>Aerospace/Aeronautical Engineering Intern; Aerospace Development Program (Engineering); Software Engineering Intern; Mechanical Engineering Intern; Electrical Engineering Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>careers.honeywell.com/us/en/students-graduates</t>
+          <t>icfcjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/s</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -3388,34 +3388,34 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Two to three stages: an online coding assessment on HackerRank or HackerEarth with 3 medium-to-hard questions and a 90-minute time limit (for technical roles), followed by a combined technical and HR interview lasting 20–45 minutes. Some roles add a panel interview with the hiring manager and future</t>
+          <t>After applying online, candidates complete aptitude assessments, then move to a phone screen with HR covering behavioral questions. Finalists interview with the hiring team, often including both behavioral and technical questions. Some roles include an assessment center with individual and group exe</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>No. Honeywell doesn't sponsor employment visas for interns. You must be authorized to work in the United States without current or future sponsorship. International students on valid CPT or OPT authorization are generall</t>
+          <t>Most Honeywell Aerospace internships require applicants to be a U.S. Person (U.S. citizen, permanent resident, or asylee/refugee) due to ITAR and EAR export control regulations. Honeywell states it can't consider applica</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed from day one and roles close when filled</t>
+          <t>Effectively yes. JDs state they "may close before the stated closing date"</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>$19–$42/hr depending on role; SWE interns average ~$36.50/hr, engineering interns ~$24–$27/hr</t>
+          <t>$20 to $42/hr posted range; aerospace engineer interns report $42/hr, software engineer interns $36.50/hr (Levels.fyi)</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 26 US intern requisitions posted August 25 to 27, 2026. Apply Before March 31, 2027 (printed on each requisition; Honeywell says the period may be shortened)</t>
+          <t>Open now for summer 2027: 36 US intern requisitions posted August 27 to September 8, 2026. Employer's estimate: applications accepted through the end of March 2027, which it says may be shortened as positions fill</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -3425,17 +3425,17 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–December 2026</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Aerospace/Aeronautical Engineering Intern; Aerospace Development Program (Engineering); Software Engineering Intern; Mechanical Engineering Intern; Electrical Engineering Intern  (5 of 6 tracks)</t>
+          <t>IT / Technology Internship; Graduate Analytics Internship; Data Science / Informatics Internship  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>icfcjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/s</t>
+          <t>careers.humana.com/us/en/students-professional-programs</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -3445,34 +3445,34 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>After applying online, candidates complete aptitude assessments, then move to a phone screen with HR covering behavioral questions. Finalists interview with the hiring team, often including both behavioral and technical questions. Some roles include an assessment center with individual and group exe</t>
+          <t>A resume/ATS screen, a recruiter phone screen (~20–30 min), a pre-recorded video interview with behavioral questions, then two to three formal rounds (behavioral STAR plus a technical or case component), and reference checks for finalists. Expect roughly 8–12 weeks from application to offer.</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Most Honeywell Aerospace internships require applicants to be a U.S. Person (U.S. citizen, permanent resident, or asylee/refugee) due to ITAR and EAR export control regulations. Honeywell states it can't consider applica</t>
+          <t>No. Postings state Humana "does not provide visa sponsorship or support for OPT/CPT/J1," and candidates must not require sponsorship now or in the future. This is a hard filter for F-1/OPT and H-1B-track international st</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. JDs state they "may close before the stated closing date"</t>
+          <t>Yes (expected). The prior cycle used rolling admissions with a mid-October priority deadline; postings are removed once a track is filled (the Summer 2026 actua</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>$20 to $42/hr posted range; aerospace engineer interns report $42/hr, software engineer interns $36.50/hr (Levels.fyi)</t>
+          <t>Paid. Summer 2026 actuarial and IT postings listed a wide $37,440–$96,800/year band (actual intern pay sits toward the lower/middle); travel and housing provide</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 36 US intern requisitions posted August 27 to September 8, 2026. Employer's estimate: applications accepted through the end of March 2027, which it says may be shortened as positions fill</t>
+          <t>OPEN NOW. Summer 2027 roles are live on careers.humana.com as of August 2026, including Actuarial Internship and Technology Internship. Priority deadline around mid-October 2026; rolling admissions through December 2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>August–December 2026</t>
+          <t>August 2026 – June 2027</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>IT / Technology Internship; Graduate Analytics Internship; Data Science / Informatics Internship  (3 of 5 tracks)</t>
+          <t>Software Engineering Internship; Data Science &amp; Analytics Internship; Machine Learning PhD Internship  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>careers.humana.com/us/en/students-professional-programs</t>
+          <t>instacart.careers/current-openings</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -3502,34 +3502,30 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>A resume/ATS screen, a recruiter phone screen (~20–30 min), a pre-recorded video interview with behavioral questions, then two to three formal rounds (behavioral STAR plus a technical or case component), and reference checks for finalists. Expect roughly 8–12 weeks from application to offer.</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>No. Postings state Humana "does not provide visa sponsorship or support for OPT/CPT/J1," and candidates must not require sponsorship now or in the future. This is a hard filter for F-1/OPT and H-1B-track international st</t>
-        </is>
-      </c>
+          <t xml:space="preserve">SWE candidates go through a five-stage pipeline: resume screening, a 70-minute CodeSignal assessment with 4 tasks scored 300–850, a 30-minute recruiter call, a 45–60 minute live coding screen via CoderPad, and a virtual onsite with 3–4 rounds covering coding, system design, behavioral, and a hiring </t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>Yes (expected). The prior cycle used rolling admissions with a mid-October priority deadline; postings are removed once a track is filled (the Summer 2026 actua</t>
+          <t>Effectively yes. Optimal submission is the first 3 weeks after posting; early applicants hear back in 5–7 days</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Paid. Summer 2026 actuarial and IT postings listed a wide $37,440–$96,800/year band (actual intern pay sits toward the lower/middle); travel and housing provide</t>
+          <t>SWE: $9,500–$10,500/mo; DS: $8,500–$9,500/mo; plus $3,000–$4,000 housing stipend</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 roles are live on careers.humana.com as of August 2026, including Actuarial Internship and Technology Internship. Priority deadline around mid-October 2026; rolling admissions through December 2026</t>
+          <t>Expected Aug–Sep 2026 for SWE/DS summer 2027; APM: ~10 days in early March 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -3539,17 +3535,17 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – June 2027</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Internship; Data Science &amp; Analytics Internship; Machine Learning PhD Internship  (3 of 4 tracks)</t>
+          <t>Software Engineering; Mechanical Engineering; Computer Vision / AI; Electrical Engineering; Manufacturing Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>instacart.careers/current-openings</t>
+          <t>careers.intuitive.com/en/career-opportunities/students-and-u</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -3559,30 +3555,34 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE candidates go through a five-stage pipeline: resume screening, a 70-minute CodeSignal assessment with 4 tasks scored 300–850, a 30-minute recruiter call, a 45–60 minute live coding screen via CoderPad, and a virtual onsite with 3–4 rounds covering coding, system design, behavioral, and a hiring </t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr"/>
+          <t>Two main stages: a 30–45 minute phone screen with the hiring manager (not a recruiter), then a 2–2.5 hour Zoom interview with the hiring team including both technical and behavioral components. Some roles include a final VP interview. Intuitive uses a C-C-E-E (Character, Capacity, Energy, Experience</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>Not on every role. International students on F-1 visas in the US are eligible for many postings, making Intuitive more accessible than competitors like Medtronic (which excludes F-1/OPT/CPT), but check each one: the summ</t>
+        </is>
+      </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Optimal submission is the first 3 weeks after posting; early applicants hear back in 5–7 days</t>
+          <t>Yes. Every hiring team proceeds to interviews at different points; positions fill continuously</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>SWE: $9,500–$10,500/mo; DS: $8,500–$9,500/mo; plus $3,000–$4,000 housing stipend</t>
+          <t>$44–$82/hr depending on role and education level, plus housing allowance</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>Expected Aug–Sep 2026 for SWE/DS summer 2027; APM: ~10 days in early March 2027 (documented pattern; not yet posted)</t>
+          <t>Open now: first summer 2027 postings live since Aug 31, 2026; rolling through spring 2027 (no single deadline)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -3592,17 +3592,17 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August 2026 – March 2027</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Mechanical Engineering; Computer Vision / AI; Electrical Engineering; Manufacturing Engineering  (5 of 6 tracks)</t>
+          <t>Engineering; IT / Software Engineering; Data Science &amp; Analytics  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>careers.intuitive.com/en/career-opportunities/students-and-u</t>
+          <t>careers.deere.com/careers?seniority=Intern&amp;domain=johndeere.</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -3612,34 +3612,34 @@
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Two main stages: a 30–45 minute phone screen with the hiring manager (not a recruiter), then a 2–2.5 hour Zoom interview with the hiring team including both technical and behavioral components. Some roles include a final VP interview. Intuitive uses a C-C-E-E (Character, Capacity, Energy, Experience</t>
+          <t>An online application, then for IT/SWE a HackerRank Fullstack Assessment, followed by a phone screen with HR and a one-on-one behavioral interview with the hiring manager. Average time from application to hire is about 19 days. Glassdoor rates difficulty at 3.1 out of 5, with 87% positive experience</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Not on every role. International students on F-1 visas in the US are eligible for many postings, making Intuitive more accessible than competitors like Medtronic (which excludes F-1/OPT/CPT), but check each one: the summ</t>
+          <t>Generally not available. Most postings state "US Visa sponsorship isn't available." Some IT roles accept F-1/CPT; check each listing</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Yes. Every hiring team proceeds to interviews at different points; positions fill continuously</t>
+          <t>Likely yes. Postings note "this job may close before the stated closing date, you're encouraged to apply as soon as possible"</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>$44–$82/hr depending on role and education level, plus housing allowance</t>
+          <t>$23 to $36/hr depending on role and location; SWE interns report $28–36/hr (Levels.fyi). Sponsored housing, relocation assistance, 401(k), healthcare</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>Open now: first summer 2027 postings live since Aug 31, 2026; rolling through spring 2027 (no single deadline)</t>
+          <t>Open now for summer 2027: twelve US 2027 intern requisitions went live August 31 to September 22, 2026 (Accounting and Finance, IT, Data and Analytics, A&amp;T and C&amp;F Marketing and Sales, Supply Management and Logistics, HR and Labor Relations, Product, Manufacturing and Weld Engineering, Environmental Engineering in Ankeny, and Manufacturing and Product Engineering in Coffeyville KS). On the prior p</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Jump Trading</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -3649,17 +3649,17 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – March 2027</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Engineering; IT / Software Engineering; Data Science &amp; Analytics  (3 of 6 tracks)</t>
+          <t>Campus Quantitative Trader (Intern); Campus Quantitative Researcher (Intern); Campus AI Research Engineer (Intern); Campus Software Engineer (Intern); Campus Data Engineer / UI Software Engineer (Intern); Campus Systems Engineer (Intern); Campus FPGA Engineer (Intern)</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>careers.deere.com/careers?seniority=Intern&amp;domain=johndeere.</t>
+          <t>jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -3669,34 +3669,34 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>An online application, then for IT/SWE a HackerRank Fullstack Assessment, followed by a phone screen with HR and a one-on-one behavioral interview with the hiring manager. Average time from application to hire is about 19 days. Glassdoor rates difficulty at 3.1 out of 5, with 87% positive experience</t>
+          <t>Typically 4 to 5 rounds over 3 to 6 weeks: a timed online assessment with algorithmic problems, 1 to 2 phone screens with live C++ coding, 2 to 3 on-site interviews covering advanced C++, system design, mathematics, and probability, then a final team-match discussion. The bar is comparable to HRT an</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>Generally not available. Most postings state "US Visa sponsorship isn't available." Some IT roles accept F-1/CPT; check each listing</t>
+          <t>International students encouraged to apply; CPT/OPT-eligible candidates accepted. The firm sponsors work visas for full-time positions</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Postings note "this job may close before the stated closing date, you're encouraged to apply as soon as possible"</t>
+          <t>Effectively yes. No published deadlines; positions are filled as suitable candidates are identified. Apply early</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>$23 to $36/hr depending on role and location; SWE interns report $28–36/hr (Levels.fyi). Sponsored housing, relocation assistance, 401(k), healthcare</t>
+          <t>SWE Chicago $120/hr ($20,833/month) with corporate housing and $20K sign-on (Summer 2026 data, Levels.fyi). Annualized total comp estimated at $170K–$210K prora</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: twelve US 2027 intern requisitions went live August 31 to September 22, 2026 (Accounting and Finance, IT, Data and Analytics, A&amp;T and C&amp;F Marketing and Sales, Supply Management and Logistics, HR and Labor Relations, Product, Manufacturing and Weld Engineering, Environmental Engineering in Ankeny, and Manufacturing and Product Engineering in Coffeyville KS). On the prior p</t>
+          <t>OPEN NOW for summer 2027. Jump's students and new grads page states it is "opening 2027 roles by region, starting with the US." 11 US intern requisitions (Chicago and New York) were live on August 15, 2026. No published closing date; review is rolling and seats fill as candidates are identified</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Campus Quantitative Trader (Intern); Campus Quantitative Researcher (Intern); Campus AI Research Engineer (Intern); Campus Software Engineer (Intern); Campus Data Engineer / UI Software Engineer (Intern); Campus Systems Engineer (Intern); Campus FPGA Engineer (Intern)</t>
+          <t>IT / Information Technology Intern; Engineering / Manufacturing Intern (+ Finance, HR, EH&amp;S)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>jumptrading.com/hr/students-new-grads</t>
+          <t>careers.keurigdrpepper.com/en/campusjobs</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -3726,34 +3726,34 @@
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Typically 4 to 5 rounds over 3 to 6 weeks: a timed online assessment with algorithmic problems, 1 to 2 phone screens with live C++ coding, 2 to 3 on-site interviews covering advanced C++, system design, mathematics, and probability, then a final team-match discussion. The bar is comparable to HRT an</t>
+          <t>Apply online, then a resume screen, then a HireVue one-way video interview with five KDP values-based questions, then hiring-manager review, then live team interview(s), then an offer. Technical roles add a ~60-minute technical round. Glassdoor rates the interview experience 55% positive with an ave</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>International students encouraged to apply; CPT/OPT-eligible candidates accepted. The firm sponsors work visas for full-time positions</t>
+          <t>No, for interns. Intern JDs require existing US work authorization with no future sponsorship need; F-1 students needing future sponsorship are explicitly excluded. (KDP does sponsor H-1B for some full-time hires, but no</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. No published deadlines; positions are filled as suitable candidates are identified. Apply early</t>
+          <t>Partially. KDP posts specific, dated intern requisitions (e.g., "Summer 2026 Intern - Supply Chain Analyst") and reviews them on a rolling basis per requisition</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>SWE Chicago $120/hr ($20,833/month) with corporate housing and $20K sign-on (Summer 2026 data, Levels.fyi). Annualized total comp estimated at $170K–$210K prora</t>
+          <t>Officially posted: $31.00/hour plus a $2,500 sign-on bonus (undergrad Supply Chain Analyst, Frisco); $2,250/week (≈$56.25/hr) for the MBA Associate Brand Manage</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027. Jump's students and new grads page states it is "opening 2027 roles by region, starting with the US." 11 US intern requisitions (Chicago and New York) were live on August 15, 2026. No published closing date; review is rolling and seats fill as candidates are identified</t>
+          <t>OPEN NOW. Summer 2027 Intern roles are live across Supply Chain, Operations Management, and other tracks as of August 2026. Rolling review; popular Frisco corporate roles fill fast</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>IT / Information Technology Intern; Engineering / Manufacturing Intern (+ Finance, HR, EH&amp;S)  (2 of 6 tracks)</t>
+          <t>Ticketmaster Software Engineering; LN Concerts, Talent Analytics &amp; Finance  (2 of 7 tracks)</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>careers.keurigdrpepper.com/en/campusjobs</t>
+          <t>livenation.wd1.myworkdayjobs.com/LNExternalSite</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -3783,34 +3783,34 @@
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>Apply online, then a resume screen, then a HireVue one-way video interview with five KDP values-based questions, then hiring-manager review, then live team interview(s), then an offer. Technical roles add a ~60-minute technical round. Glassdoor rates the interview experience 55% positive with an ave</t>
+          <t>Most candidates start with a HireVue on-demand video or a 20–30 minute recruiter call, then a 45–60 minute hiring manager interview with behavioral and situational questions. Ticketmaster tech roles add a HackerRank coding challenge. Glassdoor rates the intern interview difficulty at 2.5 out of 5, w</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>No, for interns. Intern JDs require existing US work authorization with no future sponsorship need; F-1 students needing future sponsorship are explicitly excluded. (KDP does sponsor H-1B for some full-time hires, but no</t>
+          <t>Live Nation requires US work authorization and doesn't provide H-1B visa sponsorship for internships. International students on F-1 visas can qualify by securing CPT through their university before the start date. OPT an</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Partially. KDP posts specific, dated intern requisitions (e.g., "Summer 2026 Intern - Supply Chain Analyst") and reviews them on a rolling basis per requisition</t>
+          <t>Yes, de facto. Positions close as they fill; the posted deadline (e.g., Feb 1 for College Associate) is a ceiling, not a target</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Officially posted: $31.00/hour plus a $2,500 sign-on bonus (undergrad Supply Chain Analyst, Frisco); $2,250/week (≈$56.25/hr) for the MBA Associate Brand Manage</t>
+          <t>Corporate/marketing: $16–$22/hr; College Associate (Media &amp; Sponsorship): ~$20/hr; Ticketmaster SWE: $35–$55/hr</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 Intern roles are live across Supply Chain, Operations Management, and other tracks as of August 2026. Rolling review; popular Frisco corporate roles fill fast</t>
+          <t>Expected September–October 2026 for College Associate and Venue Nation; Ticketmaster tech opened in late August in the 2026 cycle but had not posted as of September 27, 2026 (documented 2026-cycle pattern)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Ticketmaster Software Engineering; LN Concerts, Talent Analytics &amp; Finance  (2 of 7 tracks)</t>
+          <t>R&amp;D Engineering; Software Engineering; Quality Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>livenation.wd1.myworkdayjobs.com/LNExternalSite</t>
+          <t>medtronic.com/en-us/our-company/careers/early-careers.html</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -3840,34 +3840,34 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Most candidates start with a HireVue on-demand video or a 20–30 minute recruiter call, then a 45–60 minute hiring manager interview with behavioral and situational questions. Ticketmaster tech roles add a HackerRank coding challenge. Glassdoor rates the intern interview difficulty at 2.5 out of 5, w</t>
+          <t>Two rounds after the online assessment: a 20-to-30-minute HR phone screen covering background and fit, then a Zoom interview with the hiring manager focused on behavioral STAR questions and light technical discussion. Glassdoor rates difficulty 2.8 out of 5. No in-person interview is required.</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>Live Nation requires US work authorization and doesn't provide H-1B visa sponsorship for internships. International students on F-1 visas can qualify by securing CPT through their university before the start date. OPT an</t>
+          <t xml:space="preserve">No. The program explicitly does not provide work-authorization sponsorship of any kind. Candidates must be U.S. citizens or permanent residents. F-1 OPT/CPT is not accepted, and the posting names F-1, E, H-1, H-2, L, B, </t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>Yes, de facto. Positions close as they fill; the posted deadline (e.g., Feb 1 for College Associate) is a ceiling, not a target</t>
+          <t>Yes. Medtronic reviews and extends offers as applications arrive; positions may close early</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Corporate/marketing: $16–$22/hr; College Associate (Media &amp; Sponsorship): ~$20/hr; Ticketmaster SWE: $35–$55/hr</t>
+          <t>$22–$45/hr depending on track, plus $4,000–$7,000 housing stipend for relocating interns</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Expected September–October 2026 for College Associate and Venue Nation; Ticketmaster tech opened in late August in the 2026 cycle but had not posted as of September 27, 2026 (documented 2026-cycle pattern)</t>
+          <t>OPEN NOW. Summer 2027 roles are live on Medtronic's Workday portal as of August 2026, including Software Engineering, Supply Chain, and Operations Engineering. Application window expected to close around mid-October 2026 (rolling)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering; Software Engineering; Quality Engineering  (3 of 6 tracks)</t>
+          <t>Software Engineering; Data Science; Hardware Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>medtronic.com/en-us/our-company/careers/early-careers.html</t>
+          <t>careers.microsoft.com/students/</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -3897,34 +3897,34 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Two rounds after the online assessment: a 20-to-30-minute HR phone screen covering background and fit, then a Zoom interview with the hiring manager focused on behavioral STAR questions and light technical discussion. Glassdoor rates difficulty 2.8 out of 5. No in-person interview is required.</t>
+          <t>Average 37 days from application to hire decision (Glassdoor data, 141 submissions). The typical flow: resume screen (1–3 weeks), OA (1 week to complete), interview loop (1–4 weeks after OA), then offer (1–2 weeks after final loop).</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. The program explicitly does not provide work-authorization sponsorship of any kind. Candidates must be U.S. citizens or permanent residents. F-1 OPT/CPT is not accepted, and the posting names F-1, E, H-1, H-2, L, B, </t>
+          <t>Yes. Most international students at US universities use CPT (Curricular Practical Training) under their F-1 visa, which does not require employer sponsorship. Microsoft is also one of the largest H-1B sponsors for full-t</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>Yes. Medtronic reviews and extends offers as applications arrive; positions may close early</t>
+          <t>Yes. Offers go out in waves Oct–Dec; first-come advantage is well documented</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>$22–$45/hr depending on track, plus $4,000–$7,000 housing stipend for relocating interns</t>
+          <t>SWE ~$52.50/hr + $7K–$10K housing; Research PhD up to $76.56/hr; official monthly $5,460–$13,270</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 roles are live on Medtronic's Workday portal as of August 2026, including Software Engineering, Supply Chain, and Operations Engineering. Application window expected to close around mid-October 2026 (rolling)</t>
+          <t>Open now, in waves: US intern requisitions posting continuously since August 10, 2026 on apply.careers.microsoft.com (20 live in mid-September across hardware, cleared software, PM, supply chain, finance); the university SWE intern postings appeared around September 3 and closed within nine days. No year or deadline is printed; rolling</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Navan</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -3934,17 +3934,17 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Science; Hardware Engineering  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern; AI/ML Research Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>careers.microsoft.com/students/</t>
+          <t>navan.com/careers/openings</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -3954,34 +3954,34 @@
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Average 37 days from application to hire decision (Glassdoor data, 141 submissions). The typical flow: resume screen (1–3 weeks), OA (1 week to complete), interview loop (1–4 weeks after OA), then offer (1–2 weeks after final loop).</t>
+          <t>Navan's intern interview funnel spans 3 to 4 stages for engineering roles, condensed from the full-time 5-round process: 1. Apply on navan.com/careers/openings . Search for internship or Compass program roles and submit. Monitor the page starting late summer 2026. Navan's candidate resources page re</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Yes. Most international students at US universities use CPT (Curricular Practical Training) under their F-1 visa, which does not require employer sponsorship. Microsoft is also one of the largest H-1B sponsors for full-t</t>
+          <t>Navan sponsors H-1B visas for full-time employees (18 LCAs filed, all certified). The 2022 Compass cohort included an international student from Vietnam, suggesting CPT support for interns</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Yes. Offers go out in waves Oct–Dec; first-come advantage is well documented</t>
+          <t>Likely cohort-based, not rolling. The structured Compass branding, small cohort sizes, and early finalization suggest a fixed review window rather than continuo</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>SWE ~$52.50/hr + $7K–$10K housing; Research PhD up to $76.56/hr; official monthly $5,460–$13,270</t>
+          <t>Estimated $40 to $55 per hour ($6,900 to $9,500/month) for SWE interns in the Bay Area. Glassdoor reports an average of approximately $34/hour across all intern</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Open now, in waves: US intern requisitions posting continuously since August 10, 2026 on apply.careers.microsoft.com (20 live in mid-September across hardware, cleared software, PM, supply chain, finance); the university SWE intern postings appeared around September 3 and closed within nine days. No year or deadline is printed; rolling</t>
+          <t>Expected August to October 2026 for summer 2027 roles. Navan does not publish a public timeline; selections are finalized well before the program starts. Projected from 2022–2023 Compass cycles</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Navan</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; AI/ML Research Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern; Machine Learning Engineer Intern; Machine Learning/AI Scientist Intern; Data Engineering Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>navan.com/careers/openings</t>
+          <t>jobs.netflix.com/careers/internships</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -4011,34 +4011,30 @@
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Navan's intern interview funnel spans 3 to 4 stages for engineering roles, condensed from the full-time 5-round process: 1. Apply on navan.com/careers/openings . Search for internship or Compass program roles and submit. Monitor the page starting late summer 2026. Navan's candidate resources page re</t>
-        </is>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>Navan sponsors H-1B visas for full-time employees (18 LCAs filed, all certified). The 2022 Compass cohort included an international student from Vietnam, suggesting CPT support for interns</t>
-        </is>
-      </c>
+          <t>Officially, a take-home assessment followed by approximately two to three interview rounds. Candidates report the SWE take-home is a two-part CodeSignal assessment of roughly 90 minutes each, including an AI-assisted coding section, then live coding, system design, and a hiring-manager round.</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Likely cohort-based, not rolling. The structured Compass branding, small cohort sizes, and early finalization suggest a fixed review window rather than continuo</t>
+          <t>Yes. Postings stay open "no less than 7 days" and come down when filled; specialist and PhD roles roll December into spring</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>Estimated $40 to $55 per hour ($6,900 to $9,500/month) for SWE interns in the Bay Area. Glassdoor reports an average of approximately $34/hour across all intern</t>
+          <t>$40 to $110/hr official JD ranges; SWE median $63/hr plus $10,000 housing (Levels.fyi, self-reported)</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>Expected August to October 2026 for summer 2027 roles. Navan does not publish a public timeline; selections are finalized well before the program starts. Projected from 2022–2023 Compass cycles</t>
+          <t>Applications for summer 2027 expected to open ~mid-August to October 2026, rolling to March 2027; the flagship SWE role opened ~Oct 1 and closed Oct 31, 2025 last cycle (documented pattern; summer 2027 roles not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Nissan</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -4053,12 +4049,12 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Machine Learning Engineer Intern; Machine Learning/AI Scientist Intern; Data Engineering Intern  (4 of 6 tracks)</t>
+          <t>R&amp;D Engineering; Supply Chain Analytics; Software Engineering; Data Science / Analytics; Manufacturing / Process Engineering  (5 of 7 tracks)</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>jobs.netflix.com/careers/internships</t>
+          <t>alliance.wd3.myworkdayjobs.com/en-US/nissanjobs</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4068,30 +4064,34 @@
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>Officially, a take-home assessment followed by approximately two to three interview rounds. Candidates report the SWE take-home is a two-part CodeSignal assessment of roughly 90 minutes each, including an AI-assisted coding section, then live coding, system design, and a hiring-manager round.</t>
-        </is>
-      </c>
-      <c r="H65" s="6" t="inlineStr"/>
+          <t>The process is relatively straightforward. After applying online, selected candidates have a recruiter phone or video screen, followed by an interview with the hiring manager (sometimes a panel of 2 to 3 people). Glassdoor rates the difficulty at 2.4 out of 5 for Nissan North America intern roles wi</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>No. Multiple Nissan internship postings explicitly state no sponsorship. Candidates must be legally authorized to work in the United States without employer sponsorship. E-Verify is used to validate employment eligibilit</t>
+        </is>
+      </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Yes. Postings stay open "no less than 7 days" and come down when filled; specialist and PhD roles roll December into spring</t>
+          <t>Likely yes. Positions are removed as they fill; last cycle's postings came down by mid-October</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>$40 to $110/hr official JD ranges; SWE median $63/hr plus $10,000 housing (Levels.fyi, self-reported)</t>
+          <t>$21–$28/hr reported range; top-end $27.54/hr (Levels.fyi). Plus company car and potential housing</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open ~mid-August to October 2026, rolling to March 2027; the flagship SWE role opened ~Oct 1 and closed Oct 31, 2025 last cycle (documented pattern; summer 2027 roles not yet posted)</t>
+          <t>Expected August–October 2026 for Summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Nissan</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -4101,17 +4101,17 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering; Supply Chain Analytics; Software Engineering; Data Science / Analytics; Manufacturing / Process Engineering  (5 of 7 tracks)</t>
+          <t>Software Engineering; Deep Learning / AI Research; Hardware Engineering (ASIC/VLSI); CUDA / ML Systems &amp; Compilers  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>alliance.wd3.myworkdayjobs.com/en-US/nissanjobs</t>
+          <t>nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4121,34 +4121,30 @@
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>The process is relatively straightforward. After applying online, selected candidates have a recruiter phone or video screen, followed by an interview with the hiring manager (sometimes a panel of 2 to 3 people). Glassdoor rates the difficulty at 2.4 out of 5 for Nissan North America intern roles wi</t>
-        </is>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>No. Multiple Nissan internship postings explicitly state no sponsorship. Candidates must be legally authorized to work in the United States without employer sponsorship. E-Verify is used to validate employment eligibilit</t>
-        </is>
-      </c>
+          <t>Technical and thorough. Many software roles start with a HackerRank assessment (two to three coding questions plus multiple-choice, LeetCode-medium), then three to five technical rounds of live coding and C++ or OS deep-dives, plus a project discussion. Research roles focus on publications.</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Positions are removed as they fill; last cycle's postings came down by mid-October</t>
+          <t>Yes. JDs say NVIDIA "accepts applications on an ongoing basis"; ~60% of offers out by end of November</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>$21–$28/hr reported range; top-end $27.54/hr (Levels.fyi). Plus company car and potential housing</t>
+          <t>$20 to $94/hr NVIDIA-stated JD range, roughly $6.7k to $10k/mo, plus housing stipend and relocation</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Expected August–October 2026 for Summer 2027 (documented pattern; not yet posted)</t>
+          <t>Open now for summer 2027: 20 US 2027-titled intern requisitions live since August 19, 2026 (13-track NVIDIA 2027 Internships series plus PhD research); no close date printed on the requisitions</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -4158,17 +4154,17 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Deep Learning / AI Research; Hardware Engineering (ASIC/VLSI); CUDA / ML Systems &amp; Compilers  (4 of 6 tracks)</t>
+          <t>Software Engineer Intern; Software Engineer Intern, AI; Business Technology Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>nvidia.com/en-us/about-nvidia/careers/university-recruiting/</t>
+          <t>app.ripplematch.com/v2/public/company/okta</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4178,30 +4174,34 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Technical and thorough. Many software roles start with a HackerRank assessment (two to three coding questions plus multiple-choice, LeetCode-medium), then three to five technical rounds of live coding and C++ or OS deep-dives, plus a project discussion. Research roles focus on publications.</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr"/>
+          <t>Six steps: online application via RippleMatch or Okta Careers, a CodeSignal pre-screen, a 30-minute recruiter call, two 60-minute live CodeSignal technical interviews (algorithms plus data structures at LeetCode easy/medium), and a 30-minute hiring manager behavioral round. The whole process average</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly disclosed for interns. International offices (Toronto, Dublin, Bangalore, Sydney) available. Contact recruiters directly</t>
+        </is>
+      </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Yes. JDs say NVIDIA "accepts applications on an ongoing basis"; ~60% of offers out by end of November</t>
+          <t>Yes, implied. Average application-to-hire is 13 days (Glassdoor), and roles close once filled. Apply within the first two weeks of a posting</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>$20 to $94/hr NVIDIA-stated JD range, roughly $6.7k to $10k/mo, plus housing stipend and relocation</t>
+          <t>SWE intern SF: $55/hr in 2025, roughly $9,500/mo. Plus $5,650 housing stipend, $200/mo phone/internet, $500 WFH stipend</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 20 US 2027-titled intern requisitions live since August 19, 2026 (13-track NVIDIA 2027 Internships series plus PhD research); no close date printed on the requisitions</t>
+          <t>Expected late Aug to Sep 2026 for tech; sales, marketing, and ops roles post Nov to Dec 2026. Projected from prior cycles, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Software Engineer Intern, AI; Business Technology Intern  (3 of 6 tracks)</t>
+          <t>Technology Analyst (SWE)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>app.ripplematch.com/v2/public/company/okta</t>
+          <t>pimco.com/us/en/about-us/careers/students/internships</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Six steps: online application via RippleMatch or Okta Careers, a CodeSignal pre-screen, a 30-minute recruiter call, two 60-minute live CodeSignal technical interviews (algorithms plus data structures at LeetCode easy/medium), and a 30-minute hiring manager behavioral round. The whole process average</t>
+          <t>PIMCO runs a four-stage funnel, and because the process is rolling, each stage can start within weeks of the previous one: 1. Apply through pimco.com/careers or your school's Career Services portal. PIMCO posts separate listings per track, so pick your strongest-fit division. On-campus candidates sh</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly disclosed for interns. International offices (Toronto, Dublin, Bangalore, Sydney) available. Contact recruiters directly</t>
+          <t xml:space="preserve">Yes, with conditions. PIMCO sponsors CPT (Curricular Practical Training) for international students currently enrolled at US universities for summer internship positions. For full-time hires, OPT and STEM OPT extensions </t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Yes, implied. Average application-to-hire is 13 days (Glassdoor), and roles close once filled. Apply within the first two weeks of a posting</t>
+          <t>Yes. PIMCO encourages early submission and reviews applications as they arrive</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>SWE intern SF: $55/hr in 2025, roughly $9,500/mo. Plus $5,650 housing stipend, $200/mo phone/internet, $500 WFH stipend</t>
+          <t>$90,000 annualized for Summer Analysts (~$7,500/month); MBA associates ~$175,000 annualized</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Expected late Aug to Sep 2026 for tech; sales, marketing, and ops roles post Nov to Dec 2026. Projected from prior cycles, not yet posted</t>
+          <t>OPEN NOW. Summer 2027 intern roles are live on pimco.com/careers as of August 2026, across Finance, Product Strategy, Private Strategies, and other tracks. Rolling review; apply by October for priority consideration</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>Pratt &amp; Whitney</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Technology Analyst (SWE)  (1 of 6 tracks)</t>
+          <t>Mechanical / Aerospace Engineering Intern; Materials &amp; Processes Engineering Intern; Electrical Engineering Intern; Digital Technology Intern; Engineering Leadership Development Program (LDP)  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>pimco.com/us/en/about-us/careers/students/internships</t>
+          <t>careers.rtx.com/global/en/pratt-whitney</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4288,34 +4288,34 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>PIMCO runs a four-stage funnel, and because the process is rolling, each stage can start within weeks of the previous one: 1. Apply through pimco.com/careers or your school's Career Services portal. PIMCO posts separate listings per track, so pick your strongest-fit division. On-campus candidates sh</t>
+          <t>The process typically includes a recruiter phone screen (15 to 30 minutes) followed by a hiring manager interview (30 to 60 minutes, video or onsite). The interview is primarily behavioral, focusing on teamwork, problem-solving, and interest in aerospace, with some technical discussion of your cours</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes, with conditions. PIMCO sponsors CPT (Curricular Practical Training) for international students currently enrolled at US universities for summer internship positions. For full-time hires, OPT and STEM OPT extensions </t>
+          <t>Most U.S. positions require U.S. citizenship due to ITAR and defense program access. Some commercial-engine roles may be open to permanent residents. Check each posting</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Yes. PIMCO encourages early submission and reviews applications as they arrive</t>
+          <t>Yes. RTX reviews applications on a rolling basis and extends offers throughout the fall and winter. Applying early gives you the widest selection of teams and l</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>$90,000 annualized for Summer Analysts (~$7,500/month); MBA associates ~$175,000 annualized</t>
+          <t>$25 to $34 per hour depending on role and education level. Glassdoor reports an average of approximately $29/hr; Levels.fyi reports $33.73/hr for mechanical eng</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 intern roles are live on pimco.com/careers as of August 2026, across Finance, Product Strategy, Private Strategies, and other tracks. Rolling review; apply by October for priority consideration</t>
+          <t>Expected August to October 2026 for summer 2027 roles. Rolling review; some postings close as early as mid-November. Projected from prior-cycle patterns</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney</t>
+          <t>Raytheon</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–November 2026</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Mechanical / Aerospace Engineering Intern; Materials &amp; Processes Engineering Intern; Electrical Engineering Intern; Digital Technology Intern; Engineering Leadership Development Program (LDP)  (5 of 6 tracks)</t>
+          <t>Software Engineering; Mechanical Engineering; Electrical Engineering; Systems Engineering; Aerospace Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>careers.rtx.com/global/en/pratt-whitney</t>
+          <t>careers.rtx.com/global/en/campus</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4345,34 +4345,30 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>The process typically includes a recruiter phone screen (15 to 30 minutes) followed by a hiring manager interview (30 to 60 minutes, video or onsite). The interview is primarily behavioral, focusing on teamwork, problem-solving, and interest in aerospace, with some technical discussion of your cours</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>Most U.S. positions require U.S. citizenship due to ITAR and defense program access. Some commercial-engine roles may be open to permanent residents. Check each posting</t>
-        </is>
-      </c>
+          <t>Raytheon uses behavioral interviews based on the STAR method (Situation, Task, Action, Result). Expect a phone or video interview with the hiring manager and 2–3 team members, lasting 30–60 minutes. Questions focus on past teamwork experiences, problem solving, and cultural fit rather than intense t</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Yes. RTX reviews applications on a rolling basis and extends offers throughout the fall and winter. Applying early gives you the widest selection of teams and l</t>
+          <t>Effectively yes. Positions close once the applicant pool is sufficient or after ~40 days</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>$25 to $34 per hour depending on role and education level. Glassdoor reports an average of approximately $29/hr; Levels.fyi reports $33.73/hr for mechanical eng</t>
+          <t>$27–$43/hr depending on role, location, and level; $2,500–$5,000 relocation stipend</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Expected August to October 2026 for summer 2027 roles. Rolling review; some postings close as early as mid-November. Projected from prior-cycle patterns</t>
+          <t>Expected August–September 2026 through November 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Raytheon</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -4387,12 +4383,12 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Mechanical Engineering; Electrical Engineering; Systems Engineering; Aerospace Engineering  (5 of 6 tracks)</t>
+          <t>AI Agents / AI Tooling; Cloud Infrastructure  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>careers.rtx.com/global/en/campus</t>
+          <t>jobs.ashbyhq.com/replit</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4402,30 +4398,30 @@
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Raytheon uses behavioral interviews based on the STAR method (Situation, Task, Action, Result). Expect a phone or video interview with the hiring manager and 2–3 team members, lasting 30–60 minutes. Questions focus on past teamwork experiences, problem solving, and cultural fit rather than intense t</t>
+          <t>Four official stages, applied "from interns to experienced leaders": a recruiter call, a hiring-manager call, a technical exercise (live or take-home, reviewed together), and a panel, followed by an offer. Historically there is also a timed code challenge (under one hour) as an application gate. Rep</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions close once the applicant pool is sufficient or after ~40 days</t>
+          <t>Likely yes. The Summer 2026 role was a single rolling listing, and recruiting content describes Replit posting internships "on an early rolling" basis. No offic</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>$27–$43/hr depending on role, location, and level; $2,500–$5,000 relocation stipend</t>
+          <t>Replit's JD lists "salary not specified" plus equity and stipends. A LinkedIn aggregator snippet showed ~$10,000 (most consistent with a monthly figure); Glassd</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Expected August–September 2026 through November 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Not officially published. Based on the Summer 2026 cycle (posted ~mid-July 2026) and August 2026 recruiting signals, applications for summer 2027 are expected to open ~Aug–Nov 2026 on an early, rolling basis</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -4435,17 +4431,17 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>August–November 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>AI Agents / AI Tooling; Cloud Infrastructure  (2 of 4 tracks)</t>
+          <t>Software Engineer Intern; Community Apprenticeship (SWE); Data Scientist PhD Intern; Applied Scientist PhD Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/replit</t>
+          <t>careers.roblox.com/early-career</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -4455,30 +4451,34 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Four official stages, applied "from interns to experienced leaders": a recruiter call, a hiring-manager call, a technical exercise (live or take-home, reviewed together), and a panel, followed by an offer. Historically there is also a timed code challenge (under one hour) as an application gate. Rep</t>
-        </is>
-      </c>
-      <c r="H72" s="6" t="inlineStr"/>
+          <t>Expect 2 to 4 months total. The typical flow: resume screen (1-2 weeks), OA invitation (1-3 weeks after), technical screen scheduling (1-3 weeks), virtual onsite (1-2 weeks after screen), and offer (1-2 weeks after onsite). Community reports indicate some candidates experience significant delays and</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>No. Roblox does not sponsor H-1B or other visas for intern positions. However, international students with existing US work authorization (F-1 CPT, OPT, or STEM OPT) are eligible. Roblox does sponsor H-1B for full-time r</t>
+        </is>
+      </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. The Summer 2026 role was a single rolling listing, and recruiting content describes Replit posting internships "on an early rolling" basis. No offic</t>
+          <t>Yes. Positions fill continuously until closed; no fixed deadline published</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>Replit's JD lists "salary not specified" plus equity and stipends. A LinkedIn aggregator snippet showed ~$10,000 (most consistent with a monthly figure); Glassd</t>
+          <t>SWE/PM $62/hr, Research $72/hr, Design $58/hr + $10,000 housing stipend + free meals</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>Not officially published. Based on the Summer 2026 cycle (posted ~mid-July 2026) and August 2026 recruiting signals, applications for summer 2027 are expected to open ~Aug–Nov 2026 on an early, rolling basis</t>
+          <t>Open now for summer 2027: Software Engineer Intern (posted August 5, 2026), Product Management Intern and Product Design Intern (posted September 2, 2026). Rolling review, no fixed deadline</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Royal Caribbean</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August 2026 – April 2027</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Community Apprenticeship (SWE); Data Scientist PhD Intern; Applied Scientist PhD Intern  (4 of 6 tracks)</t>
+          <t>Technology; Data Analytics &amp; AI  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>careers.roblox.com/early-career</t>
+          <t>careers.royalcaribbeangroup.com/intern-program/</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -4508,34 +4508,34 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Expect 2 to 4 months total. The typical flow: resume screen (1-2 weeks), OA invitation (1-3 weeks after), technical screen scheduling (1-3 weeks), virtual onsite (1-2 weeks after screen), and offer (1-2 weeks after onsite). Community reports indicate some candidates experience significant delays and</t>
+          <t>After applying online, most candidates complete a HireVue asynchronous video interview with 3–5 behavioral questions. Those who pass advance to a recruiter screen and then a hiring manager interview lasting 30–60 minutes. Technical roles may add coding challenges or case studies. The process typical</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>No. Roblox does not sponsor H-1B or other visas for intern positions. However, international students with existing US work authorization (F-1 CPT, OPT, or STEM OPT) are eligible. Roblox does sponsor H-1B for full-time r</t>
+          <t>Royal Caribbean requires permanent US work authorization and doesn't sponsor H-1B visas for interns. However, CPT and OPT are accepted, so international students with valid CPT or OPT authorization can apply. You must al</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions fill continuously until closed; no fixed deadline published</t>
+          <t>Yes. Applications are "reviewed on a rolling basis" and positions "may close before the stated closing date"</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>SWE/PM $62/hr, Research $72/hr, Design $58/hr + $10,000 housing stipend + free meals</t>
+          <t>$21–$24/hr official (undergraduate); Glassdoor averages ~$33/hr for technical roles; $1,000–$2,000 relocation stipend for non-local interns</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Software Engineer Intern (posted August 5, 2026), Product Management Intern and Product Design Intern (posted September 2, 2026). Rolling review, no fixed deadline</t>
+          <t>First wave started: the Intern, Finance (Summer 2027) posting in Miami, FL went up September 16, 2026, with no closing date stated. It was the only US internship listed on October 10, 2026. Other functions: expected August–November 2026 (first wave) and January–April 2027 (second wave) for summer 2027 (documented pattern)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Royal Caribbean</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -4545,17 +4545,17 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>August 2026 – April 2027</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Technology; Data Analytics &amp; AI  (2 of 6 tracks)</t>
+          <t>Software Engineering (SWE); AI &amp; Data Science Analyst; AI Research; Product Security Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>careers.royalcaribbeangroup.com/intern-program/</t>
+          <t>salesforce.wd12.myworkdayjobs.com/en-US/Futureforce_Internsh</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -4565,34 +4565,34 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>After applying online, most candidates complete a HireVue asynchronous video interview with 3–5 behavioral questions. Those who pass advance to a recruiter screen and then a hiring manager interview lasting 30–60 minutes. Technical roles may add coding challenges or case studies. The process typical</t>
+          <t>Typically 3 to 5 stages: an online assessment on HackerRank (2 to 3 problems, 60 to 90 minutes), a recruiter phone screen (30 minutes), 1 to 2 technical coding interviews, and a behavioral/values interview weighted equally with technical performance. Total timeline averages 25 days.</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>Royal Caribbean requires permanent US work authorization and doesn't sponsor H-1B visas for interns. However, CPT and OPT are accepted, so international students with valid CPT or OPT authorization can apply. You must al</t>
+          <t>F-1 CPT students attending US or Canadian universities are fully eligible. J-1 sponsorship from outside the US is rare for the general Futureforce pool. H-1B sponsorship is available for full-time conversion after the in</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are "reviewed on a rolling basis" and positions "may close before the stated closing date"</t>
+          <t>Yes, explicitly. Most spots fill by December; week-one applicants interview at 40–60% higher rates</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>$21–$24/hr official (undergraduate); Glassdoor averages ~$33/hr for technical roles; $1,000–$2,000 relocation stipend for non-local interns</t>
+          <t>$46–$68/hr depending on track and location, plus $5,250–$9,000 housing/relocation stipend</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Expected August–November 2026 (first wave) and January–April 2027 (second wave) for summer 2027 (documented pattern; not yet posted)</t>
+          <t xml:space="preserve">OPEN for summer 2027 on the Software Engineer track: Software Engineer Intern posted Aug 31, 2026 (San Francisco, Palo Alto, New York, Seattle, Bellevue, Burlington, Atlanta, Indianapolis), no end date printed, still live Oct 6. Also live: Product GTM Strategy Intern, San Francisco (posted Oct 2, no end date) and three MBA Business Value &amp; Strategic Selling Consultant Intern reqs, New York (close </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -4602,17 +4602,17 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August 2026</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (SWE); AI &amp; Data Science Analyst; AI Research; Product Security Engineering  (4 of 6 tracks)</t>
+          <t>Software Engineer Intern; Hardware Engineering Intern; Data Science / ML (via SWE posting)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>salesforce.wd12.myworkdayjobs.com/en-US/Futureforce_Internsh</t>
+          <t>samsara.com/company/careers/emerging-talent</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -4622,34 +4622,30 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 5 stages: an online assessment on HackerRank (2 to 3 problems, 60 to 90 minutes), a recruiter phone screen (30 minutes), 1 to 2 technical coding interviews, and a behavioral/values interview weighted equally with technical performance. Total timeline averages 25 days.</t>
-        </is>
-      </c>
-      <c r="H75" s="6" t="inlineStr">
-        <is>
-          <t>F-1 CPT students attending US or Canadian universities are fully eligible. J-1 sponsorship from outside the US is rare for the general Futureforce pool. H-1B sponsorship is available for full-time conversion after the in</t>
-        </is>
-      </c>
+          <t>Four stages over about a month: an online assessment (CoderPad or Codility, four to five timed LeetCode-style DSA questions, roughly one hour), a live technical coding round (one question plus a follow-up, with a light behavioral warm-up), a final behavioral round with a senior engineer, then an off</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Yes, explicitly. Most spots fill by December; week-one applicants interview at 40–60% higher rates</t>
+          <t>Yes. Samsara hires on a rolling basis until positions are filled, with a firm November 26 backstop. Apply early (strong candidates interview before the deadline</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>$46–$68/hr depending on track and location, plus $5,250–$9,000 housing/relocation stipend</t>
+          <t>$61.90/hr (official current SF SWE intern posting), with relocation assistance. Community data (Levels.fyi) shows prior SF cohorts around $52/hr (~$9,000/mo) pl</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPEN for summer 2027 on the Software Engineer track: Software Engineer Intern posted Aug 31, 2026 (San Francisco, Palo Alto, New York, Seattle, Bellevue, Burlington, Atlanta, Indianapolis), no end date printed, still live Oct 6. Also live: Product GTM Strategy Intern, San Francisco (posted Oct 2, no end date) and three MBA Business Value &amp; Strategic Selling Consultant Intern reqs, New York (close </t>
+          <t>Open now and accepting applications (as of August 2026). Applications officially close November 26 at 11:59pm ET (year inferred 2026); cohort finalized late November / early December.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -4659,17 +4655,17 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>August 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Hardware Engineering Intern; Data Science / ML (via SWE posting)  (3 of 5 tracks)</t>
+          <t>Software Engineering Intern; Machine Learning Research Intern; SEAL Research Scientist Intern; AI Builder Intern; Technical Advisor Intern (GenAI)  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>samsara.com/company/careers/emerging-talent</t>
+          <t>scale.com/careers/university</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -4679,30 +4675,34 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Four stages over about a month: an online assessment (CoderPad or Codility, four to five timed LeetCode-style DSA questions, roughly one hour), a live technical coding round (one question plus a follow-up, with a light behavioral warm-up), a final behavioral round with a senior engineer, then an off</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr"/>
+          <t>Typically: a recruiter screen, a HackerRank OA with 1-2 medium-hard coding problems in 60 minutes, then a final loop covering coding, system design, and behavioral questions. The system design round is reportedly the hardest, focusing on data pipelines and throughput at scale. Some intern candidates</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>Scale AI requires U.S. work authorization for most roles. The Technical Advisor track specifies 'fully remote within the U.S.' and public-sector roles may require security clearance. Scale doesn't explicitly confirm visa</t>
+        </is>
+      </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Yes. Samsara hires on a rolling basis until positions are filled, with a firm November 26 backstop. Apply early (strong candidates interview before the deadline</t>
+          <t>Yes. Scale AI reviews applications as they arrive; the Summer 2026 rolling deadline was September 30</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>$61.90/hr (official current SF SWE intern posting), with relocation assistance. Community data (Levels.fyi) shows prior SF cohorts around $52/hr (~$9,000/mo) pl</t>
+          <t>$60/hr (~$10,400/month) + $7,000 housing stipend + free meals (SF office)</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>Open now and accepting applications (as of August 2026). Applications officially close November 26 at 11:59pm ET (year inferred 2026); cohort finalized late November / early December.</t>
+          <t>Applications for summer 2027 expected to open August to October 2026 (rolling; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -4712,17 +4712,17 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Machine Learning Research Intern; SEAL Research Scientist Intern; AI Builder Intern; Technical Advisor Intern (GenAI)  (5 of 6 tracks)</t>
+          <t>Software Engineering; Data Engineering; Product Data Science; Applied ML Engineering; Infrastructure Engineering; Security Engineering</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>scale.com/careers/university</t>
+          <t>shopify.com/careers</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -4732,34 +4732,34 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Typically: a recruiter screen, a HackerRank OA with 1-2 medium-hard coding problems in 60 minutes, then a final loop covering coding, system design, and behavioral questions. The system design round is reportedly the hardest, focusing on data pipelines and throughput at scale. Some intern candidates</t>
+          <t>Shopify’s funnel is faster than most big tech and distinctly different from the standard LeetCode gauntlet, averaging 3–5 weeks from application to decision: 1. Apply at shopify.com/careers with a resume, application questions, your LinkedIn, and a personal website or GitHub link. Shopify’s postings</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Scale AI requires U.S. work authorization for most roles. The Technical Advisor track specifies 'fully remote within the U.S.' and public-sector roles may require security clearance. Scale doesn't explicitly confirm visa</t>
+          <t>No. Every internship posting states you must be legally entitled to work in the hiring country for the full duration. Shopify doesn't provide immigration sponsorship for intern candidates. However, candidates on existing</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Yes. Scale AI reviews applications as they arrive; the Summer 2026 rolling deadline was September 30</t>
+          <t>Yes. Applications reviewed on a rolling basis, and postings warn they "may close before the stated closing date"</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>$60/hr (~$10,400/month) + $7,000 housing stipend + free meals (SF office)</t>
+          <t>US: $42–$45/hr + $1,000–$2,500/mo housing stipend; Canada: CAD $27–$35/hr</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open August to October 2026 (rolling; not yet posted)</t>
+          <t>Expected August–September 2026 for summer 2027; fall 2027 postings expected January–March 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Engineering; Product Data Science; Applied ML Engineering; Infrastructure Engineering; Security Engineering</t>
+          <t>Agent Engineering (Early Career); Software Engineer (General)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>shopify.com/careers</t>
+          <t>sierra.ai/early-career-program</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -4789,34 +4789,34 @@
       </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Shopify’s funnel is faster than most big tech and distinctly different from the standard LeetCode gauntlet, averaging 3–5 weeks from application to decision: 1. Apply at shopify.com/careers with a resume, application questions, your LinkedIn, and a personal website or GitHub link. Shopify’s postings</t>
+          <t>You apply, complete a take-home or online technical assessment, then attend in-person onsite interviews at a Sierra office. Onsites include coding rounds (LeetCode medium-to-hard), system design for AI agents, and behavioral questions aligned with Sierra's five values. Glassdoor rates the difficulty</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>No. Every internship posting states you must be legally entitled to work in the hiring country for the full duration. Shopify doesn't provide immigration sponsorship for intern candidates. However, candidates on existing</t>
+          <t>Sierra sponsors visas but cannot guarantee sponsorship for every candidate. From their FAQ: 'We'll do our best to support your visa process.' Relocation assistance available</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis, and postings warn they "may close before the stated closing date"</t>
+          <t>Yes. Sierra reviews applications on a rolling basis. From their FAQ: 'We encourage you to apply early to avoid missing out.' No fixed deadline; positions may cl</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>US: $42–$45/hr + $1,000–$2,500/mo housing stipend; Canada: CAD $27–$35/hr</t>
+          <t xml:space="preserve">Estimated $55 to $75 per hour ($11,000 to $15,000/month) based on comparable AI startup benchmarks. Not confirmed by Sierra. Full-time SWE median total comp is </t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>Expected August–September 2026 for summer 2027; fall 2027 postings expected January–March 2027 (documented pattern; not yet posted)</t>
+          <t>Expected August to September 2026 for summer 2027 roles. Rolling review with interviews wrapping by December 2026. Projected from the Fall 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Snap</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>Agent Engineering (Early Career); Software Engineer (General)  (2 of 4 tracks)</t>
+          <t>Software Engineer Intern; Machine Learning Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>sierra.ai/early-career-program</t>
+          <t>careers.snap.com/emerging-talent</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -4846,34 +4846,34 @@
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a take-home or online technical assessment, then attend in-person onsite interviews at a Sierra office. Onsites include coding rounds (LeetCode medium-to-hard), system design for AI agents, and behavioral questions aligned with Sierra's five values. Glassdoor rates the difficulty</t>
+          <t>You apply online, complete a recruiter phone screen (20 to 30 minutes), do 1 to 2 technical phone screens on CoderPad, then attend SnapFest, a full-day virtual onsite with 2 to 3 coding rounds, system design, and a behavioral round. Decisions typically come 1 to 2 weeks after SnapFest.</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Sierra sponsors visas but cannot guarantee sponsorship for every candidate. From their FAQ: 'We'll do our best to support your visa process.' Relocation assistance available</t>
+          <t>CPT supported for F-1 students. OPT and 24-month STEM OPT extension available. H-1B sponsorship limited and lottery-dependent</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Yes. Sierra reviews applications on a rolling basis. From their FAQ: 'We encourage you to apply early to avoid missing out.' No fixed deadline; positions may cl</t>
+          <t>Yes. Snap reviews applications on a rolling basis. Apply by mid-October for priority consideration; after mid-November, most seats are filled</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimated $55 to $75 per hour ($11,000 to $15,000/month) based on comparable AI startup benchmarks. Not confirmed by Sierra. Full-time SWE median total comp is </t>
+          <t>$50 to $68 per hour depending on role and location. SWE median around $52/hr; Research interns around $58/hr. Housing stipend of $1,200 to $2,500/month (Levels.</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>Expected August to September 2026 for summer 2027 roles. Rolling review with interviews wrapping by December 2026. Projected from the Fall 2026 cycle</t>
+          <t>Expected late August to early September 2026 for summer 2027 technical roles. Priority deadline around mid-October 2026, positions fill through mid-November 2026. Projected from prior cycle</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Snap</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Machine Learning Engineering Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern (Backend); Software Engineer Intern (Frontend); Data Reliability Engineering Intern; Data Science / BI Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>careers.snap.com/emerging-talent</t>
+          <t>sofi.com/careers/university-recruiting/</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -4903,34 +4903,34 @@
       </c>
       <c r="G80" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (20 to 30 minutes), do 1 to 2 technical phone screens on CoderPad, then attend SnapFest, a full-day virtual onsite with 2 to 3 coding rounds, system design, and a behavioral round. Decisions typically come 1 to 2 weeks after SnapFest.</t>
+          <t>SoFi's interview includes a recruiter phone screen, a HackerRank coding assessment with two LeetCode Easy to Medium problems, a technical interview with the hiring manager, and a behavioral round. The process emphasizes practical problem-solving, clean code, and alignment with SoFi's core values.</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. OPT and 24-month STEM OPT extension available. H-1B sponsorship limited and lottery-dependent</t>
+          <t>F-1 CPT supported for interns. H-1B sponsorship available but selective for full-time conversion</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Yes. Snap reviews applications on a rolling basis. Apply by mid-October for priority consideration; after mid-November, most seats are filled</t>
+          <t>Yes, confirmed. Applications reviewed continuously; 60–70% of offers go to September–October applicants</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>$50 to $68 per hour depending on role and location. SWE median around $52/hr; Research interns around $58/hr. Housing stipend of $1,200 to $2,500/month (Levels.</t>
+          <t>SWE intern SF: $55/hr (~$9,533/mo) plus $5,000 sign-on bonus and housing stipend. Product and finance roles: $35–$48/hr</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Expected late August to early September 2026 for summer 2027 technical roles. Priority deadline around mid-October 2026, positions fill through mid-November 2026. Projected from prior cycle</t>
+          <t>Expected late August to early September 2026 for summer 2027; rolling through mid-November 2026. Projected from the prior cycle, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Backend); Software Engineer Intern (Frontend); Data Reliability Engineering Intern; Data Science / BI Intern  (4 of 6 tracks)</t>
+          <t>Engineering Intern; Software Engineering Intern; Graduate Engineer Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>sofi.com/careers/university-recruiting/</t>
+          <t>spacex.com/careers/jobs/?keyword=internship</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -4960,34 +4960,34 @@
       </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>SoFi's interview includes a recruiter phone screen, a HackerRank coding assessment with two LeetCode Easy to Medium problems, a technical interview with the hiring manager, and a behavioral round. The process emphasizes practical problem-solving, clean code, and alignment with SoFi's core values.</t>
+          <t>SpaceX's interview funnel is technically demanding and project-depth-driven. The total process runs 4 to 12 weeks from application to offer, with Glassdoor reporting an average of 17 days for intern roles: 1. Apply at spacex.com/careers within 48 to 72 hours of a posting going live. Submit your resu</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for interns. H-1B sponsorship available but selective for full-time conversion</t>
+          <t>No. SpaceX requires U.S. Person status under ITAR regulations. F-1 visa holders are ineligible regardless of CPT or OPT work authorization. H-1B holders are generally ineligible. SpaceX does not sponsor work visas for in</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed continuously; 60–70% of offers go to September–October applicants</t>
+          <t>Yes. No fixed cohort deadlines. Apply within 48–72 hours of a posting going live for best odds</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>SWE intern SF: $55/hr (~$9,533/mo) plus $5,000 sign-on bonus and housing stipend. Product and finance roles: $35–$48/hr</t>
+          <t>$28–$40/hr undergrad (varies by level); $83K–$100K annualized for graduate interns</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Expected late August to early September 2026 for summer 2027; rolling through mid-November 2026. Projected from the prior cycle, not yet posted</t>
+          <t>Applications for summer 2027 expected to open late Aug–Sep 2026 (projected from prior cycle); rolling admissions, positions fill as qualified candidates found</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern; Software Engineering Intern; Graduate Engineer Intern  (3 of 6 tracks)</t>
+          <t>R&amp;D Engineering Intern; Software Engineering Intern; Quality Engineering Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>spacex.com/careers/jobs/?keyword=internship</t>
+          <t>careers.stryker.com/students-and-graduates</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -5017,34 +5017,34 @@
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>SpaceX's interview funnel is technically demanding and project-depth-driven. The total process runs 4 to 12 weeks from application to offer, with Glassdoor reporting an average of 17 days for intern roles: 1. Apply at spacex.com/careers within 48 to 72 hours of a posting going live. Submit your resu</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), take the Gallup StrengthsFinder assessment (30 to 90 minutes with a trained analyst), then 2 to 3 follow-up interviews with the hiring manager and department heads. Average time from first interview to offer is about 31 days.</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>No. SpaceX requires U.S. Person status under ITAR regulations. F-1 visa holders are ineligible regardless of CPT or OPT work authorization. H-1B holders are generally ineligible. SpaceX does not sponsor work visas for in</t>
+          <t>Not available. Candidates must be legally authorized to work in the U.S. without sponsorship now or in the future. F-1 students with CPT may still be eligible</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>Yes. No fixed cohort deadlines. Apply within 48–72 hours of a posting going live for best odds</t>
+          <t>Yes. Stryker reviews applications and extends offers on a rolling basis from September through early March. Earlier applicants face the most open seats</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>$28–$40/hr undergrad (varies by level); $83K–$100K annualized for graduate interns</t>
+          <t>$25 to $35 per hour depending on role and location ($4,300 to $6,000/month). Software engineering interns reported $33.50/hr on Levels.fyi. Housing stipend or c</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open late Aug–Sep 2026 (projected from prior cycle); rolling admissions, positions fill as qualified candidates found</t>
+          <t>Open now for summer 2027: 38 Summer 2027 intern requisitions posted August 31 to September 9, 2026. No deadline is printed on the requisitions (one carries a November 20, 2026 end date); prior cycles ran into early March 2027 for remaining seats</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering Intern; Software Engineering Intern; Quality Engineering Intern  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>careers.stryker.com/students-and-graduates</t>
+          <t>corporate.target.com/careers/career-areas/intern-entry-level</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -5074,34 +5074,34 @@
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), take the Gallup StrengthsFinder assessment (30 to 90 minutes with a trained analyst), then 2 to 3 follow-up interviews with the hiring manager and department heads. Average time from first interview to offer is about 31 days.</t>
+          <t>You apply online, pass resume screening, complete a HireVue asynchronous video interview with 3 to 5 behavioral questions, then a 45- to 60-minute first-round behavioral interview, then a final-round virtual Super Day with 2 to 3 back-to-back interviews. The average time to hire is about 19 days.</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>Not available. Candidates must be legally authorized to work in the U.S. without sponsorship now or in the future. F-1 students with CPT may still be eligible</t>
+          <t>Target generally does not provide visa sponsorship for the majority of its internship roles. U.S. work authorization typically required without sponsorship</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Yes. Stryker reviews applications and extends offers on a rolling basis from September through early March. Earlier applicants face the most open seats</t>
+          <t>Yes. Target reviews applications on a rolling basis until positions are filled. Apply in August for the strongest consideration</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>$25 to $35 per hour depending on role and location ($4,300 to $6,000/month). Software engineering interns reported $33.50/hr on Levels.fyi. Housing stipend or c</t>
+          <t>$24 to $50 per hour depending on role and location. SWE interns average about $34/hr (Levels.fyi). Housing stipend of $2,000 to $3,500 for relocating interns, p</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 38 Summer 2027 intern requisitions posted August 31 to September 9, 2026. No deadline is printed on the requisitions (one carries a November 20, 2026 end date); prior cycles ran into early March 2027 for remaining seats</t>
+          <t>Open now for summer 2027. The first HQ requisition (Financial Analyst Intern) went live August 21, 2026, the Store Executive and Distribution Center Operations Manager waves followed in late August and early September, and Software Engineering posted September 10. No close date is printed on the requisitions; 126 US postings confirmed live on Target's Workday board September 21, 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern  (1 of 6 tracks)</t>
+          <t>Software Engineering; Data Science  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>corporate.target.com/careers/career-areas/intern-entry-level</t>
+          <t>jobs.uber.com/en/teams/emerging-talent/</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -5131,34 +5131,34 @@
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>You apply online, pass resume screening, complete a HireVue asynchronous video interview with 3 to 5 behavioral questions, then a 45- to 60-minute first-round behavioral interview, then a final-round virtual Super Day with 2 to 3 back-to-back interviews. The average time to hire is about 19 days.</t>
+          <t>Uber’s SWE internship funnel runs 4 stages, averaging about 28 days from application to decision: 1. Submit your application at jobs.uber.com with a resume. List 3 to 5 city preferences in order. No cover letter required. 2. Complete the CodeSignal Online Assessment (70 minutes, 4 problems, threshol</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>Target generally does not provide visa sponsorship for the majority of its internship roles. U.S. work authorization typically required without sponsorship</t>
+          <t>Yes. Uber accepts CPT and OPT for interns. For full-time conversion, Uber filed 823 H-1B petitions in FY2025 (ranked #41 among US employers). STEM OPT 24-month extension eligible.</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>Yes. Target reviews applications on a rolling basis until positions are filled. Apply in August for the strongest consideration</t>
+          <t>Yes. Offers extended continuously; early applicants see significantly higher response rates</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>$24 to $50 per hour depending on role and location. SWE interns average about $34/hr (Levels.fyi). Housing stipend of $2,000 to $3,500 for relocating interns, p</t>
+          <t>$52/hr + housing stipend $1,000–$6,000/month + Uber credits, meals, benefits</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027. The first HQ requisition (Financial Analyst Intern) went live August 21, 2026, the Store Executive and Distribution Center Operations Manager waves followed in late August and early September, and Software Engineering posted September 10. No close date is printed on the requisitions; 126 US postings confirmed live on Target's Workday board September 21, 2026</t>
+          <t>Applications for summer 2027 expected to open August to September 2026 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -5168,17 +5168,17 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>August–October 2026</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Science  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern; Research Science Intern (AI/ML); Data Science Intern; Technical Writer Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>jobs.uber.com/en/teams/emerging-talent/</t>
+          <t>unity.com/careers/positions</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -5188,34 +5188,34 @@
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Uber’s SWE internship funnel runs 4 stages, averaging about 28 days from application to decision: 1. Submit your application at jobs.uber.com with a resume. List 3 to 5 city preferences in order. No cover letter required. 2. Complete the CodeSignal Online Assessment (70 minutes, 4 problems, threshol</t>
+          <t>The process typically involves a recruiter phone screen (30 minutes), a Codility coding assessment (timed, C#/Python/Go), one to two technical interviews with senior engineers (live coding plus problem solving), and a behavioral interview. Total process takes approximately 45 days, with a 3.1 out of</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>Yes. Uber accepts CPT and OPT for interns. For full-time conversion, Uber filed 823 H-1B petitions in FY2025 (ranked #41 among US employers). STEM OPT 24-month extension eligible.</t>
+          <t>Must be authorized to work in the country of the internship. F-1 CPT eligible for US roles. Benefits and relocation support vary by region</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>Yes. Offers extended continuously; early applicants see significantly higher response rates</t>
+          <t>Yes, likely. Roles are posted individually and remain open until filled. No single unified deadline. Apply as soon as a role appears</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>$52/hr + housing stipend $1,000–$6,000/month + Uber credits, meals, benefits</t>
+          <t>SWE intern $40 to $50/hr depending on location (SF highest at $47 to $50/hr). Housing stipend of roughly $5,400 total or $1,500 to $1,800 per month</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open August to September 2026 (documented pattern; not yet posted)</t>
+          <t>Expected late summer to early fall for the following summer. Monitor starting Aug to Oct 2026 for summer 2027 roles. Projected pattern, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Research Science Intern (AI/ML); Data Science Intern; Technical Writer Intern  (4 of 5 tracks)</t>
+          <t>Technology / IT Internship  (1 of 7 tracks)</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>unity.com/careers/positions</t>
+          <t>jobs.walgreens.com/en/students</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -5245,34 +5245,30 @@
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves a recruiter phone screen (30 minutes), a Codility coding assessment (timed, C#/Python/Go), one to two technical interviews with senior engineers (live coding plus problem solving), and a behavioral interview. Total process takes approximately 45 days, with a 3.1 out of</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>Must be authorized to work in the country of the internship. F-1 CPT eligible for US roles. Benefits and relocation support vary by region</t>
-        </is>
-      </c>
+          <t>The process typically involves 2–4 rounds: an online application, possibly an online assessment or HireVue pre-recorded video interview, a phone or video screen with a recruiter, and a final interview with the hiring manager. Expect a mix of behavioral and situational questions. Glassdoor rates inte</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Yes, likely. Roles are posted individually and remain open until filled. No single unified deadline. Apply as soon as a role appears</t>
+          <t>No explicit rolling statement for corporate programs. Community pharmacy intern positions are posted and filled continuously across 50 states</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>SWE intern $40 to $50/hr depending on location (SF highest at $47 to $50/hr). Housing stipend of roughly $5,400 total or $1,500 to $1,800 per month</t>
+          <t>$15–$33.65/hr corporate (the range printed on the three corporate support center postings we checked in October 2026); $17–$19/hr community management; $18–$31/</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Expected late summer to early fall for the following summer. Monitor starting Aug to Oct 2026 for summer 2027 roles. Projected pattern, not yet posted</t>
+          <t>Corporate support center intern postings live since August 27, 2026 (Finance-Accounting, Supply Chain, Value Realization &amp; Delivery, Centralized Services AI, Retail Merchandising; start date not printed); community management and community pharmacy intern roles post year-round</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -5282,17 +5278,17 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>August–October 2026</t>
+          <t>August–September 2026</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>Technology / IT Internship  (1 of 7 tracks)</t>
+          <t>Software Engineering (Global Tech); Data Science &amp; Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>jobs.walgreens.com/en/students</t>
+          <t>careers.walmart.com/us/en/home/careers-areas/students</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -5302,30 +5298,34 @@
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves 2–4 rounds: an online application, possibly an online assessment or HireVue pre-recorded video interview, a phone or video screen with a recruiter, and a final interview with the hiring manager. Expect a mix of behavioral and situational questions. Glassdoor rates inte</t>
-        </is>
-      </c>
-      <c r="H87" s="6" t="inlineStr"/>
+          <t>Walmart runs two distinct funnels depending on whether you're applying for a corporate/business track or a Walmart Global Tech/SWE track: 1. Apply at careers.walmart.com when summer 2027 postings go live (expected early August 2026). Each posting typically closes within 30 days. 2. Online assessment</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>No. Walmart doesn't provide visa sponsorship (H-1B, TN) for internship roles. International students on CPT or OPT are eligible, provided they have valid work authorization during the full internship period.</t>
+        </is>
+      </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>No explicit rolling statement for corporate programs. Community pharmacy intern positions are posted and filled continuously across 50 states</t>
+          <t>Yes. Interviews begin rolling in September; ~60–70% of slots fill by mid-September</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>$15–$33.65/hr corporate (the range printed on the three corporate support center postings we checked in October 2026); $17–$19/hr community management; $18–$31/</t>
+          <t>$19–$55/hr depending on role and location; SWE at Sunnyvale up to $52/hr, plus housing and relocation</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Corporate support center intern postings live since August 27, 2026 (Finance-Accounting, Supply Chain, Value Realization &amp; Delivery, Centralized Services AI, Retail Merchandising; start date not printed); community management and community pharmacy intern roles post year-round</t>
+          <t>Open now for summer 2027: 24 US Summer 2027 intern requisitions posted August 25 to September 14, 2026 (Bentonville and Hoboken); most print no close date, the cybersecurity reqs close February 5, 2027</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Wise</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (Global Tech); Data Science &amp; Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineering Intern; Data Science Intern; Data Analytics Intern  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>careers.walmart.com/us/en/home/careers-areas/students</t>
+          <t>wise.jobs/wisestart-programs</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -5355,34 +5355,34 @@
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Walmart runs two distinct funnels depending on whether you're applying for a corporate/business track or a Walmart Global Tech/SWE track: 1. Apply at careers.walmart.com when summer 2027 postings go live (expected early August 2026). Each posting typically closes within 30 days. 2. Online assessment</t>
+          <t>Wise's interview funnel is streamlined compared to FAANG loops, typically spanning about 60 days from application to offer: 1. Apply on wise.jobs . Find your target track, submit your resume and cover letter, and explain your interest in Wise and the specific role. Applications are deadline-based, n</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>No. Walmart doesn't provide visa sponsorship (H-1B, TN) for internship roles. International students on CPT or OPT are eligible, provided they have valid work authorization during the full internship period.</t>
+          <t>Candidates must be eligible to work in the posting country. Wise is a confirmed UK Skilled Worker visa sponsor for full-time roles. Intern visa sponsorship is unlikely given the 10-week duration</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>Yes. Interviews begin rolling in September; ~60–70% of slots fill by mid-September</t>
+          <t>No. Wise uses firm deadlines. The Summer 2025 Budapest SWE Intern posting had a hard close of October 31, 2024. Early submission is still recommended as competi</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>$19–$55/hr depending on role and location; SWE at Sunnyvale up to $52/hr, plus housing and relocation</t>
+          <t>$23.08/hr in London (Levels.fyi, Summer 2022). 640,000 HUF/month gross in Budapest (~$1,700 to $1,800/month, Summer 2025). Housing and transportation benefits i</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 24 US Summer 2027 intern requisitions posted August 25 to September 14, 2026 (Bentonville and Hoboken); most print no close date, the cybersecurity reqs close February 5, 2027</t>
+          <t>Expected August to September 2026 for summer 2027. Application deadline projected around late October 2026. Based on the Summer 2025 Budapest SWE Intern cycle (deadline October 31, 2024)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Wise</t>
+          <t>Wolverine Trading</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science Intern; Data Analytics Intern  (3 of 4 tracks)</t>
+          <t>Software Engineering Intern; Quantitative Trading Intern; Quantitative Researcher / Trading Systems Analyst Intern; Data Science Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>wise.jobs/wisestart-programs</t>
+          <t>wolve.com/careers</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -5412,34 +5412,34 @@
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Wise's interview funnel is streamlined compared to FAANG loops, typically spanning about 60 days from application to offer: 1. Apply on wise.jobs . Find your target track, submit your resume and cover letter, and explain your interest in Wise and the specific role. Applications are deadline-based, n</t>
+          <t xml:space="preserve">Three to five rounds over about 15 days: initial screening, technical assessment via Coderbyte (SWE) or mental math and probability test (trading), one to two phone interviews, a behavioral interview, and a half-day on-site in Chicago with technical deep-dives or market-making simulations depending </t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>Candidates must be eligible to work in the posting country. Wise is a confirmed UK Skilled Worker visa sponsor for full-time roles. Intern visa sponsorship is unlikely given the 10-week duration</t>
+          <t>Not explicitly stated. US work authorization likely required. Check with your recruiter</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>No. Wise uses firm deadlines. The Summer 2025 Budapest SWE Intern posting had a hard close of October 31, 2024. Early submission is still recommended as competi</t>
+          <t>Yes. Wolverine reviews applications on a rolling basis and closes positions once all slots are filled. Per QuantNet: most offers are made before December</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>$23.08/hr in London (Levels.fyi, Summer 2022). 640,000 HUF/month gross in Budapest (~$1,700 to $1,800/month, Summer 2025). Housing and transportation benefits i</t>
+          <t>$63 per hour ($10,920/month) for SWE interns (2024 data via Levels.fyi). $3,000 sign-on bonus. Fully paid corporate housing near the Loop, free gym, CTA pass, a</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>Expected August to September 2026 for summer 2027. Application deadline projected around late October 2026. Based on the Summer 2025 Budapest SWE Intern cycle (deadline October 31, 2024)</t>
+          <t>Expected August to September 2026 for summer 2027 roles. Rolling review; most spots filled by December 2026. Projected from prior cycles and industry patterns</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Wolverine Trading</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>August–September 2026</t>
+          <t>September–December 2026</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Quantitative Trading Intern; Quantitative Researcher / Trading Systems Analyst Intern; Data Science Intern  (4 of 5 tracks)</t>
+          <t>Developer Intern: Software / Platform (primary); Data Intern (Enterprise Analytics / Data Engineering)  (2 of 5 tracks)</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>wolve.com/careers</t>
+          <t>1password.com/careers</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -5469,34 +5469,30 @@
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three to five rounds over about 15 days: initial screening, technical assessment via Coderbyte (SWE) or mental math and probability test (trading), one to two phone interviews, a behavioral interview, and a half-day on-site in Chicago with technical deep-dives or market-making simulations depending </t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>Not explicitly stated. US work authorization likely required. Check with your recruiter</t>
-        </is>
-      </c>
+          <t>Recruiter screen (sometimes an AI-helped pre-screen) → hiring-manager interview → a ~48-hour take-home assignment → one or two technical deep-dives (coding plus design and threat-aware reasoning) → a culture/values round. There is no LeetCode-style timed online assessment; the take-home is the cente</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>Yes. Wolverine reviews applications on a rolling basis and closes positions once all slots are filled. Per QuantNet: most offers are made before December</t>
+          <t xml:space="preserve">Partly. Each cohort is posted with set term dates and reviewed as applications arrive, so applying early matters. There is no single hard per-posting deadline; </t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>$63 per hour ($10,920/month) for SWE interns (2024 data via Levels.fyi). $3,000 sign-on bonus. Fully paid corporate housing near the Loop, free gym, CTA pass, a</t>
+          <t>No official US intern rate is published. Community data (Levels.fyi, Canada-weighted): ~$31.72/hr (~$5,500/mo) average for SWE interns; Glassdoor lists Vancouve</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Expected August to September 2026 for summer 2027 roles. Rolling review; most spots filled by December 2026. Projected from prior cycles and industry patterns</t>
+          <t>Not yet posted. Summer 2027 developer-intern roles are expected to open ~Fall 2026 through Winter 2026–27, projected from prior cycles (Summer 2026 roles were posted in late 2025). All 2027 dates are expected, not official</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>Abnormal Security</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -5506,17 +5502,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>September–December 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Developer Intern: Software / Platform (primary); Data Intern (Enterprise Analytics / Data Engineering)  (2 of 5 tracks)</t>
+          <t>Software Engineer Intern (primary); ML / Detection Engineer Intern; ML Engineer Intern (Message Security); Non-technical tracks (documented 2022)  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>1password.com/careers</t>
+          <t>abnormal.ai/careers/open-roles</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -5526,30 +5522,34 @@
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Recruiter screen (sometimes an AI-helped pre-screen) → hiring-manager interview → a ~48-hour take-home assignment → one or two technical deep-dives (coding plus design and threat-aware reasoning) → a culture/values round. There is no LeetCode-style timed online assessment; the take-home is the cente</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr"/>
+          <t>Typically a recruiter screen, a hiring-manager interview, an AI-assisted technical screen, and around four team-member rounds. The technical screen is AI-native: recent candidates were given a large codebase, told to understand it using AI, then asked to implement a feature and write tests. Abnormal</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>NOT FOUND. No intern-specific visa-sponsorship information was located in public sources. Confirm sponsorship directly with the recruiter if an intern req appears. Abnormal Security has no scheduled intern program today,</t>
+        </is>
+      </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly. Each cohort is posted with set term dates and reviewed as applications arrive, so applying early matters. There is no single hard per-posting deadline; </t>
+          <t>Not confirmed for interns. Full-time roles fill on a rolling basis; overall hiring averages ~31 days (Glassdoor, 149 interviews). Historical intern roles were s</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>No official US intern rate is published. Community data (Levels.fyi, Canada-weighted): ~$31.72/hr (~$5,500/mo) average for SWE interns; Glassdoor lists Vancouve</t>
+          <t xml:space="preserve">No official 2027 figure. Community data (Levels.fyi, 2023 cycle): SWE intern ~$50.95/hr (~$8,831/mo) plus a $1,250 housing data point; Glassdoor blended intern </t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Not yet posted. Summer 2027 developer-intern roles are expected to open ~Fall 2026 through Winter 2026–27, projected from prior cycles (Summer 2026 roles were posted in late 2025). All 2027 dates are expected, not official</t>
+          <t>Not yet announced. No annual intern program exists. If a SWE/ML intern req returns, applications for summer 2027 are expected to open around fall 2026 (projected from the 2023 technical-intern cycle)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Abnormal Security</t>
+          <t>Abridge</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (primary); ML / Detection Engineer Intern; ML Engineer Intern (Message Security); Non-technical tracks (documented 2022)  (4 of 5 tracks)</t>
+          <t>Software Engineering / Full Stack Intern (documented); Software Engineer – Early Careers (full-time, new grad); Machine Learning Scientist (full-time; MS/PhD); ML Infrastructure Engineer, Model Inference (full-time); Research Scientist (full-time)</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>abnormal.ai/careers/open-roles</t>
+          <t>jobs.ashbyhq.com/abridge</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -5579,34 +5579,30 @@
       </c>
       <c r="G92" s="6" t="inlineStr">
         <is>
-          <t>Typically a recruiter screen, a hiring-manager interview, an AI-assisted technical screen, and around four team-member rounds. The technical screen is AI-native: recent candidates were given a large codebase, told to understand it using AI, then asked to implement a feature and write tests. Abnormal</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>NOT FOUND. No intern-specific visa-sponsorship information was located in public sources. Confirm sponsorship directly with the recruiter if an intern req appears. Abnormal Security has no scheduled intern program today,</t>
-        </is>
-      </c>
+          <t>Intern-specific rounds are not published. Abridge's full-time SWE process is the closest proxy: a recruiter call, a technical conversation with the hiring manager (a complex-project deep dive plus a mini system-design exercise), an onsite panel (coding, system design, and product sense), and sometim</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed for interns. Full-time roles fill on a rolling basis; overall hiring averages ~31 days (Glassdoor, 149 interviews). Historical intern roles were s</t>
+          <t>Not confirmed for interns. The Summer 2026 intern req was a single San Francisco cohort rather than an explicitly rolling posting. Full-time roles are posted in</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No official 2027 figure. Community data (Levels.fyi, 2023 cycle): SWE intern ~$50.95/hr (~$8,831/mo) plus a $1,250 housing data point; Glassdoor blended intern </t>
+          <t>$40.00/hour (Tier 1), confirmed on the official JD and Levels.fyi, roughly $83K annualized. Relocation flights to and from San Francisco are covered; housing is</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>Not yet announced. No annual intern program exists. If a SWE/ML intern req returns, applications for summer 2027 are expected to open around fall 2026 (projected from the 2023 technical-intern cycle)</t>
+          <t>Not yet published. Expected to open ~Fall 2026 for the Summer 2027 cohort, projected from the Summer 2026 cycle (that posting appeared in late 2025 / early 2026, roughly 6+ months ahead). No official Summer 2027 date confirmed as of August 2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Abridge</t>
+          <t>Activision Blizzard</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -5621,12 +5617,12 @@
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering / Full Stack Intern (documented); Software Engineer – Early Careers (full-time, new grad); Machine Learning Scientist (full-time; MS/PhD); ML Infrastructure Engineer, Model Inference (full-time); Research Scientist (full-time)</t>
+          <t>Gameplay Engineering; Engine &amp; Systems Engineering; Online Technology Engineering; Tools Engineering; Build Engineering; Knowledge Systems Engineering</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/abridge</t>
+          <t>careers.activisionblizzard.com/early-careers</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -5636,30 +5632,30 @@
       </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Intern-specific rounds are not published. Abridge's full-time SWE process is the closest proxy: a recruiter call, a technical conversation with the hiring manager (a complex-project deep dive plus a mini system-design exercise), an onsite panel (coding, system design, and product sense), and sometim</t>
+          <t>Typically about three rounds: a recruiter screen plus two technical rounds with a hiring manager and a senior engineer. Coding is described as easy LeetCode with heavy weight on resume and project depth and on which engineering area you want; some pipelines add an online Java/C++ coding test. Timeli</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed for interns. The Summer 2026 intern req was a single San Francisco cohort rather than an explicitly rolling posting. Full-time roles are posted in</t>
+          <t>Partially. There is a defined seasonal window (opens ~September), but review inside it is rolling: "a recruiter will reach out if there is a fit." Applicants ar</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>$40.00/hour (Tier 1), confirmed on the official JD and Levels.fyi, roughly $83K annualized. Relocation flights to and from San Francisco are covered; housing is</t>
+          <t>Official base pay range for the engineering intern role: $20 to $50 per hour, plus a living stipend and opt-in relocation reimbursement. Fully paid. Community e</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>Not yet published. Expected to open ~Fall 2026 for the Summer 2027 cohort, projected from the Summer 2026 cycle (that posting appeared in late 2025 / early 2026, roughly 6+ months ahead). No official Summer 2027 date confirmed as of August 2026</t>
+          <t xml:space="preserve">Open now : 17 Activision US 2027 Summer Internships posted September 10 to 16, 2026 on the Workday board (Software, Game, Graphics and Analytics Engineering, Game Design, Tech Art, Animation, Environment Art, VFX, Audio, UI/UX, Production, Game Economy, User Research, InfoSec, IT, MBA). No close dates printed; on the 2026 pattern most engineering roles close ~November and art roles run longer. No </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Activision Blizzard</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -5669,17 +5665,17 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September 2026 – March 2027</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Gameplay Engineering; Engine &amp; Systems Engineering; Online Technology Engineering; Tools Engineering; Build Engineering; Knowledge Systems Engineering</t>
+          <t>Software Engineer Intern; AI/ML Intern; Data Science Intern; Adobe Digital Academy  (4 of 9 tracks)</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>careers.activisionblizzard.com/early-careers</t>
+          <t>careers.adobe.com/us/en/intern-and-graduate</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -5689,30 +5685,34 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Typically about three rounds: a recruiter screen plus two technical rounds with a hiring manager and a senior engineer. Coding is described as easy LeetCode with heavy weight on resume and project depth and on which engineering area you want; some pipelines add an online Java/C++ coding test. Timeli</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr"/>
+          <t>You apply online, then take a 60-to-90-minute HackerRank OA with 2 to 3 medium-difficulty coding problems. Then a recruiter phone screen, a 45-to-60-minute technical deep dive (live coding or portfolio review), and a final loop of 2 to 3 rounds covering technical and behavioral questions aligned wit</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Adobe actively sponsors international students: CPT, OPT (STEM extension eligible), and H-1B. Roughly 900 H-1B petitions filed annually (community estimate)</t>
+        </is>
+      </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>Partially. There is a defined seasonal window (opens ~September), but review inside it is rolling: "a recruiter will reach out if there is a fit." Applicants ar</t>
+          <t>Yes. Applications reviewed as they come in; 70% of interview invites go to candidates who applied in the first 3 weeks (community estimate)</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>Official base pay range for the engineering intern role: $20 to $50 per hour, plus a living stipend and opt-in relocation reimbursement. Fully paid. Community e</t>
+          <t>Posted 2027 ranges: Software Engineer intern $38–$51/hr, Machine Learning Engineer intern $45–$55/hr. Community estimates run higher: undergrad/Master's $48–$62</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open now : 17 Activision US 2027 Summer Internships posted September 10 to 16, 2026 on the Workday board (Software, Game, Graphics and Analytics Engineering, Game Design, Tech Art, Animation, Environment Art, VFX, Audio, UI/UX, Production, Game Economy, User Research, InfoSec, IT, MBA). No close dates printed; on the 2026 pattern most engineering roles close ~November and art roles run longer. No </t>
+          <t>OPEN NOW for summer 2027. 2027 Intern postings went live September 18, 2026 (Software Engineer across 7 US sites at $38–$51/hr, Machine Learning Engineer, Sales Academy BDR, Solutions Consulting and other New York analyst roles); MBA Product Manager and Product Marketing Manager interns posted September 30. No deadline printed; priority window projected to close roughly early Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -5722,17 +5722,17 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – March 2027</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; AI/ML Intern; Data Science Intern; Adobe Digital Academy  (4 of 9 tracks)</t>
+          <t>Software Engineering Intern; Data Science &amp; Analytics Intern; Connect Engineering Apprentice  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>careers.adobe.com/us/en/intern-and-graduate</t>
+          <t>careers.airbnb.com/internship-programs/</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -5742,34 +5742,34 @@
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>You apply online, then take a 60-to-90-minute HackerRank OA with 2 to 3 medium-difficulty coding problems. Then a recruiter phone screen, a 45-to-60-minute technical deep dive (live coding or portfolio review), and a final loop of 2 to 3 rounds covering technical and behavioral questions aligned wit</t>
+          <t>You apply, complete a CodeSignal GCA (750+ out of 850 to pass), then a recruiter phone screen, a 45- to 60-minute technical phone interview on CoderPad, and a 3- to 4-hour virtual onsite with two coding rounds and a dedicated core-values behavioral round. Offers arrive within 1 to 2 weeks.</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>Adobe actively sponsors international students: CPT, OPT (STEM extension eligible), and H-1B. Roughly 900 H-1B petitions filed annually (community estimate)</t>
+          <t>CPT supported for F-1 students, OPT for new graduates, STEM OPT extension eligible. No J-1 sponsorship for most internship postings</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed as they come in; 70% of interview invites go to candidates who applied in the first 3 weeks (community estimate)</t>
+          <t>Yes. Airbnb reviews applications on a rolling basis and most slots are allocated by mid-November. Apply by October for priority consideration</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Posted 2027 ranges: Software Engineer intern $38–$51/hr, Machine Learning Engineer intern $45–$55/hr. Community estimates run higher: undergrad/Master's $48–$62</t>
+          <t xml:space="preserve">$49 to $68 per hour ($8,500 to $11,500/month) depending on role. Housing stipend of $4,000+/month or corporate accommodations. Levels.fyi reports $49.38/hr for </t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027. 2027 Intern postings went live September 18, 2026 (Software Engineer across 7 US sites at $38–$51/hr, Machine Learning Engineer, Sales Academy BDR, Solutions Consulting and other New York analyst roles); MBA Product Manager and Product Marketing Manager interns posted September 30. No deadline printed; priority window projected to close roughly early Oct 2026</t>
+          <t>Expected early September 2026 for summer 2027 roles. Priority deadline around mid-October 2026, rolling through late November 2026. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -5779,17 +5779,17 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>September 2026</t>
+          <t>September 2026 – June 2027</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science &amp; Analytics Intern; Connect Engineering Apprentice  (3 of 6 tracks)</t>
+          <t>SDE Intern; Applied Scientist Intern; Data Scientist Intern; Business Intelligence Engineer Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>careers.airbnb.com/internship-programs/</t>
+          <t>amazon.jobs/en/teams/internships-for-students</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -5799,34 +5799,34 @@
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a CodeSignal GCA (750+ out of 850 to pass), then a recruiter phone screen, a 45- to 60-minute technical phone interview on CoderPad, and a 3- to 4-hour virtual onsite with two coding rounds and a dedicated core-values behavioral round. Offers arrive within 1 to 2 weeks.</t>
+          <t>You apply, take a two-hour online assessment (two coding problems, a debugging section, a Work Simulation, and a Work Styles questionnaire), then one to five virtual rounds blending behavioral questions with live coding. Then offers come within five business days.</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students, OPT for new graduates, STEM OPT extension eligible. No J-1 sponsorship for most internship postings</t>
+          <t>Varies by role. Engineering and science commonly sponsor; the 2027 Finance and Operations JDs state they cannot</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>Yes. Airbnb reviews applications on a rolling basis and most slots are allocated by mid-November. Apply by October for priority consideration</t>
+          <t>Yes, confirmed. Roles are reviewed and filled rolling; apply within the first 1 to 2 weeks of a posting</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$49 to $68 per hour ($8,500 to $11,500/month) depending on role. Housing stipend of $4,000+/month or corporate accommodations. Levels.fyi reports $49.38/hr for </t>
+          <t>SDE Seattle $110,500 to $160,000 annualized base, about $53 to $77/hr (official JD). Return-offer TC ~$178k to $185k (community, Blind)</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>Expected early September 2026 for summer 2027 roles. Priority deadline around mid-October 2026, rolling through late November 2026. Projected from the Summer 2026 cycle</t>
+          <t>OPEN NOW. 37 US intern roles titled 2027 live at amazon.jobs as of Sep 21, 2026, led by the flagship Software Development Engineer Intern, Summer 2027 (USA) posted Sep 17, plus AWS Solutions Architect, Annapurna Labs, Robotics, PMT, Finance Rotation, Area Manager and WHS Specialist. Rolling review</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMC Networks</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -5836,17 +5836,17 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>September 2026 – June 2027</t>
+          <t>September–October 2026</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>SDE Intern; Applied Scientist Intern; Data Scientist Intern; Business Intelligence Engineer Intern; Data Engineer Intern  (5 of 6 tracks)</t>
+          <t>Global Technology &amp; Operations  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>amazon.jobs/en/teams/internships-for-students</t>
+          <t>amcglobalmedia.com/careers/</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -5856,34 +5856,34 @@
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>You apply, take a two-hour online assessment (two coding problems, a debugging section, a Work Simulation, and a Work Styles questionnaire), then one to five virtual rounds blending behavioral questions with live coding. Then offers come within five business days.</t>
+          <t>An initial recruiter or HR screen, then typically one or two interview rounds (a first round plus a second round with the hiring team) running through February. There is no coding online assessment; the process is resume-and-interview-based and probes genuine interest, communication, and self-direct</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>Varies by role. Engineering and science commonly sponsor; the 2027 Finance and Operations JDs state they cannot</t>
+          <t>No. The Corporate Communications posting specifies applicants must be "eligible to work in the United States without sponsorship"; expect the same across other tracks</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Roles are reviewed and filled rolling; apply within the first 1 to 2 weeks of a posting</t>
+          <t xml:space="preserve">No clear evidence of rolling. Applications appear to close on a set date (~mid-January), followed by a batched, cohort-timed interview period (first and second </t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>SDE Seattle $110,500 to $160,000 annualized base, about $53 to $77/hr (official JD). Return-offer TC ~$178k to $185k (community, Blind)</t>
+          <t>$20.00/hour for most tracks (Marketing, Communications, Programming &amp; Production) and $25.00/hour for the Legal track (J.D. students), per the summer 2026 posti</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 37 US intern roles titled 2027 live at amazon.jobs as of Sep 21, 2026, led by the flagship Software Development Engineer Intern, Summer 2027 (USA) posted Sep 17, plus AWS Solutions Architect, Annapurna Labs, Robotics, PMT, Finance Rotation, Area Manager and WHS Specialist. Rolling review</t>
+          <t>Not yet posted. Expected: applications for summer 2027 open around fall 2026 (~Sept–Oct 2026) with a deadline around mid-January 2027. Basis: the summer 2026 listings were removed Jan 14, 2026 and the summer 2025 posting closed Jan 22, 2025</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>AMC Networks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -5893,17 +5893,17 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>September–October 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>Global Technology &amp; Operations  (1 of 6 tracks)</t>
+          <t>IT &amp; Digital Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>amcglobalmedia.com/careers/</t>
+          <t>jobs.aa.com/go/Interns-&amp;-Grads/9297200/</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -5913,27 +5913,27 @@
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>An initial recruiter or HR screen, then typically one or two interview rounds (a first round plus a second round with the hiring team) running through February. There is no coding online assessment; the process is resume-and-interview-based and probes genuine interest, communication, and self-direct</t>
+          <t>You apply online, pass ATS screening, complete a recruiter phone screen (20 to 30 minutes), potentially record a HireVue video assessment, then do 1 to 2 behavioral and technical interviews (45 to 60 minutes each). Glassdoor rates interview difficulty at 2.9 out of 5.</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>No. The Corporate Communications posting specifies applicants must be "eligible to work in the United States without sponsorship"; expect the same across other tracks</t>
+          <t>CPT supported for F-1 students during internships. H-1B sponsorship is limited for entry-level programs; most postings require existing U.S. work authorization</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No clear evidence of rolling. Applications appear to close on a set date (~mid-January), followed by a batched, cohort-timed interview period (first and second </t>
+          <t>Yes. American Airlines reviews applications on a rolling basis and extends offers through November to early February. Early applicants see roughly 40% higher in</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>$20.00/hour for most tracks (Marketing, Communications, Programming &amp; Production) and $25.00/hour for the Legal track (J.D. students), per the summer 2026 posti</t>
+          <t>Undergraduate: $28–$35/hr; Graduate: $40–$52/hr. SWE interns reported $33.75/hr (Levels.fyi, Summer 2025). Relocation stipend of $2,000–$3,000. No company-provi</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>Not yet posted. Expected: applications for summer 2027 open around fall 2026 (~Sept–Oct 2026) with a deadline around mid-January 2027. Basis: the summer 2026 listings were removed Jan 14, 2026 and the summer 2025 posting closed Jan 22, 2025</t>
+          <t>American Airlines says internship applications open in September, with rolling review, and publishes no specific dates or deadlines. On October 10, 2026, no internship postings were listed on jobs.aa.com. Projected from the prior cycle, not confirmed for this one: priority deadline around late October, final deadline mid-November</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -16295,12 +16295,12 @@
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
+          <t>See guide</t>
         </is>
       </c>
       <c r="E283" s="7" t="inlineStr">
         <is>
-          <t>careers.ulta.com/internships</t>
+          <t>ubs.com/global/en/careers/early-careers.html</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -16310,30 +16310,34 @@
       </c>
       <c r="G283" s="6" t="inlineStr">
         <is>
-          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
-        </is>
-      </c>
-      <c r="H283" s="6" t="inlineStr"/>
+          <t>Four to five back-to-back interviews, each roughly 30 minutes, with Associates, VPs, and Directors. The format mixes behavioral questions (resume walkthrough, teamwork, setback stories) with technical questions for front-office roles (DCF, three-statement linking, EV vs. equity value, LBO basics). S</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="inlineStr">
+        <is>
+          <t>Many US internship positions explicitly state they do not offer employment-based immigration sponsorship, including OPT and CPT. This is confirmed across Global Banking, Global Wealth Management, and Asset Management pos</t>
+        </is>
+      </c>
       <c r="I283" s="6" t="inlineStr">
         <is>
-          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
+          <t>Yes. UBS reviews on a rolling basis; front-office US Summer 2027 seats filled by May 2026, so early-window seats go fast. Five US 2027 Summer Internship posting</t>
         </is>
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>$25.00 per hour on the 2027-cycle corporate postings we checked (Corporate Strategy, Audit, Ecommerce) and $30.00 per hour on the distribution-center postings w</t>
+          <t>$43–$55/hr depending on division (Global Banking $52.88; Global Wealth Management $43.27)</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>Open now for Summer 2027: 22 US intern postings live on Oct 1, 2026 (15 corporate at Bolingbrook, 7 distribution center), posted Sept 14–23, 2026. No deadline printed on the postings we checked; the 2026 cycle closed January 1, so a deadline around January 1, 2027 is expected. Apply early for priority</t>
+          <t>Open now for summer 2027: US internships in Technology, Group Risk Control and Chief Operating Office (New York/New Jersey and Raleigh) were listed on UBS's early-careers job gateway on October 10, 2026. Front-office US tracks (Investment Banking, Global Markets, Wealth Management, Asset Management, Research) were not listed that day and are expected December 2026 to January 2027, rolling until fi</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -16348,12 +16352,12 @@
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
+          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
+          <t>careers.ulta.com/internships</t>
         </is>
       </c>
       <c r="F284" s="7" t="inlineStr">
@@ -16363,34 +16367,30 @@
       </c>
       <c r="G284" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
-        </is>
-      </c>
-      <c r="H284" s="6" t="inlineStr">
-        <is>
-          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
-        </is>
-      </c>
+          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
+        </is>
+      </c>
+      <c r="H284" s="6" t="inlineStr"/>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
+          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
         </is>
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
+          <t>$25.00 per hour on the 2027-cycle corporate postings we checked (Corporate Strategy, Audit, Ecommerce) and $30.00 per hour on the distribution-center postings w</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr">
         <is>
-          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Open now for Summer 2027: 22 US intern postings live on Oct 1, 2026 (15 corporate at Bolingbrook, 7 distribution center), posted Sept 14–23, 2026. No deadline printed on the postings we checked; the 2026 cycle closed January 1, so a deadline around January 1, 2027 is expected. Apply early for priority</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -16400,17 +16400,17 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern  (1 of 3 tracks)</t>
+          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E285" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/weaviate</t>
+          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
         </is>
       </c>
       <c r="F285" s="7" t="inlineStr">
@@ -16420,34 +16420,34 @@
       </c>
       <c r="G285" s="6" t="inlineStr">
         <is>
-          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
+          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
         </is>
       </c>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
+          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
+          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
         </is>
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
+          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
+          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -16457,17 +16457,17 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – March 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
+          <t>Software Engineer Intern  (1 of 3 tracks)</t>
         </is>
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>coreweave.com/careers/weights-biases</t>
+          <t>jobs.ashbyhq.com/weaviate</t>
         </is>
       </c>
       <c r="F286" s="7" t="inlineStr">
@@ -16477,34 +16477,34 @@
       </c>
       <c r="G286" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
+          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
+          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
+          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
         </is>
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
+          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
         </is>
       </c>
       <c r="K286" s="6" t="inlineStr">
         <is>
-          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -16514,17 +16514,17 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>October 2026 – March 2027</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E287" s="7" t="inlineStr">
         <is>
-          <t>wellsfargojobs.com/en/early-careers/</t>
+          <t>coreweave.com/careers/weights-biases</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
@@ -16534,34 +16534,34 @@
       </c>
       <c r="G287" s="6" t="inlineStr">
         <is>
-          <t>Four stages. First, an online application with resume upload and motivation questions. Second, an online assessment with cognitive or situational judgment tests (coding challenges for tech roles). Third, a HireVue video interview with 3 to 7 behavioral questions and a 24 to 48 hour preparation windo</t>
+          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
         </is>
       </c>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>No. Wells Fargo explicitly requires authorization to work in the United States on a full-time basis and does not sponsor work visas for internships, post-graduation programs, or permanent employment. There is no assistan</t>
+          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
         <is>
-          <t>Yes. Wells Fargo reviews and fills positions as qualified candidates are identified</t>
+          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
         </is>
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>$31–$53/hr ($64,500 to $110,000+ annualized); CIB IB at top with $2,500 housing stipend</t>
+          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostly closed for summer 2027. As of October 6, 2026, Finance, HR, Audit, Commercial Banking, Consumer Banking and Lending, Global Payments, Wealth &amp; Investment Management, Corporate Risk, COO, Quantitative Analytics and Public Affairs have all come down. Still live for summer 2027: Technology Software Engineering (Posting End Date October 13, 2026) and the MBA Investment Banking Summer Associate </t>
+          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -16571,17 +16571,17 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>Decision Analytics Associate (DAA); Business Technology Solutions Associate (BTSA)  (2 of 4 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>jobs.zs.com/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
+          <t>wellsfargojobs.com/en/early-careers/</t>
         </is>
       </c>
       <c r="F288" s="7" t="inlineStr">
@@ -16591,34 +16591,34 @@
       </c>
       <c r="G288" s="6" t="inlineStr">
         <is>
-          <t>The process runs two to four rounds: an online aptitude test covering logical, quantitative, and verbal reasoning, then case and behavioral interviews. ZS cases are candidate-led and often pharma or healthcare themed. Final rounds may include a written case presentation where you analyze a data pack</t>
+          <t>Four stages. First, an online application with resume upload and motivation questions. Second, an online assessment with cognitive or situational judgment tests (coding challenges for tech roles). Third, a HireVue video interview with 3 to 7 behavioral questions and a 24 to 48 hour preparation windo</t>
         </is>
       </c>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>Yes. ZS's official FAQ states the firm offers visa sponsorship for full-time employees and support for interns with a student visa. Sponsorship type and reimbursement may vary based on location, role, and status. ZS file</t>
+          <t>No. Wells Fargo explicitly requires authorization to work in the United States on a full-time basis and does not sponsor work visas for internships, post-graduation programs, or permanent employment. There is no assistan</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>Yes. ZS recruits on a rolling basis during campus season; intern spots fill as strong candidates clear the rounds</t>
+          <t>Yes. Wells Fargo reviews and fills positions as qualified candidates are identified</t>
         </is>
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>~$34/hr general intern range ($25–$46); Strategy Insights &amp; Planning ~$50/hr; Business Technology Solutions ~$63/hr</t>
+          <t>$31–$53/hr ($64,500 to $110,000+ annualized); CIB IB at top with $2,500 housing stipend</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: nine North America intern postings live on jobs.zs.com as of October 1, 2026 (posted September 1–2). Rolling review; no deadline printed in the postings we checked</t>
+          <t xml:space="preserve">Mostly closed for summer 2027. As of October 6, 2026, Finance, HR, Audit, Commercial Banking, Consumer Banking and Lending, Global Payments, Wealth &amp; Investment Management, Corporate Risk, COO, Quantitative Analytics and Public Affairs have all come down. Still live for summer 2027: Technology Software Engineering (Posting End Date October 13, 2026) and the MBA Investment Banking Summer Associate </t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -16628,17 +16628,17 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
+          <t>Decision Analytics Associate (DAA); Business Technology Solutions Associate (BTSA)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr">
         <is>
-          <t>biibhr.wd3.myworkdayjobs.com/external</t>
+          <t>jobs.zs.com/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
@@ -16648,34 +16648,34 @@
       </c>
       <c r="G289" s="6" t="inlineStr">
         <is>
-          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
+          <t>The process runs two to four rounds: an online aptitude test covering logical, quantitative, and verbal reasoning, then case and behavioral interviews. ZS cases are candidate-led and often pharma or healthcare themed. Final rounds may include a written case presentation where you analyze a data pack</t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
+          <t>Yes. ZS's official FAQ states the firm offers visa sponsorship for full-time employees and support for interns with a student visa. Sponsorship type and reimbursement may vary based on location, role, and status. ZS file</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
         <is>
-          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
+          <t>Yes. ZS recruits on a rolling basis during campus season; intern spots fill as strong candidates clear the rounds</t>
         </is>
       </c>
       <c r="J289" s="6" t="inlineStr">
         <is>
-          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
+          <t>~$34/hr general intern range ($25–$46); Strategy Insights &amp; Planning ~$50/hr; Business Technology Solutions ~$63/hr</t>
         </is>
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted as of October 1, 2026). Separate January to June 2027 co-ops are open now</t>
+          <t>Open now for summer 2027: nine North America intern postings live on jobs.zs.com as of October 1, 2026 (posted September 1–2). Rolling review; no deadline printed in the postings we checked</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -16685,17 +16685,17 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>December 2026</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>Cubist Quantitative Researcher; Cubist Quantitative Developer; Technology – Software Engineer; Data Engineer (Market Intelligence); AI Analyst  (5 of 6 tracks)</t>
+          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>careers.point72.com/?experience=internships</t>
+          <t>biibhr.wd3.myworkdayjobs.com/external</t>
         </is>
       </c>
       <c r="F290" s="7" t="inlineStr">
@@ -16705,34 +16705,34 @@
       </c>
       <c r="G290" s="6" t="inlineStr">
         <is>
-          <t>The Academy runs a five-stage funnel that's more structured than most hedge fund processes. Each stage is designed to filter for a specific trait: 1. Submit your application at careers.point72.com with your resume, essays, and supplementary materials. Expect a 300-word essay on "market inefficiency"</t>
+          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
         </is>
       </c>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>Yes. Point72 sponsors CPT, OPT, and H-1B visas. The firm had approximately 150 visa approvals in FY2025. That said, the process is selective, and third-party estimates suggest roughly 30 to 40% odds for Academy graduates</t>
+          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>Yes. No set deadline; candidates reviewed as they apply until the program is at capacity</t>
+          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
         </is>
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>Academy: $120K–$140K annualized + $2,500–$5,000 signing bonus; Cubist Summer 2027 Quantitative Research intern (KEPL, PhD): $240K–$300K annualized base, prorate</t>
+          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
         </is>
       </c>
       <c r="K290" s="6" t="inlineStr">
         <is>
-          <t>US Academy, summer 2028: expected to open around December 2026 (the summer 2027 posting went live in early December 2025 and closed by early May 2026). Open now for summer 2027: Investment Services Internship (New York/Stamford), Cubist and Point72 quant research intern roles, and the Academy internship in Hong Kong, Singapore and Japan. All rolling.</t>
+          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted as of October 1, 2026). Separate January to June 2027 co-ops are open now</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -16742,17 +16742,17 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>December 2026</t>
         </is>
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
+          <t>Cubist Quantitative Researcher; Cubist Quantitative Developer; Technology – Software Engineer; Data Engineer (Market Intelligence); AI Analyst  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr">
         <is>
-          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
+          <t>careers.point72.com/?experience=internships</t>
         </is>
       </c>
       <c r="F291" s="7" t="inlineStr">
@@ -16762,30 +16762,34 @@
       </c>
       <c r="G291" s="6" t="inlineStr">
         <is>
-          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
-        </is>
-      </c>
-      <c r="H291" s="6" t="inlineStr"/>
+          <t>The Academy runs a five-stage funnel that's more structured than most hedge fund processes. Each stage is designed to filter for a specific trait: 1. Submit your application at careers.point72.com with your resume, essays, and supplementary materials. Expect a 300-word essay on "market inefficiency"</t>
+        </is>
+      </c>
+      <c r="H291" s="6" t="inlineStr">
+        <is>
+          <t>Yes. Point72 sponsors CPT, OPT, and H-1B visas. The firm had approximately 150 visa approvals in FY2025. That said, the process is selective, and third-party estimates suggest roughly 30 to 40% odds for Academy graduates</t>
+        </is>
+      </c>
       <c r="I291" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
+          <t>Yes. No set deadline; candidates reviewed as they apply until the program is at capacity</t>
         </is>
       </c>
       <c r="J291" s="6" t="inlineStr">
         <is>
-          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
+          <t>Academy: $120K–$140K annualized + $2,500–$5,000 signing bonus; Cubist Summer 2027 Quantitative Research intern (KEPL, PhD): $240K–$300K annualized base, prorate</t>
         </is>
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
+          <t>US Academy, summer 2028: expected to open around December 2026 (the summer 2027 posting went live in early December 2025 and closed by early May 2026). Open now for summer 2027: Investment Services Internship (New York/Stamford), Cubist and Point72 quant research intern roles, and the Academy internship in Hong Kong, Singapore and Japan. All rolling.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -16795,17 +16799,17 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>iXp Software Engineering; iXp AI Software Developer; iXp Data Engineering  (3 of 6 tracks)</t>
+          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>jobs.sap.com/go/Intern-Jobs-in-the-United-States/872801/</t>
+          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
         </is>
       </c>
       <c r="F292" s="7" t="inlineStr">
@@ -16815,34 +16819,30 @@
       </c>
       <c r="G292" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typically 3 to 4 stages: automated coding challenge via Codility or HackerRank (60 to 90 minutes, LeetCode Medium), recruiter phone screen (30 minutes), technical interview (60 to 75 minutes), and behavioral interview (45 to 60 minutes, STAR method). Select roles include an Assessment Center with a </t>
-        </is>
-      </c>
-      <c r="H292" s="6" t="inlineStr">
-        <is>
-          <t>F-1 CPT and OPT fully eligible. Some roles explicitly do not provide visa sponsorship; check individual JDs. H-1B available for full-time conversion</t>
-        </is>
-      </c>
+          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
+        </is>
+      </c>
+      <c r="H292" s="6" t="inlineStr"/>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed rolling; submissions in the first 2 weeks get higher visibility. Employee referrals advance at 3 to 5x the cold-applicatio</t>
+          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
         </is>
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>SWE US $32 to $56/hr (~$5,500 to $8,500/month). Master's-level candidates earn 15 to 20% premiums. Full posted range $15 to $62/hr across all roles</t>
+          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
         </is>
       </c>
       <c r="K292" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 iXp roles: not posted yet on October 6, 2026; expected around February to April 2027, projected from the 1 to 3 month lead on current postings. Off-cycle US iXp roles (6 to 12 months, starting October 2026 to early 2027) are open now</t>
+          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -16852,17 +16852,17 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>GEICO TDP Software &amp; AI Intern  (1 of 6 tracks)</t>
+          <t>iXp Software Engineering; iXp AI Software Developer; iXp Data Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E293" s="7" t="inlineStr">
         <is>
-          <t>geico.wd1.myworkdayjobs.com/External</t>
+          <t>jobs.sap.com/go/Intern-Jobs-in-the-United-States/872801/</t>
         </is>
       </c>
       <c r="F293" s="7" t="inlineStr">
@@ -16872,34 +16872,34 @@
       </c>
       <c r="G293" s="6" t="inlineStr">
         <is>
-          <t>Most subsidiaries use 1 to 2 rounds: a recruiter phone screen followed by a hiring-manager interview. GEICO tech adds a technical skills assessment. Behavioral questions focus on integrity, problem-solving, teamwork, and long-term thinking using the STAR method.</t>
+          <t xml:space="preserve">Typically 3 to 4 stages: automated coding challenge via Codility or HackerRank (60 to 90 minutes, LeetCode Medium), recruiter phone screen (30 minutes), technical interview (60 to 75 minutes), and behavioral interview (45 to 60 minutes, STAR method). Select roles include an Assessment Center with a </t>
         </is>
       </c>
       <c r="H293" s="6" t="inlineStr">
         <is>
-          <t>Generally no. GEICO explicitly does not sponsor employment authorization for intern roles. Other subsidiaries typically require existing U.S. work authorization</t>
+          <t>F-1 CPT and OPT fully eligible. Some roles explicitly do not provide visa sponsorship; check individual JDs. H-1B available for full-time conversion</t>
         </is>
       </c>
       <c r="I293" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated by any subsidiary. Most roles accept applications until filled. Apply as soon as postings appear for the best odds</t>
+          <t>Yes, confirmed. Applications reviewed rolling; submissions in the first 2 weeks get higher visibility. Employee referrals advance at 3 to 5x the cold-applicatio</t>
         </is>
       </c>
       <c r="J293" s="6" t="inlineStr">
         <is>
-          <t>Varies widely: GEICO tech $28 to $50+/hr (official JD), BHSI $24 to $43/hr, BH Energy IT $17.50 to $21.50/hr, BNSF ~$20/hr (community), BH GUARD $15 to $20/hr</t>
+          <t>SWE US $32 to $56/hr (~$5,500 to $8,500/month). Master's-level candidates earn 15 to 20% premiums. Full posted range $15 to $62/hr across all roles</t>
         </is>
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
+          <t>Summer 2027 iXp roles: not posted yet on October 6, 2026; expected around February to April 2027, projected from the 1 to 3 month lead on current postings. Off-cycle US iXp roles (6 to 12 months, starting October 2026 to early 2027) are open now</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -16914,12 +16914,12 @@
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
-          <t>Engineering / Developer  (1 of 6 tracks)</t>
+          <t>GEICO TDP Software &amp; AI Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E294" s="7" t="inlineStr">
         <is>
-          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
+          <t>geico.wd1.myworkdayjobs.com/External</t>
         </is>
       </c>
       <c r="F294" s="7" t="inlineStr">
@@ -16929,34 +16929,34 @@
       </c>
       <c r="G294" s="6" t="inlineStr">
         <is>
-          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
+          <t>Most subsidiaries use 1 to 2 rounds: a recruiter phone screen followed by a hiring-manager interview. GEICO tech adds a technical skills assessment. Behavioral questions focus on integrity, problem-solving, teamwork, and long-term thinking using the STAR method.</t>
         </is>
       </c>
       <c r="H294" s="6" t="inlineStr">
         <is>
-          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
+          <t>Generally no. GEICO explicitly does not sponsor employment authorization for intern roles. Other subsidiaries typically require existing U.S. work authorization</t>
         </is>
       </c>
       <c r="I294" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
+          <t>Not officially stated by any subsidiary. Most roles accept applications until filled. Apply as soon as postings appear for the best odds</t>
         </is>
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
-          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
+          <t>Varies widely: GEICO tech $28 to $50+/hr (official JD), BHSI $24 to $43/hr, BH Energy IT $17.50 to $21.50/hr, BNSF ~$20/hr (community), BH GUARD $15 to $20/hr</t>
         </is>
       </c>
       <c r="K294" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
+          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -16966,17 +16966,17 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>March–September 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
+          <t>Engineering / Developer  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E295" s="7" t="inlineStr">
         <is>
-          <t>careers.l3harris.com/en/new-grads-and-interns</t>
+          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
@@ -16986,34 +16986,34 @@
       </c>
       <c r="G295" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
+          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
         </is>
       </c>
       <c r="H295" s="6" t="inlineStr">
         <is>
-          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
+          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
         <is>
-          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
+          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
         </is>
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
+          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
         </is>
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
+          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
+          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
         <is>
-          <t>rocketlabcorp.com/careers/internships/</t>
+          <t>careers.l3harris.com/en/new-grads-and-interns</t>
         </is>
       </c>
       <c r="F296" s="7" t="inlineStr">
@@ -17043,34 +17043,34 @@
       </c>
       <c r="G296" s="6" t="inlineStr">
         <is>
-          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
         </is>
       </c>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
+          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
+          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
         </is>
       </c>
       <c r="J296" s="6" t="inlineStr">
         <is>
-          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
+          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
         </is>
       </c>
       <c r="K296" s="6" t="inlineStr">
         <is>
-          <t>Open now: about 30 Spring 2027 and Summer 2027 intern postings live on Rocket Lab's Greenhouse board since September 9 to 13, 2026 (Long Beach, CA); no published deadline. ITAR: US citizen, green card holder, or other US person status required</t>
+          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -17080,17 +17080,17 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>June–August 2027</t>
+          <t>March–September 2027</t>
         </is>
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>IS/Technology Intern  (1 of 6 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E297" s="7" t="inlineStr">
         <is>
-          <t>careers.amgen.com/en/students-graduates</t>
+          <t>rocketlabcorp.com/careers/internships/</t>
         </is>
       </c>
       <c r="F297" s="7" t="inlineStr">
@@ -17100,34 +17100,34 @@
       </c>
       <c r="G297" s="6" t="inlineStr">
         <is>
-          <t>After applying, expect a recruiter phone screen lasting about 25 to 30 minutes, followed by a 45 to 90 minute hiring manager interview focused on technical skills and behavioral questions in the STAR format. Some roles add a final panel round with multiple stakeholders, which can run two to four hou</t>
+          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
         </is>
       </c>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>No. Every Amgen internship posting states that the company doesn't provide immigration sponsorship for intern roles. International students on CPT or OPT may be eligible to participate, but H-1B sponsorship isn't offered</t>
+          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; positions may close once filled</t>
+          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
         </is>
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>Undergrad $25–$32/hr; graduate $35–$45/hr; housing/relocation stipend for on-site roles</t>
+          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
         </is>
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>Open now: 25 US Summer 2027 requisitions posted August 28 to September 8, 2026; Amgen prints no deadline and accepts applications until it has enough candidates (rolling)</t>
+          <t>Open now: about 30 Spring 2027 and Summer 2027 intern postings live on Rocket Lab's Greenhouse board since September 9 to 13, 2026 (Long Beach, CA); no published deadline. ITAR: US citizen, green card holder, or other US person status required</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -17137,17 +17137,17 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June–August 2027</t>
         </is>
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern; Software Engineering Intern; Electrical Engineering Intern; Cybersecurity Intern; IT / PTECH Intern  (5 of 6 tracks)</t>
+          <t>IS/Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E298" s="7" t="inlineStr">
         <is>
-          <t>jobs.baesystems.com/global/en/leap</t>
+          <t>careers.amgen.com/en/students-graduates</t>
         </is>
       </c>
       <c r="F298" s="7" t="inlineStr">
@@ -17157,34 +17157,34 @@
       </c>
       <c r="G298" s="6" t="inlineStr">
         <is>
-          <t>You apply online, may complete a gamified online assessment, then a 30-minute recruiter phone screen, a non-technical behavioral interview with a hiring manager using STAR+R format, and for engineering roles a technical or in-person interview. Average time to hire is about 17 days (Glassdoor).</t>
+          <t>After applying, expect a recruiter phone screen lasting about 25 to 30 minutes, followed by a 45 to 90 minute hiring manager interview focused on technical skills and behavioral questions in the STAR format. Some roles add a final panel round with multiple stakeholders, which can run two to four hou</t>
         </is>
       </c>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>Very rare. The vast majority of positions require U.S. citizenship or U.S. Person status (citizen, permanent resident, refugee, or asylee). Security-clearance roles require U.S. citizenship specifically</t>
+          <t>No. Every Amgen internship posting states that the company doesn't provide immigration sponsorship for intern roles. International students on CPT or OPT may be eligible to participate, but H-1B sponsorship isn't offered</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">
         <is>
-          <t>Yes. BAE Systems reviews applications as they arrive and fills seats on a rolling basis. Apply within the first few weeks of a posting for the best response rat</t>
+          <t>Yes. Applications reviewed on a rolling basis; positions may close once filled</t>
         </is>
       </c>
       <c r="J298" s="6" t="inlineStr">
         <is>
-          <t>$20 to $37 per hour depending on role level and location. Technical Intern I (freshman-level) starts around $14 to $20/hr; senior technical interns reach $30 to</t>
+          <t>Undergrad $25–$32/hr; graduate $35–$45/hr; housing/relocation stipend for on-site roles</t>
         </is>
       </c>
       <c r="K298" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027. 44 US internship-level Summer 2027 reqs posted on jobs.baesystems.com on September 3, 2026 (one more September 10), across software, systems, electrical, mechanical, RF and microelectronics engineering in New Hampshire, Iowa, New York and San Diego. No deadline is printed on the requisitions</t>
+          <t>Open now: 25 US Summer 2027 requisitions posted August 28 to September 8, 2026; Amgen prints no deadline and accepts applications until it has enough candidates (rolling)</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -17194,17 +17194,17 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>June–December 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>Summer Games: Software Developer Intern; Summer Games: Data Scientist Intern; Summer Games: Systems Engineering Intern; Summer Games: Cybersecurity Intern; Summer Hire: Engineering / Technical  (5 of 6 tracks)</t>
+          <t>Systems Engineering Intern; Software Engineering Intern; Electrical Engineering Intern; Cybersecurity Intern; IT / PTECH Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E299" s="7" t="inlineStr">
         <is>
-          <t>careers.boozallen.com/</t>
+          <t>jobs.baesystems.com/global/en/leap</t>
         </is>
       </c>
       <c r="F299" s="7" t="inlineStr">
@@ -17214,34 +17214,34 @@
       </c>
       <c r="G299" s="6" t="inlineStr">
         <is>
-          <t>Two rounds over roughly four to six weeks. First, a 30-minute recruiter phone or video screen focused on your resume and motivation. Then one to two team interviews with client-facing consultants, heavily behavioral with some technical questions. Glassdoor rates difficulty at 2.4 out of 5.</t>
+          <t>You apply online, may complete a gamified online assessment, then a 30-minute recruiter phone screen, a non-technical behavioral interview with a hiring manager using STAR+R format, and for engineering roles a technical or in-person interview. Average time to hire is about 17 days (Glassdoor).</t>
         </is>
       </c>
       <c r="H299" s="6" t="inlineStr">
         <is>
-          <t>Almost never. The majority of roles require US citizenship for government security clearance eligibility. Non-US citizens cannot obtain clearance</t>
+          <t>Very rare. The vast majority of positions require U.S. citizenship or U.S. Person status (citizen, permanent resident, refugee, or asylee). Security-clearance roles require U.S. citizenship specifically</t>
         </is>
       </c>
       <c r="I299" s="6" t="inlineStr">
         <is>
-          <t>Yes. Booz Allen reviews applications on a rolling basis starting in late August and continuing through the spring. Apply early in the cycle for the most open se</t>
+          <t>Yes. BAE Systems reviews applications as they arrive and fills seats on a rolling basis. Apply within the first few weeks of a posting for the best response rat</t>
         </is>
       </c>
       <c r="J299" s="6" t="inlineStr">
         <is>
-          <t>$26 to $46 per hour depending on role, location, and degree level (Glassdoor, 194 salary reports). Levels.fyi reports $30/hr for SWE interns. No housing or relo</t>
+          <t>$20 to $37 per hour depending on role level and location. Technical Intern I (freshman-level) starts around $14 to $20/hr; senior technical interns reach $30 to</t>
         </is>
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: University Summer 2027 requisitions posting since August 28, 2026 (70 or more live as of September 28, 2026 across McLean, DC, Fayetteville, Beavercreek, Rome NY, Atlanta, Charleston SC, Huntsville AL, Honolulu, San Diego and El Segundo), Workday end dates from about December 2 to December 14, 2026; US citizenship required on cleared roles</t>
+          <t>OPEN NOW for summer 2027. 44 US internship-level Summer 2027 reqs posted on jobs.baesystems.com on September 3, 2026 (one more September 10), across software, systems, electrical, mechanical, RF and microelectronics engineering in New Hampshire, Iowa, New York and San Diego. No deadline is printed on the requisitions</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
@@ -17251,17 +17251,17 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June–December 2027</t>
         </is>
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
-          <t>InnoTech Software Engineering Intern; InnoTech Data Science &amp; Analytics Intern  (2 of 6 tracks)</t>
+          <t>Summer Games: Software Developer Intern; Summer Games: Data Scientist Intern; Summer Games: Systems Engineering Intern; Summer Games: Cybersecurity Intern; Summer Hire: Engineering / Technical  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>jobs.cvshealth.com/us/en/students</t>
+          <t>careers.boozallen.com/</t>
         </is>
       </c>
       <c r="F300" s="7" t="inlineStr">
@@ -17271,34 +17271,34 @@
       </c>
       <c r="G300" s="6" t="inlineStr">
         <is>
-          <t>You apply through Workday, complete a HireVue on-demand video assessment with behavioral questions, then have one or two live virtual interviews with hiring managers. Some tracks include a Superday with four to five 30-minute interviews. Decisions come within one to two weeks.</t>
+          <t>Two rounds over roughly four to six weeks. First, a 30-minute recruiter phone or video screen focused on your resume and motivation. Then one to two team interviews with client-facing consultants, heavily behavioral with some technical questions. Glassdoor rates difficulty at 2.4 out of 5.</t>
         </is>
       </c>
       <c r="H300" s="6" t="inlineStr">
         <is>
-          <t>Limited. Select post-graduation Analytics, Data Science, and MBA roles may offer sponsorship. PharmD and niche cybersecurity roles may also qualify. Most internship tracks do not sponsor</t>
+          <t>Almost never. The majority of roles require US citizenship for government security clearance eligibility. Non-US citizens cannot obtain clearance</t>
         </is>
       </c>
       <c r="I300" s="6" t="inlineStr">
         <is>
-          <t>Yes. CVS Health reviews applications on a rolling basis. Apply in September or October for the best response rates</t>
+          <t>Yes. Booz Allen reviews applications on a rolling basis starting in late August and continuing through the spring. Apply early in the cycle for the most open se</t>
         </is>
       </c>
       <c r="J300" s="6" t="inlineStr">
         <is>
-          <t>$20 to $55 per hour depending on track. Undergraduate corporate roles around $23 to $28/hr; graduate and software engineering roles $45 to $55/hr. Housing stipe</t>
+          <t>$26 to $46 per hour depending on role, location, and degree level (Glassdoor, 194 salary reports). Levels.fyi reports $30/hr for SWE interns. No housing or relo</t>
         </is>
       </c>
       <c r="K300" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 37 Summer 2027 reqs posted September 2 to 9, 2026 (corporate Finance, Supply Chain &amp; Logistics, General Management, plus Retail Store Management in ~30 metros). No deadline: CVS accepts applications "on an ongoing basis" (one Finance req shows an October 31, 2026 end date). Prior cycles ran to March or until filled</t>
+          <t>Open now for summer 2027: University Summer 2027 requisitions posting since August 28, 2026 (70 or more live as of September 28, 2026 across McLean, DC, Fayetteville, Beavercreek, Rome NY, Atlanta, Charleston SC, Huntsville AL, Honolulu, San Diego and El Segundo), Workday end dates from about December 2 to December 14, 2026; US citizenship required on cleared roles</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -17308,17 +17308,17 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>June–December 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Product); SWE Intern (Developer Tools); SWE Intern (Infrastructure); Data Engineer / Data Scientist Intern  (4 of 5 tracks)</t>
+          <t>InnoTech Software Engineering Intern; InnoTech Data Science &amp; Analytics Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E301" s="7" t="inlineStr">
         <is>
-          <t>figma.com/careers/</t>
+          <t>jobs.cvshealth.com/us/en/students</t>
         </is>
       </c>
       <c r="F301" s="7" t="inlineStr">
@@ -17328,34 +17328,34 @@
       </c>
       <c r="G301" s="6" t="inlineStr">
         <is>
-          <t>Figma's interview process spans 3 to 5 weeks with 4 to 6 rounds: a recruiter screen, a Byteboard technical assessment, a hiring manager interview, and a multi-session virtual onsite covering applied coding, system design, behavioral questions, and project deep-dives. For Product Design interns, a Ja</t>
+          <t>You apply through Workday, complete a HireVue on-demand video assessment with behavioral questions, then have one or two live virtual interviews with hiring managers. Some tracks include a Superday with four to five 30-minute interviews. Decisions come within one to two weeks.</t>
         </is>
       </c>
       <c r="H301" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated in job descriptions. Figma is an equal opportunity employer with global offices in 12+ cities</t>
+          <t>Limited. Select post-graduation Analytics, Data Science, and MBA roles may offer sponsorship. PharmD and niche cybersecurity roles may also qualify. Most internship tracks do not sponsor</t>
         </is>
       </c>
       <c r="I301" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling with batch review. The SWE Intern (2026) listing was live Aug 29, 2025 to Jan 29, 2026, closing once filled</t>
+          <t>Yes. CVS Health reviews applications on a rolling basis. Apply in September or October for the best response rates</t>
         </is>
       </c>
       <c r="J301" s="6" t="inlineStr">
         <is>
-          <t>SWE intern NYC $60/hr ($10,400/mo), SF $51.06/hr ($8,850/mo). Plus $2,000/mo housing stipend, meals, travel reimbursement</t>
+          <t>$20 to $55 per hour depending on track. Undergraduate corporate roles around $23 to $28/hr; graduate and software engineering roles $45 to $55/hr. Housing stipe</t>
         </is>
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027: Software Engineer Intern (Summer 2027), Brand Design Intern (Summer 2027), Product Design Intern (2027) and Data Science Intern (2027) posted September 14 to 15, 2026, plus Software Engineer Intern (Winter 2027). SF or New York hub, summer start dates May 3, May 17, June 1 or June 14, 2027. Rolling, no published deadline</t>
+          <t>Open now for summer 2027: 37 Summer 2027 reqs posted September 2 to 9, 2026 (corporate Finance, Supply Chain &amp; Logistics, General Management, plus Retail Store Management in ~30 metros). No deadline: CVS accepts applications "on an ongoing basis" (one Finance req shows an October 31, 2026 end date). Prior cycles ran to March or until filled</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -17365,17 +17365,17 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–December 2027</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>FOX Technology Internship Program  (1 of 6 tracks)</t>
+          <t>SWE Intern (Product); SWE Intern (Developer Tools); SWE Intern (Infrastructure); Data Engineer / Data Scientist Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E302" s="7" t="inlineStr">
         <is>
-          <t>foxcareers.com/internships</t>
+          <t>figma.com/careers/</t>
         </is>
       </c>
       <c r="F302" s="7" t="inlineStr">
@@ -17385,30 +17385,34 @@
       </c>
       <c r="G302" s="6" t="inlineStr">
         <is>
-          <t>First a resume and cover letter (state your top interest areas), then a pre-recorded one-way video interview, then a live hiring-manager interview. You must show knowledge of FOX and the media or sports industry. Decisions can arrive within about a week of the hiring-manager round, though silence be</t>
-        </is>
-      </c>
-      <c r="H302" s="6" t="inlineStr"/>
+          <t>Figma's interview process spans 3 to 5 weeks with 4 to 6 rounds: a recruiter screen, a Byteboard technical assessment, a hiring manager interview, and a multi-session virtual onsite covering applied coding, system design, behavioral questions, and project deep-dives. For Product Design interns, a Ja</t>
+        </is>
+      </c>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated in job descriptions. Figma is an equal opportunity employer with global offices in 12+ cities</t>
+        </is>
+      </c>
       <c r="I302" s="6" t="inlineStr">
         <is>
-          <t>Yes, partially. The official page states interns are accepted on a rolling basis for each term, with a hard deadline as the backstop. Apply early.</t>
+          <t>Likely rolling with batch review. The SWE Intern (2026) listing was live Aug 29, 2025 to Jan 29, 2026, closing once filled</t>
         </is>
       </c>
       <c r="J302" s="6" t="inlineStr">
         <is>
-          <t>$20.00/hour standard; disclosed corporate range $20.00–$30.00/hour. No housing or relocation provided. (Glassdoor/Indeed averages of ~$29–$35/hr blend in gradua</t>
+          <t>SWE intern NYC $60/hr ($10,400/mo), SF $51.06/hr ($8,850/mo). Plus $2,000/mo housing stipend, meals, travel reimbursement</t>
         </is>
       </c>
       <c r="K302" s="6" t="inlineStr">
         <is>
-          <t>For a summer 2027 role, applications are open now. FOX posted its Summer 2027 program reqs on September 28, 2026, and the postings we checked set a general application deadline of Sunday, January 10, 2027, with two sessions (June 7 to July 30, 2027 or June 21 to August 13, 2027). Spring 2027 reqs are also live, with a November 22, 2026 deadline.</t>
+          <t>OPEN NOW for summer 2027: Software Engineer Intern (Summer 2027), Brand Design Intern (Summer 2027), Product Design Intern (2027) and Data Science Intern (2027) posted September 14 to 15, 2026, plus Software Engineer Intern (Winter 2027). SF or New York hub, summer start dates May 3, May 17, June 1 or June 14, 2027. Rolling, no published deadline</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>Glean</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -17423,12 +17427,12 @@
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern: Backend &amp; Infrastructure; SWE Intern: ML / NLP / Search; SWE Intern: UI / Full-Stack; SWE Intern: Security  (4 of 5 tracks)</t>
+          <t>FOX Technology Internship Program  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E303" s="7" t="inlineStr">
         <is>
-          <t>glean.com/careers</t>
+          <t>foxcareers.com/internships</t>
         </is>
       </c>
       <c r="F303" s="7" t="inlineStr">
@@ -17438,34 +17442,30 @@
       </c>
       <c r="G303" s="6" t="inlineStr">
         <is>
-          <t>Glean's SWE intern interview is notably streamlined at just two rounds, shorter than most comparable companies: 1. Apply on glean.com/careers or the Greenhouse board . The Summer 2027 SWE intern posting is live now; submit in October. Tailor your resume to highlight backend, infrastructure, ML, or f</t>
-        </is>
-      </c>
-      <c r="H303" s="6" t="inlineStr">
-        <is>
-          <t>Glean files H-1B visas for full-time roles (9 LCAs in FY2026, median salary $210,000). CPT/OPT likely supported for interns based on past hiring patterns, though not explicitly confirmed</t>
-        </is>
-      </c>
+          <t>First a resume and cover letter (state your top interest areas), then a pre-recorded one-way video interview, then a live hiring-manager interview. You must show knowledge of FOX and the media or sports industry. Decisions can arrive within about a week of the hiring-manager round, though silence be</t>
+        </is>
+      </c>
+      <c r="H303" s="6" t="inlineStr"/>
       <c r="I303" s="6" t="inlineStr">
         <is>
-          <t>Yes (effectively). Glean does not publish a hard deadline. Postings remain open until filled or the cohort is complete. Applying by October to November gives th</t>
+          <t>Yes, partially. The official page states interns are accepted on a rolling basis for each term, with a hard deadline as the backstop. Apply early.</t>
         </is>
       </c>
       <c r="J303" s="6" t="inlineStr">
         <is>
-          <t>$57 to $69 per hour ($10,000+/month) for SWE interns. Levels.fyi verified $57.69/hr for Summer 2025 with ~5% year-over-year increases. Housing stipend of $1,000</t>
+          <t>$20.00/hour standard; disclosed corporate range $20.00–$30.00/hour. No housing or relocation provided. (Glassdoor/Indeed averages of ~$29–$35/hr blend in gradua</t>
         </is>
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: the Software Engineer, Intern (Summer 2027) listing is live on Greenhouse (updated October 2, 2026). No deadline is published; rolling review, and positions may close by December 2026 as the cohort fills</t>
+          <t>For a summer 2027 role, applications are open now. FOX posted its Summer 2027 program reqs on September 28, 2026, and the postings we checked set a general application deadline of Sunday, January 10, 2027, with two sessions (June 7 to July 30, 2027 or June 21 to August 13, 2027). Spring 2027 reqs are also live, with a November 22, 2026 deadline.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Glean</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -17480,12 +17480,12 @@
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; General Engineering Intern (potential)  (2 of 4 tracks)</t>
+          <t>SWE Intern: Backend &amp; Infrastructure; SWE Intern: ML / NLP / Search; SWE Intern: UI / Full-Stack; SWE Intern: Security  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E304" s="7" t="inlineStr">
         <is>
-          <t>harvey.ai/careers</t>
+          <t>glean.com/careers</t>
         </is>
       </c>
       <c r="F304" s="7" t="inlineStr">
@@ -17495,34 +17495,34 @@
       </c>
       <c r="G304" s="6" t="inlineStr">
         <is>
-          <t>The intern tech screen is a 60-minute live coding session with a Harvey engineer, working through a real-world problem collaboratively. It is practical and applied rather than pure leetcode, and the Summer 2027 posting says the process includes AI-assisted coding sessions where you work with AI tool</t>
+          <t>Glean's SWE intern interview is notably streamlined at just two rounds, shorter than most comparable companies: 1. Apply on glean.com/careers or the Greenhouse board . The Summer 2027 SWE intern posting is live now; submit in October. Tailor your resume to highlight backend, infrastructure, ML, or f</t>
         </is>
       </c>
       <c r="H304" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsored for full-time roles (11 LCAs filed FY2026). Intern CPT/OPT plausible but not explicitly confirmed</t>
+          <t>Glean files H-1B visas for full-time roles (9 LCAs in FY2026, median salary $210,000). CPT/OPT likely supported for interns based on past hiring patterns, though not explicitly confirmed</t>
         </is>
       </c>
       <c r="I304" s="6" t="inlineStr">
         <is>
-          <t>Yes. No fixed deadline. The Summer 2026 SWE intern listing was removed within roughly 3 months of posting. Apply in the first weeks for the best odds</t>
+          <t>Yes (effectively). Glean does not publish a hard deadline. Postings remain open until filled or the cohort is complete. Applying by October to November gives th</t>
         </is>
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
-          <t>$62 to $72/hr in New York and San Francisco (summer 2027 posting); relocation support available. Earlier cycles: $60 to $65/hr plus a $1,666/month housing stipe</t>
+          <t>$57 to $69 per hour ($10,000+/month) for SWE interns. Levels.fyi verified $57.69/hr for Summer 2025 with ~5% year-over-year increases. Housing stipend of $1,000</t>
         </is>
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027: open now. SWE intern roles posted 2 October 2026 (New York, San Francisco); rolling, no stated deadline. The summer 2026 listing came down within about 3 months</t>
+          <t>Open now for summer 2027: the Software Engineer, Intern (Summer 2027) listing is live on Greenhouse (updated October 2, 2026). No deadline is published; rolling review, and positions may close by December 2026 as the cohort fills</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -17537,12 +17537,12 @@
       </c>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>Engineering; IT/Data Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineering Intern; General Engineering Intern (potential)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E305" s="7" t="inlineStr">
         <is>
-          <t>careers.honda.com/us/en/Students</t>
+          <t>harvey.ai/careers</t>
         </is>
       </c>
       <c r="F305" s="7" t="inlineStr">
@@ -17552,34 +17552,34 @@
       </c>
       <c r="G305" s="6" t="inlineStr">
         <is>
-          <t>Honda’s hiring process is straightforward and shorter than many competitors, typically two to three steps: 1. Apply at careers.honda.com or connect via campus career fairs and Handshake. Browse co-op/internship openings and apply to the requisition matching your major and semester of interest. 2. Pr</t>
+          <t>The intern tech screen is a 60-minute live coding session with a Harvey engineer, working through a real-world problem collaboratively. It is practical and applied rather than pure leetcode, and the Summer 2027 posting says the process includes AI-assisted coding sessions where you work with AI tool</t>
         </is>
       </c>
       <c r="H305" s="6" t="inlineStr">
         <is>
-          <t>No. Honda explicitly states: “Applicants requiring sponsorship for employment visa status now or in the future (e.g., F-1 CPT/OPT, H-1B, TN, etc.) will not be considered.” This is stricter than most automotive competitor</t>
+          <t>H-1B sponsored for full-time roles (11 LCAs filed FY2026). Intern CPT/OPT plausible but not explicitly confirmed</t>
         </is>
       </c>
       <c r="I305" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Applications span 4–8 months per term, and Honda recruits continuously at campus events and through Handshake</t>
+          <t>Yes. No fixed deadline. The Summer 2026 SWE intern listing was removed within roughly 3 months of posting. Apply in the first weeks for the best odds</t>
         </is>
       </c>
       <c r="J305" s="6" t="inlineStr">
         <is>
-          <t>$23 to $35/hr official range across tracks; engineering tops out at $35.22/hr, plus 1.5x overtime</t>
+          <t>$62 to $72/hr in New York and San Francisco (summer 2027 posting); relocation support available. Earlier cycles: $60 to $65/hr plus a $1,666/month housing stipe</t>
         </is>
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>Open now: Summer 2027 Co-op/Intern postings for Engineering, IT/Data Analytics, Business, Environmental/Safety/Sustainability, Creative Design and Research, and Equipment Service are live on careers.honda.com (as of September 28, 2026); rolling review through about March or April 2027</t>
+          <t>Summer 2027: open now. SWE intern roles posted 2 October 2026 (New York, San Francisco); rolling, no stated deadline. The summer 2026 listing came down within about 3 months</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
@@ -17589,17 +17589,17 @@
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D306" s="6" t="inlineStr">
         <is>
-          <t>Engineering; Software Engineering; Cybersecurity  (3 of 6 tracks)</t>
+          <t>Engineering; IT/Data Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E306" s="7" t="inlineStr">
         <is>
-          <t>lockheedmartin.eightfold.ai/careers?query=intern&amp;amp;locatio</t>
+          <t>careers.honda.com/us/en/Students</t>
         </is>
       </c>
       <c r="F306" s="7" t="inlineStr">
@@ -17609,30 +17609,34 @@
       </c>
       <c r="G306" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lockheed Martin's interview process averages about 31 days from application to offer, with a Glassdoor difficulty rating of 2.6 out of 5. Here's what to expect: 1. Create a profile on lockheedmartin.eightfold.ai (Lockheed's careers portal). Search for intern positions by business area, location, or </t>
-        </is>
-      </c>
-      <c r="H306" s="6" t="inlineStr"/>
+          <t>Honda’s hiring process is straightforward and shorter than many competitors, typically two to three steps: 1. Apply at careers.honda.com or connect via campus career fairs and Handshake. Browse co-op/internship openings and apply to the requisition matching your major and semester of interest. 2. Pr</t>
+        </is>
+      </c>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>No. Honda explicitly states: “Applicants requiring sponsorship for employment visa status now or in the future (e.g., F-1 CPT/OPT, H-1B, TN, etc.) will not be considered.” This is stricter than most automotive competitor</t>
+        </is>
+      </c>
       <c r="I306" s="6" t="inlineStr">
         <is>
-          <t>Yes. Individual postings close after 90 days or when the applicant pool is sufficient. Apply within 5–30 days of posting for optimal consideration</t>
+          <t>Likely yes. Applications span 4–8 months per term, and Honda recruits continuously at campus events and through Handshake</t>
         </is>
       </c>
       <c r="J306" s="6" t="inlineStr">
         <is>
-          <t>$22–$40/hr depending on role and level. SWE interns up to $40/hr; mechanical at $32.50/hr. Housing stipend $850–$5,500/month</t>
+          <t>$23 to $35/hr official range across tracks; engineering tops out at $35.22/hr, plus 1.5x overtime</t>
         </is>
       </c>
       <c r="K306" s="6" t="inlineStr">
         <is>
-          <t>Open now: summer 2027 college intern requisitions posted September 14 to 23, 2026 (finance, contracts, proposal, embedded software, cybersecurity, radar and electronics engineering); rolling through spring</t>
+          <t>Open now: Summer 2027 Co-op/Intern postings for Engineering, IT/Data Analytics, Business, Environmental/Safety/Sustainability, Creative Design and Research, and Equipment Service are live on careers.honda.com (as of September 28, 2026); rolling review through about March or April 2027</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -17642,17 +17646,17 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Exploratory SWE / Tech Launchpad); Data Analytics / Data Science Intern (Tech Launchpad)  (2 of 5 tracks)</t>
+          <t>Engineering; Software Engineering; Cybersecurity  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E307" s="7" t="inlineStr">
         <is>
-          <t>talent.lowes.com/us/en/internships</t>
+          <t>lockheedmartin.eightfold.ai/careers?query=intern&amp;amp;locatio</t>
         </is>
       </c>
       <c r="F307" s="7" t="inlineStr">
@@ -17662,30 +17666,30 @@
       </c>
       <c r="G307" s="6" t="inlineStr">
         <is>
-          <t>Lowe's does not officially publish its intern interview process, so the steps below combine the official portal and rolling-review facts with community-reported detail (third-party, labeled). Tech and business tracks diverge at the final rounds. 1. Apply through the official portal. Go to talent.low</t>
+          <t xml:space="preserve">Lockheed Martin's interview process averages about 31 days from application to offer, with a Glassdoor difficulty rating of 2.6 out of 5. Here's what to expect: 1. Create a profile on lockheedmartin.eightfold.ai (Lockheed's careers portal). Search for intern positions by business area, location, or </t>
         </is>
       </c>
       <c r="H307" s="6" t="inlineStr"/>
       <c r="I307" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Effectively yes. Official 2026 postings carried the standard Workday caveat that a role “may close before the stated closing date,” and prior-cycle third-party </t>
+          <t>Yes. Individual postings close after 90 days or when the applicant pool is sufficient. Apply within 5–30 days of posting for optimal consideration</t>
         </is>
       </c>
       <c r="J307" s="6" t="inlineStr">
         <is>
-          <t>Paid, with eligibility for a Lowe's Housing Benefit and a 10% associate discount. Exact intern rate is not published on official postings. Community estimates p</t>
+          <t>$22–$40/hr depending on role and level. SWE interns up to $40/hr; mechanical at $32.50/hr. Housing stipend $850–$5,500/month</t>
         </is>
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>Open now for Summer 2027. Lowe's began posting Summer 2027 undergrad internships on September 14, 2026 (Software Engineering, Digital Product Management, Merchandising, Store Operations, Private Brands and more), and the postings we checked list no closing date. Review is rolling, so apply as early as possible</t>
+          <t>Open now: summer 2027 college intern requisitions posted September 14 to 23, 2026 (finance, contracts, proposal, embedded software, cybersecurity, radar and electronics engineering); rolling through spring</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
@@ -17700,12 +17704,12 @@
       </c>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>Refining Chemical Engineering; Midstream Engineering (MPLX)  (2 of 6 tracks)</t>
+          <t>Software Engineering Intern (Exploratory SWE / Tech Launchpad); Data Analytics / Data Science Intern (Tech Launchpad)  (2 of 5 tracks)</t>
         </is>
       </c>
       <c r="E308" s="7" t="inlineStr">
         <is>
-          <t>mpc.wd1.myworkdayjobs.com/MPCCareers?workerSubType=762d3bc56</t>
+          <t>talent.lowes.com/us/en/internships</t>
         </is>
       </c>
       <c r="F308" s="7" t="inlineStr">
@@ -17715,34 +17719,30 @@
       </c>
       <c r="G308" s="6" t="inlineStr">
         <is>
-          <t>After applying online, you may complete aptitude and personality assessments. If shortlisted, expect a phone screen with a recruiter followed by one or two interviews with the hiring manager and team members. Questions are primarily behavioral using the STAR method, with some technical questions for</t>
-        </is>
-      </c>
-      <c r="H308" s="6" t="inlineStr">
-        <is>
-          <t>No. Every MPC intern and co-op posting states that candidates must be authorized to work in the US on a full-time indefinite basis without the need for employment visa sponsorship now or in the future. This means interna</t>
-        </is>
-      </c>
+          <t>Lowe's does not officially publish its intern interview process, so the steps below combine the official portal and rolling-review facts with community-reported detail (third-party, labeled). Tech and business tracks diverge at the final rounds. 1. Apply through the official portal. Go to talent.low</t>
+        </is>
+      </c>
+      <c r="H308" s="6" t="inlineStr"/>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>Not officially, but postings warn they "may close before the stated closing date" and encourage applying "as soon as possible"</t>
+          <t xml:space="preserve">Effectively yes. Official 2026 postings carried the standard Workday caveat that a role “may close before the stated closing date,” and prior-cycle third-party </t>
         </is>
       </c>
       <c r="J308" s="6" t="inlineStr">
         <is>
-          <t>$20 to $42/hr depending on role; engineering interns $32-$42/hr; $4,500 relocation allowance</t>
+          <t>Paid, with eligibility for a Lowe's Housing Benefit and a 10% associate discount. Exact intern rate is not published on official postings. Community estimates p</t>
         </is>
       </c>
       <c r="K308" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027, Spring 2027, and Fall 2026 intern/co-op roles are live on MPC's Workday portal as of August 2026, including Finance, Accounting, and Supply Chain. Rolling review</t>
+          <t>Open now for Summer 2027. Lowe's began posting Summer 2027 undergrad internships on September 14, 2026 (Software Engineering, Digital Product Management, Merchandising, Store Operations, Private Brands and more), and the postings we checked list no closing date. Review is rolling, so apply as early as possible</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>Old Mission</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -17757,12 +17757,12 @@
       </c>
       <c r="D309" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer); Quant Trader Micro-Intern (Winter); Quant Trader Graduate Program; SWE Graduate Program (August)</t>
+          <t>Refining Chemical Engineering; Midstream Engineering (MPLX)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E309" s="7" t="inlineStr">
         <is>
-          <t>oldmissioncapital.com/careers/</t>
+          <t>mpc.wd1.myworkdayjobs.com/MPCCareers?workerSubType=762d3bc56</t>
         </is>
       </c>
       <c r="F309" s="7" t="inlineStr">
@@ -17772,34 +17772,34 @@
       </c>
       <c r="G309" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">You apply through Greenhouse, pass a resume screen, then complete a HackerRank OA (30 MCQs on CS fundamentals plus 2 coding problems, rated one of the hardest in the industry). If you advance, there is a phone/video interview and a final 2-hour in-person onsite at the Chicago office. Total process: </t>
+          <t>After applying online, you may complete aptitude and personality assessments. If shortlisted, expect a phone screen with a recruiter followed by one or two interviews with the hiring manager and team members. Questions are primarily behavioral using the STAR method, with some technical questions for</t>
         </is>
       </c>
       <c r="H309" s="6" t="inlineStr">
         <is>
-          <t>Yes. Ellis.com data shows Old Mission has filed H-1B visa sponsorship with a median salary of $162,500, suggesting openness to international students</t>
+          <t>No. Every MPC intern and co-op posting states that candidates must be authorized to work in the US on a full-time indefinite basis without the need for employment visa sponsorship now or in the future. This means interna</t>
         </is>
       </c>
       <c r="I309" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Reddit reports candidates being rejected before completing their OA, suggesting continuous resume screening. The narrow window and small cohorts rew</t>
+          <t>Not officially, but postings warn they "may close before the stated closing date" and encourage applying "as soon as possible"</t>
         </is>
       </c>
       <c r="J309" s="6" t="inlineStr">
         <is>
-          <t>SWE intern: $150,000 to $200,000 annualized ($2,885 to $3,846/week). Quant Trader micro-intern: $2,500/week (~$130K annualized). Free corporate housing and dail</t>
+          <t>$20 to $42/hr depending on role; engineering interns $32-$42/hr; $4,500 relocation allowance</t>
         </is>
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>Open now. SWE internship (summer 2027): posted July 15, 2026 and still live on October 6, 2026; no closing date published, closes when filled. Quant Trader Micro-Internship (January 2027): posted October 1, 2026</t>
+          <t>OPEN NOW. Summer 2027, Spring 2027, and Fall 2026 intern/co-op roles are live on MPC's Workday portal as of August 2026, including Finance, Accounting, and Supply Chain. Rolling review</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>P&amp;G</t>
+          <t>Old Mission</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -17809,17 +17809,17 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Information Technology  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern (Summer); Quant Trader Micro-Intern (Winter); Quant Trader Graduate Program; SWE Graduate Program (August)</t>
         </is>
       </c>
       <c r="E310" s="7" t="inlineStr">
         <is>
-          <t>pgcareers.com/us/en/internships</t>
+          <t>oldmissioncapital.com/careers/</t>
         </is>
       </c>
       <c r="F310" s="7" t="inlineStr">
@@ -17829,34 +17829,34 @@
       </c>
       <c r="G310" s="6" t="inlineStr">
         <is>
-          <t>P&amp;G's funnel is assessment-heavy and fast. The company estimates 4 to 8 weeks from application to offer, but the real gate is not the interview; it is the two-stage assessment battery that eliminates over 70 percent of applicants before any human reviews their file: 1. Apply at pgcareers.com . Creat</t>
+          <t xml:space="preserve">You apply through Greenhouse, pass a resume screen, then complete a HackerRank OA (30 MCQs on CS fundamentals plus 2 coding problems, rated one of the hardest in the industry). If you advance, there is a phone/video interview and a final 2-hour in-person onsite at the Chicago office. Total process: </t>
         </is>
       </c>
       <c r="H310" s="6" t="inlineStr">
         <is>
-          <t>It varies by role. Some postings (e.g., R&amp;D 2026) explicitly state immigration sponsorship is not available. Others do support it: P&amp;G filed 7 H1B labor condition applications in FY2025. For internships, CPT and OPT auth</t>
+          <t>Yes. Ellis.com data shows Old Mission has filed H-1B visa sponsorship with a median salary of $162,500, suggesting openness to international students</t>
         </is>
       </c>
       <c r="I310" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions fill before posted deadlines. First-come advantage is real</t>
+          <t>Likely yes. Reddit reports candidates being rejected before completing their OA, suggesting continuous resume screening. The narrow window and small cohorts rew</t>
         </is>
       </c>
       <c r="J310" s="6" t="inlineStr">
         <is>
-          <t>$29 to $50 per hour depending on track (R&amp;D and engineering at the top; ~$35/hr IT and data science)</t>
+          <t>SWE intern: $150,000 to $200,000 annualized ($2,885 to $3,846/week). Quant Trader micro-intern: $2,500/week (~$130K annualized). Free corporate housing and dail</t>
         </is>
       </c>
       <c r="K310" s="6" t="inlineStr">
         <is>
-          <t>Open now. Summer 2027 US internship reqs live on P&amp;G's Workday board since August 24, 2026 (Cincinnati wave) with R&amp;D PhD reqs added September 11 to 18; no posting end date listed, rolling review (confirmed Sep 21, 2026)</t>
+          <t>Open now. SWE internship (summer 2027): posted July 15, 2026 and still live on October 6, 2026; no closing date published, closes when filled. Quant Trader Micro-Internship (January 2027): posted October 1, 2026</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>P&amp;G</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -17866,17 +17866,17 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D311" s="6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern / Product Engineering Co-Op (primary); Manufacturing / Manufacturing &amp; Production Engineering Intern; Aerospace / Electromechanical (NVH) Engineering Intern (ITAR)  (3 of 6 tracks)</t>
+          <t>Information Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E311" s="7" t="inlineStr">
         <is>
-          <t>parkercareers.ttcportals.com/search/students/jobs</t>
+          <t>pgcareers.com/us/en/internships</t>
         </is>
       </c>
       <c r="F311" s="7" t="inlineStr">
@@ -17886,34 +17886,34 @@
       </c>
       <c r="G311" s="6" t="inlineStr">
         <is>
-          <t>Mostly behavioral. Expect a recruiter phone call to schedule, then a one-on-one (sometimes panel) interview focused on character, work ethic, and teamwork, plus a role overview and occasionally a facility walkthrough. Difficulty is rated "average" (2.9/5), about 75% of candidates report a positive e</t>
+          <t>P&amp;G's funnel is assessment-heavy and fast. The company estimates 4 to 8 weeks from application to offer, but the real gate is not the interview; it is the two-stage assessment battery that eliminates over 70 percent of applicants before any human reviews their file: 1. Apply at pgcareers.com . Creat</t>
         </is>
       </c>
       <c r="H311" s="6" t="inlineStr">
         <is>
-          <t>Not indicated. Most engineering intern postings limit eligibility to US Citizen or US Permanent Resident, with no international sponsorship stated for those reqs. Aerospace/defense tracks add an ITAR/EAR restriction (see</t>
+          <t>It varies by role. Some postings (e.g., R&amp;D 2026) explicitly state immigration sponsorship is not available. Others do support it: P&amp;G filed 7 H1B labor condition applications in FY2025. For internships, CPT and OPT auth</t>
         </is>
       </c>
       <c r="I311" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling and continuous. Parker held 44 concurrent student reqs on Aug 6, 2026, each with its own deadline. Many carry the note "this job may cl</t>
+          <t>Yes. Positions fill before posted deadlines. First-come advantage is real</t>
         </is>
       </c>
       <c r="J311" s="6" t="inlineStr">
         <is>
-          <t>No single official company-wide rate; pay is set per division. One Parker HR intern posting listed $19 to $31/hr (employer-provided). Community data (Glassdoor,</t>
+          <t>$29 to $50 per hour depending on track (R&amp;D and engineering at the top; ~$35/hr IT and data science)</t>
         </is>
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>Open now, division by division. Summer 2027 reqs have been posting since September 9, 2026 (Chemical Engineering, Applications Engineering, Accounting, Regulatory Compliance, NVH Engineering and more); 56 US student roles were live on October 6, 2026. Each req has its own deadline; priority deadlines around December 2026 to January 2027 (expected). Prior cycle anchor: a Summer/Spring 2026 ME inter</t>
+          <t>Open now. Summer 2027 US internship reqs live on P&amp;G's Workday board since August 24, 2026 (Cincinnati wave) with R&amp;D PhD reqs added September 11 to 18; no posting end date listed, rolling review (confirmed Sep 21, 2026)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -17928,12 +17928,12 @@
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Master's Machine Learning; PhD Machine Learning (ATG); Data Science; UX Quantitative Research; IT Software Engineering</t>
+          <t>Mechanical Engineering Intern / Product Engineering Co-Op (primary); Manufacturing / Manufacturing &amp; Production Engineering Intern; Aerospace / Electromechanical (NVH) Engineering Intern (ITAR)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E312" s="7" t="inlineStr">
         <is>
-          <t>pinterestcareers.com/early-career/university-recruiting/</t>
+          <t>parkercareers.ttcportals.com/search/students/jobs</t>
         </is>
       </c>
       <c r="F312" s="7" t="inlineStr">
@@ -17943,30 +17943,34 @@
       </c>
       <c r="G312" s="6" t="inlineStr">
         <is>
-          <t>It is lean. You apply, take the CodeSignal General Coding Assessment (scored out of 600), do a 30-minute recruiter screen, then one 1-hour technical interview before a hiring committee decides. That is a single live technical round, versus the three or four a new grad faces. It is CodeSignal, not Ha</t>
-        </is>
-      </c>
-      <c r="H312" s="6" t="inlineStr"/>
+          <t>Mostly behavioral. Expect a recruiter phone call to schedule, then a one-on-one (sometimes panel) interview focused on character, work ethic, and teamwork, plus a role overview and occasionally a facility walkthrough. Difficulty is rated "average" (2.9/5), about 75% of candidates report a positive e</t>
+        </is>
+      </c>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>Not indicated. Most engineering intern postings limit eligibility to US Citizen or US Permanent Resident, with no international sponsorship stated for those reqs. Aerospace/defense tracks add an ITAR/EAR restriction (see</t>
+        </is>
+      </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t>Yes. The summer 2027 reqs opened October 1, 2026 and fill rolling through the August-to-April peak season</t>
+          <t>Yes, effectively rolling and continuous. Parker held 44 concurrent student reqs on Aug 6, 2026, each with its own deadline. Many carry the note "this job may cl</t>
         </is>
       </c>
       <c r="J312" s="6" t="inlineStr">
         <is>
-          <t>Official 2027 postings: SWE and UX Engineering $8,250 to $11,000/mo; Master's ML and Data Science $11,000/mo; PhD ML and Data Science $12,100/mo</t>
+          <t>No single official company-wide rate; pay is set per division. One Parker HR intern posting listed $19 to $31/hr (employer-provided). Community data (Glassdoor,</t>
         </is>
       </c>
       <c r="K312" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 US intern reqs went live on pinterestcareers.com on October 1, 2026 (Software Engineer, Master's and PhD Machine Learning, Master's and PhD Data Science, UX Engineering, UX Quantitative Research). No deadline posted; review is rolling</t>
+          <t>Open now, division by division. Summer 2027 reqs have been posting since September 9, 2026 (Chemical Engineering, Applications Engineering, Accounting, Regulatory Compliance, NVH Engineering and more); 56 US student roles were live on October 6, 2026. Each req has its own deadline; priority deadlines around December 2026 to January 2027 (expected). Prior cycle anchor: a Summer/Spring 2026 ME inter</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -17981,12 +17985,12 @@
       </c>
       <c r="D313" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Technical Game Design; Research Scientist (AI)  (3 of 6 tracks)</t>
+          <t>Software Engineering; Master's Machine Learning; PhD Machine Learning (ATG); Data Science; UX Quantitative Research; IT Software Engineering</t>
         </is>
       </c>
       <c r="E313" s="7" t="inlineStr">
         <is>
-          <t>riotgames.com/en/work-with-us/jobs</t>
+          <t>pinterestcareers.com/early-career/university-recruiting/</t>
         </is>
       </c>
       <c r="F313" s="7" t="inlineStr">
@@ -17996,30 +18000,30 @@
       </c>
       <c r="G313" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">For SWE: a HackerRank OA (2 hours, 4 to 5 medium LeetCode problems), then 3 to 4 remote interviews over about 3 weeks testing technical skills, behavioral alignment, and culture fit. Creative tracks get take-home craft tests instead of the OA. Average time from application to decision is roughly 70 </t>
+          <t>It is lean. You apply, take the CodeSignal General Coding Assessment (scored out of 600), do a 30-minute recruiter screen, then one 1-hour technical interview before a hiring committee decides. That is a single live technical round, versus the three or four a new grad faces. It is CodeSignal, not Ha</t>
         </is>
       </c>
       <c r="H313" s="6" t="inlineStr"/>
       <c r="I313" s="6" t="inlineStr">
         <is>
-          <t>Partially. Review is rolling within each deadline window; applying early is recommended</t>
+          <t>Yes. The summer 2027 reqs opened October 1, 2026 and fill rolling through the August-to-April peak season</t>
         </is>
       </c>
       <c r="J313" s="6" t="inlineStr">
         <is>
-          <t>$56.59/hr SWE; $35–$43/hr non-engineering; ~$2K/mo housing stipend</t>
+          <t>Official 2027 postings: SWE and UX Engineering $8,250 to $11,000/mo; Master's ML and Data Science $11,000/mo; PhD ML and Data Science $12,100/mo</t>
         </is>
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>Open now for SWE: the summer 2027 Software Engineering Intern posting went live 1 October 2026 and closes November 6, 2026. Other tracks for summer 2027 not posted as of 6 October 2026; expected later this fall and open through about January 2027 (projected from prior cycle)</t>
+          <t>OPEN NOW. Summer 2027 US intern reqs went live on pinterestcareers.com on October 1, 2026 (Software Engineer, Master's and PhD Machine Learning, Master's and PhD Data Science, UX Engineering, UX Quantitative Research). No deadline posted; review is rolling</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -18029,17 +18033,17 @@
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>June–August 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>UTG Software Engineering; Machine Learning Engineering  (2 of 6 tracks)</t>
+          <t>Software Engineering; Technical Game Design; Research Scientist (AI)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E314" s="7" t="inlineStr">
         <is>
-          <t>careers.servicenow.com/early-careers/</t>
+          <t>riotgames.com/en/work-with-us/jobs</t>
         </is>
       </c>
       <c r="F314" s="7" t="inlineStr">
@@ -18049,34 +18053,30 @@
       </c>
       <c r="G314" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 5 stages: a HackerRank online assessment (60 to 105 minutes with MCQs and 2 to 3 coding problems), a recruiter phone screen (20 to 30 minutes), 2 to 3 technical video interviews covering DSA, OOP, OS, and project discussion, and a hiring manager behavioral round. Total timeline averag</t>
-        </is>
-      </c>
-      <c r="H314" s="6" t="inlineStr">
-        <is>
-          <t>F-1 CPT/OPT actively supported. STEM OPT extension approved for technical roles. H-1B sponsorship available at full-time conversion for high performers</t>
-        </is>
-      </c>
+          <t xml:space="preserve">For SWE: a HackerRank OA (2 hours, 4 to 5 medium LeetCode problems), then 3 to 4 remote interviews over about 3 weeks testing technical skills, behavioral alignment, and culture fit. Creative tracks get take-home craft tests instead of the OA. Average time from application to decision is roughly 70 </t>
+        </is>
+      </c>
+      <c r="H314" s="6" t="inlineStr"/>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed rolling; priority given to the first 2 to 3 weeks after opening. Popular locations fill within 4 to 8 weeks</t>
+          <t>Partially. Review is rolling within each deadline window; applying early is recommended</t>
         </is>
       </c>
       <c r="J314" s="6" t="inlineStr">
         <is>
-          <t>SWE Bay Area $55.14 to $55.58/hr (~$9,558/month). San Diego $47 to $50/hr. Marketing $33.51/hr. Plus ~$5,000 housing stipend and up to $5,000 sign-on bonus</t>
+          <t>$56.59/hr SWE; $35–$43/hr non-engineering; ~$2K/mo housing stipend</t>
         </is>
       </c>
       <c r="K314" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 Finance Intern (Undergrad) open now in Santa Clara and West Palm Beach. Technical roles not yet posted as of October 1, 2026 (prior cycle opened early August); watch the board weekly</t>
+          <t>Open now for SWE: the summer 2027 Software Engineering Intern posting went live 1 October 2026 and closes November 6, 2026. Other tracks for summer 2027 not posted as of 6 October 2026; expected later this fall and open through about January 2027 (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -18086,17 +18086,17 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–August 2027</t>
         </is>
       </c>
       <c r="D315" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
+          <t>UTG Software Engineering; Machine Learning Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E315" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/xai</t>
+          <t>careers.servicenow.com/early-careers/</t>
         </is>
       </c>
       <c r="F315" s="7" t="inlineStr">
@@ -18106,34 +18106,34 @@
       </c>
       <c r="G315" s="6" t="inlineStr">
         <is>
-          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
+          <t>Typically 3 to 5 stages: a HackerRank online assessment (60 to 105 minutes with MCQs and 2 to 3 coding problems), a recruiter phone screen (20 to 30 minutes), 2 to 3 technical video interviews covering DSA, OOP, OS, and project discussion, and a hiring manager behavioral round. Total timeline averag</t>
         </is>
       </c>
       <c r="H315" s="6" t="inlineStr">
         <is>
-          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
+          <t>F-1 CPT/OPT actively supported. STEM OPT extension approved for technical roles. H-1B sponsorship available at full-time conversion for high performers</t>
         </is>
       </c>
       <c r="I315" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
+          <t>Yes, confirmed. Applications reviewed rolling; priority given to the first 2 to 3 weeks after opening. Popular locations fill within 4 to 8 weeks</t>
         </is>
       </c>
       <c r="J315" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per the summer 2027 postings: software engineering $30/hr (freshman/sophomore), $34 (junior/senior), $36 to $40 (completed degrees); business operations $24.50 </t>
+          <t>SWE Bay Area $55.14 to $55.58/hr (~$9,558/month). San Diego $47 to $50/hr. Marketing $33.51/hr. Plus ~$5,000 housing stipend and up to $5,000 sign-on bonus</t>
         </is>
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>Open now: Summer 2027 Software Engineering and Business Operations internships posted 2 October 2026 (Spring 2027 versions posted the same day). Rolling, no deadline published; positions close once filled</t>
+          <t>Summer 2027 Finance Intern (Undergrad) open now in Santa Clara and West Palm Beach. Technical roles not yet posted as of October 1, 2026 (prior cycle opened early August); watch the board weekly</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -18143,17 +18143,17 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>August–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>Risk &amp; Financial Advisory Intern (incl. Cyber)  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>apply.deloitte.com/careers/SearchJobs</t>
+          <t>job-boards.greenhouse.io/xai</t>
         </is>
       </c>
       <c r="F316" s="7" t="inlineStr">
@@ -18161,28 +18161,36 @@
           <t>guide</t>
         </is>
       </c>
-      <c r="G316" s="6" t="inlineStr"/>
-      <c r="H316" s="6" t="inlineStr"/>
+      <c r="G316" s="6" t="inlineStr">
+        <is>
+          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
+        </is>
+      </c>
+      <c r="H316" s="6" t="inlineStr">
+        <is>
+          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
+        </is>
+      </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>Hard deadlines. Each posting states the day recruiting ends (Oct 11, 2026 for most audit roles, Oct 25 for summer 2028 tax), and the first summer 2028 tax requi</t>
+          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
         </is>
       </c>
       <c r="J316" s="6" t="inlineStr">
         <is>
-          <t>The summer 2028 tax requisition published $25–$48/hr, unchanged from the 2027 range. Official 2027 ranges: audit $25.64–$51.44/hr, tax $25–$48/hr, Discovery $28</t>
+          <t xml:space="preserve">Per the summer 2027 postings: software engineering $30/hr (freshman/sophomore), $34 (junior/senior), $36 to $40 (completed degrees); business operations $24.50 </t>
         </is>
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027 and summer 2028. Audit &amp; Assurance postings for both summers close Oct 11, 2026. That covers several summer 2027 tracks plus the first summer 2028 Financial Statement Audit role; the Japanese Services Group summer 2027 role runs to Nov 29. Tax: summer 2028 Accounting is open until Oct 25, 2026; the earlier summer 2028 requisition (code 361830) closed Aug 12. Discovery recr</t>
+          <t>Open now: Summer 2027 Software Engineering and Business Operations internships posted 2 October 2026 (Spring 2027 versions posted the same day). Rolling, no deadline published; positions close once filled</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -18192,17 +18200,17 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>September 2027 – February 2028</t>
+          <t>August–September 2027</t>
         </is>
       </c>
       <c r="D317" s="6" t="inlineStr">
         <is>
-          <t>Quality Engineering Intern; R&amp;D / Vehicle Engineering Intern  (2 of 6 tracks)</t>
+          <t>Risk &amp; Financial Advisory Intern (incl. Cyber)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E317" s="7" t="inlineStr">
         <is>
-          <t>jobs.porsche.com</t>
+          <t>apply.deloitte.com/careers/SearchJobs</t>
         </is>
       </c>
       <c r="F317" s="7" t="inlineStr">
@@ -18210,36 +18218,28 @@
           <t>guide</t>
         </is>
       </c>
-      <c r="G317" s="6" t="inlineStr">
-        <is>
-          <t>Expect one to two interview rounds: a phone or video screen covering your background and motivation, followed by a deeper behavioral interview or case study with the hiring manager. Porsche Consulting roles include two case studies. PCNA candidates report an average of 43 days from application to hi</t>
-        </is>
-      </c>
-      <c r="H317" s="6" t="inlineStr">
-        <is>
-          <t>Check each posting individually. PCNA roles typically require US work authorization. Porsche AG roles in Germany follow German student-visa rules</t>
-        </is>
-      </c>
+      <c r="G317" s="6" t="inlineStr"/>
+      <c r="H317" s="6" t="inlineStr"/>
       <c r="I317" s="6" t="inlineStr">
         <is>
-          <t>Yes. Porsche posts and fills internship roles on a rolling basis. Some roles stay open only weeks, so apply promptly when a posting appears</t>
+          <t>Hard deadlines. Each posting states the day recruiting ends (Oct 11, 2026 for most audit roles, Oct 25 for summer 2028 tax), and the first summer 2028 tax requi</t>
         </is>
       </c>
       <c r="J317" s="6" t="inlineStr">
         <is>
-          <t>$18 to $20 per hour on the PCNA intern postings live in October 2026 ($19 to $21 for a Porsche Design of America retail role in Costa Mesa). Indeed reports an a</t>
+          <t>The summer 2028 tax requisition published $25–$48/hr, unchanged from the 2027 range. Official 2027 ranges: audit $25.64–$51.44/hr, tax $25–$48/hr, Discovery $28</t>
         </is>
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>Open now: PCNA posted at least 10 intern roles between September 15 and 30, 2026, most running March to September 2027 (Accounting, Finance, Compliance, Aftersales Projects and Strategy, Digital Transformation and Data Intelligence), plus a Miami role running February to September 2027. More postings may follow through January 2027. Porsche AG recommends applying about six months before desired st</t>
+          <t>Open now for summer 2027 and summer 2028. Audit &amp; Assurance postings for both summers close Oct 11, 2026. That covers several summer 2027 tracks plus the first summer 2028 Financial Statement Audit role; the Japanese Services Group summer 2027 role runs to Nov 29. Tax: summer 2028 Accounting is open until Oct 25, 2026; the earlier summer 2028 requisition (code 361830) closed Aug 12. Discovery recr</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -18249,17 +18249,17 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>December 2027</t>
+          <t>September 2027 – February 2028</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
+          <t>Quality Engineering Intern; R&amp;D / Vehicle Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E318" s="7" t="inlineStr">
         <is>
-          <t>pepsicojobs.com/internshipsprograms</t>
+          <t>jobs.porsche.com</t>
         </is>
       </c>
       <c r="F318" s="7" t="inlineStr">
@@ -18269,50 +18269,54 @@
       </c>
       <c r="G318" s="6" t="inlineStr">
         <is>
-          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
-        </is>
-      </c>
-      <c r="H318" s="6" t="inlineStr"/>
+          <t>Expect one to two interview rounds: a phone or video screen covering your background and motivation, followed by a deeper behavioral interview or case study with the hiring manager. Porsche Consulting roles include two case studies. PCNA candidates report an average of 43 days from application to hi</t>
+        </is>
+      </c>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>Check each posting individually. PCNA roles typically require US work authorization. Porsche AG roles in Germany follow German student-visa rules</t>
+        </is>
+      </c>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
+          <t>Yes. Porsche posts and fills internship roles on a rolling basis. Some roles stay open only weeks, so apply promptly when a posting appears</t>
         </is>
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
-          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
+          <t>$18 to $20 per hour on the PCNA intern postings live in October 2026 ($19 to $21 for a Porsche Design of America retail role in Costa Mesa). Indeed reports an a</t>
         </is>
       </c>
       <c r="K318" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
+          <t>Open now: PCNA posted at least 10 intern roles between September 15 and 30, 2026, most running March to September 2027 (Accounting, Finance, Compliance, Aftersales Projects and Strategy, Digital Transformation and Data Intelligence), plus a Miami role running February to September 2027. More postings may follow through January 2027. Porsche AG recommends applying about six months before desired st</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="B319" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Window open - check now</t>
         </is>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>December 2027</t>
         </is>
       </c>
       <c r="D319" s="6" t="inlineStr">
         <is>
-          <t>Media Tech Internship  (1 of 6 tracks)</t>
+          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E319" s="7" t="inlineStr">
         <is>
-          <t>jobs.comcast.com/early-career</t>
+          <t>pepsicojobs.com/internshipsprograms</t>
         </is>
       </c>
       <c r="F319" s="7" t="inlineStr">
@@ -18322,34 +18326,30 @@
       </c>
       <c r="G319" s="6" t="inlineStr">
         <is>
-          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
-        </is>
-      </c>
-      <c r="H319" s="6" t="inlineStr">
-        <is>
-          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
-        </is>
-      </c>
+          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
+        </is>
+      </c>
+      <c r="H319" s="6" t="inlineStr"/>
       <c r="I319" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
+          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
         </is>
       </c>
       <c r="J319" s="6" t="inlineStr">
         <is>
-          <t>Comcast SWE: $40/hr; NBCUniversal: $25/hr; sign-on bonus possible but not guaranteed</t>
+          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
         </is>
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
+          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="B320" s="8" t="inlineStr">
@@ -18359,17 +18359,17 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – March 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>AI / ML Development Intern; Engineering &amp; Manufacturing Intern  (2 of 6 tracks)</t>
+          <t>Media Tech Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E320" s="7" t="inlineStr">
         <is>
-          <t>careers.gene.com/us/en/internship-opportunities</t>
+          <t>jobs.comcast.com/early-career</t>
         </is>
       </c>
       <c r="F320" s="7" t="inlineStr">
@@ -18379,34 +18379,34 @@
       </c>
       <c r="G320" s="6" t="inlineStr">
         <is>
-          <t>You apply with a resume, cover letter, and letters of recommendation. Then a phone screen with HR, a call with the hiring manager (sometimes including a short research presentation), a knowledge interview on your field, and a behavioral round using the STAR method. The average time to offer is 37 da</t>
+          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
         </is>
       </c>
       <c r="H320" s="6" t="inlineStr">
         <is>
-          <t>International students may apply. Visa sponsorship availability varies by position and department. You must be legally authorized to work in the US during the internship</t>
+          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
         </is>
       </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>Yes. Genentech posts positions on an ongoing basis from November through March and reviews applications as they arrive. Applying early maximizes your chances</t>
+          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
         </is>
       </c>
       <c r="J320" s="6" t="inlineStr">
         <is>
-          <t>$22 to $50 per hour depending on role, degree level, and year in school. Software engineer interns: $45/hr (Levels.fyi). Data science interns: $50/hr (Levels.fy</t>
+          <t>Comcast SWE: $40/hr; NBCUniversal: $25/hr; sign-on bonus possible but not guaranteed</t>
         </is>
       </c>
       <c r="K320" s="6" t="inlineStr">
         <is>
-          <t>Expected November 2026 through March 2027 for summer 2027 roles. Most hiring decisions made by end of March. Projected from prior cycles</t>
+          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
@@ -18416,17 +18416,17 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November 2026 – March 2027</t>
         </is>
       </c>
       <c r="D321" s="6" t="inlineStr">
         <is>
-          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
+          <t>AI / ML Development Intern; Engineering &amp; Manufacturing Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E321" s="7" t="inlineStr">
         <is>
-          <t>deepmind.google/student-researcher-program/</t>
+          <t>careers.gene.com/us/en/internship-opportunities</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
@@ -18436,30 +18436,34 @@
       </c>
       <c r="G321" s="6" t="inlineStr">
         <is>
-          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
-        </is>
-      </c>
-      <c r="H321" s="6" t="inlineStr"/>
+          <t>You apply with a resume, cover letter, and letters of recommendation. Then a phone screen with HR, a call with the hiring manager (sometimes including a short research presentation), a knowledge interview on your field, and a behavioral round using the STAR method. The average time to offer is 37 da</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr">
+        <is>
+          <t>International students may apply. Visa sponsorship availability varies by position and department. You must be legally authorized to work in the US during the internship</t>
+        </is>
+      </c>
       <c r="I321" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
+          <t>Yes. Genentech posts positions on an ongoing basis from November through March and reviews applications as they arrive. Applying early maximizes your chances</t>
         </is>
       </c>
       <c r="J321" s="6" t="inlineStr">
         <is>
-          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
+          <t>$22 to $50 per hour depending on role, degree level, and year in school. Software engineer interns: $45/hr (Levels.fyi). Data science interns: $50/hr (Levels.fy</t>
         </is>
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
+          <t>Expected November 2026 through March 2027 for summer 2027 roles. Most hiring decisions made by end of March. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
@@ -18469,17 +18473,17 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
-          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
+          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E322" s="7" t="inlineStr">
         <is>
-          <t>apply.workable.com/huggingface</t>
+          <t>deepmind.google/student-researcher-program/</t>
         </is>
       </c>
       <c r="F322" s="7" t="inlineStr">
@@ -18489,34 +18493,30 @@
       </c>
       <c r="G322" s="6" t="inlineStr">
         <is>
-          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
-        </is>
-      </c>
-      <c r="H322" s="6" t="inlineStr">
-        <is>
-          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
-        </is>
-      </c>
+          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr"/>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
+          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
         </is>
       </c>
       <c r="J322" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
+          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
         </is>
       </c>
       <c r="K322" s="6" t="inlineStr">
         <is>
-          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
+          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -18526,17 +18526,17 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – September 2027</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E323" s="7" t="inlineStr">
         <is>
-          <t>jefferies.tal.net</t>
+          <t>apply.workable.com/huggingface</t>
         </is>
       </c>
       <c r="F323" s="7" t="inlineStr">
@@ -18546,34 +18546,34 @@
       </c>
       <c r="G323" s="6" t="inlineStr">
         <is>
-          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
+          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
         </is>
       </c>
       <c r="H323" s="6" t="inlineStr">
         <is>
-          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
+          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
         </is>
       </c>
       <c r="I323" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
+          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
         </is>
       </c>
       <c r="J323" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
+          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
         </is>
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted. Still live as of October 2, 2026: 2027 Jefferies Finance Summer Analyst roles (Data Analytics; Financial Planning &amp; Accounting), the</t>
+          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Magna</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
@@ -18583,17 +18583,17 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – September 2027</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern (primary); Manufacturing / Process Engineering Intern; Software / Solution Engineering Intern; Engineering Co-Op  (4 of 6 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E324" s="7" t="inlineStr">
         <is>
-          <t>magna.com/careers/students</t>
+          <t>jefferies.tal.net</t>
         </is>
       </c>
       <c r="F324" s="7" t="inlineStr">
@@ -18603,30 +18603,34 @@
       </c>
       <c r="G324" s="6" t="inlineStr">
         <is>
-          <t>Rolling and division-run: a recruiter or HR screen, then a hiring-manager interview (often on-site at the plant), plus a role-specific technical round for engineering, data, and software candidates. Community reports describe it as conversational and project- and fundamentals-focused, not heavy on L</t>
-        </is>
-      </c>
-      <c r="H324" s="6" t="inlineStr"/>
+          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
+        </is>
+      </c>
+      <c r="H324" s="6" t="inlineStr">
+        <is>
+          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
+        </is>
+      </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>Yes. Intern and co-op reqs are posted and filled per-division on a rolling basis; there is no single company-wide deadline. Reqs close when filled, so apply ear</t>
+          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
         </is>
       </c>
       <c r="J324" s="6" t="inlineStr">
         <is>
-          <t>An official Magna Powertrain engineering co-op JD lists $25/hour. Community aggregators put general intern pay around $18 to $34/hr (Indeed ~$20.54/hr; Glassdoo</t>
+          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
         </is>
       </c>
       <c r="K324" s="6" t="inlineStr">
         <is>
-          <t>Partly open. About 23 US intern and co-op reqs are live on Workday as of October 6, 2026 (Muncie IN Finance and Purchasing; Auburn Hills and Southfield engineering and IT; Troy humanoid robotics; Northwood OH and Grand Rapids co-ops; Holland, Holly and Bowling Green quality and IT; Highland Park program management and EHS), posted August to early October. Some earlier reqs have already closed, inc</t>
+          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted. Still live as of October 2, 2026: 2027 Jefferies Finance Summer Analyst roles (Data Analytics; Financial Planning &amp; Accounting), the</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Magna</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -18636,17 +18640,17 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D325" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern  (1 of 5 tracks)</t>
+          <t>Mechanical Engineering Intern (primary); Manufacturing / Process Engineering Intern; Software / Solution Engineering Intern; Engineering Co-Op  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E325" s="7" t="inlineStr">
         <is>
-          <t>marqeta.com/company/careers</t>
+          <t>magna.com/careers/students</t>
         </is>
       </c>
       <c r="F325" s="7" t="inlineStr">
@@ -18656,34 +18660,30 @@
       </c>
       <c r="G325" s="6" t="inlineStr">
         <is>
-          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
-        </is>
-      </c>
-      <c r="H325" s="6" t="inlineStr">
-        <is>
-          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
-        </is>
-      </c>
+          <t>Rolling and division-run: a recruiter or HR screen, then a hiring-manager interview (often on-site at the plant), plus a role-specific technical round for engineering, data, and software candidates. Community reports describe it as conversational and project- and fundamentals-focused, not heavy on L</t>
+        </is>
+      </c>
+      <c r="H325" s="6" t="inlineStr"/>
       <c r="I325" s="6" t="inlineStr">
         <is>
-          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
+          <t>Yes. Intern and co-op reqs are posted and filled per-division on a rolling basis; there is no single company-wide deadline. Reqs close when filled, so apply ear</t>
         </is>
       </c>
       <c r="J325" s="6" t="inlineStr">
         <is>
-          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
+          <t>An official Magna Powertrain engineering co-op JD lists $25/hour. Community aggregators put general intern pay around $18 to $34/hr (Indeed ~$20.54/hr; Glassdoo</t>
         </is>
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
+          <t>Partly open. About 23 US intern and co-op reqs are live on Workday as of October 6, 2026 (Muncie IN Finance and Purchasing; Auburn Hills and Southfield engineering and IT; Troy humanoid robotics; Northwood OH and Grand Rapids co-ops; Holland, Holly and Bowling Green quality and IT; Highland Park program management and EHS), posted August to early October. Some earlier reqs have already closed, inc</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
@@ -18693,17 +18693,17 @@
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – January 2027</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>Business — Analytics  (1 of 7 tracks)</t>
+          <t>Software Engineering Intern  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E326" s="7" t="inlineStr">
         <is>
-          <t>ogilvyearlycareers.com/the-summer-internship</t>
+          <t>marqeta.com/company/careers</t>
         </is>
       </c>
       <c r="F326" s="7" t="inlineStr">
@@ -18713,30 +18713,34 @@
       </c>
       <c r="G326" s="6" t="inlineStr">
         <is>
-          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
-        </is>
-      </c>
-      <c r="H326" s="6" t="inlineStr"/>
+          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
+        </is>
+      </c>
+      <c r="H326" s="6" t="inlineStr">
+        <is>
+          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
+        </is>
+      </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
+          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
         </is>
       </c>
       <c r="J326" s="6" t="inlineStr">
         <is>
-          <t>$20 to $25/hr posted range (2026 cycle)</t>
+          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
         </is>
       </c>
       <c r="K326" s="6" t="inlineStr">
         <is>
-          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
+          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -18746,17 +18750,17 @@
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – January 2027</t>
         </is>
       </c>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
+          <t>Business — Analytics  (1 of 7 tracks)</t>
         </is>
       </c>
       <c r="E327" s="7" t="inlineStr">
         <is>
-          <t>ouraring.com/careers</t>
+          <t>ogilvyearlycareers.com/the-summer-internship</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
@@ -18766,34 +18770,30 @@
       </c>
       <c r="G327" s="6" t="inlineStr">
         <is>
-          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
-        </is>
-      </c>
-      <c r="H327" s="6" t="inlineStr">
-        <is>
-          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
-        </is>
-      </c>
+          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
+        </is>
+      </c>
+      <c r="H327" s="6" t="inlineStr"/>
       <c r="I327" s="6" t="inlineStr">
         <is>
-          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
+          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
         </is>
       </c>
       <c r="J327" s="6" t="inlineStr">
         <is>
-          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
+          <t>$20 to $25/hr posted range (2026 cycle)</t>
         </is>
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
+          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -18803,17 +18803,17 @@
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – March 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>Genentech Summer Internship; Genentech Research Intern (PhD); Genentech Co-Op  (3 of 7 tracks)</t>
+          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E328" s="7" t="inlineStr">
         <is>
-          <t>careers.roche.com/global/en/roche-internship-program</t>
+          <t>ouraring.com/careers</t>
         </is>
       </c>
       <c r="F328" s="7" t="inlineStr">
@@ -18823,30 +18823,34 @@
       </c>
       <c r="G328" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">After applying, most candidates go through a phone or video screen (20 to 30 minutes) followed by one to three interviews mixing technical and behavioral questions. Some programs add an assessment center, group exercise, or presentation. The entire process averages about 42 days from application to </t>
-        </is>
-      </c>
-      <c r="H328" s="6" t="inlineStr"/>
+          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
+        </is>
+      </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>Implied yes. Postings may close before stated deadlines and Genentech posts positions "on an ongoing basis"</t>
+          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr">
         <is>
-          <t>Roche median $37/hr ($28–$49); Genentech median $35/hr ($28–$45); PhD AI/ML $40–$50/hr per official postings</t>
+          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
         </is>
       </c>
       <c r="K328" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 main wave expected Nov 2026–Mar 2027 (documented pattern; not yet posted). No Roche internship postings live in the US as of Oct 1, 2026; Genentech posts separately on careers.gene.com</t>
+          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -18856,17 +18860,17 @@
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November 2026 – March 2027</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>Process / Chemical Engineering Intern; Mechanical / Project Engineering Intern; Petroleum / Well Engineering Intern; Information Digital Technology (IDT) Intern  (4 of 6 tracks)</t>
+          <t>Genentech Summer Internship; Genentech Research Intern (PhD); Genentech Co-Op  (3 of 7 tracks)</t>
         </is>
       </c>
       <c r="E329" s="7" t="inlineStr">
         <is>
-          <t>shell.com/careers/about-careers-at-shell/assessed-internship</t>
+          <t>careers.roche.com/global/en/roche-internship-program</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
@@ -18876,34 +18880,30 @@
       </c>
       <c r="G329" s="6" t="inlineStr">
         <is>
-          <t>You apply online (5 to 10 minutes), complete four HireVue game-based assessments (20 minutes), then a Virtual Job Tryout plus On-Demand Video Interview (40 minutes), and finally a live case-study presentation with two Shell professionals. Average time from application to hire is about 120 days.</t>
-        </is>
-      </c>
-      <c r="H329" s="6" t="inlineStr">
-        <is>
-          <t>Limited. US positions require US citizenship, permanent residency, or valid work authorization. Candidates on temporary visas (H-1, F-1, J-1) are generally not eligible. Limited PhD sponsorship in certain disciplines</t>
-        </is>
-      </c>
+          <t xml:space="preserve">After applying, most candidates go through a phone or video screen (20 to 30 minutes) followed by one to three interviews mixing technical and behavioral questions. Some programs add an assessment center, group exercise, or presentation. The entire process averages about 42 days from application to </t>
+        </is>
+      </c>
+      <c r="H329" s="6" t="inlineStr"/>
       <c r="I329" s="6" t="inlineStr">
         <is>
-          <t>Yes. Shell states that positions may close before the stated deadline and encourages applicants to apply as soon as possible</t>
+          <t>Implied yes. Postings may close before stated deadlines and Genentech posts positions "on an ongoing basis"</t>
         </is>
       </c>
       <c r="J329" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$25 to $45 per hour for general interns, $35 to $61 per hour for engineering interns (Glassdoor, 6,335 salary submissions). Business Analyst Intern: $22.50 per </t>
+          <t>Roche median $37/hr ($28–$49); Genentech median $35/hr ($28–$45); PhD AI/ML $40–$50/hr per official postings</t>
         </is>
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 to early 2027 for US summer 2027 roles. The 2026 US program posted in January 2026; the 2027 cycle is already appearing globally as of July 2026. Projected from prior cycles</t>
+          <t>Summer 2027 main wave expected Nov 2026–Mar 2027 (documented pattern; not yet posted). No Roche internship postings live in the US as of Oct 1, 2026; Genentech posts separately on careers.gene.com</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Analysis Group</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -18913,17 +18913,17 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>Data Science Intern (when available)  (1 of 4 tracks)</t>
+          <t>Process / Chemical Engineering Intern; Mechanical / Project Engineering Intern; Petroleum / Well Engineering Intern; Information Digital Technology (IDT) Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E330" s="7" t="inlineStr">
         <is>
-          <t>analysisgroup.com/careers/career-path/summer-analyst-intern/</t>
+          <t>shell.com/careers/about-careers-at-shell/assessed-internship</t>
         </is>
       </c>
       <c r="F330" s="7" t="inlineStr">
@@ -18933,34 +18933,34 @@
       </c>
       <c r="G330" s="6" t="inlineStr">
         <is>
-          <t>Analysis Group's funnel is interview-focused with no standardized online assessment , and the average time from application to hire is about 23 days : 1. Apply on the Analysis Group careers portal . Upload your resume, cover letter (include geographic preferences for offices), and unofficial transcr</t>
+          <t>You apply online (5 to 10 minutes), complete four HireVue game-based assessments (20 minutes), then a Virtual Job Tryout plus On-Demand Video Interview (40 minutes), and finally a live case-study presentation with two Shell professionals. Average time from application to hire is about 120 days.</t>
         </is>
       </c>
       <c r="H330" s="6" t="inlineStr">
         <is>
-          <t>Yes, for consultant and data science positions. Not available for administrative roles</t>
+          <t>Limited. US positions require US citizenship, permanent residency, or valid work authorization. Candidates on temporary visas (H-1, F-1, J-1) are generally not eligible. Limited PhD sponsorship in certain disciplines</t>
         </is>
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>Applications are reviewed by the posted deadline. If no deadline is listed, review is rolling. Apply now for the strongest position: late Generalist and Account</t>
+          <t>Yes. Shell states that positions may close before the stated deadline and encourages applicants to apply as soon as possible</t>
         </is>
       </c>
       <c r="J330" s="6" t="inlineStr">
         <is>
-          <t>Summer Analyst ~$1,750 to $2,100/week (~$35/hr annualized on Glassdoor), plus ~$1,500 sign-on bonus. Summer Associate ~$2,400 to $2,800/week</t>
+          <t xml:space="preserve">$25 to $45 per hour for general interns, $35 to $61 per hour for engineering interns (Glassdoor, 6,335 salary submissions). Business Analyst Intern: $22.50 per </t>
         </is>
       </c>
       <c r="K330" s="6" t="inlineStr">
         <is>
-          <t>Still open for Summer Analyst (2027 start): the Generalist and Accounting deadline of September 30, 2026 has passed, but both postings were live on October 2, 2026 and the firm keeps reviewing on a rolling basis, considering late applicants pending availability. Health Care (HEOR, Epidemiology &amp; Market Access) deadline: October 28, 2026. Summer Associate: expected December 2026 to March 2027</t>
+          <t>Expected late 2026 to early 2027 for US summer 2027 roles. The 2026 US program posted in January 2026; the 2027 cycle is already appearing globally as of July 2026. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Analysis Group</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -18970,17 +18970,17 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
+          <t>Data Science Intern (when available)  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E331" s="7" t="inlineStr">
         <is>
-          <t>search.jobs.barclays/internships</t>
+          <t>analysisgroup.com/careers/career-path/summer-analyst-intern/</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -18990,34 +18990,34 @@
       </c>
       <c r="G331" s="6" t="inlineStr">
         <is>
-          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
+          <t>Analysis Group's funnel is interview-focused with no standardized online assessment , and the average time from application to hire is about 23 days : 1. Apply on the Analysis Group careers portal . Upload your resume, cover letter (include geographic preferences for offices), and unofficial transcr</t>
         </is>
       </c>
       <c r="H331" s="6" t="inlineStr">
         <is>
-          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
+          <t>Yes, for consultant and data science positions. Not available for administrative roles</t>
         </is>
       </c>
       <c r="I331" s="6" t="inlineStr">
         <is>
-          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
+          <t>Applications are reviewed by the posted deadline. If no deadline is listed, review is rolling. Apply now for the strongest position: late Generalist and Account</t>
         </is>
       </c>
       <c r="J331" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
+          <t>Summer Analyst ~$1,750 to $2,100/week (~$35/hr annualized on Glassdoor), plus ~$1,500 sign-on bonus. Summer Associate ~$2,400 to $2,800/week</t>
         </is>
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>Summer 2028 Summer Analyst (IB, Markets): not open yet, expected around December 2026 to February 2027, rolling. Summer 2027, still open on 6 October 2026: Technology Developer, Operations and Compliance Analyst (Whippany, NJ), US Consumer Bank Analyst (Wilmington, DE), Banking Associate for MBA students (New York, Chicago, San Francisco, Houston) and Quantitative Finance Associate (New York). The</t>
+          <t>Still open for Summer Analyst (2027 start): the Generalist and Accounting deadline of September 30, 2026 has passed, but both postings were live on October 2, 2026 and the firm keeps reviewing on a rolling basis, considering late applicants pending availability. Health Care (HEOR, Epidemiology &amp; Market Access) deadline: October 28, 2026. Summer Associate: expected December 2026 to March 2027</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -19027,17 +19027,17 @@
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – January 2027</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
+          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E332" s="7" t="inlineStr">
         <is>
-          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
+          <t>search.jobs.barclays/internships</t>
         </is>
       </c>
       <c r="F332" s="7" t="inlineStr">
@@ -19047,30 +19047,34 @@
       </c>
       <c r="G332" s="6" t="inlineStr">
         <is>
-          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
-        </is>
-      </c>
-      <c r="H332" s="6" t="inlineStr"/>
+          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
+        </is>
+      </c>
+      <c r="H332" s="6" t="inlineStr">
+        <is>
+          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
+        </is>
+      </c>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
+          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
         </is>
       </c>
       <c r="J332" s="6" t="inlineStr">
         <is>
-          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
+          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
         </is>
       </c>
       <c r="K332" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to January 2027 for summer 2028; Corporate Functions deadlines extend through mid-2027 (documented pattern; not yet posted)</t>
+          <t>Summer 2028 Summer Analyst (IB, Markets): not open yet, expected around December 2026 to February 2027, rolling. Summer 2027, still open on 6 October 2026: Technology Developer, Operations and Compliance Analyst (Whippany, NJ), US Consumer Bank Analyst (Wilmington, DE), Banking Associate for MBA students (New York, Chicago, San Francisco, Houston) and Quantitative Finance Associate (New York). The</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -19085,12 +19089,12 @@
       </c>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
+          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E333" s="7" t="inlineStr">
         <is>
-          <t>jobs.citi.com/</t>
+          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
@@ -19100,34 +19104,30 @@
       </c>
       <c r="G333" s="6" t="inlineStr">
         <is>
-          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
-        </is>
-      </c>
-      <c r="H333" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
-        </is>
-      </c>
+          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
+        </is>
+      </c>
+      <c r="H333" s="6" t="inlineStr"/>
       <c r="I333" s="6" t="inlineStr">
         <is>
-          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
+          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
         </is>
       </c>
       <c r="J333" s="6" t="inlineStr">
         <is>
-          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
+          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
         </is>
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 18 US Summer Analyst requisitions live now on Citi's Workday board, confirmed September 21, 2026: Corporate Banking (Atlanta, Houston, San Francisco), Commercial Banking (Houston), Markets Sales and Trading and Quantitative Analysis (New York), Services (New York), Wealth (New York, Miami, Dallas, Los Angeles) and Risk, Internal Audit an</t>
+          <t>Expected December 2026 to January 2027 for summer 2028; Corporate Functions deadlines extend through mid-2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -19137,17 +19137,17 @@
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>December 2026 – January 2027</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
+          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t>careers.db.com/students-graduates/internship-programme/</t>
+          <t>jobs.citi.com/</t>
         </is>
       </c>
       <c r="F334" s="7" t="inlineStr">
@@ -19157,34 +19157,34 @@
       </c>
       <c r="G334" s="6" t="inlineStr">
         <is>
-          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
+          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
         </is>
       </c>
       <c r="H334" s="6" t="inlineStr">
         <is>
-          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
+          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
         </is>
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
+          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
         </is>
       </c>
       <c r="J334" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
+          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
         </is>
       </c>
       <c r="K334" s="6" t="inlineStr">
         <is>
-          <t>Partly open. Technology, Data and Innovation internship roles for 2027 are live as of August 2026. IB (summer 2028) still expected ~Dec 2026 through spring 2027 (UK/EMEA as early as Dec 2026). Rolling review</t>
+          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 18 US Summer Analyst requisitions live now on Citi's Workday board, confirmed September 21, 2026: Corporate Banking (Atlanta, Houston, San Francisco), Commercial Banking (Houston), Markets Sales and Trading and Quantitative Analysis (New York), Services (New York), Wealth (New York, Miami, Dallas, Los Angeles) and Risk, Internal Audit an</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -19194,17 +19194,17 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>December 2026</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D335" s="6" t="inlineStr">
         <is>
-          <t>Technology Intern  (1 of 6 tracks)</t>
+          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t>apply.starbucks.com/careers?query=intern</t>
+          <t>careers.db.com/students-graduates/internship-programme/</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
@@ -19214,34 +19214,34 @@
       </c>
       <c r="G335" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a recruiter phone screen (15 to 20 minutes), then 2 to 3 behavioral interview rounds (45 to 60 minutes each) using the STAR method. Technology roles add a coding assessment. The total process spans 6 to 10 weeks. Glassdoor rates difficulty at 2.2 out of 5.</t>
+          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
         </is>
       </c>
       <c r="H335" s="6" t="inlineStr">
         <is>
-          <t>Limited. CPT may be supported for F-1 students on a case-by-case basis, but most postings state sponsorship is not provided. Check the work-authorization line on each specific role</t>
+          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
         </is>
       </c>
       <c r="I335" s="6" t="inlineStr">
         <is>
-          <t>Partially. Starbucks reviews applications on a priority basis through October, then continues on a rolling basis until positions are filled. Technology and supp</t>
+          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
         </is>
       </c>
       <c r="J335" s="6" t="inlineStr">
         <is>
-          <t>$25 to $45 per hour depending on role and level. Technology roles $28 to $45 per hour (Levels.fyi reports $28/hr for SWE interns, Summer 2023). Corporate housin</t>
+          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
         </is>
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>Expected late August 2026 for summer 2027 roles. Priority review through October 2026, with some postings remaining open through December 2026. Projected from prior cycle</t>
+          <t>Partly open. Technology, Data and Innovation internship roles for 2027 are live as of August 2026. IB (summer 2028) still expected ~Dec 2026 through spring 2027 (UK/EMEA as early as Dec 2026). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="B336" s="8" t="inlineStr">
@@ -19256,12 +19256,12 @@
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
-          <t>ML / Data (SF)  (1 of 6 tracks)</t>
+          <t>Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E336" s="7" t="inlineStr">
         <is>
-          <t>strava.com/careers</t>
+          <t>apply.starbucks.com/careers?query=intern</t>
         </is>
       </c>
       <c r="F336" s="7" t="inlineStr">
@@ -19271,30 +19271,34 @@
       </c>
       <c r="G336" s="6" t="inlineStr">
         <is>
-          <t>Strava does not publish a single official interview process, and it varies by track. The steps below combine the application flow from the jobs board with community-reported (paraphrased) round structure, so treat the interview specifics as directional: 1. Find and filter the reqs. Go to the Ashby b</t>
-        </is>
-      </c>
-      <c r="H336" s="6" t="inlineStr"/>
+          <t>You apply, complete a recruiter phone screen (15 to 20 minutes), then 2 to 3 behavioral interview rounds (45 to 60 minutes each) using the STAR method. Technology roles add a coding assessment. The total process spans 6 to 10 weeks. Glassdoor rates difficulty at 2.2 out of 5.</t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>Limited. CPT may be supported for F-1 students on a case-by-case basis, but most postings state sponsorship is not provided. Check the work-authorization line on each specific role</t>
+        </is>
+      </c>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Strava posts discipline-specific intern reqs (Web, Server, iOS, Android, ML) on separate timelines, each with its own "Deadline to Apply," and fills </t>
+          <t>Partially. Starbucks reviews applications on a priority basis through October, then continues on a rolling basis until positions are filled. Technology and supp</t>
         </is>
       </c>
       <c r="J336" s="6" t="inlineStr">
         <is>
-          <t>$40.00/hour (stated directly on Strava intern JDs), plus a housing stipend to live in SF for the three-month summer (~$2,500/month per Levels.fyi). That works o</t>
+          <t>$25 to $45 per hour depending on role and level. Technology roles $28 to $45 per hour (Levels.fyi reports $28/hr for SWE interns, Summer 2023). Corporate housin</t>
         </is>
       </c>
       <c r="K336" s="6" t="inlineStr">
         <is>
-          <t>Not yet published (expected). Applications for summer 2027 are expected to open in fall/winter 2026 with deadlines in late winter to spring 2027. Documented prior cycles: Summer 2025 (Web, SF) closed April 14, 2025; Summer 2026 (Server/Data Platform, SF) closed March 7, 2026</t>
+          <t>Expected late August 2026 for summer 2027 roles. Priority review through October 2026, with some postings remaining open through December 2026. Projected from prior cycle</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -19304,17 +19308,17 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – January 2027</t>
+          <t>December 2026</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
         <is>
-          <t>See guide</t>
+          <t>ML / Data (SF)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E337" s="7" t="inlineStr">
         <is>
-          <t>ubs.com/global/en/careers/early-careers.html</t>
+          <t>strava.com/careers</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
@@ -19324,27 +19328,23 @@
       </c>
       <c r="G337" s="6" t="inlineStr">
         <is>
-          <t>Four to five back-to-back interviews, each roughly 30 minutes, with Associates, VPs, and Directors. The format mixes behavioral questions (resume walkthrough, teamwork, setback stories) with technical questions for front-office roles (DCF, three-statement linking, EV vs. equity value, LBO basics). S</t>
-        </is>
-      </c>
-      <c r="H337" s="6" t="inlineStr">
-        <is>
-          <t>Many US internship positions explicitly state they do not offer employment-based immigration sponsorship, including OPT and CPT. This is confirmed across Global Banking, Global Wealth Management, and Asset Management pos</t>
-        </is>
-      </c>
+          <t>Strava does not publish a single official interview process, and it varies by track. The steps below combine the application flow from the jobs board with community-reported (paraphrased) round structure, so treat the interview specifics as directional: 1. Find and filter the reqs. Go to the Ashby b</t>
+        </is>
+      </c>
+      <c r="H337" s="6" t="inlineStr"/>
       <c r="I337" s="6" t="inlineStr">
         <is>
-          <t>Yes. UBS reviews on a rolling basis; US Summer 2027 filled by May 2026, so early-window seats go fast. Verify current status on the official careers portal</t>
+          <t xml:space="preserve">Partially. Strava posts discipline-specific intern reqs (Web, Server, iOS, Android, ML) on separate timelines, each with its own "Deadline to Apply," and fills </t>
         </is>
       </c>
       <c r="J337" s="6" t="inlineStr">
         <is>
-          <t>$43–$55/hr depending on division (Global Banking $52.88; Global Wealth Management $43.27)</t>
+          <t>$40.00/hour (stated directly on Strava intern JDs), plus a housing stipend to live in SF for the three-month summer (~$2,500/month per Levels.fyi). That works o</t>
         </is>
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to January 2027 (US), rolling until filled; September openings are typically UK/EMEA, not US</t>
+          <t>Not yet published (expected). Applications for summer 2027 are expected to open in fall/winter 2026 with deadlines in late winter to spring 2027. Documented prior cycles: Summer 2025 (Web, SF) closed April 14, 2025; Summer 2026 (Server/Data Platform, SF) closed March 7, 2026</t>
         </is>
       </c>
     </row>
@@ -25643,7 +25643,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -25665,7 +25665,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Asana</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -25687,7 +25687,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -25709,7 +25709,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -25731,7 +25731,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -25753,7 +25753,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -25775,7 +25775,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -25797,7 +25797,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Brex</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -25819,7 +25819,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>Collins Aerospace</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -25841,7 +25841,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Collins Aerospace</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -25863,7 +25863,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>CRA</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -25885,7 +25885,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>CRA</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -25907,7 +25907,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -25929,7 +25929,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -25951,7 +25951,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
@@ -25973,7 +25973,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -25995,7 +25995,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Etsy</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
@@ -26017,7 +26017,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Etsy</t>
+          <t>Expedia</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -26039,7 +26039,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -26061,7 +26061,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -26083,7 +26083,7 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -26105,7 +26105,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -26127,7 +26127,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>HashiCorp</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -26149,7 +26149,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>HashiCorp</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -26171,7 +26171,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Hilton</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -26193,7 +26193,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -26215,7 +26215,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Honeywell Aerospace</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -26237,7 +26237,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -26259,7 +26259,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -26281,7 +26281,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -26303,7 +26303,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>John Deere</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -26325,7 +26325,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>John Deere</t>
+          <t>Jump Trading</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -26347,7 +26347,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
@@ -26369,7 +26369,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -26391,7 +26391,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Live Nation</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -26413,7 +26413,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -26435,7 +26435,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Navan</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
@@ -26457,7 +26457,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Navan</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -26479,7 +26479,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Nissan</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -26501,7 +26501,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Nissan</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -26523,7 +26523,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
@@ -26545,7 +26545,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>PIMCO</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -26567,7 +26567,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>PIMCO</t>
+          <t>Pratt &amp; Whitney</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
@@ -26589,7 +26589,7 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Pratt &amp; Whitney</t>
+          <t>Raytheon</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
@@ -26611,7 +26611,7 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Raytheon</t>
+          <t>Replit</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -26633,7 +26633,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Replit</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -26655,7 +26655,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Royal Caribbean</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -26677,7 +26677,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Royal Caribbean</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
@@ -26699,7 +26699,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
@@ -26721,7 +26721,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -26743,7 +26743,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -26765,7 +26765,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -26787,7 +26787,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>Snap</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -26809,7 +26809,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Snap</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -26831,7 +26831,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -26853,7 +26853,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -26875,7 +26875,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
@@ -26897,7 +26897,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
@@ -26919,7 +26919,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
@@ -26941,7 +26941,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
@@ -26963,7 +26963,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -26985,7 +26985,7 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Wise</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -27007,7 +27007,7 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Wise</t>
+          <t>Wolverine Trading</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -27029,7 +27029,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Wolverine Trading</t>
+          <t>1Password</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -27051,7 +27051,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>1Password</t>
+          <t>Abnormal Security</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -27073,7 +27073,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Abnormal Security</t>
+          <t>Abridge</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -27095,7 +27095,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Abridge</t>
+          <t>Activision Blizzard</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -27117,7 +27117,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Activision Blizzard</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
@@ -27139,7 +27139,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -27161,7 +27161,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
@@ -27183,7 +27183,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>AMC Networks</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
@@ -27205,7 +27205,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>AMC Networks</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -31275,7 +31275,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -31297,7 +31297,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -31319,7 +31319,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -31341,7 +31341,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -31385,7 +31385,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -31407,7 +31407,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -31429,7 +31429,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -31451,7 +31451,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -31473,7 +31473,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -31495,7 +31495,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -31517,7 +31517,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -31539,7 +31539,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -31561,7 +31561,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -31583,7 +31583,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -31605,7 +31605,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -31627,7 +31627,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -31649,7 +31649,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
@@ -31671,7 +31671,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -31693,7 +31693,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -31715,7 +31715,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>Glean</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -31737,7 +31737,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Glean</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -31759,7 +31759,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -31781,7 +31781,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
@@ -31803,7 +31803,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -31825,7 +31825,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
@@ -31847,7 +31847,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>Old Mission</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -31869,7 +31869,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>P&amp;G</t>
+          <t>Old Mission</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -31891,7 +31891,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>P&amp;G</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -31913,7 +31913,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -31935,7 +31935,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -31957,7 +31957,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -31979,7 +31979,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -32001,7 +32001,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -32023,7 +32023,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -32045,7 +32045,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -32067,12 +32067,12 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="B319" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Window open - check now</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
@@ -32089,7 +32089,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="B320" s="8" t="inlineStr">
@@ -32111,7 +32111,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
@@ -32133,7 +32133,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
@@ -32155,7 +32155,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -32177,7 +32177,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Magna</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
@@ -32199,7 +32199,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Magna</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -32221,7 +32221,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
@@ -32243,7 +32243,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -32265,7 +32265,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -32287,7 +32287,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -32309,7 +32309,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Analysis Group</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -32331,7 +32331,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Analysis Group</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -32353,7 +32353,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -32375,7 +32375,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -32397,7 +32397,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -32419,7 +32419,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -32441,7 +32441,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="B336" s="8" t="inlineStr">
@@ -32463,7 +32463,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-11 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-12 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -13059,7 +13059,7 @@
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t>The summer 2028 tax requisition published $25–$48/hr, unchanged from the 2027 range. Official 2027 ranges: audit $25.64–$51.44/hr, tax $25–$48/hr, Discovery $28</t>
+          <t>$23.22–$59.50/hr spans every wage range and flat rate printed on the audit, tax and Summer Scholar intern postings listed Oct 11, 2026, before geographic adjust</t>
         </is>
       </c>
       <c r="K225" s="6" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>$5,300–$10,600/mo by degree level + housing stipend for CA placements</t>
+          <t xml:space="preserve">$6,100–$14,600/month printed on 24 of the 48 summer 2027 postings listed on October 11, 2026: $6,100 on four design postings, $6,400–$10,300 on the two Digital </t>
         </is>
       </c>
       <c r="K238" s="6" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="H308" s="6" t="inlineStr">
         <is>
-          <t>Intel does not sponsor H-1B visas for internships, but F-1 CPT is actively supported and roughly 30 to 40% of the intern population consists of international students using CPT authorization. Check each posting individua</t>
+          <t>All 13 Bachelor's and graduate program requisitions listed on October 11, 2026 state that the position is not eligible for employment-based visa/immigration sponsorship, and so do three of the 22 PhD-specific requisition</t>
         </is>
       </c>
       <c r="I308" s="6" t="inlineStr">
@@ -17730,7 +17730,7 @@
       </c>
       <c r="J308" s="6" t="inlineStr">
         <is>
-          <t>$30 to $77/hr depending on degree and location, plus $3,000–$8,000 housing stipend</t>
+          <t>$67.5K–$171K/yr, printed as annual salary ranges on the US intern requisitions for Bachelor's, Master's and PhD students listed October 11, 2026 (the Bachelor's</t>
         </is>
       </c>
       <c r="K308" s="6" t="inlineStr">
@@ -22186,7 +22186,7 @@
       </c>
       <c r="J388" s="6" t="inlineStr">
         <is>
-          <t>$32–$35/hr for Consulting, Strategy &amp; AI Summer Analysts; $27–$35/hr for Technology (JD-posted ranges)</t>
+          <t>$27–$35/hr printed in four summer 2027 postings listed on October 11, 2026: Entry Level Advisory Summer Analyst (Advisory Consulting, Strategy, Industry X, Song</t>
         </is>
       </c>
       <c r="K388" s="6" t="inlineStr">
@@ -37677,7 +37677,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -37687,7 +37687,7 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>AWS Student Builder Group Leader — Deadline: Oct 4, 2026 (11:59 PM PST) (Extended from Aug 16)</t>
+          <t>AWS Student Builder Group Leader — Deadline: Jan 10, 2027 (11:59 PM PST) (Next Cohort; Fall 2026 Cohort Closed Oct 4, 2026)</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr"/>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-12 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-13 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Watchlist'!$A$2:$K$411</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Underclassman programs'!$A$2:$F$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-13 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-14 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr">
         <is>
-          <t>Hard deadlines. Each posting states the day recruiting ends (Oct 11, 2026 for most audit roles, Oct 25 for summer 2028 tax), and the first summer 2028 tax requi</t>
+          <t>Stated end dates, and they can move. Each posting states the day recruiting ends (Oct 25, 2026 on the Financial Statement Audit and summer 2028 tax postings). T</t>
         </is>
       </c>
       <c r="J225" s="6" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>Partly open: most Audit &amp; Assurance postings set Oct 11, 2026 as the last day of recruiting, and summer 2028 tax runs to Oct 25, 2026. The Oct 11 date covers seven summer 2027 audit postings plus the first summer 2028 Financial Statement Audit role; the Japanese Services Group summer 2027 audit role runs to Nov 29, 2026. Tax: summer 2028 Accounting and summer 2027 Global Employer Services run to O</t>
+          <t>Partly open: Financial Statement Audit intern postings for summer 2027 and summer 2028 and the summer 2028 tax posting all state Oct 25, 2026 as the last day of recruiting. The Financial Statement Audit postings were extended from Oct 11 to Oct 25; the six other summer 2027 audit postings that stated Oct 11 are no longer listed. The Japanese Services Group summer 2027 audit role runs to Nov 29, 20</t>
         </is>
       </c>
     </row>
@@ -34944,7 +34944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -35941,18 +35941,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027, Python / C++ / Full Stack / C# .NET)</t>
+          <t>Systems Engineering Intern II — Summer 2027 (Current Sophomores; Complete 2nd Undergraduate Year Before Summer 2027; EE/</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Akuna Capital</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr"/>
+          <t>BAE Systems</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL 2026-07-14</t>
+          <t>Nashua / Hudson / Manchester / Merrimack, NH (on-site) Oct 13, 2026</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
@@ -35962,25 +35966,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Postings (community list)</t>
+          <t>Underclassmen Internships</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (apps reviewed from Aug 2026) 🇺🇸</t>
+          <t>Freshman Internship — Summer 2027 (Complete Freshman Year Before Summer; Return as Sophomore; Paid 64-Hour Civil Enginee</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr"/>
+          <t>Gateway Engineers</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA (multiple US) 2026-06-11</t>
+          <t>Pittsburgh, PA (in-person) Oct 13, 2026</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
@@ -35990,25 +35998,25 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Postings (community list)</t>
+          <t>Underclassmen Internships</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027, Python / C++ / Full Stack / C# .NET)</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Aquatic Capital</t>
+          <t>Akuna Capital</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr"/>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL 2026-04-02</t>
+          <t>Chicago, IL 2026-07-14</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
@@ -36025,18 +36033,18 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Software Engineer Intern (apps reviewed from Aug 2026) 🇺🇸</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Arrowstreet Capital</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr"/>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA 2026-07-09</t>
+          <t>Costa Mesa, CA (multiple US) 2026-06-11</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
@@ -36053,18 +36061,18 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Spring 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>Aquatic Capital</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>Chicago, IL 2026-04-02</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -36081,18 +36089,18 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern I (Summer 2027) 🇺🇸</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Arrowstreet Capital</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Nashua, NH 2026-07-14</t>
+          <t>Boston, MA 2026-07-09</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
@@ -36109,18 +36117,18 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Global Technology Summer Analyst, Cybersecurity Analyst 🛂</t>
+          <t>Software Engineering Intern (Spring 2027)</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>multiple US 2026-06-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -36137,18 +36145,18 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Global Technology Summer Analyst, Business Analyst 🛂</t>
+          <t>Software Engineering Intern I (Summer 2027) 🇺🇸</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr"/>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>multiple US 2026-06-28</t>
+          <t>Nashua, NH 2026-07-14</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -36165,18 +36173,18 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Software Developer Intern (Spring 2027) 🇺🇸</t>
+          <t>Global Technology Summer Analyst, Cybersecurity Analyst 🛂</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA (multiple US) 2026-06-10</t>
+          <t>multiple US 2026-06-28</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
@@ -36193,18 +36201,18 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Avionics Software Intern (Spring 2027) 🇺🇸</t>
+          <t>Global Technology Summer Analyst, Business Analyst 🛂</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr"/>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA (multiple US) 2026-06-10</t>
+          <t>multiple US 2026-06-28</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -36221,18 +36229,18 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer 2027) 🛂</t>
+          <t>Software Developer Intern (Spring 2027) 🇺🇸</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Circleback</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA 2026-06-16</t>
+          <t>Seattle, WA (multiple US) 2026-06-10</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
@@ -36249,18 +36257,18 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Future Intern, Early Interest (Summer 2027, Software / AI/ML / Cyber) 🇺🇸</t>
+          <t>Avionics Software Intern (Spring 2027) 🇺🇸</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>CloudFit Software</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr"/>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Lynchburg, VA -</t>
+          <t>Seattle, WA (multiple US) 2026-06-10</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -36277,18 +36285,18 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern / Research Intern, Interpretability (Summer 2027)</t>
+          <t>Software Engineering Intern (Summer 2027) 🛂</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>CTGT</t>
+          <t>Circleback</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr"/>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA 2026-06-27</t>
+          <t>San Francisco, CA 2026-06-16</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -36305,18 +36313,18 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Future Intern, Early Interest (Summer 2027, Software / AI/ML / Cyber) 🇺🇸</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Cubist Systematic Strategies</t>
+          <t>CloudFit Software</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr"/>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>New York, NY -</t>
+          <t>Lynchburg, VA -</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -36333,18 +36341,18 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Software Developer Intern</t>
+          <t>Software Engineering Intern / Research Intern, Interpretability (Summer 2027)</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>D. E. Shaw</t>
+          <t>CTGT</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>New York, NY 2026-04-29</t>
+          <t>San Francisco, CA 2026-06-27</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -36361,12 +36369,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>D. E. Shaw</t>
+          <t>Cubist Systematic Strategies</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr"/>
@@ -36389,18 +36397,18 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineering Intern ⏳</t>
+          <t>Software Developer Intern</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>DimeHealth AI</t>
+          <t>D. E. Shaw</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr"/>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>New York, NY -</t>
+          <t>New York, NY 2026-04-29</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -36417,18 +36425,18 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Information Technology Intern (2027 Summer) 🛂</t>
+          <t>Systems Engineering Intern</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>DTCC</t>
+          <t>D. E. Shaw</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr"/>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ (multiple US) 2026-07-08</t>
+          <t>New York, NY -</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
@@ -36445,18 +36453,18 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Forward Deployed Engineering Intern ⏳</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Ellipsis Labs</t>
+          <t>DimeHealth AI</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr"/>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>New York, NY 2026-03-27</t>
+          <t>New York, NY -</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -36473,18 +36481,18 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Software Developer Intern ⏳</t>
+          <t>Information Technology Intern (2027 Summer) 🛂</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>DTCC</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr"/>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Verona, WI -</t>
+          <t>Jersey City, NJ (multiple US) 2026-07-08</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
@@ -36501,18 +36509,18 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Software Developer Intern (Summer 2027)</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Five Rings</t>
+          <t>Ellipsis Labs</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr"/>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>New York, NY 2026-07-15</t>
+          <t>New York, NY 2026-03-27</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
@@ -36529,18 +36537,18 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>Digital Technology Intern (Spring 2027)</t>
+          <t>Software Developer Intern ⏳</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>GE Appliances</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr"/>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Louisville, KY 2026-06-01</t>
+          <t>Verona, WI -</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
@@ -36557,18 +36565,18 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, BS (Summer 2027)</t>
+          <t>Software Developer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Five Rings</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr"/>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Mountain View, CA (multiple US) 2026-07-20</t>
+          <t>New York, NY 2026-07-15</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -36585,18 +36593,18 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer 2027, C++ / Python)</t>
+          <t>Digital Technology Intern (Spring 2027)</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Hudson River Trading</t>
+          <t>GE Appliances</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr"/>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>New York, NY (multiple) 2026-07-14</t>
+          <t>Louisville, KY 2026-06-01</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -36613,18 +36621,18 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027)</t>
+          <t>Software Engineering Intern, BS (Summer 2027)</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>IMC Trading</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr"/>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL 2026-06-28</t>
+          <t>Mountain View, CA (multiple US) 2026-07-20</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
@@ -36641,18 +36649,18 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning Research Intern (Summer 2027)</t>
+          <t>Software Engineering Intern (Summer 2027, C++ / Python)</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>IMC Trading</t>
+          <t>Hudson River Trading</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL 2026-06-28</t>
+          <t>New York, NY (multiple) 2026-07-14</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -36669,18 +36677,18 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (1) 🇺🇸</t>
+          <t>Software Engineer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Kudu Dynamics</t>
+          <t>IMC Trading</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr"/>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Chantilly, VA -</t>
+          <t>Chicago, IL 2026-06-28</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
@@ -36697,18 +36705,18 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (2) 🇺🇸</t>
+          <t>Machine Learning Research Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Kudu Dynamics</t>
+          <t>IMC Trading</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr"/>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Chantilly, VA -</t>
+          <t>Chicago, IL 2026-06-28</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
@@ -36725,7 +36733,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (3) 🇺🇸</t>
+          <t>Software Engineer Intern (1) 🇺🇸</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -36753,18 +36761,18 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Technical Intern, Software / Cyber / AI (Spring 2027, remote)</t>
+          <t>Software Engineer Intern (2) 🇺🇸</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>LA-Tech.org</t>
+          <t>Kudu Dynamics</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr"/>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA / Remote (US) 2026-07-09</t>
+          <t>Chantilly, VA -</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -36781,18 +36789,18 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Pixel Serving</t>
+          <t>Software Engineer Intern (3) 🇺🇸</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>LiveRamp</t>
+          <t>Kudu Dynamics</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr"/>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>New York, NY 2026-05-21</t>
+          <t>Chantilly, VA -</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
@@ -36809,18 +36817,18 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Summer Intern (CS / Software / Engineering) 🇺🇸</t>
+          <t>Technical Intern, Software / Cyber / AI (Spring 2027, remote)</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>LufCo</t>
+          <t>LA-Tech.org</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr"/>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Aberdeen, MD -</t>
+          <t>Los Angeles, CA / Remote (US) 2026-07-09</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -36837,18 +36845,18 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern 🇺🇸 ⏳</t>
+          <t>Software Engineer Intern, Pixel Serving</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Naive</t>
+          <t>LiveRamp</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr"/>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA / Remote (US) -</t>
+          <t>New York, NY 2026-05-21</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -36865,18 +36873,18 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Full Stack Engineering Intern 🇺🇸 ⏳</t>
+          <t>Summer Intern (CS / Software / Engineering) 🇺🇸</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Nash</t>
+          <t>LufCo</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr"/>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA -</t>
+          <t>Aberdeen, MD -</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
@@ -36893,18 +36901,18 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Agent Platform / Full Stack (2026-2027)</t>
+          <t>Software Engineer Intern 🇺🇸 ⏳</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Netic</t>
+          <t>Naive</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr"/>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA 2026-07-16</t>
+          <t>San Francisco, CA / Remote (US) -</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
@@ -36921,18 +36929,18 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, BCI Applications ⏳</t>
+          <t>Full Stack Engineering Intern 🇺🇸 ⏳</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Neuralink</t>
+          <t>Nash</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr"/>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Fremont, CA 2026-07-16</t>
+          <t>San Francisco, CA -</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
@@ -36949,18 +36957,18 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027, June Start)</t>
+          <t>Software Engineer Intern, Agent Platform / Full Stack (2026-2027)</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Old Mission</t>
+          <t>Netic</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr"/>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL 2026-07-15</t>
+          <t>San Francisco, CA 2026-07-16</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -36977,18 +36985,18 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Austin)</t>
+          <t>Software Engineer Intern, BCI Applications ⏳</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Optiver</t>
+          <t>Neuralink</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr"/>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX 2026-06-28</t>
+          <t>Fremont, CA 2026-07-16</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
@@ -37005,18 +37013,18 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Chicago)</t>
+          <t>Software Engineer Intern (Summer 2027, June Start)</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Optiver</t>
+          <t>Old Mission</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr"/>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL 2026-06-28</t>
+          <t>Chicago, IL 2026-07-15</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
@@ -37033,18 +37041,18 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer 2027, grad 2028)</t>
+          <t>Software Engineer Intern (Austin)</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Optiver</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr"/>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>New York, NY (multiple US) 2026-07-09</t>
+          <t>Austin, TX 2026-06-28</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -37061,18 +37069,18 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Infrastructure (Summer 2027, grad 2028)</t>
+          <t>Software Engineer Intern (Chicago)</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Optiver</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr"/>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>New York, NY (multiple US) 2026-07-09</t>
+          <t>Chicago, IL 2026-06-28</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -37089,7 +37097,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Production Infrastructure (Summer 2027, grad 2028)</t>
+          <t>Software Engineer Intern (Summer 2027, grad 2028)</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
@@ -37117,7 +37125,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Defense Tech (Summer 2027, grad 2028)</t>
+          <t>Software Engineer Intern, Infrastructure (Summer 2027, grad 2028)</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -37128,7 +37136,7 @@
       <c r="C77" s="6" t="inlineStr"/>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Washington, DC (multiple US) 2026-07-09</t>
+          <t>New York, NY (multiple US) 2026-07-09</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -37145,7 +37153,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer Intern, Commercial (Summer 2027, grad Dec 2027 / Spring 2028)</t>
+          <t>Software Engineer Intern, Production Infrastructure (Summer 2027, grad 2028)</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
@@ -37173,7 +37181,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Year at Palantir, Forward Deployed Software Engineer Intern ⏳</t>
+          <t>Software Engineer Intern, Defense Tech (Summer 2027, grad 2028)</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -37184,7 +37192,7 @@
       <c r="C79" s="6" t="inlineStr"/>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>New York, NY (multiple US) 2026-07-09</t>
+          <t>Washington, DC (multiple US) 2026-07-09</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -37201,18 +37209,18 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Backend / Full Stack / ML (Winter 2027)</t>
+          <t>Forward Deployed Software Engineer Intern, Commercial (Summer 2027, grad Dec 2027 / Spring 2028)</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr"/>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA / New York, NY / Seattle, WA 2026-06-27</t>
+          <t>New York, NY (multiple US) 2026-07-09</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -37229,18 +37237,18 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Futureforce) 🔒</t>
+          <t>Year at Palantir, Forward Deployed Software Engineer Intern ⏳</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr"/>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA -</t>
+          <t>New York, NY (multiple US) 2026-07-09</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -37257,18 +37265,18 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Electrical Engineering Intern (Summer 2027)</t>
+          <t>Software Engineer Intern, Backend / Full Stack / ML (Winter 2027)</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Second Order Effects</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr"/>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>El Segundo, CA / Redmond, WA 2026-07-19</t>
+          <t>San Francisco, CA / New York, NY / Seattle, WA 2026-06-27</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -37285,18 +37293,18 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Fall 2026 / Winter 2027)</t>
+          <t>Software Engineer Intern (Futureforce) 🔒</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Skydio</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr"/>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>San Mateo, CA 2026-05-06</t>
+          <t>San Francisco, CA -</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -37313,18 +37321,18 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer Intern 🇺🇸</t>
+          <t>Electrical Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Stoke Space</t>
+          <t>Second Order Effects</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr"/>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Kent, WA 2026-05-05</t>
+          <t>El Segundo, CA / Redmond, WA 2026-07-19</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -37341,18 +37349,18 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Strategy Developer Intern (Summer 2027, June start)</t>
+          <t>Software Engineer Intern (Fall 2026 / Winter 2027)</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Susquehanna</t>
+          <t>Skydio</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr"/>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Bala Cynwyd, PA -</t>
+          <t>San Mateo, CA 2026-05-06</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -37369,18 +37377,18 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Trading System Engineering Intern 🇺🇸</t>
+          <t>Software Engineer Intern 🇺🇸</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Susquehanna</t>
+          <t>Stoke Space</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr"/>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Bala Cynwyd, PA -</t>
+          <t>Kent, WA 2026-05-05</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -37397,18 +37405,18 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (North America, Summer 2027)</t>
+          <t>Quantitative Strategy Developer Intern (Summer 2027, June start)</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>The Trade Desk</t>
+          <t>Susquehanna</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr"/>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO (multiple US) 2026-07-16</t>
+          <t>Bala Cynwyd, PA -</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -37425,18 +37433,18 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Applied Scientist Intern, Monetization Technology (PhD, 2027 Start)</t>
+          <t>Trading System Engineering Intern 🇺🇸</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Susquehanna</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr"/>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>San Jose, CA 2026-04-16</t>
+          <t>Bala Cynwyd, PA -</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
@@ -37453,18 +37461,18 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern (Summer 2027)</t>
+          <t>Software Engineering Intern (North America, Summer 2027)</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Tower Research Capital</t>
+          <t>The Trade Desk</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr"/>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>New York, NY / Chicago, IL 2026-07-06</t>
+          <t>Denver, CO (multiple US) 2026-07-16</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
@@ -37481,18 +37489,18 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Engineering Intern (12 roles: process, equipment, CIM / software)</t>
+          <t>Applied Scientist Intern, Monetization Technology (PhD, 2027 Start)</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>TSMC Arizona</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr"/>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ 2026-06-04</t>
+          <t>San Jose, CA 2026-04-16</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -37509,18 +37517,18 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>AI Research Scientist Intern (MS / PhD)</t>
+          <t>Quantitative Developer Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Two Sigma</t>
+          <t>Tower Research Capital</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr"/>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>New York, NY 2026-07-08</t>
+          <t>New York, NY / Chicago, IL 2026-07-06</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -37537,18 +37545,18 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer 2027, Uber Career Prep)</t>
+          <t>Engineering Intern (12 roles: process, equipment, CIM / software)</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>TSMC Arizona</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr"/>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA / Seattle, WA / Sunnyvale, CA 2026-07-20</t>
+          <t>Phoenix, AZ 2026-06-04</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -37565,18 +37573,18 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Engineering Intern (Summer 2027) 🛂 🇺🇸</t>
+          <t>AI Research Scientist Intern (MS / PhD)</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Unison (GE Aerospace)</t>
+          <t>Two Sigma</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr"/>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Jacksonville, FL 2026-07-16</t>
+          <t>New York, NY 2026-07-08</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -37593,18 +37601,18 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern (2027)</t>
+          <t>Software Engineering Intern (Summer 2027, Uber Career Prep)</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Voloridge Investment Management</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr"/>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Jupiter, FL 2026-06-15</t>
+          <t>San Francisco, CA / Seattle, WA / Sunnyvale, CA 2026-07-20</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -37621,18 +37629,18 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Quant Developer Intern</t>
+          <t>Engineering Intern (Summer 2027) 🛂 🇺🇸</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Walleye Capital</t>
+          <t>Unison (GE Aerospace)</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr"/>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA -</t>
+          <t>Jacksonville, FL 2026-07-16</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -37649,18 +37657,18 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer 2027)</t>
+          <t>Quantitative Developer Intern (2027)</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Voloridge Investment Management</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr"/>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>San Jose, CA 2026-07-20</t>
+          <t>Jupiter, FL 2026-06-15</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -37677,20 +37685,20 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Quant Developer Intern</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>AWS Student Builder Group Leader — Deadline: Jan 10, 2027 (11:59 PM PST) (Next Cohort; Fall 2026 Cohort Closed Oct 4, 2026)</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr"/>
+          <t>Walleye Capital</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr"/>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Boston, MA -</t>
+        </is>
+      </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37698,27 +37706,27 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Postings (community list)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Software Engineering Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>AWS / NextGen</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>AWS Global University Program — Deadline: Rolling</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr"/>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr"/>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>San Jose, CA 2026-07-20</t>
+        </is>
+      </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37726,24 +37734,24 @@
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Postings (community list)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>⏳ OPENS SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Word of Life Bible Institute</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Campus Expert — Deadline: Annual Window (Applications Open Each July; Next: July 2027)</t>
+          <t>Student Ambassador Scholarship — 2027–2028 — Deadline: Not published for this ambassador application (live form)</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr"/>
@@ -37761,7 +37769,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Summer of Code</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
@@ -37771,7 +37779,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Google Student Influencer Program (2026) — Deadline: Check site</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr"/>
@@ -37782,24 +37790,24 @@
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Outreachy</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>Microsoft Learn Student Ambassadors — Deadline: Rolling</t>
+          <t>open-source, stipend, open to intl</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr"/>
@@ -37810,27 +37818,31 @@
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs always open)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Software Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Monster Energy</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>College Ambassador Team (CAT) — Deadline: Check site</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr"/>
+          <t>SWE intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37838,27 +37850,31 @@
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Machine Learning &amp; AI Undergrad Internship</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Pearson Campus Ambassador — Deadline: Rolling</t>
-        </is>
-      </c>
-      <c r="D103" s="5" t="inlineStr"/>
+          <t>ML / AI intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37866,27 +37882,31 @@
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Hardware Undergrad Engineering Internship</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Princess Polly</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>College Ambassador — Deadline: Rolling</t>
-        </is>
-      </c>
-      <c r="D104" s="5" t="inlineStr"/>
+          <t>hardware intern (undergrad)</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37894,27 +37914,31 @@
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>Student Fellows Program</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>Student Marketeer — Deadline: Rolling</t>
-        </is>
-      </c>
-      <c r="D105" s="5" t="inlineStr"/>
+          <t>data and AI fellowship</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>check site</t>
+        </is>
+      </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37922,27 +37946,31 @@
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Ambassador Programs</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Summer of Code</t>
+          <t>2027 US Summer Internship, Early Interest</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="inlineStr"/>
+          <t>early interest pipeline</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37950,27 +37978,31 @@
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Learn Student Ambassadors</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Outreachy</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>open-source, stipend, open to intl</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr"/>
+          <t>ambassador program</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>rolling</t>
+        </is>
+      </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -37978,24 +38010,24 @@
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs always open)</t>
+          <t>Pipelines (programs open now)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Software Undergrad Engineering Internship</t>
+          <t>MLH Fellowship</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>MLH</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>SWE intern (undergrad)</t>
+          <t>remote SWE fellowship, stipend</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -38017,22 +38049,22 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; AI Undergrad Internship</t>
+          <t>Neo Scholars</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Neo</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>ML / AI intern (undergrad)</t>
+          <t>CS undergrad fellowship</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>approx June 14 to 30, 2026</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
@@ -38049,22 +38081,22 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Hardware Undergrad Engineering Internship</t>
+          <t>AI Builder, Emerging Talent</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>hardware intern (undergrad)</t>
+          <t>emerging talent program</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>rolling</t>
+          <t>check site</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
@@ -38081,22 +38113,22 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Student Fellows Program</t>
+          <t>2027 Summer Internships, Express Your Interest</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Schonfeld</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>data and AI fellowship</t>
+          <t>express interest pipeline, full roles open Aug 2026</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>check site</t>
+          <t>rolling</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
@@ -38113,24 +38145,20 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>2027 US Summer Internship, Early Interest</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>American Meteorological Society</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>early interest pipeline</t>
-        </is>
-      </c>
-      <c r="D112" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>AMS First-Year Undergraduate Scholarship (2027)</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr"/>
       <c r="E112" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38138,31 +38166,27 @@
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Learn Student Ambassadors</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Elks National Foundation</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>ambassador program</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>Most Valuable Student Scholarship — 2027 Incoming College Cohort</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr"/>
       <c r="E113" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38170,31 +38194,27 @@
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>MLH Fellowship</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>MLH</t>
+          <t>Hagan Scholarship Foundation</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>remote SWE fellowship, stipend</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>Hagan Scholarship — Incoming College Freshmen, 2027–2028</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr"/>
       <c r="E114" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38202,31 +38222,27 @@
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Neo Scholars</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Neo</t>
+          <t>Jack Kent Cooke Foundation</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>CS undergrad fellowship</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>approx June 14 to 30, 2026</t>
-        </is>
-      </c>
+          <t>College Scholarship Program — Entering Fall 2027</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr"/>
       <c r="E115" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38234,31 +38250,27 @@
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>AI Builder, Emerging Talent</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>James Madison University</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>emerging talent program</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>check site</t>
-        </is>
-      </c>
+          <t>School of Media Arts and Design Incoming First-Year Journalism Scholarships (Fall 2027)</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38266,31 +38278,27 @@
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>2027 Summer Internships, Express Your Interest</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Schonfeld</t>
+          <t>Lander University Foundation / College of Nursing</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>express interest pipeline, full roles open Aug 2026</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>rolling</t>
-        </is>
-      </c>
+          <t>Nahn Joo Chang Scholarship — Incoming First-Year Pre-Nursing (2027–2028)</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr"/>
       <c r="E117" s="7" t="inlineStr">
         <is>
           <t>apply</t>
@@ -38298,7 +38306,7 @@
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Pipelines (programs open now)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38310,12 +38318,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Hagan Scholarship Foundation</t>
+          <t>Montana State University Honors College</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>Hagan Scholarship (HS Senior; 3.5+ GPA; Household Income ≤ $125K; 4-Yr Non-Profit College — No CC/Online)</t>
+          <t>Presidential Scholarship — Incoming First-Year Students, Fall 2027</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr"/>
@@ -38326,7 +38334,7 @@
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38338,12 +38346,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Northeastern State University Foundation</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>WiSE - Women in Science &amp; Engineering (Class of 2030)</t>
+          <t>Incoming Freshman Foundation Scholarships — 2027–2028</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr"/>
@@ -38354,7 +38362,7 @@
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38366,12 +38374,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>National Merit Scholarship Corporation</t>
+          <t>RMIT University / George Alexander Foundation</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>National Merit Scholarship (PSAT/NMSQT Junior Year)</t>
+          <t>George Alexander Foundation Scholarship — First Year of Tertiary Study, 2027</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr"/>
@@ -38382,7 +38390,7 @@
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38394,12 +38402,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Optimist International</t>
+          <t>RMIT University / IDEA</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>Optimist International Essay Contest (Under 19 on Oct 1; 700–800 word essay; 2026-27 topic announced)</t>
+          <t>IDEA Photography Scholarship for Excellence — Incoming First-Year, 2027</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
@@ -38410,7 +38418,7 @@
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38422,12 +38430,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Posse Foundation</t>
+          <t>UNCF / Fidelity Investments</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>Posse Scholarship (Nomination-Based; Partner Cities)</t>
+          <t>Fidelity Scholars Bachelor’s Degree Program (Incoming 2027–2028 Freshmen)</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr"/>
@@ -38438,7 +38446,7 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38450,12 +38458,12 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Regeneron / Society for Science</t>
+          <t>University of North Texas / Terry Foundation</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>Regeneron Science Talent Search (HS Senior STEM Research)</t>
+          <t>Terry Freshman Scholarship — Fall 2027</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr"/>
@@ -38466,7 +38474,7 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Rising Freshmen &amp; Class of 2030 Opportunities</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38478,12 +38486,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Wayne State College</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>Adobe NEXT// Campus Leader — Deadline: Check site</t>
+          <t>Career Scholars Cooperative Education Program — Incoming Freshmen (Fall 2027)</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr"/>
@@ -38494,7 +38502,7 @@
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
@@ -38506,12 +38514,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative</t>
+          <t>Western Kentucky University</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>Career Pathways Initiative Fellowship — Deadline: Rolling</t>
+          <t>Potter College Creative Arts Scholarship — Incoming Freshman Creative Writing Track (2027–28)</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr"/>
@@ -38522,24 +38530,24 @@
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+          <t>Rising Freshmen &amp; First-Year Opportunities</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bain Capital</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>Databricks Student Fellows Program — Deadline: Check site</t>
+          <t>Investors of Tomorrow — Boston (November 2026) — Deadline: October 25, 2026 (11:59 PM EST, as published)</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr"/>
@@ -38557,17 +38565,17 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>Baird</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>ElevenLabs Ambassador Program — Deadline: Rolling</t>
+          <t>Women in Equity Research Event (2026) — Deadline: Oct 15, 2026</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr"/>
@@ -38590,12 +38598,12 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>GirlsWhoML</t>
+          <t>Baker McKenzie</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>Thinking About Thinking 2026 Ambassador Programme — Deadline: Check site</t>
+          <t>First Year Scheme 2027 — Deadline: February 1, 2027 (time not published)</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr"/>
@@ -38613,17 +38621,17 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>AI Fellowship Program — Deadline: Check site</t>
+          <t>EMEA Future Leaders Spring Insight Programme (2027) — Deadline: Oct 16, 2026</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr"/>
@@ -38646,12 +38654,12 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>IOScholarships</t>
+          <t>Citadel / Citadel Securities</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>AWS re/Start — Deadline: Rolling (Cohort: Sep 15–Dec 15, 2026)</t>
+          <t>Discover — U.S. (2027) — Deadline: March 5, 2027</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr"/>
@@ -38674,12 +38682,12 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Citadel / Citadel Securities</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>Bridge — Deadline: Sep 27, 2026 (New York) / Jan 3, 2027 (London)</t>
+          <t>Discover — EMEA (2027) — Deadline: January 29, 2027</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr"/>
@@ -38702,12 +38710,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Citadel Securities</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>FTTP — First-Year Trading &amp; Technology Program — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>Discover — Hong Kong (2027) — Deadline: February 14, 2027</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr"/>
@@ -38730,12 +38738,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Jane Street</t>
+          <t>Five Rings</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>FOCUS — Deadline: Rolling (Sign Up to Be Notified)</t>
+          <t>LINK 2027: Software Development Intensive Program — Deadline: No deadline published; application form currently open</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr"/>
@@ -38753,17 +38761,17 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Lime Connect</t>
+          <t>Girls Who Invest</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>Lime Connect Network Membership — Deadline: Rolling</t>
+          <t>GWI Scholars Program (2027) — Deadline: October 15, 2026 (11:59 PM Local Time)</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr"/>
@@ -38781,17 +38789,17 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>MLT (Management Leadership for Tomorrow)</t>
+          <t>Houlihan Lokey</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>MLT Career Prep (Class of 2029) — Deadline: Aug 1, 2026 – Jan 15, 2027 (Phased)</t>
+          <t>Investment Banking Insight Day — Corporate Finance (2026) — Deadline: Oct 19, 2026</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr"/>
@@ -38814,12 +38822,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Moonshot (formerly OpenTrade)</t>
+          <t>Icahn School of Medicine at Mount Sinai</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Moonshot Fellowship (formerly OpenTrade Fellowship) — Deadline: Rolling (Limited Spots)</t>
+          <t>FlexMed Early Assurance Program — 2027 Application — Deadline: January 14, 2027 at 11:59 PM EST, including all materials</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr"/>
@@ -38842,12 +38850,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Insight Partners</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Campus Leaders — Deadline: Rolling</t>
+          <t>Inclusion by Insight Virtual Summit (2027) — Deadline: November 6, 2026 (5:00 PM ET)</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr"/>
@@ -38870,12 +38878,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>SHPE</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>2026 SHPE National Convention — Deadline: Check site (Event: Oct 28–31, 2026)</t>
+          <t>Bridge — London (2027) — Deadline: January 3, 2027 (11:59 PM GMT)</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr"/>
@@ -38898,12 +38906,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>WomenHack</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>Women in Tech Career Fair — Deadline: Varies per event</t>
+          <t>FTTP — First-Year Trading &amp; Technology — London (2027) — Deadline: January 3, 2027 (11:59 PM GMT)</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr"/>
@@ -38926,12 +38934,12 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Jane Street</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>Student Researcher, BS/MS, Fall 2026 — Deadline: Nov 27, 2026 (Rolling; May Close Earlier)</t>
+          <t>FTTP — First-Year Trading &amp; Technology — New York (2027) — Deadline: January 31, 2027 (11:59 PM EST)</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr"/>
@@ -38942,12 +38950,908 @@
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Jane Street</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>FOCUS — London (2027) — Deadline: November 8, 2026 (11:59 PM GMT)</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr"/>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Jane Street</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>FOCUS — New York (2027) — Deadline: November 15, 2026 (11:59 PM EST)</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr"/>
+      <c r="E142" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University — Life Design Lab</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>BioTech Engineering Internship Academy (Spring 2027) — Deadline: Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr"/>
+      <c r="E143" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>Investment Banking &amp; Markets Insights Program (December 2026) — Deadline: October 15, 2026 (12:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr"/>
+      <c r="E144" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>KeyBanc Capital Markets</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Investment Banking Sophomore Series (2027) — Deadline: October 30, 2026</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr"/>
+      <c r="E145" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Latham &amp; Watkins</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>2027 First-Year Spring Scheme — London — Deadline: January 31, 2027 (time not published)</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr"/>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Lincoln International</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Sophomore Job Shadow Program (2026) — Deadline: Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr"/>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Lincoln International</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Women in Finance Workshop (2026) — Deadline: Oct 30, 2026</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr"/>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>MLT (Management Leadership for Tomorrow)</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Career Prep (Class of 2029) — Deadline: January 15, 2027 (11:59 PM EST); SWE/Technology/Corporate Priority November 1, 2026</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr"/>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Novogradac &amp; Company</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>2027 Summer Leadership Program — Atlanta/Alpharetta — Deadline: No deadline published; live job-specific application</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr"/>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Optiver</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>FutureFocus: Quants (2027) — Deadline: December 6, 2026 (UK/Ireland) / February 1, 2027 (EU), 23:59 CET</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr"/>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Plante Moran</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>2027 Expo — Summer Student Leadership Program — Deadline: No deadline published; live job-specific application</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr"/>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Point72</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>Academy Spring Insight Programme — UK (2027) — Deadline: Nov 15, 2026, 11:59pm UTC</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr"/>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Stifel</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>Emerging Leaders Webinar (October 2026) — Deadline: October 14, 2026 (11:59 PM EST, as published)</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr"/>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>Discovery — Trading System Engineer (2027) — Deadline: November 16, 2026</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr"/>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>Discovery — Quantitative Trading &amp; Strategy Development (2027) — Deadline: November 16, 2026</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr"/>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>Discovery — Equity + Macro Research (2027) — Deadline: November 16, 2026</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr"/>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Discovery — Growth Equity (2027) — Deadline: Not published (live application)</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr"/>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Discovery — Operations (2027) — Deadline: Not published (live application)</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr"/>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Susquehanna</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>Discovery — Capital Markets (2027) — Deadline: Not published (live application)</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr"/>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>University of Minnesota Twin Cities — Pre-Health Student Resource Center</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>Health Profession Pathways — Spring 2027 First-Year Cohort — Deadline: October 21, 2026 (time and time zone not published)</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr"/>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>Weiss Asset Management</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>Underclassmen Fellowship — January 2027 — Deadline: October 16, 2026 at 5:00 PM EDT</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr"/>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Programs (Fellowships, Externships, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Barry Goldwater Scholarship &amp; Excellence in Education Foundation</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>Goldwater Summer Research Internship (2027) — Deadline: Nov 2, 2026</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr"/>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
           <t>Underclassmen Research Programs</t>
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>Cornell University / Einaudi Center</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>Laidlaw Leadership and Research Program, 2027–2029 — Deadline: January 6, 2027 (time zone not published)</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr"/>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>🔥 CLOSING SOON]</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Dartmouth College / Thayer School of Engineering</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Early Research Access in the Sciences (ERAS) / First Year Research in Engineering Experience (FYREE), Winter–Spring 2027 — Deadline: Faculty interviews: October</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr"/>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Dartmouth College — Leslie Center for the Humanities</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Student Research Fellows in Nineteenth-Century Studies (2027–28) — Deadline: March 29, 2027 (timezone/time not stated)</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr"/>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Penn State / NASA Pennsylvania Space Grant Consortium</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Undergraduate Research Internship Program (URIP), 2027 — Deadline: November 1, 2026 (time zone not published)</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr"/>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Stanford University — Public Humanities</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>Humanities Research Intensive (Spring Break 2027) — Deadline: Nov 2, 2026, 11:59pm</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr"/>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>The Rockefeller University / CUNY Hunter College</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Hunter × RockEDU Scholars (2027) — Deadline: Jan 4, 2027, 5:00pm ET (including recommendation)</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr"/>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>University of Florida — Center for Undergraduate Research</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>Emerging Scholars Program (2027) — Deadline: November 1, 2026, 11:59pm (timezone not stated)</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr"/>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Laidlaw Undergraduate Research and Leadership Programme, 2026–2027 Intake — Deadline: January 22, 2027 at 23:59 (time zone not stated by provider)</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr"/>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>✅ OPEN]</t>
+        </is>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>University of North Carolina Wilmington</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>First-Year Research Experience (FYRE), Spring 2027 — Deadline: October 29, 2026 at 5:00 PM (time zone not published)</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr"/>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>Underclassmen Research Programs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:F140"/>
+  <autoFilter ref="A2:F172"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -39074,6 +39978,38 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E143" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E144" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E145" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E146" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E147" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E148" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E149" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E150" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E151" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E152" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E153" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E154" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E155" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E169" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E170" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E171" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E172" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-15 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-16 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -20372,7 +20372,7 @@
       </c>
       <c r="D356" s="6" t="inlineStr">
         <is>
-          <t>Technology SA; Quantitative Finance SA  (2 of 12 tracks)</t>
+          <t>Technology SA; Quantitative Finance SA  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E356" s="7" t="inlineStr">
@@ -40273,7 +40273,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-16 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-17 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -14649,17 +14649,17 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – January 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data / Analytics  (2 of 6 tracks)</t>
+          <t>Digital / Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>careers.paramount.com/go/Interns/8710100/</t>
+          <t>pfizer.com/en/about/careers/pfizer-futures</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
@@ -14669,30 +14669,30 @@
       </c>
       <c r="G254" s="6" t="inlineStr">
         <is>
-          <t>Most roles follow a two-round process. Round one is a recruiter phone screen lasting 15-30 minutes covering your background, interest in entertainment, and availability. Round two is a Zoom interview with the hiring team, often including behavioral questions like "What media do you consume?" and "Wh</t>
+          <t xml:space="preserve">Pfizer's funnel has two to three interview levels, and the process typically runs 4 to 8 weeks from application to final decision: 1. Apply through the Pfizer Futures page , which links to the Atrium application portal (summer 2027 window: October 5 to November 8, 2026). Pfizer's Workday board does </t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr"/>
       <c r="I254" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as qualified candidates apply; no individual status feedback provided</t>
+          <t>Yes. "Applications reviewed on a rolling basis" (all JD postings). Community reports 70% of top-track slots go within first 45 days</t>
         </is>
       </c>
       <c r="J254" s="6" t="inlineStr">
         <is>
-          <t>$23/hr median (Glassdoor, 266 reports); $19-$23/hr business roles, $34-$45/hr engineering roles</t>
+          <t>$26–$29/hr undergrad (official); $45–$52/hr PhD (community-reported). Housing stipend available for relocated interns</t>
         </is>
       </c>
       <c r="K254" s="6" t="inlineStr">
         <is>
-          <t>Expected October-November 2026 through late December 2026 / early January 2027 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Open now. Applications for summer 2027 opened October 5, 2026 and close November 8, 2026 (stated on the Pfizer Futures page and on every summer 2027 posting)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Physical Intelligence</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -14702,17 +14702,17 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>Digital / Technology  (1 of 6 tracks)</t>
+          <t>Research Intern (Robotics/AI); ML Infra Intern; Robotics SWE Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>pfizer.com/en/about/careers/pfizer-futures</t>
+          <t>jobs.ashbyhq.com/physicalintelligence</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
@@ -14722,30 +14722,34 @@
       </c>
       <c r="G255" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pfizer's funnel has two to three interview levels, and the process typically runs 4 to 8 weeks from application to final decision: 1. Apply through the Pfizer Futures page , which links to the Atrium application portal (summer 2027 window: October 5 to November 8, 2026). Pfizer's Workday board does </t>
-        </is>
-      </c>
-      <c r="H255" s="6" t="inlineStr"/>
+          <t>Physical Intelligence does not publish its interview process, but recruiter job descriptions mention structured interviewer calibration, and the loop for comparable robotics AI research roles follows a predictable pattern: 1. Apply on the Ashby ATS or pi.website/join-us . Upload your resume, publica</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t>Likely supported for qualified candidates. CPT standard for F-1 students. Not explicitly confirmed on PI's website; verify during application</t>
+        </is>
+      </c>
       <c r="I255" s="6" t="inlineStr">
         <is>
-          <t>Yes. "Applications reviewed on a rolling basis" (all JD postings). Community reports 70% of top-track slots go within first 45 days</t>
+          <t>Yes (DEFAULT tier). No publicly documented rigid cycle. Positions are posted when research teams identify needs. Apply as soon as you see a listing</t>
         </is>
       </c>
       <c r="J255" s="6" t="inlineStr">
         <is>
-          <t>$26–$29/hr undergrad (official); $45–$52/hr PhD (community-reported). Housing stipend available for relocated interns</t>
+          <t>Estimated $8,000 to $12,000/month for PhD research interns; $5,000 to $7,000/month for MS. Robot Operator roles approximately $25/hr. Based on comparable SF rob</t>
         </is>
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>Open now. Applications for summer 2027 opened October 5, 2026 and close November 8, 2026 (stated on the Pfizer Futures page and on every summer 2027 posting)</t>
+          <t>Expected October to December 2026 for summer 2027 roles. Rolling review; likely closes January to February 2027. Projected from company growth trajectory and industry norms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>Physical Intelligence</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -14760,12 +14764,12 @@
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>Research Intern (Robotics/AI); ML Infra Intern; Robotics SWE Intern  (3 of 5 tracks)</t>
+          <t>Summer Research Internship: Generative AI Features (prior cycle)  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/physicalintelligence</t>
+          <t>jobs.ashbyhq.com/pika</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
@@ -14775,34 +14779,34 @@
       </c>
       <c r="G256" s="6" t="inlineStr">
         <is>
-          <t>Physical Intelligence does not publish its interview process, but recruiter job descriptions mention structured interviewer calibration, and the loop for comparable robotics AI research roles follows a predictable pattern: 1. Apply on the Ashby ATS or pi.website/join-us . Upload your resume, publica</t>
+          <t>Based on TechPrep candidate reports, the process takes 3 to 5 weeks and includes a recruiter screen (15 to 30 minutes), a technical phone screen with live Python coding (about 60 minutes), and a virtual onsite with 4 to 5 rounds covering DSA, system design for GPU inference and video pipelines, a cr</t>
         </is>
       </c>
       <c r="H256" s="6" t="inlineStr">
         <is>
-          <t>Likely supported for qualified candidates. CPT standard for F-1 students. Not explicitly confirmed on PI's website; verify during application</t>
+          <t>Not explicitly confirmed. Likely supports OPT/CPT for F-1 students given Palo Alto location and funding level. Verify during recruiter screen</t>
         </is>
       </c>
       <c r="I256" s="6" t="inlineStr">
         <is>
-          <t>Yes (DEFAULT tier). No publicly documented rigid cycle. Positions are posted when research teams identify needs. Apply as soon as you see a listing</t>
+          <t>Yes. The current Research Intern listing offers flexible part-time and full-time terms with no fixed deadline, suggesting continuous hiring. Apply as soon as th</t>
         </is>
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>Estimated $8,000 to $12,000/month for PhD research interns; $5,000 to $7,000/month for MS. Robot Operator roles approximately $25/hr. Based on comparable SF rob</t>
+          <t>$10,000/month (from prior BuiltInSF listing). Catered lunch and dinner in office. Weekly team events. Housing and transportation not included</t>
         </is>
       </c>
       <c r="K256" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. Rolling review; likely closes January to February 2027. Projected from company growth trajectory and industry norms</t>
+          <t>Expected October to December 2026 for summer 2027 roles. Rolling intake; the previous summer listing was removed September 2025, suggesting a similar rhythm</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Plaid</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -14812,17 +14816,17 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>Summer Research Internship: Generative AI Features (prior cycle)  (1 of 4 tracks)</t>
+          <t>Software Engineering Intern; Data Science Intern; Security Engineering Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/pika</t>
+          <t>plaid.com/careers/</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
@@ -14832,34 +14836,34 @@
       </c>
       <c r="G257" s="6" t="inlineStr">
         <is>
-          <t>Based on TechPrep candidate reports, the process takes 3 to 5 weeks and includes a recruiter screen (15 to 30 minutes), a technical phone screen with live Python coding (about 60 minutes), and a virtual onsite with 4 to 5 rounds covering DSA, system design for GPU inference and video pipelines, a cr</t>
+          <t>Four stages over 4 to 6 weeks: resume screening (15 to 20% advance), a 30-minute recruiter phone screen (non-technical), a 45- to 60-minute technical phone screen via CodeSignal or Karat (LeetCode Easy-Medium), and a 3- to 4-hour virtual onsite with two coding rounds, one behavioral round, sometimes</t>
         </is>
       </c>
       <c r="H257" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed. Likely supports OPT/CPT for F-1 students given Palo Alto location and funding level. Verify during recruiter screen</t>
+          <t>F-1 CPT and OPT accepted (university-sponsored). Plaid does not directly sponsor visa status for interns. Full-time conversion supports OPT, STEM Extension, and H-1B</t>
         </is>
       </c>
       <c r="I257" s="6" t="inlineStr">
         <is>
-          <t>Yes. The current Research Intern listing offers flexible part-time and full-time terms with no fixed deadline, suggesting continuous hiring. Apply as soon as th</t>
+          <t>Yes, rolling with soft deadlines. Positions close by team as they fill. Applying in the first two weeks after a posting goes live yields the fastest responses (</t>
         </is>
       </c>
       <c r="J257" s="6" t="inlineStr">
         <is>
-          <t>$10,000/month (from prior BuiltInSF listing). Catered lunch and dinner in office. Weekly team events. Housing and transportation not included</t>
+          <t>$49 to $61 per hour ($8,500 to $10,500/month) depending on role and location. Housing stipend of $2,500 to $3,500/month. Sign-on/relocation of $9,000 to $10,000</t>
         </is>
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. Rolling intake; the previous summer listing was removed September 2025, suggesting a similar rhythm</t>
+          <t>Not open as of October 6, 2026: no internship on Plaid's job board. The projected August 15, 2026 opening did not happen, and archived snapshots show no public intern posting in the summer 2026 cycle either, so no date can be projected with confidence</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>Raymond James</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -14874,12 +14878,12 @@
       </c>
       <c r="D258" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science Intern; Security Engineering Intern  (3 of 5 tracks)</t>
+          <t>Information Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>plaid.com/careers/</t>
+          <t>raymondjames.wd1.myworkdayjobs.com/RaymondJamesEarlyCareers</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
@@ -14889,34 +14893,34 @@
       </c>
       <c r="G258" s="6" t="inlineStr">
         <is>
-          <t>Four stages over 4 to 6 weeks: resume screening (15 to 20% advance), a 30-minute recruiter phone screen (non-technical), a 45- to 60-minute technical phone screen via CodeSignal or Karat (LeetCode Easy-Medium), and a 3- to 4-hour virtual onsite with two coding rounds, one behavioral round, sometimes</t>
+          <t>Raymond James runs a five-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through the Raymond James Workday portal with your resume, cover letter, and transcripts. Raymond James posts separate listings per division, so choose your strongest</t>
         </is>
       </c>
       <c r="H258" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT and OPT accepted (university-sponsored). Plaid does not directly sponsor visa status for interns. Full-time conversion supports OPT, STEM Extension, and H-1B</t>
+          <t>No. Raymond James does not offer visa sponsorship for internships. Applicants must be legally authorized to work in the U.S. without visa sponsorship now or in the future, including beyond OPT/EAD. International students</t>
         </is>
       </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
-          <t>Yes, rolling with soft deadlines. Positions close by team as they fill. Applying in the first two weeks after a posting goes live yields the fastest responses (</t>
+          <t>Yes. Raymond James reviews applications on a rolling basis; apply within the first 2–3 weeks</t>
         </is>
       </c>
       <c r="J258" s="6" t="inlineStr">
         <is>
-          <t>$49 to $61 per hour ($8,500 to $10,500/month) depending on role and location. Housing stipend of $2,500 to $3,500/month. Sign-on/relocation of $9,000 to $10,000</t>
+          <t>$72,000–$95,000 annualized by division (IB Summer Analyst ~$95,000; general intern ~$72,000)</t>
         </is>
       </c>
       <c r="K258" s="6" t="inlineStr">
         <is>
-          <t>Not open as of October 6, 2026: no internship on Plaid's job board. The projected August 15, 2026 opening did not happen, and archived snapshots show no public intern posting in the summer 2026 cycle either, so no date can be projected with confidence</t>
+          <t>Open now for summer 2027: IB Summer Analyst roles posting group by group on the Raymond James Early Careers Workday portal (Chicago Financial Services Oct 5, Charlotte Consumer Oct 12, McLean Diversified Industrials Oct 15, 2026; McLean closes Oct 22). The September 11 wave (St. Petersburg M&amp;A, Capital Markets, Equity Research) is already down. Summer 2028: Sophomore IB Bootcamp open since October</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>Raymond James</t>
+          <t>RBC Capital Markets</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -14926,17 +14930,17 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>Information Technology  (1 of 6 tracks)</t>
+          <t>QTS (Quantitative Technology &amp; Strategy)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>raymondjames.wd1.myworkdayjobs.com/RaymondJamesEarlyCareers</t>
+          <t>rbc.wd3.myworkdayjobs.com/RBCEARLYTALENT1</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
@@ -14946,34 +14950,34 @@
       </c>
       <c r="G259" s="6" t="inlineStr">
         <is>
-          <t>Raymond James runs a five-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through the Raymond James Workday portal with your resume, cover letter, and transcripts. Raymond James posts separate listings per division, so choose your strongest</t>
+          <t>You apply, complete a HireVue video assessment (four to five questions, zero retakes, 15 to 25% pass rate), then a 60-minute first-round phone or video interview mixing behavioral and technical questions, and finally a Superday with VPs, Directors, and MDs. Candidates report offers within one to two</t>
         </is>
       </c>
       <c r="H259" s="6" t="inlineStr">
         <is>
-          <t>No. Raymond James does not offer visa sponsorship for internships. Applicants must be legally authorized to work in the U.S. without visa sponsorship now or in the future, including beyond OPT/EAD. International students</t>
+          <t>Strong track record: 273 H-1B filings with 100% approval rate. CPT supported for F-1 students</t>
         </is>
       </c>
       <c r="I259" s="6" t="inlineStr">
         <is>
-          <t>Yes. Raymond James reviews applications on a rolling basis; apply within the first 2–3 weeks</t>
+          <t>Yes. RBC reviews applications on a rolling basis and fills interview slots continuously. Apply in the first one to two weeks for the best odds</t>
         </is>
       </c>
       <c r="J259" s="6" t="inlineStr">
         <is>
-          <t>$72,000–$95,000 annualized by division (IB Summer Analyst ~$95,000; general intern ~$72,000)</t>
+          <t>$2,115/week (~$110,000 annualized) for U.S. IB/CM roles. $7,000 housing stipend, dinner stipend after 7 PM, car service after 9 PM, relocation up to $2,000 dome</t>
         </is>
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: IB Summer Analyst roles posting group by group on the Raymond James Early Careers Workday portal (Chicago Financial Services Oct 5, Charlotte Consumer Oct 12, McLean Diversified Industrials Oct 15, 2026; McLean closes Oct 22). The September 11 wave (St. Petersburg M&amp;A, Capital Markets, Equity Research) is already down. Summer 2028: Sophomore IB Bootcamp open since October</t>
+          <t>Summer 2028 IB Summer Analyst: NOT YET OPEN. Applications for summer 2028 expected to open around Oct to Nov 2026 and close around late Jan to early Mar 2027 (last two cycles: posted Sep 27, 2024 and Nov 3, 2025; closed Mar 3, 2025 and Jan 30, 2026). Still open for summer 2027: COO Operations, Quantitative Technology Services (Jersey City, Raleigh) and Global Markets Quantitative Trading Summer An</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>RBC Capital Markets</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -14983,17 +14987,17 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D260" s="6" t="inlineStr">
         <is>
-          <t>QTS (Quantitative Technology &amp; Strategy)  (1 of 6 tracks)</t>
+          <t>Data Science &amp; Bioinformatics; Technology/IT (AI/ML); Supply Chain &amp; Engineering  (3 of 12 tracks)</t>
         </is>
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>rbc.wd3.myworkdayjobs.com/RBCEARLYTALENT1</t>
+          <t>careers.regeneron.com/en/career-pathways/early-careers/</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr">
@@ -15003,34 +15007,34 @@
       </c>
       <c r="G260" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a HireVue video assessment (four to five questions, zero retakes, 15 to 25% pass rate), then a 60-minute first-round phone or video interview mixing behavioral and technical questions, and finally a Superday with VPs, Directors, and MDs. Candidates report offers within one to two</t>
+          <t>The standard process is: ATS resume screen, recruiter phone screen (20 to 30 minutes), HireVue on-demand video interview (AI-scored on transcript alignment), then a live hiring manager interview via MS Teams (45 to 60 minutes). Select roles add an in-person final round at Tarrytown with 3 to 5 inter</t>
         </is>
       </c>
       <c r="H260" s="6" t="inlineStr">
         <is>
-          <t>Strong track record: 273 H-1B filings with 100% approval rate. CPT supported for F-1 students</t>
+          <t>No. Regeneron does not directly sponsor visas for interns. International students on F-1 visas must secure CPT (Curricular Practical Training) authorization through their university before the internship starts. You'll n</t>
         </is>
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>Yes. RBC reviews applications on a rolling basis and fills interview slots continuously. Apply in the first one to two weeks for the best odds</t>
+          <t>Yes. Positions filled as qualified candidates are identified within the window</t>
         </is>
       </c>
       <c r="J260" s="6" t="inlineStr">
         <is>
-          <t>$2,115/week (~$110,000 annualized) for U.S. IB/CM roles. $7,000 housing stipend, dinner stipend after 7 PM, car service after 9 PM, relocation up to $2,000 dome</t>
+          <t>$17.90–$50.90/hr by degree level + $1,400/mo housing stipend + free meals and gym</t>
         </is>
       </c>
       <c r="K260" s="6" t="inlineStr">
         <is>
-          <t>Summer 2028 IB Summer Analyst: NOT YET OPEN. Applications for summer 2028 expected to open around Oct to Nov 2026 and close around late Jan to early Mar 2027 (last two cycles: posted Sep 27, 2024 and Nov 3, 2025; closed Mar 3, 2025 and Jan 30, 2026). Still open for summer 2027: COO Operations, Quantitative Technology Services (Jersey City, Raleigh) and Global Markets Quantitative Trading Summer An</t>
+          <t>For summer 2027: 2027 Co-op (22 reqs) and MBA BuiLD postings open since October 1 to 2, 2026. Standard 10-week summer intern postings not yet live as of October 6, 2026; expected October to November 2026, later than last cycle</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Relativity Space</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -15045,12 +15049,12 @@
       </c>
       <c r="D261" s="6" t="inlineStr">
         <is>
-          <t>Data Science &amp; Bioinformatics; Technology/IT (AI/ML); Supply Chain &amp; Engineering  (3 of 12 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Test Engineering; Robotics Software  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>careers.regeneron.com/en/career-pathways/early-careers/</t>
+          <t>relativityspace.com/internships</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr">
@@ -15060,34 +15064,34 @@
       </c>
       <c r="G261" s="6" t="inlineStr">
         <is>
-          <t>The standard process is: ATS resume screen, recruiter phone screen (20 to 30 minutes), HireVue on-demand video interview (AI-scored on transcript alignment), then a live hiring manager interview via MS Teams (45 to 60 minutes). Select roles add an in-person final round at Tarrytown with 3 to 5 inter</t>
+          <t>The standard process has 2–3 stages: a 30-minute recruiter phone screen covering background, projects, and career goals; a 45–60-minute technical interview specific to your role (coding for SWE, materials analysis for manufacturing, thermodynamics for propulsion); and a behavioral interview assessin</t>
         </is>
       </c>
       <c r="H261" s="6" t="inlineStr">
         <is>
-          <t>No. Regeneron does not directly sponsor visas for interns. International students on F-1 visas must secure CPT (Curricular Practical Training) authorization through their university before the internship starts. You'll n</t>
+          <t>Most engineering roles require U.S. Person status under ITAR regulations (U.S. citizen, permanent resident, refugee, or asylee). F-1 visa holders are generally ineligible for hardware roles involving flight software, pro</t>
         </is>
       </c>
       <c r="I261" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified within the window</t>
+          <t>Yes. Positions filled as qualified candidates are identified; earlier applications get more attention</t>
         </is>
       </c>
       <c r="J261" s="6" t="inlineStr">
         <is>
-          <t>$17.90–$50.90/hr by degree level + $1,400/mo housing stipend + free meals and gym</t>
+          <t>Posted ranges for current intern roles: $39 to $44/hr for software and data science, $34 to $42/hr for engineering, $27 to $30/hr for design and policy roles; i</t>
         </is>
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>For summer 2027: 2027 Co-op (22 reqs) and MBA BuiLD postings open since October 1 to 2, 2026. Standard 10-week summer intern postings not yet live as of October 6, 2026; expected October to November 2026, later than last cycle</t>
+          <t>Open now: 30 US intern postings live as of October 6, 2026 (first batch listed July 10, 2026, more added through October 5). Rolling review, no published deadline; peak interviews expected October 2026 to February 2027</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>Relativity Space</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -15102,12 +15106,12 @@
       </c>
       <c r="D262" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Test Engineering; Robotics Software  (4 of 6 tracks)</t>
+          <t>SWE Intern — Workers AI / AI Platform; SWE Intern — Cloudflare Workers; ML Engineering Intern; SWE Intern — Infrastructure / Systems</t>
         </is>
       </c>
       <c r="E262" s="7" t="inlineStr">
         <is>
-          <t>relativityspace.com/internships</t>
+          <t>cloudflare.com/careers/early-talent/</t>
         </is>
       </c>
       <c r="F262" s="7" t="inlineStr">
@@ -15117,34 +15121,34 @@
       </c>
       <c r="G262" s="6" t="inlineStr">
         <is>
-          <t>The standard process has 2–3 stages: a 30-minute recruiter phone screen covering background, projects, and career goals; a 45–60-minute technical interview specific to your role (coding for SWE, materials analysis for manufacturing, thermodynamics for propulsion); and a behavioral interview assessin</t>
+          <t xml:space="preserve">All applications go through Cloudflare's 1111 Interns program. The funnel spans 3 to 4 weeks from application to decision: 1. Apply on cloudflare.com/careers/early-talent . Search for internship roles mentioning Workers AI, AI Platform, or Machine Learning. Postings typically go live around October </t>
         </is>
       </c>
       <c r="H262" s="6" t="inlineStr">
         <is>
-          <t>Most engineering roles require U.S. Person status under ITAR regulations (U.S. citizen, permanent resident, refugee, or asylee). F-1 visa holders are generally ineligible for hardware roles involving flight software, pro</t>
+          <t>F-1 CPT supported for US intern positions. International hub offices in London, Lisbon, and Bengaluru available for non-US students</t>
         </is>
       </c>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified; earlier applications get more attention</t>
+          <t>Yes. Cloudflare reviews applications on a rolling basis. Interviews run November through February with offers December through March. Apply as early as possible</t>
         </is>
       </c>
       <c r="J262" s="6" t="inlineStr">
         <is>
-          <t>Posted ranges for current intern roles: $39 to $44/hr for software and data science, $34 to $42/hr for engineering, $27 to $30/hr for design and policy roles; i</t>
+          <t>$45 to $53 per hour (~$7,800 to $9,200/month) for US engineering interns. $1,000/month housing stipend plus relocation support. No Replicate-specific data exist</t>
         </is>
       </c>
       <c r="K262" s="6" t="inlineStr">
         <is>
-          <t>Open now: 30 US intern postings live as of October 6, 2026 (first batch listed July 10, 2026, more added through October 5). Rolling review, no published deadline; peak interviews expected October 2026 to February 2027</t>
+          <t>Expected mid-October 2026 for summer 2027 roles. Rolling review through February 2027. Projected from the 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -15154,17 +15158,17 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D263" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern — Workers AI / AI Platform; SWE Intern — Cloudflare Workers; ML Engineering Intern; SWE Intern — Infrastructure / Systems</t>
+          <t>Software Engineering Intern; Mechanical Engineering Intern; Manufacturing Engineering Intern; AI, ML &amp; Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>cloudflare.com/careers/early-talent/</t>
+          <t>careers.rivian.com/students</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
@@ -15174,34 +15178,34 @@
       </c>
       <c r="G263" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">All applications go through Cloudflare's 1111 Interns program. The funnel spans 3 to 4 weeks from application to decision: 1. Apply on cloudflare.com/careers/early-talent . Search for internship roles mentioning Workers AI, AI Platform, or Machine Learning. Postings typically go live around October </t>
+          <t>You apply online, complete a 30- to 45-minute recruiter phone screen, then face 1 to 2 technical interview rounds (coding on HackerRank for SWE or engineering fundamentals for hardware) plus a behavioral round and a hiring-manager chat. Glassdoor rates difficulty at 2.8 out of 5.</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for US intern positions. International hub offices in London, Lisbon, and Bengaluru available for non-US students</t>
+          <t>Valid work authorization required. F-1 CPT supported; international students reviewed case-by-case. Some roles carry export-control restrictions</t>
         </is>
       </c>
       <c r="I263" s="6" t="inlineStr">
         <is>
-          <t>Yes. Cloudflare reviews applications on a rolling basis. Interviews run November through February with offers December through March. Apply as early as possible</t>
+          <t>Yes. Rivian reviews applications and schedules interviews on a rolling basis from October through March. Early applicants face the most open seats</t>
         </is>
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
-          <t>$45 to $53 per hour (~$7,800 to $9,200/month) for US engineering interns. $1,000/month housing stipend plus relocation support. No Replicate-specific data exist</t>
+          <t>$25 to $51 per hour depending on role and location. Palo Alto SWE interns report $51/hr ($8,840/mo). Housing stipend of $2,000 to $2,500/mo plus relocation assi</t>
         </is>
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>Expected mid-October 2026 for summer 2027 roles. Rolling review through February 2027. Projected from the 2026 cycle</t>
+          <t>Summer 2027 is starting to post: the first role (Finance Analyst intern, Palo Alto) went live 2 October 2026, and most summer 2027 roles are expected later this fall (October to November 2026, projected from prior-cycle timing). Interviews run through March 2027</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rockstar Games</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -15216,12 +15220,12 @@
       </c>
       <c r="D264" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Mechanical Engineering Intern; Manufacturing Engineering Intern; AI, ML &amp; Data Science Intern  (4 of 6 tracks)</t>
+          <t>Data Analytics / Data Science; Hardware Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>careers.rivian.com/students</t>
+          <t>job-boards.greenhouse.io/rsgur</t>
         </is>
       </c>
       <c r="F264" s="7" t="inlineStr">
@@ -15231,34 +15235,34 @@
       </c>
       <c r="G264" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a 30- to 45-minute recruiter phone screen, then face 1 to 2 technical interview rounds (coding on HackerRank for SWE or engineering fundamentals for hardware) plus a behavioral round and a hiring-manager chat. Glassdoor rates difficulty at 2.8 out of 5.</t>
+          <t>The process varies by role but typically spans 3 to 5 rounds over approximately 60 days. For Data Science interns, expect an initial 30-minute Zoom screening, a multi-day take-home data analysis project, follow-up technical discussions, and a final 60-minute panel interview. Game Design roles includ</t>
         </is>
       </c>
       <c r="H264" s="6" t="inlineStr">
         <is>
-          <t>Valid work authorization required. F-1 CPT supported; international students reviewed case-by-case. Some roles carry export-control restrictions</t>
+          <t>US-based listings require eligibility to work in the US, which typically means US citizens, permanent residents, or students with valid work authorization such as CPT or OPT for F-1 visa holders. Rockstar doesn't confirm</t>
         </is>
       </c>
       <c r="I264" s="6" t="inlineStr">
         <is>
-          <t>Yes. Rivian reviews applications and schedules interviews on a rolling basis from October through March. Early applicants face the most open seats</t>
+          <t>Not confirmed. Some roles close within weeks of posting; others stay open until spring. Early application is strongly recommended</t>
         </is>
       </c>
       <c r="J264" s="6" t="inlineStr">
         <is>
-          <t>$25 to $51 per hour depending on role and location. Palo Alto SWE interns report $51/hr ($8,840/mo). Housing stipend of $2,000 to $2,500/mo plus relocation assi</t>
+          <t>$34/hr confirmed for NYC Data Science (Greenhouse listing); Glassdoor range $26–$47/hr across roles</t>
         </is>
       </c>
       <c r="K264" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 is starting to post: the first role (Finance Analyst intern, Palo Alto) went live 2 October 2026, and most summer 2027 roles are expected later this fall (October to November 2026, projected from prior-cycle timing). Interviews run through March 2027</t>
+          <t>Expected October–November 2026 for summer 2027 (based on documented Summer 2026 cycle; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -15268,17 +15272,17 @@
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026 – June 2027</t>
         </is>
       </c>
       <c r="D265" s="6" t="inlineStr">
         <is>
-          <t>Data Analytics / Data Science; Hardware Engineering  (2 of 6 tracks)</t>
+          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical / Multi-Disciplined Engineer Intern; Systems Engineering Intern / Co-op; Digital Technology / Cyber, Finance &amp; Supply Chain</t>
         </is>
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/rsgur</t>
+          <t>careers.rtx.com/global/en/campus</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr">
@@ -15288,34 +15292,34 @@
       </c>
       <c r="G265" s="6" t="inlineStr">
         <is>
-          <t>The process varies by role but typically spans 3 to 5 rounds over approximately 60 days. For Data Science interns, expect an initial 30-minute Zoom screening, a multi-day take-home data analysis project, follow-up technical discussions, and a final 60-minute panel interview. Game Design roles includ</t>
+          <t>A recruiter screen, often a HireVue recorded video, then a behavioral hiring-manager or Zoom interview (sometimes a panel or a single director), a possible in-person step, and an offer. It is behavioral-heavy (conflict, leadership, teamwork, datasets) with no documented timed coding assessment. Turn</t>
         </is>
       </c>
       <c r="H265" s="6" t="inlineStr">
         <is>
-          <t>US-based listings require eligibility to work in the US, which typically means US citizens, permanent residents, or students with valid work authorization such as CPT or OPT for F-1 visa holders. Rockstar doesn't confirm</t>
+          <t>No. US citizenship is required for nearly all US roles (ITAR-controlled defense work); software reqs are tagged "No H1B Sponsorship." A minority of roles require an active SECRET clearance on day one</t>
         </is>
       </c>
       <c r="I265" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Some roles close within weeks of posting; others stay open until spring. Early application is strongly recommended</t>
+          <t>Yes, confirmed. Each req states the window closes "approximately 40 days from the date the notice was posted," subject to candidate flow and business need. In p</t>
         </is>
       </c>
       <c r="J265" s="6" t="inlineStr">
         <is>
-          <t>$34/hr confirmed for NYC Data Science (Greenhouse listing); Glassdoor range $26–$47/hr across roles</t>
+          <t>No single official hourly figure; Levels.fyi (community) shows roughly $27–43/hr by business unit, role, location, and class standing (RTX SWE interns average ~</t>
         </is>
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>Expected October–November 2026 for summer 2027 (based on documented Summer 2026 cycle; not yet posted)</t>
+          <t>OPEN NOW, short windows. 240 US intern and co-op reqs live on October 2, 2026 (195 titled 2027, 112 titled Summer 2027), about 150 of them posted September 28 to October 2 in a second wave after the first one of September 2 to 11; half of a 30-req September sample carried a Workday end date only 5 to 6 days after posting, and the new wave repeats that (end dates 4 to 33 days out in the reqs we ope</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -15325,17 +15329,17 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – June 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D266" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical / Multi-Disciplined Engineer Intern; Systems Engineering Intern / Co-op; Digital Technology / Cyber, Finance &amp; Supply Chain</t>
+          <t>ML Research Intern; Software Engineering Intern (inferred); Applied ML / Computer Vision Intern (inferred)  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>careers.rtx.com/global/en/campus</t>
+          <t>runway.com/careers</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
@@ -15345,34 +15349,34 @@
       </c>
       <c r="G266" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, often a HireVue recorded video, then a behavioral hiring-manager or Zoom interview (sometimes a panel or a single director), a possible in-person step, and an offer. It is behavioral-heavy (conflict, leadership, teamwork, datasets) with no documented timed coding assessment. Turn</t>
+          <t>The process typically takes 2 to 4 weeks (average 20 days on Glassdoor) and includes a recruiter screen (30 minutes), technical assessment (45 to 60 minutes of coding in Python and TypeScript), virtual onsite (pair programming, code review, systems design), and leadership meetings with senior leader</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr">
         <is>
-          <t>No. US citizenship is required for nearly all US roles (ITAR-controlled defense work); software reqs are tagged "No H1B Sponsorship." A minority of roles require an active SECRET clearance on day one</t>
+          <t>H-1B sponsorship confirmed for full-time roles. CPT/OPT likely supported for international students (standard for AI companies at this tier). No explicit visa restriction stated</t>
         </is>
       </c>
       <c r="I266" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Each req states the window closes "approximately 40 days from the date the notice was posted," subject to candidate flow and business need. In p</t>
+          <t>Likely yes. No fixed deadline exists. Glassdoor data (80 interviews) shows an average of 20 days from application to decision. Apply as soon as a posting appear</t>
         </is>
       </c>
       <c r="J266" s="6" t="inlineStr">
         <is>
-          <t>No single official hourly figure; Levels.fyi (community) shows roughly $27–43/hr by business unit, role, location, and class standing (RTX SWE interns average ~</t>
+          <t>Indeed estimates approximately $4,015/month ($3,734 to $4,497 range), though this is based on limited data. Full-time research roles pay $320K+ median, suggesti</t>
         </is>
       </c>
       <c r="K266" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW, short windows. 240 US intern and co-op reqs live on October 2, 2026 (195 titled 2027, 112 titled Summer 2027), about 150 of them posted September 28 to October 2 in a second wave after the first one of September 2 to 11; half of a 30-req September sample carried a Workday end date only 5 to 6 days after posting, and the new wave repeats that (end dates 4 to 33 days out in the reqs we ope</t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed public deadline; roles fill on a rolling basis. Projected from general AI startup hiring patterns</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -15382,17 +15386,17 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026 – May 2027</t>
         </is>
       </c>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; Software Engineering Intern (inferred); Applied ML / Computer Vision Intern (inferred)  (3 of 4 tracks)</t>
+          <t>SRA AI/ML Research Intern; SRA Software Engineering Intern; SAS Engineering Summer Intern; SDS Cloud/AI Intern  (4 of 7 tracks)</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>runway.com/careers</t>
+          <t>samsung.com/us/careers/internships/</t>
         </is>
       </c>
       <c r="F267" s="7" t="inlineStr">
@@ -15402,34 +15406,34 @@
       </c>
       <c r="G267" s="6" t="inlineStr">
         <is>
-          <t>The process typically takes 2 to 4 weeks (average 20 days on Glassdoor) and includes a recruiter screen (30 minutes), technical assessment (45 to 60 minutes of coding in Python and TypeScript), virtual onsite (pair programming, code review, systems design), and leadership meetings with senior leader</t>
+          <t>There is no standardized coding assessment across Samsung. Samsung Research America interviews focus on your research publications, design choices, and a project proposal with a potential mentor. Samsung Electronics America uses a short skills test plus two interviews covering behavioral and technic</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsorship confirmed for full-time roles. CPT/OPT likely supported for international students (standard for AI companies at this tier). No explicit visa restriction stated</t>
+          <t>SRA JDs state applicants need legal US work authorization or visa sponsorship eligibility. Samsung has a track record of H-1B sponsorship for full-time roles; F-1 CPT is the typical intern path</t>
         </is>
       </c>
       <c r="I267" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No fixed deadline exists. Glassdoor data (80 interviews) shows an average of 20 days from application to decision. Apply as soon as a posting appear</t>
+          <t xml:space="preserve">Semi-rolling. Samsung encourages checking year-round, but most positions fill during defined windows. SAS had a firm deadline (~late March) in the prior cycle; </t>
         </is>
       </c>
       <c r="J267" s="6" t="inlineStr">
         <is>
-          <t>Indeed estimates approximately $4,015/month ($3,734 to $4,497 range), though this is based on limited data. Full-time research roles pay $320K+ median, suggesti</t>
+          <t>$27 to $63/hr depending on division and role. SWE ~$62/hr (Levels.fyi); SRA research $48 to $63/hr (official JD); SAS engineering ~$30/hr. Housing stipend and r</t>
         </is>
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed public deadline; roles fill on a rolling basis. Projected from general AI startup hiring patterns</t>
+          <t>Partly open: on October 11, 2026, Samsung Austin Semiconductor (SAS) listed one 2027 Summer Internship posting, posted August 4, 2026, with a printed end date of May 31, 2027. Samsung Research America (SRA) and Samsung Electronics America (SEA) listed no intern roles that day; the SRA internship board carried only a general posting for sharing a resume. SRA research reqs ~Oct 2026 and SEA summer p</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -15439,17 +15443,17 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – May 2027</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D268" s="6" t="inlineStr">
         <is>
-          <t>SRA AI/ML Research Intern; SRA Software Engineering Intern; SAS Engineering Summer Intern; SDS Cloud/AI Intern  (4 of 7 tracks)</t>
+          <t>Digital / Technology; Data Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>samsung.com/us/careers/internships/</t>
+          <t>join.sephora.com/careers?query=intern</t>
         </is>
       </c>
       <c r="F268" s="7" t="inlineStr">
@@ -15459,34 +15463,34 @@
       </c>
       <c r="G268" s="6" t="inlineStr">
         <is>
-          <t>There is no standardized coding assessment across Samsung. Samsung Research America interviews focus on your research publications, design choices, and a project proposal with a potential mentor. Samsung Electronics America uses a short skills test plus two interviews covering behavioral and technic</t>
+          <t>Typically 3 to 4 stages over roughly 22 days: an on-demand video interview with behavioral and beauty-passion questions, a recruiter phone screen, a hiring manager interview, and for competitive tracks a final panel or Superday with senior leaders. Some roles include a 60 to 90 minute online assessm</t>
         </is>
       </c>
       <c r="H268" s="6" t="inlineStr">
         <is>
-          <t>SRA JDs state applicants need legal US work authorization or visa sponsorship eligibility. Samsung has a track record of H-1B sponsorship for full-time roles; F-1 CPT is the typical intern path</t>
+          <t>No. Sephora does not sponsor H-1B visas for internships. International students must have independent work authorization through CPT or OPT. You must be authorized to work in the U.S. without employer sponsorship.</t>
         </is>
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi-rolling. Samsung encourages checking year-round, but most positions fill during defined windows. SAS had a firm deadline (~late March) in the prior cycle; </t>
+          <t>Yes. Applications reviewed on a rolling basis; last cycle gave priority consideration by mid-October</t>
         </is>
       </c>
       <c r="J268" s="6" t="inlineStr">
         <is>
-          <t>$27 to $63/hr depending on division and role. SWE ~$62/hr (Levels.fyi); SRA research $48 to $63/hr (official JD); SAS engineering ~$30/hr. Housing stipend and r</t>
+          <t>$22–$25/hr depending on role (~$9,000 total at top rate)</t>
         </is>
       </c>
       <c r="K268" s="6" t="inlineStr">
         <is>
-          <t>Partly open: on October 11, 2026, Samsung Austin Semiconductor (SAS) listed one 2027 Summer Internship posting, posted August 4, 2026, with a printed end date of May 31, 2027. Samsung Research America (SRA) and Samsung Electronics America (SEA) listed no intern roles that day; the SRA internship board carried only a general posting for sharing a resume. SRA research reqs ~Oct 2026 and SEA summer p</t>
+          <t>Not posted yet. No US summer 2027 internships on Sephora's careers sites on October 6, 2026, later than last cycle's early-September opening. Expected from October 2026 into early 2027; last cycle closed by mid-November</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -15496,17 +15500,17 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>Digital / Technology; Data Analytics  (2 of 6 tracks)</t>
+          <t>Aerospace Engineer Intern; Mechanical Engineer Intern; Propulsion Engineer Intern; Systems Engineer Intern; Electrical Engineer Intern; Software Engineer Intern</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
         <is>
-          <t>join.sephora.com/careers?query=intern</t>
+          <t>sierraspace.com/careers/internship/</t>
         </is>
       </c>
       <c r="F269" s="7" t="inlineStr">
@@ -15516,34 +15520,34 @@
       </c>
       <c r="G269" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 stages over roughly 22 days: an on-demand video interview with behavioral and beauty-passion questions, a recruiter phone screen, a hiring manager interview, and for competitive tracks a final panel or Superday with senior leaders. Some roles include a 60 to 90 minute online assessm</t>
+          <t>Sierra Space does not publish a formal, round-by-round intern interview structure, so the steps below combine the official application flow with community-reported interview signal (Reddit r/aerospace): treat the interview specifics as directional, not official: 1. Monitor the internship page (summe</t>
         </is>
       </c>
       <c r="H269" s="6" t="inlineStr">
         <is>
-          <t>No. Sephora does not sponsor H-1B visas for internships. International students must have independent work authorization through CPT or OPT. You must be authorized to work in the U.S. without employer sponsorship.</t>
+          <t>Not available. Because of ITAR / export-control work, F-1 visa sponsorship is not offered for internships, and non-US-persons are effectively screened out. Security-clearance eligibility is also required</t>
         </is>
       </c>
       <c r="I269" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; last cycle gave priority consideration by mid-October</t>
+          <t xml:space="preserve">Partially. Individual postings state the deadline stays open "until a qualified pool of candidates is identified," so roles close once filled. Apply as soon as </t>
         </is>
       </c>
       <c r="J269" s="6" t="inlineStr">
         <is>
-          <t>$22–$25/hr depending on role (~$9,000 total at top rate)</t>
+          <t>$31.00/hour on the live 2027 Systems Engineer Intern posting ($30.00/hour on the 2026 Colorado Engineering Intern posting). Community sources vary: Glassdoor ~$</t>
         </is>
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>Not posted yet. No US summer 2027 internships on Sephora's careers sites on October 6, 2026, later than last cycle's early-September opening. Expected from October 2026 into early 2027; last cycle closed by mid-November</t>
+          <t>Open for summer 2027: the first req (2027 Systems Engineer Intern, Colorado) posted October 1, 2026, about a month later than the September pattern. More function reqs expected through fall 2026, with a deadline expected around December 2026 (not confirmed)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -15558,12 +15562,12 @@
       </c>
       <c r="D270" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineer Intern; Mechanical Engineer Intern; Propulsion Engineer Intern; Systems Engineer Intern; Electrical Engineer Intern; Software Engineer Intern</t>
+          <t>Software Engineer Intern; Software Engineer Intern (AI/ML); Data Engineer Intern; Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E270" s="7" t="inlineStr">
         <is>
-          <t>sierraspace.com/careers/internship/</t>
+          <t>careers.snowflake.com/us/en/university</t>
         </is>
       </c>
       <c r="F270" s="7" t="inlineStr">
@@ -15573,34 +15577,34 @@
       </c>
       <c r="G270" s="6" t="inlineStr">
         <is>
-          <t>Sierra Space does not publish a formal, round-by-round intern interview structure, so the steps below combine the official application flow with community-reported interview signal (Reddit r/aerospace): treat the interview specifics as directional, not official: 1. Monitor the internship page (summe</t>
+          <t>You apply, complete a 30-minute recruiter phone screen, take a 90- to 120-minute HackerRank OA with 2 to 3 medium-to-hard problems, then two technical coding interviews plus a behavioral round. Offers come within 3 to 5 business days of the final interview. Total timeline: 6 to 10 weeks.</t>
         </is>
       </c>
       <c r="H270" s="6" t="inlineStr">
         <is>
-          <t>Not available. Because of ITAR / export-control work, F-1 visa sponsorship is not offered for internships, and non-US-persons are effectively screened out. Security-clearance eligibility is also required</t>
+          <t>F-1 CPT supported for internships, OPT for new graduates. STEM-designated employer (24-month OPT extension eligible). No J-1 sponsorship</t>
         </is>
       </c>
       <c r="I270" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Individual postings state the deadline stays open "until a qualified pool of candidates is identified," so roles close once filled. Apply as soon as </t>
+          <t>Yes. Snowflake reviews applications on a rolling basis and extends offers as seats fill. Apply in the first two weeks of a posting for the best response rates</t>
         </is>
       </c>
       <c r="J270" s="6" t="inlineStr">
         <is>
-          <t>$31.00/hour on the live 2027 Systems Engineer Intern posting ($30.00/hour on the 2026 Colorado Engineering Intern posting). Community sources vary: Glassdoor ~$</t>
+          <t>$55 per hour ($9,533 per month) for SWE interns per Levels.fyi. Housing stipend of $2,000 to $2,500 per month. Some offers include a relocation bonus of $500 to</t>
         </is>
       </c>
       <c r="K270" s="6" t="inlineStr">
         <is>
-          <t>Open for summer 2027: the first req (2027 Systems Engineer Intern, Colorado) posted October 1, 2026, about a month later than the September pattern. More function reqs expected through fall 2026, with a deadline expected around December 2026 (not confirmed)</t>
+          <t>Not open yet: no US summer 2027 intern postings were live on 1 October 2026. Prior cycles opened in early September, so this cycle is running late. Once postings appear, expect priority screening within the first two to three weeks (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -15615,12 +15619,12 @@
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Software Engineer Intern (AI/ML); Data Engineer Intern; Data Science Intern  (4 of 6 tracks)</t>
+          <t>Technology (SWE / Data Engineering); Technology Analyst  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr">
         <is>
-          <t>careers.snowflake.com/us/en/university</t>
+          <t>careers.southwestair.com/us/en/campus-reach</t>
         </is>
       </c>
       <c r="F271" s="7" t="inlineStr">
@@ -15630,34 +15634,34 @@
       </c>
       <c r="G271" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a 30-minute recruiter phone screen, take a 90- to 120-minute HackerRank OA with 2 to 3 medium-to-hard problems, then two technical coding interviews plus a behavioral round. Offers come within 3 to 5 business days of the final interview. Total timeline: 6 to 10 weeks.</t>
+          <t>It is an on-demand video interview with pre-set behavioral prompts and timed responses. The focus is entirely on culture fit, not technical skills. Southwest assesses alignment with their three core values: Warrior Spirit (resilience), Servant's Heart (service), and Fun-LUVing Attitude (positivity).</t>
         </is>
       </c>
       <c r="H271" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for internships, OPT for new graduates. STEM-designated employer (24-month OPT extension eligible). No J-1 sponsorship</t>
+          <t>Effectively no. Southwest requires unrestricted US work authorization without sponsorship. International students on F-1 visas using CPT or OPT are generally ineligible unless they hold separate permanent work authorizat</t>
         </is>
       </c>
       <c r="I271" s="6" t="inlineStr">
         <is>
-          <t>Yes. Snowflake reviews applications on a rolling basis and extends offers as seats fill. Apply in the first two weeks of a posting for the best response rates</t>
+          <t>Semi-rolling inside each fixed window. Southwest reviews on a rolling basis and may close early once the candidate pool is full</t>
         </is>
       </c>
       <c r="J271" s="6" t="inlineStr">
         <is>
-          <t>$55 per hour ($9,533 per month) for SWE interns per Levels.fyi. Housing stipend of $2,000 to $2,500 per month. Some offers include a relocation bonus of $500 to</t>
+          <t>$20–$30/hr + up to $2,000 housing stipend + free unlimited standby flights on all Southwest routes</t>
         </is>
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>Not open yet: no US summer 2027 intern postings were live on 1 October 2026. Prior cycles opened in early September, so this cycle is running late. Once postings appear, expect priority screening within the first two to three weeks (projected from prior cycle)</t>
+          <t>Open now for summer 2027: about 32 internships across all departments posted October 1, 2026. No closing date is published; last cycle the Tech and Revenue Management window ran 8 days (October 7 to 15, 2025), so expect these to close within days</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -15672,12 +15676,12 @@
       </c>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE / Data Engineering); Technology Analyst  (2 of 6 tracks)</t>
+          <t>Engineering Intern; Software Engineering Intern; Graduate Engineer Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E272" s="7" t="inlineStr">
         <is>
-          <t>careers.southwestair.com/us/en/campus-reach</t>
+          <t>spacex.com/careers/jobs/?keyword=internship</t>
         </is>
       </c>
       <c r="F272" s="7" t="inlineStr">
@@ -15687,34 +15691,34 @@
       </c>
       <c r="G272" s="6" t="inlineStr">
         <is>
-          <t>It is an on-demand video interview with pre-set behavioral prompts and timed responses. The focus is entirely on culture fit, not technical skills. Southwest assesses alignment with their three core values: Warrior Spirit (resilience), Servant's Heart (service), and Fun-LUVing Attitude (positivity).</t>
+          <t>SpaceX's interview funnel is technically demanding and project-depth-driven. The total process runs 4 to 12 weeks from application to offer, with Glassdoor reporting an average of 17 days for intern roles: 1. Apply at spacex.com/careers within 48 to 72 hours of a posting going live. Submit your resu</t>
         </is>
       </c>
       <c r="H272" s="6" t="inlineStr">
         <is>
-          <t>Effectively no. Southwest requires unrestricted US work authorization without sponsorship. International students on F-1 visas using CPT or OPT are generally ineligible unless they hold separate permanent work authorizat</t>
+          <t>No. SpaceX requires U.S. Person status under ITAR regulations. F-1 visa holders are ineligible regardless of CPT or OPT work authorization. H-1B holders are generally ineligible. SpaceX does not sponsor work visas for in</t>
         </is>
       </c>
       <c r="I272" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling inside each fixed window. Southwest reviews on a rolling basis and may close early once the candidate pool is full</t>
+          <t>Yes. No fixed cohort deadlines. Apply within 48–72 hours of a posting going live for best odds</t>
         </is>
       </c>
       <c r="J272" s="6" t="inlineStr">
         <is>
-          <t>$20–$30/hr + up to $2,000 housing stipend + free unlimited standby flights on all Southwest routes</t>
+          <t>$24.50–$40/hr by posting and academic level, as printed in the Summer 2027 postings listed on October 11, 2026: Engineering and Civil Engineering $28.00 to $30.</t>
         </is>
       </c>
       <c r="K272" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: about 32 internships across all departments posted October 1, 2026. No closing date is published; last cycle the Tech and Revenue Management window ran 8 days (October 7 to 15, 2025), so expect these to close within days</t>
+          <t>Open now for summer 2027: six Summer 2027 internship postings were listed on SpaceX's job board on October 11, 2026, each first published August 3, 2026. No closing date is printed; rolling admissions, positions fill as qualified candidates found</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -15729,12 +15733,12 @@
       </c>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern; Software Engineering Intern; Graduate Engineer Intern  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern (Backend/Full-Stack); C++ Software Engineer Intern; Solutions Engineer Intern; Security Engineering Intern; Data Science Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E273" s="7" t="inlineStr">
         <is>
-          <t>spacex.com/careers/jobs/?keyword=internship</t>
+          <t>careers.cisco.com/global/en/splunk</t>
         </is>
       </c>
       <c r="F273" s="7" t="inlineStr">
@@ -15744,34 +15748,34 @@
       </c>
       <c r="G273" s="6" t="inlineStr">
         <is>
-          <t>SpaceX's interview funnel is technically demanding and project-depth-driven. The total process runs 4 to 12 weeks from application to offer, with Glassdoor reporting an average of 17 days for intern roles: 1. Apply at spacex.com/careers within 48 to 72 hours of a posting going live. Submit your resu</t>
+          <t>A recruiter phone screen (15 to 30 minutes), then a Karat technical assessment (15-minute MCQ quiz plus 60-minute live coding), then a hiring manager behavioral interview (45 to 60 minutes). Some roles add a virtual onsite with 2 to 4 additional rounds. Total timeline is 3 to 5 weeks from first cont</t>
         </is>
       </c>
       <c r="H273" s="6" t="inlineStr">
         <is>
-          <t>No. SpaceX requires U.S. Person status under ITAR regulations. F-1 visa holders are ineligible regardless of CPT or OPT work authorization. H-1B holders are generally ineligible. SpaceX does not sponsor work visas for in</t>
+          <t>Roles available in US, Canada, UK, Germany, Poland, Australia, Japan, Singapore. US roles likely require valid work authorization (CPT for F-1 students)</t>
         </is>
       </c>
       <c r="I273" s="6" t="inlineStr">
         <is>
-          <t>Yes. No fixed cohort deadlines. Apply within 48–72 hours of a posting going live for best odds</t>
+          <t>Yes, confirmed. In prior cycles Splunk posted roles in early September and filled them progressively through February. The US posting listed on October 11, 2026</t>
         </is>
       </c>
       <c r="J273" s="6" t="inlineStr">
         <is>
-          <t>$24.50–$40/hr by posting and academic level, as printed in the Summer 2027 postings listed on October 11, 2026: Engineering and Civil Engineering $28.00 to $30.</t>
+          <t>SWE intern $42 to $60/hr ($7,280 to $10,400/mo) depending on location. Housing stipends $2,000 to $6,000 for select offices</t>
         </is>
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: six Summer 2027 internship postings were listed on SpaceX's job board on October 11, 2026, each first published August 3, 2026. No closing date is printed; rolling admissions, positions fill as qualified candidates found</t>
+          <t>Partly open: on October 11, 2026, one US Splunk intern posting was accepting applications on careers.cisco.com, Splunk Solutions Engineer (Intern) - United States, posted October 7, 2026. It names no summer and no closing date, and says applications are accepted until further notice. No Splunk-branded software engineering intern posting was listed that day. The earlier estimate of an early Septemb</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -15781,17 +15785,17 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Backend/Full-Stack); C++ Software Engineer Intern; Solutions Engineer Intern; Security Engineering Intern; Data Science Intern  (5 of 6 tracks)</t>
+          <t>Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E274" s="7" t="inlineStr">
         <is>
-          <t>careers.cisco.com/global/en/splunk</t>
+          <t>apply.starbucks.com/careers?query=intern</t>
         </is>
       </c>
       <c r="F274" s="7" t="inlineStr">
@@ -15801,34 +15805,34 @@
       </c>
       <c r="G274" s="6" t="inlineStr">
         <is>
-          <t>A recruiter phone screen (15 to 30 minutes), then a Karat technical assessment (15-minute MCQ quiz plus 60-minute live coding), then a hiring manager behavioral interview (45 to 60 minutes). Some roles add a virtual onsite with 2 to 4 additional rounds. Total timeline is 3 to 5 weeks from first cont</t>
+          <t>You apply, complete a recruiter phone screen (15 to 20 minutes), then 2 to 3 behavioral interview rounds (45 to 60 minutes each) using the STAR method. Technology roles add a coding assessment. The total process spans 6 to 10 weeks. Glassdoor rates difficulty at 2.2 out of 5.</t>
         </is>
       </c>
       <c r="H274" s="6" t="inlineStr">
         <is>
-          <t>Roles available in US, Canada, UK, Germany, Poland, Australia, Japan, Singapore. US roles likely require valid work authorization (CPT for F-1 students)</t>
+          <t>Limited. CPT may be supported for F-1 students on a case-by-case basis, but most postings state sponsorship is not provided. Check the work-authorization line on each specific role</t>
         </is>
       </c>
       <c r="I274" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. In prior cycles Splunk posted roles in early September and filled them progressively through February. The US posting listed on October 11, 2026</t>
+          <t>Partially. In the prior cycle Starbucks reviewed applications on a priority basis through October, then continued on a rolling basis until positions were filled</t>
         </is>
       </c>
       <c r="J274" s="6" t="inlineStr">
         <is>
-          <t>SWE intern $42 to $60/hr ($7,280 to $10,400/mo) depending on location. Housing stipends $2,000 to $6,000 for select offices</t>
+          <t>$25 to $45 per hour depending on role and level. Technology roles $28 to $45 per hour (Levels.fyi reports $28/hr for SWE interns, Summer 2023). Corporate housin</t>
         </is>
       </c>
       <c r="K274" s="6" t="inlineStr">
         <is>
-          <t>Partly open: on October 11, 2026, one US Splunk intern posting was accepting applications on careers.cisco.com, Splunk Solutions Engineer (Intern) - United States, posted October 7, 2026. It names no summer and no closing date, and says applications are accepted until further notice. No Splunk-branded software engineering intern posting was listed that day. The earlier estimate of an early Septemb</t>
+          <t>Not posted as of October 11, 2026: no US internship posting was listed on apply.starbucks.com that day. The earlier estimate (late August 2026 opening, priority review through October 2026, some postings open through December 2026) was projected from the prior cycle. Starbucks’s internships page says applications open around fall each year</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -15838,17 +15842,17 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>Technology Intern  (1 of 6 tracks)</t>
+          <t>AI / Self-Driving (Autopilot); Software Engineering (Vehicle); Battery / Cell Engineering; Supply Chain Analytics  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E275" s="7" t="inlineStr">
         <is>
-          <t>apply.starbucks.com/careers?query=intern</t>
+          <t>tesla.com/careers/internships</t>
         </is>
       </c>
       <c r="F275" s="7" t="inlineStr">
@@ -15858,34 +15862,34 @@
       </c>
       <c r="G275" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a recruiter phone screen (15 to 20 minutes), then 2 to 3 behavioral interview rounds (45 to 60 minutes each) using the STAR method. Technology roles add a coding assessment. The total process spans 6 to 10 weeks. Glassdoor rates difficulty at 2.2 out of 5.</t>
+          <t>Typically 3 to 4 rounds: a recruiter phone screen (15 to 30 minutes), an online coding assessment via Codility (about 85 minutes, 2 to 3 LeetCode-Medium problems), a live technical interview (45 to 60 minutes), and a manager or final round. Non-SWE roles may replace the coding assessment with a proj</t>
         </is>
       </c>
       <c r="H275" s="6" t="inlineStr">
         <is>
-          <t>Limited. CPT may be supported for F-1 students on a case-by-case basis, but most postings state sponsorship is not provided. Check the work-authorization line on each specific role</t>
+          <t>Tesla accepts F-1 CPT and OPT for internships. You'll need to verify 40-hour-per-week work authorization for the on-site requirement. H-1B sponsorship for full-time roles after internship conversion is handled case by ca</t>
         </is>
       </c>
       <c r="I275" s="6" t="inlineStr">
         <is>
-          <t>Partially. In the prior cycle Starbucks reviewed applications on a priority basis through October, then continued on a rolling basis until positions were filled</t>
+          <t>Yes. Tesla reviews applications immediately upon submission and may recruit up to 4 months after posting</t>
         </is>
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
-          <t>$25 to $45 per hour depending on role and level. Technology roles $28 to $45 per hour (Levels.fyi reports $28/hr for SWE interns, Summer 2023). Corporate housin</t>
+          <t>SWE $58.80/hr (Levels.fyi); AI/Self-Driving $48–$72/hr; manufacturing $20–$50/hr + housing $700–$3,000/mo</t>
         </is>
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>Not posted as of October 11, 2026: no US internship posting was listed on apply.starbucks.com that day. The earlier estimate (late August 2026 opening, priority review through October 2026, some postings open through December 2026) was projected from the prior cycle. Starbucks’s internships page says applications open around fall each year</t>
+          <t>Winter/Spring 2027 cohort open now (about 280 US listings live 1 October 2026, January 2027 start, minimum 12 weeks full time); summer 2027 postings have started (7 US listings live 1 October 2026, May/June 2027 start), more expected through November 2026 with peak hiring November 2026 through February 2027 (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -15900,12 +15904,12 @@
       </c>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>AI / Self-Driving (Autopilot); Software Engineering (Vehicle); Battery / Cell Engineering; Supply Chain Analytics  (4 of 6 tracks)</t>
+          <t>Embedded Software Engineering; Digital IC Design; Product/Test Engineering; Manufacturing/Process Engineering; Applications Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E276" s="7" t="inlineStr">
         <is>
-          <t>tesla.com/careers/internships</t>
+          <t>careers.ti.com/en/sites/CX/jobs?keyword=intern</t>
         </is>
       </c>
       <c r="F276" s="7" t="inlineStr">
@@ -15915,34 +15919,34 @@
       </c>
       <c r="G276" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 rounds: a recruiter phone screen (15 to 30 minutes), an online coding assessment via Codility (about 85 minutes, 2 to 3 LeetCode-Medium problems), a live technical interview (45 to 60 minutes), and a manager or final round. Non-SWE roles may replace the coding assessment with a proj</t>
+          <t xml:space="preserve">TI's interview funnel is shorter than most tech companies, averaging 22 days from application to offer. But the technical content is domain-specific rather than algorithm-focused, so generic LeetCode prep will not help you here: 1. Apply at careers.ti.com with a resume. No cover letter is required. </t>
         </is>
       </c>
       <c r="H276" s="6" t="inlineStr">
         <is>
-          <t>Tesla accepts F-1 CPT and OPT for internships. You'll need to verify 40-hour-per-week work authorization for the on-site requirement. H-1B sponsorship for full-time roles after internship conversion is handled case by ca</t>
+          <t xml:space="preserve">Yes. For internships: CPT authorization from your school is sufficient (no employer petition needed). For full-time: TI actively sponsors H-1B visas and filed 122 petitions with 122 approved in FY2025. TN visas are also </t>
         </is>
       </c>
       <c r="I276" s="6" t="inlineStr">
         <is>
-          <t>Yes. Tesla reviews applications immediately upon submission and may recruit up to 4 months after posting</t>
+          <t>Yes. Applications reviewed on a rolling basis. First-come advantage is real; positions may fill before the soft November close</t>
         </is>
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
-          <t>SWE $58.80/hr (Levels.fyi); AI/Self-Driving $48–$72/hr; manufacturing $20–$50/hr + housing $700–$3,000/mo</t>
+          <t>$28 to $47/hr depending on degree, role, and location, plus $2,300–$8,000 housing stipend</t>
         </is>
       </c>
       <c r="K276" s="6" t="inlineStr">
         <is>
-          <t>Winter/Spring 2027 cohort open now (about 280 US listings live 1 October 2026, January 2027 start, minimum 12 weeks full time); summer 2027 postings have started (7 US listings live 1 October 2026, May/June 2027 start), more expected through November 2026 with peak hiring November 2026 through February 2027 (projected from prior cycle)</t>
+          <t>Open now: 65 US intern reqs live on October 2, 2026, all posted September 1 to 28, 2026. 63 are titled without a year and print no close date (mostly degree-track engineering, software and business roles that appear to be for summer 2027, plus one Encore returnship and three SkillBridge roles); the other two are 2027-titled Manufacturing Technician (AAS/certificate) roles with Apply Before Novembe</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -15952,17 +15956,17 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering; Digital IC Design; Product/Test Engineering; Manufacturing/Process Engineering; Applications Engineering  (5 of 6 tracks)</t>
+          <t>Information Technology Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E277" s="7" t="inlineStr">
         <is>
-          <t>careers.ti.com/en/sites/CX/jobs?keyword=intern</t>
+          <t>jobs.tjx.com/global/en/studentsus</t>
         </is>
       </c>
       <c r="F277" s="7" t="inlineStr">
@@ -15972,34 +15976,30 @@
       </c>
       <c r="G277" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TI's interview funnel is shorter than most tech companies, averaging 22 days from application to offer. But the technical content is domain-specific rather than algorithm-focused, so generic LeetCode prep will not help you here: 1. Apply at careers.ti.com with a resume. No cover letter is required. </t>
-        </is>
-      </c>
-      <c r="H277" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes. For internships: CPT authorization from your school is sufficient (no employer petition needed). For full-time: TI actively sponsors H-1B visas and filed 122 petitions with 122 approved in FY2025. TN visas are also </t>
-        </is>
-      </c>
+          <t>Officially: a HireVue one-way video interview, then a case study, then behavioral interviews. The HireVue is about five recorded questions with roughly a minute to prep each, including an allocate-the-product scenario. The case study tests retail math, and the final round is often two interviewers f</t>
+        </is>
+      </c>
+      <c r="H277" s="6" t="inlineStr"/>
       <c r="I277" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis. First-come advantage is real; positions may fill before the soft November close</t>
+          <t>Yes (community-reported). TJX interviews merchandising interns as applications arrive, and many roles fill before the formal deadline. Apply the first week post</t>
         </is>
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
-          <t>$28 to $47/hr depending on degree, role, and location, plus $2,300–$8,000 housing stipend</t>
+          <t>No official rate published. Community and Levels.fyi data: merchandising interns ~$21–$26/hr; software-engineer interns ~$22/hr. Housing and relocation are unre</t>
         </is>
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>Open now: 65 US intern reqs live on October 2, 2026, all posted September 1 to 28, 2026. 63 are titled without a year and print no close date (mostly degree-track engineering, software and business roles that appear to be for summer 2027, plus one Encore returnship and three SkillBridge roles); the other two are 2027-titled Manufacturing Technician (AAS/certificate) roles with Apply Before Novembe</t>
+          <t xml:space="preserve">PARTLY CLOSED for summer 2027 (verified October 6, 2026 on TJX's Workday board). Still live: the Merchandising Internship Program (posted September 1, 2026; listed through December 31), Logistics (Supply Chain), Distribution Operations (20 US sites, listed through November 2) and Retail Management (Stores) in Phoenix and Tucson. Closed: Financial Accounting and Financial Analyst (deadline October </t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Together AI</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -16009,17 +16009,17 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>Information Technology Internship  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Security Engineer Intern  (2 of 7 tracks)</t>
         </is>
       </c>
       <c r="E278" s="7" t="inlineStr">
         <is>
-          <t>jobs.tjx.com/global/en/studentsus</t>
+          <t>job-boards.greenhouse.io/togetherai</t>
         </is>
       </c>
       <c r="F278" s="7" t="inlineStr">
@@ -16029,30 +16029,30 @@
       </c>
       <c r="G278" s="6" t="inlineStr">
         <is>
-          <t>Officially: a HireVue one-way video interview, then a case study, then behavioral interviews. The HireVue is about five recorded questions with roughly a minute to prep each, including an allocate-the-product scenario. The case study tests retail math, and the final round is often two interviewers f</t>
+          <t xml:space="preserve">For research interns, expect a PyTorch-based coding screen focused on ML-systems problems rather than traditional LeetCode. For engineering interns, expect coding interviews on distributed systems and full-stack development. The overall difficulty is rated 8 out of 10, comparable to Nvidia core GPU </t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr"/>
       <c r="I278" s="6" t="inlineStr">
         <is>
-          <t>Yes (community-reported). TJX interviews merchandising interns as applications arrive, and many roles fill before the formal deadline. Apply the first week post</t>
+          <t>Not stated. Positions close once filled; no fixed deadline published for most roles</t>
         </is>
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
-          <t>No official rate published. Community and Levels.fyi data: merchandising interns ~$21–$26/hr; software-engineer interns ~$22/hr. Housing and relocation are unre</t>
+          <t>$58–$70/hr across the six Summer 2027 postings listed on October 11, 2026: $58/hr for Software Engineer Intern and Software Development In Test Intern, $58 to $</t>
         </is>
       </c>
       <c r="K278" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTLY CLOSED for summer 2027 (verified October 6, 2026 on TJX's Workday board). Still live: the Merchandising Internship Program (posted September 1, 2026; listed through December 31), Logistics (Supply Chain), Distribution Operations (20 US sites, listed through November 2) and Retail Management (Stores) in Phoenix and Tucson. Closed: Financial Accounting and Financial Analyst (deadline October </t>
+          <t>Open now for summer 2027: Six Summer 2027 intern postings were listed on Together AI's Greenhouse board on October 11, 2026, all first published September 18, 2026. None of the six prints an application deadline.</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -16062,17 +16062,17 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Security Engineer Intern  (2 of 7 tracks)</t>
+          <t>Software / IT (Phoenix)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E279" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/togetherai</t>
+          <t>careers.tsmc.com/en_US/</t>
         </is>
       </c>
       <c r="F279" s="7" t="inlineStr">
@@ -16082,30 +16082,34 @@
       </c>
       <c r="G279" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">For research interns, expect a PyTorch-based coding screen focused on ML-systems problems rather than traditional LeetCode. For engineering interns, expect coding interviews on distributed systems and full-stack development. The overall difficulty is rated 8 out of 10, comparable to Nvidia core GPU </t>
-        </is>
-      </c>
-      <c r="H279" s="6" t="inlineStr"/>
+          <t>TSMC's hiring funnel depends on whether you are applying for an engineering or software role, and the split matters: 1. Find your track at careers.tsmc.com and filter by US locations plus "intern." Arizona alone has 12+ engineering tracks, so read the specific JD carefully before applying. 2. Submit</t>
+        </is>
+      </c>
+      <c r="H279" s="6" t="inlineStr">
+        <is>
+          <t>No. TSMC explicitly excludes H-1B, OPT, O-1, and TN visa holders from US internship positions. Applicants must have long-term work authorization without any current or future employer sponsorship. Arizona postings use sl</t>
+        </is>
+      </c>
       <c r="I279" s="6" t="inlineStr">
         <is>
-          <t>Not stated. Positions close once filled; no fixed deadline published for most roles</t>
+          <t>Partially. Window is defined but review within it is rolling; apply early</t>
         </is>
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>$58–$70/hr across the six Summer 2027 postings listed on October 11, 2026: $58/hr for Software Engineer Intern and Software Development In Test Intern, $58 to $</t>
+          <t>$23 to $48/hr depending on location, role, and degree (Camas WA entry to San Jose PhD research)</t>
         </is>
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Six Summer 2027 intern postings were listed on Together AI's Greenhouse board on October 11, 2026, all first published September 18, 2026. None of the six prints an application deadline.</t>
+          <t>Applications for summer 2027 expected to open October to December 2026 and close by March 2027 (earliest AZ postings live as of July 2026; projected from prior cycles)</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ubisoft</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -16115,17 +16119,17 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>Software / IT (Phoenix)  (1 of 6 tracks)</t>
+          <t>Data &amp; Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>careers.tsmc.com/en_US/</t>
+          <t>ubisoft.com/en-us/company/careers/search</t>
         </is>
       </c>
       <c r="F280" s="7" t="inlineStr">
@@ -16135,34 +16139,30 @@
       </c>
       <c r="G280" s="6" t="inlineStr">
         <is>
-          <t>TSMC's hiring funnel depends on whether you are applying for an engineering or software role, and the split matters: 1. Find your track at careers.tsmc.com and filter by US locations plus "intern." Arizona alone has 12+ engineering tracks, so read the specific JD carefully before applying. 2. Submit</t>
-        </is>
-      </c>
-      <c r="H280" s="6" t="inlineStr">
-        <is>
-          <t>No. TSMC explicitly excludes H-1B, OPT, O-1, and TN visa holders from US internship positions. Applicants must have long-term work authorization without any current or future employer sponsorship. Arizona postings use sl</t>
-        </is>
-      </c>
+          <t>For programming roles, expect 4 rounds: an online MCQ assessment covering OOP, OS, C++, and data structures; two technical interviews testing CS fundamentals and game-specific knowledge like 3D math and engine concepts; and a short HR round. For other roles, expect 2 to 3 rounds including a recruite</t>
+        </is>
+      </c>
+      <c r="H280" s="6" t="inlineStr"/>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>Partially. Window is defined but review within it is rolling; apply early</t>
+          <t>Effectively yes. Each studio reviews applications as they come in; positions close once filled. Structured programs (Develop at Ubisoft, Graduate Program, NEXT)</t>
         </is>
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>$23 to $48/hr depending on location, role, and degree (Camas WA entry to San Jose PhD research)</t>
+          <t>$23 to $33/hr for US interns (Indeed and Glassdoor ranges); ~$18 to $22 CAD/hr for Montreal co-ops</t>
         </is>
       </c>
       <c r="K280" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open October to December 2026 and close by March 2027 (earliest AZ postings live as of July 2026; projected from prior cycles)</t>
+          <t>Studio postings expected December 2026 through March 2027; Develop at Ubisoft mentorship opens October 2026</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>Ubisoft</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -16177,12 +16177,12 @@
       </c>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics  (1 of 6 tracks)</t>
+          <t>See guide</t>
         </is>
       </c>
       <c r="E281" s="7" t="inlineStr">
         <is>
-          <t>ubisoft.com/en-us/company/careers/search</t>
+          <t>ubs.com/global/en/careers/early-careers.html</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
@@ -16192,30 +16192,34 @@
       </c>
       <c r="G281" s="6" t="inlineStr">
         <is>
-          <t>For programming roles, expect 4 rounds: an online MCQ assessment covering OOP, OS, C++, and data structures; two technical interviews testing CS fundamentals and game-specific knowledge like 3D math and engine concepts; and a short HR round. For other roles, expect 2 to 3 rounds including a recruite</t>
-        </is>
-      </c>
-      <c r="H281" s="6" t="inlineStr"/>
+          <t>Four to five back-to-back interviews, each roughly 30 minutes, with Associates, VPs, and Directors. The format mixes behavioral questions (resume walkthrough, teamwork, setback stories) with technical questions for front-office roles (DCF, three-statement linking, EV vs. equity value, LBO basics). S</t>
+        </is>
+      </c>
+      <c r="H281" s="6" t="inlineStr">
+        <is>
+          <t>Many US internship positions explicitly state they do not offer employment-based immigration sponsorship, including OPT and CPT. This is confirmed across Global Banking, Global Wealth Management, and Asset Management pos</t>
+        </is>
+      </c>
       <c r="I281" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Each studio reviews applications as they come in; positions close once filled. Structured programs (Develop at Ubisoft, Graduate Program, NEXT)</t>
+          <t>Yes. UBS reviews on a rolling basis; front-office US Summer 2027 seats filled by May 2026, so early-window seats go fast. Five US 2027 Summer Internship posting</t>
         </is>
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>$23 to $33/hr for US interns (Indeed and Glassdoor ranges); ~$18 to $22 CAD/hr for Montreal co-ops</t>
+          <t>$43–$55/hr depending on division (Global Banking $52.88; Global Wealth Management $43.27)</t>
         </is>
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>Studio postings expected December 2026 through March 2027; Develop at Ubisoft mentorship opens October 2026</t>
+          <t>Open now for summer 2027: US internships in Technology, Group Risk Control and Chief Operating Office (New York/New Jersey and Raleigh) were listed on UBS's early-careers job gateway on October 10, 2026. Front-office US tracks (Investment Banking, Global Markets, Wealth Management, Asset Management, Research) were not listed that day and are expected December 2026 to January 2027, rolling until fi</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -16230,12 +16234,12 @@
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>See guide</t>
+          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>ubs.com/global/en/careers/early-careers.html</t>
+          <t>careers.ulta.com/internships</t>
         </is>
       </c>
       <c r="F282" s="7" t="inlineStr">
@@ -16245,34 +16249,30 @@
       </c>
       <c r="G282" s="6" t="inlineStr">
         <is>
-          <t>Four to five back-to-back interviews, each roughly 30 minutes, with Associates, VPs, and Directors. The format mixes behavioral questions (resume walkthrough, teamwork, setback stories) with technical questions for front-office roles (DCF, three-statement linking, EV vs. equity value, LBO basics). S</t>
-        </is>
-      </c>
-      <c r="H282" s="6" t="inlineStr">
-        <is>
-          <t>Many US internship positions explicitly state they do not offer employment-based immigration sponsorship, including OPT and CPT. This is confirmed across Global Banking, Global Wealth Management, and Asset Management pos</t>
-        </is>
-      </c>
+          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr"/>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t>Yes. UBS reviews on a rolling basis; front-office US Summer 2027 seats filled by May 2026, so early-window seats go fast. Five US 2027 Summer Internship posting</t>
+          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
         </is>
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>$43–$55/hr depending on division (Global Banking $52.88; Global Wealth Management $43.27)</t>
+          <t>$25.00 per hour on the 2027-cycle corporate postings we checked (Corporate Strategy, Audit, Ecommerce) and $30.00 per hour on the distribution-center postings w</t>
         </is>
       </c>
       <c r="K282" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: US internships in Technology, Group Risk Control and Chief Operating Office (New York/New Jersey and Raleigh) were listed on UBS's early-careers job gateway on October 10, 2026. Front-office US tracks (Investment Banking, Global Markets, Wealth Management, Asset Management, Research) were not listed that day and are expected December 2026 to January 2027, rolling until fi</t>
+          <t>Open now for Summer 2027: 22 US intern postings live on Oct 1, 2026 (15 corporate at Bolingbrook, 7 distribution center), posted Sept 14–23, 2026. No deadline printed on the postings we checked; the 2026 cycle closed January 1, so a deadline around January 1, 2027 is expected. Apply early for priority</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -16287,12 +16287,12 @@
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
+          <t>Global Solutions Technology; Cybersecurity / AI Risk; AI/ML Engineering; Data Science &amp; Analytics  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E283" s="7" t="inlineStr">
         <is>
-          <t>careers.ulta.com/internships</t>
+          <t>mycareer.verizon.com/life-at-verizon/students-internships/</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -16302,30 +16302,34 @@
       </c>
       <c r="G283" s="6" t="inlineStr">
         <is>
-          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
-        </is>
-      </c>
-      <c r="H283" s="6" t="inlineStr"/>
+          <t>After applying online, most candidates complete a Candidates Assessment on Workday (the ADEPT-15 personality test, about 25–30 minutes), followed by a self-recorded video interview with 6 behavioral questions and 2 attempts each. Strong candidates advance to a phone or virtual interview, and some ro</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. All Verizon internship postings require "authorization to work in the U.S. without restrictions or need for future sponsorship." International students on F-1 visas may qualify through CPT or OPT work authorization, </t>
+        </is>
+      </c>
       <c r="I283" s="6" t="inlineStr">
         <is>
-          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
+          <t>Effectively yes. Postings "may close before the stated closing date"; applicants encouraged to apply as soon as possible</t>
         </is>
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>$25.00 per hour on the 2027-cycle corporate postings we checked (Corporate Strategy, Audit, Ecommerce) and $30.00 per hour on the distribution-center postings w</t>
+          <t>$23–$36/hr depending on role; 401(k) match on first 6%, full benefits from day one</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>Open now for Summer 2027: 22 US intern postings live on Oct 1, 2026 (15 corporate at Bolingbrook, 7 distribution center), posted Sept 14–23, 2026. No deadline printed on the postings we checked; the 2026 cycle closed January 1, so a deadline around January 1, 2027 is expected. Apply early for priority</t>
+          <t>Partly open for summer 2027: on October 15, 2026 Verizon's careers board listed two US summer 2027 internships, both Verizon Consumer Group roles in Basking Ridge, NJ (Verizon Value; Home &amp; Mobile Value Prop), posted October 12, 2026, with an end date of October 17, 2026 (Verizon asks applicants to apply prior to it). No other US summer 2027 internship was listed that day; in the 2026 cycle, Publi</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -16340,12 +16344,12 @@
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>Global Solutions Technology; Cybersecurity / AI Risk; AI/ML Engineering; Data Science &amp; Analytics  (4 of 6 tracks)</t>
+          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>mycareer.verizon.com/life-at-verizon/students-internships/</t>
+          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
         </is>
       </c>
       <c r="F284" s="7" t="inlineStr">
@@ -16355,34 +16359,34 @@
       </c>
       <c r="G284" s="6" t="inlineStr">
         <is>
-          <t>After applying online, most candidates complete a Candidates Assessment on Workday (the ADEPT-15 personality test, about 25–30 minutes), followed by a self-recorded video interview with 6 behavioral questions and 2 attempts each. Strong candidates advance to a phone or virtual interview, and some ro</t>
+          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
         </is>
       </c>
       <c r="H284" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. All Verizon internship postings require "authorization to work in the U.S. without restrictions or need for future sponsorship." International students on F-1 visas may qualify through CPT or OPT work authorization, </t>
+          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
         </is>
       </c>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Postings "may close before the stated closing date"; applicants encouraged to apply as soon as possible</t>
+          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
         </is>
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>$23–$36/hr depending on role; 401(k) match on first 6%, full benefits from day one</t>
+          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr">
         <is>
-          <t>Partly open for summer 2027: on October 15, 2026 Verizon's careers board listed two US summer 2027 internships, both Verizon Consumer Group roles in Basking Ridge, NJ (Verizon Value; Home &amp; Mobile Value Prop), posted October 12, 2026, with an end date of October 17, 2026 (Verizon asks applicants to apply prior to it). No other US summer 2027 internship was listed that day; in the 2026 cycle, Publi</t>
+          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -16392,17 +16396,17 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
+          <t>Software Engineering (Global Tech); Data Science &amp; Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E285" s="7" t="inlineStr">
         <is>
-          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
+          <t>careers.walmart.com/us/en/home/careers-areas/students</t>
         </is>
       </c>
       <c r="F285" s="7" t="inlineStr">
@@ -16412,34 +16416,34 @@
       </c>
       <c r="G285" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
+          <t>Walmart runs two distinct funnels depending on whether you're applying for a corporate/business track or a Walmart Global Tech/SWE track: 1. Apply at careers.walmart.com . Summer 2027 postings started going live on August 25, 2026, and 17 US intern requisitions were listed on October 11, 2026. Ten p</t>
         </is>
       </c>
       <c r="H285" s="6" t="inlineStr">
         <is>
-          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
+          <t>No. Walmart doesn't provide visa sponsorship (H-1B, TN) for internship roles. International students on CPT or OPT are eligible, provided they have valid work authorization during the full internship period.</t>
         </is>
       </c>
       <c r="I285" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
+          <t>Yes. Interviews begin rolling in September; ~60–70% of slots fill by mid-September</t>
         </is>
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
+          <t>$19–$55/hr depending on role and location; SWE at Sunnyvale up to $52/hr, plus housing and relocation</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t xml:space="preserve">Open now for summer 2027: 17 US Summer 2027 intern requisitions were listed on October 11, 2026 (first postings August 25, newest October 9, 2026). Ten print no close date; data science closes January 29, 2027, cybersecurity February 5, 2027, and three supply chain and transportation reqs March 1, 2027. The Accounting and Finance Development Program and Automation Engineer postings were no longer </t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -16449,17 +16453,17 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (Global Tech); Data Science &amp; Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern  (1 of 3 tracks)</t>
         </is>
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>careers.walmart.com/us/en/home/careers-areas/students</t>
+          <t>jobs.ashbyhq.com/weaviate</t>
         </is>
       </c>
       <c r="F286" s="7" t="inlineStr">
@@ -16469,34 +16473,34 @@
       </c>
       <c r="G286" s="6" t="inlineStr">
         <is>
-          <t>Walmart runs two distinct funnels depending on whether you're applying for a corporate/business track or a Walmart Global Tech/SWE track: 1. Apply at careers.walmart.com . Summer 2027 postings started going live on August 25, 2026, and 17 US intern requisitions were listed on October 11, 2026. Ten p</t>
+          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>No. Walmart doesn't provide visa sponsorship (H-1B, TN) for internship roles. International students on CPT or OPT are eligible, provided they have valid work authorization during the full internship period.</t>
+          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>Yes. Interviews begin rolling in September; ~60–70% of slots fill by mid-September</t>
+          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
         </is>
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>$19–$55/hr depending on role and location; SWE at Sunnyvale up to $52/hr, plus housing and relocation</t>
+          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
         </is>
       </c>
       <c r="K286" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open now for summer 2027: 17 US Summer 2027 intern requisitions were listed on October 11, 2026 (first postings August 25, newest October 9, 2026). Ten print no close date; data science closes January 29, 2027, cybersecurity February 5, 2027, and three supply chain and transportation reqs March 1, 2027. The Accounting and Finance Development Program and Automation Engineer postings were no longer </t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -16506,17 +16510,17 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026 – March 2027</t>
         </is>
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern  (1 of 3 tracks)</t>
+          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E287" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/weaviate</t>
+          <t>coreweave.com/careers/weights-biases</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
@@ -16526,34 +16530,34 @@
       </c>
       <c r="G287" s="6" t="inlineStr">
         <is>
-          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
+          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
         </is>
       </c>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
+          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
+          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
         </is>
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
+          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
+          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -16563,17 +16567,17 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – March 2027</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>coreweave.com/careers/weights-biases</t>
+          <t>wellsfargojobs.com/en/early-careers/</t>
         </is>
       </c>
       <c r="F288" s="7" t="inlineStr">
@@ -16583,34 +16587,34 @@
       </c>
       <c r="G288" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
+          <t>Four stages. First, an online application with resume upload and motivation questions. Second, an online assessment with cognitive or situational judgment tests (coding challenges for tech roles). Third, a HireVue video interview with 3 to 7 behavioral questions and a 24 to 48 hour preparation windo</t>
         </is>
       </c>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
+          <t>No. Wells Fargo explicitly requires authorization to work in the United States on a full-time basis and does not sponsor work visas for internships, post-graduation programs, or permanent employment. There is no assistan</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
+          <t>Yes. Wells Fargo reviews and fills positions as qualified candidates are identified</t>
         </is>
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
+          <t>$31–$53/hr ($64,500 to $110,000+ annualized); CIB IB at top with $2,500 housing stipend</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
+          <t xml:space="preserve">Mostly closed for summer 2027. As of October 6, 2026, Finance, HR, Audit, Commercial Banking, Consumer Banking and Lending, Global Payments, Wealth &amp; Investment Management, Corporate Risk, COO, Quantitative Analytics and Public Affairs have all come down. Still live for summer 2027: Technology Software Engineering (Posting End Date October 13, 2026) and the MBA Investment Banking Summer Associate </t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>William Blair</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -16620,17 +16624,17 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>Working in Technology (WiT) Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr">
         <is>
-          <t>wellsfargojobs.com/en/early-careers/</t>
+          <t>williamblair.com/Careers/Campus-Recruiting</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
@@ -16640,34 +16644,34 @@
       </c>
       <c r="G289" s="6" t="inlineStr">
         <is>
-          <t>Four stages. First, an online application with resume upload and motivation questions. Second, an online assessment with cognitive or situational judgment tests (coding challenges for tech roles). Third, a HireVue video interview with 3 to 7 behavioral questions and a 24 to 48 hour preparation windo</t>
+          <t xml:space="preserve">William Blair's funnel spans four stages from application to offer: 1. Apply on williamblair.com/Careers . Search for IB Summer Analyst or other tracks, select your preferred location(s), and submit resume, cover letter, and transcript. Multiple position and location applications are permitted. For </t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>No. Wells Fargo explicitly requires authorization to work in the United States on a full-time basis and does not sponsor work visas for internships, post-graduation programs, or permanent employment. There is no assistan</t>
+          <t>Not for IB Summer Analyst roles: the 2027 postings say William Blair is not hiring candidates who now or in the future require visa sponsorship. Check each posting for other tracks</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
         <is>
-          <t>Yes. Wells Fargo reviews and fills positions as qualified candidates are identified</t>
+          <t>Yes. William Blair reviews applications on a rolling basis. For on-campus partners, specific deadlines are posted on school career sites. Apply as early as poss</t>
         </is>
       </c>
       <c r="J289" s="6" t="inlineStr">
         <is>
-          <t>$31–$53/hr ($64,500 to $110,000+ annualized); CIB IB at top with $2,500 housing stipend</t>
+          <t>$110,000 annualized base (about $2,115 per week) on the 2027 IB Summer Analyst postings. $5,000 housing stipend plus up to $1,200 domestic relocation. Dinner st</t>
         </is>
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostly closed for summer 2027. As of October 6, 2026, Finance, HR, Audit, Commercial Banking, Consumer Banking and Lending, Global Payments, Wealth &amp; Investment Management, Corporate Risk, COO, Quantitative Analytics and Public Affairs have all come down. Still live for summer 2027: Technology Software Engineering (Posting End Date October 13, 2026) and the MBA Investment Banking Summer Associate </t>
+          <t>Expected from about November 2026 into early 2027 for Summer 2028 IB roles (projected: the first 2027 Summer Analyst application posted in December 2025). Suited pre-interview assessment within 48 hours of applying, then rolling interviews and Superdays. Summer 2027 still open: Sports, Media &amp; Entertainment Summer Analyst (New York), posted October 14, 2026</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>William Blair</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -16682,12 +16686,12 @@
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>Working in Technology (WiT) Intern  (1 of 6 tracks)</t>
+          <t>Decision Analytics Associate (DAA); Business Technology Solutions Associate (BTSA)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>williamblair.com/Careers/Campus-Recruiting</t>
+          <t>jobs.zs.com/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
         </is>
       </c>
       <c r="F290" s="7" t="inlineStr">
@@ -16697,34 +16701,34 @@
       </c>
       <c r="G290" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">William Blair's funnel spans four stages from application to offer: 1. Apply on williamblair.com/Careers . Search for IB Summer Analyst or other tracks, select your preferred location(s), and submit resume, cover letter, and transcript. Multiple position and location applications are permitted. For </t>
+          <t>The process runs two to four rounds: an online aptitude test covering logical, quantitative, and verbal reasoning, then case and behavioral interviews. ZS cases are candidate-led and often pharma or healthcare themed. Final rounds may include a written case presentation where you analyze a data pack</t>
         </is>
       </c>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>Not for IB Summer Analyst roles: the 2027 postings say William Blair is not hiring candidates who now or in the future require visa sponsorship. Check each posting for other tracks</t>
+          <t>Yes. ZS's official FAQ states the firm offers visa sponsorship for full-time employees and support for interns with a student visa. Sponsorship type and reimbursement may vary based on location, role, and status. ZS file</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>Yes. William Blair reviews applications on a rolling basis. For on-campus partners, specific deadlines are posted on school career sites. Apply as early as poss</t>
+          <t>Yes. ZS recruits on a rolling basis during campus season; intern spots fill as strong candidates clear the rounds</t>
         </is>
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized base (about $2,115 per week) on the 2027 IB Summer Analyst postings. $5,000 housing stipend plus up to $1,200 domestic relocation. Dinner st</t>
+          <t>~$34/hr general intern range ($25–$46); Strategy Insights &amp; Planning ~$50/hr; Business Technology Solutions ~$63/hr</t>
         </is>
       </c>
       <c r="K290" s="6" t="inlineStr">
         <is>
-          <t>Expected from about November 2026 into early 2027 for Summer 2028 IB roles (projected: the first 2027 Summer Analyst application posted in December 2025). Suited pre-interview assessment within 48 hours of applying, then rolling interviews and Superdays. Summer 2027 still open: Sports, Media &amp; Entertainment Summer Analyst (New York), posted October 14, 2026</t>
+          <t>Open now for summer 2027: nine North America intern postings live on jobs.zs.com as of October 1, 2026 (posted September 1–2). Rolling review; no deadline printed in the postings we checked</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -16734,17 +16738,17 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>Decision Analytics Associate (DAA); Business Technology Solutions Associate (BTSA)  (2 of 4 tracks)</t>
+          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E291" s="7" t="inlineStr">
         <is>
-          <t>jobs.zs.com/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
+          <t>biibhr.wd3.myworkdayjobs.com/external</t>
         </is>
       </c>
       <c r="F291" s="7" t="inlineStr">
@@ -16754,34 +16758,34 @@
       </c>
       <c r="G291" s="6" t="inlineStr">
         <is>
-          <t>The process runs two to four rounds: an online aptitude test covering logical, quantitative, and verbal reasoning, then case and behavioral interviews. ZS cases are candidate-led and often pharma or healthcare themed. Final rounds may include a written case presentation where you analyze a data pack</t>
+          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
         </is>
       </c>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>Yes. ZS's official FAQ states the firm offers visa sponsorship for full-time employees and support for interns with a student visa. Sponsorship type and reimbursement may vary based on location, role, and status. ZS file</t>
+          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
         </is>
       </c>
       <c r="I291" s="6" t="inlineStr">
         <is>
-          <t>Yes. ZS recruits on a rolling basis during campus season; intern spots fill as strong candidates clear the rounds</t>
+          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
         </is>
       </c>
       <c r="J291" s="6" t="inlineStr">
         <is>
-          <t>~$34/hr general intern range ($25–$46); Strategy Insights &amp; Planning ~$50/hr; Business Technology Solutions ~$63/hr</t>
+          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
         </is>
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: nine North America intern postings live on jobs.zs.com as of October 1, 2026 (posted September 1–2). Rolling review; no deadline printed in the postings we checked</t>
+          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted as of October 1, 2026). Separate January to June 2027 co-ops are open now</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -16791,17 +16795,17 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>December 2026</t>
         </is>
       </c>
       <c r="D292" s="6" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
+          <t>Cubist Quantitative Researcher; Cubist Quantitative Developer; Technology – Software Engineer; Data Engineer (Market Intelligence); AI Analyst  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E292" s="7" t="inlineStr">
         <is>
-          <t>biibhr.wd3.myworkdayjobs.com/external</t>
+          <t>careers.point72.com/?experience=internships</t>
         </is>
       </c>
       <c r="F292" s="7" t="inlineStr">
@@ -16811,34 +16815,34 @@
       </c>
       <c r="G292" s="6" t="inlineStr">
         <is>
-          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
+          <t>The Academy runs a five-stage funnel that's more structured than most hedge fund processes. Each stage is designed to filter for a specific trait: 1. Submit your application at careers.point72.com with your resume, essays, and supplementary materials. Expect a 300-word essay on "market inefficiency"</t>
         </is>
       </c>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
+          <t>Yes. Point72 sponsors CPT, OPT, and H-1B visas. The firm had approximately 150 visa approvals in FY2025. That said, the process is selective, and third-party estimates suggest roughly 30 to 40% odds for Academy graduates</t>
         </is>
       </c>
       <c r="I292" s="6" t="inlineStr">
         <is>
-          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
+          <t>Yes. No set deadline; candidates reviewed as they apply until the program is at capacity</t>
         </is>
       </c>
       <c r="J292" s="6" t="inlineStr">
         <is>
-          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
+          <t>Academy: $120K–$140K annualized + $2,500–$5,000 signing bonus; Cubist Summer 2027 Quantitative Research intern (KEPL, PhD): $240K–$300K annualized base, prorate</t>
         </is>
       </c>
       <c r="K292" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted as of October 1, 2026). Separate January to June 2027 co-ops are open now</t>
+          <t>US Academy, summer 2028: expected to open around December 2026 (the summer 2027 posting went live in early December 2025 and closed by early May 2026). Open now for summer 2027: Investment Services Internship (New York/Stamford), Cubist and Point72 quant research intern roles, and the Academy internship in Hong Kong, Singapore and Japan. All rolling.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -16848,17 +16852,17 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>December 2026</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>Cubist Quantitative Researcher; Cubist Quantitative Developer; Technology – Software Engineer; Data Engineer (Market Intelligence); AI Analyst  (5 of 6 tracks)</t>
+          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E293" s="7" t="inlineStr">
         <is>
-          <t>careers.point72.com/?experience=internships</t>
+          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
         </is>
       </c>
       <c r="F293" s="7" t="inlineStr">
@@ -16868,34 +16872,30 @@
       </c>
       <c r="G293" s="6" t="inlineStr">
         <is>
-          <t>The Academy runs a five-stage funnel that's more structured than most hedge fund processes. Each stage is designed to filter for a specific trait: 1. Submit your application at careers.point72.com with your resume, essays, and supplementary materials. Expect a 300-word essay on "market inefficiency"</t>
-        </is>
-      </c>
-      <c r="H293" s="6" t="inlineStr">
-        <is>
-          <t>Yes. Point72 sponsors CPT, OPT, and H-1B visas. The firm had approximately 150 visa approvals in FY2025. That said, the process is selective, and third-party estimates suggest roughly 30 to 40% odds for Academy graduates</t>
-        </is>
-      </c>
+          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
+        </is>
+      </c>
+      <c r="H293" s="6" t="inlineStr"/>
       <c r="I293" s="6" t="inlineStr">
         <is>
-          <t>Yes. No set deadline; candidates reviewed as they apply until the program is at capacity</t>
+          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
         </is>
       </c>
       <c r="J293" s="6" t="inlineStr">
         <is>
-          <t>Academy: $120K–$140K annualized + $2,500–$5,000 signing bonus; Cubist Summer 2027 Quantitative Research intern (KEPL, PhD): $240K–$300K annualized base, prorate</t>
+          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
         </is>
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>US Academy, summer 2028: expected to open around December 2026 (the summer 2027 posting went live in early December 2025 and closed by early May 2026). Open now for summer 2027: Investment Services Internship (New York/Stamford), Cubist and Point72 quant research intern roles, and the Academy internship in Hong Kong, Singapore and Japan. All rolling.</t>
+          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -16905,17 +16905,17 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D294" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
+          <t>iXp Software Engineering; iXp AI Software Developer; iXp Data Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E294" s="7" t="inlineStr">
         <is>
-          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
+          <t>jobs.sap.com/go/Intern-Jobs-in-the-United-States/872801/</t>
         </is>
       </c>
       <c r="F294" s="7" t="inlineStr">
@@ -16925,30 +16925,34 @@
       </c>
       <c r="G294" s="6" t="inlineStr">
         <is>
-          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
-        </is>
-      </c>
-      <c r="H294" s="6" t="inlineStr"/>
+          <t xml:space="preserve">Typically 3 to 4 stages: automated coding challenge via Codility or HackerRank (60 to 90 minutes, LeetCode Medium), recruiter phone screen (30 minutes), technical interview (60 to 75 minutes), and behavioral interview (45 to 60 minutes, STAR method). Select roles include an Assessment Center with a </t>
+        </is>
+      </c>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>F-1 CPT and OPT fully eligible. Some roles explicitly do not provide visa sponsorship; check individual JDs. H-1B available for full-time conversion</t>
+        </is>
+      </c>
       <c r="I294" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
+          <t>Yes, confirmed. Applications reviewed rolling; submissions in the first 2 weeks get higher visibility. Employee referrals advance at 3 to 5x the cold-applicatio</t>
         </is>
       </c>
       <c r="J294" s="6" t="inlineStr">
         <is>
-          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
+          <t>SWE US $32 to $56/hr (~$5,500 to $8,500/month). Master's-level candidates earn 15 to 20% premiums. Full posted range $15 to $62/hr across all roles</t>
         </is>
       </c>
       <c r="K294" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
+          <t>Summer 2027 iXp roles: not posted yet on October 6, 2026; expected around February to April 2027, projected from the 1 to 3 month lead on current postings. Off-cycle US iXp roles (6 to 12 months, starting October 2026 to early 2027) are open now</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -16958,17 +16962,17 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>iXp Software Engineering; iXp AI Software Developer; iXp Data Engineering  (3 of 6 tracks)</t>
+          <t>GEICO TDP Software &amp; AI Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E295" s="7" t="inlineStr">
         <is>
-          <t>jobs.sap.com/go/Intern-Jobs-in-the-United-States/872801/</t>
+          <t>geico.wd1.myworkdayjobs.com/External</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
@@ -16978,34 +16982,34 @@
       </c>
       <c r="G295" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typically 3 to 4 stages: automated coding challenge via Codility or HackerRank (60 to 90 minutes, LeetCode Medium), recruiter phone screen (30 minutes), technical interview (60 to 75 minutes), and behavioral interview (45 to 60 minutes, STAR method). Select roles include an Assessment Center with a </t>
+          <t>Most subsidiaries use 1 to 2 rounds: a recruiter phone screen followed by a hiring-manager interview. GEICO tech adds a technical skills assessment. Behavioral questions focus on integrity, problem-solving, teamwork, and long-term thinking using the STAR method.</t>
         </is>
       </c>
       <c r="H295" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT and OPT fully eligible. Some roles explicitly do not provide visa sponsorship; check individual JDs. H-1B available for full-time conversion</t>
+          <t>Generally no. GEICO explicitly does not sponsor employment authorization for intern roles. Other subsidiaries typically require existing U.S. work authorization</t>
         </is>
       </c>
       <c r="I295" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed rolling; submissions in the first 2 weeks get higher visibility. Employee referrals advance at 3 to 5x the cold-applicatio</t>
+          <t>Not officially stated by any subsidiary. Most roles accept applications until filled. Apply as soon as postings appear for the best odds</t>
         </is>
       </c>
       <c r="J295" s="6" t="inlineStr">
         <is>
-          <t>SWE US $32 to $56/hr (~$5,500 to $8,500/month). Master's-level candidates earn 15 to 20% premiums. Full posted range $15 to $62/hr across all roles</t>
+          <t>Varies widely: GEICO tech $28 to $50+/hr (official JD), BHSI $24 to $43/hr, BH Energy IT $17.50 to $21.50/hr, BNSF ~$20/hr (community), BH GUARD $15 to $20/hr</t>
         </is>
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 iXp roles: not posted yet on October 6, 2026; expected around February to April 2027, projected from the 1 to 3 month lead on current postings. Off-cycle US iXp roles (6 to 12 months, starting October 2026 to early 2027) are open now</t>
+          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -17020,12 +17024,12 @@
       </c>
       <c r="D296" s="6" t="inlineStr">
         <is>
-          <t>GEICO TDP Software &amp; AI Intern  (1 of 6 tracks)</t>
+          <t>Engineering / Developer  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E296" s="7" t="inlineStr">
         <is>
-          <t>geico.wd1.myworkdayjobs.com/External</t>
+          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
         </is>
       </c>
       <c r="F296" s="7" t="inlineStr">
@@ -17035,34 +17039,34 @@
       </c>
       <c r="G296" s="6" t="inlineStr">
         <is>
-          <t>Most subsidiaries use 1 to 2 rounds: a recruiter phone screen followed by a hiring-manager interview. GEICO tech adds a technical skills assessment. Behavioral questions focus on integrity, problem-solving, teamwork, and long-term thinking using the STAR method.</t>
+          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
         </is>
       </c>
       <c r="H296" s="6" t="inlineStr">
         <is>
-          <t>Generally no. GEICO explicitly does not sponsor employment authorization for intern roles. Other subsidiaries typically require existing U.S. work authorization</t>
+          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
         </is>
       </c>
       <c r="I296" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated by any subsidiary. Most roles accept applications until filled. Apply as soon as postings appear for the best odds</t>
+          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
         </is>
       </c>
       <c r="J296" s="6" t="inlineStr">
         <is>
-          <t>Varies widely: GEICO tech $28 to $50+/hr (official JD), BHSI $24 to $43/hr, BH Energy IT $17.50 to $21.50/hr, BNSF ~$20/hr (community), BH GUARD $15 to $20/hr</t>
+          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
         </is>
       </c>
       <c r="K296" s="6" t="inlineStr">
         <is>
-          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
+          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -17072,17 +17076,17 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>March–September 2027</t>
         </is>
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>Engineering / Developer  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E297" s="7" t="inlineStr">
         <is>
-          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
+          <t>careers.l3harris.com/en/new-grads-and-interns</t>
         </is>
       </c>
       <c r="F297" s="7" t="inlineStr">
@@ -17092,34 +17096,34 @@
       </c>
       <c r="G297" s="6" t="inlineStr">
         <is>
-          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
         </is>
       </c>
       <c r="H297" s="6" t="inlineStr">
         <is>
-          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
+          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
         </is>
       </c>
       <c r="I297" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
+          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
         </is>
       </c>
       <c r="J297" s="6" t="inlineStr">
         <is>
-          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
+          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
         </is>
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
+          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -17134,12 +17138,12 @@
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E298" s="7" t="inlineStr">
         <is>
-          <t>careers.l3harris.com/en/new-grads-and-interns</t>
+          <t>rocketlabcorp.com/careers/internships/</t>
         </is>
       </c>
       <c r="F298" s="7" t="inlineStr">
@@ -17149,34 +17153,34 @@
       </c>
       <c r="G298" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
+          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
         </is>
       </c>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
+          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
         </is>
       </c>
       <c r="I298" s="6" t="inlineStr">
         <is>
-          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
+          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
         </is>
       </c>
       <c r="J298" s="6" t="inlineStr">
         <is>
-          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
+          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
         </is>
       </c>
       <c r="K298" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
+          <t>Open now: about 30 Spring 2027 and Summer 2027 intern postings live on Rocket Lab's Greenhouse board since September 9 to 13, 2026 (Long Beach, CA); no published deadline. ITAR: US citizen, green card holder, or other US person status required</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -17186,17 +17190,17 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>March–September 2027</t>
+          <t>June–August 2027</t>
         </is>
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
+          <t>IS/Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E299" s="7" t="inlineStr">
         <is>
-          <t>rocketlabcorp.com/careers/internships/</t>
+          <t>careers.amgen.com/en/students-graduates</t>
         </is>
       </c>
       <c r="F299" s="7" t="inlineStr">
@@ -17206,34 +17210,34 @@
       </c>
       <c r="G299" s="6" t="inlineStr">
         <is>
-          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
+          <t>After applying, expect a recruiter phone screen lasting about 25 to 30 minutes, followed by a 45 to 90 minute hiring manager interview focused on technical skills and behavioral questions in the STAR format. Some roles add a final panel round with multiple stakeholders, which can run two to four hou</t>
         </is>
       </c>
       <c r="H299" s="6" t="inlineStr">
         <is>
-          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
+          <t>No. Every Amgen internship posting states that the company doesn't provide immigration sponsorship for intern roles. International students on CPT or OPT may be eligible to participate, but H-1B sponsorship isn't offered</t>
         </is>
       </c>
       <c r="I299" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
+          <t>Yes. Applications reviewed on a rolling basis; positions may close once filled</t>
         </is>
       </c>
       <c r="J299" s="6" t="inlineStr">
         <is>
-          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
+          <t>Undergrad $25–$32/hr; graduate $35–$45/hr; housing/relocation stipend for on-site roles</t>
         </is>
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>Open now: about 30 Spring 2027 and Summer 2027 intern postings live on Rocket Lab's Greenhouse board since September 9 to 13, 2026 (Long Beach, CA); no published deadline. ITAR: US citizen, green card holder, or other US person status required</t>
+          <t>Open now: 25 US Summer 2027 requisitions posted August 28 to September 8, 2026; Amgen prints no deadline and accepts applications until it has enough candidates (rolling)</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
@@ -17243,17 +17247,17 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>June–August 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
-          <t>IS/Technology Intern  (1 of 6 tracks)</t>
+          <t>Systems Engineering Intern; Software Engineering Intern; Electrical Engineering Intern; Cybersecurity Intern; IT / PTECH Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E300" s="7" t="inlineStr">
         <is>
-          <t>careers.amgen.com/en/students-graduates</t>
+          <t>jobs.baesystems.com/global/en/leap</t>
         </is>
       </c>
       <c r="F300" s="7" t="inlineStr">
@@ -17263,34 +17267,34 @@
       </c>
       <c r="G300" s="6" t="inlineStr">
         <is>
-          <t>After applying, expect a recruiter phone screen lasting about 25 to 30 minutes, followed by a 45 to 90 minute hiring manager interview focused on technical skills and behavioral questions in the STAR format. Some roles add a final panel round with multiple stakeholders, which can run two to four hou</t>
+          <t>You apply online, may complete a gamified online assessment, then a 30-minute recruiter phone screen, a non-technical behavioral interview with a hiring manager using STAR+R format, and for engineering roles a technical or in-person interview. Average time to hire is about 17 days (Glassdoor).</t>
         </is>
       </c>
       <c r="H300" s="6" t="inlineStr">
         <is>
-          <t>No. Every Amgen internship posting states that the company doesn't provide immigration sponsorship for intern roles. International students on CPT or OPT may be eligible to participate, but H-1B sponsorship isn't offered</t>
+          <t>Very rare. The vast majority of positions require U.S. citizenship or U.S. Person status (citizen, permanent resident, refugee, or asylee). Security-clearance roles require U.S. citizenship specifically</t>
         </is>
       </c>
       <c r="I300" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; positions may close once filled</t>
+          <t>Yes. BAE Systems reviews applications as they arrive and fills seats on a rolling basis. Apply within the first few weeks of a posting for the best response rat</t>
         </is>
       </c>
       <c r="J300" s="6" t="inlineStr">
         <is>
-          <t>Undergrad $25–$32/hr; graduate $35–$45/hr; housing/relocation stipend for on-site roles</t>
+          <t>$20 to $37 per hour depending on role level and location. Technical Intern I (freshman-level) starts around $14 to $20/hr; senior technical interns reach $30 to</t>
         </is>
       </c>
       <c r="K300" s="6" t="inlineStr">
         <is>
-          <t>Open now: 25 US Summer 2027 requisitions posted August 28 to September 8, 2026; Amgen prints no deadline and accepts applications until it has enough candidates (rolling)</t>
+          <t>OPEN NOW for summer 2027. 44 US internship-level Summer 2027 reqs posted on jobs.baesystems.com on September 3, 2026 (one more September 10), across software, systems, electrical, mechanical, RF and microelectronics engineering in New Hampshire, Iowa, New York and San Diego. No deadline is printed on the requisitions</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -17300,17 +17304,17 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June–December 2027</t>
         </is>
       </c>
       <c r="D301" s="6" t="inlineStr">
         <is>
-          <t>Systems Engineering Intern; Software Engineering Intern; Electrical Engineering Intern; Cybersecurity Intern; IT / PTECH Intern  (5 of 6 tracks)</t>
+          <t>Summer Games: Software Developer Intern; Summer Games: Data Scientist Intern; Summer Games: Systems Engineering Intern; Summer Games: Cybersecurity Intern; Summer Hire: Engineering / Technical  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E301" s="7" t="inlineStr">
         <is>
-          <t>jobs.baesystems.com/global/en/leap</t>
+          <t>careers.boozallen.com/</t>
         </is>
       </c>
       <c r="F301" s="7" t="inlineStr">
@@ -17320,34 +17324,34 @@
       </c>
       <c r="G301" s="6" t="inlineStr">
         <is>
-          <t>You apply online, may complete a gamified online assessment, then a 30-minute recruiter phone screen, a non-technical behavioral interview with a hiring manager using STAR+R format, and for engineering roles a technical or in-person interview. Average time to hire is about 17 days (Glassdoor).</t>
+          <t>Two rounds over roughly four to six weeks. First, a 30-minute recruiter phone or video screen focused on your resume and motivation. Then one to two team interviews with client-facing consultants, heavily behavioral with some technical questions. Glassdoor rates difficulty at 2.4 out of 5.</t>
         </is>
       </c>
       <c r="H301" s="6" t="inlineStr">
         <is>
-          <t>Very rare. The vast majority of positions require U.S. citizenship or U.S. Person status (citizen, permanent resident, refugee, or asylee). Security-clearance roles require U.S. citizenship specifically</t>
+          <t>Almost never. The majority of roles require US citizenship for government security clearance eligibility. Non-US citizens cannot obtain clearance</t>
         </is>
       </c>
       <c r="I301" s="6" t="inlineStr">
         <is>
-          <t>Yes. BAE Systems reviews applications as they arrive and fills seats on a rolling basis. Apply within the first few weeks of a posting for the best response rat</t>
+          <t>Yes. Booz Allen reviews applications on a rolling basis starting in late August and continuing through the spring. Apply early in the cycle for the most open se</t>
         </is>
       </c>
       <c r="J301" s="6" t="inlineStr">
         <is>
-          <t>$20 to $37 per hour depending on role level and location. Technical Intern I (freshman-level) starts around $14 to $20/hr; senior technical interns reach $30 to</t>
+          <t>$26 to $46 per hour depending on role, location, and degree level (Glassdoor, 194 salary reports). Levels.fyi reports $30/hr for SWE interns. No housing or relo</t>
         </is>
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027. 44 US internship-level Summer 2027 reqs posted on jobs.baesystems.com on September 3, 2026 (one more September 10), across software, systems, electrical, mechanical, RF and microelectronics engineering in New Hampshire, Iowa, New York and San Diego. No deadline is printed on the requisitions</t>
+          <t>Open now for summer 2027: University Summer 2027 requisitions posting since August 28, 2026 (70 or more live as of September 28, 2026 across McLean, DC, Fayetteville, Beavercreek, Rome NY, Atlanta, Charleston SC, Huntsville AL, Honolulu, San Diego and El Segundo), Workday end dates from about December 2 to December 14, 2026; US citizenship required on cleared roles</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -17357,17 +17361,17 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>June–December 2027</t>
+          <t>June–November 2027</t>
         </is>
       </c>
       <c r="D302" s="6" t="inlineStr">
         <is>
-          <t>Summer Games: Software Developer Intern; Summer Games: Data Scientist Intern; Summer Games: Systems Engineering Intern; Summer Games: Cybersecurity Intern; Summer Hire: Engineering / Technical  (5 of 6 tracks)</t>
+          <t>Quantitative Trader – Intern; Quantitative Research Analyst – Intern (BS/MS); Quantitative Researcher – PhD Intern; Software Engineer – Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E302" s="7" t="inlineStr">
         <is>
-          <t>careers.boozallen.com/</t>
+          <t>citadel.com/careers/internships/</t>
         </is>
       </c>
       <c r="F302" s="7" t="inlineStr">
@@ -17377,34 +17381,30 @@
       </c>
       <c r="G302" s="6" t="inlineStr">
         <is>
-          <t>Two rounds over roughly four to six weeks. First, a 30-minute recruiter phone or video screen focused on your resume and motivation. Then one to two team interviews with client-facing consultants, heavily behavioral with some technical questions. Glassdoor rates difficulty at 2.4 out of 5.</t>
-        </is>
-      </c>
-      <c r="H302" s="6" t="inlineStr">
-        <is>
-          <t>Almost never. The majority of roles require US citizenship for government security clearance eligibility. Non-US citizens cannot obtain clearance</t>
-        </is>
-      </c>
+          <t>Expect an online assessment heavy on probability and coding, then a 45 to 60 minute technical video interview (CoderPad for quant research; Python and C++ are the core languages), then three to five technical-plus-behavioral interviews, followed by team matching across both firms. Trading candidates</t>
+        </is>
+      </c>
+      <c r="H302" s="6" t="inlineStr"/>
       <c r="I302" s="6" t="inlineStr">
         <is>
-          <t>Yes. Booz Allen reviews applications on a rolling basis starting in late August and continuing through the spring. Apply early in the cycle for the most open se</t>
+          <t>No official policy, but postings carry no deadlines and third-party trackers report ~70% of offers signed by mid-October. Treat it as rolling and apply week 1</t>
         </is>
       </c>
       <c r="J302" s="6" t="inlineStr">
         <is>
-          <t>$26 to $46 per hour depending on role, location, and degree level (Glassdoor, 194 salary reports). Levels.fyi reports $30/hr for SWE interns. No housing or relo</t>
+          <t>$4,500–$5,800/week base for SWE and quant trading interns (current JDs); $3,500–$4,000/week for FI&amp;M trading; plus sign-on bonus and ~$15,000 housing stipend or</t>
         </is>
       </c>
       <c r="K302" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: University Summer 2027 requisitions posting since August 28, 2026 (70 or more live as of September 28, 2026 across McLean, DC, Fayetteville, Beavercreek, Rome NY, Atlanta, Charleston SC, Huntsville AL, Honolulu, San Diego and El Segundo), Workday end dates from about December 2 to December 14, 2026; US citizenship required on cleared roles</t>
+          <t>Summer 2027 roles: LIVE NOW (rechecked October 15, 2026), no stated deadlines. Summer 2028: Equities Citadel Associate Program Summer Internship 2028 OPEN NOW (live October 15, 2026; the 2027 edition was already up by December 2025). Other summer 2028 roles: expected to post June–August 2027, most offers by October–November 2027 (projected)</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -17414,17 +17414,17 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>June–November 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>Quantitative Trader – Intern; Quantitative Research Analyst – Intern (BS/MS); Quantitative Researcher – PhD Intern; Software Engineer – Intern  (4 of 6 tracks)</t>
+          <t>InnoTech Software Engineering Intern; InnoTech Data Science &amp; Analytics Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E303" s="7" t="inlineStr">
         <is>
-          <t>citadel.com/careers/internships/</t>
+          <t>jobs.cvshealth.com/us/en/students</t>
         </is>
       </c>
       <c r="F303" s="7" t="inlineStr">
@@ -17434,30 +17434,34 @@
       </c>
       <c r="G303" s="6" t="inlineStr">
         <is>
-          <t>Expect an online assessment heavy on probability and coding, then a 45 to 60 minute technical video interview (CoderPad for quant research; Python and C++ are the core languages), then three to five technical-plus-behavioral interviews, followed by team matching across both firms. Trading candidates</t>
-        </is>
-      </c>
-      <c r="H303" s="6" t="inlineStr"/>
+          <t>You apply through Workday, complete a HireVue on-demand video assessment with behavioral questions, then have one or two live virtual interviews with hiring managers. Some tracks include a Superday with four to five 30-minute interviews. Decisions come within one to two weeks.</t>
+        </is>
+      </c>
+      <c r="H303" s="6" t="inlineStr">
+        <is>
+          <t>Limited. Select post-graduation Analytics, Data Science, and MBA roles may offer sponsorship. PharmD and niche cybersecurity roles may also qualify. Most internship tracks do not sponsor</t>
+        </is>
+      </c>
       <c r="I303" s="6" t="inlineStr">
         <is>
-          <t>No official policy, but postings carry no deadlines and third-party trackers report ~70% of offers signed by mid-October. Treat it as rolling and apply week 1</t>
+          <t>Yes. CVS Health reviews applications on a rolling basis. Apply in September or October for the best response rates</t>
         </is>
       </c>
       <c r="J303" s="6" t="inlineStr">
         <is>
-          <t>$4,500–$5,800/week base for SWE and quant trading interns (current JDs); $3,500–$4,000/week for FI&amp;M trading; plus sign-on bonus and ~$15,000 housing stipend or</t>
+          <t>$20 to $55 per hour depending on track. Undergraduate corporate roles around $23 to $28/hr; graduate and software engineering roles $45 to $55/hr. Housing stipe</t>
         </is>
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 roles: LIVE NOW (rechecked October 15, 2026), no stated deadlines. Summer 2028: Equities Citadel Associate Program Summer Internship 2028 OPEN NOW (live October 15, 2026; the 2027 edition was already up by December 2025). Other summer 2028 roles: expected to post June–August 2027, most offers by October–November 2027 (projected)</t>
+          <t>Open now for summer 2027: 37 Summer 2027 reqs posted September 2 to 9, 2026 (corporate Finance, Supply Chain &amp; Logistics, General Management, plus Retail Store Management in ~30 metros). No deadline: CVS accepts applications "on an ongoing basis" (one Finance req shows an October 31, 2026 end date). Prior cycles ran to March or until filled</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -17467,17 +17471,17 @@
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June–December 2027</t>
         </is>
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>InnoTech Software Engineering Intern; InnoTech Data Science &amp; Analytics Intern  (2 of 6 tracks)</t>
+          <t>SWE Intern (Product); SWE Intern (Developer Tools); SWE Intern (Infrastructure); Data Engineer / Data Scientist Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E304" s="7" t="inlineStr">
         <is>
-          <t>jobs.cvshealth.com/us/en/students</t>
+          <t>figma.com/careers/</t>
         </is>
       </c>
       <c r="F304" s="7" t="inlineStr">
@@ -17487,34 +17491,34 @@
       </c>
       <c r="G304" s="6" t="inlineStr">
         <is>
-          <t>You apply through Workday, complete a HireVue on-demand video assessment with behavioral questions, then have one or two live virtual interviews with hiring managers. Some tracks include a Superday with four to five 30-minute interviews. Decisions come within one to two weeks.</t>
+          <t>Figma's interview process spans 3 to 5 weeks with 4 to 6 rounds: a recruiter screen, a Byteboard technical assessment, a hiring manager interview, and a multi-session virtual onsite covering applied coding, system design, behavioral questions, and project deep-dives. For Product Design interns, a Ja</t>
         </is>
       </c>
       <c r="H304" s="6" t="inlineStr">
         <is>
-          <t>Limited. Select post-graduation Analytics, Data Science, and MBA roles may offer sponsorship. PharmD and niche cybersecurity roles may also qualify. Most internship tracks do not sponsor</t>
+          <t>Not explicitly stated in job descriptions. Figma is an equal opportunity employer with global offices in 12+ cities</t>
         </is>
       </c>
       <c r="I304" s="6" t="inlineStr">
         <is>
-          <t>Yes. CVS Health reviews applications on a rolling basis. Apply in September or October for the best response rates</t>
+          <t>Likely rolling with batch review. The SWE Intern (2026) listing was live Aug 29, 2025 to Jan 29, 2026, closing once filled</t>
         </is>
       </c>
       <c r="J304" s="6" t="inlineStr">
         <is>
-          <t>$20 to $55 per hour depending on track. Undergraduate corporate roles around $23 to $28/hr; graduate and software engineering roles $45 to $55/hr. Housing stipe</t>
+          <t>SWE intern NYC $60/hr ($10,400/mo), SF $51.06/hr ($8,850/mo). Plus $2,000/mo housing stipend, meals, travel reimbursement</t>
         </is>
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 37 Summer 2027 reqs posted September 2 to 9, 2026 (corporate Finance, Supply Chain &amp; Logistics, General Management, plus Retail Store Management in ~30 metros). No deadline: CVS accepts applications "on an ongoing basis" (one Finance req shows an October 31, 2026 end date). Prior cycles ran to March or until filled</t>
+          <t>OPEN NOW for summer 2027: Software Engineer Intern (Summer 2027), Brand Design Intern (Summer 2027), Product Design Intern (2027) and Data Science Intern (2027) posted September 14 to 15, 2026, plus Software Engineer Intern (Winter 2027). SF or New York hub, summer start dates May 3, May 17, June 1 or June 14, 2027. Rolling, no published deadline</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -17524,17 +17528,17 @@
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>June–December 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D305" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Product); SWE Intern (Developer Tools); SWE Intern (Infrastructure); Data Engineer / Data Scientist Intern  (4 of 5 tracks)</t>
+          <t>FOX Technology Internship Program  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E305" s="7" t="inlineStr">
         <is>
-          <t>figma.com/careers/</t>
+          <t>foxcareers.com/internships</t>
         </is>
       </c>
       <c r="F305" s="7" t="inlineStr">
@@ -17544,34 +17548,30 @@
       </c>
       <c r="G305" s="6" t="inlineStr">
         <is>
-          <t>Figma's interview process spans 3 to 5 weeks with 4 to 6 rounds: a recruiter screen, a Byteboard technical assessment, a hiring manager interview, and a multi-session virtual onsite covering applied coding, system design, behavioral questions, and project deep-dives. For Product Design interns, a Ja</t>
-        </is>
-      </c>
-      <c r="H305" s="6" t="inlineStr">
-        <is>
-          <t>Not explicitly stated in job descriptions. Figma is an equal opportunity employer with global offices in 12+ cities</t>
-        </is>
-      </c>
+          <t>First a resume and cover letter (state your top interest areas), then a pre-recorded one-way video interview, then a live hiring-manager interview. You must show knowledge of FOX and the media or sports industry. Decisions can arrive within about a week of the hiring-manager round, though silence be</t>
+        </is>
+      </c>
+      <c r="H305" s="6" t="inlineStr"/>
       <c r="I305" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling with batch review. The SWE Intern (2026) listing was live Aug 29, 2025 to Jan 29, 2026, closing once filled</t>
+          <t>Yes, partially. The official page states interns are accepted on a rolling basis for each term, with a hard deadline as the backstop. Apply early.</t>
         </is>
       </c>
       <c r="J305" s="6" t="inlineStr">
         <is>
-          <t>SWE intern NYC $60/hr ($10,400/mo), SF $51.06/hr ($8,850/mo). Plus $2,000/mo housing stipend, meals, travel reimbursement</t>
+          <t>$20.00/hour standard; disclosed corporate range $20.00–$30.00/hour. No housing or relocation provided. (Glassdoor/Indeed averages of ~$29–$35/hr blend in gradua</t>
         </is>
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027: Software Engineer Intern (Summer 2027), Brand Design Intern (Summer 2027), Product Design Intern (2027) and Data Science Intern (2027) posted September 14 to 15, 2026, plus Software Engineer Intern (Winter 2027). SF or New York hub, summer start dates May 3, May 17, June 1 or June 14, 2027. Rolling, no published deadline</t>
+          <t>For a summer 2027 role, applications are open now. FOX posted its Summer 2027 program reqs on September 28, 2026, and the postings we checked set a general application deadline of Sunday, January 10, 2027, with two sessions (June 7 to July 30, 2027 or June 21 to August 13, 2027). Spring 2027 reqs are also live, with a November 22, 2026 deadline.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Glean</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
@@ -17586,12 +17586,12 @@
       </c>
       <c r="D306" s="6" t="inlineStr">
         <is>
-          <t>FOX Technology Internship Program  (1 of 6 tracks)</t>
+          <t>SWE Intern: Backend &amp; Infrastructure; SWE Intern: ML / NLP / Search; SWE Intern: UI / Full-Stack; SWE Intern: Security  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E306" s="7" t="inlineStr">
         <is>
-          <t>foxcareers.com/internships</t>
+          <t>glean.com/careers</t>
         </is>
       </c>
       <c r="F306" s="7" t="inlineStr">
@@ -17601,30 +17601,34 @@
       </c>
       <c r="G306" s="6" t="inlineStr">
         <is>
-          <t>First a resume and cover letter (state your top interest areas), then a pre-recorded one-way video interview, then a live hiring-manager interview. You must show knowledge of FOX and the media or sports industry. Decisions can arrive within about a week of the hiring-manager round, though silence be</t>
-        </is>
-      </c>
-      <c r="H306" s="6" t="inlineStr"/>
+          <t>Glean's SWE intern interview is notably streamlined at just two rounds, shorter than most comparable companies: 1. Apply on glean.com/careers or the Greenhouse board . The Summer 2027 SWE intern posting is live now; submit in October. Tailor your resume to highlight backend, infrastructure, ML, or f</t>
+        </is>
+      </c>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>Glean files H-1B visas for full-time roles (9 LCAs in FY2026, median salary $210,000). CPT/OPT likely supported for interns based on past hiring patterns, though not explicitly confirmed</t>
+        </is>
+      </c>
       <c r="I306" s="6" t="inlineStr">
         <is>
-          <t>Yes, partially. The official page states interns are accepted on a rolling basis for each term, with a hard deadline as the backstop. Apply early.</t>
+          <t>Yes (effectively). Glean does not publish a hard deadline. Postings remain open until filled or the cohort is complete. Applying by October to November gives th</t>
         </is>
       </c>
       <c r="J306" s="6" t="inlineStr">
         <is>
-          <t>$20.00/hour standard; disclosed corporate range $20.00–$30.00/hour. No housing or relocation provided. (Glassdoor/Indeed averages of ~$29–$35/hr blend in gradua</t>
+          <t>$57 to $69 per hour ($10,000+/month) for SWE interns. Levels.fyi verified $57.69/hr for Summer 2025 with ~5% year-over-year increases. Housing stipend of $1,000</t>
         </is>
       </c>
       <c r="K306" s="6" t="inlineStr">
         <is>
-          <t>For a summer 2027 role, applications are open now. FOX posted its Summer 2027 program reqs on September 28, 2026, and the postings we checked set a general application deadline of Sunday, January 10, 2027, with two sessions (June 7 to July 30, 2027 or June 21 to August 13, 2027). Spring 2027 reqs are also live, with a November 22, 2026 deadline.</t>
+          <t>Open now for summer 2027: the Software Engineer, Intern (Summer 2027) listing is live on Greenhouse (updated October 2, 2026). No deadline is published; rolling review, and positions may close by December 2026 as the cohort fills</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>Glean</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -17639,12 +17643,12 @@
       </c>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern: Backend &amp; Infrastructure; SWE Intern: ML / NLP / Search; SWE Intern: UI / Full-Stack; SWE Intern: Security  (4 of 5 tracks)</t>
+          <t>Software Engineering Intern; General Engineering Intern (potential)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E307" s="7" t="inlineStr">
         <is>
-          <t>glean.com/careers</t>
+          <t>harvey.ai/careers</t>
         </is>
       </c>
       <c r="F307" s="7" t="inlineStr">
@@ -17654,34 +17658,34 @@
       </c>
       <c r="G307" s="6" t="inlineStr">
         <is>
-          <t>Glean's SWE intern interview is notably streamlined at just two rounds, shorter than most comparable companies: 1. Apply on glean.com/careers or the Greenhouse board . The Summer 2027 SWE intern posting is live now; submit in October. Tailor your resume to highlight backend, infrastructure, ML, or f</t>
+          <t>The intern tech screen is a 60-minute live coding session with a Harvey engineer, working through a real-world problem collaboratively. It is practical and applied rather than pure leetcode, and the Summer 2027 posting says the process includes AI-assisted coding sessions where you work with AI tool</t>
         </is>
       </c>
       <c r="H307" s="6" t="inlineStr">
         <is>
-          <t>Glean files H-1B visas for full-time roles (9 LCAs in FY2026, median salary $210,000). CPT/OPT likely supported for interns based on past hiring patterns, though not explicitly confirmed</t>
+          <t>H-1B sponsored for full-time roles (11 LCAs filed FY2026). Intern CPT/OPT plausible but not explicitly confirmed</t>
         </is>
       </c>
       <c r="I307" s="6" t="inlineStr">
         <is>
-          <t>Yes (effectively). Glean does not publish a hard deadline. Postings remain open until filled or the cohort is complete. Applying by October to November gives th</t>
+          <t>Yes. No fixed deadline. The Summer 2026 SWE intern listing was removed within roughly 3 months of posting. Apply in the first weeks for the best odds</t>
         </is>
       </c>
       <c r="J307" s="6" t="inlineStr">
         <is>
-          <t>$57 to $69 per hour ($10,000+/month) for SWE interns. Levels.fyi verified $57.69/hr for Summer 2025 with ~5% year-over-year increases. Housing stipend of $1,000</t>
+          <t>$62 to $72/hr in New York and San Francisco (summer 2027 posting); relocation support available. Earlier cycles: $60 to $65/hr plus a $1,666/month housing stipe</t>
         </is>
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: the Software Engineer, Intern (Summer 2027) listing is live on Greenhouse (updated October 2, 2026). No deadline is published; rolling review, and positions may close by December 2026 as the cohort fills</t>
+          <t>Summer 2027: open now. SWE intern roles posted 2 October 2026 (New York, San Francisco); rolling, no stated deadline. The summer 2026 listing came down within about 3 months</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
@@ -17696,12 +17700,12 @@
       </c>
       <c r="D308" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; General Engineering Intern (potential)  (2 of 4 tracks)</t>
+          <t>Engineering; IT/Data Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E308" s="7" t="inlineStr">
         <is>
-          <t>harvey.ai/careers</t>
+          <t>careers.honda.com/us/en/Students</t>
         </is>
       </c>
       <c r="F308" s="7" t="inlineStr">
@@ -17711,34 +17715,34 @@
       </c>
       <c r="G308" s="6" t="inlineStr">
         <is>
-          <t>The intern tech screen is a 60-minute live coding session with a Harvey engineer, working through a real-world problem collaboratively. It is practical and applied rather than pure leetcode, and the Summer 2027 posting says the process includes AI-assisted coding sessions where you work with AI tool</t>
+          <t>Honda’s hiring process is straightforward and shorter than many competitors, typically two to three steps: 1. Apply at careers.honda.com or connect via campus career fairs and Handshake. Browse co-op/internship openings and apply to the requisition matching your major and semester of interest. 2. Pr</t>
         </is>
       </c>
       <c r="H308" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsored for full-time roles (11 LCAs filed FY2026). Intern CPT/OPT plausible but not explicitly confirmed</t>
+          <t>No. Honda explicitly states: “Applicants requiring sponsorship for employment visa status now or in the future (e.g., F-1 CPT/OPT, H-1B, TN, etc.) will not be considered.” This is stricter than most automotive competitor</t>
         </is>
       </c>
       <c r="I308" s="6" t="inlineStr">
         <is>
-          <t>Yes. No fixed deadline. The Summer 2026 SWE intern listing was removed within roughly 3 months of posting. Apply in the first weeks for the best odds</t>
+          <t>Likely yes. Applications span 4–8 months per term, and Honda recruits continuously at campus events and through Handshake</t>
         </is>
       </c>
       <c r="J308" s="6" t="inlineStr">
         <is>
-          <t>$62 to $72/hr in New York and San Francisco (summer 2027 posting); relocation support available. Earlier cycles: $60 to $65/hr plus a $1,666/month housing stipe</t>
+          <t>$23 to $35/hr official range across tracks; engineering tops out at $35.22/hr, plus 1.5x overtime</t>
         </is>
       </c>
       <c r="K308" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027: open now. SWE intern roles posted 2 October 2026 (New York, San Francisco); rolling, no stated deadline. The summer 2026 listing came down within about 3 months</t>
+          <t>Open now: Summer 2027 Co-op/Intern postings for Engineering, IT/Data Analytics, Business, Environmental/Safety/Sustainability, Creative Design and Research, and Equipment Service are live on careers.honda.com (as of September 28, 2026); rolling review through about March or April 2027</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -17753,12 +17757,12 @@
       </c>
       <c r="D309" s="6" t="inlineStr">
         <is>
-          <t>Engineering; IT/Data Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineering; AI / Machine Learning  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E309" s="7" t="inlineStr">
         <is>
-          <t>careers.honda.com/us/en/Students</t>
+          <t>jobs.intel.com/</t>
         </is>
       </c>
       <c r="F309" s="7" t="inlineStr">
@@ -17768,34 +17772,34 @@
       </c>
       <c r="G309" s="6" t="inlineStr">
         <is>
-          <t>Honda’s hiring process is straightforward and shorter than many competitors, typically two to three steps: 1. Apply at careers.honda.com or connect via campus career fairs and Handshake. Browse co-op/internship openings and apply to the requisition matching your major and semester of interest. 2. Pr</t>
+          <t>Intel's hiring funnel is multi-stage but moves quickly once it starts, averaging about 23 days from application to offer according to Glassdoor data: 1. Apply at jobs.intel.com via the Workday portal. Submit a single-column resume (Workday ATS compatibility), apply to 5 to 8 positions across multipl</t>
         </is>
       </c>
       <c r="H309" s="6" t="inlineStr">
         <is>
-          <t>No. Honda explicitly states: “Applicants requiring sponsorship for employment visa status now or in the future (e.g., F-1 CPT/OPT, H-1B, TN, etc.) will not be considered.” This is stricter than most automotive competitor</t>
+          <t>All 13 Bachelor's and graduate program requisitions listed on October 11, 2026 state that the position is not eligible for employment-based visa/immigration sponsorship, and so do three of the 22 PhD-specific requisition</t>
         </is>
       </c>
       <c r="I309" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Applications span 4–8 months per term, and Honda recruits continuously at campus events and through Handshake</t>
+          <t>Yes. Positions fill individually; no single hard deadline. Apply as soon as a role posts for priority consideration</t>
         </is>
       </c>
       <c r="J309" s="6" t="inlineStr">
         <is>
-          <t>$23 to $35/hr official range across tracks; engineering tops out at $35.22/hr, plus 1.5x overtime</t>
+          <t>$67.5K–$171K/yr, printed as annual salary ranges on the US intern requisitions for Bachelor's, Master's and PhD students listed October 11, 2026 (the Bachelor's</t>
         </is>
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>Open now: Summer 2027 Co-op/Intern postings for Engineering, IT/Data Analytics, Business, Environmental/Safety/Sustainability, Creative Design and Research, and Equipment Service are live on careers.honda.com (as of September 28, 2026); rolling review through about March or April 2027</t>
+          <t>Open now for summer 2027: seven Bachelor's and six graduate program requisitions for Spring and Summer 2027 starts were listed on Intel's Workday board on October 11, 2026. Also listed that day: an AI Solution Architect undergraduate intern requisition in Hillsboro (posted October 7, 2026), 22 PhD-specific US intern requisitions and four Master's-specific ones. The program requisitions carry posti</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -17805,17 +17809,17 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; AI / Machine Learning  (2 of 6 tracks)</t>
+          <t>Engineering; Software Engineering; Cybersecurity  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E310" s="7" t="inlineStr">
         <is>
-          <t>jobs.intel.com/</t>
+          <t>lockheedmartin.eightfold.ai/careers?query=intern&amp;amp;locatio</t>
         </is>
       </c>
       <c r="F310" s="7" t="inlineStr">
@@ -17825,34 +17829,30 @@
       </c>
       <c r="G310" s="6" t="inlineStr">
         <is>
-          <t>Intel's hiring funnel is multi-stage but moves quickly once it starts, averaging about 23 days from application to offer according to Glassdoor data: 1. Apply at jobs.intel.com via the Workday portal. Submit a single-column resume (Workday ATS compatibility), apply to 5 to 8 positions across multipl</t>
-        </is>
-      </c>
-      <c r="H310" s="6" t="inlineStr">
-        <is>
-          <t>All 13 Bachelor's and graduate program requisitions listed on October 11, 2026 state that the position is not eligible for employment-based visa/immigration sponsorship, and so do three of the 22 PhD-specific requisition</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Lockheed Martin's interview process averages about 31 days from application to offer, with a Glassdoor difficulty rating of 2.6 out of 5. Here's what to expect: 1. Create a profile on lockheedmartin.eightfold.ai (Lockheed's careers portal). Search for intern positions by business area, location, or </t>
+        </is>
+      </c>
+      <c r="H310" s="6" t="inlineStr"/>
       <c r="I310" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions fill individually; no single hard deadline. Apply as soon as a role posts for priority consideration</t>
+          <t>Yes. Individual postings close after 90 days or when the applicant pool is sufficient. Apply within 5–30 days of posting for optimal consideration</t>
         </is>
       </c>
       <c r="J310" s="6" t="inlineStr">
         <is>
-          <t>$67.5K–$171K/yr, printed as annual salary ranges on the US intern requisitions for Bachelor's, Master's and PhD students listed October 11, 2026 (the Bachelor's</t>
+          <t>$22–$40/hr depending on role and level. SWE interns up to $40/hr; mechanical at $32.50/hr. Housing stipend $850–$5,500/month</t>
         </is>
       </c>
       <c r="K310" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: seven Bachelor's and six graduate program requisitions for Spring and Summer 2027 starts were listed on Intel's Workday board on October 11, 2026. Also listed that day: an AI Solution Architect undergraduate intern requisition in Hillsboro (posted October 7, 2026), 22 PhD-specific US intern requisitions and four Master's-specific ones. The program requisitions carry posti</t>
+          <t>Open now: summer 2027 college intern requisitions posted September 14 to 23, 2026 (finance, contracts, proposal, embedded software, cybersecurity, radar and electronics engineering); rolling through spring</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -17862,17 +17862,17 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D311" s="6" t="inlineStr">
         <is>
-          <t>Engineering; Software Engineering; Cybersecurity  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern (Exploratory SWE / Tech Launchpad); Data Analytics / Data Science Intern (Tech Launchpad)  (2 of 5 tracks)</t>
         </is>
       </c>
       <c r="E311" s="7" t="inlineStr">
         <is>
-          <t>lockheedmartin.eightfold.ai/careers?query=intern&amp;amp;locatio</t>
+          <t>talent.lowes.com/us/en/internships</t>
         </is>
       </c>
       <c r="F311" s="7" t="inlineStr">
@@ -17882,30 +17882,30 @@
       </c>
       <c r="G311" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lockheed Martin's interview process averages about 31 days from application to offer, with a Glassdoor difficulty rating of 2.6 out of 5. Here's what to expect: 1. Create a profile on lockheedmartin.eightfold.ai (Lockheed's careers portal). Search for intern positions by business area, location, or </t>
+          <t>Lowe's does not officially publish its intern interview process, so the steps below combine the official portal and rolling-review facts with community-reported detail (third-party, labeled). Tech and business tracks diverge at the final rounds. 1. Apply through the official portal. Go to talent.low</t>
         </is>
       </c>
       <c r="H311" s="6" t="inlineStr"/>
       <c r="I311" s="6" t="inlineStr">
         <is>
-          <t>Yes. Individual postings close after 90 days or when the applicant pool is sufficient. Apply within 5–30 days of posting for optimal consideration</t>
+          <t xml:space="preserve">Effectively yes. Official 2026 postings carried the standard Workday caveat that a role “may close before the stated closing date,” and prior-cycle third-party </t>
         </is>
       </c>
       <c r="J311" s="6" t="inlineStr">
         <is>
-          <t>$22–$40/hr depending on role and level. SWE interns up to $40/hr; mechanical at $32.50/hr. Housing stipend $850–$5,500/month</t>
+          <t>Paid, with eligibility for a Lowe's Housing Benefit and a 10% associate discount. Exact intern rate is not published on official postings. Community estimates p</t>
         </is>
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>Open now: summer 2027 college intern requisitions posted September 14 to 23, 2026 (finance, contracts, proposal, embedded software, cybersecurity, radar and electronics engineering); rolling through spring</t>
+          <t>Open now for Summer 2027. Lowe's began posting Summer 2027 undergrad internships on September 14, 2026 (Software Engineering, Digital Product Management, Merchandising, Store Operations, Private Brands and more), and the postings we checked list no closing date. Review is rolling, so apply as early as possible</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -17920,12 +17920,12 @@
       </c>
       <c r="D312" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Exploratory SWE / Tech Launchpad); Data Analytics / Data Science Intern (Tech Launchpad)  (2 of 5 tracks)</t>
+          <t>Refining Chemical Engineering; Midstream Engineering (MPLX)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E312" s="7" t="inlineStr">
         <is>
-          <t>talent.lowes.com/us/en/internships</t>
+          <t>mpc.wd1.myworkdayjobs.com/MPCCareers?workerSubType=762d3bc56</t>
         </is>
       </c>
       <c r="F312" s="7" t="inlineStr">
@@ -17935,30 +17935,34 @@
       </c>
       <c r="G312" s="6" t="inlineStr">
         <is>
-          <t>Lowe's does not officially publish its intern interview process, so the steps below combine the official portal and rolling-review facts with community-reported detail (third-party, labeled). Tech and business tracks diverge at the final rounds. 1. Apply through the official portal. Go to talent.low</t>
-        </is>
-      </c>
-      <c r="H312" s="6" t="inlineStr"/>
+          <t>After applying online, you may complete aptitude and personality assessments. If shortlisted, expect a phone screen with a recruiter followed by one or two interviews with the hiring manager and team members. Questions are primarily behavioral using the STAR method, with some technical questions for</t>
+        </is>
+      </c>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>No. Every MPC intern and co-op posting states that candidates must be authorized to work in the US on a full-time indefinite basis without the need for employment visa sponsorship now or in the future. This means interna</t>
+        </is>
+      </c>
       <c r="I312" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Effectively yes. Official 2026 postings carried the standard Workday caveat that a role “may close before the stated closing date,” and prior-cycle third-party </t>
+          <t>Not officially, but postings warn they "may close before the stated closing date" and encourage applying "as soon as possible"</t>
         </is>
       </c>
       <c r="J312" s="6" t="inlineStr">
         <is>
-          <t>Paid, with eligibility for a Lowe's Housing Benefit and a 10% associate discount. Exact intern rate is not published on official postings. Community estimates p</t>
+          <t>$20 to $42/hr depending on role; engineering interns $32-$42/hr; $4,500 relocation allowance</t>
         </is>
       </c>
       <c r="K312" s="6" t="inlineStr">
         <is>
-          <t>Open now for Summer 2027. Lowe's began posting Summer 2027 undergrad internships on September 14, 2026 (Software Engineering, Digital Product Management, Merchandising, Store Operations, Private Brands and more), and the postings we checked list no closing date. Review is rolling, so apply as early as possible</t>
+          <t>OPEN NOW. Summer 2027, Spring 2027, and Fall 2026 intern/co-op roles are live on MPC's Workday portal as of August 2026, including Finance, Accounting, and Supply Chain. Rolling review</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Nissan</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -17968,17 +17972,17 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–October 2027</t>
         </is>
       </c>
       <c r="D313" s="6" t="inlineStr">
         <is>
-          <t>Refining Chemical Engineering; Midstream Engineering (MPLX)  (2 of 6 tracks)</t>
+          <t>R&amp;D Engineering; Supply Chain Analytics; Software Engineering; Data Science / Analytics; Manufacturing / Process Engineering  (5 of 7 tracks)</t>
         </is>
       </c>
       <c r="E313" s="7" t="inlineStr">
         <is>
-          <t>mpc.wd1.myworkdayjobs.com/MPCCareers?workerSubType=762d3bc56</t>
+          <t>alliance.wd3.myworkdayjobs.com/en-US/nissanjobs</t>
         </is>
       </c>
       <c r="F313" s="7" t="inlineStr">
@@ -17988,34 +17992,34 @@
       </c>
       <c r="G313" s="6" t="inlineStr">
         <is>
-          <t>After applying online, you may complete aptitude and personality assessments. If shortlisted, expect a phone screen with a recruiter followed by one or two interviews with the hiring manager and team members. Questions are primarily behavioral using the STAR method, with some technical questions for</t>
+          <t>The process is relatively straightforward. After applying online, selected candidates have a recruiter phone or video screen, followed by an interview with the hiring manager (sometimes a panel of 2 to 3 people). Glassdoor rates the difficulty at 2.4 out of 5 for Nissan North America intern roles wi</t>
         </is>
       </c>
       <c r="H313" s="6" t="inlineStr">
         <is>
-          <t>No. Every MPC intern and co-op posting states that candidates must be authorized to work in the US on a full-time indefinite basis without the need for employment visa sponsorship now or in the future. This means interna</t>
+          <t>No. Multiple Nissan internship postings explicitly state no sponsorship. Candidates must be legally authorized to work in the United States without employer sponsorship. E-Verify is used to validate employment eligibilit</t>
         </is>
       </c>
       <c r="I313" s="6" t="inlineStr">
         <is>
-          <t>Not officially, but postings warn they "may close before the stated closing date" and encourage applying "as soon as possible"</t>
+          <t>Likely yes. Positions are removed as they fill; last cycle's postings came down by mid-October</t>
         </is>
       </c>
       <c r="J313" s="6" t="inlineStr">
         <is>
-          <t>$20 to $42/hr depending on role; engineering interns $32-$42/hr; $4,500 relocation allowance</t>
+          <t>$21–$28/hr reported range; top-end $27.54/hr (Levels.fyi). Plus company car and potential housing</t>
         </is>
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027, Spring 2027, and Fall 2026 intern/co-op roles are live on MPC's Workday portal as of August 2026, including Finance, Accounting, and Supply Chain. Rolling review</t>
+          <t>Open now for summer 2027: 45 US intern postings titled Summer 2027 were listed on the Alliance Workday portal on October 11, 2026, most posted October 7 to 9, 2026. No closing date is printed on the postings.</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>Nissan</t>
+          <t>Old Mission</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -18025,17 +18029,17 @@
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>June–October 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D314" s="6" t="inlineStr">
         <is>
-          <t>R&amp;D Engineering; Supply Chain Analytics; Software Engineering; Data Science / Analytics; Manufacturing / Process Engineering  (5 of 7 tracks)</t>
+          <t>Software Engineer Intern (Summer); Quant Trader Micro-Intern (Winter); Quant Trader Graduate Program; SWE Graduate Program (August)</t>
         </is>
       </c>
       <c r="E314" s="7" t="inlineStr">
         <is>
-          <t>alliance.wd3.myworkdayjobs.com/en-US/nissanjobs</t>
+          <t>oldmissioncapital.com/careers/</t>
         </is>
       </c>
       <c r="F314" s="7" t="inlineStr">
@@ -18045,34 +18049,34 @@
       </c>
       <c r="G314" s="6" t="inlineStr">
         <is>
-          <t>The process is relatively straightforward. After applying online, selected candidates have a recruiter phone or video screen, followed by an interview with the hiring manager (sometimes a panel of 2 to 3 people). Glassdoor rates the difficulty at 2.4 out of 5 for Nissan North America intern roles wi</t>
+          <t xml:space="preserve">You apply through Greenhouse, pass a resume screen, then complete a HackerRank OA (30 MCQs on CS fundamentals plus 2 coding problems, rated one of the hardest in the industry). If you advance, there is a phone/video interview and a final 2-hour in-person onsite at the Chicago office. Total process: </t>
         </is>
       </c>
       <c r="H314" s="6" t="inlineStr">
         <is>
-          <t>No. Multiple Nissan internship postings explicitly state no sponsorship. Candidates must be legally authorized to work in the United States without employer sponsorship. E-Verify is used to validate employment eligibilit</t>
+          <t>Yes. Ellis.com data shows Old Mission has filed H-1B visa sponsorship with a median salary of $162,500, suggesting openness to international students</t>
         </is>
       </c>
       <c r="I314" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Positions are removed as they fill; last cycle's postings came down by mid-October</t>
+          <t>Likely yes. Reddit reports candidates being rejected before completing their OA, suggesting continuous resume screening. The narrow window and small cohorts rew</t>
         </is>
       </c>
       <c r="J314" s="6" t="inlineStr">
         <is>
-          <t>$21–$28/hr reported range; top-end $27.54/hr (Levels.fyi). Plus company car and potential housing</t>
+          <t>SWE intern: $150,000 to $200,000 annualized ($2,885 to $3,846/week). Quant Trader micro-intern: $2,500/week (~$130K annualized). Free corporate housing and dail</t>
         </is>
       </c>
       <c r="K314" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 45 US intern postings titled Summer 2027 were listed on the Alliance Workday portal on October 11, 2026, most posted October 7 to 9, 2026. No closing date is printed on the postings.</t>
+          <t>Open now. SWE internship (summer 2027): posted July 15, 2026 and still live on October 6, 2026; no closing date published, closes when filled. Quant Trader Micro-Internship (January 2027): posted October 1, 2026</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>Old Mission</t>
+          <t>P&amp;G</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -18082,17 +18086,17 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–September 2027</t>
         </is>
       </c>
       <c r="D315" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Summer); Quant Trader Micro-Intern (Winter); Quant Trader Graduate Program; SWE Graduate Program (August)</t>
+          <t>Information Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E315" s="7" t="inlineStr">
         <is>
-          <t>oldmissioncapital.com/careers/</t>
+          <t>pgcareers.com/us/en/internships</t>
         </is>
       </c>
       <c r="F315" s="7" t="inlineStr">
@@ -18102,34 +18106,34 @@
       </c>
       <c r="G315" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">You apply through Greenhouse, pass a resume screen, then complete a HackerRank OA (30 MCQs on CS fundamentals plus 2 coding problems, rated one of the hardest in the industry). If you advance, there is a phone/video interview and a final 2-hour in-person onsite at the Chicago office. Total process: </t>
+          <t>P&amp;G's funnel is assessment-heavy and fast. The company estimates 4 to 8 weeks from application to offer, but the real gate is not the interview; it is the two-stage assessment battery that eliminates over 70 percent of applicants before any human reviews their file: 1. Apply at pgcareers.com . Creat</t>
         </is>
       </c>
       <c r="H315" s="6" t="inlineStr">
         <is>
-          <t>Yes. Ellis.com data shows Old Mission has filed H-1B visa sponsorship with a median salary of $162,500, suggesting openness to international students</t>
+          <t>It varies by role. Some postings (e.g., R&amp;D 2026) explicitly state immigration sponsorship is not available. Others do support it: P&amp;G filed 7 H1B labor condition applications in FY2025. For internships, CPT and OPT auth</t>
         </is>
       </c>
       <c r="I315" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. Reddit reports candidates being rejected before completing their OA, suggesting continuous resume screening. The narrow window and small cohorts rew</t>
+          <t>Yes. Positions fill before posted deadlines. First-come advantage is real</t>
         </is>
       </c>
       <c r="J315" s="6" t="inlineStr">
         <is>
-          <t>SWE intern: $150,000 to $200,000 annualized ($2,885 to $3,846/week). Quant Trader micro-intern: $2,500/week (~$130K annualized). Free corporate housing and dail</t>
+          <t>$29 to $50 per hour depending on track (R&amp;D and engineering at the top; ~$35/hr IT and data science)</t>
         </is>
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>Open now. SWE internship (summer 2027): posted July 15, 2026 and still live on October 6, 2026; no closing date published, closes when filled. Quant Trader Micro-Internship (January 2027): posted October 1, 2026</t>
+          <t>Open now. Summer 2027 US internship reqs live on P&amp;G's Workday board since August 24, 2026 (Cincinnati wave) with R&amp;D PhD reqs added September 11 to 18; no posting end date listed, rolling review (confirmed Sep 21, 2026)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>P&amp;G</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -18139,17 +18143,17 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>June–September 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>Information Technology  (1 of 6 tracks)</t>
+          <t>Mechanical Engineering Intern / Product Engineering Co-Op (primary); Manufacturing / Manufacturing &amp; Production Engineering Intern; Aerospace / Electromechanical (NVH) Engineering Intern (ITAR)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>pgcareers.com/us/en/internships</t>
+          <t>parkercareers.ttcportals.com/search/students/jobs</t>
         </is>
       </c>
       <c r="F316" s="7" t="inlineStr">
@@ -18159,34 +18163,34 @@
       </c>
       <c r="G316" s="6" t="inlineStr">
         <is>
-          <t>P&amp;G's funnel is assessment-heavy and fast. The company estimates 4 to 8 weeks from application to offer, but the real gate is not the interview; it is the two-stage assessment battery that eliminates over 70 percent of applicants before any human reviews their file: 1. Apply at pgcareers.com . Creat</t>
+          <t>Mostly behavioral. Expect a recruiter phone call to schedule, then a one-on-one (sometimes panel) interview focused on character, work ethic, and teamwork, plus a role overview and occasionally a facility walkthrough. Difficulty is rated "average" (2.9/5), about 75% of candidates report a positive e</t>
         </is>
       </c>
       <c r="H316" s="6" t="inlineStr">
         <is>
-          <t>It varies by role. Some postings (e.g., R&amp;D 2026) explicitly state immigration sponsorship is not available. Others do support it: P&amp;G filed 7 H1B labor condition applications in FY2025. For internships, CPT and OPT auth</t>
+          <t>Not indicated. Most engineering intern postings limit eligibility to US Citizen or US Permanent Resident, with no international sponsorship stated for those reqs. Aerospace/defense tracks add an ITAR/EAR restriction (see</t>
         </is>
       </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions fill before posted deadlines. First-come advantage is real</t>
+          <t>Yes, effectively rolling and continuous. Parker held 44 concurrent student reqs on Aug 6, 2026, each with its own deadline. Many carry the note "this job may cl</t>
         </is>
       </c>
       <c r="J316" s="6" t="inlineStr">
         <is>
-          <t>$29 to $50 per hour depending on track (R&amp;D and engineering at the top; ~$35/hr IT and data science)</t>
+          <t>No single official company-wide rate; pay is set per division. One Parker HR intern posting listed $19 to $31/hr (employer-provided). Community data (Glassdoor,</t>
         </is>
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>Open now. Summer 2027 US internship reqs live on P&amp;G's Workday board since August 24, 2026 (Cincinnati wave) with R&amp;D PhD reqs added September 11 to 18; no posting end date listed, rolling review (confirmed Sep 21, 2026)</t>
+          <t>Open now, division by division. Summer 2027 reqs have been posting since September 9, 2026 (Chemical Engineering, Applications Engineering, Accounting, Regulatory Compliance, NVH Engineering and more); 56 US student roles were live on October 6, 2026. Each req has its own deadline; priority deadlines around December 2026 to January 2027 (expected). Prior cycle anchor: a Summer/Spring 2026 ME inter</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -18201,12 +18205,12 @@
       </c>
       <c r="D317" s="6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern / Product Engineering Co-Op (primary); Manufacturing / Manufacturing &amp; Production Engineering Intern; Aerospace / Electromechanical (NVH) Engineering Intern (ITAR)  (3 of 6 tracks)</t>
+          <t>Software Engineering; Master's Machine Learning; PhD Machine Learning (ATG); Data Science; UX Quantitative Research; IT Software Engineering</t>
         </is>
       </c>
       <c r="E317" s="7" t="inlineStr">
         <is>
-          <t>parkercareers.ttcportals.com/search/students/jobs</t>
+          <t>pinterestcareers.com/early-career/university-recruiting/</t>
         </is>
       </c>
       <c r="F317" s="7" t="inlineStr">
@@ -18216,34 +18220,30 @@
       </c>
       <c r="G317" s="6" t="inlineStr">
         <is>
-          <t>Mostly behavioral. Expect a recruiter phone call to schedule, then a one-on-one (sometimes panel) interview focused on character, work ethic, and teamwork, plus a role overview and occasionally a facility walkthrough. Difficulty is rated "average" (2.9/5), about 75% of candidates report a positive e</t>
-        </is>
-      </c>
-      <c r="H317" s="6" t="inlineStr">
-        <is>
-          <t>Not indicated. Most engineering intern postings limit eligibility to US Citizen or US Permanent Resident, with no international sponsorship stated for those reqs. Aerospace/defense tracks add an ITAR/EAR restriction (see</t>
-        </is>
-      </c>
+          <t>It is lean. You apply, take the CodeSignal General Coding Assessment (scored out of 600), do a 30-minute recruiter screen, then one 1-hour technical interview before a hiring committee decides. That is a single live technical round, versus the three or four a new grad faces. It is CodeSignal, not Ha</t>
+        </is>
+      </c>
+      <c r="H317" s="6" t="inlineStr"/>
       <c r="I317" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling and continuous. Parker held 44 concurrent student reqs on Aug 6, 2026, each with its own deadline. Many carry the note "this job may cl</t>
+          <t>Yes. The summer 2027 reqs opened October 1, 2026 and fill rolling through the August-to-April peak season</t>
         </is>
       </c>
       <c r="J317" s="6" t="inlineStr">
         <is>
-          <t>No single official company-wide rate; pay is set per division. One Parker HR intern posting listed $19 to $31/hr (employer-provided). Community data (Glassdoor,</t>
+          <t>Official 2027 postings: SWE and UX Engineering $8,250 to $11,000/mo; Master's ML and Data Science $11,000/mo; PhD ML and Data Science $12,100/mo</t>
         </is>
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>Open now, division by division. Summer 2027 reqs have been posting since September 9, 2026 (Chemical Engineering, Applications Engineering, Accounting, Regulatory Compliance, NVH Engineering and more); 56 US student roles were live on October 6, 2026. Each req has its own deadline; priority deadlines around December 2026 to January 2027 (expected). Prior cycle anchor: a Summer/Spring 2026 ME inter</t>
+          <t>OPEN NOW. Summer 2027 US intern reqs went live on pinterestcareers.com on October 1, 2026 (Software Engineer, Master's and PhD Machine Learning, Master's and PhD Data Science, UX Engineering, UX Quantitative Research). No deadline posted; review is rolling</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -18258,12 +18258,12 @@
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Master's Machine Learning; PhD Machine Learning (ATG); Data Science; UX Quantitative Research; IT Software Engineering</t>
+          <t>Software Engineering; Technical Game Design; Research Scientist (AI)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E318" s="7" t="inlineStr">
         <is>
-          <t>pinterestcareers.com/early-career/university-recruiting/</t>
+          <t>riotgames.com/en/work-with-us/jobs</t>
         </is>
       </c>
       <c r="F318" s="7" t="inlineStr">
@@ -18273,30 +18273,30 @@
       </c>
       <c r="G318" s="6" t="inlineStr">
         <is>
-          <t>It is lean. You apply, take the CodeSignal General Coding Assessment (scored out of 600), do a 30-minute recruiter screen, then one 1-hour technical interview before a hiring committee decides. That is a single live technical round, versus the three or four a new grad faces. It is CodeSignal, not Ha</t>
+          <t xml:space="preserve">For SWE: a HackerRank OA (2 hours, 4 to 5 medium LeetCode problems), then 3 to 4 remote interviews over about 3 weeks testing technical skills, behavioral alignment, and culture fit. Creative tracks get take-home craft tests instead of the OA. Average time from application to decision is roughly 70 </t>
         </is>
       </c>
       <c r="H318" s="6" t="inlineStr"/>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>Yes. The summer 2027 reqs opened October 1, 2026 and fill rolling through the August-to-April peak season</t>
+          <t>Partially. Review is rolling within each deadline window; applying early is recommended</t>
         </is>
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
-          <t>Official 2027 postings: SWE and UX Engineering $8,250 to $11,000/mo; Master's ML and Data Science $11,000/mo; PhD ML and Data Science $12,100/mo</t>
+          <t>$56.59/hr SWE; $35–$43/hr non-engineering; ~$2K/mo housing stipend</t>
         </is>
       </c>
       <c r="K318" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 US intern reqs went live on pinterestcareers.com on October 1, 2026 (Software Engineer, Master's and PhD Machine Learning, Master's and PhD Data Science, UX Engineering, UX Quantitative Research). No deadline posted; review is rolling</t>
+          <t>Open now for SWE: the summer 2027 Software Engineering Intern posting went live 1 October 2026 and closes November 6, 2026. Other tracks for summer 2027 not posted as of 6 October 2026; expected later this fall and open through about January 2027 (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -18311,12 +18311,12 @@
       </c>
       <c r="D319" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Technical Game Design; Research Scientist (AI)  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern; Machine Learning Research Intern; SEAL Research Scientist Intern; AI Builder Intern; Technical Advisor Intern (GenAI)  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E319" s="7" t="inlineStr">
         <is>
-          <t>riotgames.com/en/work-with-us/jobs</t>
+          <t>scale.com/careers/university</t>
         </is>
       </c>
       <c r="F319" s="7" t="inlineStr">
@@ -18326,30 +18326,34 @@
       </c>
       <c r="G319" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">For SWE: a HackerRank OA (2 hours, 4 to 5 medium LeetCode problems), then 3 to 4 remote interviews over about 3 weeks testing technical skills, behavioral alignment, and culture fit. Creative tracks get take-home craft tests instead of the OA. Average time from application to decision is roughly 70 </t>
-        </is>
-      </c>
-      <c r="H319" s="6" t="inlineStr"/>
+          <t>Typically: a recruiter screen, a HackerRank OA with 1-2 medium-hard coding problems in 60 minutes, then a final loop covering coding, system design, and behavioral questions. The system design round is reportedly the hardest, focusing on data pipelines and throughput at scale. Some intern candidates</t>
+        </is>
+      </c>
+      <c r="H319" s="6" t="inlineStr">
+        <is>
+          <t>Scale AI requires U.S. work authorization for most roles. The Technical Advisor track specifies 'fully remote within the U.S.' and public-sector roles may require security clearance. Scale doesn't explicitly confirm visa</t>
+        </is>
+      </c>
       <c r="I319" s="6" t="inlineStr">
         <is>
-          <t>Partially. Review is rolling within each deadline window; applying early is recommended</t>
+          <t>Yes. Scale AI reviews applications as they arrive; the Summer 2026 rolling deadline was September 30</t>
         </is>
       </c>
       <c r="J319" s="6" t="inlineStr">
         <is>
-          <t>$56.59/hr SWE; $35–$43/hr non-engineering; ~$2K/mo housing stipend</t>
+          <t>$60/hr (~$10,400/month) + $7,000 housing stipend + free meals (SF office)</t>
         </is>
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>Open now for SWE: the summer 2027 Software Engineering Intern posting went live 1 October 2026 and closes November 6, 2026. Other tracks for summer 2027 not posted as of 6 October 2026; expected later this fall and open through about January 2027 (projected from prior cycle)</t>
+          <t>Open now for summer 2027: Scale AI's Software Engineering Intern (Summer 2027) posting for San Francisco went live September 4, 2026 and was still listed on October 11, 2026. No deadline is printed on the posting, and no other US intern track was listed that day.</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -18359,17 +18363,17 @@
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–August 2027</t>
         </is>
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Machine Learning Research Intern; SEAL Research Scientist Intern; AI Builder Intern; Technical Advisor Intern (GenAI)  (5 of 6 tracks)</t>
+          <t>UTG Software Engineering; Machine Learning Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E320" s="7" t="inlineStr">
         <is>
-          <t>scale.com/careers/university</t>
+          <t>careers.servicenow.com/early-careers/</t>
         </is>
       </c>
       <c r="F320" s="7" t="inlineStr">
@@ -18379,34 +18383,34 @@
       </c>
       <c r="G320" s="6" t="inlineStr">
         <is>
-          <t>Typically: a recruiter screen, a HackerRank OA with 1-2 medium-hard coding problems in 60 minutes, then a final loop covering coding, system design, and behavioral questions. The system design round is reportedly the hardest, focusing on data pipelines and throughput at scale. Some intern candidates</t>
+          <t>Typically 3 to 5 stages: a HackerRank online assessment (60 to 105 minutes with MCQs and 2 to 3 coding problems), a recruiter phone screen (20 to 30 minutes), 2 to 3 technical video interviews covering DSA, OOP, OS, and project discussion, and a hiring manager behavioral round. Total timeline averag</t>
         </is>
       </c>
       <c r="H320" s="6" t="inlineStr">
         <is>
-          <t>Scale AI requires U.S. work authorization for most roles. The Technical Advisor track specifies 'fully remote within the U.S.' and public-sector roles may require security clearance. Scale doesn't explicitly confirm visa</t>
+          <t>F-1 CPT/OPT actively supported. STEM OPT extension approved for technical roles. H-1B sponsorship available at full-time conversion for high performers</t>
         </is>
       </c>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t>Yes. Scale AI reviews applications as they arrive; the Summer 2026 rolling deadline was September 30</t>
+          <t>Yes, confirmed. Applications reviewed rolling; priority given to the first 2 to 3 weeks after opening. Popular locations fill within 4 to 8 weeks</t>
         </is>
       </c>
       <c r="J320" s="6" t="inlineStr">
         <is>
-          <t>$60/hr (~$10,400/month) + $7,000 housing stipend + free meals (SF office)</t>
+          <t>SWE Bay Area $55.14 to $55.58/hr (~$9,558/month). San Diego $47 to $50/hr. Marketing $33.51/hr. Plus ~$5,000 housing stipend and up to $5,000 sign-on bonus</t>
         </is>
       </c>
       <c r="K320" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Scale AI's Software Engineering Intern (Summer 2027) posting for San Francisco went live September 4, 2026 and was still listed on October 11, 2026. No deadline is printed on the posting, and no other US intern track was listed that day.</t>
+          <t>Summer 2027 Finance Intern (Undergrad) open now in Santa Clara and West Palm Beach. Technical roles not yet posted as of October 1, 2026 (prior cycle opened early August); watch the board weekly</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -18416,17 +18420,17 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>June–August 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D321" s="6" t="inlineStr">
         <is>
-          <t>UTG Software Engineering; Machine Learning Engineering  (2 of 6 tracks)</t>
+          <t>Agent Engineering (Early Career); Software Engineer (General)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E321" s="7" t="inlineStr">
         <is>
-          <t>careers.servicenow.com/early-careers/</t>
+          <t>sierra.ai/early-career-program</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
@@ -18436,34 +18440,34 @@
       </c>
       <c r="G321" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 5 stages: a HackerRank online assessment (60 to 105 minutes with MCQs and 2 to 3 coding problems), a recruiter phone screen (20 to 30 minutes), 2 to 3 technical video interviews covering DSA, OOP, OS, and project discussion, and a hiring manager behavioral round. Total timeline averag</t>
+          <t>You apply, complete a take-home or online technical assessment, then attend in-person onsite interviews at a Sierra office. Onsites include coding rounds (LeetCode medium-to-hard), system design for AI agents, and behavioral questions aligned with Sierra's five values. Glassdoor rates the difficulty</t>
         </is>
       </c>
       <c r="H321" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT/OPT actively supported. STEM OPT extension approved for technical roles. H-1B sponsorship available at full-time conversion for high performers</t>
+          <t>Sierra sponsors visas but cannot guarantee sponsorship for every candidate. From their FAQ: 'We'll do our best to support your visa process.' Relocation assistance available</t>
         </is>
       </c>
       <c r="I321" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed rolling; priority given to the first 2 to 3 weeks after opening. Popular locations fill within 4 to 8 weeks</t>
+          <t>Yes. An earlier version of Sierra's FAQ said applications are reviewed on a rolling basis and added: 'We encourage you to apply early to avoid missing out.' Tha</t>
         </is>
       </c>
       <c r="J321" s="6" t="inlineStr">
         <is>
-          <t>SWE Bay Area $55.14 to $55.58/hr (~$9,558/month). San Diego $47 to $50/hr. Marketing $33.51/hr. Plus ~$5,000 housing stipend and up to $5,000 sign-on bonus</t>
+          <t xml:space="preserve">Estimated $55 to $75 per hour ($11,000 to $15,000/month) based on comparable AI startup benchmarks. Not confirmed by Sierra. Full-time SWE median total comp is </t>
         </is>
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 Finance Intern (Undergrad) open now in Santa Clara and West Palm Beach. Technical roles not yet posted as of October 1, 2026 (prior cycle opened early August); watch the board weekly</t>
+          <t>Open now for summer 2027: the Software Engineer Intern, Agent (Summer 2027) posting, dated August 31, 2026, was listed on Sierra's job board on October 11, 2026. No closing date is printed on the posting. Rolling review with interviews wrapping by December 2026, a timeline projected from the Fall 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -18478,12 +18482,12 @@
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
-          <t>Agent Engineering (Early Career); Software Engineer (General)  (2 of 4 tracks)</t>
+          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E322" s="7" t="inlineStr">
         <is>
-          <t>sierra.ai/early-career-program</t>
+          <t>job-boards.greenhouse.io/xai</t>
         </is>
       </c>
       <c r="F322" s="7" t="inlineStr">
@@ -18493,34 +18497,34 @@
       </c>
       <c r="G322" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a take-home or online technical assessment, then attend in-person onsite interviews at a Sierra office. Onsites include coding rounds (LeetCode medium-to-hard), system design for AI agents, and behavioral questions aligned with Sierra's five values. Glassdoor rates the difficulty</t>
+          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
         </is>
       </c>
       <c r="H322" s="6" t="inlineStr">
         <is>
-          <t>Sierra sponsors visas but cannot guarantee sponsorship for every candidate. From their FAQ: 'We'll do our best to support your visa process.' Relocation assistance available</t>
+          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
         </is>
       </c>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>Yes. An earlier version of Sierra's FAQ said applications are reviewed on a rolling basis and added: 'We encourage you to apply early to avoid missing out.' Tha</t>
+          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
         </is>
       </c>
       <c r="J322" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estimated $55 to $75 per hour ($11,000 to $15,000/month) based on comparable AI startup benchmarks. Not confirmed by Sierra. Full-time SWE median total comp is </t>
+          <t xml:space="preserve">Per the summer 2027 postings: software engineering $30/hr (freshman/sophomore), $34 (junior/senior), $36 to $40 (completed degrees); business operations $24.50 </t>
         </is>
       </c>
       <c r="K322" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: the Software Engineer Intern, Agent (Summer 2027) posting, dated August 31, 2026, was listed on Sierra's job board on October 11, 2026. No closing date is printed on the posting. Rolling review with interviews wrapping by December 2026, a timeline projected from the Fall 2026 cycle</t>
+          <t>Open now: Summer 2027 Software Engineering and Business Operations internships posted 2 October 2026 (Spring 2027 versions posted the same day). Rolling, no deadline published; positions close once filled</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -18530,17 +18534,17 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>September 2027 – February 2028</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
+          <t>Quality Engineering Intern; R&amp;D / Vehicle Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E323" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/xai</t>
+          <t>jobs.porsche.com</t>
         </is>
       </c>
       <c r="F323" s="7" t="inlineStr">
@@ -18550,34 +18554,34 @@
       </c>
       <c r="G323" s="6" t="inlineStr">
         <is>
-          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
+          <t>Expect one to two interview rounds: a phone or video screen covering your background and motivation, followed by a deeper behavioral interview or case study with the hiring manager. Porsche Consulting roles include two case studies. PCNA candidates report an average of 43 days from application to hi</t>
         </is>
       </c>
       <c r="H323" s="6" t="inlineStr">
         <is>
-          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
+          <t>Check each posting individually. PCNA roles typically require US work authorization. Porsche AG roles in Germany follow German student-visa rules</t>
         </is>
       </c>
       <c r="I323" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
+          <t>Yes. Porsche posts and fills internship roles on a rolling basis. Some roles stay open only weeks, so apply promptly when a posting appears</t>
         </is>
       </c>
       <c r="J323" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per the summer 2027 postings: software engineering $30/hr (freshman/sophomore), $34 (junior/senior), $36 to $40 (completed degrees); business operations $24.50 </t>
+          <t>$18 to $20 per hour on the PCNA intern postings live in October 2026 ($19 to $21 for a Porsche Design of America retail role in Costa Mesa). Indeed reports an a</t>
         </is>
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>Open now: Summer 2027 Software Engineering and Business Operations internships posted 2 October 2026 (Spring 2027 versions posted the same day). Rolling, no deadline published; positions close once filled</t>
+          <t>Open now: PCNA posted at least 10 intern roles between September 15 and 30, 2026, most running March to September 2027 (Accounting, Finance, Compliance, Aftersales Projects and Strategy, Digital Transformation and Data Intelligence), plus a Miami role running February to September 2027. More postings may follow through January 2027. Porsche AG recommends applying about six months before desired st</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Qatalyst Partners</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -18587,17 +18591,17 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>September 2027 – February 2028</t>
+          <t>September–October 2027</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>Quality Engineering Intern; R&amp;D / Vehicle Engineering Intern  (2 of 6 tracks)</t>
+          <t>1 track: Tech M&amp;A Summer Analyst. Qatalyst is a pure advisory firm with no separate S&amp;T, research, or capital markets divisions</t>
         </is>
       </c>
       <c r="E324" s="7" t="inlineStr">
         <is>
-          <t>jobs.porsche.com</t>
+          <t>app.joinhandshake.com/employers/qatalyst-partners-44145</t>
         </is>
       </c>
       <c r="F324" s="7" t="inlineStr">
@@ -18607,34 +18611,34 @@
       </c>
       <c r="G324" s="6" t="inlineStr">
         <is>
-          <t>Expect one to two interview rounds: a phone or video screen covering your background and motivation, followed by a deeper behavioral interview or case study with the hiring manager. Porsche Consulting roles include two case studies. PCNA candidates report an average of 43 days from application to hi</t>
+          <t>Qatalyst's funnel is compact and intense, typically spanning 2 to 3 weeks from first contact to offer: 1. Network before you apply (6+ months ahead). Identify 10 to 15 Qatalyst analysts and associates on LinkedIn, prioritizing university alumni. Conduct informational interviews in November to Decemb</t>
         </is>
       </c>
       <c r="H324" s="6" t="inlineStr">
         <is>
-          <t>Check each posting individually. PCNA roles typically require US work authorization. Porsche AG roles in Germany follow German student-visa rules</t>
+          <t>Not publicly confirmed. The firm recruits primarily from US universities; international students should contact uscareers@qatalyst.com directly</t>
         </is>
       </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>Yes. Porsche posts and fills internship roles on a rolling basis. Some roles stay open only weeks, so apply promptly when a posting appears</t>
+          <t>Semi-rolling. Positions fill on a rolling basis within the September-to-April window. The small class means spots disappear fast; apply when the portal opens</t>
         </is>
       </c>
       <c r="J324" s="6" t="inlineStr">
         <is>
-          <t>$18 to $20 per hour on the PCNA intern postings live in October 2026 ($19 to $21 for a Porsche Design of America retail role in Costa Mesa). Indeed reports an a</t>
+          <t>$110,000 to $120,000 annualized base (~$21,000 to $23,000 pro-rated for 10 weeks). Housing/relocation stipend included. Full-time Year 1 total comp: $225,000 to</t>
         </is>
       </c>
       <c r="K324" s="6" t="inlineStr">
         <is>
-          <t>Open now: PCNA posted at least 10 intern roles between September 15 and 30, 2026, most running March to September 2027 (Accounting, Finance, Compliance, Aftersales Projects and Strategy, Digital Transformation and Data Intelligence), plus a Miami role running February to September 2027. More postings may follow through January 2027. Porsche AG recommends applying about six months before desired st</t>
+          <t>Expected September to October 2027 for Summer 2028 roles. Interviews run January through March 2028, with most offers by late March. Projected from prior cycles. Summer 2027: US postings expected September to December 2026 (Adventis Finance); London 2027 internship open now</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Qatalyst Partners</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -18644,17 +18648,17 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>September–October 2027</t>
+          <t>December 2027</t>
         </is>
       </c>
       <c r="D325" s="6" t="inlineStr">
         <is>
-          <t>1 track: Tech M&amp;A Summer Analyst. Qatalyst is a pure advisory firm with no separate S&amp;T, research, or capital markets divisions</t>
+          <t>Agent Software Engineer Intern; Agent Software Engineer – New Grad (adjacent pipeline)  (2 of 3 tracks)</t>
         </is>
       </c>
       <c r="E325" s="7" t="inlineStr">
         <is>
-          <t>app.joinhandshake.com/employers/qatalyst-partners-44145</t>
+          <t>jobs.ashbyhq.com/decagon</t>
         </is>
       </c>
       <c r="F325" s="7" t="inlineStr">
@@ -18664,34 +18668,34 @@
       </c>
       <c r="G325" s="6" t="inlineStr">
         <is>
-          <t>Qatalyst's funnel is compact and intense, typically spanning 2 to 3 weeks from first contact to offer: 1. Network before you apply (6+ months ahead). Identify 10 to 15 Qatalyst analysts and associates on LinkedIn, prioritizing university alumni. Conduct informational interviews in November to Decemb</t>
+          <t>A recruiter screen, a 45- to 60-minute technical phone screen in TypeScript or Python, then a full-day on-site with coding pair, system design, project deep dive, and behavioral rounds. The entire process averages 13 days. Expect AI-agent-specific system design questions.</t>
         </is>
       </c>
       <c r="H325" s="6" t="inlineStr">
         <is>
-          <t>Not publicly confirmed. The firm recruits primarily from US universities; international students should contact uscareers@qatalyst.com directly</t>
+          <t>Full-time H-1B confirmed (11 LCAs in FY2026). Intern CPT/OPT not explicitly confirmed; likely supported given the University department classification</t>
         </is>
       </c>
       <c r="I325" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling. Positions fill on a rolling basis within the September-to-April window. The small class means spots disappear fast; apply when the portal opens</t>
+          <t xml:space="preserve">Likely yes. The Summer 2026 listing remained open for several months. Glassdoor reports a 13-day average hiring process, suggesting quick turnaround consistent </t>
         </is>
       </c>
       <c r="J325" s="6" t="inlineStr">
         <is>
-          <t>$110,000 to $120,000 annualized base (~$21,000 to $23,000 pro-rated for 10 weeks). Housing/relocation stipend included. Full-time Year 1 total comp: $225,000 to</t>
+          <t xml:space="preserve">$3,000/week (~$75/hr at 40 hours a week) plus a $10,000 housing stipend, as printed on the Engineering Intern (Summer 2027) posting listed on October 11, 2026. </t>
         </is>
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>Expected September to October 2027 for Summer 2028 roles. Interviews run January through March 2028, with most offers by late March. Projected from prior cycles. Summer 2027: US postings expected September to December 2026 (Adventis Finance); London 2027 internship open now</t>
+          <t>Open now for summer 2027: Decagon's Engineering Intern (Summer 2027) posting for San Francisco was listed on its Ashby board on October 11, 2026, with no closing date printed. Posted August 20, 2026. Rolling review is likely</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
@@ -18706,12 +18710,12 @@
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>Agent Software Engineer Intern; Agent Software Engineer – New Grad (adjacent pipeline)  (2 of 3 tracks)</t>
+          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E326" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/decagon</t>
+          <t>pepsicojobs.com/internshipsprograms</t>
         </is>
       </c>
       <c r="F326" s="7" t="inlineStr">
@@ -18721,54 +18725,50 @@
       </c>
       <c r="G326" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a 45- to 60-minute technical phone screen in TypeScript or Python, then a full-day on-site with coding pair, system design, project deep dive, and behavioral rounds. The entire process averages 13 days. Expect AI-agent-specific system design questions.</t>
-        </is>
-      </c>
-      <c r="H326" s="6" t="inlineStr">
-        <is>
-          <t>Full-time H-1B confirmed (11 LCAs in FY2026). Intern CPT/OPT not explicitly confirmed; likely supported given the University department classification</t>
-        </is>
-      </c>
+          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
+        </is>
+      </c>
+      <c r="H326" s="6" t="inlineStr"/>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Likely yes. The Summer 2026 listing remained open for several months. Glassdoor reports a 13-day average hiring process, suggesting quick turnaround consistent </t>
+          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
         </is>
       </c>
       <c r="J326" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$3,000/week (~$75/hr at 40 hours a week) plus a $10,000 housing stipend, as printed on the Engineering Intern (Summer 2027) posting listed on October 11, 2026. </t>
+          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
         </is>
       </c>
       <c r="K326" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Decagon's Engineering Intern (Summer 2027) posting for San Francisco was listed on its Ashby board on October 11, 2026, with no closing date printed. Posted August 20, 2026. Rolling review is likely</t>
+          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
-        </is>
-      </c>
-      <c r="B327" s="4" t="inlineStr">
-        <is>
-          <t>Window open - check now</t>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>December 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
+          <t>Media Tech Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E327" s="7" t="inlineStr">
         <is>
-          <t>pepsicojobs.com/internshipsprograms</t>
+          <t>jobs.comcast.com/early-career</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
@@ -18778,30 +18778,34 @@
       </c>
       <c r="G327" s="6" t="inlineStr">
         <is>
-          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
-        </is>
-      </c>
-      <c r="H327" s="6" t="inlineStr"/>
+          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
+        </is>
+      </c>
+      <c r="H327" s="6" t="inlineStr">
+        <is>
+          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
+        </is>
+      </c>
       <c r="I327" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
+          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
         </is>
       </c>
       <c r="J327" s="6" t="inlineStr">
         <is>
-          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
+          <t>Not published on Comcast's or NBCUniversal's own pages; check each posting</t>
         </is>
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
+          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -18811,17 +18815,17 @@
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>Media Tech Internship  (1 of 6 tracks)</t>
+          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E328" s="7" t="inlineStr">
         <is>
-          <t>jobs.comcast.com/early-career</t>
+          <t>deepmind.google/student-researcher-program/</t>
         </is>
       </c>
       <c r="F328" s="7" t="inlineStr">
@@ -18831,34 +18835,30 @@
       </c>
       <c r="G328" s="6" t="inlineStr">
         <is>
-          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
-        </is>
-      </c>
-      <c r="H328" s="6" t="inlineStr">
-        <is>
-          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
-        </is>
-      </c>
+          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr"/>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
+          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr">
         <is>
-          <t>Comcast SWE: $40/hr; NBCUniversal: $25/hr; sign-on bonus possible but not guaranteed</t>
+          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
         </is>
       </c>
       <c r="K328" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
+          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -18868,17 +18868,17 @@
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
+          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E329" s="7" t="inlineStr">
         <is>
-          <t>deepmind.google/student-researcher-program/</t>
+          <t>apply.workable.com/huggingface</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
@@ -18888,30 +18888,34 @@
       </c>
       <c r="G329" s="6" t="inlineStr">
         <is>
-          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
-        </is>
-      </c>
-      <c r="H329" s="6" t="inlineStr"/>
+          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
+        </is>
+      </c>
+      <c r="H329" s="6" t="inlineStr">
+        <is>
+          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
+        </is>
+      </c>
       <c r="I329" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
+          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
         </is>
       </c>
       <c r="J329" s="6" t="inlineStr">
         <is>
-          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
+          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
         </is>
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
+          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -18921,17 +18925,17 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – September 2027</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E330" s="7" t="inlineStr">
         <is>
-          <t>apply.workable.com/huggingface</t>
+          <t>jefferies.tal.net</t>
         </is>
       </c>
       <c r="F330" s="7" t="inlineStr">
@@ -18941,34 +18945,34 @@
       </c>
       <c r="G330" s="6" t="inlineStr">
         <is>
-          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
+          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
         </is>
       </c>
       <c r="H330" s="6" t="inlineStr">
         <is>
-          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
+          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
         </is>
       </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
+          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
         </is>
       </c>
       <c r="J330" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
+          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
         </is>
       </c>
       <c r="K330" s="6" t="inlineStr">
         <is>
-          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
+          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted. Still live as of October 2, 2026: 2027 Jefferies Finance Summer Analyst roles (Data Analytics; Financial Planning &amp; Accounting), the</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -18978,17 +18982,17 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – September 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>6+ tracks: KP LAUNCH, Business/IT, Research &amp; Evaluation, Community Health, Pharmacy, Administrative Fellowship, plus clinical placements</t>
         </is>
       </c>
       <c r="E331" s="7" t="inlineStr">
         <is>
-          <t>jefferies.tal.net</t>
+          <t>kaiserpermanentejobs.org/category/internships-jobs/641/48394</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -18998,34 +19002,34 @@
       </c>
       <c r="G331" s="6" t="inlineStr">
         <is>
-          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
+          <t>Glassdoor rates intern interviews at 2.7 out of 5 difficulty, and 72% of candidates report a positive experience. Expect a 30- to 45-minute interview with 6 to 8 questions, a mix of behavioral (STAR format) and role-specific. The tone is conversational. IT roles may include technical scenario questi</t>
         </is>
       </c>
       <c r="H331" s="6" t="inlineStr">
         <is>
-          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
+          <t>Not typically offered for internship programs. Applicants must provide proof of eligibility to work in the United States. CPT/OPT not explicitly confirmed for intern roles</t>
         </is>
       </c>
       <c r="I331" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
+          <t>Most tracks are not strictly rolling. KP LAUNCH and Business/IT have fixed windows with a single deadline. Research reviews after the close. Administrative Fell</t>
         </is>
       </c>
       <c r="J331" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
+          <t>$25.09–$29.16/hr for KP LAUNCH College interns, based on education year, as listed on the KP LAUNCH site on October 11, 2026. The one IT internship listed on ka</t>
         </is>
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted. Still live as of October 2, 2026: 2027 Jefferies Finance Summer Analyst roles (Data Analytics; Financial Planning &amp; Accounting), the</t>
+          <t>Varies by track. On October 11, 2026, no posting on kaiserpermanentejobs.org named summer 2027. KP LAUNCH: opens November 16, 2026 and closes January 8, 2027, per the KP LAUNCH site. Business/IT: expected January to April 2027. Research: expected February to March 2027. Administrative Fellowship: closed August 31, 2026 for programs starting in 2027. Business/IT and Research months follow Kaiser Pe</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Magna</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -19040,12 +19044,12 @@
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>6+ tracks: KP LAUNCH, Business/IT, Research &amp; Evaluation, Community Health, Pharmacy, Administrative Fellowship, plus clinical placements</t>
+          <t>Mechanical Engineering Intern (primary); Manufacturing / Process Engineering Intern; Software / Solution Engineering Intern; Engineering Co-Op  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E332" s="7" t="inlineStr">
         <is>
-          <t>kaiserpermanentejobs.org/category/internships-jobs/641/48394</t>
+          <t>magna.com/careers/students</t>
         </is>
       </c>
       <c r="F332" s="7" t="inlineStr">
@@ -19055,34 +19059,30 @@
       </c>
       <c r="G332" s="6" t="inlineStr">
         <is>
-          <t>Glassdoor rates intern interviews at 2.7 out of 5 difficulty, and 72% of candidates report a positive experience. Expect a 30- to 45-minute interview with 6 to 8 questions, a mix of behavioral (STAR format) and role-specific. The tone is conversational. IT roles may include technical scenario questi</t>
-        </is>
-      </c>
-      <c r="H332" s="6" t="inlineStr">
-        <is>
-          <t>Not typically offered for internship programs. Applicants must provide proof of eligibility to work in the United States. CPT/OPT not explicitly confirmed for intern roles</t>
-        </is>
-      </c>
+          <t>Rolling and division-run: a recruiter or HR screen, then a hiring-manager interview (often on-site at the plant), plus a role-specific technical round for engineering, data, and software candidates. Community reports describe it as conversational and project- and fundamentals-focused, not heavy on L</t>
+        </is>
+      </c>
+      <c r="H332" s="6" t="inlineStr"/>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>Most tracks are not strictly rolling. KP LAUNCH and Business/IT have fixed windows with a single deadline. Research reviews after the close. Administrative Fell</t>
+          <t>Yes. Intern and co-op reqs are posted and filled per-division on a rolling basis; there is no single company-wide deadline. Reqs close when filled, so apply ear</t>
         </is>
       </c>
       <c r="J332" s="6" t="inlineStr">
         <is>
-          <t>$25.09–$29.16/hr for KP LAUNCH College interns, based on education year, as listed on the KP LAUNCH site on October 11, 2026. The one IT internship listed on ka</t>
+          <t>An official Magna Powertrain engineering co-op JD lists $25/hour. Community aggregators put general intern pay around $18 to $34/hr (Indeed ~$20.54/hr; Glassdoo</t>
         </is>
       </c>
       <c r="K332" s="6" t="inlineStr">
         <is>
-          <t>Varies by track. On October 11, 2026, no posting on kaiserpermanentejobs.org named summer 2027. KP LAUNCH: opens November 16, 2026 and closes January 8, 2027, per the KP LAUNCH site. Business/IT: expected January to April 2027. Research: expected February to March 2027. Administrative Fellowship: closed August 31, 2026 for programs starting in 2027. Business/IT and Research months follow Kaiser Pe</t>
+          <t>Partly open. About 23 US intern and co-op reqs are live on Workday as of October 6, 2026 (Muncie IN Finance and Purchasing; Auburn Hills and Southfield engineering and IT; Troy humanoid robotics; Northwood OH and Grand Rapids co-ops; Holland, Holly and Bowling Green quality and IT; Highland Park program management and EHS), posted August to early October. Some earlier reqs have already closed, inc</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Magna</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -19092,17 +19092,17 @@
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern (primary); Manufacturing / Process Engineering Intern; Software / Solution Engineering Intern; Engineering Co-Op  (4 of 6 tracks)</t>
+          <t>Software Engineering Intern  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E333" s="7" t="inlineStr">
         <is>
-          <t>magna.com/careers/students</t>
+          <t>marqeta.com/company/careers</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
@@ -19112,30 +19112,34 @@
       </c>
       <c r="G333" s="6" t="inlineStr">
         <is>
-          <t>Rolling and division-run: a recruiter or HR screen, then a hiring-manager interview (often on-site at the plant), plus a role-specific technical round for engineering, data, and software candidates. Community reports describe it as conversational and project- and fundamentals-focused, not heavy on L</t>
-        </is>
-      </c>
-      <c r="H333" s="6" t="inlineStr"/>
+          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
+        </is>
+      </c>
+      <c r="H333" s="6" t="inlineStr">
+        <is>
+          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
+        </is>
+      </c>
       <c r="I333" s="6" t="inlineStr">
         <is>
-          <t>Yes. Intern and co-op reqs are posted and filled per-division on a rolling basis; there is no single company-wide deadline. Reqs close when filled, so apply ear</t>
+          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
         </is>
       </c>
       <c r="J333" s="6" t="inlineStr">
         <is>
-          <t>An official Magna Powertrain engineering co-op JD lists $25/hour. Community aggregators put general intern pay around $18 to $34/hr (Indeed ~$20.54/hr; Glassdoo</t>
+          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
         </is>
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>Partly open. About 23 US intern and co-op reqs are live on Workday as of October 6, 2026 (Muncie IN Finance and Purchasing; Auburn Hills and Southfield engineering and IT; Troy humanoid robotics; Northwood OH and Grand Rapids co-ops; Holland, Holly and Bowling Green quality and IT; Highland Park program management and EHS), posted August to early October. Some earlier reqs have already closed, inc</t>
+          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -19145,17 +19149,17 @@
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – January 2027</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern  (1 of 5 tracks)</t>
+          <t>Business — Analytics  (1 of 7 tracks)</t>
         </is>
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t>marqeta.com/company/careers</t>
+          <t>ogilvyearlycareers.com/the-summer-internship</t>
         </is>
       </c>
       <c r="F334" s="7" t="inlineStr">
@@ -19165,34 +19169,30 @@
       </c>
       <c r="G334" s="6" t="inlineStr">
         <is>
-          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
-        </is>
-      </c>
-      <c r="H334" s="6" t="inlineStr">
-        <is>
-          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
-        </is>
-      </c>
+          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
+        </is>
+      </c>
+      <c r="H334" s="6" t="inlineStr"/>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
+          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
         </is>
       </c>
       <c r="J334" s="6" t="inlineStr">
         <is>
-          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
+          <t>$20 to $25/hr posted range (2026 cycle)</t>
         </is>
       </c>
       <c r="K334" s="6" t="inlineStr">
         <is>
-          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
+          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -19202,17 +19202,17 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – January 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D335" s="6" t="inlineStr">
         <is>
-          <t>Business — Analytics  (1 of 7 tracks)</t>
+          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t>ogilvyearlycareers.com/the-summer-internship</t>
+          <t>ouraring.com/careers</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
@@ -19222,30 +19222,34 @@
       </c>
       <c r="G335" s="6" t="inlineStr">
         <is>
-          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
-        </is>
-      </c>
-      <c r="H335" s="6" t="inlineStr"/>
+          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
+        </is>
+      </c>
+      <c r="H335" s="6" t="inlineStr">
+        <is>
+          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
+        </is>
+      </c>
       <c r="I335" s="6" t="inlineStr">
         <is>
-          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
+          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
         </is>
       </c>
       <c r="J335" s="6" t="inlineStr">
         <is>
-          <t>$20 to $25/hr posted range (2026 cycle)</t>
+          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
         </is>
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
+          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B336" s="8" t="inlineStr">
@@ -19255,17 +19259,17 @@
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – March 2027</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
+          <t>Genentech Summer Internship; Genentech Research Intern (PhD); Genentech Co-Op  (3 of 7 tracks)</t>
         </is>
       </c>
       <c r="E336" s="7" t="inlineStr">
         <is>
-          <t>ouraring.com/careers</t>
+          <t>careers.roche.com/global/en/roche-internship-program</t>
         </is>
       </c>
       <c r="F336" s="7" t="inlineStr">
@@ -19275,34 +19279,30 @@
       </c>
       <c r="G336" s="6" t="inlineStr">
         <is>
-          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
-        </is>
-      </c>
-      <c r="H336" s="6" t="inlineStr">
-        <is>
-          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
-        </is>
-      </c>
+          <t xml:space="preserve">After applying, most candidates go through a phone or video screen (20 to 30 minutes) followed by one to three interviews mixing technical and behavioral questions. Some programs add an assessment center, group exercise, or presentation. The entire process averages about 42 days from application to </t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr"/>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
+          <t>Implied yes. Postings may close before stated deadlines and Genentech posts positions "on an ongoing basis"</t>
         </is>
       </c>
       <c r="J336" s="6" t="inlineStr">
         <is>
-          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
+          <t>Roche median $37/hr ($28–$49); Genentech median $35/hr ($28–$45); PhD AI/ML $40–$50/hr per official postings</t>
         </is>
       </c>
       <c r="K336" s="6" t="inlineStr">
         <is>
-          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
+          <t>Summer 2027 main wave expected Nov 2026–Mar 2027 (documented pattern; not yet posted). No Roche internship postings live in the US as of Oct 1, 2026; Genentech posts separately on careers.gene.com</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Analysis Group</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -19312,17 +19312,17 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – March 2027</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
         <is>
-          <t>Genentech Summer Internship; Genentech Research Intern (PhD); Genentech Co-Op  (3 of 7 tracks)</t>
+          <t>Data Science Intern (when available)  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E337" s="7" t="inlineStr">
         <is>
-          <t>careers.roche.com/global/en/roche-internship-program</t>
+          <t>analysisgroup.com/careers/career-path/summer-analyst-intern/</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
@@ -19332,30 +19332,34 @@
       </c>
       <c r="G337" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">After applying, most candidates go through a phone or video screen (20 to 30 minutes) followed by one to three interviews mixing technical and behavioral questions. Some programs add an assessment center, group exercise, or presentation. The entire process averages about 42 days from application to </t>
-        </is>
-      </c>
-      <c r="H337" s="6" t="inlineStr"/>
+          <t>Analysis Group's funnel is interview-focused with no standardized online assessment , and the average time from application to hire is about 23 days : 1. Apply on the Analysis Group careers portal . Upload your resume, cover letter (include geographic preferences for offices), and unofficial transcr</t>
+        </is>
+      </c>
+      <c r="H337" s="6" t="inlineStr">
+        <is>
+          <t>Yes, for consultant and data science positions. Not available for administrative roles</t>
+        </is>
+      </c>
       <c r="I337" s="6" t="inlineStr">
         <is>
-          <t>Implied yes. Postings may close before stated deadlines and Genentech posts positions "on an ongoing basis"</t>
+          <t>Applications are reviewed by the posted deadline. If no deadline is listed, review is rolling. Apply now for the strongest position: late Generalist and Account</t>
         </is>
       </c>
       <c r="J337" s="6" t="inlineStr">
         <is>
-          <t>Roche median $37/hr ($28–$49); Genentech median $35/hr ($28–$45); PhD AI/ML $40–$50/hr per official postings</t>
+          <t>Summer Analyst ~$1,750 to $2,100/week (~$35/hr annualized on Glassdoor), plus ~$1,500 sign-on bonus. Summer Associate ~$2,400 to $2,800/week</t>
         </is>
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 main wave expected Nov 2026–Mar 2027 (documented pattern; not yet posted). No Roche internship postings live in the US as of Oct 1, 2026; Genentech posts separately on careers.gene.com</t>
+          <t>Still open for Summer Analyst (2027 start): the Generalist and Accounting deadline of September 30, 2026 has passed, but both postings were live on October 2, 2026 and the firm keeps reviewing on a rolling basis, considering late applicants pending availability. Health Care (HEOR, Epidemiology &amp; Market Access) deadline: October 28, 2026. Summer Associate: expected December 2026 to March 2027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>Analysis Group</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B338" s="8" t="inlineStr">
@@ -19365,17 +19369,17 @@
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
         <is>
-          <t>Data Science Intern (when available)  (1 of 4 tracks)</t>
+          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E338" s="7" t="inlineStr">
         <is>
-          <t>analysisgroup.com/careers/career-path/summer-analyst-intern/</t>
+          <t>search.jobs.barclays/internships</t>
         </is>
       </c>
       <c r="F338" s="7" t="inlineStr">
@@ -19385,34 +19389,34 @@
       </c>
       <c r="G338" s="6" t="inlineStr">
         <is>
-          <t>Analysis Group's funnel is interview-focused with no standardized online assessment , and the average time from application to hire is about 23 days : 1. Apply on the Analysis Group careers portal . Upload your resume, cover letter (include geographic preferences for offices), and unofficial transcr</t>
+          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
         </is>
       </c>
       <c r="H338" s="6" t="inlineStr">
         <is>
-          <t>Yes, for consultant and data science positions. Not available for administrative roles</t>
+          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
         </is>
       </c>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>Applications are reviewed by the posted deadline. If no deadline is listed, review is rolling. Apply now for the strongest position: late Generalist and Account</t>
+          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
         </is>
       </c>
       <c r="J338" s="6" t="inlineStr">
         <is>
-          <t>Summer Analyst ~$1,750 to $2,100/week (~$35/hr annualized on Glassdoor), plus ~$1,500 sign-on bonus. Summer Associate ~$2,400 to $2,800/week</t>
+          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
         </is>
       </c>
       <c r="K338" s="6" t="inlineStr">
         <is>
-          <t>Still open for Summer Analyst (2027 start): the Generalist and Accounting deadline of September 30, 2026 has passed, but both postings were live on October 2, 2026 and the firm keeps reviewing on a rolling basis, considering late applicants pending availability. Health Care (HEOR, Epidemiology &amp; Market Access) deadline: October 28, 2026. Summer Associate: expected December 2026 to March 2027</t>
+          <t>Summer 2028 Summer Analyst (IB, Markets): not open yet, expected around December 2026 to February 2027, rolling. Summer 2027, still open on 15 October 2026: Technology Developer (Whippany, NJ), US Consumer Bank Analyst (Wilmington, DE) and Banking Associate for MBA students (New York, Chicago, San Francisco, Houston). The other US summer 2027 tracks (Operations, Compliance, Quantitative Finance As</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
@@ -19422,17 +19426,17 @@
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>December 2026 – January 2027</t>
         </is>
       </c>
       <c r="D339" s="6" t="inlineStr">
         <is>
-          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
+          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E339" s="7" t="inlineStr">
         <is>
-          <t>search.jobs.barclays/internships</t>
+          <t>jobs.citi.com/</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
@@ -19442,34 +19446,34 @@
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
+          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
         </is>
       </c>
       <c r="H339" s="6" t="inlineStr">
         <is>
-          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
+          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
         </is>
       </c>
       <c r="I339" s="6" t="inlineStr">
         <is>
-          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
+          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
         </is>
       </c>
       <c r="J339" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
+          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
         </is>
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>Summer 2028 Summer Analyst (IB, Markets): not open yet, expected around December 2026 to February 2027, rolling. Summer 2027, still open on 15 October 2026: Technology Developer (Whippany, NJ), US Consumer Bank Analyst (Wilmington, DE) and Banking Associate for MBA students (New York, Chicago, San Francisco, Houston). The other US summer 2027 tracks (Operations, Compliance, Quantitative Finance As</t>
+          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 18 US Summer Analyst requisitions live now on Citi's Workday board, confirmed September 21, 2026: Corporate Banking (Atlanta, Houston, San Francisco), Commercial Banking (Houston), Markets Sales and Trading and Quantitative Analysis (New York), Services (New York), Wealth (New York, Miami, Dallas, Los Angeles) and Risk, Internal Audit an</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B340" s="8" t="inlineStr">
@@ -19479,17 +19483,17 @@
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – January 2027</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
+          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E340" s="7" t="inlineStr">
         <is>
-          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
+          <t>careers.db.com/students-graduates/internship-programme/</t>
         </is>
       </c>
       <c r="F340" s="7" t="inlineStr">
@@ -19499,30 +19503,34 @@
       </c>
       <c r="G340" s="6" t="inlineStr">
         <is>
-          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
-        </is>
-      </c>
-      <c r="H340" s="6" t="inlineStr"/>
+          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
+        </is>
+      </c>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
+        </is>
+      </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
+          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
         </is>
       </c>
       <c r="J340" s="6" t="inlineStr">
         <is>
-          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
+          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
         </is>
       </c>
       <c r="K340" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to January 2027 for summer 2028; Corporate Functions deadlines extend through mid-2027 (documented pattern; not yet posted)</t>
+          <t>Partly open. Technology, Data and Innovation internship roles for 2027 went live in August 2026. IB (summer 2028) expected from about December 2026, rolling into spring 2027 (the first 2027 Summer Analyst application posted in December 2025, per Adventis Finance). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
@@ -19532,17 +19540,17 @@
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – January 2027</t>
+          <t>December 2026</t>
         </is>
       </c>
       <c r="D341" s="6" t="inlineStr">
         <is>
-          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
+          <t>ML / Data (SF)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E341" s="7" t="inlineStr">
         <is>
-          <t>jobs.citi.com/</t>
+          <t>strava.com/careers</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
@@ -19552,34 +19560,30 @@
       </c>
       <c r="G341" s="6" t="inlineStr">
         <is>
-          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
-        </is>
-      </c>
-      <c r="H341" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
-        </is>
-      </c>
+          <t>Strava does not publish a single official interview process, and it varies by track. The steps below combine the application flow from the jobs board with community-reported (paraphrased) round structure, so treat the interview specifics as directional: 1. Find and filter the reqs. Go to the Ashby b</t>
+        </is>
+      </c>
+      <c r="H341" s="6" t="inlineStr"/>
       <c r="I341" s="6" t="inlineStr">
         <is>
-          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
+          <t xml:space="preserve">Partially. Strava posts discipline-specific intern reqs (Web, Server, iOS, Android, ML) on separate timelines, each with its own "Deadline to Apply," and fills </t>
         </is>
       </c>
       <c r="J341" s="6" t="inlineStr">
         <is>
-          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
+          <t>$40.00/hour (stated directly on Strava intern JDs), plus a housing stipend to live in SF for the three-month summer (~$2,500/month per Levels.fyi). That works o</t>
         </is>
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 18 US Summer Analyst requisitions live now on Citi's Workday board, confirmed September 21, 2026: Corporate Banking (Atlanta, Houston, San Francisco), Commercial Banking (Houston), Markets Sales and Trading and Quantitative Analysis (New York), Services (New York), Wealth (New York, Miami, Dallas, Los Angeles) and Risk, Internal Audit an</t>
+          <t>Not yet published (expected). Applications for summer 2027 are expected to open in fall/winter 2026 with deadlines in late winter to spring 2027. Documented prior cycles: Summer 2025 (Web, SF) closed April 14, 2025; Summer 2026 (Server/Data Platform, SF) closed March 7, 2026</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Volkswagen</t>
         </is>
       </c>
       <c r="B342" s="8" t="inlineStr">
@@ -19594,12 +19598,12 @@
       </c>
       <c r="D342" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
+          <t>Engineering (Chattanooga); Purchasing/Value Engineering (Chattanooga)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E342" s="7" t="inlineStr">
         <is>
-          <t>careers.db.com/students-graduates/internship-programme/</t>
+          <t>careers.vw.com/go/Interns/8943400/</t>
         </is>
       </c>
       <c r="F342" s="7" t="inlineStr">
@@ -19609,54 +19613,50 @@
       </c>
       <c r="G342" s="6" t="inlineStr">
         <is>
-          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
-        </is>
-      </c>
-      <c r="H342" s="6" t="inlineStr">
-        <is>
-          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
-        </is>
-      </c>
+          <t>After applying on careers.vw.com, you will have a phone screening with an HR specialist, followed by a behavioral interview with the hiring manager. VW uses the BAR format: Background, Action, Result. Prepare specific examples of how you have handled challenges, and expect questions about teamwork a</t>
+        </is>
+      </c>
+      <c r="H342" s="6" t="inlineStr"/>
       <c r="I342" s="6" t="inlineStr">
         <is>
-          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
+          <t>Yes. VWGoA posts intern roles on a rolling basis and fills them as qualified candidates are identified</t>
         </is>
       </c>
       <c r="J342" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
+          <t>$20 to $35/hr depending on role and location; engineering and tech roles trend higher</t>
         </is>
       </c>
       <c r="K342" s="6" t="inlineStr">
         <is>
-          <t>Partly open. Technology, Data and Innovation internship roles for 2027 went live in August 2026. IB (summer 2028) expected from about December 2026, rolling into spring 2027 (the first 2027 Summer Analyst application posted in December 2025, per Adventis Finance). Rolling review</t>
+          <t>Expected December 2026 to March 2027 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="B343" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="B343" s="9" t="inlineStr">
+        <is>
+          <t>Later this cycle</t>
         </is>
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>December 2026</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D343" s="6" t="inlineStr">
         <is>
-          <t>ML / Data (SF)  (1 of 6 tracks)</t>
+          <t>Digital Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E343" s="7" t="inlineStr">
         <is>
-          <t>strava.com/careers</t>
+          <t>careers.adidas-group.com/teams/students/internships-students</t>
         </is>
       </c>
       <c r="F343" s="7" t="inlineStr">
@@ -19666,50 +19666,50 @@
       </c>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>Strava does not publish a single official interview process, and it varies by track. The steps below combine the application flow from the jobs board with community-reported (paraphrased) round structure, so treat the interview specifics as directional: 1. Find and filter the reqs. Go to the Ashby b</t>
+          <t>Adidas runs a multi-stage funnel that stretches from early January through March, roughly 8–10 weeks from application to offer: 1. Apply at careers.adidas-group.com during the one-week window (~January 1–8). Submit your resume plus the creative "1-Pager": a single-page PDF responding to a brand prom</t>
         </is>
       </c>
       <c r="H343" s="6" t="inlineStr"/>
       <c r="I343" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Strava posts discipline-specific intern reqs (Web, Server, iOS, Android, ML) on separate timelines, each with its own "Deadline to Apply," and fills </t>
+          <t>No. Fixed one-week cohort window. Roles can close early within the window once sufficient candidates apply</t>
         </is>
       </c>
       <c r="J343" s="6" t="inlineStr">
         <is>
-          <t>$40.00/hour (stated directly on Strava intern JDs), plus a housing stipend to live in SF for the three-month summer (~$2,500/month per Levels.fyi). That works o</t>
+          <t>$25–$45/hr (Glassdoor); ~$26/hr average (Indeed); some roles include a housing stipend</t>
         </is>
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>Not yet published (expected). Applications for summer 2027 are expected to open in fall/winter 2026 with deadlines in late winter to spring 2027. Documented prior cycles: Summer 2025 (Web, SF) closed April 14, 2025; Summer 2026 (Server/Data Platform, SF) closed March 7, 2026</t>
+          <t>Expected January 1–8, 2027 for summer 2027 (one-week fixed window; projected from 2026 cycle)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
-        </is>
-      </c>
-      <c r="B344" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>AppLovin</t>
+        </is>
+      </c>
+      <c r="B344" s="9" t="inlineStr">
+        <is>
+          <t>Later this cycle</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
         <is>
-          <t>Engineering (Chattanooga); Purchasing/Value Engineering (Chattanooga)  (2 of 6 tracks)</t>
+          <t>Software Engineering Intern (Ad Serving Platform); Data Scientist Intern; Mobile Software Engineering Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E344" s="7" t="inlineStr">
         <is>
-          <t>careers.vw.com/go/Interns/8943400/</t>
+          <t>applovin.com/en/careers</t>
         </is>
       </c>
       <c r="F344" s="7" t="inlineStr">
@@ -19719,30 +19719,34 @@
       </c>
       <c r="G344" s="6" t="inlineStr">
         <is>
-          <t>After applying on careers.vw.com, you will have a phone screening with an HR specialist, followed by a behavioral interview with the hiring manager. VW uses the BAR format: Background, Action, Result. Prepare specific examples of how you have handled challenges, and expect questions about teamwork a</t>
-        </is>
-      </c>
-      <c r="H344" s="6" t="inlineStr"/>
+          <t>A recruiter phone screen (15 to 30 minutes), a technical phone screen with LeetCode easy/medium problems (45 minutes), then a virtual onsite with two coding rounds, a Director interview, and a CTO interview. The process averages about 23 days. Glassdoor rates the SWE intern interview difficulty at 2</t>
+        </is>
+      </c>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>H-1B sponsored for full-time roles. F-1 students can participate via CPT. Job postings do not restrict to US citizens or permanent residents</t>
+        </is>
+      </c>
       <c r="I344" s="6" t="inlineStr">
         <is>
-          <t>Yes. VWGoA posts intern roles on a rolling basis and fills them as qualified candidates are identified</t>
+          <t>Yes, likely rolling. AppLovin does not publish fixed deadlines. The Summer 2025 SWE intern posting appeared in February 2025 and closed once filled. Apply early</t>
         </is>
       </c>
       <c r="J344" s="6" t="inlineStr">
         <is>
-          <t>$20 to $35/hr depending on role and location; engineering and tech roles trend higher</t>
+          <t>$60 to $80 per hour ($10,400 to $13,867/month) depending on role and cycle. Levels.fyi reports $60/hr for Summer 2024; the 2025 JD listed $70/hr base for CA/NY/</t>
         </is>
       </c>
       <c r="K344" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to March 2027 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Expected late January to February 2027 for summer 2027 roles. Rolling review until positions are filled, typically by March or April 2027. Projected from the 2025 cycle</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19752,17 +19756,17 @@
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D345" s="6" t="inlineStr">
         <is>
-          <t>Digital Analytics  (1 of 6 tracks)</t>
+          <t>BCG X Data Science  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E345" s="7" t="inlineStr">
         <is>
-          <t>careers.adidas-group.com/teams/students/internships-students</t>
+          <t>careers.bcg.com/global/en/internship-opportunities</t>
         </is>
       </c>
       <c r="F345" s="7" t="inlineStr">
@@ -19772,30 +19776,34 @@
       </c>
       <c r="G345" s="6" t="inlineStr">
         <is>
-          <t>Adidas runs a multi-stage funnel that stretches from early January through March, roughly 8–10 weeks from application to offer: 1. Apply at careers.adidas-group.com during the one-week window (~January 1–8). Submit your resume plus the creative "1-Pager": a single-page PDF responding to a brand prom</t>
-        </is>
-      </c>
-      <c r="H345" s="6" t="inlineStr"/>
+          <t>BCG's interview funnel has five stages, with the Casey chatbot as the unique gatekeeping step. The total process from application to offer averages 4 to 8 weeks (about 32 days per Glassdoor): 1. Apply at careers.bcg.com with a one-page resume, tailored cover letter, academic information (GPA, test s</t>
+        </is>
+      </c>
+      <c r="H345" s="6" t="inlineStr">
+        <is>
+          <t>Yes. BCG sponsors H-1B visas for full-time hires and is experienced with the sponsorship process. Summer interns typically work on CPT (Curricular Practical Training) authorization, with OPT and STEM-OPT extensions for f</t>
+        </is>
+      </c>
       <c r="I345" s="6" t="inlineStr">
         <is>
-          <t>No. Fixed one-week cohort window. Roles can close early within the window once sufficient candidates apply</t>
+          <t>No. BCG uses fixed deadline windows, but applying to the earlier deadline is strongly recommended because more interview spots remain open</t>
         </is>
       </c>
       <c r="J345" s="6" t="inlineStr">
         <is>
-          <t>$25–$45/hr (Glassdoor); ~$26/hr average (Indeed); some roles include a housing stipend</t>
+          <t>~$2,000–$2,500/week for undergraduate Summer Associate interns (~$20,000–$30,000 total summer)</t>
         </is>
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>Expected January 1–8, 2027 for summer 2027 (one-week fixed window; projected from 2026 cycle)</t>
+          <t>Expected portal open January–February 2027 and primary deadline around April 2027; final deadline August–September 2027 for summer 2028 (pattern-based projection; confirm on the official careers portal)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19805,17 +19813,17 @@
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D346" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Ad Serving Platform); Data Scientist Intern; Mobile Software Engineering Intern  (3 of 5 tracks)</t>
+          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E346" s="7" t="inlineStr">
         <is>
-          <t>applovin.com/en/careers</t>
+          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
         </is>
       </c>
       <c r="F346" s="7" t="inlineStr">
@@ -19825,34 +19833,30 @@
       </c>
       <c r="G346" s="6" t="inlineStr">
         <is>
-          <t>A recruiter phone screen (15 to 30 minutes), a technical phone screen with LeetCode easy/medium problems (45 minutes), then a virtual onsite with two coding rounds, a Director interview, and a CTO interview. The process averages about 23 days. Glassdoor rates the SWE intern interview difficulty at 2</t>
-        </is>
-      </c>
-      <c r="H346" s="6" t="inlineStr">
-        <is>
-          <t>H-1B sponsored for full-time roles. F-1 students can participate via CPT. Job postings do not restrict to US citizens or permanent residents</t>
-        </is>
-      </c>
+          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr"/>
       <c r="I346" s="6" t="inlineStr">
         <is>
-          <t>Yes, likely rolling. AppLovin does not publish fixed deadlines. The Summer 2025 SWE intern posting appeared in February 2025 and closed once filled. Apply early</t>
+          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
         </is>
       </c>
       <c r="J346" s="6" t="inlineStr">
         <is>
-          <t>$60 to $80 per hour ($10,400 to $13,867/month) depending on role and cycle. Levels.fyi reports $60/hr for Summer 2024; the 2025 JD listed $70/hr base for CA/NY/</t>
+          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
         </is>
       </c>
       <c r="K346" s="6" t="inlineStr">
         <is>
-          <t>Expected late January to February 2027 for summer 2027 roles. Rolling review until positions are filled, typically by March or April 2027. Projected from the 2025 cycle</t>
+          <t>Not posted yet for summer 2028 (checked October 17, 2026). Projected from mid-December 2026 for Global Banking and Global Markets, because the first 2027 Summer Analyst postings went up December 15 and 16, 2025; Corporate Functions roles followed from February to May 2026. Sophomores: the Open Sophomore Opportunity Summit (January 13 and 14, 2027) is taking applications now</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Cerebras</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19862,17 +19866,17 @@
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D347" s="6" t="inlineStr">
         <is>
-          <t>BCG X Data Science  (1 of 6 tracks)</t>
+          <t>Kernel Engineering Intern; Applied ML / ML Framework Intern; AI Cloud / Inference Service Intern; Hardware Engineering / CoDesign Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E347" s="7" t="inlineStr">
         <is>
-          <t>careers.bcg.com/global/en/internship-opportunities</t>
+          <t>cerebras.ai/internships</t>
         </is>
       </c>
       <c r="F347" s="7" t="inlineStr">
@@ -19882,34 +19886,34 @@
       </c>
       <c r="G347" s="6" t="inlineStr">
         <is>
-          <t>BCG's interview funnel has five stages, with the Casey chatbot as the unique gatekeeping step. The total process from application to offer averages 4 to 8 weeks (about 32 days per Glassdoor): 1. Apply at careers.bcg.com with a one-page resume, tailored cover letter, academic information (GPA, test s</t>
+          <t>Expect one to three rounds of 30 to 60 minutes each: a screening call with the hiring manager, a technical coding round with LeetCode-medium problems, and sometimes a domain-specific deep-technical round. The entire process typically completes in two to four weeks from posting to offer.</t>
         </is>
       </c>
       <c r="H347" s="6" t="inlineStr">
         <is>
-          <t>Yes. BCG sponsors H-1B visas for full-time hires and is experienced with the sponsorship process. Summer interns typically work on CPT (Curricular Practical Training) authorization, with OPT and STEM-OPT extensions for f</t>
+          <t>International students typically need CPT or OPT authorization. Cerebras sponsors H-1B for full-time roles (132 applications filed, $177K avg salary). Canadian interns in Toronto do not need a US visa</t>
         </is>
       </c>
       <c r="I347" s="6" t="inlineStr">
         <is>
-          <t>No. BCG uses fixed deadline windows, but applying to the earlier deadline is strongly recommended because more interview spots remain open</t>
+          <t>Yes. Cerebras uses rolling admissions and the process takes two to four weeks from posting to offer. Apply early in the January window</t>
         </is>
       </c>
       <c r="J347" s="6" t="inlineStr">
         <is>
-          <t>~$2,000–$2,500/week for undergraduate Summer Associate interns (~$20,000–$30,000 total summer)</t>
+          <t>Toronto: $30 to $36/hr CAD (Levels.fyi verified). US (Sunnyvale): estimated $45 to $55/hr USD (extrapolated; no verified US intern data). Daily catered lunch in</t>
         </is>
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>Expected portal open January–February 2027 and primary deadline around April 2027; final deadline August–September 2027 for summer 2028 (pattern-based projection; confirm on the official careers portal)</t>
+          <t>Summer 2027: expected January 2027 opening, rolling deadline through February–March 2027. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>Cerebras</t>
+          <t>Edelman</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19919,17 +19923,17 @@
       </c>
       <c r="C348" s="5" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
         <is>
-          <t>Kernel Engineering Intern; Applied ML / ML Framework Intern; AI Cloud / Inference Service Intern; Hardware Engineering / CoDesign Intern  (4 of 5 tracks)</t>
+          <t>Digital; Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E348" s="7" t="inlineStr">
         <is>
-          <t>cerebras.ai/internships</t>
+          <t>edelman.com/careers</t>
         </is>
       </c>
       <c r="F348" s="7" t="inlineStr">
@@ -19939,34 +19943,30 @@
       </c>
       <c r="G348" s="6" t="inlineStr">
         <is>
-          <t>Expect one to three rounds of 30 to 60 minutes each: a screening call with the hiring manager, a technical coding round with LeetCode-medium problems, and sometimes a domain-specific deep-technical round. The entire process typically completes in two to four weeks from posting to offer.</t>
-        </is>
-      </c>
-      <c r="H348" s="6" t="inlineStr">
-        <is>
-          <t>International students typically need CPT or OPT authorization. Cerebras sponsors H-1B for full-time roles (132 applications filed, $177K avg salary). Canadian interns in Toronto do not need a US visa</t>
-        </is>
-      </c>
+          <t>After applying through Workday, expect a phone or video screen with a recruiter, followed by one-on-one or panel interviews with team members. About 18% of candidates report a skills or writing test. Prepare to discuss why you want to work in PR, your writing experience, current events knowledge, an</t>
+        </is>
+      </c>
+      <c r="H348" s="6" t="inlineStr"/>
       <c r="I348" s="6" t="inlineStr">
         <is>
-          <t>Yes. Cerebras uses rolling admissions and the process takes two to four weeks from posting to offer. Apply early in the January window</t>
+          <t>Yes. Talent Acquisition reviews applications "on a rolling basis," but a firm deadline still applies (March 20 in the 2026 cycle)</t>
         </is>
       </c>
       <c r="J348" s="6" t="inlineStr">
         <is>
-          <t>Toronto: $30 to $36/hr CAD (Levels.fyi verified). US (Sunnyvale): estimated $45 to $55/hr USD (extrapolated; no verified US intern data). Daily catered lunch in</t>
+          <t>$22/hr in the 2026 cycle (up from $20/hr in 2024); no housing reimbursement</t>
         </is>
       </c>
       <c r="K348" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027: expected January 2027 opening, rolling deadline through February–March 2027. Projected from prior cycles</t>
+          <t>Expected late January/early February to mid-March 2027 for summer 2027 (documented Feb-March pattern across 2024 and 2026 cycles; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>Edelman</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19976,17 +19976,17 @@
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>January–June 2027</t>
         </is>
       </c>
       <c r="D349" s="6" t="inlineStr">
         <is>
-          <t>Digital; Technology  (2 of 6 tracks)</t>
+          <t>Technology / Software Engineering Intern; Cybersecurity Intern; Global Operations &amp; Analytics (SMB) Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E349" s="7" t="inlineStr">
         <is>
-          <t>edelman.com/careers</t>
+          <t>jobs.globalpayments.com/early-careers</t>
         </is>
       </c>
       <c r="F349" s="7" t="inlineStr">
@@ -19996,30 +19996,34 @@
       </c>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>After applying through Workday, expect a phone or video screen with a recruiter, followed by one-on-one or panel interviews with team members. About 18% of candidates report a skills or writing test. Prepare to discuss why you want to work in PR, your writing experience, current events knowledge, an</t>
-        </is>
-      </c>
-      <c r="H349" s="6" t="inlineStr"/>
+          <t xml:space="preserve">Global Payments' interview process is straightforward and moves quickly, with Indeed reporting that over half of candidates complete it within two weeks: 1. Find openings and apply on jobs.globalpayments.com . Set job alerts on LinkedIn and the Global Payments careers portal beginning in late 2026. </t>
+        </is>
+      </c>
+      <c r="H349" s="6" t="inlineStr">
+        <is>
+          <t>No official intern-specific visa policy confirmed. Global Payments has an established H-1B sponsorship track record for full-time roles. International students on CPT/OPT should confirm directly with recruiters</t>
+        </is>
+      </c>
       <c r="I349" s="6" t="inlineStr">
         <is>
-          <t>Yes. Talent Acquisition reviews applications "on a rolling basis," but a firm deadline still applies (March 20 in the 2026 cycle)</t>
+          <t>Not explicitly stated. Past postings on Reddit were marked CLOSED relatively quickly, suggesting fixed windows with limited spots rather than true rolling admis</t>
         </is>
       </c>
       <c r="J349" s="6" t="inlineStr">
         <is>
-          <t>$22/hr in the 2026 cycle (up from $20/hr in 2024); no housing reimbursement</t>
+          <t>$22 to $28/hr ($3,800 to $4,900/month) depending on role and location. Levels.fyi reports $22.00/hr for an Atlanta SWE intern (Summer 2023). Indeed estimates an</t>
         </is>
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>Expected late January/early February to mid-March 2027 for summer 2027 (documented Feb-March pattern across 2024 and 2026 cycles; not yet posted)</t>
+          <t>Postings historically appear January to April for the same summer. The Summer 2027 early careers page directed candidates to check back as of July 2026. Begin monitoring in late 2026 or early 2027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20029,17 +20033,17 @@
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
-          <t>January–June 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
         <is>
-          <t>Technology / Software Engineering Intern; Cybersecurity Intern; Global Operations &amp; Analytics (SMB) Intern  (3 of 5 tracks)</t>
+          <t>Digital &amp; Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E350" s="7" t="inlineStr">
         <is>
-          <t>jobs.globalpayments.com/early-careers</t>
+          <t>us.gsk.com/en-us/careers/early-careers/internships-and-co-op</t>
         </is>
       </c>
       <c r="F350" s="7" t="inlineStr">
@@ -20049,34 +20053,34 @@
       </c>
       <c r="G350" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global Payments' interview process is straightforward and moves quickly, with Indeed reporting that over half of candidates complete it within two weeks: 1. Find openings and apply on jobs.globalpayments.com . Set job alerts on LinkedIn and the Global Payments careers portal beginning in late 2026. </t>
+          <t>GSK uses a four-stage process: online application, a "World of GSK" digital assessment (situational judgement plus cognitive test, about 45 to 60 minutes), a HireVue job simulation with video and written responses, and a final Assessment Centre with group exercises, a case study presentation, and be</t>
         </is>
       </c>
       <c r="H350" s="6" t="inlineStr">
         <is>
-          <t>No official intern-specific visa policy confirmed. Global Payments has an established H-1B sponsorship track record for full-time roles. International students on CPT/OPT should confirm directly with recruiters</t>
+          <t>GSK US typically doesn't provide visa sponsorship for internships or the Future Leaders Program. However, policies can vary by role and location, so check individual job descriptions. International candidates should conf</t>
         </is>
       </c>
       <c r="I350" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated. Past postings on Reddit were marked CLOSED relatively quickly, suggesting fixed windows with limited spots rather than true rolling admis</t>
+          <t>Yes. GSK reviews on a rolling basis and recommends applying early; adverts "may close at any time"</t>
         </is>
       </c>
       <c r="J350" s="6" t="inlineStr">
         <is>
-          <t>$22 to $28/hr ($3,800 to $4,900/month) depending on role and location. Levels.fyi reports $22.00/hr for an Atlanta SWE intern (Summer 2023). Indeed estimates an</t>
+          <t>$24.70/hr average (Glassdoor, 22% above national average); range $14–$41+/hr by role and location</t>
         </is>
       </c>
       <c r="K350" s="6" t="inlineStr">
         <is>
-          <t>Postings historically appear January to April for the same summer. The Summer 2027 early careers page directed candidates to check back as of July 2026. Begin monitoring in late 2026 or early 2027</t>
+          <t>US postings expected January to March 2027; rolling review, adverts may close at any time (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20091,12 +20095,12 @@
       </c>
       <c r="D351" s="6" t="inlineStr">
         <is>
-          <t>Digital &amp; Technology  (1 of 6 tracks)</t>
+          <t>Software Engineer Program Internship; Data Science Analyst Summer  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E351" s="7" t="inlineStr">
         <is>
-          <t>us.gsk.com/en-us/careers/early-careers/internships-and-co-op</t>
+          <t>careers.jpmorgan.com/us/en/students/programs</t>
         </is>
       </c>
       <c r="F351" s="7" t="inlineStr">
@@ -20106,34 +20110,30 @@
       </c>
       <c r="G351" s="6" t="inlineStr">
         <is>
-          <t>GSK uses a four-stage process: online application, a "World of GSK" digital assessment (situational judgement plus cognitive test, about 45 to 60 minutes), a HireVue job simulation with video and written responses, and a final Assessment Centre with group exercises, a case study presentation, and be</t>
-        </is>
-      </c>
-      <c r="H351" s="6" t="inlineStr">
-        <is>
-          <t>GSK US typically doesn't provide visa sponsorship for internships or the Future Leaders Program. However, policies can vary by role and location, so check individual job descriptions. International candidates should conf</t>
-        </is>
-      </c>
+          <t>The process runs three stages for nearly every US summer program: 1. Online application. Resume plus program and location choice. JPMorgan's FAQ recommends you focus "on no more than three summer internship program applications." So pick deliberately instead of carpet-bombing every track. 2. HireVue</t>
+        </is>
+      </c>
+      <c r="H351" s="6" t="inlineStr"/>
       <c r="I351" s="6" t="inlineStr">
         <is>
-          <t>Yes. GSK reviews on a rolling basis and recommends applying early; adverts "may close at any time"</t>
+          <t>Yes. Official FAQ: applications reviewed "on a rolling basis"</t>
         </is>
       </c>
       <c r="J351" s="6" t="inlineStr">
         <is>
-          <t>$24.70/hr average (Glassdoor, 22% above national average); range $14–$41+/hr by role and location</t>
+          <t>IB &amp; Markets: pro-rated $110,000/yr base; software engineering ~$60/hr (Levels.fyi)</t>
         </is>
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>US postings expected January to March 2027; rolling review, adverts may close at any time (documented pattern; not yet posted)</t>
+          <t>For summer 2028 internships: IB applications expected to open Jan–Mar 2027, most other programs spring 2027 (projected from last cycle; JPMorgan hasn't published official 2028 dates yet)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20143,17 +20143,17 @@
       </c>
       <c r="C352" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Program Internship; Data Science Analyst Summer  (2 of 6 tracks)</t>
+          <t>Technology Summer Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E352" s="7" t="inlineStr">
         <is>
-          <t>careers.jpmorgan.com/us/en/students/programs</t>
+          <t>kkr.com/careers/student-careers</t>
         </is>
       </c>
       <c r="F352" s="7" t="inlineStr">
@@ -20163,30 +20163,34 @@
       </c>
       <c r="G352" s="6" t="inlineStr">
         <is>
-          <t>The process runs three stages for nearly every US summer program: 1. Online application. Resume plus program and location choice. JPMorgan's FAQ recommends you focus "on no more than three summer internship program applications." So pick deliberately instead of carpet-bombing every track. 2. HireVue</t>
-        </is>
-      </c>
-      <c r="H352" s="6" t="inlineStr"/>
+          <t>KKR's funnel is rigorous and multi-stage, designed to filter 7,000 applicants down to roughly 50 offers. The full process spans about 35 days on average : 1. Apply on kkr.com/careers/student-careers . The portal opens in early January and closes within about seven weeks. Apply within the first 48 ho</t>
+        </is>
+      </c>
+      <c r="H352" s="6" t="inlineStr">
+        <is>
+          <t>CPT sponsorship for international summer interns; H-1B sponsorship selective</t>
+        </is>
+      </c>
       <c r="I352" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official FAQ: applications reviewed "on a rolling basis"</t>
+          <t>Yes. Applications are reviewed on a rolling basis; applying within the first 48 hours is strongly advised</t>
         </is>
       </c>
       <c r="J352" s="6" t="inlineStr">
         <is>
-          <t>IB &amp; Markets: pro-rated $110,000/yr base; software engineering ~$60/hr (Levels.fyi)</t>
+          <t>$100,000 to $110,000 annualized base (~$19,200 to $21,200 prorated for 10 weeks), plus housing/relocation stipend and discretionary bonus</t>
         </is>
       </c>
       <c r="K352" s="6" t="inlineStr">
         <is>
-          <t>For summer 2028 internships: IB applications expected to open Jan–Mar 2027, most other programs spring 2027 (projected from last cycle; JPMorgan hasn't published official 2028 dates yet)</t>
+          <t>Expected January to February 2027 for Summer 2028 Analyst. Projected from the 2027 cycle (Jan 2 to ~Feb 21, 2026); not yet posted</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>Miro</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20196,17 +20200,17 @@
       </c>
       <c r="C353" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January–August 2027</t>
         </is>
       </c>
       <c r="D353" s="6" t="inlineStr">
         <is>
-          <t>Technology Summer Intern  (1 of 6 tracks)</t>
+          <t>Graduate Software Engineer (primary); Data &amp; Machine Learning exposure (adjacent)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E353" s="7" t="inlineStr">
         <is>
-          <t>kkr.com/careers/student-careers</t>
+          <t>miro.com/careers/open-positions/</t>
         </is>
       </c>
       <c r="F353" s="7" t="inlineStr">
@@ -20216,34 +20220,34 @@
       </c>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>KKR's funnel is rigorous and multi-stage, designed to filter 7,000 applicants down to roughly 50 offers. The full process spans about 35 days on average : 1. Apply on kkr.com/careers/student-careers . The portal opens in early January and closes within about seven weeks. Apply within the first 48 ho</t>
+          <t>Five stages: a 30-minute recruiter screen, a 90-to-120-minute hiring-manager interview against the "Miro Mindset," a Skill Assessment case or presentation, a cross-functional "Meet the Team" panel, and a leadership round. A decision usually follows within two weeks. There is no documented LeetCode-s</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
         <is>
-          <t>CPT sponsorship for international summer interns; H-1B sponsorship selective</t>
+          <t>No US intern visa pathway is described. The graduate roles are EU-based and require the right to work in Amsterdam or Berlin, with no relocation assistance in the latest job description. US applicants would need EU right</t>
         </is>
       </c>
       <c r="I353" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed on a rolling basis; applying within the first 48 hours is strongly advised</t>
+          <t>No. The Graduate program opens on a fixed annual cadence (postings each January, a single August cohort start). APM recruits in an annual Fall/Winter window. On</t>
         </is>
       </c>
       <c r="J353" s="6" t="inlineStr">
         <is>
-          <t>$100,000 to $110,000 annualized base (~$19,200 to $21,200 prorated for 10 weeks), plus housing/relocation stipend and discretionary bonus</t>
+          <t>Not published for the graduate program. For market context only (community/aggregator, not official): Netherlands Miro SWE comp runs roughly €93K–€159K per Leve</t>
         </is>
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>Expected January to February 2027 for Summer 2028 Analyst. Projected from the 2027 cycle (Jan 2 to ~Feb 21, 2026); not yet posted</t>
+          <t>Graduate Software Engineer postings expected to open ~January 2027 for an August 2027 cohort (repeating January-open / August-start pattern; labeled expected, not yet published). APM recruits each Fall/Winter.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>Miro</t>
+          <t>Mistral AI</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20253,17 +20257,17 @@
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-          <t>January–August 2027</t>
+          <t>January–April 2027</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>Graduate Software Engineer (primary); Data &amp; Machine Learning exposure (adjacent)  (2 of 4 tracks)</t>
+          <t>Applied Scientist / Research Engineer Intern; Software Engineer Intern; Applied AI / Forward-Deployed ML Engineer Intern; AI Data Solutions Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E354" s="7" t="inlineStr">
         <is>
-          <t>miro.com/careers/open-positions/</t>
+          <t>mistral.ai/careers/</t>
         </is>
       </c>
       <c r="F354" s="7" t="inlineStr">
@@ -20273,34 +20277,34 @@
       </c>
       <c r="G354" s="6" t="inlineStr">
         <is>
-          <t>Five stages: a 30-minute recruiter screen, a 90-to-120-minute hiring-manager interview against the "Miro Mindset," a Skill Assessment case or presentation, a cross-functional "Meet the Team" panel, and a leadership round. A decision usually follows within two weeks. There is no documented LeetCode-s</t>
+          <t>Expect 3 to 5 rounds over 2 to 4 weeks: a recruiter screen, a 60-minute live technical coding assessment, an ML/LLM deep-dive conversation covering transformers and MoE architecture, a system-design or pair-programming round, and a behavioral/values round on open-weights philosophy and EU AI Act awa</t>
         </is>
       </c>
       <c r="H354" s="6" t="inlineStr">
         <is>
-          <t>No US intern visa pathway is described. The graduate roles are EU-based and require the right to work in Amsterdam or Berlin, with no relocation assistance in the latest job description. US applicants would need EU right</t>
+          <t>Yes. Financial assistance for moving expenses, visa sponsorship, and settling-in services confirmed on careers page. 20 H-1B cases filed with 100% approval rate for US roles</t>
         </is>
       </c>
       <c r="I354" s="6" t="inlineStr">
         <is>
-          <t>No. The Graduate program opens on a fixed annual cadence (postings each January, a single August cohort start). APM recruits in an annual Fall/Winter window. On</t>
+          <t>Yes. Mistral posts internships as individual requisitions throughout the year. There is no centralized application deadline or cohort start date</t>
         </is>
       </c>
       <c r="J354" s="6" t="inlineStr">
         <is>
-          <t>Not published for the graduate program. For market context only (community/aggregator, not official): Netherlands Miro SWE comp runs roughly €93K–€159K per Leve</t>
+          <t>Paris: EUR 1,200 to 2,500/month (third-party estimates). US (Palo Alto): $8,000 to $11,000/month. Mistral does not publish salary ranges officially</t>
         </is>
       </c>
       <c r="K354" s="6" t="inlineStr">
         <is>
-          <t>Graduate Software Engineer postings expected to open ~January 2027 for an August 2027 cohort (repeating January-open / August-start pattern; labeled expected, not yet published). APM recruits each Fall/Winter.</t>
+          <t>Expected January to April 2027 for summer 2027 start. Roles posted on a rolling basis year-round; no single cohort deadline</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>Mistral AI</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20310,17 +20314,17 @@
       </c>
       <c r="C355" s="5" t="inlineStr">
         <is>
-          <t>January–April 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D355" s="6" t="inlineStr">
         <is>
-          <t>Applied Scientist / Research Engineer Intern; Software Engineer Intern; Applied AI / Forward-Deployed ML Engineer Intern; AI Data Solutions Intern  (4 of 6 tracks)</t>
+          <t>Technology SA; Quantitative Finance SA  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E355" s="7" t="inlineStr">
         <is>
-          <t>mistral.ai/careers/</t>
+          <t>morganstanley.com/people-opportunities/students-graduates</t>
         </is>
       </c>
       <c r="F355" s="7" t="inlineStr">
@@ -20330,34 +20334,30 @@
       </c>
       <c r="G355" s="6" t="inlineStr">
         <is>
-          <t>Expect 3 to 5 rounds over 2 to 4 weeks: a recruiter screen, a 60-minute live technical coding assessment, an ML/LLM deep-dive conversation covering transformers and MoE architecture, a system-design or pair-programming round, and a behavioral/values round on open-weights philosophy and EU AI Act awa</t>
-        </is>
-      </c>
-      <c r="H355" s="6" t="inlineStr">
-        <is>
-          <t>Yes. Financial assistance for moving expenses, visa sponsorship, and settling-in services confirmed on careers page. 20 H-1B cases filed with 100% approval rate for US roles</t>
-        </is>
-      </c>
+          <t>The funnel is consistent across divisions, with one quant-track branch: 1. Apply at the Campus portal (reached via morganstanley.com's students &amp; graduates page ). IB asks you to rank up to three IBD groups and three office locations; the Americas cap is 9 applications per year (3 intern). 2. HireVu</t>
+        </is>
+      </c>
+      <c r="H355" s="6" t="inlineStr"/>
       <c r="I355" s="6" t="inlineStr">
         <is>
-          <t>Yes. Mistral posts internships as individual requisitions throughout the year. There is no centralized application deadline or cohort start date</t>
+          <t>Yes — official posting language; apply the first week the window opens</t>
         </is>
       </c>
       <c r="J355" s="6" t="inlineStr">
         <is>
-          <t>Paris: EUR 1,200 to 2,500/month (third-party estimates). US (Palo Alto): $8,000 to $11,000/month. Mistral does not publish salary ranges officially</t>
+          <t>$52.89/hr IB &amp; WM (official postings); Technology $70K–$110K annualized</t>
         </is>
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>Expected January to April 2027 for summer 2027 start. Roles posted on a rolling basis year-round; no single cohort deadline</t>
+          <t>For summer 2028: IB expected ~Jan 1 – mid-Feb 2027; WM ~Mar 2027; firm divisions Feb–May 2027; Technology &amp; Operations spring–fall 2027 (projected from the documented 2027 cycle; not yet official)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20367,17 +20367,17 @@
       </c>
       <c r="C356" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
         <is>
-          <t>Technology SA; Quantitative Finance SA  (2 of 6 tracks)</t>
+          <t>Technology  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E356" s="7" t="inlineStr">
         <is>
-          <t>morganstanley.com/people-opportunities/students-graduates</t>
+          <t>nomuracampus.tal.net/vx/lang-en-GB/mobile-0/appcentre-ext/br</t>
         </is>
       </c>
       <c r="F356" s="7" t="inlineStr">
@@ -20387,30 +20387,30 @@
       </c>
       <c r="G356" s="6" t="inlineStr">
         <is>
-          <t>The funnel is consistent across divisions, with one quant-track branch: 1. Apply at the Campus portal (reached via morganstanley.com's students &amp; graduates page ). IB asks you to rank up to three IBD groups and three office locations; the Americas cap is 9 applications per year (3 intern). 2. HireVu</t>
+          <t>In the Americas, there is no HireVue. After a phone interview with a junior banker, finalists attend a Superday with 3 to 4 back-to-back interviews with an associate, VP, and ED or MD. Questions mix behavioral (STAR, “Why Nomura?”) with technical (DCF, financial statements, deal discussions). Global</t>
         </is>
       </c>
       <c r="H356" s="6" t="inlineStr"/>
       <c r="I356" s="6" t="inlineStr">
         <is>
-          <t>Yes — official posting language; apply the first week the window opens</t>
+          <t>Yes. Nomura “screens, interviews, and makes offers while the program is still accepting applications”</t>
         </is>
       </c>
       <c r="J356" s="6" t="inlineStr">
         <is>
-          <t>$52.89/hr IB &amp; WM (official postings); Technology $70K–$110K annualized</t>
+          <t>Global Markets SA: $110,000/yr pro-rated (official JD); SWE interns ~$50/hr in NYC (Levels.fyi)</t>
         </is>
       </c>
       <c r="K356" s="6" t="inlineStr">
         <is>
-          <t>For summer 2028: IB expected ~Jan 1 – mid-Feb 2027; WM ~Mar 2027; firm divisions Feb–May 2027; Technology &amp; Operations spring–fall 2027 (projected from the documented 2027 cycle; not yet official)</t>
+          <t>Partly open. 2027 Risk Management and Quantitative Risk Management Summer Analyst roles are live as of August 2026. IB and Global Markets still expected ~January to late March 2027; Technology ~July 2027. Rolling review</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20425,12 +20425,12 @@
       </c>
       <c r="D357" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 5 tracks)</t>
+          <t>Software Engineering; Data Engineering; Product Data Science; Applied ML Engineering; Infrastructure Engineering; Security Engineering</t>
         </is>
       </c>
       <c r="E357" s="7" t="inlineStr">
         <is>
-          <t>nomuracampus.tal.net/vx/lang-en-GB/mobile-0/appcentre-ext/br</t>
+          <t>shopify.com/careers</t>
         </is>
       </c>
       <c r="F357" s="7" t="inlineStr">
@@ -20440,30 +20440,34 @@
       </c>
       <c r="G357" s="6" t="inlineStr">
         <is>
-          <t>In the Americas, there is no HireVue. After a phone interview with a junior banker, finalists attend a Superday with 3 to 4 back-to-back interviews with an associate, VP, and ED or MD. Questions mix behavioral (STAR, “Why Nomura?”) with technical (DCF, financial statements, deal discussions). Global</t>
-        </is>
-      </c>
-      <c r="H357" s="6" t="inlineStr"/>
+          <t>Shopify’s funnel is faster than most big tech and distinctly different from the standard LeetCode gauntlet, averaging 3–5 weeks from application to decision: 1. Apply at shopify.com/careers with a resume, application questions, your LinkedIn, and a personal website or GitHub link. Shopify’s postings</t>
+        </is>
+      </c>
+      <c r="H357" s="6" t="inlineStr">
+        <is>
+          <t>No. Every internship posting states you must be legally entitled to work in the hiring country for the full duration. Shopify doesn't provide immigration sponsorship for intern candidates. However, candidates on existing</t>
+        </is>
+      </c>
       <c r="I357" s="6" t="inlineStr">
         <is>
-          <t>Yes. Nomura “screens, interviews, and makes offers while the program is still accepting applications”</t>
+          <t>Yes. Applications reviewed on a rolling basis, and postings warn they "may close before the stated closing date". The two US summer 2027 postings listed on Octo</t>
         </is>
       </c>
       <c r="J357" s="6" t="inlineStr">
         <is>
-          <t>Global Markets SA: $110,000/yr pro-rated (official JD); SWE interns ~$50/hr in NYC (Levels.fyi)</t>
+          <t>$85,000–$93,700/year base pay range for US locations (US Software Engineering Internships Summer 2027) and $103,000–$111,000/year (US Applied Machine Learning E</t>
         </is>
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>Partly open. 2027 Risk Management and Quantitative Risk Management Summer Analyst roles are live as of August 2026. IB and Global Markets still expected ~January to late March 2027; Technology ~July 2027. Rolling review</t>
+          <t>Closed for summer 2027 (US): US Applied Machine Learning Engineering Internships Summer 2027 (posted September 21, 2026) and US Software Engineering Internships Summer 2027 (posted September 28, 2026) stated that applications closed on October 12, 2026 at 11:59pm EDT. Neither was listed on shopify.com/careers on October 14, 2026, and no other intern posting was listed there that day. Fall 2027 pos</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Skild AI</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20478,12 +20482,12 @@
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Engineering; Product Data Science; Applied ML Engineering; Infrastructure Engineering; Security Engineering</t>
+          <t>Research Intern — Robot Learning / ML (Confirmed); Robotics Engineering Intern (Inferred); Robot Operator / Technician (Intern-Adjacent)  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E358" s="7" t="inlineStr">
         <is>
-          <t>shopify.com/careers</t>
+          <t>skild.ai/career</t>
         </is>
       </c>
       <c r="F358" s="7" t="inlineStr">
@@ -20493,34 +20497,34 @@
       </c>
       <c r="G358" s="6" t="inlineStr">
         <is>
-          <t>Shopify’s funnel is faster than most big tech and distinctly different from the standard LeetCode gauntlet, averaging 3–5 weeks from application to decision: 1. Apply at shopify.com/careers with a resume, application questions, your LinkedIn, and a personal website or GitHub link. Shopify’s postings</t>
+          <t>Based on Glassdoor data from five interviews, the process typically includes a recruiter screen focused on background and technical alignment, a live coding round on CoderPad (example: write Multi-Headed Self Attention in PyTorch from scratch without autocomplete), and a final interview loop with te</t>
         </is>
       </c>
       <c r="H358" s="6" t="inlineStr">
         <is>
-          <t>No. Every internship posting states you must be legally entitled to work in the hiring country for the full duration. Shopify doesn't provide immigration sponsorship for intern candidates. However, candidates on existing</t>
+          <t>US work authorization required. F-1 CPT/OPT likely accepted. No confirmed direct visa sponsorship for interns</t>
         </is>
       </c>
       <c r="I358" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis, and postings warn they "may close before the stated closing date". The two US summer 2027 postings listed on Octo</t>
+          <t>Likely yes. With roughly 100 employees, hiring is opportunistic rather than cycle-based. Roles appear as team needs arise</t>
         </is>
       </c>
       <c r="J358" s="6" t="inlineStr">
         <is>
-          <t>$85,000–$93,700/year base pay range for US locations (US Software Engineering Internships Summer 2027) and $103,000–$111,000/year (US Applied Machine Learning E</t>
+          <t>No confirmed intern salary. Estimated $40 to $55 per hour for research/ML interns based on comparable robotics AI startup rates. Robot Operator roles pay $20 to</t>
         </is>
       </c>
       <c r="K358" s="6" t="inlineStr">
         <is>
-          <t>Closed for summer 2027 (US): US Applied Machine Learning Engineering Internships Summer 2027 (posted September 21, 2026) and US Software Engineering Internships Summer 2027 (posted September 28, 2026) stated that applications closed on October 12, 2026 at 11:59pm EDT. Neither was listed on shopify.com/careers on October 14, 2026, and no other intern posting was listed there that day. Fall 2027 pos</t>
+          <t>Not confirmed. Estimated January to March 2027 for summer 2027 roles, based on one confirmed intern datapoint and startup hiring norms. Low confidence</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>Skild AI</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20530,17 +20534,17 @@
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D359" s="6" t="inlineStr">
         <is>
-          <t>Research Intern — Robot Learning / ML (Confirmed); Robotics Engineering Intern (Inferred); Robot Operator / Technician (Intern-Adjacent)  (3 of 4 tracks)</t>
+          <t>Engineering &amp; Data Science; Machine Learning Engineering; Research Scientist (PhD)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E359" s="7" t="inlineStr">
         <is>
-          <t>skild.ai/career</t>
+          <t>lifeatspotify.com/jobs</t>
         </is>
       </c>
       <c r="F359" s="7" t="inlineStr">
@@ -20550,34 +20554,30 @@
       </c>
       <c r="G359" s="6" t="inlineStr">
         <is>
-          <t>Based on Glassdoor data from five interviews, the process typically includes a recruiter screen focused on background and technical alignment, a live coding round on CoderPad (example: write Multi-Headed Self Attention in PyTorch from scratch without autocomplete), and a final interview loop with te</t>
-        </is>
-      </c>
-      <c r="H359" s="6" t="inlineStr">
-        <is>
-          <t>US work authorization required. F-1 CPT/OPT likely accepted. No confirmed direct visa sponsorship for interns</t>
-        </is>
-      </c>
+          <t>A Lever application (resume; no cover letter is mentioned), then typically three rounds about a week apart: recruiter call, technical or craft interview, and a values interview. Engineering candidates report live coding over screen share. Community reports average about 39 days, and decisions arrive</t>
+        </is>
+      </c>
+      <c r="H359" s="6" t="inlineStr"/>
       <c r="I359" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. With roughly 100 employees, hiring is opportunistic rather than cycle-based. Roles appear as team needs arise</t>
+          <t>No. One hard deadline (Feb 5, 2026 at 12:00 PM ET last cycle); decisions to everyone by mid-April</t>
         </is>
       </c>
       <c r="J359" s="6" t="inlineStr">
         <is>
-          <t>No confirmed intern salary. Estimated $40 to $55 per hour for research/ML interns based on comparable robotics AI startup rates. Robot Operator roles pay $20 to</t>
+          <t>Official posted rates: $32/hr business tracks, $44/hr J.D. &amp; MBA, $51/hr eng/ML/data science, $55–60/hr PhD research</t>
         </is>
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Estimated January to March 2027 for summer 2027 roles, based on one confirmed intern datapoint and startup hiring norms. Low confidence</t>
+          <t>Applications for summer 2027 expected to open mid-to-late January 2027, hard deadline early February 2027 at 12 PM ET; PhD research roles ~late November 2026 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20587,17 +20587,17 @@
       </c>
       <c r="C360" s="5" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; Data Science; Machine Learning Engineering; Research Scientist (PhD)  (3 of 6 tracks)</t>
+          <t>SWE Intern (Health); SWE Intern (App Infrastructure); SWE Co-op; PM, AI Experiences (MBA)  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E360" s="7" t="inlineStr">
         <is>
-          <t>lifeatspotify.com/jobs</t>
+          <t>whoop.com/us/en/careers/</t>
         </is>
       </c>
       <c r="F360" s="7" t="inlineStr">
@@ -20607,30 +20607,34 @@
       </c>
       <c r="G360" s="6" t="inlineStr">
         <is>
-          <t>A Lever application (resume; no cover letter is mentioned), then typically three rounds about a week apart: recruiter call, technical or craft interview, and a values interview. Engineering candidates report live coding over screen share. Community reports average about 39 days, and decisions arrive</t>
-        </is>
-      </c>
-      <c r="H360" s="6" t="inlineStr"/>
+          <t>Typically 3 to 4 stages over about 19 days: a recruiter screen, a technical interview on Codility with practical day-to-day problems (AI tools allowed with disclosure), and 1 to 2 behavioral and leadership rounds. WHOOP explicitly avoids LeetCode-style brainteasers.</t>
+        </is>
+      </c>
+      <c r="H360" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated. WHOOP does not disclose sponsorship policy for interns publicly; international students should inquire directly</t>
+        </is>
+      </c>
       <c r="I360" s="6" t="inlineStr">
         <is>
-          <t>No. One hard deadline (Feb 5, 2026 at 12:00 PM ET last cycle); decisions to everyone by mid-April</t>
+          <t>Yes, implicitly. No published deadlines; positions close when filled. Apply within the first 2 to 4 weeks of a posting</t>
         </is>
       </c>
       <c r="J360" s="6" t="inlineStr">
         <is>
-          <t>Official posted rates: $32/hr business tracks, $44/hr J.D. &amp; MBA, $51/hr eng/ML/data science, $55–60/hr PhD research</t>
+          <t>SWE Intern ~$35/hr ($72K annualized median) plus free WHOOP membership and device</t>
         </is>
       </c>
       <c r="K360" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open mid-to-late January 2027, hard deadline early February 2027 at 12 PM ET; PhD research roles ~late November 2026 (documented pattern; not yet posted)</t>
+          <t>Expected January to March 2027 for summer starts, based on prior posting patterns. Projected, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>AI21 Labs</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20640,17 +20644,17 @@
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D361" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Health); SWE Intern (App Infrastructure); SWE Co-op; PM, AI Experiences (MBA)  (4 of 6 tracks)</t>
+          <t>ML Research Intern; Software Engineering Intern  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E361" s="7" t="inlineStr">
         <is>
-          <t>whoop.com/us/en/careers/</t>
+          <t>linkedin.com/company/ai21-labs/jobs/</t>
         </is>
       </c>
       <c r="F361" s="7" t="inlineStr">
@@ -20660,34 +20664,34 @@
       </c>
       <c r="G361" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 stages over about 19 days: a recruiter screen, a technical interview on Codility with practical day-to-day problems (AI tools allowed with disclosure), and 1 to 2 behavioral and leadership rounds. WHOOP explicitly avoids LeetCode-style brainteasers.</t>
+          <t>The typical process involves 5 rounds over approximately 3 weeks: recruiter screen, hiring manager interview, take-home assignment simulating real project work, panel interview presenting your results, and a final culture-fit meeting. For research roles, expect deep dives into publications and resea</t>
         </is>
       </c>
       <c r="H361" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated. WHOOP does not disclose sponsorship policy for interns publicly; international students should inquire directly</t>
+          <t>Tel Aviv: Masa Israel assists with B-1 work visa for international candidates. NYC: J-1 or CPT/OPT for US-enrolled students. Arrangements may change if the Nvidia acquisition completes</t>
         </is>
       </c>
       <c r="I361" s="6" t="inlineStr">
         <is>
-          <t>Yes, implicitly. No published deadlines; positions close when filled. Apply within the first 2 to 4 weeks of a posting</t>
+          <t>Likely yes. AI21 does not publish a fixed application cycle. The Masa Israel pathway also operates on a rolling basis</t>
         </is>
       </c>
       <c r="J361" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern ~$35/hr ($72K annualized median) plus free WHOOP membership and device</t>
+          <t>Estimated ILS 6,000 to 12,000/mo (~$1,600 to $3,300/mo) in Tel Aviv. NYC roles estimated at $4,000 to $7,000/mo. No verified AI21 intern salary data exists</t>
         </is>
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>Expected January to March 2027 for summer starts, based on prior posting patterns. Projected, not yet posted</t>
+          <t>No fixed public cycle. Israeli AI startups typically post 2 to 4 months before start. Estimated window: February to April 2027 for a summer start</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>AI21 Labs</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20697,17 +20701,17 @@
       </c>
       <c r="C362" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>February–March 2027</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; Software Engineering Intern  (2 of 4 tracks)</t>
+          <t>Software Engineering Intern; Analytics Consulting Intern; Data &amp; Analytics Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E362" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/company/ai21-labs/jobs/</t>
+          <t>braze.com/company/careers</t>
         </is>
       </c>
       <c r="F362" s="7" t="inlineStr">
@@ -20717,34 +20721,34 @@
       </c>
       <c r="G362" s="6" t="inlineStr">
         <is>
-          <t>The typical process involves 5 rounds over approximately 3 weeks: recruiter screen, hiring manager interview, take-home assignment simulating real project work, panel interview presenting your results, and a final culture-fit meeting. For research roles, expect deep dives into publications and resea</t>
+          <t>Typically 2 to 5 rounds: recruiter screen, hiring manager interview, technical interview (live coding for SWE or tailored assessment for non-SWE), and a team interview. The process is rated A+ (84 out of 100) on Comparably. 60% rate it Average difficulty, 33% Difficult. 50% of candidates hear back t</t>
         </is>
       </c>
       <c r="H362" s="6" t="inlineStr">
         <is>
-          <t>Tel Aviv: Masa Israel assists with B-1 work visa for international candidates. NYC: J-1 or CPT/OPT for US-enrolled students. Arrangements may change if the Nvidia acquisition completes</t>
+          <t>Evaluated case-by-case. The application asks whether you will require sponsorship. Braze sponsors H-1B and E-3 visas for full-time roles; intern-specific sponsorship is not explicitly confirmed</t>
         </is>
       </c>
       <c r="I362" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. AI21 does not publish a fixed application cycle. The Masa Israel pathway also operates on a rolling basis</t>
+          <t>Yes. Braze uses Greenhouse ATS and reviews applications on a rolling basis. Postings are removed once the class is filled. The SWE posting for Summer 2026 was r</t>
         </is>
       </c>
       <c r="J362" s="6" t="inlineStr">
         <is>
-          <t>Estimated ILS 6,000 to 12,000/mo (~$1,600 to $3,300/mo) in Tel Aviv. NYC roles estimated at $4,000 to $7,000/mo. No verified AI21 intern salary data exists</t>
+          <t>$60/hr for SWE interns (~$10,400/month) in NYC. $45/hr for Analytics Consulting interns (~$7,800/month). Levels.fyi reports $60/hr for Summer 2024 and 2026</t>
         </is>
       </c>
       <c r="K362" s="6" t="inlineStr">
         <is>
-          <t>No fixed public cycle. Israeli AI startups typically post 2 to 4 months before start. Estimated window: February to April 2027 for a summer start</t>
+          <t>Expected September–October 2026 for summer 2027 roles. SWE posting historically closes by mid-January. Analytics and other tracks may remain open into February–March. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20754,17 +20758,17 @@
       </c>
       <c r="C363" s="5" t="inlineStr">
         <is>
-          <t>February–March 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Analytics Consulting Intern; Data &amp; Analytics Intern  (3 of 6 tracks)</t>
+          <t>Engineering Graduate Program (SWE); Software Engineer Intern (Ad-hoc); Data Engineering / Data Science; Security Engineering  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E363" s="7" t="inlineStr">
         <is>
-          <t>braze.com/company/careers</t>
+          <t>jobs.deel.com/job-boards/klarna</t>
         </is>
       </c>
       <c r="F363" s="7" t="inlineStr">
@@ -20774,34 +20778,34 @@
       </c>
       <c r="G363" s="6" t="inlineStr">
         <is>
-          <t>Typically 2 to 5 rounds: recruiter screen, hiring manager interview, technical interview (live coding for SWE or tailored assessment for non-SWE), and a team interview. The process is rated A+ (84 out of 100) on Comparably. 60% rate it Average difficulty, 33% Difficult. 50% of candidates hear back t</t>
+          <t>The process typically spans 5 to 6 rounds over 36 to 62 days: recruiter screen, a 12- to 15-minute video-proctored logic test, a technical OA on HackerRank, a 60-minute technical phone screen, a 3- to 4-hour virtual onsite loop, and a behavioral round with an AI-competency assessment. Glassdoor rate</t>
         </is>
       </c>
       <c r="H363" s="6" t="inlineStr">
         <is>
-          <t>Evaluated case-by-case. The application asks whether you will require sponsorship. Braze sponsors H-1B and E-3 visas for full-time roles; intern-specific sponsorship is not explicitly confirmed</t>
+          <t>Klarna states it will provide visa assistance when a position is offered. No relocation assistance for the Graduate Program. On-site presence in Stockholm required</t>
         </is>
       </c>
       <c r="I363" s="6" t="inlineStr">
         <is>
-          <t>Yes. Braze uses Greenhouse ATS and reviews applications on a rolling basis. Postings are removed once the class is filled. The SWE posting for Summer 2026 was r</t>
+          <t>Not confirmed. Graduate Program applications appear batch-reviewed within a defined Q1 window. Ad-hoc summer postings are likely filled as they appear</t>
         </is>
       </c>
       <c r="J363" s="6" t="inlineStr">
         <is>
-          <t>$60/hr for SWE interns (~$10,400/month) in NYC. $45/hr for Analytics Consulting interns (~$7,800/month). Levels.fyi reports $60/hr for Summer 2024 and 2026</t>
+          <t>Graduate Program: ~52K EUR total comp at L1 in Stockholm. Summer intern pay not published; US fintech benchmark is $35 to $50/hr. Benefits include 30 days leave</t>
         </is>
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>Expected September–October 2026 for summer 2027 roles. SWE posting historically closes by mid-January. Analytics and other tracks may remain open into February–March. Projected from the Summer 2026 cycle</t>
+          <t>Graduate Program: expected Q1 2027 (Feb to Apr) for a Sep to Oct 2027 start. Ad-hoc summer internships: postings may appear Fall 2026 through Winter 2027 for Jun to Aug 2027 roles</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20811,17 +20815,17 @@
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>Engineering Graduate Program (SWE); Software Engineer Intern (Ad-hoc); Data Engineering / Data Science; Security Engineering  (4 of 5 tracks)</t>
+          <t>Quantitative Intern; Engineering &amp; AI Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E364" s="7" t="inlineStr">
         <is>
-          <t>jobs.deel.com/job-boards/klarna</t>
+          <t>campusjobs.mlp.com/careers</t>
         </is>
       </c>
       <c r="F364" s="7" t="inlineStr">
@@ -20831,34 +20835,34 @@
       </c>
       <c r="G364" s="6" t="inlineStr">
         <is>
-          <t>The process typically spans 5 to 6 rounds over 36 to 62 days: recruiter screen, a 12- to 15-minute video-proctored logic test, a technical OA on HackerRank, a 60-minute technical phone screen, a 3- to 4-hour virtual onsite loop, and a behavioral round with an AI-competency assessment. Glassdoor rate</t>
+          <t>Apply online, complete an OA on HackerRank or CodeSignal (2 coding problems, LeetCode Medium/Hard, ~20 to 30% pass rate), then a 15- to 20-minute recruiter screen, 1 to 2 technical phone interviews (45 to 60 minutes), and a 3- to 4-hour Superday with 3-5 back-to-back interviews. Offers often come wi</t>
         </is>
       </c>
       <c r="H364" s="6" t="inlineStr">
         <is>
-          <t>Klarna states it will provide visa assistance when a position is offered. No relocation assistance for the Graduate Program. On-site presence in Stockholm required</t>
+          <t>CPT supported for F-1 students. OPT and H-1B generally supported for full-time conversions. Pod-level hiring may affect sponsorship timing</t>
         </is>
       </c>
       <c r="I364" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Graduate Program applications appear batch-reviewed within a defined Q1 window. Ad-hoc summer postings are likely filled as they appear</t>
+          <t>Yes. Millennium explicitly states roles are filled on a rolling basis. The golden window is August through September; by November most spots are gone</t>
         </is>
       </c>
       <c r="J364" s="6" t="inlineStr">
         <is>
-          <t>Graduate Program: ~52K EUR total comp at L1 in Stockholm. Summer intern pay not published; US fintech benchmark is $35 to $50/hr. Benefits include 30 days leave</t>
+          <t>SWE: $80/hr ($13,867/mo) plus $5,000-$10,000 housing stipend. Quant Research: ~$112/hr (~$19,400/mo). Total 10-week take-home: $32,000-$45,000+. Levels.fyi veri</t>
         </is>
       </c>
       <c r="K364" s="6" t="inlineStr">
         <is>
-          <t>Graduate Program: expected Q1 2027 (Feb to Apr) for a Sep to Oct 2027 start. Ad-hoc summer internships: postings may appear Fall 2026 through Winter 2027 for Jun to Aug 2027 roles</t>
+          <t>Expected early August 2027 (historically August 1-3) for Summer 2028 roles. Rolling basis; apply within the first two weeks. Investment Internship track opens and fills much earlier (early 2027)</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20868,17 +20872,17 @@
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>February–March 2027</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
         <is>
-          <t>Quantitative Intern; Engineering &amp; AI Intern  (2 of 6 tracks)</t>
+          <t>PlayStation/SIE Software Engineer Intern; Sony Electronics Software Engineer Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E365" s="7" t="inlineStr">
         <is>
-          <t>campusjobs.mlp.com/careers</t>
+          <t>sonyjobs.com/internships.html</t>
         </is>
       </c>
       <c r="F365" s="7" t="inlineStr">
@@ -20888,34 +20892,34 @@
       </c>
       <c r="G365" s="6" t="inlineStr">
         <is>
-          <t>Apply online, complete an OA on HackerRank or CodeSignal (2 coding problems, LeetCode Medium/Hard, ~20 to 30% pass rate), then a 15- to 20-minute recruiter screen, 1 to 2 technical phone interviews (45 to 60 minutes), and a 3- to 4-hour Superday with 3-5 back-to-back interviews. Offers often come wi</t>
+          <t>Most divisions follow a three- to four-round process: recruiter screen or video interview, a technical or supervisor round, and a panel or leadership behavioral round. PlayStation SWE roles include live coding on algorithms and system design. Sony Music uses a SparkHire video screen. Glassdoor rates</t>
         </is>
       </c>
       <c r="H365" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. OPT and H-1B generally supported for full-time conversions. Pod-level hiring may affect sponsorship timing</t>
+          <t>PlayStation/SIE: F-1 visa holders eligible, CPT supported. Sony Electronics SWE roles: H-1B sponsorship and STEM OPT/CPT welcomed. Sony Pictures and Sony Music: must be authorized to work in the U.S. for the duration. Ch</t>
         </is>
       </c>
       <c r="I365" s="6" t="inlineStr">
         <is>
-          <t>Yes. Millennium explicitly states roles are filled on a rolling basis. The golden window is August through September; by November most spots are gone</t>
+          <t>Sony Pictures recruits on a rolling basis until the right candidate is found. PlayStation and Sony Electronics typically review in waves. Apply as soon as posti</t>
         </is>
       </c>
       <c r="J365" s="6" t="inlineStr">
         <is>
-          <t>SWE: $80/hr ($13,867/mo) plus $5,000-$10,000 housing stipend. Quant Research: ~$112/hr (~$19,400/mo). Total 10-week take-home: $32,000-$45,000+. Levels.fyi veri</t>
+          <t>Varies widely by division and role. PlayStation SWE: $49.50 to $53/hr ($8,580 to $9,187/mo). Sony Electronics SWE: $25 to $40/hr. General entertainment roles: a</t>
         </is>
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>Expected early August 2027 (historically August 1-3) for Summer 2028 roles. Rolling basis; apply within the first two weeks. Investment Internship track opens and fills much earlier (early 2027)</t>
+          <t>Varies by division. Sony Music: expected deadline late January 2027. Sony Pictures: postings expected February 2027 for summer. PlayStation/SIE and Sony Electronics: expected fall 2026 to spring 2027. All dates projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20930,12 +20934,12 @@
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
-          <t>PlayStation/SIE Software Engineer Intern; Sony Electronics Software Engineer Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern / Co-op (primary); Mobile Engineering (Android / iOS); AI / Machine Learning; Data Science Intern; Cybersecurity / Security Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E366" s="7" t="inlineStr">
         <is>
-          <t>sonyjobs.com/internships.html</t>
+          <t>careers.toasttab.com/early-career</t>
         </is>
       </c>
       <c r="F366" s="7" t="inlineStr">
@@ -20945,34 +20949,34 @@
       </c>
       <c r="G366" s="6" t="inlineStr">
         <is>
-          <t>Most divisions follow a three- to four-round process: recruiter screen or video interview, a technical or supervisor round, and a panel or leadership behavioral round. PlayStation SWE roles include live coding on algorithms and system design. Sony Music uses a SparkHire video screen. Glassdoor rates</t>
+          <t>A recruiter screen, a HackerRank online assessment (two questions, easy-to-medium), and a technical superday with a roughly one-hour live round, plus a behavioral conversation. Expect easy-medium DSA (graph traversal/DFS), restaurant-domain design, and heavy edge-case follow-up.</t>
         </is>
       </c>
       <c r="H366" s="6" t="inlineStr">
         <is>
-          <t>PlayStation/SIE: F-1 visa holders eligible, CPT supported. Sony Electronics SWE roles: H-1B sponsorship and STEM OPT/CPT welcomed. Sony Pictures and Sony Music: must be authorized to work in the U.S. for the duration. Ch</t>
+          <t>NOT FOUND (Toast publishes no explicit intern sponsorship statement; confirm with the recruiter</t>
         </is>
       </c>
       <c r="I366" s="6" t="inlineStr">
         <is>
-          <t>Sony Pictures recruits on a rolling basis until the right candidate is found. PlayStation and Sony Electronics typically review in waves. Apply as soon as posti</t>
+          <t xml:space="preserve">Partly. Each cycle opens in a defined window rather than year-round, but resumes are reviewed on an ongoing basis within the window. Toast advises checking the </t>
         </is>
       </c>
       <c r="J366" s="6" t="inlineStr">
         <is>
-          <t>Varies widely by division and role. PlayStation SWE: $49.50 to $53/hr ($8,580 to $9,187/mo). Sony Electronics SWE: $25 to $40/hr. General entertainment roles: a</t>
+          <t>Set by role, non-negotiable, disclosed at the recruiter screen. SWE interns near $38/hr median (~$34–41/hr) on Levels.fyi (community); Toast's official Fall 202</t>
         </is>
       </c>
       <c r="K366" s="6" t="inlineStr">
         <is>
-          <t>Varies by division. Sony Music: expected deadline late January 2027. Sony Pictures: postings expected February 2027 for summer. PlayStation/SIE and Sony Electronics: expected fall 2026 to spring 2027. All dates projected from prior cycles</t>
+          <t>Summer internship applications typically open February–March; expected Feb–March 2027 for a June 2027 start. Fall co-op opens ~June–July, Spring co-op ~October (all 2027 dates expected, projected from Toast's documented recurring windows)</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20982,17 +20986,17 @@
       </c>
       <c r="C367" s="5" t="inlineStr">
         <is>
-          <t>February–March 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D367" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern / Co-op (primary); Mobile Engineering (Android / iOS); AI / Machine Learning; Data Science Intern; Cybersecurity / Security Engineering  (5 of 6 tracks)</t>
+          <t>Software Engineering Intern (primary); Embedded Software Intern; Electrical Engineering Intern; Software Test Engineering Intern; Mechanical / General Engineering Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E367" s="7" t="inlineStr">
         <is>
-          <t>careers.toasttab.com/early-career</t>
+          <t>aptiv.com/en/jobs/students/aptiv-early-talent</t>
         </is>
       </c>
       <c r="F367" s="7" t="inlineStr">
@@ -21002,34 +21006,34 @@
       </c>
       <c r="G367" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a HackerRank online assessment (two questions, easy-to-medium), and a technical superday with a roughly one-hour live round, plus a behavioral conversation. Expect easy-medium DSA (graph traversal/DFS), restaurant-domain design, and heavy edge-case follow-up.</t>
+          <t>Typically three rounds: a stream-specific technical round (fundamentals, C code snippets, protocols like UART/I2C/SPI, basic data structures, tech trends), a technical/managerial round with a deep dive on your resume projects, and an HR/behavioral round. Electrical and power-electronics candidates o</t>
         </is>
       </c>
       <c r="H367" s="6" t="inlineStr">
         <is>
-          <t>NOT FOUND (Toast publishes no explicit intern sponsorship statement; confirm with the recruiter</t>
+          <t>Varies by req. The Troy Software Engineering Intern posting accepts US citizens, permanent residents, and US student-visa holders, but the Embedded Software Intern posting states visa sponsorship is not available. Always</t>
         </is>
       </c>
       <c r="I367" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly. Each cycle opens in a defined window rather than year-round, but resumes are reviewed on an ongoing basis within the window. Toast advises checking the </t>
+          <t xml:space="preserve">Yes. Aptiv posts individual intern reqs by team and location, and each closes when filled ("this job may close before the stated closing date, apply as soon as </t>
         </is>
       </c>
       <c r="J367" s="6" t="inlineStr">
         <is>
-          <t>Set by role, non-negotiable, disclosed at the recruiter screen. SWE interns near $38/hr median (~$34–41/hr) on Levels.fyi (community); Toast's official Fall 202</t>
+          <t>No official intern pay is published on the JDs. Community-reported: median ~$29/hr, range ~$22–$37/hr (Glassdoor, 24 salaries, Apr 2025); Levels.fyi lists a har</t>
         </is>
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>Summer internship applications typically open February–March; expected Feb–March 2027 for a June 2027 start. Fall co-op opens ~June–July, Spring co-op ~October (all 2027 dates expected, projected from Toast's documented recurring windows)</t>
+          <t>Not published as a fixed calendar. Summer 2027 reqs began posting on September 9, 2026 and are expected to keep rolling into winter/spring 2027. A prior-cycle Troy SWE intern req listed "Apply by 20 Nov 2025," so apply the week a relevant req appears.</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Ferrari</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -21039,17 +21043,17 @@
       </c>
       <c r="C368" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>March–April 2027</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (primary); Embedded Software Intern; Electrical Engineering Intern; Software Test Engineering Intern; Mechanical / General Engineering Intern  (5 of 6 tracks)</t>
+          <t>F1 Engineering Academy; Vehicle Assembly Process Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E368" s="7" t="inlineStr">
         <is>
-          <t>aptiv.com/en/jobs/students/aptiv-early-talent</t>
+          <t>ferrari.com/en-EN/corporate/career</t>
         </is>
       </c>
       <c r="F368" s="7" t="inlineStr">
@@ -21059,34 +21063,30 @@
       </c>
       <c r="G368" s="6" t="inlineStr">
         <is>
-          <t>Typically three rounds: a stream-specific technical round (fundamentals, C code snippets, protocols like UART/I2C/SPI, basic data structures, tech trends), a technical/managerial round with a deep dive on your resume projects, and an HR/behavioral round. Electrical and power-electronics candidates o</t>
-        </is>
-      </c>
-      <c r="H368" s="6" t="inlineStr">
-        <is>
-          <t>Varies by req. The Troy Software Engineering Intern posting accepts US citizens, permanent residents, and US student-visa holders, but the Embedded Software Intern posting states visa sponsorship is not available. Always</t>
-        </is>
-      </c>
+          <t>Expect multiple rounds. For the F1 Engineering Academy: CV screening, HR phone or Teams call, then an assessment center in Maranello with line managers and mentors. For general roles: automated screening, possible psychometric test, video interview, and final technical interviews with senior enginee</t>
+        </is>
+      </c>
+      <c r="H368" s="6" t="inlineStr"/>
       <c r="I368" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. Aptiv posts individual intern reqs by team and location, and each closes when filled ("this job may close before the stated closing date, apply as soon as </t>
+          <t>Partially. Flagship academies have fixed deadlines with structured assessments. General roles on jobs.ferrari.com fill as received</t>
         </is>
       </c>
       <c r="J368" s="6" t="inlineStr">
         <is>
-          <t>No official intern pay is published on the JDs. Community-reported: median ~$29/hr, range ~$22–$37/hr (Glassdoor, 24 salaries, Apr 2025); Levels.fyi lists a har</t>
+          <t>~EUR 700–1,200/month plus meals (Italy); ~$35/hr estimate (US, Glassdoor)</t>
         </is>
       </c>
       <c r="K368" s="6" t="inlineStr">
         <is>
-          <t>Not published as a fixed calendar. Summer 2027 reqs began posting on September 9, 2026 and are expected to keep rolling into winter/spring 2027. A prior-cycle Troy SWE intern req listed "Apply by 20 Nov 2025," so apply the week a relevant req appears.</t>
+          <t>F1 Engineering Academy: expected Q1 2027 (March–April deadline). Design Academy: expected spring–summer 2027 (June–July deadline). General roles: year-round</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -21096,17 +21096,17 @@
       </c>
       <c r="C369" s="5" t="inlineStr">
         <is>
-          <t>March–April 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>F1 Engineering Academy; Vehicle Assembly Process Engineering  (2 of 6 tracks)</t>
+          <t>Finance &amp; Data Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E369" s="7" t="inlineStr">
         <is>
-          <t>ferrari.com/en-EN/corporate/career</t>
+          <t>wmg.com/emerging-talent</t>
         </is>
       </c>
       <c r="F369" s="7" t="inlineStr">
@@ -21116,30 +21116,30 @@
       </c>
       <c r="G369" s="6" t="inlineStr">
         <is>
-          <t>Expect multiple rounds. For the F1 Engineering Academy: CV screening, HR phone or Teams call, then an assessment center in Maranello with line managers and mentors. For general roles: automated screening, possible psychometric test, video interview, and final technical interviews with senior enginee</t>
+          <t>It varies by hiring manager but includes at least one interview, often a recorded HireVue-style video screen followed by a live Zoom or in-person round (a 1:1 with the hiring manager and/or a panel). Some interviews run as short as 15 minutes, and offers can arrive within days of the live round.</t>
         </is>
       </c>
       <c r="H369" s="6" t="inlineStr"/>
       <c r="I369" s="6" t="inlineStr">
         <is>
-          <t>Partially. Flagship academies have fixed deadlines with structured assessments. General roles on jobs.ferrari.com fill as received</t>
+          <t>Yes. WMG reviews ETA applications on a rolling basis and urges applying as early as possible; placements can fill before the posted deadline</t>
         </is>
       </c>
       <c r="J369" s="6" t="inlineStr">
         <is>
-          <t>~EUR 700–1,200/month plus meals (Italy); ~$35/hr estimate (US, Glassdoor)</t>
+          <t>$17.00–$18.42/hour (employer-provided on ETA postings). Housing not provided. Academic credit available. Ignore inflated Glassdoor aggregate estimates; the JD f</t>
         </is>
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>F1 Engineering Academy: expected Q1 2027 (March–April deadline). Design Academy: expected spring–summer 2027 (June–July deadline). General roles: year-round</t>
+          <t>Not posted yet. Summer 2027 applications expected to open ~March 2027 with a deadline ~mid-April 2027 (expected), projected from Summer 2026 (deadline April 17, 2026). Nearest window: Spring 2027 cohort, applications expected November 2026 to January 2027 (no ETA roles posted on October 6, 2026). Fall window: July to August</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Canva</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -21149,17 +21149,17 @@
       </c>
       <c r="C370" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>April–May 2027</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
         <is>
-          <t>Finance &amp; Data Analytics  (1 of 6 tracks)</t>
+          <t>Software Engineering; ML / AI Engineering; Growth Engineering; Data Science  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E370" s="7" t="inlineStr">
         <is>
-          <t>wmg.com/emerging-talent</t>
+          <t>lifeatcanva.com/en/early-careers/</t>
         </is>
       </c>
       <c r="F370" s="7" t="inlineStr">
@@ -21169,30 +21169,30 @@
       </c>
       <c r="G370" s="6" t="inlineStr">
         <is>
-          <t>It varies by hiring manager but includes at least one interview, often a recorded HireVue-style video screen followed by a live Zoom or in-person round (a 1:1 with the hiring manager and/or a panel). Some interviews run as short as 15 minutes, and offers can arrive within days of the live round.</t>
+          <t>For engineering interns, expect a 90-minute online assessment (3 coding questions, Java-only for backend), followed by a recruiter Zoom call, then a technical interview with LeetCode-style problems and system design. ML/AI adds math-heavy MCQs. The process takes about 4–5 weeks. Canva encourages usi</t>
         </is>
       </c>
       <c r="H370" s="6" t="inlineStr"/>
       <c r="I370" s="6" t="inlineStr">
         <is>
-          <t>Yes. WMG reviews ETA applications on a rolling basis and urges applying as early as possible; placements can fill before the posted deadline</t>
+          <t>Partially. ANZ has a defined ~30-day window; US roles recruit on a rolling basis. Both close when filled</t>
         </is>
       </c>
       <c r="J370" s="6" t="inlineStr">
         <is>
-          <t>$17.00–$18.42/hour (employer-provided on ETA postings). Housing not provided. Academic credit available. Ignore inflated Glassdoor aggregate estimates; the JD f</t>
+          <t>AU: ~A$28–38/hr + meals. US: ~$46–60/hr (SWE), ~$52–60/hr (ML/AI), with relocation assistance</t>
         </is>
       </c>
       <c r="K370" s="6" t="inlineStr">
         <is>
-          <t>Not posted yet. Summer 2027 applications expected to open ~March 2027 with a deadline ~mid-April 2027 (expected), projected from Summer 2026 (deadline April 17, 2026). Nearest window: Spring 2027 cohort, applications expected November 2026 to January 2027 (no ETA roles posted on October 6, 2026). Fall window: July to August</t>
+          <t>ANZ: expected April–May 2027 for Dec 2027 start (~30-day window). US: expected Sep–Nov 2027 for May–Aug 2028 (rolling)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>Canva</t>
+          <t>AQR Capital</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -21202,17 +21202,17 @@
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>April–May 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D371" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; ML / AI Engineering; Growth Engineering; Data Science  (4 of 6 tracks)</t>
+          <t>Engineering Summer Analyst; Front Office Dev Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E371" s="7" t="inlineStr">
         <is>
-          <t>lifeatcanva.com/en/early-careers/</t>
+          <t>careers.aqr.com/jobs/category/university-jobs</t>
         </is>
       </c>
       <c r="F371" s="7" t="inlineStr">
@@ -21222,30 +21222,34 @@
       </c>
       <c r="G371" s="6" t="inlineStr">
         <is>
-          <t>For engineering interns, expect a 90-minute online assessment (3 coding questions, Java-only for backend), followed by a recruiter Zoom call, then a technical interview with LeetCode-style problems and system design. ML/AI adds math-heavy MCQs. The process takes about 4–5 weeks. Canva encourages usi</t>
-        </is>
-      </c>
-      <c r="H371" s="6" t="inlineStr"/>
+          <t>Four rounds: a 30-minute recruiter screen, a 60-to-90-minute technical phone screen (probability, statistics, coding), a 5-to-7-interview on-site covering statistics, Python coding, research discussion, domain depth, and behavioral fit, then a decision within 1 to 3 weeks.</t>
+        </is>
+      </c>
+      <c r="H371" s="6" t="inlineStr">
+        <is>
+          <t>CPT for enrolled international students, OPT with STEM extension supported, H-1B for full-time conversion (~50 approvals FY2025)</t>
+        </is>
+      </c>
       <c r="I371" s="6" t="inlineStr">
         <is>
-          <t>Partially. ANZ has a defined ~30-day window; US roles recruit on a rolling basis. Both close when filled</t>
+          <t>Not confirmed rolling. Applications close mid-August; interviews take place throughout September. Apply early in the window</t>
         </is>
       </c>
       <c r="J371" s="6" t="inlineStr">
         <is>
-          <t>AU: ~A$28–38/hr + meals. US: ~$46–60/hr (SWE), ~$52–60/hr (ML/AI), with relocation assistance</t>
+          <t>Research: ~$65–80/hr ($30K–35K+ for 10 weeks). Portfolio/Engineering: ~$55–65/hr ($25K–30K). Housing stipend provided (community estimates)</t>
         </is>
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>ANZ: expected April–May 2027 for Dec 2027 start (~30-day window). US: expected Sep–Nov 2027 for May–Aug 2028 (rolling)</t>
+          <t>June 30 to mid-August 2026 for Summer 2027. Summer 2028 expected to follow the same late-June pattern in 2027</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>AQR Capital</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -21260,12 +21264,12 @@
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
-          <t>Engineering Summer Analyst; Front Office Dev Engineering  (2 of 6 tracks)</t>
+          <t>Global Technology (BA / SWE)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E372" s="7" t="inlineStr">
         <is>
-          <t>careers.aqr.com/jobs/category/university-jobs</t>
+          <t>careers.bankofamerica.com/en-us/students</t>
         </is>
       </c>
       <c r="F372" s="7" t="inlineStr">
@@ -21275,34 +21279,34 @@
       </c>
       <c r="G372" s="6" t="inlineStr">
         <is>
-          <t>Four rounds: a 30-minute recruiter screen, a 60-to-90-minute technical phone screen (probability, statistics, coding), a 5-to-7-interview on-site covering statistics, Python coding, research discussion, domain depth, and behavioral fit, then a decision within 1 to 3 weeks.</t>
+          <t>It starts with a HireVue on-demand video interview: a few behavioral questions, about 30 seconds of prep, and up to three minutes per answer. Strong candidates advance to a super day of two to four interviews, behavioral with a technical or case round for front-office desks. No aptitude games.</t>
         </is>
       </c>
       <c r="H372" s="6" t="inlineStr">
         <is>
-          <t>CPT for enrolled international students, OPT with STEM extension supported, H-1B for full-time conversion (~50 approvals FY2025)</t>
+          <t>No. The postings state the bank is "unable to consider candidates who will require visa sponsorship now, or in the future." It's a hard gate, not a preference, so if you'll need sponsorship, these US summer analyst progr</t>
         </is>
       </c>
       <c r="I372" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed rolling. Applications close mid-August; interviews take place throughout September. Apply early in the window</t>
+          <t>Yes. Official: recruiting is "on a rolling basis once applications open" and "programs will close as positions are filled"</t>
         </is>
       </c>
       <c r="J372" s="6" t="inlineStr">
         <is>
-          <t>Research: ~$65–80/hr ($30K–35K+ for 10 weeks). Portfolio/Engineering: ~$55–65/hr ($25K–30K). Housing stipend provided (community estimates)</t>
+          <t>Community-labeled: NYC business analyst intern ~$45.50/hr + $3,400 bonus (Levels.fyi); front-office base ~$110k prorated</t>
         </is>
       </c>
       <c r="K372" s="6" t="inlineStr">
         <is>
-          <t>June 30 to mid-August 2026 for Summer 2027. Summer 2028 expected to follow the same late-June pattern in 2027</t>
+          <t>Front office: expected spring to summer 2027, rolling. Enterprise tracks: summer to fall 2027, deadlines around October (projected pattern)</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -21317,12 +21321,12 @@
       </c>
       <c r="D373" s="6" t="inlineStr">
         <is>
-          <t>Global Technology (BA / SWE)  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Cloud Security Intern; AI/ML Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E373" s="7" t="inlineStr">
         <is>
-          <t>careers.bankofamerica.com/en-us/students</t>
+          <t>crowdstrike.com/en-us/careers/university-interns/</t>
         </is>
       </c>
       <c r="F373" s="7" t="inlineStr">
@@ -21332,34 +21336,34 @@
       </c>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>It starts with a HireVue on-demand video interview: a few behavioral questions, about 30 seconds of prep, and up to three minutes per answer. Strong candidates advance to a super day of two to four interviews, behavioral with a technical or case round for front-office desks. No aptitude games.</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), take a 60- to 90-minute technical assessment (HackerRank for engineering, take-home for intelligence), then a virtual onsite with 2 to 3 technical sessions plus a behavioral round. Decisions come within 1 to 2 weeks. Total proce</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr">
         <is>
-          <t>No. The postings state the bank is "unable to consider candidates who will require visa sponsorship now, or in the future." It's a hard gate, not a preference, so if you'll need sponsorship, these US summer analyst progr</t>
+          <t>CPT supported for F-1 students. STEM OPT extension eligible. Selective H-1B sponsorship for early-career roles. Security-clearance roles require U.S. citizenship</t>
         </is>
       </c>
       <c r="I373" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official: recruiting is "on a rolling basis once applications open" and "programs will close as positions are filled"</t>
+          <t>Yes. CrowdStrike reviews applications on a rolling basis and fills seats as strong candidates clear the pipeline. Apply early for priority consideration</t>
         </is>
       </c>
       <c r="J373" s="6" t="inlineStr">
         <is>
-          <t>Community-labeled: NYC business analyst intern ~$45.50/hr + $3,400 bonus (Levels.fyi); front-office base ~$110k prorated</t>
+          <t>$28–$55/hr depending on role. SWE interns ~$43/hr (~$7,450/month). Intelligence interns $28–$35/hr. Housing stipend up to $4,500/month for eligible participants</t>
         </is>
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>Front office: expected spring to summer 2027, rolling. Enterprise tracks: summer to fall 2027, deadlines around October (projected pattern)</t>
+          <t>FIRST POSTINGS LIVE: Sales Excellence Elite Intern (Summer 2027) reqs posted Sep 16, 2026 and a Global Sales Programs Intern (Summer 2027) on Sep 28, 2026 on CrowdStrike's Workday board (Austin). Engineering and security intern reqs not yet posted as of Oct 1, 2026; expect them through fall. Bulk offers projected by December 2026</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Electric</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21369,17 +21373,17 @@
       </c>
       <c r="C374" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–October 2027</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Cloud Security Intern; AI/ML Intern  (3 of 6 tracks)</t>
+          <t>Engineering Intern (GE Aerospace); AI / Digital Technology Intern (GE Aerospace)  (2 of 8 tracks)</t>
         </is>
       </c>
       <c r="E374" s="7" t="inlineStr">
         <is>
-          <t>crowdstrike.com/en-us/careers/university-interns/</t>
+          <t>careers.geaerospace.com/global/en/us-internships</t>
         </is>
       </c>
       <c r="F374" s="7" t="inlineStr">
@@ -21389,34 +21393,34 @@
       </c>
       <c r="G374" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), take a 60- to 90-minute technical assessment (HackerRank for engineering, take-home for intelligence), then a virtual onsite with 2 to 3 technical sessions plus a behavioral round. Decisions come within 1 to 2 weeks. Total proce</t>
+          <t>The process typically has three stages: a recruiter phone screen (15 to 30 minutes), a technical screen or video interview with the hiring manager (30 to 45 minutes covering resume and engineering or technical questions), and a behavioral interview using the STAR method. The average time from applic</t>
         </is>
       </c>
       <c r="H374" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. STEM OPT extension eligible. Selective H-1B sponsorship for early-career roles. Security-clearance roles require U.S. citizenship</t>
+          <t>Limited. Many GE Aerospace roles require U.S. persons status (U.S. citizens, permanent residents, or protected individuals). Some non-defense roles at GE Vernova and GE HealthCare may accept work-authorized international</t>
         </is>
       </c>
       <c r="I374" s="6" t="inlineStr">
         <is>
-          <t>Yes. CrowdStrike reviews applications on a rolling basis and fills seats as strong candidates clear the pipeline. Apply early for priority consideration</t>
+          <t>Yes, continuous rolling. GE reviews applications on a rolling basis and postings go live continuously through the fall. Apply within the first few weeks of a po</t>
         </is>
       </c>
       <c r="J374" s="6" t="inlineStr">
         <is>
-          <t>$28–$55/hr depending on role. SWE interns ~$43/hr (~$7,450/month). Intelligence interns $28–$35/hr. Housing stipend up to $4,500/month for eligible participants</t>
+          <t>$20 to $26 per hour depending on year of study and division. Housing and relocation assistance provided to eligible students (reported at approximately $225 per</t>
         </is>
       </c>
       <c r="K374" s="6" t="inlineStr">
         <is>
-          <t>FIRST POSTINGS LIVE: Sales Excellence Elite Intern (Summer 2027) reqs posted Sep 16, 2026 and a Global Sales Programs Intern (Summer 2027) on Sep 28, 2026 on CrowdStrike's Workday board (Austin). Engineering and security intern reqs not yet posted as of Oct 1, 2026; expect them through fall. Bulk offers projected by December 2026</t>
+          <t>Summer 2027 GE Aerospace roles are live now (as of July 2026 on the GE Aerospace careers portal), added on a rolling basis with new roles through fall 2026. On-campus and virtual events in September, virtual interviews in October, most offers by November 2026. Apply as soon as a matching role posts</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>General Electric</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21426,17 +21430,17 @@
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
-          <t>June–October 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D375" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern (GE Aerospace); AI / Digital Technology Intern (GE Aerospace)  (2 of 8 tracks)</t>
+          <t>Engineering Co-op (Chemical / Electrical Controls); Data Science / Analytics Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E375" s="7" t="inlineStr">
         <is>
-          <t>careers.geaerospace.com/global/en/us-internships</t>
+          <t>careers.thehersheycompany.com/go/Interns/9002600/</t>
         </is>
       </c>
       <c r="F375" s="7" t="inlineStr">
@@ -21446,34 +21450,34 @@
       </c>
       <c r="G375" s="6" t="inlineStr">
         <is>
-          <t>The process typically has three stages: a recruiter phone screen (15 to 30 minutes), a technical screen or video interview with the hiring manager (30 to 45 minutes covering resume and engineering or technical questions), and a behavioral interview using the STAR method. The average time from applic</t>
+          <t>Usually one behavioral (STAR) video interview with two team members, tailored to your resume, plus a background check and drug test. Average difficulty is low (2.8/5), ~26 days to hire, 67% positive on Glassdoor. There is no standardized timed online assessment for the corporate funnel.</t>
         </is>
       </c>
       <c r="H375" s="6" t="inlineStr">
         <is>
-          <t>Limited. Many GE Aerospace roles require U.S. persons status (U.S. citizens, permanent residents, or protected individuals). Some non-defense roles at GE Vernova and GE HealthCare may accept work-authorized international</t>
+          <t>NO) every intern JD states Hershey will not provide immigration-related support for internships, and will not sponsor (e.g., H-1B) for entry-level roles later either. The single biggest eligibility filter</t>
         </is>
       </c>
       <c r="I375" s="6" t="inlineStr">
         <is>
-          <t>Yes, continuous rolling. GE reviews applications on a rolling basis and postings go live continuously through the fall. Apply within the first few weeks of a po</t>
+          <t>Partly. Standing "Future Opportunities" postings collect applications continuously and are drawn from as team needs arise; individual summer cohorts still calib</t>
         </is>
       </c>
       <c r="J375" s="6" t="inlineStr">
         <is>
-          <t>$20 to $26 per hour depending on year of study and division. Housing and relocation assistance provided to eligible students (reported at approximately $225 per</t>
+          <t>No official rate published. Community/aggregator data: Engineering interns ~$25/hr (Indeed), a ChemE year-long co-op at $23/hr (Reddit), a remote Data Scientist</t>
         </is>
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 GE Aerospace roles are live now (as of July 2026 on the GE Aerospace careers portal), added on a rolling basis with new roles through fall 2026. On-campus and virtual events in September, virtual interviews in October, most offers by November 2026. Apply as soon as a matching role posts</t>
+          <t>Opening now. First Summer 2027 posting live: Electrical Controls Co-Op (Summer 2027), posted October 2, 2026, alongside Spring 2027 co-ops. Corporate Finance, Category Management and Supply Chain summer 2027 internships not posted yet as of October 6, 2026 (the Summer 2026 Finance posting went live Aug 8, 2025)</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21488,12 +21492,12 @@
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Engineering Co-op (Chemical / Electrical Controls); Data Science / Analytics Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering (SWE); Data Science &amp; AI  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E376" s="7" t="inlineStr">
         <is>
-          <t>careers.thehersheycompany.com/go/Interns/9002600/</t>
+          <t>ibm.com/careers/internships</t>
         </is>
       </c>
       <c r="F376" s="7" t="inlineStr">
@@ -21503,34 +21507,34 @@
       </c>
       <c r="G376" s="6" t="inlineStr">
         <is>
-          <t>Usually one behavioral (STAR) video interview with two team members, tailored to your resume, plus a background check and drug test. Average difficulty is low (2.8/5), ~26 days to hire, 67% positive on Glassdoor. There is no standardized timed online assessment for the corporate funnel.</t>
+          <t>IBM's hiring funnel runs 4–10 weeks from application to offer, with three core rounds for standard internships and four to five for Extreme Blue: 1. Apply at ibm.com/careers/internships with your resume and an IBM Careers profile. Use keywords from your target JD (watsonx, OpenShift, hybrid cloud) b</t>
         </is>
       </c>
       <c r="H376" s="6" t="inlineStr">
         <is>
-          <t>NO) every intern JD states Hershey will not provide immigration-related support for internships, and will not sponsor (e.g., H-1B) for entry-level roles later either. The single biggest eligibility filter</t>
+          <t>Most US internship postings explicitly state that IBM will not provide visa sponsorship. Exceptions sometimes exist for PhD Research interns and Extreme Blue participants. International students must verify work authoriz</t>
         </is>
       </c>
       <c r="I376" s="6" t="inlineStr">
         <is>
-          <t>Partly. Standing "Future Opportunities" postings collect applications continuously and are drawn from as team needs arise; individual summer cohorts still calib</t>
+          <t>Yes. Positions filled as qualified candidates are identified; early applicants face less competition</t>
         </is>
       </c>
       <c r="J376" s="6" t="inlineStr">
         <is>
-          <t>No official rate published. Community/aggregator data: Engineering interns ~$25/hr (Indeed), a ChemE year-long co-op at $23/hr (Reddit), a remote Data Scientist</t>
+          <t>$32–$88/hr depending on track (SWE ~$75, Research ~$88, PM ~$66); relocation stipend $2–4K</t>
         </is>
       </c>
       <c r="K376" s="6" t="inlineStr">
         <is>
-          <t>Opening now. First Summer 2027 posting live: Electrical Controls Co-Op (Summer 2027), posted October 2, 2026, alongside Spring 2027 co-ops. Corporate Finance, Category Management and Supply Chain summer 2027 internships not posted yet as of October 6, 2026 (the Summer 2026 Finance posting went live Aug 8, 2025)</t>
+          <t>OPEN. The summer 2027 wave is broadly open on careers.ibm.com as of August 2026, with roles across Product Management, Business Transformation Consulting, Application Development, Sales, and more. Rolling review through January 2027</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21540,17 +21544,17 @@
       </c>
       <c r="C377" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–November 2027</t>
         </is>
       </c>
       <c r="D377" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (SWE); Data Science &amp; AI  (2 of 6 tracks)</t>
+          <t>Technology &amp; Digital / Data Analytics Intern; 84.51° Data Scientist Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E377" s="7" t="inlineStr">
         <is>
-          <t>ibm.com/careers/internships</t>
+          <t>krogerfamilycareers.com/en/sites/CX_2001/pages/5015</t>
         </is>
       </c>
       <c r="F377" s="7" t="inlineStr">
@@ -21560,34 +21564,34 @@
       </c>
       <c r="G377" s="6" t="inlineStr">
         <is>
-          <t>IBM's hiring funnel runs 4–10 weeks from application to offer, with three core rounds for standard internships and four to five for Extreme Blue: 1. Apply at ibm.com/careers/internships with your resume and an IBM Careers profile. Use keywords from your target JD (watsonx, OpenShift, hybrid cloud) b</t>
+          <t>Typically a HireVue one-way video interview, then a behavioral panel (STAR questions mapped to Kroger's core values), and a final leadership conversation. Technology and data roles add an assessment: Reddit reports a coding challenge (Swift) plus a "game" challenge. Corporate non-technical roles usu</t>
         </is>
       </c>
       <c r="H377" s="6" t="inlineStr">
         <is>
-          <t>Most US internship postings explicitly state that IBM will not provide visa sponsorship. Exceptions sometimes exist for PhD Research interns and Extreme Blue participants. International students must verify work authoriz</t>
+          <t>No. JDs require work authorization that does not now or in the future require sponsorship, explicitly excluding H-1B, F-1/OPT, and TN. Kroger does not sponsor interns</t>
         </is>
       </c>
       <c r="I377" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified; early applicants face less competition</t>
+          <t>Yes. Both Kroger corporate and 84.51° fill intern roles on a rolling basis and unpost them as they fill. Applying in September or October materially beats Decem</t>
         </is>
       </c>
       <c r="J377" s="6" t="inlineStr">
         <is>
-          <t>$32–$88/hr depending on track (SWE ~$75, Research ~$88, PM ~$66); relocation stipend $2–4K</t>
+          <t>No official intern pay published ("competitive pay"). Community and aggregator estimates: ~$14–$27/hr, with technical and 84.51° roles reportedly higher ($22–$4</t>
         </is>
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>OPEN. The summer 2027 wave is broadly open on careers.ibm.com as of August 2026, with roles across Product Management, Business Transformation Consulting, Application Development, Sales, and more. Rolling review through January 2027</t>
+          <t>Summer 2027 is partly open. Kroger's own careers board showed six Summer 2027 intern reqs on September 27, 2026: supply chain Quality, Maintenance, Human Resources and Continuous Improvement in Denver (posted September 1, listed through November 30), Transportation in Nashville (posted September 23), and a Construction Project Engineer intern in Hutchinson, KS. Program dates are May 17 to August 6</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21597,17 +21601,17 @@
       </c>
       <c r="C378" s="5" t="inlineStr">
         <is>
-          <t>June–November 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D378" s="6" t="inlineStr">
         <is>
-          <t>Technology &amp; Digital / Data Analytics Intern; 84.51° Data Scientist Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern / Co-op; Production Engineering Intern; Data Scientist Intern, Product Analytics; Research Scientist Intern (PhD, AI/FAIR); ML / AI Software Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E378" s="7" t="inlineStr">
         <is>
-          <t>krogerfamilycareers.com/en/sites/CX_2001/pages/5015</t>
+          <t>metacareers.com/careerprograms/students/</t>
         </is>
       </c>
       <c r="F378" s="7" t="inlineStr">
@@ -21617,34 +21621,30 @@
       </c>
       <c r="G378" s="6" t="inlineStr">
         <is>
-          <t>Typically a HireVue one-way video interview, then a behavioral panel (STAR questions mapped to Kroger's core values), and a final leadership conversation. Technology and data roles add an assessment: Reddit reports a coding challenge (Swift) plus a "game" challenge. Corporate non-technical roles usu</t>
-        </is>
-      </c>
-      <c r="H378" s="6" t="inlineStr">
-        <is>
-          <t>No. JDs require work authorization that does not now or in the future require sponsorship, explicitly excluding H-1B, F-1/OPT, and TN. Kroger does not sponsor interns</t>
-        </is>
-      </c>
+          <t>A recruiter screen, a 45-minute CoderPad phone screen with about 2 LeetCode Easy-to-Medium problems, then a four-round loop of 2 coding, 1 design, and 1 behavioral round. A CodeSignal online assessment appears for many candidates, and Meta is rolling out an AI-assisted coding round in 2026.</t>
+        </is>
+      </c>
+      <c r="H378" s="6" t="inlineStr"/>
       <c r="I378" s="6" t="inlineStr">
         <is>
-          <t>Yes. Both Kroger corporate and 84.51° fill intern roles on a rolling basis and unpost them as they fill. Applying in September or October materially beats Decem</t>
+          <t>Yes. AI-research JDs state "various start dates throughout the year"; quotas fill by roughly December</t>
         </is>
       </c>
       <c r="J378" s="6" t="inlineStr">
         <is>
-          <t>No official intern pay published ("competitive pay"). Community and aggregator estimates: ~$14–$27/hr, with technical and 84.51° roles reportedly higher ($22–$4</t>
+          <t>$7,188 to $12,134/month official JD bands, plus housing assistance (~$2,600/mo commonly cited); SWE community figure ~$51.35/hr</t>
         </is>
       </c>
       <c r="K378" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 is partly open. Kroger's own careers board showed six Summer 2027 intern reqs on September 27, 2026: supply chain Quality, Maintenance, Human Resources and Continuous Improvement in Denver (posted September 1, listed through November 30), Transportation in Nashville (posted September 23), and a Construction Project Engineer intern in Hutchinson, KS. Program dates are May 17 to August 6</t>
+          <t>Opening now, rolling: the first summer 2027 req (Data Engineer Intern, Product Analytics) went live on 29 September 2026; the Software Engineer intern req was not yet posted on 1 October 2026, and more summer 2027 reqs are expected through the fall (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21659,12 +21659,12 @@
       </c>
       <c r="D379" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern / Co-op; Production Engineering Intern; Data Scientist Intern, Product Analytics; Research Scientist Intern (PhD, AI/FAIR); ML / AI Software Engineer Intern  (5 of 6 tracks)</t>
+          <t>SWE Intern; OCI SWE Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E379" s="7" t="inlineStr">
         <is>
-          <t>metacareers.com/careerprograms/students/</t>
+          <t>oracle.com/careers/students-grads/internships/</t>
         </is>
       </c>
       <c r="F379" s="7" t="inlineStr">
@@ -21674,30 +21674,34 @@
       </c>
       <c r="G379" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a 45-minute CoderPad phone screen with about 2 LeetCode Easy-to-Medium problems, then a four-round loop of 2 coding, 1 design, and 1 behavioral round. A CodeSignal online assessment appears for many candidates, and Meta is rolling out an AI-assisted coding round in 2026.</t>
-        </is>
-      </c>
-      <c r="H379" s="6" t="inlineStr"/>
+          <t>You apply, then a recruiter phone-screens you for 20 to 30 minutes. Next come two technical interviews of 45 to 60 minutes each covering data structures, algorithms, SQL, OOP, and a resume deep-dive. A behavioral round follows. For OCI or Labs roles, expect a 3-to-4-hour Super Day with multiple back</t>
+        </is>
+      </c>
+      <c r="H379" s="6" t="inlineStr">
+        <is>
+          <t>Oracle ranks in the top 15 U.S. H-1B sponsors . CPT and OPT accepted. Some government-facing roles require U.S. citizenship</t>
+        </is>
+      </c>
       <c r="I379" s="6" t="inlineStr">
         <is>
-          <t>Yes. AI-research JDs state "various start dates throughout the year"; quotas fill by roughly December</t>
+          <t>Yes, rolling. Early applicants get faster screening and wider team-placement options. Competition intensifies and available roles narrow after October</t>
         </is>
       </c>
       <c r="J379" s="6" t="inlineStr">
         <is>
-          <t>$7,188 to $12,134/month official JD bands, plus housing assistance (~$2,600/mo commonly cited); SWE community figure ~$51.35/hr</t>
+          <t>Standard SWE Austin ~$41/hr (~$7,100/mo). OCI roles $53 to $55/hr. AI/ML premium roles $55 to $65/hr. Housing stipend $2,166 to $8,000/mo depending on location</t>
         </is>
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>Opening now, rolling: the first summer 2027 req (Data Engineer Intern, Product Analytics) went live on 29 September 2026; the Software Engineer intern req was not yet posted on 1 October 2026, and more summer 2027 reqs are expected through the fall (projected from prior cycle)</t>
+          <t>Partly open: Sales Development Rep Intern (Summer 2027) live in Austin, Nashville, Burlington, Denver and Santa Monica since September 18, 2026, plus a Nashville Financial Analyst Intern; software engineering roles not posted as of September 28, 2026. Roles stay open rolling but narrow fast</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21712,12 +21716,12 @@
       </c>
       <c r="D380" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern; OCI SWE Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering; Data / Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E380" s="7" t="inlineStr">
         <is>
-          <t>oracle.com/careers/students-grads/internships/</t>
+          <t>careers.paramount.com/go/Interns/8710100/</t>
         </is>
       </c>
       <c r="F380" s="7" t="inlineStr">
@@ -21727,27 +21731,23 @@
       </c>
       <c r="G380" s="6" t="inlineStr">
         <is>
-          <t>You apply, then a recruiter phone-screens you for 20 to 30 minutes. Next come two technical interviews of 45 to 60 minutes each covering data structures, algorithms, SQL, OOP, and a resume deep-dive. A behavioral round follows. For OCI or Labs roles, expect a 3-to-4-hour Super Day with multiple back</t>
-        </is>
-      </c>
-      <c r="H380" s="6" t="inlineStr">
-        <is>
-          <t>Oracle ranks in the top 15 U.S. H-1B sponsors . CPT and OPT accepted. Some government-facing roles require U.S. citizenship</t>
-        </is>
-      </c>
+          <t>Most roles follow a two-round process. Round one is a recruiter phone screen lasting 15-30 minutes covering your background, interest in entertainment, and availability. Round two is a Zoom interview with the hiring team, often including behavioral questions like "What media do you consume?" and "Wh</t>
+        </is>
+      </c>
+      <c r="H380" s="6" t="inlineStr"/>
       <c r="I380" s="6" t="inlineStr">
         <is>
-          <t>Yes, rolling. Early applicants get faster screening and wider team-placement options. Competition intensifies and available roles narrow after October</t>
+          <t>Effectively yes. Positions fill as qualified candidates apply; no individual status feedback provided</t>
         </is>
       </c>
       <c r="J380" s="6" t="inlineStr">
         <is>
-          <t>Standard SWE Austin ~$41/hr (~$7,100/mo). OCI roles $53 to $55/hr. AI/ML premium roles $55 to $65/hr. Housing stipend $2,166 to $8,000/mo depending on location</t>
+          <t>$23/hr median (Glassdoor, 266 reports); $19-$23/hr business roles, $34-$45/hr engineering roles</t>
         </is>
       </c>
       <c r="K380" s="6" t="inlineStr">
         <is>
-          <t>Partly open: Sales Development Rep Intern (Summer 2027) live in Austin, Nashville, Burlington, Denver and Santa Monica since September 18, 2026, plus a Nashville Financial Analyst Intern; software engineering roles not posted as of September 28, 2026. Roles stay open rolling but narrow fast</t>
+          <t>Not published on Paramount's own pages; watch careers.paramount.com Interns for summer 2027 postings</t>
         </is>
       </c>
     </row>
@@ -30637,7 +30637,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -30659,7 +30659,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Physical Intelligence</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -30681,7 +30681,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>Physical Intelligence</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -30703,7 +30703,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Plaid</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -30725,7 +30725,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>Raymond James</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -30747,7 +30747,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>Raymond James</t>
+          <t>RBC Capital Markets</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -30769,7 +30769,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>RBC Capital Markets</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -30791,7 +30791,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Relativity Space</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -30813,7 +30813,7 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>Relativity Space</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -30835,7 +30835,7 @@
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -30857,7 +30857,7 @@
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rockstar Games</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -30879,7 +30879,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -30901,7 +30901,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -30923,7 +30923,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -30945,7 +30945,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -30967,7 +30967,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -30989,7 +30989,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -31011,7 +31011,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -31033,7 +31033,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -31055,7 +31055,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -31077,7 +31077,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -31099,7 +31099,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -31121,7 +31121,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -31143,7 +31143,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -31165,7 +31165,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Together AI</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -31187,7 +31187,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -31209,7 +31209,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Ubisoft</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -31231,7 +31231,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>Ubisoft</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -31253,7 +31253,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -31275,7 +31275,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -31297,7 +31297,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -31319,7 +31319,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -31341,7 +31341,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -31363,7 +31363,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -31385,7 +31385,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -31407,7 +31407,7 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>William Blair</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -31429,7 +31429,7 @@
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>William Blair</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -31451,7 +31451,7 @@
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
@@ -31473,7 +31473,7 @@
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
@@ -31495,7 +31495,7 @@
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
@@ -31517,7 +31517,7 @@
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
@@ -31539,7 +31539,7 @@
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
@@ -31561,7 +31561,7 @@
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
@@ -31583,7 +31583,7 @@
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
@@ -31605,7 +31605,7 @@
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
@@ -31627,7 +31627,7 @@
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
@@ -31649,7 +31649,7 @@
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>BAE Systems</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
@@ -31671,7 +31671,7 @@
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
         <is>
-          <t>BAE Systems</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
@@ -31693,7 +31693,7 @@
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
@@ -31715,7 +31715,7 @@
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
@@ -31737,7 +31737,7 @@
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
@@ -31759,7 +31759,7 @@
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
@@ -31781,7 +31781,7 @@
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Glean</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
@@ -31803,7 +31803,7 @@
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
         <is>
-          <t>Glean</t>
+          <t>Harvey</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
@@ -31825,7 +31825,7 @@
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
         <is>
-          <t>Harvey</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
@@ -31847,7 +31847,7 @@
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
@@ -31869,7 +31869,7 @@
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
@@ -31891,7 +31891,7 @@
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
@@ -31913,7 +31913,7 @@
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
@@ -31935,7 +31935,7 @@
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>Nissan</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
@@ -31957,7 +31957,7 @@
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
         <is>
-          <t>Nissan</t>
+          <t>Old Mission</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
@@ -31979,7 +31979,7 @@
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
         <is>
-          <t>Old Mission</t>
+          <t>P&amp;G</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
@@ -32001,7 +32001,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>P&amp;G</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -32023,7 +32023,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -32045,7 +32045,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Riot Games</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -32067,7 +32067,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Riot Games</t>
+          <t>Scale AI</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -32089,7 +32089,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Scale AI</t>
+          <t>ServiceNow</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -32111,7 +32111,7 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow</t>
+          <t>Sierra</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
@@ -32133,7 +32133,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Sierra</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
@@ -32155,7 +32155,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
@@ -32177,7 +32177,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Qatalyst Partners</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
@@ -32199,7 +32199,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Qatalyst Partners</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
@@ -32221,7 +32221,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
@@ -32243,12 +32243,12 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
-        </is>
-      </c>
-      <c r="B327" s="4" t="inlineStr">
-        <is>
-          <t>Window open - check now</t>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="B327" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
@@ -32265,7 +32265,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -32287,7 +32287,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -32309,7 +32309,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -32331,7 +32331,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -32353,7 +32353,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Magna</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -32375,7 +32375,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Magna</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -32397,7 +32397,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -32419,7 +32419,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -32441,7 +32441,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B336" s="8" t="inlineStr">
@@ -32463,7 +32463,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Analysis Group</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -32485,7 +32485,7 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>Analysis Group</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B338" s="8" t="inlineStr">
@@ -32507,7 +32507,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
@@ -32529,7 +32529,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B340" s="8" t="inlineStr">
@@ -32551,7 +32551,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
@@ -32573,7 +32573,7 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Volkswagen</t>
         </is>
       </c>
       <c r="B342" s="8" t="inlineStr">
@@ -32595,12 +32595,12 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>Strava</t>
-        </is>
-      </c>
-      <c r="B343" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="B343" s="9" t="inlineStr">
+        <is>
+          <t>Later this cycle</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -32617,12 +32617,12 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
-        </is>
-      </c>
-      <c r="B344" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>AppLovin</t>
+        </is>
+      </c>
+      <c r="B344" s="9" t="inlineStr">
+        <is>
+          <t>Later this cycle</t>
         </is>
       </c>
       <c r="C344" s="7" t="inlineStr">
@@ -32639,7 +32639,7 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -32661,7 +32661,7 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -32683,7 +32683,7 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>Cerebras</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -32705,7 +32705,7 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>Cerebras</t>
+          <t>Edelman</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -32727,7 +32727,7 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>Edelman</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -32749,7 +32749,7 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -32771,7 +32771,7 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -32793,7 +32793,7 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -32815,7 +32815,7 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>Miro</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -32837,7 +32837,7 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>Miro</t>
+          <t>Mistral AI</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -32859,7 +32859,7 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>Mistral AI</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -32881,7 +32881,7 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -32903,7 +32903,7 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -32925,7 +32925,7 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Skild AI</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -32947,7 +32947,7 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>Skild AI</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -32969,7 +32969,7 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -32991,7 +32991,7 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>AI21 Labs</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -33013,7 +33013,7 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>AI21 Labs</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -33035,7 +33035,7 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -33057,7 +33057,7 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -33079,7 +33079,7 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -33101,7 +33101,7 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -33123,7 +33123,7 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -33145,7 +33145,7 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Ferrari</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -33167,7 +33167,7 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -33189,7 +33189,7 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Canva</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -33211,7 +33211,7 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>Canva</t>
+          <t>AQR Capital</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -33233,7 +33233,7 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>AQR Capital</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -33255,7 +33255,7 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -33277,7 +33277,7 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Electric</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -33299,7 +33299,7 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>General Electric</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -33321,7 +33321,7 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -33343,7 +33343,7 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -33365,7 +33365,7 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -33387,7 +33387,7 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -33409,7 +33409,7 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -38733,7 +38733,7 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
@@ -39265,7 +39265,7 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
@@ -39321,7 +39321,7 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
@@ -39377,7 +39377,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
@@ -39405,7 +39405,7 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-17 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-18 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -39937,7 +39937,7 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B176" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-18 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-19 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38565,7 +38565,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -39433,7 +39433,7 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -40105,7 +40105,7 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
@@ -40217,7 +40217,7 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-19 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-20 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -39965,7 +39965,7 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
@@ -40161,7 +40161,7 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-20 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-21 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -39041,7 +39041,7 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-23 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-24 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="K228" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 60 US intern requisitions were listed on GM's Workday job board on October 21, 2026, with the nearest scheduled end dates on October 23 (Human Interface Design) and October 30, 2026. At least 28 requisitions have closed since postings began August 17, 2026, including the seven motorsports postings (end date October 15, 2026), Sales Intern (end date October 9, 2026), PFMEA</t>
+          <t>Open now for summer 2027: 60 US intern requisitions were listed on GM's Workday job board on October 21, 2026. Human Interface Design came down after its October 23 end date, and on October 24 the nearest scheduled end dates were October 30 and November 6, 2026. At least 28 requisitions have closed since postings began August 17, 2026, including the seven motorsports postings (end date October 15,</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–October 2027</t>
         </is>
       </c>
       <c r="D317" s="6" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>Open now, with short posting end dates. Three Summer 2027 reqs live on T-Mobile's Workday as of October 22, 2026: Software Engineering Intern (Bellevue, ends October 23, 2026), Human Resources &amp; Workplace Experience (ends October 26, 2026) and Software Engineer, Cloud Security (Atlanta and Frisco, ends October 27, 2026). Other tracks not yet posted</t>
+          <t>Open now, with short posting end dates. Two Summer 2027 reqs live on T-Mobile's Workday on October 24, 2026: Human Resources &amp; Workplace Experience (ends October 26, 2026) and Software Engineer, Cloud Security (Atlanta and Frisco, ends October 27, 2026). The Software Engineering Intern req (Bellevue) closed after its October 23 end date. Other tracks not yet posted</t>
         </is>
       </c>
     </row>
@@ -19351,12 +19351,12 @@
       </c>
       <c r="J337" s="6" t="inlineStr">
         <is>
-          <t>$85,000–$125,000 annualized depending on division and location (IB and Markets at the top; Technology and Services lower)</t>
+          <t>$60,000–$135,000 annualized on the 12 US Summer Analyst 2027 postings live October 24, 2026 (Technology $80,000–$110,000; Corporate Banking Houston $100,000–$13</t>
         </is>
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 18 US Summer Analyst requisitions live now on Citi's Workday board, confirmed September 21, 2026: Corporate Banking (Atlanta, Houston, San Francisco), Commercial Banking (Houston), Markets Sales and Trading and Quantitative Analysis (New York), Services (New York), Wealth (New York, Miami, Dallas, Los Angeles) and Risk, Internal Audit an</t>
+          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 12 US Summer Analyst requisitions live on Citi's Workday board on October 24, 2026: seven Technology reqs posted October 23 (Application Development in Irving, Jacksonville, Tampa and New York/New Jersey; Cyber Security in Irving; Production Support in New York and Tampa), each printing a close date of October 30, 2026 , plus Corporate B</t>
         </is>
       </c>
     </row>
@@ -39097,7 +39097,7 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-25 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-26 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -39125,7 +39125,7 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -39135,7 +39135,7 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>Bridge — London (2027) — Deadline: January 3, 2027 (11:59 PM GMT)</t>
+          <t>FOCUS — London (2027) — Deadline: November 8, 2026 (11:59 PM GMT)</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr"/>
@@ -39163,7 +39163,7 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>FTTP — First-Year Trading &amp; Technology — London (2027) — Deadline: January 3, 2027 (11:59 PM GMT)</t>
+          <t>Bridge — London (2027) — Deadline: January 3, 2027 (11:59 PM GMT)</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr"/>
@@ -39191,7 +39191,7 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>FTTP — First-Year Trading &amp; Technology — New York (2027) — Deadline: January 31, 2027 (11:59 PM EST)</t>
+          <t>FTTP — First-Year Trading &amp; Technology — London (2027) — Deadline: January 3, 2027 (11:59 PM GMT)</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr"/>
@@ -39219,7 +39219,7 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>FOCUS — London (2027) — Deadline: November 8, 2026 (11:59 PM GMT)</t>
+          <t>FTTP — First-Year Trading &amp; Technology — New York (2027) — Deadline: January 31, 2027 (11:59 PM EST)</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr"/>

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-26 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-27 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -18133,7 +18133,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -18143,17 +18143,17 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>June–October 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D316" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data / Analytics; Cybersecurity  (3 of 6 tracks)</t>
+          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E316" s="7" t="inlineStr">
         <is>
-          <t>careers.t-mobile.com/internship</t>
+          <t>job-boards.greenhouse.io/xai</t>
         </is>
       </c>
       <c r="F316" s="7" t="inlineStr">
@@ -18163,34 +18163,34 @@
       </c>
       <c r="G316" s="6" t="inlineStr">
         <is>
-          <t>Typically a recruiter phone screen, then a behavioral or hiring-manager round (sometimes a group interview), with an online assessment added for some technology roles. After interviews, candidates often fill out a form to rank project teams. Glassdoor rates interview difficulty a moderate 2.7/5, and</t>
+          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
         </is>
       </c>
       <c r="H316" s="6" t="inlineStr">
         <is>
-          <t>The Summer 2027 postings (live October 22, 2026) print no sponsorship sentence; the SWE postings require authorization to work in the US now and in the future. Prior-cycle JDs said T-Mobile does not sponsor work visas, i</t>
+          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
         </is>
       </c>
       <c r="I316" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively. Roles are posted on a 1:1 basis and close once the position is filled, so apply the week a req opens</t>
+          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
         </is>
       </c>
       <c r="J316" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Summer 2027 postings (live October 22, 2026): $27 to $50/hr for Software Engineering and Cloud Security, $26–$47/hr for Human Resources &amp; Workplace Experience. </t>
+          <t xml:space="preserve">Per the summer 2027 postings: software engineering $30/hr (freshman/sophomore), $34 (junior/senior), $36 to $40 (completed degrees); business operations $24.50 </t>
         </is>
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>Open now, with short posting end dates. Two Summer 2027 reqs live on T-Mobile's Workday on October 24, 2026: Human Resources &amp; Workplace Experience (ends October 26, 2026) and Software Engineer, Cloud Security (Atlanta and Frisco, ends October 27, 2026). The Software Engineering Intern req (Bellevue) closed after its October 23 end date. Other tracks not yet posted</t>
+          <t>Open now: Summer 2027 Software Engineering and Business Operations internships posted 2 October 2026 (Spring 2027 versions posted the same day). Rolling, no deadline published; positions close once filled</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -18200,17 +18200,17 @@
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>September 2027 – February 2028</t>
         </is>
       </c>
       <c r="D317" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; ML Research Intern; Engineering Intern (ME/EE/Controls); AI Infrastructure Intern; Data Engineer Intern  (5 of 6 tracks)</t>
+          <t>Quality Engineering Intern; R&amp;D / Vehicle Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E317" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/xai</t>
+          <t>jobs.porsche.com</t>
         </is>
       </c>
       <c r="F317" s="7" t="inlineStr">
@@ -18220,34 +18220,34 @@
       </c>
       <c r="G317" s="6" t="inlineStr">
         <is>
-          <t>Four rounds for SWE: an initial engineer call (15–30 minutes), a CodeSignal coding assessment (60 minutes), 2–3 onsite or virtual coding rounds, and a system design challenge. Glassdoor rates the difficulty at 3.24 out of 5. The total timeline runs 2–6 weeks.</t>
+          <t>Expect one to two interview rounds: a phone or video screen covering your background and motivation, followed by a deeper behavioral interview or case study with the hiring manager. Porsche Consulting roles include two case studies. PCNA candidates report an average of 43 days from application to hi</t>
         </is>
       </c>
       <c r="H317" s="6" t="inlineStr">
         <is>
-          <t>Mixed signals: careers page says yes, some listings say no. CPT/OPT for F-1 is standard; direct sponsorship varies by role</t>
+          <t>Check each posting individually. PCNA roles typically require US work authorization. Porsche AG roles in Germany follow German student-visa rules</t>
         </is>
       </c>
       <c r="I317" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions posted on Greenhouse and reviewed on a rolling basis until filled</t>
+          <t>Yes. Porsche posts and fills internship roles on a rolling basis. Some roles stay open only weeks, so apply promptly when a posting appears</t>
         </is>
       </c>
       <c r="J317" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per the summer 2027 postings: software engineering $30/hr (freshman/sophomore), $34 (junior/senior), $36 to $40 (completed degrees); business operations $24.50 </t>
+          <t>$18 to $20 per hour on the PCNA intern postings live in October 2026 ($19 to $21 for a Porsche Design of America retail role in Costa Mesa). Indeed reports an a</t>
         </is>
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>Open now: Summer 2027 Software Engineering and Business Operations internships posted 2 October 2026 (Spring 2027 versions posted the same day). Rolling, no deadline published; positions close once filled</t>
+          <t>Open now: PCNA posted at least 10 intern roles between September 15 and 30, 2026, most running March to September 2027 (Accounting, Finance, Compliance, Aftersales Projects and Strategy, Digital Transformation and Data Intelligence), plus a Miami role running February to September 2027. More postings may follow through January 2027. Porsche AG recommends applying about six months before desired st</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Qatalyst Partners</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -18257,17 +18257,17 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>September 2027 – February 2028</t>
+          <t>September–October 2027</t>
         </is>
       </c>
       <c r="D318" s="6" t="inlineStr">
         <is>
-          <t>Quality Engineering Intern; R&amp;D / Vehicle Engineering Intern  (2 of 6 tracks)</t>
+          <t>1 track: Tech M&amp;A Summer Analyst. Qatalyst is a pure advisory firm with no separate S&amp;T, research, or capital markets divisions</t>
         </is>
       </c>
       <c r="E318" s="7" t="inlineStr">
         <is>
-          <t>jobs.porsche.com</t>
+          <t>app.joinhandshake.com/employers/qatalyst-partners-44145</t>
         </is>
       </c>
       <c r="F318" s="7" t="inlineStr">
@@ -18277,34 +18277,34 @@
       </c>
       <c r="G318" s="6" t="inlineStr">
         <is>
-          <t>Expect one to two interview rounds: a phone or video screen covering your background and motivation, followed by a deeper behavioral interview or case study with the hiring manager. Porsche Consulting roles include two case studies. PCNA candidates report an average of 43 days from application to hi</t>
+          <t>Qatalyst's funnel is compact and intense, typically spanning 2 to 3 weeks from first contact to offer: 1. Network before you apply (6+ months ahead). Identify 10 to 15 Qatalyst analysts and associates on LinkedIn, prioritizing university alumni. Conduct informational interviews in November to Decemb</t>
         </is>
       </c>
       <c r="H318" s="6" t="inlineStr">
         <is>
-          <t>Check each posting individually. PCNA roles typically require US work authorization. Porsche AG roles in Germany follow German student-visa rules</t>
+          <t>Not publicly confirmed. The firm recruits primarily from US universities; international students should contact uscareers@qatalyst.com directly</t>
         </is>
       </c>
       <c r="I318" s="6" t="inlineStr">
         <is>
-          <t>Yes. Porsche posts and fills internship roles on a rolling basis. Some roles stay open only weeks, so apply promptly when a posting appears</t>
+          <t>Semi-rolling. Positions fill on a rolling basis within the September-to-April window. The small class means spots disappear fast; apply when the portal opens</t>
         </is>
       </c>
       <c r="J318" s="6" t="inlineStr">
         <is>
-          <t>$18 to $20 per hour on the PCNA intern postings live in October 2026 ($19 to $21 for a Porsche Design of America retail role in Costa Mesa). Indeed reports an a</t>
+          <t>$110,000 to $120,000 annualized base (~$21,000 to $23,000 pro-rated for 10 weeks). Housing/relocation stipend included. Full-time Year 1 total comp: $225,000 to</t>
         </is>
       </c>
       <c r="K318" s="6" t="inlineStr">
         <is>
-          <t>Open now: PCNA posted at least 10 intern roles between September 15 and 30, 2026, most running March to September 2027 (Accounting, Finance, Compliance, Aftersales Projects and Strategy, Digital Transformation and Data Intelligence), plus a Miami role running February to September 2027. More postings may follow through January 2027. Porsche AG recommends applying about six months before desired st</t>
+          <t>Expected September to October 2027 for Summer 2028 roles. Interviews run January through March 2028, with most offers by late March. Projected from prior cycles. Summer 2027: US postings expected September to December 2026 (Adventis Finance); London 2027 internship open now</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Qatalyst Partners</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -18314,17 +18314,17 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>September–October 2027</t>
+          <t>December 2027</t>
         </is>
       </c>
       <c r="D319" s="6" t="inlineStr">
         <is>
-          <t>1 track: Tech M&amp;A Summer Analyst. Qatalyst is a pure advisory firm with no separate S&amp;T, research, or capital markets divisions</t>
+          <t>Agent Software Engineer Intern; Agent Software Engineer – New Grad (adjacent pipeline)  (2 of 3 tracks)</t>
         </is>
       </c>
       <c r="E319" s="7" t="inlineStr">
         <is>
-          <t>app.joinhandshake.com/employers/qatalyst-partners-44145</t>
+          <t>jobs.ashbyhq.com/decagon</t>
         </is>
       </c>
       <c r="F319" s="7" t="inlineStr">
@@ -18334,34 +18334,34 @@
       </c>
       <c r="G319" s="6" t="inlineStr">
         <is>
-          <t>Qatalyst's funnel is compact and intense, typically spanning 2 to 3 weeks from first contact to offer: 1. Network before you apply (6+ months ahead). Identify 10 to 15 Qatalyst analysts and associates on LinkedIn, prioritizing university alumni. Conduct informational interviews in November to Decemb</t>
+          <t>A recruiter screen, a 45- to 60-minute technical phone screen in TypeScript or Python, then a full-day on-site with coding pair, system design, project deep dive, and behavioral rounds. The entire process averages 13 days. Expect AI-agent-specific system design questions.</t>
         </is>
       </c>
       <c r="H319" s="6" t="inlineStr">
         <is>
-          <t>Not publicly confirmed. The firm recruits primarily from US universities; international students should contact uscareers@qatalyst.com directly</t>
+          <t>Full-time H-1B confirmed (11 LCAs in FY2026). Intern CPT/OPT not explicitly confirmed; likely supported given the University department classification</t>
         </is>
       </c>
       <c r="I319" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling. Positions fill on a rolling basis within the September-to-April window. The small class means spots disappear fast; apply when the portal opens</t>
+          <t xml:space="preserve">Likely yes. The Summer 2026 listing remained open for several months. Glassdoor reports a 13-day average hiring process, suggesting quick turnaround consistent </t>
         </is>
       </c>
       <c r="J319" s="6" t="inlineStr">
         <is>
-          <t>$110,000 to $120,000 annualized base (~$21,000 to $23,000 pro-rated for 10 weeks). Housing/relocation stipend included. Full-time Year 1 total comp: $225,000 to</t>
+          <t xml:space="preserve">$3,000/week (~$75/hr at 40 hours a week) plus a $10,000 housing stipend, as printed on the Engineering Intern (Summer 2027) posting listed on October 11, 2026. </t>
         </is>
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>Expected September to October 2027 for Summer 2028 roles. Interviews run January through March 2028, with most offers by late March. Projected from prior cycles. Summer 2027: US postings expected September to December 2026 (Adventis Finance); London 2027 internship open now</t>
+          <t>Open now for summer 2027: Decagon's Engineering Intern (Summer 2027) posting for San Francisco was listed on its Ashby board on October 11, 2026, with no closing date printed. Posted August 20, 2026. Rolling review is likely</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -18376,12 +18376,12 @@
       </c>
       <c r="D320" s="6" t="inlineStr">
         <is>
-          <t>Agent Software Engineer Intern; Agent Software Engineer – New Grad (adjacent pipeline)  (2 of 3 tracks)</t>
+          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E320" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/decagon</t>
+          <t>pepsicojobs.com/internshipsprograms</t>
         </is>
       </c>
       <c r="F320" s="7" t="inlineStr">
@@ -18391,54 +18391,50 @@
       </c>
       <c r="G320" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a 45- to 60-minute technical phone screen in TypeScript or Python, then a full-day on-site with coding pair, system design, project deep dive, and behavioral rounds. The entire process averages 13 days. Expect AI-agent-specific system design questions.</t>
-        </is>
-      </c>
-      <c r="H320" s="6" t="inlineStr">
-        <is>
-          <t>Full-time H-1B confirmed (11 LCAs in FY2026). Intern CPT/OPT not explicitly confirmed; likely supported given the University department classification</t>
-        </is>
-      </c>
+          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
+        </is>
+      </c>
+      <c r="H320" s="6" t="inlineStr"/>
       <c r="I320" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Likely yes. The Summer 2026 listing remained open for several months. Glassdoor reports a 13-day average hiring process, suggesting quick turnaround consistent </t>
+          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
         </is>
       </c>
       <c r="J320" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$3,000/week (~$75/hr at 40 hours a week) plus a $10,000 housing stipend, as printed on the Engineering Intern (Summer 2027) posting listed on October 11, 2026. </t>
+          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
         </is>
       </c>
       <c r="K320" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Decagon's Engineering Intern (Summer 2027) posting for San Francisco was listed on its Ashby board on October 11, 2026, with no closing date printed. Posted August 20, 2026. Rolling review is likely</t>
+          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
-        </is>
-      </c>
-      <c r="B321" s="4" t="inlineStr">
-        <is>
-          <t>Window open - check now</t>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>December 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D321" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE/Data Science)  (1 of 6 tracks)</t>
+          <t>Media Tech Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E321" s="7" t="inlineStr">
         <is>
-          <t>pepsicojobs.com/internshipsprograms</t>
+          <t>jobs.comcast.com/early-career</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
@@ -18448,30 +18444,34 @@
       </c>
       <c r="G321" s="6" t="inlineStr">
         <is>
-          <t>PepsiCo's funnel has more steps than a typical CPG firm but moves fast, averaging about 15 days from application to decision according to Glassdoor: 1. Find your track at pepsicojobs.com using the career-area filter. PepsiCo's recruiting chatbot (Chester Cheetah) can help match roles. Upload your re</t>
-        </is>
-      </c>
-      <c r="H321" s="6" t="inlineStr"/>
+          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr">
+        <is>
+          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
+        </is>
+      </c>
       <c r="I321" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as strong candidates apply; PepsiCo recommends applying within the first 1–2 weeks</t>
+          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
         </is>
       </c>
       <c r="J321" s="6" t="inlineStr">
         <is>
-          <t>$20–$37/hr depending on role and location; supply chain interns at Frito-Lay report $33/hr plus a $2,250 housing stipend</t>
+          <t>Not published on Comcast's or NBCUniversal's own pages; check each posting</t>
         </is>
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 10+ Summer 2027 intern roles live at pepsicojobs.com, including R&amp;D, HR, and Winter 2027 Co-op tracks. Rolling review (documented pattern from 2026 cycle: Aug 25–Oct 31, 2025)</t>
+          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
@@ -18481,17 +18481,17 @@
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – February 2027</t>
         </is>
       </c>
       <c r="D322" s="6" t="inlineStr">
         <is>
-          <t>Media Tech Internship  (1 of 6 tracks)</t>
+          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E322" s="7" t="inlineStr">
         <is>
-          <t>jobs.comcast.com/early-career</t>
+          <t>deepmind.google/student-researcher-program/</t>
         </is>
       </c>
       <c r="F322" s="7" t="inlineStr">
@@ -18501,34 +18501,30 @@
       </c>
       <c r="G322" s="6" t="inlineStr">
         <is>
-          <t>No standardized coding online assessment for most roles. The first round is a HireVue one-way video with 4 to 6 behavioral questions, followed by an HR screen, then a 45-minute panel interview. The entire process is behavioral for the majority of positions. Some SWE roles may include technical quest</t>
-        </is>
-      </c>
-      <c r="H322" s="6" t="inlineStr">
-        <is>
-          <t>No. Both require interns to be presently authorized to work in the United States without sponsorship. F-1 CPT, F-1 OPT, J-1, and M-1 visa holders are not eligible unless they can adjust to a non-sponsored work authorizat</t>
-        </is>
-      </c>
+          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr"/>
       <c r="I322" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling. Official deadline exists but programs close early due to volume; apply week one</t>
+          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
         </is>
       </c>
       <c r="J322" s="6" t="inlineStr">
         <is>
-          <t>Not published on Comcast's or NBCUniversal's own pages; check each posting</t>
+          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
         </is>
       </c>
       <c r="K322" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open mid-November 2026; may close early December 2026 (semi-rolling, volume-dependent, projected from prior cycle)</t>
+          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -18538,17 +18534,17 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – February 2027</t>
+          <t>November 2026 – January 2027</t>
         </is>
       </c>
       <c r="D323" s="6" t="inlineStr">
         <is>
-          <t>Student Researcher (PhD); Student Researcher (BS/MS); SWE Intern (via Google)  (3 of 5 tracks)</t>
+          <t>Software Engineering Intern  (1 of 3 tracks)</t>
         </is>
       </c>
       <c r="E323" s="7" t="inlineStr">
         <is>
-          <t>deepmind.google/student-researcher-program/</t>
+          <t>gusto.com/about/careers</t>
         </is>
       </c>
       <c r="F323" s="7" t="inlineStr">
@@ -18558,30 +18554,34 @@
       </c>
       <c r="G323" s="6" t="inlineStr">
         <is>
-          <t>The process spans six to ten weeks across five stages: recruiter screen, hiring manager chat, one to two technical phone screens, a full-day onsite loop with four to five rounds, and a hiring committee review. Research roles include a paper discussion, ML coding, and a math and theory round. AI tool</t>
-        </is>
-      </c>
-      <c r="H323" s="6" t="inlineStr"/>
+          <t>The process has five stages: a CodeSignal GCA with 3 coding questions, a recruiter phone screen via Zoom, a 60-minute technical interview with 1 to 2 LeetCode medium-to-hard problems, a 90-minute collaborative work session simulating pair programming, and two 30-minute behavioral interviews covering</t>
+        </is>
+      </c>
+      <c r="H323" s="6" t="inlineStr">
+        <is>
+          <t>Not available for SWE in past cycles: Gusto's SWE intern postings stated the role is not available for sponsorship. The Summer 2027 Finance Intern posting (closed October 26, 2026) printed no sponsorship line</t>
+        </is>
+      </c>
       <c r="I323" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official: "reviewed on a rolling basis" and the window "may close earlier if all available projects are full"</t>
+          <t>For SWE, yes in past cycles: Gusto extends offers on a rolling basis within the application window. The Summer 2027 Finance Intern posting instead had a fixed d</t>
         </is>
       </c>
       <c r="J323" s="6" t="inlineStr">
         <is>
-          <t>Research interns: ~$72/hr ($12,500/mo) + $9,000 housing at Mountain View (Levels.fyi, 2025 data)</t>
+          <t>SWE, Summer 2026 cycle (no Summer 2027 SWE posting yet): $58.65/hr undergrad, $64.42/hr graduate (SF &amp; NYC). $46.63/hr undergrad, $51.44/hr graduate (Denver). P</t>
         </is>
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>Expected late 2026 to early 2027 for Summer 2027 Student Researcher; SWE Intern Summer 2027 has already closed (documented pattern; not yet posted for 2028)</t>
+          <t>Finance Intern (Summer 2027): closed (posted October 13, deadline October 26, 2026). SWE intern (Summer 2027): not yet posted as of October 27, 2026; expected this fall, with rolling offers November through January, projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
@@ -18591,17 +18591,17 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – January 2027</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D324" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern  (1 of 3 tracks)</t>
+          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E324" s="7" t="inlineStr">
         <is>
-          <t>gusto.com/about/careers</t>
+          <t>apply.workable.com/huggingface</t>
         </is>
       </c>
       <c r="F324" s="7" t="inlineStr">
@@ -18611,34 +18611,34 @@
       </c>
       <c r="G324" s="6" t="inlineStr">
         <is>
-          <t>The process has five stages: a CodeSignal GCA with 3 coding questions, a recruiter phone screen via Zoom, a 60-minute technical interview with 1 to 2 LeetCode medium-to-hard problems, a 90-minute collaborative work session simulating pair programming, and two 30-minute behavioral interviews covering</t>
+          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
         </is>
       </c>
       <c r="H324" s="6" t="inlineStr">
         <is>
-          <t>Not available for SWE in past cycles: Gusto's SWE intern postings stated the role is not available for sponsorship. The Summer 2027 Finance Intern posting, live October 22, 2026, prints no sponsorship line</t>
+          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
         </is>
       </c>
       <c r="I324" s="6" t="inlineStr">
         <is>
-          <t>For SWE, yes in past cycles: Gusto extends offers on a rolling basis within the application window. The Summer 2027 Finance Intern posting instead has a fixed d</t>
+          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
         </is>
       </c>
       <c r="J324" s="6" t="inlineStr">
         <is>
-          <t>SWE, Summer 2026 cycle (no Summer 2027 SWE posting yet): $58.65/hr undergrad, $64.42/hr graduate (SF &amp; NYC). $46.63/hr undergrad, $51.44/hr graduate (Denver). P</t>
+          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
         </is>
       </c>
       <c r="K324" s="6" t="inlineStr">
         <is>
-          <t>Finance Intern (Summer 2027): live on Greenhouse since October 13, 2026, deadline Monday, October 26, 2026 at 4:00 pm PST. SWE intern (Summer 2027): not yet posted as of October 22, 2026; expected this fall, with rolling offers November through January, projected from the Summer 2026 cycle</t>
+          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -18648,17 +18648,17 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – September 2027</t>
         </is>
       </c>
       <c r="D325" s="6" t="inlineStr">
         <is>
-          <t>FineWeb ML Research Intern (Science); Generative AI Intern (Science); Embodied AI Intern (Science); ML for Code Intern (Open Source)  (4 of 6 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E325" s="7" t="inlineStr">
         <is>
-          <t>apply.workable.com/huggingface</t>
+          <t>jefferies.tal.net</t>
         </is>
       </c>
       <c r="F325" s="7" t="inlineStr">
@@ -18668,34 +18668,34 @@
       </c>
       <c r="G325" s="6" t="inlineStr">
         <is>
-          <t>No traditional timed OA. You receive a take-home project (build a Spaces demo, replicate a baseline, fix a library bug), then have 1 to 2 technical calls and a culture and behavioral round. The whole process takes about 3 to 4 weeks of active interviews and roughly 1.5 months from application to off</t>
+          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
         </is>
       </c>
       <c r="H325" s="6" t="inlineStr">
         <is>
-          <t>H-1B confirmed for full-time roles (3 petitions filed FY2025, 100% approved). Intern-specific J-1 or F-1 CPT sponsorship not explicitly confirmed but likely given the track record</t>
+          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
         </is>
       </c>
       <c r="I325" s="6" t="inlineStr">
         <is>
-          <t>Yes. Individual team internships open and close at different times. No single batch deadline exists</t>
+          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
         </is>
       </c>
       <c r="J325" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roughly $18/hr in Paris (35,000 EUR/year) or roughly $24/hr in New York ($50,000/year). Housing allowance and transportation stipend included. Pay is below Big </t>
+          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
         </is>
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>Expected late November to December 2026 for Summer 2027 roles. No fixed deadline announced; positions fill on a rolling, team-by-team basis. Projected from prior cycles</t>
+          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted. Still live as of October 2, 2026: 2027 Jefferies Finance Summer Analyst roles (Data Analytics; Financial Planning &amp; Accounting), the</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
@@ -18705,17 +18705,17 @@
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – September 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D326" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>6+ tracks: KP LAUNCH, Business/IT, Research &amp; Evaluation, Community Health, Pharmacy, Administrative Fellowship, plus clinical placements</t>
         </is>
       </c>
       <c r="E326" s="7" t="inlineStr">
         <is>
-          <t>jefferies.tal.net</t>
+          <t>kaiserpermanentejobs.org/category/internships-jobs/641/48394</t>
         </is>
       </c>
       <c r="F326" s="7" t="inlineStr">
@@ -18725,34 +18725,34 @@
       </c>
       <c r="G326" s="6" t="inlineStr">
         <is>
-          <t>Three to five one-on-one interviews over a half-day to full day, typically in-office in New York. Interviewers are VPs, Directors, and Managing Directors. Expect heavy technical questions (DCF, LBO, comparable analysis, EV/equity bridge) plus behavioral and cultural-fit evaluation. Offers often come</t>
+          <t>Glassdoor rates intern interviews at 2.7 out of 5 difficulty, and 72% of candidates report a positive experience. Expect a 30- to 45-minute interview with 6 to 8 questions, a mix of behavioral (STAR format) and role-specific. The tone is conversational. IT roles may include technical scenario questi</t>
         </is>
       </c>
       <c r="H326" s="6" t="inlineStr">
         <is>
-          <t>F-1 sponsorship available; STEM OPT extension eligible; H-1B lottery participation confirmed. Must be authorized to work in the U.S. for the summer period</t>
+          <t>Not typically offered for internship programs. Applicants must provide proof of eligibility to work in the United States. CPT/OPT not explicitly confirmed for intern roles</t>
         </is>
       </c>
       <c r="I326" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Jefferies reviews applications on a rolling basis; candidates who apply in the first two to three weeks have significantly higher callback rates</t>
+          <t>Most tracks are not strictly rolling. KP LAUNCH and Business/IT have fixed windows with a single deadline. Research reviews after the close. Administrative Fell</t>
         </is>
       </c>
       <c r="J326" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">~$110,000 annualized base (~$52.88/hr), plus 1.5x overtime for hours over 40/week. Total summer earnings with OT: $35,000 to $45,000. Housing stipend of $2,000 </t>
+          <t>$25.09–$29.16/hr for KP LAUNCH College interns, based on education year, as listed on the KP LAUNCH site on October 11, 2026. The one IT internship listed on ka</t>
         </is>
       </c>
       <c r="K326" s="6" t="inlineStr">
         <is>
-          <t>Projected ~November 2026 to February 2027 (rolling) for IB Summer Analyst, with deadlines by ~April 2027; diversity programs in the January to February 2027 window. Projected from the prior cycle (summer 2027 IB opened ~December 2025 to January 2026), not yet posted. Still live as of October 2, 2026: 2027 Jefferies Finance Summer Analyst roles (Data Analytics; Financial Planning &amp; Accounting), the</t>
+          <t>Varies by track. On October 11, 2026, no posting on kaiserpermanentejobs.org named summer 2027. KP LAUNCH: opens November 16, 2026 and closes January 8, 2027, per the KP LAUNCH site. Business/IT: expected January to April 2027. Research: expected February to March 2027. Administrative Fellowship: closed August 31, 2026 for programs starting in 2027. Business/IT and Research months follow Kaiser Pe</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Magna</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -18767,12 +18767,12 @@
       </c>
       <c r="D327" s="6" t="inlineStr">
         <is>
-          <t>6+ tracks: KP LAUNCH, Business/IT, Research &amp; Evaluation, Community Health, Pharmacy, Administrative Fellowship, plus clinical placements</t>
+          <t>Mechanical Engineering Intern (primary); Manufacturing / Process Engineering Intern; Software / Solution Engineering Intern; Engineering Co-Op  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E327" s="7" t="inlineStr">
         <is>
-          <t>kaiserpermanentejobs.org/category/internships-jobs/641/48394</t>
+          <t>magna.com/careers/students</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
@@ -18782,34 +18782,30 @@
       </c>
       <c r="G327" s="6" t="inlineStr">
         <is>
-          <t>Glassdoor rates intern interviews at 2.7 out of 5 difficulty, and 72% of candidates report a positive experience. Expect a 30- to 45-minute interview with 6 to 8 questions, a mix of behavioral (STAR format) and role-specific. The tone is conversational. IT roles may include technical scenario questi</t>
-        </is>
-      </c>
-      <c r="H327" s="6" t="inlineStr">
-        <is>
-          <t>Not typically offered for internship programs. Applicants must provide proof of eligibility to work in the United States. CPT/OPT not explicitly confirmed for intern roles</t>
-        </is>
-      </c>
+          <t>Rolling and division-run: a recruiter or HR screen, then a hiring-manager interview (often on-site at the plant), plus a role-specific technical round for engineering, data, and software candidates. Community reports describe it as conversational and project- and fundamentals-focused, not heavy on L</t>
+        </is>
+      </c>
+      <c r="H327" s="6" t="inlineStr"/>
       <c r="I327" s="6" t="inlineStr">
         <is>
-          <t>Most tracks are not strictly rolling. KP LAUNCH and Business/IT have fixed windows with a single deadline. Research reviews after the close. Administrative Fell</t>
+          <t>Yes. Intern and co-op reqs are posted and filled per-division on a rolling basis; there is no single company-wide deadline. Reqs close when filled, so apply ear</t>
         </is>
       </c>
       <c r="J327" s="6" t="inlineStr">
         <is>
-          <t>$25.09–$29.16/hr for KP LAUNCH College interns, based on education year, as listed on the KP LAUNCH site on October 11, 2026. The one IT internship listed on ka</t>
+          <t>An official Magna Powertrain engineering co-op JD lists $25/hour. Community aggregators put general intern pay around $18 to $34/hr (Indeed ~$20.54/hr; Glassdoo</t>
         </is>
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>Varies by track. On October 11, 2026, no posting on kaiserpermanentejobs.org named summer 2027. KP LAUNCH: opens November 16, 2026 and closes January 8, 2027, per the KP LAUNCH site. Business/IT: expected January to April 2027. Research: expected February to March 2027. Administrative Fellowship: closed August 31, 2026 for programs starting in 2027. Business/IT and Research months follow Kaiser Pe</t>
+          <t>Partly open. About 23 US intern and co-op reqs are live on Workday as of October 6, 2026 (Muncie IN Finance and Purchasing; Auburn Hills and Southfield engineering and IT; Troy humanoid robotics; Northwood OH and Grand Rapids co-ops; Holland, Holly and Bowling Green quality and IT; Highland Park program management and EHS), posted August to early October. Some earlier reqs have already closed, inc</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Magna</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -18819,17 +18815,17 @@
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November–December 2026</t>
         </is>
       </c>
       <c r="D328" s="6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern (primary); Manufacturing / Process Engineering Intern; Software / Solution Engineering Intern; Engineering Co-Op  (4 of 6 tracks)</t>
+          <t>Software Engineering Intern  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E328" s="7" t="inlineStr">
         <is>
-          <t>magna.com/careers/students</t>
+          <t>marqeta.com/company/careers</t>
         </is>
       </c>
       <c r="F328" s="7" t="inlineStr">
@@ -18839,30 +18835,34 @@
       </c>
       <c r="G328" s="6" t="inlineStr">
         <is>
-          <t>Rolling and division-run: a recruiter or HR screen, then a hiring-manager interview (often on-site at the plant), plus a role-specific technical round for engineering, data, and software candidates. Community reports describe it as conversational and project- and fundamentals-focused, not heavy on L</t>
-        </is>
-      </c>
-      <c r="H328" s="6" t="inlineStr"/>
+          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
+        </is>
+      </c>
       <c r="I328" s="6" t="inlineStr">
         <is>
-          <t>Yes. Intern and co-op reqs are posted and filled per-division on a rolling basis; there is no single company-wide deadline. Reqs close when filled, so apply ear</t>
+          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
         </is>
       </c>
       <c r="J328" s="6" t="inlineStr">
         <is>
-          <t>An official Magna Powertrain engineering co-op JD lists $25/hour. Community aggregators put general intern pay around $18 to $34/hr (Indeed ~$20.54/hr; Glassdoo</t>
+          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
         </is>
       </c>
       <c r="K328" s="6" t="inlineStr">
         <is>
-          <t>Partly open. About 23 US intern and co-op reqs are live on Workday as of October 6, 2026 (Muncie IN Finance and Purchasing; Auburn Hills and Southfield engineering and IT; Troy humanoid robotics; Northwood OH and Grand Rapids co-ops; Holland, Holly and Bowling Green quality and IT; Highland Park program management and EHS), posted August to early October. Some earlier reqs have already closed, inc</t>
+          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -18872,17 +18872,17 @@
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>November–December 2026</t>
+          <t>November 2026 – January 2027</t>
         </is>
       </c>
       <c r="D329" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern  (1 of 5 tracks)</t>
+          <t>Business — Analytics  (1 of 7 tracks)</t>
         </is>
       </c>
       <c r="E329" s="7" t="inlineStr">
         <is>
-          <t>marqeta.com/company/careers</t>
+          <t>ogilvyearlycareers.com/the-summer-internship</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
@@ -18892,34 +18892,30 @@
       </c>
       <c r="G329" s="6" t="inlineStr">
         <is>
-          <t>The intern interview typically includes three stages: a 30-minute recruiter video screen, a 60-minute technical coding session on HackerRank with 1 to 2 medium-level algorithm problems, and a final pair programming round lasting 45 to 60 minutes where you collaborate with an engineer. The full proce</t>
-        </is>
-      </c>
-      <c r="H329" s="6" t="inlineStr">
-        <is>
-          <t>US-based remote positions. International visa sponsorship status not confirmed in public postings</t>
-        </is>
-      </c>
+          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
+        </is>
+      </c>
+      <c r="H329" s="6" t="inlineStr"/>
       <c r="I329" s="6" t="inlineStr">
         <is>
-          <t>Partially. Marqeta collects candidates via the #MarqetaShip Talent Network year-round but conducts formal interview rounds within a defined window (late April t</t>
+          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
         </is>
       </c>
       <c r="J329" s="6" t="inlineStr">
         <is>
-          <t>$40 to $50 per hour ($6,933 to $8,667/month) depending on location tier: National ($40/hr), Premium ($45/hr), Premium Plus ($50/hr). Levels.fyi reports $45/hr a</t>
+          <t>$20 to $25/hr posted range (2026 cycle)</t>
         </is>
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>Talent Network expected to open November–December 2026. Formal intern postings projected January–March 2027. Interviews in late April through mid-May 2027. Projected from the Summer 2026 cycle</t>
+          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -18929,17 +18925,17 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – January 2027</t>
+          <t>November 2026</t>
         </is>
       </c>
       <c r="D330" s="6" t="inlineStr">
         <is>
-          <t>Business — Analytics  (1 of 7 tracks)</t>
+          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E330" s="7" t="inlineStr">
         <is>
-          <t>ogilvyearlycareers.com/the-summer-internship</t>
+          <t>ouraring.com/careers</t>
         </is>
       </c>
       <c r="F330" s="7" t="inlineStr">
@@ -18949,30 +18945,34 @@
       </c>
       <c r="G330" s="6" t="inlineStr">
         <is>
-          <t>After submitting your application (with portfolio for creative roles), expect a phone screen followed by a one-on-one interview. The process averages about four weeks. Interviewers ask behavioral questions, assess your knowledge of Ogilvy's clients and campaigns, and evaluate cultural fit. Reddit us</t>
-        </is>
-      </c>
-      <c r="H330" s="6" t="inlineStr"/>
+          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
+        </is>
+      </c>
+      <c r="H330" s="6" t="inlineStr">
+        <is>
+          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
+        </is>
+      </c>
       <c r="I330" s="6" t="inlineStr">
         <is>
-          <t>No. Fixed deadline (January 5 in the 2026 cycle). Batch review after close</t>
+          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
         </is>
       </c>
       <c r="J330" s="6" t="inlineStr">
         <is>
-          <t>$20 to $25/hr posted range (2026 cycle)</t>
+          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
         </is>
       </c>
       <c r="K330" s="6" t="inlineStr">
         <is>
-          <t>Expected late November 2026 to early January 2027 for summer 2027 (documented 2026-cycle pattern; not yet posted)</t>
+          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -18982,17 +18982,17 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>November 2026</t>
+          <t>November 2026 – March 2027</t>
         </is>
       </c>
       <c r="D331" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (primary, via EOI); Summer Trainee, Embedded SW &amp; AI-Assisted Development; Data Science / ML Intern (implied)  (3 of 5 tracks)</t>
+          <t>Genentech Summer Internship; Genentech Research Intern (PhD); Genentech Co-Op  (3 of 7 tracks)</t>
         </is>
       </c>
       <c r="E331" s="7" t="inlineStr">
         <is>
-          <t>ouraring.com/careers</t>
+          <t>careers.roche.com/global/en/roche-internship-program</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -19002,34 +19002,30 @@
       </c>
       <c r="G331" s="6" t="inlineStr">
         <is>
-          <t>Documented from the Finland trainee JD: a recruiter screen followed by a hiring-manager interview, with no coding online assessment mentioned. Glassdoor rates interview difficulty 3/5 with 82% positive experiences. Engineering roles may add a technical or portfolio discussion (system-design chat, co</t>
-        </is>
-      </c>
-      <c r="H331" s="6" t="inlineStr">
-        <is>
-          <t>Not stated. US internships require US-based enrollment and being US-based; intern visa sponsorship is not published (NOT FOUND). Oura does not relocate people for Finland-based roles. International students at US schools</t>
-        </is>
-      </c>
+          <t xml:space="preserve">After applying, most candidates go through a phone or video screen (20 to 30 minutes) followed by one to three interviews mixing technical and behavioral questions. Some programs add an assessment center, group exercise, or presentation. The entire process averages about 42 days from application to </t>
+        </is>
+      </c>
+      <c r="H331" s="6" t="inlineStr"/>
       <c r="I331" s="6" t="inlineStr">
         <is>
-          <t>No for internships. US roles are seasonal summer cohorts (10–12 weeks, June–August) recruited in a defined Nov–April window; the Finland trainee track used a fi</t>
+          <t>Implied yes. Postings may close before stated deadlines and Genentech posts positions "on an ongoing basis"</t>
         </is>
       </c>
       <c r="J331" s="6" t="inlineStr">
         <is>
-          <t>Paid, and every intern keeps an Oura Ring. Documented US rates: Hardware R&amp;D Research Intern $33–$36/hr (SF); Strategy &amp; Operations Intern $76,500–$103,500 annu</t>
+          <t>Roche median $37/hr ($28–$49); Genentech median $35/hr ($28–$45); PhD AI/ML $40–$50/hr per official postings</t>
         </is>
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>Expected ~November 2026 through April 2027 for US roles (applications for summer 2027 expected to open ~Nov 2026), based on documented prior cycles. Finland Summer Trainee deadline expected ~mid-March 2027. As of August 2026, no 2027 postings were live yet</t>
+          <t>Summer 2027 main wave expected Nov 2026–Mar 2027 (documented pattern; not yet posted). No Roche internship postings live in the US as of Oct 1, 2026; Genentech posts separately on careers.gene.com</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Analysis Group</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -19039,17 +19035,17 @@
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>November 2026 – March 2027</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D332" s="6" t="inlineStr">
         <is>
-          <t>Genentech Summer Internship; Genentech Research Intern (PhD); Genentech Co-Op  (3 of 7 tracks)</t>
+          <t>Data Science Intern (when available)  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E332" s="7" t="inlineStr">
         <is>
-          <t>careers.roche.com/global/en/roche-internship-program</t>
+          <t>analysisgroup.com/careers/career-path/summer-analyst-intern/</t>
         </is>
       </c>
       <c r="F332" s="7" t="inlineStr">
@@ -19059,30 +19055,34 @@
       </c>
       <c r="G332" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">After applying, most candidates go through a phone or video screen (20 to 30 minutes) followed by one to three interviews mixing technical and behavioral questions. Some programs add an assessment center, group exercise, or presentation. The entire process averages about 42 days from application to </t>
-        </is>
-      </c>
-      <c r="H332" s="6" t="inlineStr"/>
+          <t>Analysis Group's funnel is interview-focused with no standardized online assessment , and the average time from application to hire is about 23 days : 1. Apply on the Analysis Group careers portal . Upload your resume, cover letter (include geographic preferences for offices), and unofficial transcr</t>
+        </is>
+      </c>
+      <c r="H332" s="6" t="inlineStr">
+        <is>
+          <t>Yes, for consultant and data science positions. Not available for administrative roles</t>
+        </is>
+      </c>
       <c r="I332" s="6" t="inlineStr">
         <is>
-          <t>Implied yes. Postings may close before stated deadlines and Genentech posts positions "on an ongoing basis"</t>
+          <t>Applications are reviewed by the posted deadline. If no deadline is listed, review is rolling. Apply now for the strongest position: late Generalist and Account</t>
         </is>
       </c>
       <c r="J332" s="6" t="inlineStr">
         <is>
-          <t>Roche median $37/hr ($28–$49); Genentech median $35/hr ($28–$45); PhD AI/ML $40–$50/hr per official postings</t>
+          <t>Summer Analyst ~$1,750 to $2,100/week (~$35/hr annualized on Glassdoor), plus ~$1,500 sign-on bonus. Summer Associate ~$2,400 to $2,800/week</t>
         </is>
       </c>
       <c r="K332" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 main wave expected Nov 2026–Mar 2027 (documented pattern; not yet posted). No Roche internship postings live in the US as of Oct 1, 2026; Genentech posts separately on careers.gene.com</t>
+          <t>Still open for Summer Analyst (2027 start): the Generalist and Accounting deadline of September 30, 2026 has passed, but both postings were live on October 2, 2026 and the firm keeps reviewing on a rolling basis, considering late applicants pending availability. Health Care (HEOR, Epidemiology &amp; Market Access) deadline: October 28, 2026. Summer Associate: expected December 2026 to March 2027</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Analysis Group</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -19092,17 +19092,17 @@
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D333" s="6" t="inlineStr">
         <is>
-          <t>Data Science Intern (when available)  (1 of 4 tracks)</t>
+          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E333" s="7" t="inlineStr">
         <is>
-          <t>analysisgroup.com/careers/career-path/summer-analyst-intern/</t>
+          <t>search.jobs.barclays/internships</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
@@ -19112,34 +19112,34 @@
       </c>
       <c r="G333" s="6" t="inlineStr">
         <is>
-          <t>Analysis Group's funnel is interview-focused with no standardized online assessment , and the average time from application to hire is about 23 days : 1. Apply on the Analysis Group careers portal . Upload your resume, cover letter (include geographic preferences for offices), and unofficial transcr</t>
+          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
         </is>
       </c>
       <c r="H333" s="6" t="inlineStr">
         <is>
-          <t>Yes, for consultant and data science positions. Not available for administrative roles</t>
+          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
         </is>
       </c>
       <c r="I333" s="6" t="inlineStr">
         <is>
-          <t>Applications are reviewed by the posted deadline. If no deadline is listed, review is rolling. Apply now for the strongest position: late Generalist and Account</t>
+          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
         </is>
       </c>
       <c r="J333" s="6" t="inlineStr">
         <is>
-          <t>Summer Analyst ~$1,750 to $2,100/week (~$35/hr annualized on Glassdoor), plus ~$1,500 sign-on bonus. Summer Associate ~$2,400 to $2,800/week</t>
+          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
         </is>
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>Still open for Summer Analyst (2027 start): the Generalist and Accounting deadline of September 30, 2026 has passed, but both postings were live on October 2, 2026 and the firm keeps reviewing on a rolling basis, considering late applicants pending availability. Health Care (HEOR, Epidemiology &amp; Market Access) deadline: October 28, 2026. Summer Associate: expected December 2026 to March 2027</t>
+          <t>Summer 2028 Summer Analyst (IB, Markets): not open yet, expected around December 2026 to February 2027, rolling. Summer 2027, still open on 15 October 2026: Technology Developer (Whippany, NJ), US Consumer Bank Analyst (Wilmington, DE) and Banking Associate for MBA students (New York, Chicago, San Francisco, Houston). The other US summer 2027 tracks (Operations, Compliance, Quantitative Finance As</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -19149,17 +19149,17 @@
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>December 2026 – January 2027</t>
         </is>
       </c>
       <c r="D334" s="6" t="inlineStr">
         <is>
-          <t>Technology; Markets Quantitative Analytics  (2 of 6 tracks)</t>
+          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E334" s="7" t="inlineStr">
         <is>
-          <t>search.jobs.barclays/internships</t>
+          <t>jobs.citi.com/</t>
         </is>
       </c>
       <c r="F334" s="7" t="inlineStr">
@@ -19169,34 +19169,34 @@
       </c>
       <c r="G334" s="6" t="inlineStr">
         <is>
-          <t>Barclays runs a four-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through search.jobs.barclays or the Workday portal with your resume, transcript, and short application questions. Barclays posts separate listings per track, so choose you</t>
+          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
         </is>
       </c>
       <c r="H334" s="6" t="inlineStr">
         <is>
-          <t>No. Barclays explicitly states it will not sponsor applicants for work visas or provide any employment-based immigration sponsorship for internships, post-graduation programs, or permanent employment. This includes no as</t>
+          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
         </is>
       </c>
       <c r="I334" s="6" t="inlineStr">
         <is>
-          <t>Yes. Barclays fills on a first-come basis; competitive desks close within 4–6 weeks of posting</t>
+          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
         </is>
       </c>
       <c r="J334" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (approx. $21,150 pro-rated for 10 weeks)</t>
+          <t>$60,000–$135,000 annualized on the 12 US Summer Analyst 2027 postings live October 24, 2026 (Technology $80,000–$110,000; Corporate Banking Houston $100,000–$13</t>
         </is>
       </c>
       <c r="K334" s="6" t="inlineStr">
         <is>
-          <t>Summer 2028 Summer Analyst (IB, Markets): not open yet, expected around December 2026 to February 2027, rolling. Summer 2027, still open on 15 October 2026: Technology Developer (Whippany, NJ), US Consumer Bank Analyst (Wilmington, DE) and Banking Associate for MBA students (New York, Chicago, San Francisco, Houston). The other US summer 2027 tracks (Operations, Compliance, Quantitative Finance As</t>
+          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 12 US Summer Analyst requisitions live on Citi's Workday board on October 24, 2026: seven Technology reqs posted October 23 (Application Development in Irving, Jacksonville, Tampa and New York/New Jersey; Cyber Security in Irving; Production Support in New York and Tampa), each printing a close date of October 30, 2026 , plus Corporate B</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -19206,17 +19206,17 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – January 2027</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D335" s="6" t="inlineStr">
         <is>
-          <t>Markets – Quantitative Analysis; Technology – Application Development  (2 of 6 tracks)</t>
+          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E335" s="7" t="inlineStr">
         <is>
-          <t>jobs.citi.com/</t>
+          <t>careers.db.com/students-graduates/internship-programme/</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
@@ -19226,34 +19226,34 @@
       </c>
       <c r="G335" s="6" t="inlineStr">
         <is>
-          <t>Citi runs a five-stage funnel. The rolling timeline means each stage can start within days of the previous one: 1. Create an account on jobs.citi.com and apply through the Program Finder. Upload your resume, cover letter, and university transcript. Citi posts separate listings by division and locati</t>
+          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
         </is>
       </c>
       <c r="H335" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Many US postings state that applicants must not require sponsorship for US work authorization. This may exclude some international students from US-based programs. However, Citi operates in 160 or more countries and has </t>
+          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
         </is>
       </c>
       <c r="I335" s="6" t="inlineStr">
         <is>
-          <t>Yes. IB fills 80% of its class by August; all other divisions review on a rolling basis with early applicants seeing higher interview rates</t>
+          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
         </is>
       </c>
       <c r="J335" s="6" t="inlineStr">
         <is>
-          <t>$60,000–$135,000 annualized on the 12 US Summer Analyst 2027 postings live October 24, 2026 (Technology $80,000–$110,000; Corporate Banking Houston $100,000–$13</t>
+          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
         </is>
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 (juniors graduating December 2027 to June 2028): 12 US Summer Analyst requisitions live on Citi's Workday board on October 24, 2026: seven Technology reqs posted October 23 (Application Development in Irving, Jacksonville, Tampa and New York/New Jersey; Cyber Security in Irving; Production Support in New York and Tampa), each printing a close date of October 30, 2026 , plus Corporate B</t>
+          <t>Partly open. Technology, Data and Innovation internship roles for 2027 went live in August 2026. IB (summer 2028) expected from about December 2026, rolling into spring 2027 (the first 2027 Summer Analyst application posted in December 2025, per Adventis Finance). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B336" s="8" t="inlineStr">
@@ -19263,17 +19263,17 @@
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>December 2026</t>
         </is>
       </c>
       <c r="D336" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (TDI); AI &amp; Machine Learning (TDI)  (2 of 6 tracks)</t>
+          <t>ML / Data (SF)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E336" s="7" t="inlineStr">
         <is>
-          <t>careers.db.com/students-graduates/internship-programme/</t>
+          <t>strava.com/careers</t>
         </is>
       </c>
       <c r="F336" s="7" t="inlineStr">
@@ -19283,34 +19283,30 @@
       </c>
       <c r="G336" s="6" t="inlineStr">
         <is>
-          <t>The process has 4 to 6 stages: (1) online application with CV, (2) SJT (situational judgment test, the critical first filter), (3) OPQ personality test, (4) SHL general ability tests (numerical, inductive, deductive), (5) HireVue pre-recorded video interview (3 to 8 questions), and (6) Assessment Ce</t>
-        </is>
-      </c>
-      <c r="H336" s="6" t="inlineStr">
-        <is>
-          <t>It depends on the role. Deutsche Bank works with immigration providers and filed 206 H-1B LCAs in FY2025. Technology and quantitative roles often qualify for STEM OPT extensions (3 years total), making sponsorship more f</t>
-        </is>
-      </c>
+          <t>Strava does not publish a single official interview process, and it varies by track. The steps below combine the application flow from the jobs board with community-reported (paraphrased) round structure, so treat the interview specifics as directional: 1. Find and filter the reqs. Go to the Ashby b</t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr"/>
       <c r="I336" s="6" t="inlineStr">
         <is>
-          <t>Yes. Deutsche Bank fills on a rolling basis and may close roles before the stated deadline</t>
+          <t xml:space="preserve">Partially. Strava posts discipline-specific intern reqs (Web, Server, iOS, Android, ML) on separate timelines, each with its own "Deadline to Apply," and fills </t>
         </is>
       </c>
       <c r="J336" s="6" t="inlineStr">
         <is>
-          <t>$110,000 annualized (~$21,150 pro-rated) plus $3,000 housing stipend</t>
+          <t>$40.00/hour (stated directly on Strava intern JDs), plus a housing stipend to live in SF for the three-month summer (~$2,500/month per Levels.fyi). That works o</t>
         </is>
       </c>
       <c r="K336" s="6" t="inlineStr">
         <is>
-          <t>Partly open. Technology, Data and Innovation internship roles for 2027 went live in August 2026. IB (summer 2028) expected from about December 2026, rolling into spring 2027 (the first 2027 Summer Analyst application posted in December 2025, per Adventis Finance). Rolling review</t>
+          <t>Not yet published (expected). Applications for summer 2027 are expected to open in fall/winter 2026 with deadlines in late winter to spring 2027. Documented prior cycles: Summer 2025 (Web, SF) closed April 14, 2025; Summer 2026 (Server/Data Platform, SF) closed March 7, 2026</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Volkswagen</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -19320,17 +19316,17 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>December 2026</t>
+          <t>December 2026 – March 2027</t>
         </is>
       </c>
       <c r="D337" s="6" t="inlineStr">
         <is>
-          <t>ML / Data (SF)  (1 of 6 tracks)</t>
+          <t>Engineering (Chattanooga); Purchasing/Value Engineering (Chattanooga)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E337" s="7" t="inlineStr">
         <is>
-          <t>strava.com/careers</t>
+          <t>careers.vw.com/go/Interns/8943400/</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
@@ -19340,50 +19336,50 @@
       </c>
       <c r="G337" s="6" t="inlineStr">
         <is>
-          <t>Strava does not publish a single official interview process, and it varies by track. The steps below combine the application flow from the jobs board with community-reported (paraphrased) round structure, so treat the interview specifics as directional: 1. Find and filter the reqs. Go to the Ashby b</t>
+          <t>After applying on careers.vw.com, you will have a phone screening with an HR specialist, followed by a behavioral interview with the hiring manager. VW uses the BAR format: Background, Action, Result. Prepare specific examples of how you have handled challenges, and expect questions about teamwork a</t>
         </is>
       </c>
       <c r="H337" s="6" t="inlineStr"/>
       <c r="I337" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Strava posts discipline-specific intern reqs (Web, Server, iOS, Android, ML) on separate timelines, each with its own "Deadline to Apply," and fills </t>
+          <t>Yes. VWGoA posts intern roles on a rolling basis and fills them as qualified candidates are identified</t>
         </is>
       </c>
       <c r="J337" s="6" t="inlineStr">
         <is>
-          <t>$40.00/hour (stated directly on Strava intern JDs), plus a housing stipend to live in SF for the three-month summer (~$2,500/month per Levels.fyi). That works o</t>
+          <t>$20 to $35/hr depending on role and location; engineering and tech roles trend higher</t>
         </is>
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>Not yet published (expected). Applications for summer 2027 are expected to open in fall/winter 2026 with deadlines in late winter to spring 2027. Documented prior cycles: Summer 2025 (Web, SF) closed April 14, 2025; Summer 2026 (Server/Data Platform, SF) closed March 7, 2026</t>
+          <t>Expected December 2026 to March 2027 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
-        </is>
-      </c>
-      <c r="B338" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="B338" s="9" t="inlineStr">
+        <is>
+          <t>Later this cycle</t>
         </is>
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – March 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D338" s="6" t="inlineStr">
         <is>
-          <t>Engineering (Chattanooga); Purchasing/Value Engineering (Chattanooga)  (2 of 6 tracks)</t>
+          <t>Digital Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E338" s="7" t="inlineStr">
         <is>
-          <t>careers.vw.com/go/Interns/8943400/</t>
+          <t>careers.adidas-group.com/teams/students/internships-students</t>
         </is>
       </c>
       <c r="F338" s="7" t="inlineStr">
@@ -19393,30 +19389,30 @@
       </c>
       <c r="G338" s="6" t="inlineStr">
         <is>
-          <t>After applying on careers.vw.com, you will have a phone screening with an HR specialist, followed by a behavioral interview with the hiring manager. VW uses the BAR format: Background, Action, Result. Prepare specific examples of how you have handled challenges, and expect questions about teamwork a</t>
+          <t>Adidas runs a multi-stage funnel that stretches from early January through March, roughly 8–10 weeks from application to offer: 1. Apply at careers.adidas-group.com during the one-week window (~January 1–8). Submit your resume plus the creative "1-Pager": a single-page PDF responding to a brand prom</t>
         </is>
       </c>
       <c r="H338" s="6" t="inlineStr"/>
       <c r="I338" s="6" t="inlineStr">
         <is>
-          <t>Yes. VWGoA posts intern roles on a rolling basis and fills them as qualified candidates are identified</t>
+          <t>No. Fixed one-week cohort window. Roles can close early within the window once sufficient candidates apply</t>
         </is>
       </c>
       <c r="J338" s="6" t="inlineStr">
         <is>
-          <t>$20 to $35/hr depending on role and location; engineering and tech roles trend higher</t>
+          <t>$25–$45/hr (Glassdoor); ~$26/hr average (Indeed); some roles include a housing stipend</t>
         </is>
       </c>
       <c r="K338" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to March 2027 for summer 2027 (documented pattern; not yet posted)</t>
+          <t>Expected January 1–8, 2027 for summer 2027 (one-week fixed window; projected from 2026 cycle)</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19426,17 +19422,17 @@
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D339" s="6" t="inlineStr">
         <is>
-          <t>Digital Analytics  (1 of 6 tracks)</t>
+          <t>Software Engineering Intern (Ad Serving Platform); Data Scientist Intern; Mobile Software Engineering Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E339" s="7" t="inlineStr">
         <is>
-          <t>careers.adidas-group.com/teams/students/internships-students</t>
+          <t>applovin.com/en/careers</t>
         </is>
       </c>
       <c r="F339" s="7" t="inlineStr">
@@ -19446,30 +19442,34 @@
       </c>
       <c r="G339" s="6" t="inlineStr">
         <is>
-          <t>Adidas runs a multi-stage funnel that stretches from early January through March, roughly 8–10 weeks from application to offer: 1. Apply at careers.adidas-group.com during the one-week window (~January 1–8). Submit your resume plus the creative "1-Pager": a single-page PDF responding to a brand prom</t>
-        </is>
-      </c>
-      <c r="H339" s="6" t="inlineStr"/>
+          <t>A recruiter phone screen (15 to 30 minutes), a technical phone screen with LeetCode easy/medium problems (45 minutes), then a virtual onsite with two coding rounds, a Director interview, and a CTO interview. The process averages about 23 days. Glassdoor rates the SWE intern interview difficulty at 2</t>
+        </is>
+      </c>
+      <c r="H339" s="6" t="inlineStr">
+        <is>
+          <t>H-1B sponsored for full-time roles. F-1 students can participate via CPT. Job postings do not restrict to US citizens or permanent residents</t>
+        </is>
+      </c>
       <c r="I339" s="6" t="inlineStr">
         <is>
-          <t>No. Fixed one-week cohort window. Roles can close early within the window once sufficient candidates apply</t>
+          <t>Yes, likely rolling. AppLovin does not publish fixed deadlines. The Summer 2025 SWE intern posting appeared in February 2025 and closed once filled. Apply early</t>
         </is>
       </c>
       <c r="J339" s="6" t="inlineStr">
         <is>
-          <t>$25–$45/hr (Glassdoor); ~$26/hr average (Indeed); some roles include a housing stipend</t>
+          <t>$60 to $80 per hour ($10,400 to $13,867/month) depending on role and cycle. Levels.fyi reports $60/hr for Summer 2024; the 2025 JD listed $70/hr base for CA/NY/</t>
         </is>
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>Expected January 1–8, 2027 for summer 2027 (one-week fixed window; projected from 2026 cycle)</t>
+          <t>Expected late January to February 2027 for summer 2027 roles. Rolling review until positions are filled, typically by March or April 2027. Projected from the 2025 cycle</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19484,12 +19484,12 @@
       </c>
       <c r="D340" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Ad Serving Platform); Data Scientist Intern; Mobile Software Engineering Intern  (3 of 5 tracks)</t>
+          <t>BCG X Data Science  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E340" s="7" t="inlineStr">
         <is>
-          <t>applovin.com/en/careers</t>
+          <t>careers.bcg.com/global/en/internship-opportunities</t>
         </is>
       </c>
       <c r="F340" s="7" t="inlineStr">
@@ -19499,34 +19499,34 @@
       </c>
       <c r="G340" s="6" t="inlineStr">
         <is>
-          <t>A recruiter phone screen (15 to 30 minutes), a technical phone screen with LeetCode easy/medium problems (45 minutes), then a virtual onsite with two coding rounds, a Director interview, and a CTO interview. The process averages about 23 days. Glassdoor rates the SWE intern interview difficulty at 2</t>
+          <t>BCG's interview funnel has five stages, with the Casey chatbot as the unique gatekeeping step. The total process from application to offer averages 4 to 8 weeks (about 32 days per Glassdoor): 1. Apply at careers.bcg.com with a one-page resume, tailored cover letter, academic information (GPA, test s</t>
         </is>
       </c>
       <c r="H340" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsored for full-time roles. F-1 students can participate via CPT. Job postings do not restrict to US citizens or permanent residents</t>
+          <t>Yes. BCG sponsors H-1B visas for full-time hires and is experienced with the sponsorship process. Summer interns typically work on CPT (Curricular Practical Training) authorization, with OPT and STEM-OPT extensions for f</t>
         </is>
       </c>
       <c r="I340" s="6" t="inlineStr">
         <is>
-          <t>Yes, likely rolling. AppLovin does not publish fixed deadlines. The Summer 2025 SWE intern posting appeared in February 2025 and closed once filled. Apply early</t>
+          <t>No. BCG uses fixed deadline windows, but applying to the earlier deadline is strongly recommended because more interview spots remain open</t>
         </is>
       </c>
       <c r="J340" s="6" t="inlineStr">
         <is>
-          <t>$60 to $80 per hour ($10,400 to $13,867/month) depending on role and cycle. Levels.fyi reports $60/hr for Summer 2024; the 2025 JD listed $70/hr base for CA/NY/</t>
+          <t>~$2,000–$2,500/week for undergraduate Summer Associate interns (~$20,000–$30,000 total summer)</t>
         </is>
       </c>
       <c r="K340" s="6" t="inlineStr">
         <is>
-          <t>Expected late January to February 2027 for summer 2027 roles. Rolling review until positions are filled, typically by March or April 2027. Projected from the 2025 cycle</t>
+          <t>Expected portal open January–February 2027 and primary deadline around April 2027; final deadline August–September 2027 for summer 2028 (pattern-based projection; confirm on the official careers portal)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19536,17 +19536,17 @@
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D341" s="6" t="inlineStr">
         <is>
-          <t>BCG X Data Science  (1 of 6 tracks)</t>
+          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E341" s="7" t="inlineStr">
         <is>
-          <t>careers.bcg.com/global/en/internship-opportunities</t>
+          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
@@ -19556,34 +19556,30 @@
       </c>
       <c r="G341" s="6" t="inlineStr">
         <is>
-          <t>BCG's interview funnel has five stages, with the Casey chatbot as the unique gatekeeping step. The total process from application to offer averages 4 to 8 weeks (about 32 days per Glassdoor): 1. Apply at careers.bcg.com with a one-page resume, tailored cover letter, academic information (GPA, test s</t>
-        </is>
-      </c>
-      <c r="H341" s="6" t="inlineStr">
-        <is>
-          <t>Yes. BCG sponsors H-1B visas for full-time hires and is experienced with the sponsorship process. Summer interns typically work on CPT (Curricular Practical Training) authorization, with OPT and STEM-OPT extensions for f</t>
-        </is>
-      </c>
+          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
+        </is>
+      </c>
+      <c r="H341" s="6" t="inlineStr"/>
       <c r="I341" s="6" t="inlineStr">
         <is>
-          <t>No. BCG uses fixed deadline windows, but applying to the earlier deadline is strongly recommended because more interview spots remain open</t>
+          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
         </is>
       </c>
       <c r="J341" s="6" t="inlineStr">
         <is>
-          <t>~$2,000–$2,500/week for undergraduate Summer Associate interns (~$20,000–$30,000 total summer)</t>
+          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
         </is>
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>Expected portal open January–February 2027 and primary deadline around April 2027; final deadline August–September 2027 for summer 2028 (pattern-based projection; confirm on the official careers portal)</t>
+          <t>Not posted yet for summer 2028 (checked October 17, 2026). Projected from mid-December 2026 for Global Banking and Global Markets, because the first 2027 Summer Analyst postings went up December 15 and 16, 2025; Corporate Functions roles followed from February to May 2026. Sophomores: the Open Sophomore Opportunity Summit (January 13 and 14, 2027) is taking applications now</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Cerebras</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19598,12 +19594,12 @@
       </c>
       <c r="D342" s="6" t="inlineStr">
         <is>
-          <t>Corporate Functions, Technology  (1 of 6 tracks)</t>
+          <t>Kernel Engineering Intern; Applied ML / ML Framework Intern; AI Cloud / Inference Service Intern; Hardware Engineering / CoDesign Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E342" s="7" t="inlineStr">
         <is>
-          <t>usa.bnpparibas/en/homepage/join-us/our-opportunities/student</t>
+          <t>cerebras.ai/internships</t>
         </is>
       </c>
       <c r="F342" s="7" t="inlineStr">
@@ -19613,30 +19609,34 @@
       </c>
       <c r="G342" s="6" t="inlineStr">
         <is>
-          <t>BNP Paribas's funnel is longer than most banks', running about seven to eight weeks from application to offer decision: 1. Apply at group.bnpparibas/en/careers or via Handshake with a resume and application form. BNP limits applicants to one graduate scheme or spring week programme plus up to four l</t>
-        </is>
-      </c>
-      <c r="H342" s="6" t="inlineStr"/>
+          <t>Expect one to three rounds of 30 to 60 minutes each: a screening call with the hiring manager, a technical coding round with LeetCode-medium problems, and sometimes a domain-specific deep-technical round. The entire process typically completes in two to four weeks from posting to offer.</t>
+        </is>
+      </c>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>International students typically need CPT or OPT authorization. Cerebras sponsors H-1B for full-time roles (132 applications filed, $177K avg salary). Canadian interns in Toronto do not need a US visa</t>
+        </is>
+      </c>
       <c r="I342" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; first-30-day applicants show significantly higher progression rates</t>
+          <t>Yes. Cerebras uses rolling admissions and the process takes two to four weeks from posting to offer. Apply early in the January window</t>
         </is>
       </c>
       <c r="J342" s="6" t="inlineStr">
         <is>
-          <t>$110,000/yr annualized (Global Banking, Global Markets); $95,000 (Technology); $75,000 (Risk, Financial Security)</t>
+          <t>Toronto: $30 to $36/hr CAD (Levels.fyi verified). US (Sunnyvale): estimated $45 to $55/hr USD (extrapolated; no verified US intern data). Daily catered lunch in</t>
         </is>
       </c>
       <c r="K342" s="6" t="inlineStr">
         <is>
-          <t>Not posted yet for summer 2028 (checked October 17, 2026). Projected from mid-December 2026 for Global Banking and Global Markets, because the first 2027 Summer Analyst postings went up December 15 and 16, 2025; Corporate Functions roles followed from February to May 2026. Sophomores: the Open Sophomore Opportunity Summit (January 13 and 14, 2027) is taking applications now</t>
+          <t>Summer 2027: expected January 2027 opening, rolling deadline through February–March 2027. Projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>Cerebras</t>
+          <t>Edelman</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19646,17 +19646,17 @@
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D343" s="6" t="inlineStr">
         <is>
-          <t>Kernel Engineering Intern; Applied ML / ML Framework Intern; AI Cloud / Inference Service Intern; Hardware Engineering / CoDesign Intern  (4 of 5 tracks)</t>
+          <t>Digital; Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E343" s="7" t="inlineStr">
         <is>
-          <t>cerebras.ai/internships</t>
+          <t>edelman.com/careers</t>
         </is>
       </c>
       <c r="F343" s="7" t="inlineStr">
@@ -19666,34 +19666,30 @@
       </c>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>Expect one to three rounds of 30 to 60 minutes each: a screening call with the hiring manager, a technical coding round with LeetCode-medium problems, and sometimes a domain-specific deep-technical round. The entire process typically completes in two to four weeks from posting to offer.</t>
-        </is>
-      </c>
-      <c r="H343" s="6" t="inlineStr">
-        <is>
-          <t>International students typically need CPT or OPT authorization. Cerebras sponsors H-1B for full-time roles (132 applications filed, $177K avg salary). Canadian interns in Toronto do not need a US visa</t>
-        </is>
-      </c>
+          <t>After applying through Workday, expect a phone or video screen with a recruiter, followed by one-on-one or panel interviews with team members. About 18% of candidates report a skills or writing test. Prepare to discuss why you want to work in PR, your writing experience, current events knowledge, an</t>
+        </is>
+      </c>
+      <c r="H343" s="6" t="inlineStr"/>
       <c r="I343" s="6" t="inlineStr">
         <is>
-          <t>Yes. Cerebras uses rolling admissions and the process takes two to four weeks from posting to offer. Apply early in the January window</t>
+          <t>Yes. Talent Acquisition reviews applications "on a rolling basis," but a firm deadline still applies (March 20 in the 2026 cycle)</t>
         </is>
       </c>
       <c r="J343" s="6" t="inlineStr">
         <is>
-          <t>Toronto: $30 to $36/hr CAD (Levels.fyi verified). US (Sunnyvale): estimated $45 to $55/hr USD (extrapolated; no verified US intern data). Daily catered lunch in</t>
+          <t>$22/hr in the 2026 cycle (up from $20/hr in 2024); no housing reimbursement</t>
         </is>
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027: expected January 2027 opening, rolling deadline through February–March 2027. Projected from prior cycles</t>
+          <t>Expected late January/early February to mid-March 2027 for summer 2027 (documented Feb-March pattern across 2024 and 2026 cycles; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>Edelman</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19703,17 +19699,17 @@
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>January–June 2027</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
         <is>
-          <t>Digital; Technology  (2 of 6 tracks)</t>
+          <t>Technology / Software Engineering Intern; Cybersecurity Intern; Global Operations &amp; Analytics (SMB) Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E344" s="7" t="inlineStr">
         <is>
-          <t>edelman.com/careers</t>
+          <t>jobs.globalpayments.com/early-careers</t>
         </is>
       </c>
       <c r="F344" s="7" t="inlineStr">
@@ -19723,30 +19719,34 @@
       </c>
       <c r="G344" s="6" t="inlineStr">
         <is>
-          <t>After applying through Workday, expect a phone or video screen with a recruiter, followed by one-on-one or panel interviews with team members. About 18% of candidates report a skills or writing test. Prepare to discuss why you want to work in PR, your writing experience, current events knowledge, an</t>
-        </is>
-      </c>
-      <c r="H344" s="6" t="inlineStr"/>
+          <t xml:space="preserve">Global Payments' interview process is straightforward and moves quickly, with Indeed reporting that over half of candidates complete it within two weeks: 1. Find openings and apply on jobs.globalpayments.com . Set job alerts on LinkedIn and the Global Payments careers portal beginning in late 2026. </t>
+        </is>
+      </c>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>No official intern-specific visa policy confirmed. Global Payments has an established H-1B sponsorship track record for full-time roles. International students on CPT/OPT should confirm directly with recruiters</t>
+        </is>
+      </c>
       <c r="I344" s="6" t="inlineStr">
         <is>
-          <t>Yes. Talent Acquisition reviews applications "on a rolling basis," but a firm deadline still applies (March 20 in the 2026 cycle)</t>
+          <t>Not explicitly stated. Past postings on Reddit were marked CLOSED relatively quickly, suggesting fixed windows with limited spots rather than true rolling admis</t>
         </is>
       </c>
       <c r="J344" s="6" t="inlineStr">
         <is>
-          <t>$22/hr in the 2026 cycle (up from $20/hr in 2024); no housing reimbursement</t>
+          <t>$22 to $28/hr ($3,800 to $4,900/month) depending on role and location. Levels.fyi reports $22.00/hr for an Atlanta SWE intern (Summer 2023). Indeed estimates an</t>
         </is>
       </c>
       <c r="K344" s="6" t="inlineStr">
         <is>
-          <t>Expected late January/early February to mid-March 2027 for summer 2027 (documented Feb-March pattern across 2024 and 2026 cycles; not yet posted)</t>
+          <t>Postings historically appear January to April for the same summer. The Summer 2027 early careers page directed candidates to check back as of July 2026. Begin monitoring in late 2026 or early 2027</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19756,17 +19756,17 @@
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>January–June 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D345" s="6" t="inlineStr">
         <is>
-          <t>Technology / Software Engineering Intern; Cybersecurity Intern; Global Operations &amp; Analytics (SMB) Intern  (3 of 5 tracks)</t>
+          <t>Digital &amp; Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E345" s="7" t="inlineStr">
         <is>
-          <t>jobs.globalpayments.com/early-careers</t>
+          <t>us.gsk.com/en-us/careers/early-careers/internships-and-co-op</t>
         </is>
       </c>
       <c r="F345" s="7" t="inlineStr">
@@ -19776,34 +19776,34 @@
       </c>
       <c r="G345" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global Payments' interview process is straightforward and moves quickly, with Indeed reporting that over half of candidates complete it within two weeks: 1. Find openings and apply on jobs.globalpayments.com . Set job alerts on LinkedIn and the Global Payments careers portal beginning in late 2026. </t>
+          <t>GSK uses a four-stage process: online application, a "World of GSK" digital assessment (situational judgement plus cognitive test, about 45 to 60 minutes), a HireVue job simulation with video and written responses, and a final Assessment Centre with group exercises, a case study presentation, and be</t>
         </is>
       </c>
       <c r="H345" s="6" t="inlineStr">
         <is>
-          <t>No official intern-specific visa policy confirmed. Global Payments has an established H-1B sponsorship track record for full-time roles. International students on CPT/OPT should confirm directly with recruiters</t>
+          <t>GSK US typically doesn't provide visa sponsorship for internships or the Future Leaders Program. However, policies can vary by role and location, so check individual job descriptions. International candidates should conf</t>
         </is>
       </c>
       <c r="I345" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated. Past postings on Reddit were marked CLOSED relatively quickly, suggesting fixed windows with limited spots rather than true rolling admis</t>
+          <t>Yes. GSK reviews on a rolling basis and recommends applying early; adverts "may close at any time"</t>
         </is>
       </c>
       <c r="J345" s="6" t="inlineStr">
         <is>
-          <t>$22 to $28/hr ($3,800 to $4,900/month) depending on role and location. Levels.fyi reports $22.00/hr for an Atlanta SWE intern (Summer 2023). Indeed estimates an</t>
+          <t>$24.70/hr average (Glassdoor, 22% above national average); range $14–$41+/hr by role and location</t>
         </is>
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>Postings historically appear January to April for the same summer. The Summer 2027 early careers page directed candidates to check back as of July 2026. Begin monitoring in late 2026 or early 2027</t>
+          <t>US postings expected January to March 2027; rolling review, adverts may close at any time (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19818,12 +19818,12 @@
       </c>
       <c r="D346" s="6" t="inlineStr">
         <is>
-          <t>Digital &amp; Technology  (1 of 6 tracks)</t>
+          <t>Software Engineer Program Internship; Data Science Analyst Summer  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E346" s="7" t="inlineStr">
         <is>
-          <t>us.gsk.com/en-us/careers/early-careers/internships-and-co-op</t>
+          <t>careers.jpmorgan.com/us/en/students/programs</t>
         </is>
       </c>
       <c r="F346" s="7" t="inlineStr">
@@ -19833,34 +19833,30 @@
       </c>
       <c r="G346" s="6" t="inlineStr">
         <is>
-          <t>GSK uses a four-stage process: online application, a "World of GSK" digital assessment (situational judgement plus cognitive test, about 45 to 60 minutes), a HireVue job simulation with video and written responses, and a final Assessment Centre with group exercises, a case study presentation, and be</t>
-        </is>
-      </c>
-      <c r="H346" s="6" t="inlineStr">
-        <is>
-          <t>GSK US typically doesn't provide visa sponsorship for internships or the Future Leaders Program. However, policies can vary by role and location, so check individual job descriptions. International candidates should conf</t>
-        </is>
-      </c>
+          <t>The process runs three stages for nearly every US summer program: 1. Online application. Resume plus program and location choice. JPMorgan's FAQ recommends you focus "on no more than three summer internship program applications." So pick deliberately instead of carpet-bombing every track. 2. HireVue</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr"/>
       <c r="I346" s="6" t="inlineStr">
         <is>
-          <t>Yes. GSK reviews on a rolling basis and recommends applying early; adverts "may close at any time"</t>
+          <t>Yes. Official FAQ: applications reviewed "on a rolling basis"</t>
         </is>
       </c>
       <c r="J346" s="6" t="inlineStr">
         <is>
-          <t>$24.70/hr average (Glassdoor, 22% above national average); range $14–$41+/hr by role and location</t>
+          <t>IB &amp; Markets: pro-rated $110,000/yr base; software engineering ~$60/hr (Levels.fyi)</t>
         </is>
       </c>
       <c r="K346" s="6" t="inlineStr">
         <is>
-          <t>US postings expected January to March 2027; rolling review, adverts may close at any time (documented pattern; not yet posted)</t>
+          <t>For summer 2028 internships: IB applications expected to open Jan–Mar 2027, most other programs spring 2027 (projected from last cycle; JPMorgan hasn't published official 2028 dates yet)</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19870,17 +19866,17 @@
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D347" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Program Internship; Data Science Analyst Summer  (2 of 6 tracks)</t>
+          <t>Technology Summer Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E347" s="7" t="inlineStr">
         <is>
-          <t>careers.jpmorgan.com/us/en/students/programs</t>
+          <t>kkr.com/careers/student-careers</t>
         </is>
       </c>
       <c r="F347" s="7" t="inlineStr">
@@ -19890,30 +19886,34 @@
       </c>
       <c r="G347" s="6" t="inlineStr">
         <is>
-          <t>The process runs three stages for nearly every US summer program: 1. Online application. Resume plus program and location choice. JPMorgan's FAQ recommends you focus "on no more than three summer internship program applications." So pick deliberately instead of carpet-bombing every track. 2. HireVue</t>
-        </is>
-      </c>
-      <c r="H347" s="6" t="inlineStr"/>
+          <t>KKR's funnel is rigorous and multi-stage, designed to filter 7,000 applicants down to roughly 50 offers. The full process spans about 35 days on average : 1. Apply on kkr.com/careers/student-careers . The portal opens in early January and closes within about seven weeks. Apply within the first 48 ho</t>
+        </is>
+      </c>
+      <c r="H347" s="6" t="inlineStr">
+        <is>
+          <t>CPT sponsorship for international summer interns; H-1B sponsorship selective</t>
+        </is>
+      </c>
       <c r="I347" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official FAQ: applications reviewed "on a rolling basis"</t>
+          <t>Yes. Applications are reviewed on a rolling basis; applying within the first 48 hours is strongly advised</t>
         </is>
       </c>
       <c r="J347" s="6" t="inlineStr">
         <is>
-          <t>IB &amp; Markets: pro-rated $110,000/yr base; software engineering ~$60/hr (Levels.fyi)</t>
+          <t>$100,000 to $110,000 annualized base (~$19,200 to $21,200 prorated for 10 weeks), plus housing/relocation stipend and discretionary bonus</t>
         </is>
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>For summer 2028 internships: IB applications expected to open Jan–Mar 2027, most other programs spring 2027 (projected from last cycle; JPMorgan hasn't published official 2028 dates yet)</t>
+          <t>Expected January to February 2027 for Summer 2028 Analyst. Projected from the 2027 cycle (Jan 2 to ~Feb 21, 2026); not yet posted</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>Miro</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19923,17 +19923,17 @@
       </c>
       <c r="C348" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January–August 2027</t>
         </is>
       </c>
       <c r="D348" s="6" t="inlineStr">
         <is>
-          <t>Technology Summer Intern  (1 of 6 tracks)</t>
+          <t>Graduate Software Engineer (primary); Data &amp; Machine Learning exposure (adjacent)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E348" s="7" t="inlineStr">
         <is>
-          <t>kkr.com/careers/student-careers</t>
+          <t>miro.com/careers/open-positions/</t>
         </is>
       </c>
       <c r="F348" s="7" t="inlineStr">
@@ -19943,34 +19943,34 @@
       </c>
       <c r="G348" s="6" t="inlineStr">
         <is>
-          <t>KKR's funnel is rigorous and multi-stage, designed to filter 7,000 applicants down to roughly 50 offers. The full process spans about 35 days on average : 1. Apply on kkr.com/careers/student-careers . The portal opens in early January and closes within about seven weeks. Apply within the first 48 ho</t>
+          <t>Five stages: a 30-minute recruiter screen, a 90-to-120-minute hiring-manager interview against the "Miro Mindset," a Skill Assessment case or presentation, a cross-functional "Meet the Team" panel, and a leadership round. A decision usually follows within two weeks. There is no documented LeetCode-s</t>
         </is>
       </c>
       <c r="H348" s="6" t="inlineStr">
         <is>
-          <t>CPT sponsorship for international summer interns; H-1B sponsorship selective</t>
+          <t>No US intern visa pathway is described. The graduate roles are EU-based and require the right to work in Amsterdam or Berlin, with no relocation assistance in the latest job description. US applicants would need EU right</t>
         </is>
       </c>
       <c r="I348" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed on a rolling basis; applying within the first 48 hours is strongly advised</t>
+          <t>No. The Graduate program opens on a fixed annual cadence (postings each January, a single August cohort start). APM recruits in an annual Fall/Winter window. On</t>
         </is>
       </c>
       <c r="J348" s="6" t="inlineStr">
         <is>
-          <t>$100,000 to $110,000 annualized base (~$19,200 to $21,200 prorated for 10 weeks), plus housing/relocation stipend and discretionary bonus</t>
+          <t>Not published for the graduate program. For market context only (community/aggregator, not official): Netherlands Miro SWE comp runs roughly €93K–€159K per Leve</t>
         </is>
       </c>
       <c r="K348" s="6" t="inlineStr">
         <is>
-          <t>Expected January to February 2027 for Summer 2028 Analyst. Projected from the 2027 cycle (Jan 2 to ~Feb 21, 2026); not yet posted</t>
+          <t>Graduate Software Engineer postings expected to open ~January 2027 for an August 2027 cohort (repeating January-open / August-start pattern; labeled expected, not yet published). APM recruits each Fall/Winter.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>Miro</t>
+          <t>Mistral AI</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19980,17 +19980,17 @@
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
-          <t>January–August 2027</t>
+          <t>January–April 2027</t>
         </is>
       </c>
       <c r="D349" s="6" t="inlineStr">
         <is>
-          <t>Graduate Software Engineer (primary); Data &amp; Machine Learning exposure (adjacent)  (2 of 4 tracks)</t>
+          <t>Applied Scientist / Research Engineer Intern; Software Engineer Intern; Applied AI / Forward-Deployed ML Engineer Intern; AI Data Solutions Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E349" s="7" t="inlineStr">
         <is>
-          <t>miro.com/careers/open-positions/</t>
+          <t>mistral.ai/careers/</t>
         </is>
       </c>
       <c r="F349" s="7" t="inlineStr">
@@ -20000,34 +20000,34 @@
       </c>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>Five stages: a 30-minute recruiter screen, a 90-to-120-minute hiring-manager interview against the "Miro Mindset," a Skill Assessment case or presentation, a cross-functional "Meet the Team" panel, and a leadership round. A decision usually follows within two weeks. There is no documented LeetCode-s</t>
+          <t>Expect 3 to 5 rounds over 2 to 4 weeks: a recruiter screen, a 60-minute live technical coding assessment, an ML/LLM deep-dive conversation covering transformers and MoE architecture, a system-design or pair-programming round, and a behavioral/values round on open-weights philosophy and EU AI Act awa</t>
         </is>
       </c>
       <c r="H349" s="6" t="inlineStr">
         <is>
-          <t>No US intern visa pathway is described. The graduate roles are EU-based and require the right to work in Amsterdam or Berlin, with no relocation assistance in the latest job description. US applicants would need EU right</t>
+          <t>Yes. Financial assistance for moving expenses, visa sponsorship, and settling-in services confirmed on careers page. 20 H-1B cases filed with 100% approval rate for US roles</t>
         </is>
       </c>
       <c r="I349" s="6" t="inlineStr">
         <is>
-          <t>No. The Graduate program opens on a fixed annual cadence (postings each January, a single August cohort start). APM recruits in an annual Fall/Winter window. On</t>
+          <t>Yes. Mistral posts internships as individual requisitions throughout the year. There is no centralized application deadline or cohort start date</t>
         </is>
       </c>
       <c r="J349" s="6" t="inlineStr">
         <is>
-          <t>Not published for the graduate program. For market context only (community/aggregator, not official): Netherlands Miro SWE comp runs roughly €93K–€159K per Leve</t>
+          <t>Paris: EUR 1,200 to 2,500/month (third-party estimates). US (Palo Alto): $8,000 to $11,000/month. Mistral does not publish salary ranges officially</t>
         </is>
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>Graduate Software Engineer postings expected to open ~January 2027 for an August 2027 cohort (repeating January-open / August-start pattern; labeled expected, not yet published). APM recruits each Fall/Winter.</t>
+          <t>Expected January to April 2027 for summer 2027 start. Roles posted on a rolling basis year-round; no single cohort deadline</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>Mistral AI</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20037,17 +20037,17 @@
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
-          <t>January–April 2027</t>
+          <t>January–February 2027</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
         <is>
-          <t>Applied Scientist / Research Engineer Intern; Software Engineer Intern; Applied AI / Forward-Deployed ML Engineer Intern; AI Data Solutions Intern  (4 of 6 tracks)</t>
+          <t>Technology SA; Quantitative Finance SA  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E350" s="7" t="inlineStr">
         <is>
-          <t>mistral.ai/careers/</t>
+          <t>morganstanley.com/people-opportunities/students-graduates</t>
         </is>
       </c>
       <c r="F350" s="7" t="inlineStr">
@@ -20057,34 +20057,30 @@
       </c>
       <c r="G350" s="6" t="inlineStr">
         <is>
-          <t>Expect 3 to 5 rounds over 2 to 4 weeks: a recruiter screen, a 60-minute live technical coding assessment, an ML/LLM deep-dive conversation covering transformers and MoE architecture, a system-design or pair-programming round, and a behavioral/values round on open-weights philosophy and EU AI Act awa</t>
-        </is>
-      </c>
-      <c r="H350" s="6" t="inlineStr">
-        <is>
-          <t>Yes. Financial assistance for moving expenses, visa sponsorship, and settling-in services confirmed on careers page. 20 H-1B cases filed with 100% approval rate for US roles</t>
-        </is>
-      </c>
+          <t>The funnel is consistent across divisions, with one quant-track branch: 1. Apply at the Campus portal (reached via morganstanley.com's students &amp; graduates page ). IB asks you to rank up to three IBD groups and three office locations; the Americas cap is 9 applications per year (3 intern). 2. HireVu</t>
+        </is>
+      </c>
+      <c r="H350" s="6" t="inlineStr"/>
       <c r="I350" s="6" t="inlineStr">
         <is>
-          <t>Yes. Mistral posts internships as individual requisitions throughout the year. There is no centralized application deadline or cohort start date</t>
+          <t>Yes — official posting language; apply the first week the window opens</t>
         </is>
       </c>
       <c r="J350" s="6" t="inlineStr">
         <is>
-          <t>Paris: EUR 1,200 to 2,500/month (third-party estimates). US (Palo Alto): $8,000 to $11,000/month. Mistral does not publish salary ranges officially</t>
+          <t>$52.89/hr IB &amp; WM (official 2027 postings); Technology $70K–$110K annualized; Parametric 2027 internships $28.50 to $33.50/hr (postings live October 21, 2026)</t>
         </is>
       </c>
       <c r="K350" s="6" t="inlineStr">
         <is>
-          <t>Expected January to April 2027 for summer 2027 start. Roles posted on a rolling basis year-round; no single cohort deadline</t>
+          <t>For summer 2028: IB expected ~Jan 1 – mid-Feb 2027; WM ~Mar 2027; firm divisions Feb–May 2027; Technology &amp; Operations spring–fall 2027 (projected from the documented 2027 cycle; not yet official)</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20094,17 +20090,17 @@
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
-          <t>January–February 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D351" s="6" t="inlineStr">
         <is>
-          <t>Technology SA; Quantitative Finance SA  (2 of 6 tracks)</t>
+          <t>Technology  (1 of 5 tracks)</t>
         </is>
       </c>
       <c r="E351" s="7" t="inlineStr">
         <is>
-          <t>morganstanley.com/people-opportunities/students-graduates</t>
+          <t>nomuracampus.tal.net/vx/lang-en-GB/mobile-0/appcentre-ext/br</t>
         </is>
       </c>
       <c r="F351" s="7" t="inlineStr">
@@ -20114,30 +20110,30 @@
       </c>
       <c r="G351" s="6" t="inlineStr">
         <is>
-          <t>The funnel is consistent across divisions, with one quant-track branch: 1. Apply at the Campus portal (reached via morganstanley.com's students &amp; graduates page ). IB asks you to rank up to three IBD groups and three office locations; the Americas cap is 9 applications per year (3 intern). 2. HireVu</t>
+          <t>In the Americas, there is no HireVue. After a phone interview with a junior banker, finalists attend a Superday with 3 to 4 back-to-back interviews with an associate, VP, and ED or MD. Questions mix behavioral (STAR, “Why Nomura?”) with technical (DCF, financial statements, deal discussions). Global</t>
         </is>
       </c>
       <c r="H351" s="6" t="inlineStr"/>
       <c r="I351" s="6" t="inlineStr">
         <is>
-          <t>Yes — official posting language; apply the first week the window opens</t>
+          <t>Yes. Nomura “screens, interviews, and makes offers while the program is still accepting applications”</t>
         </is>
       </c>
       <c r="J351" s="6" t="inlineStr">
         <is>
-          <t>$52.89/hr IB &amp; WM (official 2027 postings); Technology $70K–$110K annualized; Parametric 2027 internships $28.50 to $33.50/hr (postings live October 21, 2026)</t>
+          <t>Global Markets SA: $110,000/yr pro-rated (official JD); SWE interns ~$50/hr in NYC (Levels.fyi)</t>
         </is>
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>For summer 2028: IB expected ~Jan 1 – mid-Feb 2027; WM ~Mar 2027; firm divisions Feb–May 2027; Technology &amp; Operations spring–fall 2027 (projected from the documented 2027 cycle; not yet official)</t>
+          <t>Partly open. 2027 Risk Management and Quantitative Risk Management Summer Analyst roles are live as of August 2026. IB and Global Markets still expected ~January to late March 2027; Technology ~July 2027. Rolling review</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20152,12 +20148,12 @@
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 5 tracks)</t>
+          <t>Software Engineering; Data Engineering; Product Data Science; Applied ML Engineering; Infrastructure Engineering; Security Engineering</t>
         </is>
       </c>
       <c r="E352" s="7" t="inlineStr">
         <is>
-          <t>nomuracampus.tal.net/vx/lang-en-GB/mobile-0/appcentre-ext/br</t>
+          <t>shopify.com/careers</t>
         </is>
       </c>
       <c r="F352" s="7" t="inlineStr">
@@ -20167,30 +20163,34 @@
       </c>
       <c r="G352" s="6" t="inlineStr">
         <is>
-          <t>In the Americas, there is no HireVue. After a phone interview with a junior banker, finalists attend a Superday with 3 to 4 back-to-back interviews with an associate, VP, and ED or MD. Questions mix behavioral (STAR, “Why Nomura?”) with technical (DCF, financial statements, deal discussions). Global</t>
-        </is>
-      </c>
-      <c r="H352" s="6" t="inlineStr"/>
+          <t>Shopify’s funnel is faster than most big tech and distinctly different from the standard LeetCode gauntlet, averaging 3–5 weeks from application to decision: 1. Apply at shopify.com/careers with a resume, application questions, your LinkedIn, and a personal website or GitHub link. Shopify’s postings</t>
+        </is>
+      </c>
+      <c r="H352" s="6" t="inlineStr">
+        <is>
+          <t>No. Every internship posting states you must be legally entitled to work in the hiring country for the full duration. Shopify doesn't provide immigration sponsorship for intern candidates. However, candidates on existing</t>
+        </is>
+      </c>
       <c r="I352" s="6" t="inlineStr">
         <is>
-          <t>Yes. Nomura “screens, interviews, and makes offers while the program is still accepting applications”</t>
+          <t>Yes. Applications reviewed on a rolling basis, and postings warn they "may close before the stated closing date". The two US summer 2027 postings listed on Octo</t>
         </is>
       </c>
       <c r="J352" s="6" t="inlineStr">
         <is>
-          <t>Global Markets SA: $110,000/yr pro-rated (official JD); SWE interns ~$50/hr in NYC (Levels.fyi)</t>
+          <t>$85,000–$93,700/year base pay range for US locations (US Software Engineering Internships Summer 2027) and $103,000–$111,000/year (US Applied Machine Learning E</t>
         </is>
       </c>
       <c r="K352" s="6" t="inlineStr">
         <is>
-          <t>Partly open. 2027 Risk Management and Quantitative Risk Management Summer Analyst roles are live as of August 2026. IB and Global Markets still expected ~January to late March 2027; Technology ~July 2027. Rolling review</t>
+          <t>Closed for summer 2027 (US): US Applied Machine Learning Engineering Internships Summer 2027 (posted September 21, 2026) and US Software Engineering Internships Summer 2027 (posted September 28, 2026) stated that applications closed on October 12, 2026 at 11:59pm EDT. Neither was listed on shopify.com/careers on October 14, 2026, and no other intern posting was listed there that day. Fall 2027 pos</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Skild AI</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20205,12 +20205,12 @@
       </c>
       <c r="D353" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Engineering; Product Data Science; Applied ML Engineering; Infrastructure Engineering; Security Engineering</t>
+          <t>Research Intern — Robot Learning / ML (Confirmed); Robotics Engineering Intern (Inferred); Robot Operator / Technician (Intern-Adjacent)  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E353" s="7" t="inlineStr">
         <is>
-          <t>shopify.com/careers</t>
+          <t>skild.ai/career</t>
         </is>
       </c>
       <c r="F353" s="7" t="inlineStr">
@@ -20220,34 +20220,34 @@
       </c>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>Shopify’s funnel is faster than most big tech and distinctly different from the standard LeetCode gauntlet, averaging 3–5 weeks from application to decision: 1. Apply at shopify.com/careers with a resume, application questions, your LinkedIn, and a personal website or GitHub link. Shopify’s postings</t>
+          <t>Based on Glassdoor data from five interviews, the process typically includes a recruiter screen focused on background and technical alignment, a live coding round on CoderPad (example: write Multi-Headed Self Attention in PyTorch from scratch without autocomplete), and a final interview loop with te</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
         <is>
-          <t>No. Every internship posting states you must be legally entitled to work in the hiring country for the full duration. Shopify doesn't provide immigration sponsorship for intern candidates. However, candidates on existing</t>
+          <t>US work authorization required. F-1 CPT/OPT likely accepted. No confirmed direct visa sponsorship for interns</t>
         </is>
       </c>
       <c r="I353" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis, and postings warn they "may close before the stated closing date". The two US summer 2027 postings listed on Octo</t>
+          <t>Likely yes. With roughly 100 employees, hiring is opportunistic rather than cycle-based. Roles appear as team needs arise</t>
         </is>
       </c>
       <c r="J353" s="6" t="inlineStr">
         <is>
-          <t>$85,000–$93,700/year base pay range for US locations (US Software Engineering Internships Summer 2027) and $103,000–$111,000/year (US Applied Machine Learning E</t>
+          <t>No confirmed intern salary. Estimated $40 to $55 per hour for research/ML interns based on comparable robotics AI startup rates. Robot Operator roles pay $20 to</t>
         </is>
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>Closed for summer 2027 (US): US Applied Machine Learning Engineering Internships Summer 2027 (posted September 21, 2026) and US Software Engineering Internships Summer 2027 (posted September 28, 2026) stated that applications closed on October 12, 2026 at 11:59pm EDT. Neither was listed on shopify.com/careers on October 14, 2026, and no other intern posting was listed there that day. Fall 2027 pos</t>
+          <t>Not confirmed. Estimated January to March 2027 for summer 2027 roles, based on one confirmed intern datapoint and startup hiring norms. Low confidence</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>Skild AI</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20257,17 +20257,17 @@
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>January 2027</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>Research Intern — Robot Learning / ML (Confirmed); Robotics Engineering Intern (Inferred); Robot Operator / Technician (Intern-Adjacent)  (3 of 4 tracks)</t>
+          <t>Engineering &amp; Data Science; Machine Learning Engineering; Research Scientist (PhD)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E354" s="7" t="inlineStr">
         <is>
-          <t>skild.ai/career</t>
+          <t>lifeatspotify.com/jobs</t>
         </is>
       </c>
       <c r="F354" s="7" t="inlineStr">
@@ -20277,34 +20277,30 @@
       </c>
       <c r="G354" s="6" t="inlineStr">
         <is>
-          <t>Based on Glassdoor data from five interviews, the process typically includes a recruiter screen focused on background and technical alignment, a live coding round on CoderPad (example: write Multi-Headed Self Attention in PyTorch from scratch without autocomplete), and a final interview loop with te</t>
-        </is>
-      </c>
-      <c r="H354" s="6" t="inlineStr">
-        <is>
-          <t>US work authorization required. F-1 CPT/OPT likely accepted. No confirmed direct visa sponsorship for interns</t>
-        </is>
-      </c>
+          <t>A Lever application (resume; no cover letter is mentioned), then typically three rounds about a week apart: recruiter call, technical or craft interview, and a values interview. Engineering candidates report live coding over screen share. Community reports average about 39 days, and decisions arrive</t>
+        </is>
+      </c>
+      <c r="H354" s="6" t="inlineStr"/>
       <c r="I354" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. With roughly 100 employees, hiring is opportunistic rather than cycle-based. Roles appear as team needs arise</t>
+          <t>No. One hard deadline (Feb 5, 2026 at 12:00 PM ET last cycle); decisions to everyone by mid-April</t>
         </is>
       </c>
       <c r="J354" s="6" t="inlineStr">
         <is>
-          <t>No confirmed intern salary. Estimated $40 to $55 per hour for research/ML interns based on comparable robotics AI startup rates. Robot Operator roles pay $20 to</t>
+          <t>Official posted rates: $32/hr business tracks, $44/hr J.D. &amp; MBA, $51/hr eng/ML/data science, $55–60/hr PhD research</t>
         </is>
       </c>
       <c r="K354" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Estimated January to March 2027 for summer 2027 roles, based on one confirmed intern datapoint and startup hiring norms. Low confidence</t>
+          <t>Applications for summer 2027 expected to open mid-to-late January 2027, hard deadline early February 2027 at 12 PM ET; PhD research roles ~late November 2026 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20314,17 +20310,17 @@
       </c>
       <c r="C355" s="5" t="inlineStr">
         <is>
-          <t>January 2027</t>
+          <t>January–March 2027</t>
         </is>
       </c>
       <c r="D355" s="6" t="inlineStr">
         <is>
-          <t>Engineering &amp; Data Science; Machine Learning Engineering; Research Scientist (PhD)  (3 of 6 tracks)</t>
+          <t>SWE Intern (Health); SWE Intern (App Infrastructure); SWE Co-op; PM, AI Experiences (MBA)  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E355" s="7" t="inlineStr">
         <is>
-          <t>lifeatspotify.com/jobs</t>
+          <t>whoop.com/us/en/careers/</t>
         </is>
       </c>
       <c r="F355" s="7" t="inlineStr">
@@ -20334,30 +20330,34 @@
       </c>
       <c r="G355" s="6" t="inlineStr">
         <is>
-          <t>A Lever application (resume; no cover letter is mentioned), then typically three rounds about a week apart: recruiter call, technical or craft interview, and a values interview. Engineering candidates report live coding over screen share. Community reports average about 39 days, and decisions arrive</t>
-        </is>
-      </c>
-      <c r="H355" s="6" t="inlineStr"/>
+          <t>Typically 3 to 4 stages over about 19 days: a recruiter screen, a technical interview on Codility with practical day-to-day problems (AI tools allowed with disclosure), and 1 to 2 behavioral and leadership rounds. WHOOP explicitly avoids LeetCode-style brainteasers.</t>
+        </is>
+      </c>
+      <c r="H355" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated. WHOOP does not disclose sponsorship policy for interns publicly; international students should inquire directly</t>
+        </is>
+      </c>
       <c r="I355" s="6" t="inlineStr">
         <is>
-          <t>No. One hard deadline (Feb 5, 2026 at 12:00 PM ET last cycle); decisions to everyone by mid-April</t>
+          <t>Yes, implicitly. No published deadlines; positions close when filled. Apply within the first 2 to 4 weeks of a posting</t>
         </is>
       </c>
       <c r="J355" s="6" t="inlineStr">
         <is>
-          <t>Official posted rates: $32/hr business tracks, $44/hr J.D. &amp; MBA, $51/hr eng/ML/data science, $55–60/hr PhD research</t>
+          <t>SWE Intern ~$35/hr ($72K annualized median) plus free WHOOP membership and device</t>
         </is>
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open mid-to-late January 2027, hard deadline early February 2027 at 12 PM ET; PhD research roles ~late November 2026 (documented pattern; not yet posted)</t>
+          <t>Expected January to March 2027 for summer starts, based on prior posting patterns. Projected, not yet posted</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>AI21 Labs</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20367,17 +20367,17 @@
       </c>
       <c r="C356" s="5" t="inlineStr">
         <is>
-          <t>January–March 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern (Health); SWE Intern (App Infrastructure); SWE Co-op; PM, AI Experiences (MBA)  (4 of 6 tracks)</t>
+          <t>ML Research Intern; Software Engineering Intern  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E356" s="7" t="inlineStr">
         <is>
-          <t>whoop.com/us/en/careers/</t>
+          <t>linkedin.com/company/ai21-labs/jobs/</t>
         </is>
       </c>
       <c r="F356" s="7" t="inlineStr">
@@ -20387,34 +20387,34 @@
       </c>
       <c r="G356" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 stages over about 19 days: a recruiter screen, a technical interview on Codility with practical day-to-day problems (AI tools allowed with disclosure), and 1 to 2 behavioral and leadership rounds. WHOOP explicitly avoids LeetCode-style brainteasers.</t>
+          <t>The typical process involves 5 rounds over approximately 3 weeks: recruiter screen, hiring manager interview, take-home assignment simulating real project work, panel interview presenting your results, and a final culture-fit meeting. For research roles, expect deep dives into publications and resea</t>
         </is>
       </c>
       <c r="H356" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated. WHOOP does not disclose sponsorship policy for interns publicly; international students should inquire directly</t>
+          <t>Tel Aviv: Masa Israel assists with B-1 work visa for international candidates. NYC: J-1 or CPT/OPT for US-enrolled students. Arrangements may change if the Nvidia acquisition completes</t>
         </is>
       </c>
       <c r="I356" s="6" t="inlineStr">
         <is>
-          <t>Yes, implicitly. No published deadlines; positions close when filled. Apply within the first 2 to 4 weeks of a posting</t>
+          <t>Likely yes. AI21 does not publish a fixed application cycle. The Masa Israel pathway also operates on a rolling basis</t>
         </is>
       </c>
       <c r="J356" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern ~$35/hr ($72K annualized median) plus free WHOOP membership and device</t>
+          <t>Estimated ILS 6,000 to 12,000/mo (~$1,600 to $3,300/mo) in Tel Aviv. NYC roles estimated at $4,000 to $7,000/mo. No verified AI21 intern salary data exists</t>
         </is>
       </c>
       <c r="K356" s="6" t="inlineStr">
         <is>
-          <t>Expected January to March 2027 for summer starts, based on prior posting patterns. Projected, not yet posted</t>
+          <t>No fixed public cycle. Israeli AI startups typically post 2 to 4 months before start. Estimated window: February to April 2027 for a summer start</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>AI21 Labs</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20424,17 +20424,17 @@
       </c>
       <c r="C357" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>February–March 2027</t>
         </is>
       </c>
       <c r="D357" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; Software Engineering Intern  (2 of 4 tracks)</t>
+          <t>Engineering; IT, Data &amp; Analytics; Software Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E357" s="7" t="inlineStr">
         <is>
-          <t>linkedin.com/company/ai21-labs/jobs/</t>
+          <t>jobs.boeing.com/internships</t>
         </is>
       </c>
       <c r="F357" s="7" t="inlineStr">
@@ -20444,34 +20444,30 @@
       </c>
       <c r="G357" s="6" t="inlineStr">
         <is>
-          <t>The typical process involves 5 rounds over approximately 3 weeks: recruiter screen, hiring manager interview, take-home assignment simulating real project work, panel interview presenting your results, and a final culture-fit meeting. For research roles, expect deep dives into publications and resea</t>
-        </is>
-      </c>
-      <c r="H357" s="6" t="inlineStr">
-        <is>
-          <t>Tel Aviv: Masa Israel assists with B-1 work visa for international candidates. NYC: J-1 or CPT/OPT for US-enrolled students. Arrangements may change if the Nvidia acquisition completes</t>
-        </is>
-      </c>
+          <t>Expect one to three behavioral, STAR-style interviews by phone or video, sometimes a HireVue recorded video or a skill-alignment survey, and occasionally an offer with no live interview. There's no standardized LeetCode coding test for standard intern reqs. Glassdoor rates difficulty about 2.8 to 2.</t>
+        </is>
+      </c>
+      <c r="H357" s="6" t="inlineStr"/>
       <c r="I357" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. AI21 does not publish a fixed application cycle. The Masa Israel pathway also operates on a rolling basis</t>
+          <t>Yes. Reqs post continuously (some literally tagged "Evergreen") and close as they fill</t>
         </is>
       </c>
       <c r="J357" s="6" t="inlineStr">
         <is>
-          <t>Estimated ILS 6,000 to 12,000/mo (~$1,600 to $3,300/mo) in Tel Aviv. NYC roles estimated at $4,000 to $7,000/mo. No verified AI21 intern salary data exists</t>
+          <t>JD annualized bands ~$38k–$89k by discipline; ~$27.88–$32.00/hr reported on Levels.fyi</t>
         </is>
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>No fixed public cycle. Israeli AI startups typically post 2 to 4 months before start. Estimated window: February to April 2027 for a summer start</t>
+          <t>Fall wave for summer 2027 mostly ended: reqs posted from August 3, 2026, most closed after the October 23, 2026 posting end date. Four reqs remain; Workday lists an end date of October 26 (Supply Chain, Methods Process Analyst), October 30 (Finance) and November 15 (Security and Fire Operations). A smaller spring wave for summer 2027 is expected February to March 2027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20486,12 +20482,12 @@
       </c>
       <c r="D358" s="6" t="inlineStr">
         <is>
-          <t>Engineering; IT, Data &amp; Analytics; Software Engineering  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern; Analytics Consulting Intern; Data &amp; Analytics Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E358" s="7" t="inlineStr">
         <is>
-          <t>jobs.boeing.com/internships</t>
+          <t>braze.com/company/careers</t>
         </is>
       </c>
       <c r="F358" s="7" t="inlineStr">
@@ -20501,30 +20497,34 @@
       </c>
       <c r="G358" s="6" t="inlineStr">
         <is>
-          <t>Expect one to three behavioral, STAR-style interviews by phone or video, sometimes a HireVue recorded video or a skill-alignment survey, and occasionally an offer with no live interview. There's no standardized LeetCode coding test for standard intern reqs. Glassdoor rates difficulty about 2.8 to 2.</t>
-        </is>
-      </c>
-      <c r="H358" s="6" t="inlineStr"/>
+          <t>Typically 2 to 5 rounds: recruiter screen, hiring manager interview, technical interview (live coding for SWE or tailored assessment for non-SWE), and a team interview. The process is rated A+ (84 out of 100) on Comparably. 60% rate it Average difficulty, 33% Difficult. 50% of candidates hear back t</t>
+        </is>
+      </c>
+      <c r="H358" s="6" t="inlineStr">
+        <is>
+          <t>Evaluated case-by-case. The application asks whether you will require sponsorship. Braze sponsors H-1B and E-3 visas for full-time roles; intern-specific sponsorship is not explicitly confirmed</t>
+        </is>
+      </c>
       <c r="I358" s="6" t="inlineStr">
         <is>
-          <t>Yes. Reqs post continuously (some literally tagged "Evergreen") and close as they fill</t>
+          <t>Yes. Braze uses Greenhouse ATS and reviews applications on a rolling basis. Postings are removed once the class is filled. The SWE posting for Summer 2026 was r</t>
         </is>
       </c>
       <c r="J358" s="6" t="inlineStr">
         <is>
-          <t>JD annualized bands ~$38k–$89k by discipline; ~$27.88–$32.00/hr reported on Levels.fyi</t>
+          <t>$60/hr for SWE interns (~$10,400/month) in NYC. $45/hr for Analytics Consulting interns (~$7,800/month). Levels.fyi reports $60/hr for Summer 2024 and 2026</t>
         </is>
       </c>
       <c r="K358" s="6" t="inlineStr">
         <is>
-          <t>Fall wave for summer 2027 mostly ended: reqs posted from August 3, 2026, most closed after the October 23, 2026 posting end date. Four reqs remain; Workday lists an end date of October 26 (Supply Chain, Methods Process Analyst), October 30 (Finance) and November 15 (Security and Fire Operations). A smaller spring wave for summer 2027 is expected February to March 2027</t>
+          <t>Expected September–October 2026 for summer 2027 roles. SWE posting historically closes by mid-January. Analytics and other tracks may remain open into February–March. Projected from the Summer 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20534,17 +20534,17 @@
       </c>
       <c r="C359" s="5" t="inlineStr">
         <is>
-          <t>February–March 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D359" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Analytics Consulting Intern; Data &amp; Analytics Intern  (3 of 6 tracks)</t>
+          <t>Engineering Graduate Program (SWE); Software Engineer Intern (Ad-hoc); Data Engineering / Data Science; Security Engineering  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E359" s="7" t="inlineStr">
         <is>
-          <t>braze.com/company/careers</t>
+          <t>jobs.deel.com/job-boards/klarna</t>
         </is>
       </c>
       <c r="F359" s="7" t="inlineStr">
@@ -20554,34 +20554,34 @@
       </c>
       <c r="G359" s="6" t="inlineStr">
         <is>
-          <t>Typically 2 to 5 rounds: recruiter screen, hiring manager interview, technical interview (live coding for SWE or tailored assessment for non-SWE), and a team interview. The process is rated A+ (84 out of 100) on Comparably. 60% rate it Average difficulty, 33% Difficult. 50% of candidates hear back t</t>
+          <t>The process typically spans 5 to 6 rounds over 36 to 62 days: recruiter screen, a 12- to 15-minute video-proctored logic test, a technical OA on HackerRank, a 60-minute technical phone screen, a 3- to 4-hour virtual onsite loop, and a behavioral round with an AI-competency assessment. Glassdoor rate</t>
         </is>
       </c>
       <c r="H359" s="6" t="inlineStr">
         <is>
-          <t>Evaluated case-by-case. The application asks whether you will require sponsorship. Braze sponsors H-1B and E-3 visas for full-time roles; intern-specific sponsorship is not explicitly confirmed</t>
+          <t>Klarna states it will provide visa assistance when a position is offered. No relocation assistance for the Graduate Program. On-site presence in Stockholm required</t>
         </is>
       </c>
       <c r="I359" s="6" t="inlineStr">
         <is>
-          <t>Yes. Braze uses Greenhouse ATS and reviews applications on a rolling basis. Postings are removed once the class is filled. The SWE posting for Summer 2026 was r</t>
+          <t>Not confirmed. Graduate Program applications appear batch-reviewed within a defined Q1 window. Ad-hoc summer postings are likely filled as they appear</t>
         </is>
       </c>
       <c r="J359" s="6" t="inlineStr">
         <is>
-          <t>$60/hr for SWE interns (~$10,400/month) in NYC. $45/hr for Analytics Consulting interns (~$7,800/month). Levels.fyi reports $60/hr for Summer 2024 and 2026</t>
+          <t>Graduate Program: ~52K EUR total comp at L1 in Stockholm. Summer intern pay not published; US fintech benchmark is $35 to $50/hr. Benefits include 30 days leave</t>
         </is>
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>Expected September–October 2026 for summer 2027 roles. SWE posting historically closes by mid-January. Analytics and other tracks may remain open into February–March. Projected from the Summer 2026 cycle</t>
+          <t>Graduate Program: expected Q1 2027 (Feb to Apr) for a Sep to Oct 2027 start. Ad-hoc summer internships: postings may appear Fall 2026 through Winter 2027 for Jun to Aug 2027 roles</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20591,17 +20591,17 @@
       </c>
       <c r="C360" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
         <is>
-          <t>Engineering Graduate Program (SWE); Software Engineer Intern (Ad-hoc); Data Engineering / Data Science; Security Engineering  (4 of 5 tracks)</t>
+          <t>Quantitative Intern; Engineering &amp; AI Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E360" s="7" t="inlineStr">
         <is>
-          <t>jobs.deel.com/job-boards/klarna</t>
+          <t>campusjobs.mlp.com/careers</t>
         </is>
       </c>
       <c r="F360" s="7" t="inlineStr">
@@ -20611,34 +20611,34 @@
       </c>
       <c r="G360" s="6" t="inlineStr">
         <is>
-          <t>The process typically spans 5 to 6 rounds over 36 to 62 days: recruiter screen, a 12- to 15-minute video-proctored logic test, a technical OA on HackerRank, a 60-minute technical phone screen, a 3- to 4-hour virtual onsite loop, and a behavioral round with an AI-competency assessment. Glassdoor rate</t>
+          <t>Apply online, complete an OA on HackerRank or CodeSignal (2 coding problems, LeetCode Medium/Hard, ~20 to 30% pass rate), then a 15- to 20-minute recruiter screen, 1 to 2 technical phone interviews (45 to 60 minutes), and a 3- to 4-hour Superday with 3-5 back-to-back interviews. Offers often come wi</t>
         </is>
       </c>
       <c r="H360" s="6" t="inlineStr">
         <is>
-          <t>Klarna states it will provide visa assistance when a position is offered. No relocation assistance for the Graduate Program. On-site presence in Stockholm required</t>
+          <t>CPT supported for F-1 students. OPT and H-1B generally supported for full-time conversions. Pod-level hiring may affect sponsorship timing</t>
         </is>
       </c>
       <c r="I360" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Graduate Program applications appear batch-reviewed within a defined Q1 window. Ad-hoc summer postings are likely filled as they appear</t>
+          <t>Yes. Millennium explicitly states roles are filled on a rolling basis. The golden window is August through September; by November most spots are gone</t>
         </is>
       </c>
       <c r="J360" s="6" t="inlineStr">
         <is>
-          <t>Graduate Program: ~52K EUR total comp at L1 in Stockholm. Summer intern pay not published; US fintech benchmark is $35 to $50/hr. Benefits include 30 days leave</t>
+          <t>SWE: $80/hr ($13,867/mo) plus $5,000-$10,000 housing stipend. Quant Research: ~$112/hr (~$19,400/mo). Total 10-week take-home: $32,000-$45,000+. Levels.fyi veri</t>
         </is>
       </c>
       <c r="K360" s="6" t="inlineStr">
         <is>
-          <t>Graduate Program: expected Q1 2027 (Feb to Apr) for a Sep to Oct 2027 start. Ad-hoc summer internships: postings may appear Fall 2026 through Winter 2027 for Jun to Aug 2027 roles</t>
+          <t>Expected early August 2027 (historically August 1-3) for Summer 2028 roles. Rolling basis; apply within the first two weeks. Investment Internship track opens and fills much earlier (early 2027)</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20648,17 +20648,17 @@
       </c>
       <c r="C361" s="5" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>February–March 2027</t>
         </is>
       </c>
       <c r="D361" s="6" t="inlineStr">
         <is>
-          <t>Quantitative Intern; Engineering &amp; AI Intern  (2 of 6 tracks)</t>
+          <t>PlayStation/SIE Software Engineer Intern; Sony Electronics Software Engineer Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E361" s="7" t="inlineStr">
         <is>
-          <t>campusjobs.mlp.com/careers</t>
+          <t>sonyjobs.com/internships.html</t>
         </is>
       </c>
       <c r="F361" s="7" t="inlineStr">
@@ -20668,34 +20668,34 @@
       </c>
       <c r="G361" s="6" t="inlineStr">
         <is>
-          <t>Apply online, complete an OA on HackerRank or CodeSignal (2 coding problems, LeetCode Medium/Hard, ~20 to 30% pass rate), then a 15- to 20-minute recruiter screen, 1 to 2 technical phone interviews (45 to 60 minutes), and a 3- to 4-hour Superday with 3-5 back-to-back interviews. Offers often come wi</t>
+          <t>Most divisions follow a three- to four-round process: recruiter screen or video interview, a technical or supervisor round, and a panel or leadership behavioral round. PlayStation SWE roles include live coding on algorithms and system design. Sony Music uses a SparkHire video screen. Glassdoor rates</t>
         </is>
       </c>
       <c r="H361" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. OPT and H-1B generally supported for full-time conversions. Pod-level hiring may affect sponsorship timing</t>
+          <t>PlayStation/SIE: F-1 visa holders eligible, CPT supported. Sony Electronics SWE roles: H-1B sponsorship and STEM OPT/CPT welcomed. Sony Pictures and Sony Music: must be authorized to work in the U.S. for the duration. Ch</t>
         </is>
       </c>
       <c r="I361" s="6" t="inlineStr">
         <is>
-          <t>Yes. Millennium explicitly states roles are filled on a rolling basis. The golden window is August through September; by November most spots are gone</t>
+          <t>Sony Pictures recruits on a rolling basis until the right candidate is found. PlayStation and Sony Electronics typically review in waves. Apply as soon as posti</t>
         </is>
       </c>
       <c r="J361" s="6" t="inlineStr">
         <is>
-          <t>SWE: $80/hr ($13,867/mo) plus $5,000-$10,000 housing stipend. Quant Research: ~$112/hr (~$19,400/mo). Total 10-week take-home: $32,000-$45,000+. Levels.fyi veri</t>
+          <t>Varies widely by division and role. PlayStation SWE: $49.50 to $53/hr ($8,580 to $9,187/mo). Sony Electronics SWE: $25 to $40/hr. General entertainment roles: a</t>
         </is>
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>Expected early August 2027 (historically August 1-3) for Summer 2028 roles. Rolling basis; apply within the first two weeks. Investment Internship track opens and fills much earlier (early 2027)</t>
+          <t>Varies by division. Sony Music: expected deadline late January 2027. Sony Pictures: postings expected February 2027 for summer. PlayStation/SIE and Sony Electronics: expected fall 2026 to spring 2027. All dates projected from prior cycles</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20710,12 +20710,12 @@
       </c>
       <c r="D362" s="6" t="inlineStr">
         <is>
-          <t>PlayStation/SIE Software Engineer Intern; Sony Electronics Software Engineer Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern / Co-op (primary); Mobile Engineering (Android / iOS); AI / Machine Learning; Data Science Intern; Cybersecurity / Security Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E362" s="7" t="inlineStr">
         <is>
-          <t>sonyjobs.com/internships.html</t>
+          <t>careers.toasttab.com/early-career</t>
         </is>
       </c>
       <c r="F362" s="7" t="inlineStr">
@@ -20725,34 +20725,34 @@
       </c>
       <c r="G362" s="6" t="inlineStr">
         <is>
-          <t>Most divisions follow a three- to four-round process: recruiter screen or video interview, a technical or supervisor round, and a panel or leadership behavioral round. PlayStation SWE roles include live coding on algorithms and system design. Sony Music uses a SparkHire video screen. Glassdoor rates</t>
+          <t>A recruiter screen, a HackerRank online assessment (two questions, easy-to-medium), and a technical superday with a roughly one-hour live round, plus a behavioral conversation. Expect easy-medium DSA (graph traversal/DFS), restaurant-domain design, and heavy edge-case follow-up.</t>
         </is>
       </c>
       <c r="H362" s="6" t="inlineStr">
         <is>
-          <t>PlayStation/SIE: F-1 visa holders eligible, CPT supported. Sony Electronics SWE roles: H-1B sponsorship and STEM OPT/CPT welcomed. Sony Pictures and Sony Music: must be authorized to work in the U.S. for the duration. Ch</t>
+          <t>NOT FOUND (Toast publishes no explicit intern sponsorship statement; confirm with the recruiter</t>
         </is>
       </c>
       <c r="I362" s="6" t="inlineStr">
         <is>
-          <t>Sony Pictures recruits on a rolling basis until the right candidate is found. PlayStation and Sony Electronics typically review in waves. Apply as soon as posti</t>
+          <t xml:space="preserve">Partly. Each cycle opens in a defined window rather than year-round, but resumes are reviewed on an ongoing basis within the window. Toast advises checking the </t>
         </is>
       </c>
       <c r="J362" s="6" t="inlineStr">
         <is>
-          <t>Varies widely by division and role. PlayStation SWE: $49.50 to $53/hr ($8,580 to $9,187/mo). Sony Electronics SWE: $25 to $40/hr. General entertainment roles: a</t>
+          <t>Set by role, non-negotiable, disclosed at the recruiter screen. SWE interns near $38/hr median (~$34–41/hr) on Levels.fyi (community); Toast's official Fall 202</t>
         </is>
       </c>
       <c r="K362" s="6" t="inlineStr">
         <is>
-          <t>Varies by division. Sony Music: expected deadline late January 2027. Sony Pictures: postings expected February 2027 for summer. PlayStation/SIE and Sony Electronics: expected fall 2026 to spring 2027. All dates projected from prior cycles</t>
+          <t>Summer internship applications typically open February–March; expected Feb–March 2027 for a June 2027 start. Fall co-op opens ~June–July, Spring co-op ~October (all 2027 dates expected, projected from Toast's documented recurring windows)</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20762,17 +20762,17 @@
       </c>
       <c r="C363" s="5" t="inlineStr">
         <is>
-          <t>February–March 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern / Co-op (primary); Mobile Engineering (Android / iOS); AI / Machine Learning; Data Science Intern; Cybersecurity / Security Engineering  (5 of 6 tracks)</t>
+          <t>Software Engineering Intern (primary); Embedded Software Intern; Electrical Engineering Intern; Software Test Engineering Intern; Mechanical / General Engineering Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E363" s="7" t="inlineStr">
         <is>
-          <t>careers.toasttab.com/early-career</t>
+          <t>aptiv.com/en/jobs/students/aptiv-early-talent</t>
         </is>
       </c>
       <c r="F363" s="7" t="inlineStr">
@@ -20782,34 +20782,34 @@
       </c>
       <c r="G363" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a HackerRank online assessment (two questions, easy-to-medium), and a technical superday with a roughly one-hour live round, plus a behavioral conversation. Expect easy-medium DSA (graph traversal/DFS), restaurant-domain design, and heavy edge-case follow-up.</t>
+          <t>Typically three rounds: a stream-specific technical round (fundamentals, C code snippets, protocols like UART/I2C/SPI, basic data structures, tech trends), a technical/managerial round with a deep dive on your resume projects, and an HR/behavioral round. Electrical and power-electronics candidates o</t>
         </is>
       </c>
       <c r="H363" s="6" t="inlineStr">
         <is>
-          <t>NOT FOUND (Toast publishes no explicit intern sponsorship statement; confirm with the recruiter</t>
+          <t>Varies by req. The Troy Software Engineering Intern posting accepts US citizens, permanent residents, and US student-visa holders, but the Embedded Software Intern posting states visa sponsorship is not available. Always</t>
         </is>
       </c>
       <c r="I363" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly. Each cycle opens in a defined window rather than year-round, but resumes are reviewed on an ongoing basis within the window. Toast advises checking the </t>
+          <t xml:space="preserve">Yes. Aptiv posts individual intern reqs by team and location, and each closes when filled ("this job may close before the stated closing date, apply as soon as </t>
         </is>
       </c>
       <c r="J363" s="6" t="inlineStr">
         <is>
-          <t>Set by role, non-negotiable, disclosed at the recruiter screen. SWE interns near $38/hr median (~$34–41/hr) on Levels.fyi (community); Toast's official Fall 202</t>
+          <t>No official intern pay is published on the JDs. Community-reported: median ~$29/hr, range ~$22–$37/hr (Glassdoor, 24 salaries, Apr 2025); Levels.fyi lists a har</t>
         </is>
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>Summer internship applications typically open February–March; expected Feb–March 2027 for a June 2027 start. Fall co-op opens ~June–July, Spring co-op ~October (all 2027 dates expected, projected from Toast's documented recurring windows)</t>
+          <t>Not published as a fixed calendar. Summer 2027 reqs began posting on September 9, 2026 and are expected to keep rolling into winter/spring 2027. A prior-cycle Troy SWE intern req listed "Apply by 20 Nov 2025," so apply the week a relevant req appears.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Ferrari</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20819,17 +20819,17 @@
       </c>
       <c r="C364" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>March–April 2027</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (primary); Embedded Software Intern; Electrical Engineering Intern; Software Test Engineering Intern; Mechanical / General Engineering Intern  (5 of 6 tracks)</t>
+          <t>F1 Engineering Academy; Vehicle Assembly Process Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E364" s="7" t="inlineStr">
         <is>
-          <t>aptiv.com/en/jobs/students/aptiv-early-talent</t>
+          <t>ferrari.com/en-EN/corporate/career</t>
         </is>
       </c>
       <c r="F364" s="7" t="inlineStr">
@@ -20839,34 +20839,30 @@
       </c>
       <c r="G364" s="6" t="inlineStr">
         <is>
-          <t>Typically three rounds: a stream-specific technical round (fundamentals, C code snippets, protocols like UART/I2C/SPI, basic data structures, tech trends), a technical/managerial round with a deep dive on your resume projects, and an HR/behavioral round. Electrical and power-electronics candidates o</t>
-        </is>
-      </c>
-      <c r="H364" s="6" t="inlineStr">
-        <is>
-          <t>Varies by req. The Troy Software Engineering Intern posting accepts US citizens, permanent residents, and US student-visa holders, but the Embedded Software Intern posting states visa sponsorship is not available. Always</t>
-        </is>
-      </c>
+          <t>Expect multiple rounds. For the F1 Engineering Academy: CV screening, HR phone or Teams call, then an assessment center in Maranello with line managers and mentors. For general roles: automated screening, possible psychometric test, video interview, and final technical interviews with senior enginee</t>
+        </is>
+      </c>
+      <c r="H364" s="6" t="inlineStr"/>
       <c r="I364" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes. Aptiv posts individual intern reqs by team and location, and each closes when filled ("this job may close before the stated closing date, apply as soon as </t>
+          <t>Partially. Flagship academies have fixed deadlines with structured assessments. General roles on jobs.ferrari.com fill as received</t>
         </is>
       </c>
       <c r="J364" s="6" t="inlineStr">
         <is>
-          <t>No official intern pay is published on the JDs. Community-reported: median ~$29/hr, range ~$22–$37/hr (Glassdoor, 24 salaries, Apr 2025); Levels.fyi lists a har</t>
+          <t>~EUR 700–1,200/month plus meals (Italy); ~$35/hr estimate (US, Glassdoor)</t>
         </is>
       </c>
       <c r="K364" s="6" t="inlineStr">
         <is>
-          <t>Not published as a fixed calendar. Summer 2027 reqs began posting on September 9, 2026 and are expected to keep rolling into winter/spring 2027. A prior-cycle Troy SWE intern req listed "Apply by 20 Nov 2025," so apply the week a relevant req appears.</t>
+          <t>F1 Engineering Academy: expected Q1 2027 (March–April deadline). Design Academy: expected spring–summer 2027 (June–July deadline). General roles: year-round</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20876,17 +20872,17 @@
       </c>
       <c r="C365" s="5" t="inlineStr">
         <is>
-          <t>March–April 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
         <is>
-          <t>F1 Engineering Academy; Vehicle Assembly Process Engineering  (2 of 6 tracks)</t>
+          <t>Finance &amp; Data Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E365" s="7" t="inlineStr">
         <is>
-          <t>ferrari.com/en-EN/corporate/career</t>
+          <t>wmg.com/emerging-talent</t>
         </is>
       </c>
       <c r="F365" s="7" t="inlineStr">
@@ -20896,30 +20892,30 @@
       </c>
       <c r="G365" s="6" t="inlineStr">
         <is>
-          <t>Expect multiple rounds. For the F1 Engineering Academy: CV screening, HR phone or Teams call, then an assessment center in Maranello with line managers and mentors. For general roles: automated screening, possible psychometric test, video interview, and final technical interviews with senior enginee</t>
+          <t>It varies by hiring manager but includes at least one interview, often a recorded HireVue-style video screen followed by a live Zoom or in-person round (a 1:1 with the hiring manager and/or a panel). Some interviews run as short as 15 minutes, and offers can arrive within days of the live round.</t>
         </is>
       </c>
       <c r="H365" s="6" t="inlineStr"/>
       <c r="I365" s="6" t="inlineStr">
         <is>
-          <t>Partially. Flagship academies have fixed deadlines with structured assessments. General roles on jobs.ferrari.com fill as received</t>
+          <t>Yes. WMG reviews ETA applications on a rolling basis and urges applying as early as possible; placements can fill before the posted deadline</t>
         </is>
       </c>
       <c r="J365" s="6" t="inlineStr">
         <is>
-          <t>~EUR 700–1,200/month plus meals (Italy); ~$35/hr estimate (US, Glassdoor)</t>
+          <t>$17.00–$18.42/hour (employer-provided on ETA postings). Housing not provided. Academic credit available. Ignore inflated Glassdoor aggregate estimates; the JD f</t>
         </is>
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>F1 Engineering Academy: expected Q1 2027 (March–April deadline). Design Academy: expected spring–summer 2027 (June–July deadline). General roles: year-round</t>
+          <t>Not posted yet. Summer 2027 applications expected to open ~March 2027 with a deadline ~mid-April 2027 (expected), projected from Summer 2026 (deadline April 17, 2026). Nearest window: Spring 2027 cohort, applications expected November 2026 to January 2027 (no ETA roles posted on October 6, 2026). Fall window: July to August</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Canva</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20929,17 +20925,17 @@
       </c>
       <c r="C366" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>April–May 2027</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
         <is>
-          <t>Finance &amp; Data Analytics  (1 of 6 tracks)</t>
+          <t>Software Engineering; ML / AI Engineering; Growth Engineering; Data Science  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E366" s="7" t="inlineStr">
         <is>
-          <t>wmg.com/emerging-talent</t>
+          <t>lifeatcanva.com/en/early-careers/</t>
         </is>
       </c>
       <c r="F366" s="7" t="inlineStr">
@@ -20949,30 +20945,30 @@
       </c>
       <c r="G366" s="6" t="inlineStr">
         <is>
-          <t>It varies by hiring manager but includes at least one interview, often a recorded HireVue-style video screen followed by a live Zoom or in-person round (a 1:1 with the hiring manager and/or a panel). Some interviews run as short as 15 minutes, and offers can arrive within days of the live round.</t>
+          <t>For engineering interns, expect a 90-minute online assessment (3 coding questions, Java-only for backend), followed by a recruiter Zoom call, then a technical interview with LeetCode-style problems and system design. ML/AI adds math-heavy MCQs. The process takes about 4–5 weeks. Canva encourages usi</t>
         </is>
       </c>
       <c r="H366" s="6" t="inlineStr"/>
       <c r="I366" s="6" t="inlineStr">
         <is>
-          <t>Yes. WMG reviews ETA applications on a rolling basis and urges applying as early as possible; placements can fill before the posted deadline</t>
+          <t>Partially. ANZ has a defined ~30-day window; US roles recruit on a rolling basis. Both close when filled</t>
         </is>
       </c>
       <c r="J366" s="6" t="inlineStr">
         <is>
-          <t>$17.00–$18.42/hour (employer-provided on ETA postings). Housing not provided. Academic credit available. Ignore inflated Glassdoor aggregate estimates; the JD f</t>
+          <t>AU: ~A$28–38/hr + meals. US: ~$46–60/hr (SWE), ~$52–60/hr (ML/AI), with relocation assistance</t>
         </is>
       </c>
       <c r="K366" s="6" t="inlineStr">
         <is>
-          <t>Not posted yet. Summer 2027 applications expected to open ~March 2027 with a deadline ~mid-April 2027 (expected), projected from Summer 2026 (deadline April 17, 2026). Nearest window: Spring 2027 cohort, applications expected November 2026 to January 2027 (no ETA roles posted on October 6, 2026). Fall window: July to August</t>
+          <t>ANZ: expected April–May 2027 for Dec 2027 start (~30-day window). US: expected Sep–Nov 2027 for May–Aug 2028 (rolling)</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>Canva</t>
+          <t>AQR Capital</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20982,17 +20978,17 @@
       </c>
       <c r="C367" s="5" t="inlineStr">
         <is>
-          <t>April–May 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D367" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; ML / AI Engineering; Growth Engineering; Data Science  (4 of 6 tracks)</t>
+          <t>Engineering Summer Analyst; Research and Portfolio Management Engineering Summer Analyst; Quantitative Prediction Markets Research Summer Analyst  (3 of 7 tracks)</t>
         </is>
       </c>
       <c r="E367" s="7" t="inlineStr">
         <is>
-          <t>lifeatcanva.com/en/early-careers/</t>
+          <t>careers.aqr.com/jobs/category/university-jobs</t>
         </is>
       </c>
       <c r="F367" s="7" t="inlineStr">
@@ -21002,30 +20998,34 @@
       </c>
       <c r="G367" s="6" t="inlineStr">
         <is>
-          <t>For engineering interns, expect a 90-minute online assessment (3 coding questions, Java-only for backend), followed by a recruiter Zoom call, then a technical interview with LeetCode-style problems and system design. ML/AI adds math-heavy MCQs. The process takes about 4–5 weeks. Canva encourages usi</t>
-        </is>
-      </c>
-      <c r="H367" s="6" t="inlineStr"/>
+          <t>Four rounds: a 30-minute recruiter screen, a 60-to-90-minute technical phone screen (probability, statistics, coding), a 5-to-7-interview on-site covering statistics, Python coding, research discussion, domain depth, and behavioral fit, then a decision within 1 to 3 weeks.</t>
+        </is>
+      </c>
+      <c r="H367" s="6" t="inlineStr">
+        <is>
+          <t>CPT for enrolled international students, OPT with STEM extension supported, H-1B for full-time conversion (~50 approvals FY2025)</t>
+        </is>
+      </c>
       <c r="I367" s="6" t="inlineStr">
         <is>
-          <t>Partially. ANZ has a defined ~30-day window; US roles recruit on a rolling basis. Both close when filled</t>
+          <t>Not confirmed rolling, but tracks close one at a time with no printed date: the Trading and Portfolio Finance postings came down in October 2026 while others st</t>
         </is>
       </c>
       <c r="J367" s="6" t="inlineStr">
         <is>
-          <t>AU: ~A$28–38/hr + meals. US: ~$46–60/hr (SWE), ~$52–60/hr (ML/AI), with relocation assistance</t>
+          <t>Research: ~$65–80/hr ($30K–35K+ for 10 weeks). Portfolio/Engineering: ~$55–65/hr ($25K–30K). Housing stipend provided (community estimates)</t>
         </is>
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>ANZ: expected April–May 2027 for Dec 2027 start (~30-day window). US: expected Sep–Nov 2027 for May–Aug 2028 (rolling)</t>
+          <t>Summer 2027 opened June 30, 2026 and did not close in mid-August: as of October 22, 2026, seven undergraduate summer analyst postings are still live with no close date printed. Summer 2028 expected to follow the same late-June pattern in 2027</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>AQR Capital</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -21040,12 +21040,12 @@
       </c>
       <c r="D368" s="6" t="inlineStr">
         <is>
-          <t>Engineering Summer Analyst; Research and Portfolio Management Engineering Summer Analyst; Quantitative Prediction Markets Research Summer Analyst  (3 of 7 tracks)</t>
+          <t>Software Engineering Internship; Data, Analytics &amp; ML Internship; Site Reliability Engineering Internship  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E368" s="7" t="inlineStr">
         <is>
-          <t>careers.aqr.com/jobs/category/university-jobs</t>
+          <t>atlassian.com/company/careers/earlycareers</t>
         </is>
       </c>
       <c r="F368" s="7" t="inlineStr">
@@ -21055,34 +21055,34 @@
       </c>
       <c r="G368" s="6" t="inlineStr">
         <is>
-          <t>Four rounds: a 30-minute recruiter screen, a 60-to-90-minute technical phone screen (probability, statistics, coding), a 5-to-7-interview on-site covering statistics, Python coding, research discussion, domain depth, and behavioral fit, then a decision within 1 to 3 weeks.</t>
+          <t>Typically 4 to 5 stages: online assessment (HackerRank, 2 to 4 problems, 60 to 90 minutes), recruiter phone screen (30 minutes), technical coding interview (code on your own laptop, 1 DSA problem with follow-ups, 45 to 60 minutes), values interview (behavioral, 45 to 60 minutes), and hiring committe</t>
         </is>
       </c>
       <c r="H368" s="6" t="inlineStr">
         <is>
-          <t>CPT for enrolled international students, OPT with STEM extension supported, H-1B for full-time conversion (~50 approvals FY2025)</t>
+          <t>US internships are not available for any work sponsorship including F-1 OPT/CPT and J-1 status. Must have eligible US work authorization</t>
         </is>
       </c>
       <c r="I368" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed rolling, but tracks close one at a time with no printed date: the Trading and Portfolio Finance postings came down in October 2026 while others st</t>
+          <t>Yes, explicitly confirmed. Atlassian recruits on a rolling basis and strongly encourages early applications within the first 2 to 3 weeks</t>
         </is>
       </c>
       <c r="J368" s="6" t="inlineStr">
         <is>
-          <t>Research: ~$65–80/hr ($30K–35K+ for 10 weeks). Portfolio/Engineering: ~$55–65/hr ($25K–30K). Housing stipend provided (community estimates)</t>
+          <t>Software Engineer Intern, 2027 Summer U.S. posting (live Oct 22, 2026): Zone A $59 to $67/hr, Zone B $54 to $60/hr, Zone C $49 to $56/hr. Other 2027 postings li</t>
         </is>
       </c>
       <c r="K368" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 opened June 30, 2026 and did not close in mid-August: as of October 22, 2026, seven undergraduate summer analyst postings are still live with no close date printed. Summer 2028 expected to follow the same late-June pattern in 2027</t>
+          <t>Summer 2027 is open (US): Software Engineer Intern, 2027 Summer U.S. posted Sep 1, 2026, and 11 US summer 2027 intern postings were live on Oct 22, 2026. No deadline stated</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -21097,12 +21097,12 @@
       </c>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Internship; Data, Analytics &amp; ML Internship; Site Reliability Engineering Internship  (3 of 6 tracks)</t>
+          <t>Global Technology (BA / SWE)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E369" s="7" t="inlineStr">
         <is>
-          <t>atlassian.com/company/careers/earlycareers</t>
+          <t>careers.bankofamerica.com/en-us/students</t>
         </is>
       </c>
       <c r="F369" s="7" t="inlineStr">
@@ -21112,34 +21112,34 @@
       </c>
       <c r="G369" s="6" t="inlineStr">
         <is>
-          <t>Typically 4 to 5 stages: online assessment (HackerRank, 2 to 4 problems, 60 to 90 minutes), recruiter phone screen (30 minutes), technical coding interview (code on your own laptop, 1 DSA problem with follow-ups, 45 to 60 minutes), values interview (behavioral, 45 to 60 minutes), and hiring committe</t>
+          <t>It starts with a HireVue on-demand video interview: a few behavioral questions, about 30 seconds of prep, and up to three minutes per answer. Strong candidates advance to a super day of two to four interviews, behavioral with a technical or case round for front-office desks. No aptitude games.</t>
         </is>
       </c>
       <c r="H369" s="6" t="inlineStr">
         <is>
-          <t>US internships are not available for any work sponsorship including F-1 OPT/CPT and J-1 status. Must have eligible US work authorization</t>
+          <t>No. The postings state the bank is "unable to consider candidates who will require visa sponsorship now, or in the future." It's a hard gate, not a preference, so if you'll need sponsorship, these US summer analyst progr</t>
         </is>
       </c>
       <c r="I369" s="6" t="inlineStr">
         <is>
-          <t>Yes, explicitly confirmed. Atlassian recruits on a rolling basis and strongly encourages early applications within the first 2 to 3 weeks</t>
+          <t>Yes. Official: recruiting is "on a rolling basis once applications open" and "programs will close as positions are filled"</t>
         </is>
       </c>
       <c r="J369" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S. posting (live Oct 22, 2026): Zone A $59 to $67/hr, Zone B $54 to $60/hr, Zone C $49 to $56/hr. Other 2027 postings li</t>
+          <t>Community-labeled: NYC business analyst intern ~$45.50/hr + $3,400 bonus (Levels.fyi); front-office base ~$110k prorated</t>
         </is>
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 is open (US): Software Engineer Intern, 2027 Summer U.S. posted Sep 1, 2026, and 11 US summer 2027 intern postings were live on Oct 22, 2026. No deadline stated</t>
+          <t>Front office: expected spring to summer 2027, rolling. Enterprise tracks: summer to fall 2027, deadlines around October (projected pattern)</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="D370" s="6" t="inlineStr">
         <is>
-          <t>Global Technology (BA / SWE)  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Cloud Security Intern; AI/ML Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E370" s="7" t="inlineStr">
         <is>
-          <t>careers.bankofamerica.com/en-us/students</t>
+          <t>crowdstrike.com/en-us/careers/university-interns/</t>
         </is>
       </c>
       <c r="F370" s="7" t="inlineStr">
@@ -21169,34 +21169,34 @@
       </c>
       <c r="G370" s="6" t="inlineStr">
         <is>
-          <t>It starts with a HireVue on-demand video interview: a few behavioral questions, about 30 seconds of prep, and up to three minutes per answer. Strong candidates advance to a super day of two to four interviews, behavioral with a technical or case round for front-office desks. No aptitude games.</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), take a 60- to 90-minute technical assessment (HackerRank for engineering, take-home for intelligence), then a virtual onsite with 2 to 3 technical sessions plus a behavioral round. Decisions come within 1 to 2 weeks. Total proce</t>
         </is>
       </c>
       <c r="H370" s="6" t="inlineStr">
         <is>
-          <t>No. The postings state the bank is "unable to consider candidates who will require visa sponsorship now, or in the future." It's a hard gate, not a preference, so if you'll need sponsorship, these US summer analyst progr</t>
+          <t>CPT supported for F-1 students. STEM OPT extension eligible. Selective H-1B sponsorship for early-career roles. Security-clearance roles require U.S. citizenship</t>
         </is>
       </c>
       <c r="I370" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official: recruiting is "on a rolling basis once applications open" and "programs will close as positions are filled"</t>
+          <t>Yes. CrowdStrike reviews applications on a rolling basis and fills seats as strong candidates clear the pipeline. Apply early for priority consideration</t>
         </is>
       </c>
       <c r="J370" s="6" t="inlineStr">
         <is>
-          <t>Community-labeled: NYC business analyst intern ~$45.50/hr + $3,400 bonus (Levels.fyi); front-office base ~$110k prorated</t>
+          <t>$28–$55/hr depending on role. SWE interns ~$43/hr (~$7,450/month). Intelligence interns $28–$35/hr. Housing stipend up to $4,500/month for eligible participants</t>
         </is>
       </c>
       <c r="K370" s="6" t="inlineStr">
         <is>
-          <t>Front office: expected spring to summer 2027, rolling. Enterprise tracks: summer to fall 2027, deadlines around October (projected pattern)</t>
+          <t>FIRST POSTINGS LIVE: Sales Excellence Elite Intern (Summer 2027) reqs posted Sep 16, 2026 and a Global Sales Programs Intern (Summer 2027) on Sep 28, 2026 on CrowdStrike's Workday board (Austin). Engineering and security intern reqs not yet posted as of Oct 1, 2026; expect them through fall. Bulk offers projected by December 2026</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Electric</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -21206,17 +21206,17 @@
       </c>
       <c r="C371" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–October 2027</t>
         </is>
       </c>
       <c r="D371" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Cloud Security Intern; AI/ML Intern  (3 of 6 tracks)</t>
+          <t>Engineering Intern (GE Aerospace); AI / Digital Technology Intern (GE Aerospace)  (2 of 8 tracks)</t>
         </is>
       </c>
       <c r="E371" s="7" t="inlineStr">
         <is>
-          <t>crowdstrike.com/en-us/careers/university-interns/</t>
+          <t>careers.geaerospace.com/global/en/us-internships</t>
         </is>
       </c>
       <c r="F371" s="7" t="inlineStr">
@@ -21226,34 +21226,34 @@
       </c>
       <c r="G371" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), take a 60- to 90-minute technical assessment (HackerRank for engineering, take-home for intelligence), then a virtual onsite with 2 to 3 technical sessions plus a behavioral round. Decisions come within 1 to 2 weeks. Total proce</t>
+          <t>The process typically has three stages: a recruiter phone screen (15 to 30 minutes), a technical screen or video interview with the hiring manager (30 to 45 minutes covering resume and engineering or technical questions), and a behavioral interview using the STAR method. The average time from applic</t>
         </is>
       </c>
       <c r="H371" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. STEM OPT extension eligible. Selective H-1B sponsorship for early-career roles. Security-clearance roles require U.S. citizenship</t>
+          <t>Limited. Many GE Aerospace roles require U.S. persons status (U.S. citizens, permanent residents, or protected individuals). Some non-defense roles at GE Vernova and GE HealthCare may accept work-authorized international</t>
         </is>
       </c>
       <c r="I371" s="6" t="inlineStr">
         <is>
-          <t>Yes. CrowdStrike reviews applications on a rolling basis and fills seats as strong candidates clear the pipeline. Apply early for priority consideration</t>
+          <t>Yes, continuous rolling. GE reviews applications on a rolling basis and postings go live continuously through the fall. Apply within the first few weeks of a po</t>
         </is>
       </c>
       <c r="J371" s="6" t="inlineStr">
         <is>
-          <t>$28–$55/hr depending on role. SWE interns ~$43/hr (~$7,450/month). Intelligence interns $28–$35/hr. Housing stipend up to $4,500/month for eligible participants</t>
+          <t>$20 to $26 per hour depending on year of study and division. Housing and relocation assistance provided to eligible students (reported at approximately $225 per</t>
         </is>
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>FIRST POSTINGS LIVE: Sales Excellence Elite Intern (Summer 2027) reqs posted Sep 16, 2026 and a Global Sales Programs Intern (Summer 2027) on Sep 28, 2026 on CrowdStrike's Workday board (Austin). Engineering and security intern reqs not yet posted as of Oct 1, 2026; expect them through fall. Bulk offers projected by December 2026</t>
+          <t>Summer 2027 GE Aerospace roles are live now (as of July 2026 on the GE Aerospace careers portal), added on a rolling basis with new roles through fall 2026. On-campus and virtual events in September, virtual interviews in October, most offers by November 2026. Apply as soon as a matching role posts</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>General Electric</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -21263,17 +21263,17 @@
       </c>
       <c r="C372" s="5" t="inlineStr">
         <is>
-          <t>June–October 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern (GE Aerospace); AI / Digital Technology Intern (GE Aerospace)  (2 of 8 tracks)</t>
+          <t>Engineering Co-op (Chemical / Electrical Controls); Data Science / Analytics Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E372" s="7" t="inlineStr">
         <is>
-          <t>careers.geaerospace.com/global/en/us-internships</t>
+          <t>careers.thehersheycompany.com/go/Interns/9002600/</t>
         </is>
       </c>
       <c r="F372" s="7" t="inlineStr">
@@ -21283,34 +21283,34 @@
       </c>
       <c r="G372" s="6" t="inlineStr">
         <is>
-          <t>The process typically has three stages: a recruiter phone screen (15 to 30 minutes), a technical screen or video interview with the hiring manager (30 to 45 minutes covering resume and engineering or technical questions), and a behavioral interview using the STAR method. The average time from applic</t>
+          <t>Usually one behavioral (STAR) video interview with two team members, tailored to your resume, plus a background check and drug test. Average difficulty is low (2.8/5), ~26 days to hire, 67% positive on Glassdoor. There is no standardized timed online assessment for the corporate funnel.</t>
         </is>
       </c>
       <c r="H372" s="6" t="inlineStr">
         <is>
-          <t>Limited. Many GE Aerospace roles require U.S. persons status (U.S. citizens, permanent residents, or protected individuals). Some non-defense roles at GE Vernova and GE HealthCare may accept work-authorized international</t>
+          <t>NO) every intern JD states Hershey will not provide immigration-related support for internships, and will not sponsor (e.g., H-1B) for entry-level roles later either. The single biggest eligibility filter</t>
         </is>
       </c>
       <c r="I372" s="6" t="inlineStr">
         <is>
-          <t>Yes, continuous rolling. GE reviews applications on a rolling basis and postings go live continuously through the fall. Apply within the first few weeks of a po</t>
+          <t>Partly. Standing "Future Opportunities" postings collect applications continuously and are drawn from as team needs arise; individual summer cohorts still calib</t>
         </is>
       </c>
       <c r="J372" s="6" t="inlineStr">
         <is>
-          <t>$20 to $26 per hour depending on year of study and division. Housing and relocation assistance provided to eligible students (reported at approximately $225 per</t>
+          <t>No official rate published. Community/aggregator data: Engineering interns ~$25/hr (Indeed), a ChemE year-long co-op at $23/hr (Reddit), a remote Data Scientist</t>
         </is>
       </c>
       <c r="K372" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 GE Aerospace roles are live now (as of July 2026 on the GE Aerospace careers portal), added on a rolling basis with new roles through fall 2026. On-campus and virtual events in September, virtual interviews in October, most offers by November 2026. Apply as soon as a matching role posts</t>
+          <t>Opening now. First Summer 2027 posting live: Electrical Controls Co-Op (Summer 2027), posted October 2, 2026, alongside Spring 2027 co-ops. Corporate Finance, Category Management and Supply Chain summer 2027 internships not posted yet as of October 6, 2026 (the Summer 2026 Finance posting went live Aug 8, 2025)</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -21325,12 +21325,12 @@
       </c>
       <c r="D373" s="6" t="inlineStr">
         <is>
-          <t>Engineering Co-op (Chemical / Electrical Controls); Data Science / Analytics Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering (SWE); Data Science &amp; AI  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E373" s="7" t="inlineStr">
         <is>
-          <t>careers.thehersheycompany.com/go/Interns/9002600/</t>
+          <t>ibm.com/careers/internships</t>
         </is>
       </c>
       <c r="F373" s="7" t="inlineStr">
@@ -21340,34 +21340,34 @@
       </c>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>Usually one behavioral (STAR) video interview with two team members, tailored to your resume, plus a background check and drug test. Average difficulty is low (2.8/5), ~26 days to hire, 67% positive on Glassdoor. There is no standardized timed online assessment for the corporate funnel.</t>
+          <t>IBM's hiring funnel runs 4–10 weeks from application to offer, with three core rounds for standard internships and four to five for Extreme Blue: 1. Apply at ibm.com/careers/internships with your resume and an IBM Careers profile. Use keywords from your target JD (watsonx, OpenShift, hybrid cloud) b</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr">
         <is>
-          <t>NO) every intern JD states Hershey will not provide immigration-related support for internships, and will not sponsor (e.g., H-1B) for entry-level roles later either. The single biggest eligibility filter</t>
+          <t>Most US internship postings explicitly state that IBM will not provide visa sponsorship. Exceptions sometimes exist for PhD Research interns and Extreme Blue participants. International students must verify work authoriz</t>
         </is>
       </c>
       <c r="I373" s="6" t="inlineStr">
         <is>
-          <t>Partly. Standing "Future Opportunities" postings collect applications continuously and are drawn from as team needs arise; individual summer cohorts still calib</t>
+          <t>Yes. Positions filled as qualified candidates are identified; early applicants face less competition</t>
         </is>
       </c>
       <c r="J373" s="6" t="inlineStr">
         <is>
-          <t>No official rate published. Community/aggregator data: Engineering interns ~$25/hr (Indeed), a ChemE year-long co-op at $23/hr (Reddit), a remote Data Scientist</t>
+          <t>$32–$88/hr depending on track (SWE ~$75, Research ~$88, PM ~$66); relocation stipend $2–4K</t>
         </is>
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>Opening now. First Summer 2027 posting live: Electrical Controls Co-Op (Summer 2027), posted October 2, 2026, alongside Spring 2027 co-ops. Corporate Finance, Category Management and Supply Chain summer 2027 internships not posted yet as of October 6, 2026 (the Summer 2026 Finance posting went live Aug 8, 2025)</t>
+          <t>OPEN. The summer 2027 wave is broadly open on careers.ibm.com as of August 2026, with roles across Product Management, Business Transformation Consulting, Application Development, Sales, and more. Rolling review through January 2027</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21377,17 +21377,17 @@
       </c>
       <c r="C374" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–November 2027</t>
         </is>
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (SWE); Data Science &amp; AI  (2 of 6 tracks)</t>
+          <t>Technology &amp; Digital / Data Analytics Intern; 84.51° Data Scientist Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E374" s="7" t="inlineStr">
         <is>
-          <t>ibm.com/careers/internships</t>
+          <t>krogerfamilycareers.com/en/sites/CX_2001/pages/5015</t>
         </is>
       </c>
       <c r="F374" s="7" t="inlineStr">
@@ -21397,34 +21397,34 @@
       </c>
       <c r="G374" s="6" t="inlineStr">
         <is>
-          <t>IBM's hiring funnel runs 4–10 weeks from application to offer, with three core rounds for standard internships and four to five for Extreme Blue: 1. Apply at ibm.com/careers/internships with your resume and an IBM Careers profile. Use keywords from your target JD (watsonx, OpenShift, hybrid cloud) b</t>
+          <t>Typically a HireVue one-way video interview, then a behavioral panel (STAR questions mapped to Kroger's core values), and a final leadership conversation. Technology and data roles add an assessment: Reddit reports a coding challenge (Swift) plus a "game" challenge. Corporate non-technical roles usu</t>
         </is>
       </c>
       <c r="H374" s="6" t="inlineStr">
         <is>
-          <t>Most US internship postings explicitly state that IBM will not provide visa sponsorship. Exceptions sometimes exist for PhD Research interns and Extreme Blue participants. International students must verify work authoriz</t>
+          <t>No. JDs require work authorization that does not now or in the future require sponsorship, explicitly excluding H-1B, F-1/OPT, and TN. Kroger does not sponsor interns</t>
         </is>
       </c>
       <c r="I374" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified; early applicants face less competition</t>
+          <t>Yes. Both Kroger corporate and 84.51° fill intern roles on a rolling basis and unpost them as they fill. Applying in September or October materially beats Decem</t>
         </is>
       </c>
       <c r="J374" s="6" t="inlineStr">
         <is>
-          <t>$32–$88/hr depending on track (SWE ~$75, Research ~$88, PM ~$66); relocation stipend $2–4K</t>
+          <t>No official intern pay published ("competitive pay"). Community and aggregator estimates: ~$14–$27/hr, with technical and 84.51° roles reportedly higher ($22–$4</t>
         </is>
       </c>
       <c r="K374" s="6" t="inlineStr">
         <is>
-          <t>OPEN. The summer 2027 wave is broadly open on careers.ibm.com as of August 2026, with roles across Product Management, Business Transformation Consulting, Application Development, Sales, and more. Rolling review through January 2027</t>
+          <t>Summer 2027 is partly open. Kroger's own careers board showed six Summer 2027 intern reqs on September 27, 2026: supply chain Quality, Maintenance, Human Resources and Continuous Improvement in Denver (posted September 1, listed through November 30), Transportation in Nashville (posted September 23), and a Construction Project Engineer intern in Hutchinson, KS. Program dates are May 17 to August 6</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21434,17 +21434,17 @@
       </c>
       <c r="C375" s="5" t="inlineStr">
         <is>
-          <t>June–November 2027</t>
+          <t>June 2027</t>
         </is>
       </c>
       <c r="D375" s="6" t="inlineStr">
         <is>
-          <t>Technology &amp; Digital / Data Analytics Intern; 84.51° Data Scientist Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern / Co-op; Production Engineering Intern; Data Scientist Intern, Product Analytics; Research Scientist Intern (PhD, AI/FAIR); ML / AI Software Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E375" s="7" t="inlineStr">
         <is>
-          <t>krogerfamilycareers.com/en/sites/CX_2001/pages/5015</t>
+          <t>metacareers.com/careerprograms/students/</t>
         </is>
       </c>
       <c r="F375" s="7" t="inlineStr">
@@ -21454,34 +21454,30 @@
       </c>
       <c r="G375" s="6" t="inlineStr">
         <is>
-          <t>Typically a HireVue one-way video interview, then a behavioral panel (STAR questions mapped to Kroger's core values), and a final leadership conversation. Technology and data roles add an assessment: Reddit reports a coding challenge (Swift) plus a "game" challenge. Corporate non-technical roles usu</t>
-        </is>
-      </c>
-      <c r="H375" s="6" t="inlineStr">
-        <is>
-          <t>No. JDs require work authorization that does not now or in the future require sponsorship, explicitly excluding H-1B, F-1/OPT, and TN. Kroger does not sponsor interns</t>
-        </is>
-      </c>
+          <t>A recruiter screen, a 45-minute CoderPad phone screen with about 2 LeetCode Easy-to-Medium problems, then a four-round loop of 2 coding, 1 design, and 1 behavioral round. A CodeSignal online assessment appears for many candidates, and Meta is rolling out an AI-assisted coding round in 2026.</t>
+        </is>
+      </c>
+      <c r="H375" s="6" t="inlineStr"/>
       <c r="I375" s="6" t="inlineStr">
         <is>
-          <t>Yes. Both Kroger corporate and 84.51° fill intern roles on a rolling basis and unpost them as they fill. Applying in September or October materially beats Decem</t>
+          <t>Yes. AI-research JDs state "various start dates throughout the year"; quotas fill by roughly December</t>
         </is>
       </c>
       <c r="J375" s="6" t="inlineStr">
         <is>
-          <t>No official intern pay published ("competitive pay"). Community and aggregator estimates: ~$14–$27/hr, with technical and 84.51° roles reportedly higher ($22–$4</t>
+          <t>$7,188 to $12,134/month official JD bands, plus housing assistance (~$2,600/mo commonly cited); SWE community figure ~$51.35/hr</t>
         </is>
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 is partly open. Kroger's own careers board showed six Summer 2027 intern reqs on September 27, 2026: supply chain Quality, Maintenance, Human Resources and Continuous Improvement in Denver (posted September 1, listed through November 30), Transportation in Nashville (posted September 23), and a Construction Project Engineer intern in Hutchinson, KS. Program dates are May 17 to August 6</t>
+          <t>Opening now, rolling: the first summer 2027 req (Data Engineer Intern, Product Analytics) went live on 29 September 2026; the Software Engineer intern req was not yet posted on 1 October 2026, and more summer 2027 reqs are expected through the fall (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21496,12 +21492,12 @@
       </c>
       <c r="D376" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern / Co-op; Production Engineering Intern; Data Scientist Intern, Product Analytics; Research Scientist Intern (PhD, AI/FAIR); ML / AI Software Engineer Intern  (5 of 6 tracks)</t>
+          <t>Software Engineer Intern; Machine Learning Engineer Intern; Machine Learning/AI Scientist Intern; Data Engineering Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E376" s="7" t="inlineStr">
         <is>
-          <t>metacareers.com/careerprograms/students/</t>
+          <t>jobs.netflix.com/careers/internships</t>
         </is>
       </c>
       <c r="F376" s="7" t="inlineStr">
@@ -21511,30 +21507,30 @@
       </c>
       <c r="G376" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, a 45-minute CoderPad phone screen with about 2 LeetCode Easy-to-Medium problems, then a four-round loop of 2 coding, 1 design, and 1 behavioral round. A CodeSignal online assessment appears for many candidates, and Meta is rolling out an AI-assisted coding round in 2026.</t>
+          <t>Officially, a take-home assessment followed by approximately two to three interview rounds. Candidates report the SWE take-home is a two-part CodeSignal assessment of roughly 90 minutes each, including an AI-assisted coding section, then live coding, system design, and a hiring-manager round.</t>
         </is>
       </c>
       <c r="H376" s="6" t="inlineStr"/>
       <c r="I376" s="6" t="inlineStr">
         <is>
-          <t>Yes. AI-research JDs state "various start dates throughout the year"; quotas fill by roughly December</t>
+          <t>Yes. Postings stay open "no less than 7 days" and come down when filled; specialist and PhD roles roll December into spring</t>
         </is>
       </c>
       <c r="J376" s="6" t="inlineStr">
         <is>
-          <t>$7,188 to $12,134/month official JD bands, plus housing assistance (~$2,600/mo commonly cited); SWE community figure ~$51.35/hr</t>
+          <t>$40 to $110/hr official JD ranges; SWE median $63/hr plus $10,000 housing (Levels.fyi, self-reported)</t>
         </is>
       </c>
       <c r="K376" s="6" t="inlineStr">
         <is>
-          <t>Opening now, rolling: the first summer 2027 req (Data Engineer Intern, Product Analytics) went live on 29 September 2026; the Software Engineer intern req was not yet posted on 1 October 2026, and more summer 2027 reqs are expected through the fall (projected from prior cycle)</t>
+          <t>Software Engineer Intern, Summer 2027 posted October 19, 2026; Netflix says it stays up through January 1, 2027, filled on a rolling basis. Other summer 2027 tracks not yet posted as of October 22, 2026; specialist roles usually roll to March. Last cycle the flagship SWE role opened ~Oct 1 and closed Oct 31, 2025</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21549,12 +21545,12 @@
       </c>
       <c r="D377" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Machine Learning Engineer Intern; Machine Learning/AI Scientist Intern; Data Engineering Intern  (4 of 6 tracks)</t>
+          <t>SWE Intern; OCI SWE Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E377" s="7" t="inlineStr">
         <is>
-          <t>jobs.netflix.com/careers/internships</t>
+          <t>oracle.com/careers/students-grads/internships/</t>
         </is>
       </c>
       <c r="F377" s="7" t="inlineStr">
@@ -21564,30 +21560,34 @@
       </c>
       <c r="G377" s="6" t="inlineStr">
         <is>
-          <t>Officially, a take-home assessment followed by approximately two to three interview rounds. Candidates report the SWE take-home is a two-part CodeSignal assessment of roughly 90 minutes each, including an AI-assisted coding section, then live coding, system design, and a hiring-manager round.</t>
-        </is>
-      </c>
-      <c r="H377" s="6" t="inlineStr"/>
+          <t>You apply, then a recruiter phone-screens you for 20 to 30 minutes. Next come two technical interviews of 45 to 60 minutes each covering data structures, algorithms, SQL, OOP, and a resume deep-dive. A behavioral round follows. For OCI or Labs roles, expect a 3-to-4-hour Super Day with multiple back</t>
+        </is>
+      </c>
+      <c r="H377" s="6" t="inlineStr">
+        <is>
+          <t>Oracle ranks in the top 15 U.S. H-1B sponsors . CPT and OPT accepted. Some government-facing roles require U.S. citizenship</t>
+        </is>
+      </c>
       <c r="I377" s="6" t="inlineStr">
         <is>
-          <t>Yes. Postings stay open "no less than 7 days" and come down when filled; specialist and PhD roles roll December into spring</t>
+          <t>Yes, rolling. Early applicants get faster screening and wider team-placement options. Competition intensifies and available roles narrow after October</t>
         </is>
       </c>
       <c r="J377" s="6" t="inlineStr">
         <is>
-          <t>$40 to $110/hr official JD ranges; SWE median $63/hr plus $10,000 housing (Levels.fyi, self-reported)</t>
+          <t>Standard SWE Austin ~$41/hr (~$7,100/mo). OCI roles $53 to $55/hr. AI/ML premium roles $55 to $65/hr. Housing stipend $2,166 to $8,000/mo depending on location</t>
         </is>
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, Summer 2027 posted October 19, 2026; Netflix says it stays up through January 1, 2027, filled on a rolling basis. Other summer 2027 tracks not yet posted as of October 22, 2026; specialist roles usually roll to March. Last cycle the flagship SWE role opened ~Oct 1 and closed Oct 31, 2025</t>
+          <t>Partly open: Sales Development Rep Intern (Summer 2027) live in Austin, Nashville, Burlington, Denver and Santa Monica since September 18, 2026, plus a Nashville Financial Analyst Intern; software engineering roles not posted as of September 28, 2026. Roles stay open rolling but narrow fast</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21602,12 +21602,12 @@
       </c>
       <c r="D378" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern; OCI SWE Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering; Data / Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E378" s="7" t="inlineStr">
         <is>
-          <t>oracle.com/careers/students-grads/internships/</t>
+          <t>careers.paramount.com/go/Interns/8710100/</t>
         </is>
       </c>
       <c r="F378" s="7" t="inlineStr">
@@ -21617,34 +21617,30 @@
       </c>
       <c r="G378" s="6" t="inlineStr">
         <is>
-          <t>You apply, then a recruiter phone-screens you for 20 to 30 minutes. Next come two technical interviews of 45 to 60 minutes each covering data structures, algorithms, SQL, OOP, and a resume deep-dive. A behavioral round follows. For OCI or Labs roles, expect a 3-to-4-hour Super Day with multiple back</t>
-        </is>
-      </c>
-      <c r="H378" s="6" t="inlineStr">
-        <is>
-          <t>Oracle ranks in the top 15 U.S. H-1B sponsors . CPT and OPT accepted. Some government-facing roles require U.S. citizenship</t>
-        </is>
-      </c>
+          <t>Most roles follow a two-round process. Round one is a recruiter phone screen lasting 15-30 minutes covering your background, interest in entertainment, and availability. Round two is a Zoom interview with the hiring team, often including behavioral questions like "What media do you consume?" and "Wh</t>
+        </is>
+      </c>
+      <c r="H378" s="6" t="inlineStr"/>
       <c r="I378" s="6" t="inlineStr">
         <is>
-          <t>Yes, rolling. Early applicants get faster screening and wider team-placement options. Competition intensifies and available roles narrow after October</t>
+          <t>Effectively yes. Positions fill as qualified candidates apply; no individual status feedback provided</t>
         </is>
       </c>
       <c r="J378" s="6" t="inlineStr">
         <is>
-          <t>Standard SWE Austin ~$41/hr (~$7,100/mo). OCI roles $53 to $55/hr. AI/ML premium roles $55 to $65/hr. Housing stipend $2,166 to $8,000/mo depending on location</t>
+          <t>$23/hr median (Glassdoor, 266 reports); $19-$23/hr business roles, $34-$45/hr engineering roles</t>
         </is>
       </c>
       <c r="K378" s="6" t="inlineStr">
         <is>
-          <t>Partly open: Sales Development Rep Intern (Summer 2027) live in Austin, Nashville, Burlington, Denver and Santa Monica since September 18, 2026, plus a Nashville Financial Analyst Intern; software engineering roles not posted as of September 28, 2026. Roles stay open rolling but narrow fast</t>
+          <t>Not published on Paramount's own pages; watch careers.paramount.com Interns for summer 2027 postings</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21654,17 +21650,17 @@
       </c>
       <c r="C379" s="5" t="inlineStr">
         <is>
-          <t>June 2027</t>
+          <t>June–August 2027</t>
         </is>
       </c>
       <c r="D379" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data / Analytics  (2 of 6 tracks)</t>
+          <t>Quantitative Trader Intern; Quantitative Systematic Trading Intern (MS/PhD); Software Engineering Intern; Quantitative Strategy Developer Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E379" s="7" t="inlineStr">
         <is>
-          <t>careers.paramount.com/go/Interns/8710100/</t>
+          <t>careers.sig.com/intern-openings/</t>
         </is>
       </c>
       <c r="F379" s="7" t="inlineStr">
@@ -21674,30 +21670,34 @@
       </c>
       <c r="G379" s="6" t="inlineStr">
         <is>
-          <t>Most roles follow a two-round process. Round one is a recruiter phone screen lasting 15-30 minutes covering your background, interest in entertainment, and availability. Round two is a Zoom interview with the hiring team, often including behavioral questions like "What media do you consume?" and "Wh</t>
-        </is>
-      </c>
-      <c r="H379" s="6" t="inlineStr"/>
+          <t>Four stages: a 20-minute online quantitative assessment (logic puzzles and brain teasers on Mettl), a phone screen (behavioral plus probability), a 60-minute technical video interview (probability math with a senior trader), and a final interview (about 90 minutes, technical plus fit, according to c</t>
+        </is>
+      </c>
+      <c r="H379" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly stated. US offices (Bala Cynwyd, NYC, Chicago) likely support CPT/OPT. Dublin and London offices serve international applicants</t>
+        </is>
+      </c>
       <c r="I379" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Positions fill as qualified candidates apply; no individual status feedback provided</t>
+          <t>Partially. SIG accepts applications on a rolling basis but recruits in a concentrated late-summer window. Applying early improves your chances</t>
         </is>
       </c>
       <c r="J379" s="6" t="inlineStr">
         <is>
-          <t>$23/hr median (Glassdoor, 266 reports); $19-$23/hr business roles, $34-$45/hr engineering roles</t>
+          <t>QT intern (Master’s/PhD): ~$8,600/week + free housing + meals. QT intern (undergrad): ~$150/hr. SWE intern: ~$69/hr + $10k sign-on. All tracks get housing, meal</t>
         </is>
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>Not published on Paramount's own pages; watch careers.paramount.com Interns for summer 2027 postings</t>
+          <t>Expected June to August 2027, based on the 2026–27 cycle when Summer 2027 roles posted June to July 2026. Projected, not yet confirmed</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21707,17 +21707,17 @@
       </c>
       <c r="C380" s="5" t="inlineStr">
         <is>
-          <t>June–August 2027</t>
+          <t>June–October 2027</t>
         </is>
       </c>
       <c r="D380" s="6" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern; Quantitative Systematic Trading Intern (MS/PhD); Software Engineering Intern; Quantitative Strategy Developer Intern  (4 of 6 tracks)</t>
+          <t>Software Engineering; Data / Analytics; Cybersecurity  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E380" s="7" t="inlineStr">
         <is>
-          <t>careers.sig.com/intern-openings/</t>
+          <t>careers.t-mobile.com/internship</t>
         </is>
       </c>
       <c r="F380" s="7" t="inlineStr">
@@ -21727,27 +21727,27 @@
       </c>
       <c r="G380" s="6" t="inlineStr">
         <is>
-          <t>Four stages: a 20-minute online quantitative assessment (logic puzzles and brain teasers on Mettl), a phone screen (behavioral plus probability), a 60-minute technical video interview (probability math with a senior trader), and a final interview (about 90 minutes, technical plus fit, according to c</t>
+          <t>Typically a recruiter phone screen, then a behavioral or hiring-manager round (sometimes a group interview), with an online assessment added for some technology roles. After interviews, candidates often fill out a form to rank project teams. Glassdoor rates interview difficulty a moderate 2.7/5, and</t>
         </is>
       </c>
       <c r="H380" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly stated. US offices (Bala Cynwyd, NYC, Chicago) likely support CPT/OPT. Dublin and London offices serve international applicants</t>
+          <t>The Summer 2027 postings (October 15 to 27, 2026) printed no sponsorship sentence; the SWE postings require authorization to work in the US now and in the future. Prior-cycle JDs said T-Mobile does not sponsor work visas</t>
         </is>
       </c>
       <c r="I380" s="6" t="inlineStr">
         <is>
-          <t>Partially. SIG accepts applications on a rolling basis but recruits in a concentrated late-summer window. Applying early improves your chances</t>
+          <t>Yes, effectively. Roles are posted on a 1:1 basis and close once the position is filled, so apply the week a req opens</t>
         </is>
       </c>
       <c r="J380" s="6" t="inlineStr">
         <is>
-          <t>QT intern (Master’s/PhD): ~$8,600/week + free housing + meals. QT intern (undergrad): ~$150/hr. SWE intern: ~$69/hr + $10k sign-on. All tracks get housing, meal</t>
+          <t>Summer 2027 postings (October 15 to 27, 2026): $27 to $50/hr for Software Engineering and Cloud Security, $26–$47/hr for Human Resources &amp; Workplace Experience.</t>
         </is>
       </c>
       <c r="K380" s="6" t="inlineStr">
         <is>
-          <t>Expected June to August 2027, based on the 2026–27 cycle when Summer 2027 roles posted June to July 2026. Projected, not yet confirmed</t>
+          <t>First Summer 2027 wave closed: Software Engineering Intern (Bellevue, ended October 23), Human Resources &amp; Workplace Experience (ended October 26) and Software Engineer, Cloud Security (Atlanta and Frisco, ended October 27, 2026). No Summer 2027 reqs were live on T-Mobile's Workday on October 27, 2026. Other tracks (Finance, Cybersecurity and more) not yet posted; last cycle they closed in April</t>
         </is>
       </c>
     </row>
@@ -32001,7 +32001,7 @@
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
         <is>
-          <t>T-Mobile</t>
+          <t>xAI</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
@@ -32023,7 +32023,7 @@
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
         <is>
-          <t>xAI</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
@@ -32045,7 +32045,7 @@
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Qatalyst Partners</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
@@ -32067,7 +32067,7 @@
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
         <is>
-          <t>Qatalyst Partners</t>
+          <t>Decagon</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
@@ -32089,7 +32089,7 @@
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
         <is>
-          <t>Decagon</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
@@ -32111,12 +32111,12 @@
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
-        </is>
-      </c>
-      <c r="B321" s="4" t="inlineStr">
-        <is>
-          <t>Window open - check now</t>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="B321" s="8" t="inlineStr">
+        <is>
+          <t>Opening soon</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -32133,7 +32133,7 @@
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Google DeepMind</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
@@ -32155,7 +32155,7 @@
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
         <is>
-          <t>Google DeepMind</t>
+          <t>Gusto</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -32177,7 +32177,7 @@
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
         <is>
-          <t>Gusto</t>
+          <t>Hugging Face</t>
         </is>
       </c>
       <c r="B324" s="8" t="inlineStr">
@@ -32199,7 +32199,7 @@
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
         <is>
-          <t>Hugging Face</t>
+          <t>Jefferies</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -32221,7 +32221,7 @@
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
         <is>
-          <t>Jefferies</t>
+          <t>Kaiser Permanente</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
@@ -32243,7 +32243,7 @@
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Magna</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -32265,7 +32265,7 @@
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
         <is>
-          <t>Magna</t>
+          <t>Marqeta</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
@@ -32287,7 +32287,7 @@
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
         <is>
-          <t>Marqeta</t>
+          <t>Ogilvy</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -32309,7 +32309,7 @@
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
         <is>
-          <t>Ogilvy</t>
+          <t>Oura</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
@@ -32331,7 +32331,7 @@
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
         <is>
-          <t>Oura</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -32353,7 +32353,7 @@
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Analysis Group</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
@@ -32375,7 +32375,7 @@
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
         <is>
-          <t>Analysis Group</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -32397,7 +32397,7 @@
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
@@ -32419,7 +32419,7 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deutsche Bank</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -32441,7 +32441,7 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>Deutsche Bank</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B336" s="8" t="inlineStr">
@@ -32463,7 +32463,7 @@
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Volkswagen</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -32485,12 +32485,12 @@
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
-        </is>
-      </c>
-      <c r="B338" s="8" t="inlineStr">
-        <is>
-          <t>Opening soon</t>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="B338" s="9" t="inlineStr">
+        <is>
+          <t>Later this cycle</t>
         </is>
       </c>
       <c r="C338" s="7" t="inlineStr">
@@ -32507,7 +32507,7 @@
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>AppLovin</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -32529,7 +32529,7 @@
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>BCG</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -32551,7 +32551,7 @@
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
         <is>
-          <t>BCG</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -32573,7 +32573,7 @@
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>Cerebras</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -32595,7 +32595,7 @@
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
         <is>
-          <t>Cerebras</t>
+          <t>Edelman</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -32617,7 +32617,7 @@
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
         <is>
-          <t>Edelman</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -32639,7 +32639,7 @@
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>GSK</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -32661,7 +32661,7 @@
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
         <is>
-          <t>GSK</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -32683,7 +32683,7 @@
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan</t>
+          <t>KKR</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -32705,7 +32705,7 @@
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
         <is>
-          <t>KKR</t>
+          <t>Miro</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -32727,7 +32727,7 @@
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
         <is>
-          <t>Miro</t>
+          <t>Mistral AI</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -32749,7 +32749,7 @@
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
         <is>
-          <t>Mistral AI</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -32771,7 +32771,7 @@
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -32793,7 +32793,7 @@
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -32815,7 +32815,7 @@
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Skild AI</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -32837,7 +32837,7 @@
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
         <is>
-          <t>Skild AI</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -32859,7 +32859,7 @@
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -32881,7 +32881,7 @@
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>AI21 Labs</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -32903,7 +32903,7 @@
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
         <is>
-          <t>AI21 Labs</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -32925,7 +32925,7 @@
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Braze</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -32947,7 +32947,7 @@
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -32969,7 +32969,7 @@
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Millennium</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -32991,7 +32991,7 @@
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
         <is>
-          <t>Millennium</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -33013,7 +33013,7 @@
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
         <is>
-          <t>Sony</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -33035,7 +33035,7 @@
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Aptiv</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -33057,7 +33057,7 @@
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
         <is>
-          <t>Aptiv</t>
+          <t>Ferrari</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -33079,7 +33079,7 @@
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>Ferrari</t>
+          <t>Warner Music Group</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -33101,7 +33101,7 @@
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
         <is>
-          <t>Warner Music Group</t>
+          <t>Canva</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -33123,7 +33123,7 @@
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
         <is>
-          <t>Canva</t>
+          <t>AQR Capital</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -33145,7 +33145,7 @@
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
         <is>
-          <t>AQR Capital</t>
+          <t>Atlassian</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -33167,7 +33167,7 @@
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
         <is>
-          <t>Atlassian</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -33189,7 +33189,7 @@
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -33211,7 +33211,7 @@
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>General Electric</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -33233,7 +33233,7 @@
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
         <is>
-          <t>General Electric</t>
+          <t>Hershey</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -33255,7 +33255,7 @@
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
         <is>
-          <t>Hershey</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -33277,7 +33277,7 @@
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -33299,7 +33299,7 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -33321,7 +33321,7 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -33343,7 +33343,7 @@
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -33365,7 +33365,7 @@
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -33387,7 +33387,7 @@
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>SIG</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -33409,7 +33409,7 @@
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
         <is>
-          <t>SIG</t>
+          <t>T-Mobile</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -38705,7 +38705,7 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>🔥 CLOSING SOON]</t>
+          <t>✅ OPEN]</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-28 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-29 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -38341,7 +38341,7 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>✅ OPEN]</t>
+          <t>🔥 CLOSING SOON]</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">

--- a/InternWatch.xlsx
+++ b/InternWatch.xlsx
@@ -508,7 +508,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-29 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
+          <t>Intern Watch - Summer 2027 tech internship calendar - regenerated 2026-10-30 from extern.com company guides. Dates are Extern's projections from prior cycles, not confirmed postings. Sorted by how soon each window opens.</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>OPEN for summer 2027 on the Software Engineer track: Software Engineer Intern posted Aug 31, 2026 (San Francisco, Palo Alto, New York, Seattle, Bellevue, Burlington, Atlanta, Indianapolis), no end date printed, still live Oct 25, 2026. Also live Oct 25: Software Engineer (Security/Government), San Francisco and Bellevue (posted Oct 19); AI Research, Palo Alto (posted Oct 20); Solution Engineer, Ne</t>
+          <t>OPEN for summer 2027 on the Software Engineer track: Software Engineer Intern posted Aug 31, 2026 (San Francisco, Palo Alto, New York, Seattle, Bellevue, Burlington, Atlanta, Indianapolis), no end date printed, still live Oct 30, 2026. Also live Oct 30: Software Engineer (Security/Government), San Francisco and Bellevue (posted Oct 19); AI Research, Palo Alto (posted Oct 20); Tableau Research, Pal</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>Not yet posted. Summer 2027 developer-intern roles are expected to open ~Fall 2026 through Winter 2026–27, projected from prior cycles (Summer 2026 roles were posted in late 2025). All 2027 dates are expected, not official</t>
+          <t xml:space="preserve">Summer 2027 not yet posted. The winter 2027 cohort is open: on October 30, 2026 the Ashby board listed 11 Winter 2027 intern roles (January to April 2027), posted October 22 and 23, 2026, each Remote (United States | Canada), no deadline printed. Summer 2027 developer-intern roles are expected to open ~Fall 2026 through Winter 2026–27, projected from prior cycles (Summer 2026 roles were posted in </t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Discord</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
@@ -12193,17 +12193,17 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>Risk &amp; Financial Advisory Intern (incl. Cyber)  (1 of 6 tracks)</t>
+          <t>SWE Intern - Perks; SWE Intern - Data Products; SWE Intern - Native Framework &amp; Tools; SWE Intern - Platform Ecosystems; ML Platform Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>apply.deloitte.com/careers/SearchJobs</t>
+          <t>discord.com/careers</t>
         </is>
       </c>
       <c r="F210" s="7" t="inlineStr">
@@ -12211,28 +12211,36 @@
           <t>guide</t>
         </is>
       </c>
-      <c r="G210" s="6" t="inlineStr"/>
-      <c r="H210" s="6" t="inlineStr"/>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>Recruiter screen (about 30 minutes), then a 1-hour coding interview with a practical, real-world problem. You can use Google, Stack Overflow, and documentation. No automated OA. Interns likely face 2 to 3 rounds total, completed in roughly 2 to 4 weeks.</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>Discord sponsors O-1, TN, E-3, H-1B1, H-1B and Green Card for full-time employees. Intern-specific visa sponsorship is not explicitly stated; confirm per role</t>
+        </is>
+      </c>
       <c r="I210" s="6" t="inlineStr">
         <is>
-          <t>Stated end dates, and they can move. Each posting states the day recruiting ends (Oct 25, 2026 on the Financial Statement Audit and summer 2028 tax postings). T</t>
+          <t>Likely yes. No hard deadline language in any JD; postings stay open until filled. Discord states they respond within two weeks of applying</t>
         </is>
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>$23.22–$59.50/hr spans every wage range and flat rate printed on the audit, tax and Summer Scholar intern postings listed Oct 11, 2026, before geographic adjust</t>
+          <t>SWE intern (Bachelor's) $63/hr (~$10,920/mo); Master's $73/hr; PhD $83/hr. Creative intern $59/hr. Housing and transportation benefits included</t>
         </is>
       </c>
       <c r="K210" s="6" t="inlineStr">
         <is>
-          <t>Partly open: Financial Statement Audit intern postings for summer 2027 and summer 2028 and the summer 2028 tax posting all state Oct 25, 2026 as the last day of recruiting. The Financial Statement Audit postings were extended from Oct 11 to Oct 25; the six other summer 2027 audit postings that stated Oct 11 are no longer listed. The Japanese Services Group summer 2027 audit role runs to Nov 29, 20</t>
+          <t>Expected October to December 2026 for summer 2027. Projected from the past two cycles (Nov 2023 for Summer 2024, late 2024 for Summer 2025); not yet posted</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
@@ -12242,17 +12250,17 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern - Perks; SWE Intern - Data Products; SWE Intern - Native Framework &amp; Tools; SWE Intern - Platform Ecosystems; ML Platform Intern  (5 of 6 tracks)</t>
+          <t>Disney Technology SWE; Disney Data Science  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>discord.com/careers</t>
+          <t>disneycareers.com/en/internships-united-states</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
@@ -12262,34 +12270,34 @@
       </c>
       <c r="G211" s="6" t="inlineStr">
         <is>
-          <t>Recruiter screen (about 30 minutes), then a 1-hour coding interview with a practical, real-world problem. You can use Google, Stack Overflow, and documentation. No automated OA. Interns likely face 2 to 3 rounds total, completed in roughly 2 to 4 weeks.</t>
+          <t>Three rounds for SWE roles: a recruiter screen, a 45–75-minute HackerRank assessment with 2–3 LeetCode-medium problems, and a virtual onsite covering system design plus behavioral questions. Disney interviewers prioritize communication over raw code, so discuss your approach before writing.</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
         <is>
-          <t>Discord sponsors O-1, TN, E-3, H-1B1, H-1B and Green Card for full-time employees. Intern-specific visa sponsorship is not explicitly stated; confirm per role</t>
+          <t>Disney requires unrestricted US work authorization. International students on F-1 visas can qualify by obtaining CPT from their school for the internship’s duration. OPT also works. Disney does not directly sponsor inter</t>
         </is>
       </c>
       <c r="I211" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No hard deadline language in any JD; postings stay open until filled. Discord states they respond within two weeks of applying</t>
+          <t>Semi-rolling within seasonal windows. Postings close in days when applicant volume is high. Apply immediately.</t>
         </is>
       </c>
       <c r="J211" s="6" t="inlineStr">
         <is>
-          <t>SWE intern (Bachelor's) $63/hr (~$10,920/mo); Master's $73/hr; PhD $83/hr. Creative intern $59/hr. Housing and transportation benefits included</t>
+          <t>$22.50/hr (non-tech) to $47/hr (grad Data Science); SWE $42/hr</t>
         </is>
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027. Projected from the past two cycles (Nov 2023 for Summer 2024, late 2024 for Summer 2025); not yet posted</t>
+          <t>Spring 2027 cohort open now: 49 reqs live 6 Oct 2026, most closing 1 to 2 weeks after posting. Summer 2027: Accounting &amp; Finance Rotation Program closed Oct 5, 2026; 3 park industrial engineering reqs live (one Disneyland, two Walt Disney World); main tech wave still expected this fall, not yet posted on 6 Oct 2026, non-tech December 2026–January 2027 (projected)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
@@ -12304,12 +12312,12 @@
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>Disney Technology SWE; Disney Data Science  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern (Agreement Desk); AI Platform Software Engineer Intern; Applied Science Intern (ML/NLP); Product Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>disneycareers.com/en/internships-united-states</t>
+          <t>careers.docusign.com/students</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
@@ -12319,34 +12327,34 @@
       </c>
       <c r="G212" s="6" t="inlineStr">
         <is>
-          <t>Three rounds for SWE roles: a recruiter screen, a 45–75-minute HackerRank assessment with 2–3 LeetCode-medium problems, and a virtual onsite covering system design plus behavioral questions. Disney interviewers prioritize communication over raw code, so discuss your approach before writing.</t>
+          <t>Typically 3 to 4 stages: recruiter phone screen (30 min), HackerRank online assessment (2 to 3 coding problems, Easy to Medium), technical interview (45 to 60 min coding), and hiring manager/behavioral round. Average time from application to offer: about 26 days.</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
         <is>
-          <t>Disney requires unrestricted US work authorization. International students on F-1 visas can qualify by obtaining CPT from their school for the internship’s duration. OPT also works. Disney does not directly sponsor inter</t>
+          <t>No. DocuSign explicitly states intern positions are not eligible for CPT, OPT, or sponsorship. US work authorization required</t>
         </is>
       </c>
       <c r="I212" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling within seasonal windows. Postings close in days when applicant volume is high. Apply immediately.</t>
+          <t>Yes, implicitly. DocuSign opens applications during specific windows and fills positions rolling until headcount is met</t>
         </is>
       </c>
       <c r="J212" s="6" t="inlineStr">
         <is>
-          <t>$22.50/hr (non-tech) to $47/hr (grad Data Science); SWE $42/hr</t>
+          <t>SWE San Francisco ~$47/hr ($8,147/month). Range across roles: $31 to $51/hr depending on track and location. Summer 2027 Seattle SWE postings: $34 to $45/hr</t>
         </is>
       </c>
       <c r="K212" s="6" t="inlineStr">
         <is>
-          <t>Spring 2027 cohort open now: 49 reqs live 6 Oct 2026, most closing 1 to 2 weeks after posting. Summer 2027: Accounting &amp; Finance Rotation Program closed Oct 5, 2026; 3 park industrial engineering reqs live (one Disneyland, two Walt Disney World); main tech wave still expected this fall, not yet posted on 6 Oct 2026, non-tech December 2026–January 2027 (projected)</t>
+          <t>Opening now for summer 2027: Software Engineering Intern roles in Seattle posted October 2 and October 5, 2026. More engineering and tech roles expected through the fall; rolling through Jan to Feb 2027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
@@ -12361,12 +12369,12 @@
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern (Agreement Desk); AI Platform Software Engineer Intern; Applied Science Intern (ML/NLP); Product Data Science Intern  (4 of 6 tracks)</t>
+          <t>Engineering Intern &amp; Co-op  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>careers.docusign.com/students</t>
+          <t>dukeenergy.wd1.myworkdayjobs.com/en-US/Search</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
@@ -12376,34 +12384,30 @@
       </c>
       <c r="G213" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 stages: recruiter phone screen (30 min), HackerRank online assessment (2 to 3 coding problems, Easy to Medium), technical interview (45 to 60 min coding), and hiring manager/behavioral round. Average time from application to offer: about 26 days.</t>
-        </is>
-      </c>
-      <c r="H213" s="6" t="inlineStr">
-        <is>
-          <t>No. DocuSign explicitly states intern positions are not eligible for CPT, OPT, or sponsorship. US work authorization required</t>
-        </is>
-      </c>
+          <t>Expect 2–3 rounds: a phone screen with a recruiter, a panel interview with 2–4 interviewers using STAR-method behavioral questions, and an optional follow-up. The process takes an average of 54 days from application to offer. Glassdoor rates difficulty at 3.1 out of 5 (medium).</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr"/>
       <c r="I213" s="6" t="inlineStr">
         <is>
-          <t>Yes, implicitly. DocuSign opens applications during specific windows and fills positions rolling until headcount is met</t>
+          <t>No. Each function has its own posting and end date; on October 30, 2026 the last undergraduate summer 2027 apply-by date was that day (Waste &amp; Groundwater, Nucl</t>
         </is>
       </c>
       <c r="J213" s="6" t="inlineStr">
         <is>
-          <t>SWE San Francisco ~$47/hr ($8,147/month). Range across roles: $31 to $51/hr depending on track and location. Summer 2027 Seattle SWE postings: $34 to $45/hr</t>
+          <t>The summer 2027 postings print no pay (checked October 30, 2026); reported pay runs $21 to $36/hr depending on role; housing stipend available for interns place</t>
         </is>
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>Opening now for summer 2027: Software Engineering Intern roles in Seattle posted October 2 and October 5, 2026. More engineering and tech roles expected through the fall; rolling through Jan to Feb 2027</t>
+          <t>Partly open for summer 2027: on October 30, 2026 the Engineering Internship &amp; Co-op Program posting was still listed and accepting applications; its text prints October 16, but its Workday end date is now November 7, 2026. Waste &amp; Groundwater Programs Engineering and Nuclear Cybersecurity (Hartsville, SC) list October 30 as the last day to apply (11:59 PM); MBA Internship November 13, 2026. Passed</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
@@ -12418,12 +12422,12 @@
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern &amp; Co-op  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Data Science Intern; Machine Learning / PhD Intern; Security Engineering Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>dukeenergy.wd1.myworkdayjobs.com/en-US/Search</t>
+          <t>jobs.ebayinc.com/us/en/emerging-talent</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
@@ -12433,30 +12437,34 @@
       </c>
       <c r="G214" s="6" t="inlineStr">
         <is>
-          <t>Expect 2–3 rounds: a phone screen with a recruiter, a panel interview with 2–4 interviewers using STAR-method behavioral questions, and an optional follow-up. The process takes an average of 54 days from application to offer. Glassdoor rates difficulty at 3.1 out of 5 (medium).</t>
-        </is>
-      </c>
-      <c r="H214" s="6" t="inlineStr"/>
+          <t>eBay's RippleMatch page, read October 22, 2026, lists a CodeSignal challenge followed by two 45-minute interviews for SWE interns. Past interns described a longer 2026 loop: recruiter screen, a 90-minute HackerRank OA, a Karat interview, then a team virtual onsite with 4 sessions. Decisions come wit</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>CPT supported for F-1 students, OPT and STEM OPT extension available, H-1B sponsorship for full-time conversion. Be transparent about status in the recruiter screen</t>
+        </is>
+      </c>
       <c r="I214" s="6" t="inlineStr">
         <is>
-          <t>No. Each function has its own posting and end date; on October 21, 2026 the undergraduate summer 2027 apply-by dates still ahead were October 29 (Substation / L</t>
+          <t>Yes. eBay reviews applications on a rolling basis. Community data shows applicants who submit within the first four weeks after postings open see 30 to 40% high</t>
         </is>
       </c>
       <c r="J214" s="6" t="inlineStr">
         <is>
-          <t>The summer 2027 postings print no pay (checked October 21, 2026); reported pay runs $21 to $36/hr depending on role; housing stipend available for interns place</t>
+          <t>Financial Analyst Intern 2027 posting (San Jose, live October 22, 2026): $30 to $37/hr in California. Past SWE interns report $50 to $68/hr ($8,500 to $11,500/m</t>
         </is>
       </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>Partly open for summer 2027: on October 21, 2026 the Engineering Internship &amp; Co-op Program posting was still listed and accepting applications after the October 16 date it prints. Apply-by dates still ahead: Substation / Line Tech in the Carolinas October 29, Waste &amp; Groundwater Programs Engineering and Nuclear Cybersecurity (Hartsville, SC) October 30, MBA Internship November 13, 2026. Passed an</t>
+          <t>Open for finance: Financial Analyst Intern 2027 (San Jose) live on RippleMatch as of October 22, 2026. SWE, data science and PM postings not yet visible. Internship applications close mid-April 2027, per eBay's RippleMatch page</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
@@ -12466,17 +12474,17 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Data Science Intern; Machine Learning / PhD Intern; Security Engineering Intern  (4 of 6 tracks)</t>
+          <t>Technology (IT / SDE); Data &amp; Analytics; Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>jobs.ebayinc.com/us/en/emerging-talent</t>
+          <t>careers.lilly.com/us/en/internships</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
@@ -12486,34 +12494,34 @@
       </c>
       <c r="G215" s="6" t="inlineStr">
         <is>
-          <t>eBay's RippleMatch page, read October 22, 2026, lists a CodeSignal challenge followed by two 45-minute interviews for SWE interns. Past interns described a longer 2026 loop: recruiter screen, a 90-minute HackerRank OA, a Karat interview, then a team virtual onsite with 4 sessions. Decisions come wit</t>
+          <t>After applying, most candidates go through a phone screen (20–30 minutes), then 2–4 virtual interviews via Microsoft Teams covering behavioral and technical questions. Some tracks include a Super Day in Indianapolis with 4–5 back-to-back interviews. Lilly uses the STAR method and evaluates against i</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students, OPT and STEM OPT extension available, H-1B sponsorship for full-time conversion. Be transparent about status in the recruiter screen</t>
+          <t>Lilly's official policy states it "will consider temporary visa and green card sponsorship for all eligible candidates and positions" on a case-by-case basis. Some business and marketing roles require unrestricted work a</t>
         </is>
       </c>
       <c r="I215" s="6" t="inlineStr">
         <is>
-          <t>Yes. eBay reviews applications on a rolling basis. Community data shows applicants who submit within the first four weeks after postings open see 30 to 40% high</t>
+          <t>Effectively yes. 60–70% of prime interview slots go to candidates who apply within the first 45 days</t>
         </is>
       </c>
       <c r="J215" s="6" t="inlineStr">
         <is>
-          <t>Financial Analyst Intern 2027 posting (San Jose, live October 22, 2026): $30 to $37/hr in California. Past SWE interns report $50 to $68/hr ($8,500 to $11,500/m</t>
+          <t>$25–$38/hr undergrad; ~$31/hr SWE (Levels.fyi); $35–$45/hr Master's; $45–$55/hr PhD</t>
         </is>
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>Open for finance: Financial Analyst Intern 2027 (San Jose) live on RippleMatch as of October 22, 2026. SWE, data science and PM postings not yet visible. Internship applications close mid-April 2027, per eBay's RippleMatch page</t>
+          <t>Open now for summer 2027: 27 US intern postings were live on Lilly's careers site on October 1, 2026, posted from late August to mid-September (rolling; the research undergraduate listing runs to December 1, 2026)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Etsy</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -12528,12 +12536,12 @@
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>Technology (IT / SDE); Data &amp; Analytics; Engineering  (3 of 6 tracks)</t>
+          <t>Software Engineering; Data Science / ML (periodic)  (2 of 3 tracks)</t>
         </is>
       </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>careers.lilly.com/us/en/internships</t>
+          <t>etsy.wd5.myworkdayjobs.com/Etsy_Careers</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
@@ -12543,34 +12551,30 @@
       </c>
       <c r="G216" s="6" t="inlineStr">
         <is>
-          <t>After applying, most candidates go through a phone screen (20–30 minutes), then 2–4 virtual interviews via Microsoft Teams covering behavioral and technical questions. Some tracks include a Super Day in Indianapolis with 4–5 back-to-back interviews. Lilly uses the STAR method and evaluates against i</t>
-        </is>
-      </c>
-      <c r="H216" s="6" t="inlineStr">
-        <is>
-          <t>Lilly's official policy states it "will consider temporary visa and green card sponsorship for all eligible candidates and positions" on a case-by-case basis. Some business and marketing roles require unrestricted work a</t>
-        </is>
-      </c>
+          <t>After applying, expect a recruiter phone screen followed by a HackerRank coding assessment (debugging or algorithm problems, 60 to 90 minutes). Finalists advance to a virtual onsite with two rounds: a live technical interview with screen-sharing and a behavioral interview with an engineering manager</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr"/>
       <c r="I216" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. 60–70% of prime interview slots go to candidates who apply within the first 45 days</t>
+          <t>Yes, effectively. The 2026 posting was open roughly 2 months (September–November), and the most competitive candidates applied within the first 4 weeks</t>
         </is>
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>$25–$38/hr undergrad; ~$31/hr SWE (Levels.fyi); $35–$45/hr Master's; $45–$55/hr PhD</t>
+          <t>Estimated $50–$65/hr (~$8,000–$10,400/month) for SWE interns; housing/relocation stipend reportedly $3,000–$5,000</t>
         </is>
       </c>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 27 US intern postings were live on Lilly's careers site on October 1, 2026, posted from late August to mid-September (rolling; the research undergraduate listing runs to December 1, 2026)</t>
+          <t>Not listed on October 11, 2026: no US internship posting was on Etsy's Workday careers portal that day. The August–September 2026 estimate for summer 2027 came from the prior cycle (posted September 2025). Summer 2028: August–September 2027 on the same pattern (estimate)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>Etsy</t>
+          <t>Expedia</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -12580,17 +12584,17 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D217" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Science / ML (periodic)  (2 of 3 tracks)</t>
+          <t>Software Development Engineering; Cloud Engineering; Data Science &amp; Analytics; Machine Learning Science  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>etsy.wd5.myworkdayjobs.com/Etsy_Careers</t>
+          <t>careers.expediagroup.com/emerging-talent-and-careers/</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
@@ -12600,30 +12604,30 @@
       </c>
       <c r="G217" s="6" t="inlineStr">
         <is>
-          <t>After applying, expect a recruiter phone screen followed by a HackerRank coding assessment (debugging or algorithm problems, 60 to 90 minutes). Finalists advance to a virtual onsite with two rounds: a live technical interview with screen-sharing and a behavioral interview with an engineering manager</t>
+          <t xml:space="preserve">The process spans 4–8 weeks with 4–5 stages: a recruiter screen, a strength-based behavioral assessment, a HackerRank online assessment with 2 coding problems and MCQs, and then 2 back-to-back 60-minute technical interviews with LeetCode-style questions. Difficulty is Easy to Medium, notably easier </t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr"/>
       <c r="I217" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively. The 2026 posting was open roughly 2 months (September–November), and the most competitive candidates applied within the first 4 weeks</t>
+          <t>Yes. Each 2027 posting says it stays live at least 5 business days and is removed once application targets are met; in earlier cycles most interview slots repor</t>
         </is>
       </c>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>Estimated $50–$65/hr (~$8,000–$10,400/month) for SWE interns; housing/relocation stipend reportedly $3,000–$5,000</t>
+          <t xml:space="preserve">Per the 2027 postings (October 15, 2026): Software Development and Mobile Engineering $45/hr with a bachelor's or $51/hr with a master's in Seattle and Austin, </t>
         </is>
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>Not listed on October 11, 2026: no US internship posting was on Etsy's Workday careers portal that day. The August–September 2026 estimate for summer 2027 came from the prior cycle (posted September 2025). Summer 2028: August–September 2027 on the same pattern (estimate)</t>
+          <t xml:space="preserve">Partly open: 6 US summer 2027 intern postings went live on Expedia's Workday board on October 12, 2026 (Software Development Engineering, Mobile Engineering, and Applied Science Master's and PhD in Austin, San Jose, and Seattle; Security Engineering and Finance Analyst in Seattle) and were still listed on October 15, 2026. No apply-by date is printed; each post is removed once application targets </t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>Fidelity</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
@@ -12633,17 +12637,17 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>Software Development Engineering; Cloud Engineering; Data Science &amp; Analytics; Machine Learning Science  (4 of 6 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>careers.expediagroup.com/emerging-talent-and-careers/</t>
+          <t>jobs.fidelity.com/en/students/internships/</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
@@ -12653,30 +12657,30 @@
       </c>
       <c r="G218" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The process spans 4–8 weeks with 4–5 stages: a recruiter screen, a strength-based behavioral assessment, a HackerRank online assessment with 2 coding problems and MCQs, and then 2 back-to-back 60-minute technical interviews with LeetCode-style questions. Difficulty is Easy to Medium, notably easier </t>
+          <t>An application with short questions, a recruiter phone screen, then one or two behavioral interviews, with HireVue video for some roles. The average timeline is about 30 days. There's no standardized coding or aptitude test for US internship roles.</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr"/>
       <c r="I218" s="6" t="inlineStr">
         <is>
-          <t>Yes. Each 2027 posting says it stays live at least 5 business days and is removed once application targets are met; in earlier cycles most interview slots repor</t>
+          <t>Yes. Interviews run "on a rolling basis" and hiring finishes by January</t>
         </is>
       </c>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Per the 2027 postings (October 15, 2026): Software Development and Mobile Engineering $45/hr with a bachelor's or $51/hr with a master's in Seattle and Austin, </t>
+          <t>$20 to $32/hr official posted range; tech interns report ~$34/hr (Levels.fyi)</t>
         </is>
       </c>
       <c r="K218" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly open: 6 US summer 2027 intern postings went live on Expedia's Workday board on October 12, 2026 (Software Development Engineering, Mobile Engineering, and Applied Science Master's and PhD in Austin, San Jose, and Seattle; Security Engineering and Finance Analyst in Seattle) and were still listed on October 15, 2026. No apply-by date is printed; each post is removed once application targets </t>
+          <t>Summer 2027, partly closed (checked October 6, 2026 on Fidelity's Workday board ): Human Resources, Fidelity Consulting Intern Analyst (closed October 1), Digital Assets Research, several quant research reqs and the spring co-op wave are closed. Still open: about 45 Investor Center branch internships, 2027 Targeted Interns and Student-Athlete (both end October 17), 2027 Corporate Accounting, MBA F</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>Fidelity</t>
+          <t>Figure AI</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
@@ -12686,17 +12690,17 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>Mechanical Engineering Intern; Electrical Engineering Intern; Software / Automation Intern; AI / Special Projects Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>jobs.fidelity.com/en/students/internships/</t>
+          <t>figure.ai/careers</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
@@ -12706,30 +12710,34 @@
       </c>
       <c r="G219" s="6" t="inlineStr">
         <is>
-          <t>An application with short questions, a recruiter phone screen, then one or two behavioral interviews, with HireVue video for some roles. The average timeline is about 30 days. There's no standardized coding or aptitude test for US internship roles.</t>
-        </is>
-      </c>
-      <c r="H219" s="6" t="inlineStr"/>
+          <t>A 4-stage loop averaging about 13 days: recruiter phone screen, technical assessment or coding challenge, 1 to 2 technical interviews with team members, and a final interview with a hiring manager. For hardware roles, expect questions about prototyping, CAD, and hands-on debugging.</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>Not explicitly confirmed for interns. F-1 CPT may be supported; verify directly with the recruiter before applying</t>
+        </is>
+      </c>
       <c r="I219" s="6" t="inlineStr">
         <is>
-          <t>Yes. Interviews run "on a rolling basis" and hiring finishes by January</t>
+          <t>Yes. Figure AI does not publish fixed deadlines. Postings remain open until filled, and the company reportedly moves fast on prioritized roles</t>
         </is>
       </c>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>$20 to $32/hr official posted range; tech interns report ~$34/hr (Levels.fyi)</t>
+          <t>$35 to $45 per hour ($40 to $45/hr for Special Projects). No confirmed housing stipend; San Jose cost-of-living is high, so budget independently</t>
         </is>
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027, partly closed (checked October 6, 2026 on Fidelity's Workday board ): Human Resources, Fidelity Consulting Intern Analyst (closed October 1), Digital Assets Research, several quant research reqs and the spring co-op wave are closed. Still open: about 45 Investor Center branch internships, 2027 Targeted Interns and Student-Athlete (both end October 17), 2027 Corporate Accounting, MBA F</t>
+          <t>Expected September to November 2026 for Summer 2027 roles. No fixed deadline; positions are filled on a rolling basis. Projected from prior cycles. As of early October 2026 no Summer 2027 role is posted; a Winter 2027 Supply Chain Analytics Intern role (January to April 2027) went live October 2</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>Figure AI</t>
+          <t>Fireworks AI</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
@@ -12739,17 +12747,17 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Intern; Electrical Engineering Intern; Software / Automation Intern; AI / Special Projects Intern  (4 of 6 tracks)</t>
+          <t>0 confirmed intern tracks. 6 potential tracks inferred from full-time team structure: AI Training Infrastructure, Cloud Infrastructure, Performance Optimization, ML Research, Full Stack/Platform, Applied ML</t>
         </is>
       </c>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>figure.ai/careers</t>
+          <t>fireworks.ai/careers</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
@@ -12759,34 +12767,34 @@
       </c>
       <c r="G220" s="6" t="inlineStr">
         <is>
-          <t>A 4-stage loop averaging about 13 days: recruiter phone screen, technical assessment or coding challenge, 1 to 2 technical interviews with team members, and a final interview with a hiring manager. For hardware roles, expect questions about prototyping, CAD, and hands-on debugging.</t>
+          <t>No intern interview process exists. The following is the full-time engineering process, which would likely serve as the template for any future intern loop: 1. Monitor fireworks.ai/careers and Greenhouse ATS . Check weekly starting fall 2026. Also monitor the Sequoia Jobs portal . If no intern roles</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed for interns. F-1 CPT may be supported; verify directly with the recruiter before applying</t>
+          <t>H-1B sponsored for full-time roles (19 LCAs filed in 2025, 7 in 2026, median salary $220K). Listed among startups sponsoring H-1B for CS new graduates</t>
         </is>
       </c>
       <c r="I220" s="6" t="inlineStr">
         <is>
-          <t>Yes. Figure AI does not publish fixed deadlines. Postings remain open until filled, and the company reportedly moves fast on prioritized roles</t>
+          <t>Not applicable yet. Full-time roles hire on a continuous/rolling basis through Greenhouse. A future intern program would likely follow the same model</t>
         </is>
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>$35 to $45 per hour ($40 to $45/hr for Special Projects). No confirmed housing stipend; San Jose cost-of-living is high, so budget independently</t>
+          <t xml:space="preserve">No intern salary data exists. Estimated $55 to $75 per hour ($9,200 to $12,500/month) based on comparable AI infrastructure startups and Fireworks AI full-time </t>
         </is>
       </c>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>Expected September to November 2026 for Summer 2027 roles. No fixed deadline; positions are filled on a rolling basis. Projected from prior cycles. As of early October 2026 no Summer 2027 role is posted; a Winter 2027 Supply Chain Analytics Intern role (January to April 2027) went live October 2</t>
+          <t>No confirmed timeline. If an intern program launches, postings would likely appear October 2026 to February 2027 (estimated from industry norms)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>Fireworks AI</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
@@ -12796,17 +12804,17 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D221" s="6" t="inlineStr">
         <is>
-          <t>0 confirmed intern tracks. 6 potential tracks inferred from full-time team structure: AI Training Infrastructure, Cloud Infrastructure, Performance Optimization, ML Research, Full Stack/Platform, Applied ML</t>
+          <t>Wind Engineering; Gas Power Engineering; Digital Technology; Nuclear Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>fireworks.ai/careers</t>
+          <t>careers.gevernova.com/early-careers</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
@@ -12816,34 +12824,34 @@
       </c>
       <c r="G221" s="6" t="inlineStr">
         <is>
-          <t>No intern interview process exists. The following is the full-time engineering process, which would likely serve as the template for any future intern loop: 1. Monitor fireworks.ai/careers and Greenhouse ATS . Check weekly starting fall 2026. Also monitor the Sequoia Jobs portal . If no intern roles</t>
+          <t>Expect 2 rounds over about 26 days total. The interview is a mix of behavioral and technical questions, though Glassdoor rates the difficulty at only 2.4 out of 5. You will likely meet with an HR representative and a team member on Zoom or Teams. Behavioral questions focus on leadership, teamwork, a</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsored for full-time roles (19 LCAs filed in 2025, 7 in 2026, median salary $220K). Listed among startups sponsoring H-1B for CS new graduates</t>
+          <t>No. All US internship postings state applicants must have "the ability to work in the United States for an unlimited amount of time without sponsorship." This language is stricter than many other companies and likely exc</t>
         </is>
       </c>
       <c r="I221" s="6" t="inlineStr">
         <is>
-          <t>Not applicable yet. Full-time roles hire on a continuous/rolling basis through Greenhouse. A future intern program would likely follow the same model</t>
+          <t>Yes. Postings are "expected to remain open for at least seven days" and close once filled. Apply within two weeks of a posting going live</t>
         </is>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No intern salary data exists. Estimated $55 to $75 per hour ($9,200 to $12,500/month) based on comparable AI infrastructure startups and Fireworks AI full-time </t>
+          <t>$21–$50/hr depending on role and year of study; housing allowance and relocation reimbursement for 50+ mile commutes</t>
         </is>
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>No confirmed timeline. If an intern program launches, postings would likely appear October 2026 to February 2027 (estimated from industry norms)</t>
+          <t>Open now for summer 2027: 66 US intern and co-op reqs titled 2027 were listed on October 30, 2026 (46 naming summer, plus Spring and Fall 2027 terms), posted from August through October 29. No single deadline; where an end date is printed it runs October 31 to November 30, 2026, so check each req</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
@@ -12853,17 +12861,17 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – January 2027</t>
         </is>
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>Wind Engineering; Gas Power Engineering; Digital Technology; Nuclear Engineering  (4 of 6 tracks)</t>
+          <t>AI / ML Development Intern; Engineering &amp; Manufacturing Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>careers.gevernova.com/early-careers</t>
+          <t>careers.gene.com/us/en/internship-opportunities</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
@@ -12873,34 +12881,34 @@
       </c>
       <c r="G222" s="6" t="inlineStr">
         <is>
-          <t>Expect 2 rounds over about 26 days total. The interview is a mix of behavioral and technical questions, though Glassdoor rates the difficulty at only 2.4 out of 5. You will likely meet with an HR representative and a team member on Zoom or Teams. Behavioral questions focus on leadership, teamwork, a</t>
+          <t>You apply with a resume, cover letter, and letters of recommendation. Then a phone screen with HR, a call with the hiring manager (sometimes including a short research presentation), a knowledge interview on your field, and a behavioral round using the STAR method. The average time to offer is 37 da</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
         <is>
-          <t>No. All US internship postings state applicants must have "the ability to work in the United States for an unlimited amount of time without sponsorship." This language is stricter than many other companies and likely exc</t>
+          <t>International students may apply. Visa sponsorship availability varies by position and department. You must be legally authorized to work in the US during the internship</t>
         </is>
       </c>
       <c r="I222" s="6" t="inlineStr">
         <is>
-          <t>Yes. Postings are "expected to remain open for at least seven days" and close once filled. Apply within two weeks of a posting going live</t>
+          <t>Yes. Genentech posts positions on an ongoing basis, in prior cycles from November through March, and reviews applications as they arrive. A posting can still ca</t>
         </is>
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>$21–$50/hr depending on role and year of study; housing allowance and relocation reimbursement for 50+ mile commutes</t>
+          <t xml:space="preserve">$25–$52/hr is the expected range printed on the two 2027 Summer Intern postings listed on October 11, 2026 (Quality Control and Hillsboro Technical Operations, </t>
         </is>
       </c>
       <c r="K222" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 62 US intern and co-op reqs titled 2027 were listed on October 11, 2026 (42 naming summer, plus Spring and Fall 2027 terms), most posted in September, the newest on October 9. No single deadline; where an end date is printed it runs October 30 to November 30, 2026, so check each req</t>
+          <t>Partly open: on October 30, 2026, four 2027 Summer Intern postings were open on Genentech's job board: three Product Technical Development internships in South San Francisco (Laboratory, Engineering and Manufacturing, and Digital Sciences focus, posted October 20), each listing October 31, 2026 as its end date, and Hillsboro Technical Operations in Hillsboro, Oregon, reposted October 21 with an en</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
@@ -12915,12 +12923,12 @@
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>AI / ML Development Intern; Engineering &amp; Manufacturing Intern  (2 of 6 tracks)</t>
+          <t>Software Engineering (Autonomous Driving); AI/ML Engineering; Manufacturing Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>careers.gene.com/us/en/internship-opportunities</t>
+          <t>search-careers.gm.com/en/early-careers/internship-program/</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
@@ -12930,34 +12938,30 @@
       </c>
       <c r="G223" s="6" t="inlineStr">
         <is>
-          <t>You apply with a resume, cover letter, and letters of recommendation. Then a phone screen with HR, a call with the hiring manager (sometimes including a short research presentation), a knowledge interview on your field, and a behavioral round using the STAR method. The average time to offer is 37 da</t>
-        </is>
-      </c>
-      <c r="H223" s="6" t="inlineStr">
-        <is>
-          <t>International students may apply. Visa sponsorship availability varies by position and department. You must be legally authorized to work in the US during the internship</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GM's hiring funnel averages 24 days from application to offer per Indeed data, though the full timeline spans 6–8 weeks when you count the rolling wait for assessment invitations: 1. Find and apply at search-careers.gm.com through the Workday portal. Upload your resume, use a permanent address (for </t>
+        </is>
+      </c>
+      <c r="H223" s="6" t="inlineStr"/>
       <c r="I223" s="6" t="inlineStr">
         <is>
-          <t>Yes. Genentech posts positions on an ongoing basis, in prior cycles from November through March, and reviews applications as they arrive. A posting can still ca</t>
+          <t>Per requisition. 36 of the 60 requisitions listed on October 21, 2026 carry a scheduled end date in GM's posting data, which the posting page itself does not di</t>
         </is>
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$25–$52/hr is the expected range printed on the two 2027 Summer Intern postings listed on October 11, 2026 (Quality Control and Hillsboro Technical Operations, </t>
+          <t>$6,100–$14,600/month printed on 33 of the 60 summer 2027 postings listed on October 21, 2026. Re-read October 22, 2026: $6,100 on the four Warren design posting</t>
         </is>
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>Partly open: on October 11, 2026, two 2027 Summer Intern postings were listed, both in Hillsboro, Oregon, with end dates of October 19 and October 20, 2026. They are Quality Control and Hillsboro Technical Operations. The main wave of summer 2027 roles is expected November 2026 through March 2027, projected from prior cycles. Most hiring decisions made by end of March</t>
+          <t>Open now for summer 2027: 60 US intern requisitions were listed on GM's Workday job board on October 21, 2026. Human Interface Design came down after its October 23 end date, and on October 24 the nearest scheduled end dates were October 30 and November 6, 2026. At least 28 requisitions have closed since postings began August 17, 2026, including the seven motorsports postings (end date October 15,</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -12967,17 +12971,17 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (Autonomous Driving); AI/ML Engineering; Manufacturing Engineering  (3 of 6 tracks)</t>
+          <t>Software Engineering, Distributed Systems Intern; Software Engineer, Model Evaluation Systems Intern; Compound AI Engineering Intern; AI Application Engineering Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>search-careers.gm.com/en/early-careers/internship-program/</t>
+          <t>groq.com/careers-at-groq</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
@@ -12987,30 +12991,34 @@
       </c>
       <c r="G224" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">GM's hiring funnel averages 24 days from application to offer per Indeed data, though the full timeline spans 6–8 weeks when you count the rolling wait for assessment invitations: 1. Find and apply at search-careers.gm.com through the Workday portal. Upload your resume, use a permanent address (for </t>
-        </is>
-      </c>
-      <c r="H224" s="6" t="inlineStr"/>
+          <t>Groq's interview process was deliberately different from the industry standard, emphasizing project work and practical skill over algorithmic puzzles: 1. Find open roles at groq.com/careers-at-groq or jobs.gem.com/groq . If no internship roles are posted, you can share your resume on the gem.com por</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>Must be authorized to work in the US or Canada. Interns typically use CPT or co-op authorization. Groq has filed 11 H-1B petitions historically for full-time roles. No explicit intern visa sponsorship statement</t>
+        </is>
+      </c>
       <c r="I224" s="6" t="inlineStr">
         <is>
-          <t>Per requisition. 36 of the 60 requisitions listed on October 21, 2026 carry a scheduled end date in GM's posting data, which the posting page itself does not di</t>
+          <t>Yes, historically. Groq did not publish fixed deadlines. Positions filled on a rolling basis once postings opened</t>
         </is>
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>$6,100–$14,600/month printed on 33 of the 60 summer 2027 postings listed on October 21, 2026. Re-read October 22, 2026: $6,100 on the four Warren design posting</t>
+          <t xml:space="preserve">$30 to $50 per hour for US technical internships. Glassdoor reports an average of $52 per hour (range $40 to $69). Housing and transportation support provided. </t>
         </is>
       </c>
       <c r="K224" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 60 US intern requisitions were listed on GM's Workday job board on October 21, 2026. Human Interface Design came down after its October 23 end date, and on October 24 the nearest scheduled end dates were October 30 and November 6, 2026. At least 28 requisitions have closed since postings began August 17, 2026, including the seven motorsports postings (end date October 15,</t>
+          <t>Historically October to November for Summer roles. Confidence is low given the Nvidia deal. Monitor both Groq and Nvidia portals starting fall 2026</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>Groq</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
@@ -13020,17 +13028,17 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D225" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering, Distributed Systems Intern; Software Engineer, Model Evaluation Systems Intern; Compound AI Engineering Intern; AI Application Engineering Intern  (4 of 5 tracks)</t>
+          <t>Software Engineering  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>groq.com/careers-at-groq</t>
+          <t>app.ripplematch.com/v2/public/company/hubspot</t>
         </is>
       </c>
       <c r="F225" s="7" t="inlineStr">
@@ -13040,34 +13048,30 @@
       </c>
       <c r="G225" s="6" t="inlineStr">
         <is>
-          <t>Groq's interview process was deliberately different from the industry standard, emphasizing project work and practical skill over algorithmic puzzles: 1. Find open roles at groq.com/careers-at-groq or jobs.gem.com/groq . If no internship roles are posted, you can share your resume on the gem.com por</t>
-        </is>
-      </c>
-      <c r="H225" s="6" t="inlineStr">
-        <is>
-          <t>Must be authorized to work in the US or Canada. Interns typically use CPT or co-op authorization. Groq has filed 11 H-1B petitions historically for full-time roles. No explicit intern visa sponsorship statement</t>
-        </is>
-      </c>
+          <t>After passing resume review, you complete a unique API-based coding challenge where you call a dummy API, manipulate data, and POST results, all in your own IDE. Then comes a 15-to-30-minute recruiter call. The final round is a roughly 2-hour technical interview split between general coding and your</t>
+        </is>
+      </c>
+      <c r="H225" s="6" t="inlineStr"/>
       <c r="I225" s="6" t="inlineStr">
         <is>
-          <t>Yes, historically. Groq did not publish fixed deadlines. Positions filled on a rolling basis once postings opened</t>
+          <t>Not confirmed. The 2024 SWE window was a fixed 3-week deadline. Apply the day it opens</t>
         </is>
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">$30 to $50 per hour for US technical internships. Glassdoor reports an average of $52 per hour (range $40 to $69). Housing and transportation support provided. </t>
+          <t>SWE: $50–$54/hr (official JD + Levels.fyi); some cycles include a $2,000 bonus. Non-SWE: ~$34/hr average (Glassdoor)</t>
         </is>
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>Historically October to November for Summer roles. Confidence is low given the Nvidia deal. Monitor both Groq and Nvidia portals starting fall 2026</t>
+          <t>Not confirmed yet. No North America summer 2027 roles on HubSpot's careers board on October 6, 2026; North America roles route through RippleMatch (login required), so check there. Expected this fall; SWE window historically just 3 weeks</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>Ideogram</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
@@ -13077,17 +13081,17 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering  (1 of 6 tracks)</t>
+          <t>ML Research Intern; ML Data Infrastructure Intern (projected); Applied AI Intern (projected); Research Engineer Intern (projected)</t>
         </is>
       </c>
       <c r="E226" s="7" t="inlineStr">
         <is>
-          <t>app.ripplematch.com/v2/public/company/hubspot</t>
+          <t>jobs.ashbyhq.com/ideogram</t>
         </is>
       </c>
       <c r="F226" s="7" t="inlineStr">
@@ -13097,30 +13101,34 @@
       </c>
       <c r="G226" s="6" t="inlineStr">
         <is>
-          <t>After passing resume review, you complete a unique API-based coding challenge where you call a dummy API, manipulate data, and POST results, all in your own IDE. Then comes a 15-to-30-minute recruiter call. The final round is a roughly 2-hour technical interview split between general coding and your</t>
-        </is>
-      </c>
-      <c r="H226" s="6" t="inlineStr"/>
+          <t>Four stages: HR screen, a technical interview on ML fundamentals (attention mechanisms, diffusion models, backpropagation derivations), a coding round, and an on-site day in Toronto concluding with a meeting with CEO Mohammad Norouzi. The full process takes approximately 2 weeks.</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>Not confirmed. Canadian study-permit holders can obtain co-op work permits. US-based applicants need existing work authorization or CPT/OPT</t>
+        </is>
+      </c>
       <c r="I226" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. The 2024 SWE window was a fixed 3-week deadline. Apply the day it opens</t>
+          <t xml:space="preserve">Yes, ad hoc. The Summer 2026 ML Research Intern listing was open approximately 268 days (October 2025 to July 2026). Postings appear based on team needs rather </t>
         </is>
       </c>
       <c r="J226" s="6" t="inlineStr">
         <is>
-          <t>SWE: $50–$54/hr (official JD + Levels.fyi); some cycles include a $2,000 bonus. Non-SWE: ~$34/hr average (Glassdoor)</t>
+          <t>Not publicly disclosed. Estimated $6,000 to $10,000 CAD/month (Toronto) or $8,000 to $12,000 USD/month (NYC) based on comparable AI startups. Equity component n</t>
         </is>
       </c>
       <c r="K226" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed yet. No North America summer 2027 roles on HubSpot's careers board on October 6, 2026; North America roles route through RippleMatch (login required), so check there. Expected this fall; SWE window historically just 3 weeks</t>
+          <t>Expected Q4 2026 (October to December 2026) for summer 2027 roles. Projected from the Summer 2026 cycle, where the listing appeared in October 2025</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>Ideogram</t>
+          <t>Inflection AI</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
@@ -13135,12 +13143,12 @@
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; ML Data Infrastructure Intern (projected); Applied AI Intern (projected); Research Engineer Intern (projected)</t>
+          <t>ML Engineering Intern; Data Science Intern; Voice AI Intern; AI Systems Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E227" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/ideogram</t>
+          <t>inflection.ai/about</t>
         </is>
       </c>
       <c r="F227" s="7" t="inlineStr">
@@ -13150,34 +13158,34 @@
       </c>
       <c r="G227" s="6" t="inlineStr">
         <is>
-          <t>Four stages: HR screen, a technical interview on ML fundamentals (attention mechanisms, diffusion models, backpropagation derivations), a coding round, and an on-site day in Toronto concluding with a meeting with CEO Mohammad Norouzi. The full process takes approximately 2 weeks.</t>
+          <t>Three stages, all virtual: a 30-minute recruiter conversation, 90 minutes of technical interviews covering coding, ML domain questions, and systems design, and a 30-minute mentor or team conversation. The full process takes about three weeks, with decisions typically within one week of the final rou</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Canadian study-permit holders can obtain co-op work permits. US-based applicants need existing work authorization or CPT/OPT</t>
+          <t>Not confirmed for interns. Inflection AI has filed a small number of H-1B petitions for full-time roles; CPT would typically apply for enrolled international students</t>
         </is>
       </c>
       <c r="I227" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes, ad hoc. The Summer 2026 ML Research Intern listing was open approximately 268 days (October 2025 to July 2026). Postings appear based on team needs rather </t>
+          <t>Not officially confirmed, but positions fill quickly, suggesting first-come review. Apply as soon as listings appear</t>
         </is>
       </c>
       <c r="J227" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed. Estimated $6,000 to $10,000 CAD/month (Toronto) or $8,000 to $12,000 USD/month (NYC) based on comparable AI startups. Equity component n</t>
+          <t>Technical: $50 to $65/hr ($8,700 to $11,300/month). Nontechnical: $25 to $40/hr. Rate scales with education level and experience. Housing stipend not confirmed</t>
         </is>
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>Expected Q4 2026 (October to December 2026) for summer 2027 roles. Projected from the Summer 2026 cycle, where the listing appeared in October 2025</t>
+          <t>Expected October to December 2026 for summer 2027 roles, based on the Summer 2026 cycle pattern. Listings close once positions are filled</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>Inflection AI</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
@@ -13187,17 +13195,17 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>ML Engineering Intern; Data Science Intern; Voice AI Intern; AI Systems Intern  (4 of 5 tracks)</t>
+          <t>Software Engineering Internship; Data Science &amp; Analytics Internship; Machine Learning PhD Internship  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E228" s="7" t="inlineStr">
         <is>
-          <t>inflection.ai/about</t>
+          <t>instacart.careers/current-openings</t>
         </is>
       </c>
       <c r="F228" s="7" t="inlineStr">
@@ -13207,34 +13215,30 @@
       </c>
       <c r="G228" s="6" t="inlineStr">
         <is>
-          <t>Three stages, all virtual: a 30-minute recruiter conversation, 90 minutes of technical interviews covering coding, ML domain questions, and systems design, and a 30-minute mentor or team conversation. The full process takes about three weeks, with decisions typically within one week of the final rou</t>
-        </is>
-      </c>
-      <c r="H228" s="6" t="inlineStr">
-        <is>
-          <t>Not confirmed for interns. Inflection AI has filed a small number of H-1B petitions for full-time roles; CPT would typically apply for enrolled international students</t>
-        </is>
-      </c>
+          <t xml:space="preserve">SWE candidates go through a five-stage pipeline: resume screening, a 70-minute CodeSignal assessment with 4 tasks scored 300–850, a 30-minute recruiter call, a 45–60 minute live coding screen via CoderPad, and a virtual onsite with 3–4 rounds covering coding, system design, behavioral, and a hiring </t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr"/>
       <c r="I228" s="6" t="inlineStr">
         <is>
-          <t>Not officially confirmed, but positions fill quickly, suggesting first-come review. Apply as soon as listings appear</t>
+          <t>Effectively yes. Optimal submission is the first 3 weeks after posting; early applicants hear back in 5–7 days</t>
         </is>
       </c>
       <c r="J228" s="6" t="inlineStr">
         <is>
-          <t>Technical: $50 to $65/hr ($8,700 to $11,300/month). Nontechnical: $25 to $40/hr. Rate scales with education level and experience. Housing stipend not confirmed</t>
+          <t>SWE: $9,500–$10,500/mo; DS: $8,500–$9,500/mo; plus $3,000–$4,000 housing stipend</t>
         </is>
       </c>
       <c r="K228" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles, based on the Summer 2026 cycle pattern. Listings close once positions are filled</t>
+          <t>Not posted as of October 11, 2026: no US internship posting for summer 2027 was listed on instacart.careers on that date. The earlier Aug–Sep 2026 estimate for SWE/DS came from the prior cycle; APM: ~10 days in early March 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>J&amp;J</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
@@ -13244,17 +13248,17 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October 2026 – June 2027</t>
         </is>
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Internship; Data Science &amp; Analytics Internship; Machine Learning PhD Internship  (3 of 4 tracks)</t>
+          <t>Technology Intern (JJT); MedTech Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
         <is>
-          <t>instacart.careers/current-openings</t>
+          <t>careers.jnj.com/en/early-career-programs/internships/</t>
         </is>
       </c>
       <c r="F229" s="7" t="inlineStr">
@@ -13264,30 +13268,34 @@
       </c>
       <c r="G229" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE candidates go through a five-stage pipeline: resume screening, a 70-minute CodeSignal assessment with 4 tasks scored 300–850, a 30-minute recruiter call, a 45–60 minute live coding screen via CoderPad, and a virtual onsite with 3–4 rounds covering coding, system design, behavioral, and a hiring </t>
-        </is>
-      </c>
-      <c r="H229" s="6" t="inlineStr"/>
+          <t>You apply online, complete a HireVue pre-recorded video with three behavioral questions, then have two to four live video interviews covering technical skills and Credo alignment. Competitive tracks may include a Superday with three to five stakeholder meetings. Average time to offer is about 19 day</t>
+        </is>
+      </c>
+      <c r="H229" s="6" t="inlineStr">
+        <is>
+          <t>Not offered on the postings checked October 22, 2026 (El Paso Finance, CLDP, MLDP, IM North America Operations); CLDP, MLDP and Operations add that students on CPT, OPT or STEM OPT require future sponsorship. Lines can d</t>
+        </is>
+      </c>
       <c r="I229" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Optimal submission is the first 3 weeks after posting; early applicants hear back in 5–7 days</t>
+          <t>Yes. J&amp;J reviews applications on a rolling basis and fills seats as qualified candidates are identified. With early tracks already live as of July 2026, early a</t>
         </is>
       </c>
       <c r="J229" s="6" t="inlineStr">
         <is>
-          <t>SWE: $9,500–$10,500/mo; DS: $8,500–$9,500/mo; plus $3,000–$4,000 housing stipend</t>
+          <t>Postings checked October 22, 2026 print $26 to $29/hr (El Paso Finance), $23.50 to $52.50/hr (IM North America Operations) and $52/hr for MBA candidates (CLDP a</t>
         </is>
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>Not posted as of October 11, 2026: no US internship posting for summer 2027 was listed on instacart.careers on that date. The earlier Aug–Sep 2026 estimate for SWE/DS came from the prior cycle; APM: ~10 days in early March 2027 (documented pattern; not yet posted)</t>
+          <t>Open now for summer 2027: careers.jnj.com listed 36 US internship postings and 42 co-op postings on October 30, 2026, with end dates from October 31, 2026 to January 2, 2027. The main 2027 wave posted September 15 to 19, 2026 (Spring 2027 and Summer 2027 co-ops, Summer 2027 interns, Finance Internship). Each requisition prints its own end date, so apply before it: the October 1 ones have closed, m</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>J&amp;J</t>
+          <t>Jump Trading</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -13297,17 +13305,17 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – June 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>Technology Intern (JJT); MedTech Engineering Intern  (2 of 6 tracks)</t>
+          <t>Campus Quantitative Trader (Intern); Campus Quantitative Researcher (Intern); Campus AI Research Engineer (Intern); Campus Software Engineer (Intern); Campus Data Engineer / UI Software Engineer (Intern); Campus Systems Engineer (Intern)</t>
         </is>
       </c>
       <c r="E230" s="7" t="inlineStr">
         <is>
-          <t>careers.jnj.com/en/early-career-programs/internships/</t>
+          <t>jumptrading.com/hr/students-new-grads</t>
         </is>
       </c>
       <c r="F230" s="7" t="inlineStr">
@@ -13317,34 +13325,34 @@
       </c>
       <c r="G230" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a HireVue pre-recorded video with three behavioral questions, then have two to four live video interviews covering technical skills and Credo alignment. Competitive tracks may include a Superday with three to five stakeholder meetings. Average time to offer is about 19 day</t>
+          <t>Typically 4 to 5 rounds over 3 to 6 weeks: a timed online assessment with algorithmic problems, 1 to 2 phone screens with live C++ coding, 2 to 3 on-site interviews covering advanced C++, system design, mathematics, and probability, then a final team-match discussion. The bar is comparable to HRT an</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
         <is>
-          <t>Not offered on the postings checked October 22, 2026 (El Paso Finance, CLDP, MLDP, IM North America Operations); CLDP, MLDP and Operations add that students on CPT, OPT or STEM OPT require future sponsorship. Lines can d</t>
+          <t>International students encouraged to apply; CPT/OPT-eligible candidates accepted. The firm sponsors work visas for full-time positions</t>
         </is>
       </c>
       <c r="I230" s="6" t="inlineStr">
         <is>
-          <t>Yes. J&amp;J reviews applications on a rolling basis and fills seats as qualified candidates are identified. With early tracks already live as of July 2026, early a</t>
+          <t>Effectively yes. No published deadlines; positions are filled as suitable candidates are identified. Apply early</t>
         </is>
       </c>
       <c r="J230" s="6" t="inlineStr">
         <is>
-          <t>Postings checked October 22, 2026 print $26 to $29/hr (El Paso Finance), $23.50 to $52.50/hr (IM North America Operations) and $52/hr for MBA candidates (CLDP a</t>
+          <t>Live US intern postings (Greenhouse, October 21, 2026) print an estimated base salary of $300,000 per year annualized (about $144/hr) for Quantitative Trader, Q</t>
         </is>
       </c>
       <c r="K230" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: careers.jnj.com listed 48 US internship postings and 69 co-op postings on October 21, 2026, with end dates from October 22, 2026 to January 2, 2027. The main 2027 wave posted September 15 to 19, 2026 (Spring 2027 and Summer 2027 co-ops, Summer 2027 interns, Finance Internship). Each requisition prints its own end date, so apply before it: the October 1 ones have closed, m</t>
+          <t>OPEN NOW for summer 2027. Jump's students and new grads page states it is "opening 2027 roles by region, starting with the US." 10 US intern requisitions (Chicago and New York) were live on Jump's Greenhouse board on October 21, 2026, and non-US regions are posted too. No published closing date; review is rolling and seats fill as candidates are identified</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>Jump Trading</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
@@ -13359,12 +13367,12 @@
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>Campus Quantitative Trader (Intern); Campus Quantitative Researcher (Intern); Campus AI Research Engineer (Intern); Campus Software Engineer (Intern); Campus Data Engineer / UI Software Engineer (Intern); Campus Systems Engineer (Intern)</t>
+          <t>Software Engineer Intern; Data Science &amp; Analytics Intern; Cybersecurity Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E231" s="7" t="inlineStr">
         <is>
-          <t>jumptrading.com/hr/students-new-grads</t>
+          <t>careers.mastercard.com/us/en/internships</t>
         </is>
       </c>
       <c r="F231" s="7" t="inlineStr">
@@ -13374,34 +13382,34 @@
       </c>
       <c r="G231" s="6" t="inlineStr">
         <is>
-          <t>Typically 4 to 5 rounds over 3 to 6 weeks: a timed online assessment with algorithmic problems, 1 to 2 phone screens with live C++ coding, 2 to 3 on-site interviews covering advanced C++, system design, mathematics, and probability, then a final team-match discussion. The bar is comparable to HRT an</t>
+          <t xml:space="preserve">You apply, complete a recruiter phone screen (15 to 30 minutes), take a 60- to 90-minute online assessment on HackerRank or Codility with 2 to 3 coding problems, then 1 to 2 technical interviews plus a behavioral round focused on the Decency Quotient. Average time from application to offer is about </t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
         <is>
-          <t>International students encouraged to apply; CPT/OPT-eligible candidates accepted. The firm sponsors work visas for full-time positions</t>
+          <t>Not available on the US Summer 2027 intern postings, and F-1 students are excluded. All 8 postings listed on October 11, 2026 print: "This role is not eligible for Mastercard's work authorization sponsorship. As such, ca</t>
         </is>
       </c>
       <c r="I231" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. No published deadlines; positions are filled as suitable candidates are identified. Apply early</t>
+          <t>Yes. Mastercard reviews applications on a rolling basis. Roles close once filled, so applying early is the clearest edge</t>
         </is>
       </c>
       <c r="J231" s="6" t="inlineStr">
         <is>
-          <t>Live US intern postings (Greenhouse, October 21, 2026) print an estimated base salary of $300,000 per year annualized (about $144/hr) for Quantitative Trader, Q</t>
+          <t>$25–$46/hr base pay printed across the 8 US Summer 2027 intern postings listed on October 11, 2026. Four St. Louis roles (Site Reliability Engineering, Enterpri</t>
         </is>
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW for summer 2027. Jump's students and new grads page states it is "opening 2027 roles by region, starting with the US." 10 US intern requisitions (Chicago and New York) were live on Jump's Greenhouse board on October 21, 2026, and non-US regions are posted too. No published closing date; review is rolling and seats fill as candidates are identified</t>
+          <t xml:space="preserve">Partly open for summer 2027: 4 US intern postings were listed on Mastercard's Campus Workday portal on October 14, 2026 (2 in St. Louis, 1 each in Arlington, VA and San Francisco), all security, engineering and data roles posted October 5 to 7, 2026, and none prints an end date. Of the 8 US postings listed on October 11, the Marketing and Communications Intern posting in Purchase, NY closed after </t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Mercor</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
@@ -13411,17 +13419,17 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Data Science &amp; Analytics Intern; Cybersecurity Intern  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern; ML / Research Engineering Intern; Data Science / Data Engineering Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>careers.mastercard.com/us/en/internships</t>
+          <t>jobs.ashbyhq.com/mercor</t>
         </is>
       </c>
       <c r="F232" s="7" t="inlineStr">
@@ -13431,34 +13439,34 @@
       </c>
       <c r="G232" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">You apply, complete a recruiter phone screen (15 to 30 minutes), take a 60- to 90-minute online assessment on HackerRank or Codility with 2 to 3 coding problems, then 1 to 2 technical interviews plus a behavioral round focused on the Decency Quotient. Average time from application to offer is about </t>
+          <t>Mercor uses its own AI interviewer as the first screen, a roughly 20-minute camera-on rapid-fire interview. Only the top 3 to 4% advance to a 72-hour take-home assignment, followed by a system design Super Day (up to 5 hours), background verification with past managers, and then an offer. There is n</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
         <is>
-          <t>Not available on the US Summer 2027 intern postings, and F-1 students are excluded. All 8 postings listed on October 11, 2026 print: "This role is not eligible for Mastercard's work authorization sponsorship. As such, ca</t>
+          <t>Not confirmed for interns. Mercor sponsors H-1B and E-3 visas for full-time employees (30 LCA filings, 86% certification rate). OPT/CPT support likely but not guaranteed</t>
         </is>
       </c>
       <c r="I232" s="6" t="inlineStr">
         <is>
-          <t>Yes. Mastercard reviews applications on a rolling basis. Roles close once filled, so applying early is the clearest edge</t>
+          <t>Not confirmed. The AI interview round appears to be administered on a rolling basis upon application. Whether reviews happen rolling or in batches is not public</t>
         </is>
       </c>
       <c r="J232" s="6" t="inlineStr">
         <is>
-          <t>$25–$46/hr base pay printed across the 8 US Summer 2027 intern postings listed on October 11, 2026. Four St. Louis roles (Site Reliability Engineering, Enterpri</t>
+          <t>SWE intern: $61K to $156K per year annualized ($32 to $57/hr estimated). Most recent Glassdoor submission (June 2026, San Francisco): $134K to $156K per year</t>
         </is>
       </c>
       <c r="K232" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partly open for summer 2027: 4 US intern postings were listed on Mastercard's Campus Workday portal on October 14, 2026 (2 in St. Louis, 1 each in Arlington, VA and San Francisco), all security, engineering and data roles posted October 5 to 7, 2026, and none prints an end date. Of the 8 US postings listed on October 11, the Marketing and Communications Intern posting in Purchase, NY closed after </t>
+          <t>OPEN, rolling. Five intern postings live as of October 28, 2026, all in-person in San Francisco: Software Engineer Intern (posted August 4, $70/hr), Data Science Intern (August 19, $70/hr), Research Intern (October 5, $80/hr) and two Research Engineer Interns (October 27, $70/hr). Interns start on a rolling basis, so summer, spring and fall terms all work; no closing date printed</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>Mercor</t>
+          <t>Modal</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
@@ -13468,17 +13476,17 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; ML / Research Engineering Intern; Data Science / Data Engineering Intern  (3 of 5 tracks)</t>
+          <t>GPU Optimization &amp; AI Infrastructure  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/mercor</t>
+          <t>jobs.ashbyhq.com/modal</t>
         </is>
       </c>
       <c r="F233" s="7" t="inlineStr">
@@ -13488,34 +13496,34 @@
       </c>
       <c r="G233" s="6" t="inlineStr">
         <is>
-          <t>Mercor uses its own AI interviewer as the first screen, a roughly 20-minute camera-on rapid-fire interview. Only the top 3 to 4% advance to a 72-hour take-home assignment, followed by a system design Super Day (up to 5 hours), background verification with past managers, and then an offer. There is n</t>
+          <t>The intern interview likely consists of a recruiter screen (30 minutes), one to two technical coding rounds in Python, Rust, or Go focusing on systems fundamentals, and a behavioral round. The full-time process is rated 8 out of 10 difficulty, comparable to Stripe and HashiCorp. Modal does not use K</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed for interns. Mercor sponsors H-1B and E-3 visas for full-time employees (30 LCA filings, 86% certification rate). OPT/CPT support likely but not guaranteed</t>
+          <t>H-1B sponsorship confirmed for full-time roles. CPT-eligible international students likely accepted for internships. Verify directly with Modal's recruiter</t>
         </is>
       </c>
       <c r="I233" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. The AI interview round appears to be administered on a rolling basis upon application. Whether reviews happen rolling or in batches is not public</t>
+          <t>Likely rolling. With only seven to eight intern spots per cohort, positions probably fill quickly once posted. Apply the day the listing appears</t>
         </is>
       </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>SWE intern: $61K to $156K per year annualized ($32 to $57/hr estimated). Most recent Glassdoor submission (June 2026, San Francisco): $134K to $156K per year</t>
+          <t>The PhD ML Research Intern listing states $15K per month. Engineering intern pay is not publicly disclosed; estimated $60 to $85 per hour based on comparable AI</t>
         </is>
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>OPEN, rolling. Five intern postings live as of October 28, 2026, all in-person in San Francisco: Software Engineer Intern (posted August 4, $70/hr), Data Science Intern (August 19, $70/hr), Research Intern (October 5, $80/hr) and two Research Engineer Interns (October 27, $70/hr). Interns start on a rolling basis, so summer, spring and fall terms all work; no closing date printed</t>
+          <t>Expected October to November 2026 for Summer 2027 roles. No confirmed dates. Projected from industry patterns and past cohort timing</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>Modal</t>
+          <t>Moderna</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
@@ -13525,17 +13533,17 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>GPU Optimization &amp; AI Infrastructure  (1 of 4 tracks)</t>
+          <t>Technical Development  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/modal</t>
+          <t>modernatx.com/en-US/careers</t>
         </is>
       </c>
       <c r="F234" s="7" t="inlineStr">
@@ -13545,34 +13553,34 @@
       </c>
       <c r="G234" s="6" t="inlineStr">
         <is>
-          <t>The intern interview likely consists of a recruiter screen (30 minutes), one to two technical coding rounds in Python, Rust, or Go focusing on systems fundamentals, and a behavioral round. The full-time process is rated 8 out of 10 difficulty, comparable to Stripe and HashiCorp. Modal does not use K</t>
+          <t>After applying, top candidates take a 60–90 minute online assessment covering scientific knowledge, quantitative reasoning, and situational judgment, needing 70–80% to advance. Next comes a recruiter phone screen, then a 45–60 minute hiring manager interview focused on technical depth and behavioral</t>
         </is>
       </c>
       <c r="H234" s="6" t="inlineStr">
         <is>
-          <t>H-1B sponsorship confirmed for full-time roles. CPT-eligible international students likely accepted for internships. Verify directly with Modal's recruiter</t>
+          <t>Moderna requires valid US work authorization for internships. F-1 students are eligible through Curricular Practical Training (CPT), which is authorized by the student's university at no cost to Moderna. OPT isn't typica</t>
         </is>
       </c>
       <c r="I234" s="6" t="inlineStr">
         <is>
-          <t>Likely rolling. With only seven to eight intern spots per cohort, positions probably fill quickly once posted. Apply the day the listing appears</t>
+          <t>Yes. Roles may close before posted deadlines once sufficient applicant pools are reached</t>
         </is>
       </c>
       <c r="J234" s="6" t="inlineStr">
         <is>
-          <t>The PhD ML Research Intern listing states $15K per month. Engineering intern pay is not publicly disclosed; estimated $60 to $85 per hour based on comparable AI</t>
+          <t>$25–$32/hr undergraduate; $35–$45/hr graduate/PhD; plus $3,000–$5,000 housing stipend</t>
         </is>
       </c>
       <c r="K234" s="6" t="inlineStr">
         <is>
-          <t>Expected October to November 2026 for Summer 2027 roles. No confirmed dates. Projected from industry patterns and past cohort timing</t>
+          <t>Open now for summer 2027: six summer 2027 internships live on the Workday portal as of October 1, 2026 (first posted August 31). Expected to close by mid-November 2026. Spring 2027 co-ops (January 18 to June 25, 2027) are posting too</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>Moderna</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -13582,17 +13590,17 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>Technical Development  (1 of 6 tracks)</t>
+          <t>Software Engineering Intern (Product); Data Science Intern  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>modernatx.com/en-US/careers</t>
+          <t>mongodb.com/company/careers/students-and-graduates</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
@@ -13602,34 +13610,34 @@
       </c>
       <c r="G235" s="6" t="inlineStr">
         <is>
-          <t>After applying, top candidates take a 60–90 minute online assessment covering scientific knowledge, quantitative reasoning, and situational judgment, needing 70–80% to advance. Next comes a recruiter phone screen, then a 45–60 minute hiring manager interview focused on technical depth and behavioral</t>
+          <t>Five stages: resume screening, a 30-minute recruiter phone screen, a 60-minute Karat technical assessment (two LeetCode easy-to-medium problems), a 2.5 to 3-hour virtual onsite with 2 to 3 panel interviews, and an offer decision. The whole process runs about 7 to 9 weeks.</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
         <is>
-          <t>Moderna requires valid US work authorization for internships. F-1 students are eligible through Curricular Practical Training (CPT), which is authorized by the student's university at no cost to Moderna. OPT isn't typica</t>
+          <t>May be available. Job postings state authorized to work in the US, with sponsorship possible</t>
         </is>
       </c>
       <c r="I235" s="6" t="inlineStr">
         <is>
-          <t>Yes. Roles may close before posted deadlines once sufficient applicant pools are reached</t>
+          <t>Effectively yes. In past cycles most positions filled by mid-October, well before the mid-November close. Apply in the first week a role posts for priority cons</t>
         </is>
       </c>
       <c r="J235" s="6" t="inlineStr">
         <is>
-          <t>$25–$32/hr undergraduate; $35–$45/hr graduate/PhD; plus $3,000–$5,000 housing stipend</t>
+          <t>SF $59.40/hr ($10,296/mo) plus $4,950/mo housing stipend. NYC $56.33/hr ($9,765/mo) plus $4,500/mo housing. Annualized range $108,160 to $112,320</t>
         </is>
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: six summer 2027 internships live on the Workday portal as of October 1, 2026 (first posted August 31). Expected to close by mid-November 2026. Spring 2027 co-ops (January 18 to June 25, 2027) are posting too</t>
+          <t>Open. On October 25, 2026, MongoDB's board listed one intern requisition, 2027 Software Engineering Intern, AMER (Austin, New York City, San Francisco), posted October 23 with no printed deadline. Rolling; apply this week</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -13644,12 +13652,12 @@
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Product); Data Science Intern  (2 of 4 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>mongodb.com/company/careers/students-and-graduates</t>
+          <t>careers.nike.com/career-areas</t>
         </is>
       </c>
       <c r="F236" s="7" t="inlineStr">
@@ -13659,34 +13667,30 @@
       </c>
       <c r="G236" s="6" t="inlineStr">
         <is>
-          <t>Five stages: resume screening, a 30-minute recruiter phone screen, a 60-minute Karat technical assessment (two LeetCode easy-to-medium problems), a 2.5 to 3-hour virtual onsite with 2 to 3 panel interviews, and an offer decision. The whole process runs about 7 to 9 weeks.</t>
-        </is>
-      </c>
-      <c r="H236" s="6" t="inlineStr">
-        <is>
-          <t>May be available. Job postings state authorized to work in the US, with sponsorship possible</t>
-        </is>
-      </c>
+          <t>After applying through Workday, most candidates receive a game-based assessment with pattern recognition, memory, and risk games via HireVue or AON/Cut-e. Next comes a HireVue on-demand video with 5–6 behavioral questions and a 2-minute answer limit. Technology roles add a coding challenge. Finalist</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr"/>
       <c r="I236" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. In past cycles most positions filled by mid-October, well before the mid-November close. Apply in the first week a role posts for priority cons</t>
+          <t>Yes. Recruiters begin screening in late September; most offers go out October–December</t>
         </is>
       </c>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>SF $59.40/hr ($10,296/mo) plus $4,950/mo housing stipend. NYC $56.33/hr ($9,765/mo) plus $4,500/mo housing. Annualized range $108,160 to $112,320</t>
+          <t>$25–$48/hr depending on role and degree level; WHQ interns get housing stipends of $3,000–$6,500</t>
         </is>
       </c>
       <c r="K236" s="6" t="inlineStr">
         <is>
-          <t>Open. On October 25, 2026, MongoDB's board listed one intern requisition, 2027 Software Engineering Intern, AMER (Austin, New York City, San Francisco), posted October 23 with no printed deadline. Rolling; apply this week</t>
+          <t>Open now for summer 2027: 23 US postings live as of October 1, 2026 (first posted September 1). Undergraduate postings end October 18 to November 1, 2026; graduate postings November 30 to December 7, 2026 (rolling)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Nintendo</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
@@ -13696,17 +13700,17 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>Software Engineering (NTD)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>careers.nike.com/career-areas</t>
+          <t>careers.nintendo.com/</t>
         </is>
       </c>
       <c r="F237" s="7" t="inlineStr">
@@ -13716,30 +13720,34 @@
       </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>After applying through Workday, most candidates receive a game-based assessment with pattern recognition, memory, and risk games via HireVue or AON/Cut-e. Next comes a HireVue on-demand video with 5–6 behavioral questions and a 2-minute answer limit. Technology roles add a coding challenge. Finalist</t>
-        </is>
-      </c>
-      <c r="H237" s="6" t="inlineStr"/>
+          <t>Nintendo’s funnel is structured and predictable, running roughly 3 to 4 months from application to offer: 1. Apply at careers.nintendo.com with a resume, cover letter showing Nintendo brand knowledge, and the Internship Questionnaire. Design roles require a portfolio. Submit before December 1. 2. Re</t>
+        </is>
+      </c>
+      <c r="H237" s="6" t="inlineStr">
+        <is>
+          <t>No. Nintendo of America requires applicants to be legally authorized to work in the United States and states that visa sponsorship is not available for internship positions. International students with valid CPT authoriz</t>
+        </is>
+      </c>
       <c r="I237" s="6" t="inlineStr">
         <is>
-          <t>Yes. Recruiters begin screening in late September; most offers go out October–December</t>
+          <t>No. Hard December 1 deadline with batch review. Offers in January, all candidates notified by February</t>
         </is>
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>$25–$48/hr depending on role and degree level; WHQ interns get housing stipends of $3,000–$6,500</t>
+          <t>Summer 2027 postings: $30–$35/hr main program (UX, Business Intelligence and IT at $35); $45/hr NTD software engineering contract roles; plus housing/travel sup</t>
         </is>
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 23 US postings live as of October 1, 2026 (first posted September 1). Undergraduate postings end October 18 to November 1, 2026; graduate postings November 30 to December 7, 2026 (rolling)</t>
+          <t>Open: 14 summer 2027 postings went live October 19, 2026 and list December 1, 2026 as the application deadline; 7 NTD software engineering roles posted October 28 to 29 print no deadline (checked October 30, 2026)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>Nintendo</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -13754,12 +13762,12 @@
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (NTD)  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Data Science Intern (Master's)  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>careers.nintendo.com/</t>
+          <t>careers.nordstrom.com/</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
@@ -13769,34 +13777,34 @@
       </c>
       <c r="G238" s="6" t="inlineStr">
         <is>
-          <t>Nintendo’s funnel is structured and predictable, running roughly 3 to 4 months from application to offer: 1. Apply at careers.nintendo.com with a resume, cover letter showing Nintendo brand knowledge, and the Internship Questionnaire. Design roles require a portfolio. Submit before December 1. 2. Re</t>
+          <t>You apply on careers.nordstrom.com, complete a HireVue on-demand video interview, take an online coding assessment (for tech roles), then have virtual interviews with hiring managers and team members. For merchandising tracks, expect a business-case exercise. For summer 2027, the postings anticipate</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
         <is>
-          <t>No. Nintendo of America requires applicants to be legally authorized to work in the United States and states that visa sponsorship is not available for internship positions. International students with valid CPT authoriz</t>
+          <t>Not available. Nordstrom is unable to sponsor visas or work authorizations for internship roles</t>
         </is>
       </c>
       <c r="I238" s="6" t="inlineStr">
         <is>
-          <t>No. Hard December 1 deadline with batch review. Offers in January, all candidates notified by February</t>
+          <t xml:space="preserve">No. Nordstrom uses batch review. Applications are screened after the October 12 to 18, 2026 window; most summer 2027 postings print interviews in November 2026 </t>
         </is>
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>$25/hr (marketing, UX, CSR) to $40/hr (NTD software engineering) + housing/travel support</t>
+          <t>Summer 2027 postings print fixed hourly rates (October 15, 2026): $25 for Merchandising, Fashion Design and Technical Apparel Design; $32 for Supply Chain Opera</t>
         </is>
       </c>
       <c r="K238" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open ~October 2026, closing December 1, 2026 (documented pattern; not yet posted)</t>
+          <t>Closed: October 12 to 18, 2026 for summer 2027 (published on Nordstrom's careers site; the Finance posting prints Monday, 10/12 through Sunday, 10/18). Seven postings were live on October 15, 2026, all posted October 12; none was open on October 21, 2026. Most postings print November 2026 interviews and decisions by January 2027; Finance prints January 2027 interviews and February 2027 decisions</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Notion</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -13806,17 +13814,17 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – June 2027</t>
         </is>
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Data Science Intern (Master's)  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern; Software Engineer, AI Intern; Data Science Intern; Mobile Engineer Intern  (4 of 5 tracks)</t>
         </is>
       </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>careers.nordstrom.com/</t>
+          <t>notion.com/careers</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
@@ -13826,34 +13834,34 @@
       </c>
       <c r="G239" s="6" t="inlineStr">
         <is>
-          <t>You apply on careers.nordstrom.com, complete a HireVue on-demand video interview, take an online coding assessment (for tech roles), then have virtual interviews with hiring managers and team members. For merchandising tracks, expect a business-case exercise. For summer 2027, the postings anticipate</t>
+          <t>Four rounds: a 30- to 60-minute recruiter screen, a 60-minute CoderPad assessment where you build a basic text editor, a 4-hour team interview block with coding, system design, and an AI-enabled round, and a 45-minute leadership conversation. The process averages 29 days.</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
         <is>
-          <t>Not available. Nordstrom is unable to sponsor visas or work authorizations for internship roles</t>
+          <t>Not available. Notion states this position is not eligible for work visa sponsorship. Applicants must be authorized to work in the US without sponsorship</t>
         </is>
       </c>
       <c r="I239" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">No. Nordstrom uses batch review. Applications are screened after the October 12 to 18, 2026 window; most summer 2027 postings print interviews in November 2026 </t>
+          <t>Yes. Notion reviews applications on a rolling basis and pulls postings once seats fill. There is no priority or final deadline. Apply the week a listing goes li</t>
         </is>
       </c>
       <c r="J239" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 postings print fixed hourly rates (October 15, 2026): $25 for Merchandising, Fashion Design and Technical Apparel Design; $32 for Supply Chain Opera</t>
+          <t>$57/hr for Bachelor's, $61/hr for Master's (SWE track). Data Science: $55/hr Bachelor's, $59/hr Master's. Housing stipend of $3,333/month. Equity included (Noti</t>
         </is>
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>Closed: October 12 to 18, 2026 for summer 2027 (published on Nordstrom's careers site; the Finance posting prints Monday, 10/12 through Sunday, 10/18). Seven postings were live on October 15, 2026, all posted October 12; none was open on October 21, 2026. Most postings print November 2026 interviews and decisions by January 2027; Finance prints January 2027 interviews and February 2027 decisions</t>
+          <t>OPEN NOW. Four intern roles are live as of October 1, 2026: Software Engineer Intern (Summer 2027), Software Engineer Intern (Winter 2027), Data Science Intern (Winter 2027), and Software Engineer Intern, Mobile (Winter 2027, posted September 24). No fixed deadlines — Notion reviews rolling and pulls listings once seats fill</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>Notion</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
@@ -13863,17 +13871,17 @@
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – June 2027</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Software Engineer, AI Intern; Data Science Intern; Mobile Engineer Intern  (4 of 5 tracks)</t>
+          <t>Digital &amp; Technology (DDIT)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>notion.com/careers</t>
+          <t>novartis.com/us-en/careers/early-talent</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
@@ -13883,34 +13891,34 @@
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>Four rounds: a 30- to 60-minute recruiter screen, a 60-minute CoderPad assessment where you build a basic text editor, a 4-hour team interview block with coding, system design, and an AI-enabled round, and a 45-minute leadership conversation. The process averages 29 days.</t>
+          <t>Typically 4–5 stages over 6–10 weeks: a digital assessment via Pymetrics or HireVue (behavioral and cognitive, 60–90 minutes), a recruiter phone screen (20–30 minutes), a hiring manager interview (45–60 minutes, technical and behavioral), and a panel or assessment center (group exercises or back-to-</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
         <is>
-          <t>Not available. Notion states this position is not eligible for work visa sponsorship. Applicants must be authorized to work in the US without sponsorship</t>
+          <t>It depends on the program. The PRISM postbaccalaureate program explicitly requires US Citizenship or Green Card. The Summer of Science program requires eligibility to work in the United States, so CPT or OPT may qualify.</t>
         </is>
       </c>
       <c r="I240" s="6" t="inlineStr">
         <is>
-          <t>Yes. Notion reviews applications on a rolling basis and pulls postings once seats fill. There is no priority or final deadline. Apply the week a listing goes li</t>
+          <t>Yes for most tracks. Research programs (Summer of Science, PRISM) have hard deadlines in early December (December 8 in the last cycle). Rotational programs have</t>
         </is>
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>$57/hr for Bachelor's, $61/hr for Master's (SWE track). Data Science: $55/hr Bachelor's, $59/hr Master's. Housing stipend of $3,333/month. Equity included (Noti</t>
+          <t>$26–$47/hr depending on level and location; Reddit reports $35–$40/hr as typical for big pharma interns. Summer of Science adds housing, travel, and health insu</t>
         </is>
       </c>
       <c r="K240" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Four intern roles are live as of October 1, 2026: Software Engineer Intern (Summer 2027), Software Engineer Intern (Winter 2027), Data Science Intern (Winter 2027), and Software Engineer Intern, Mobile (Winter 2027, posted September 24). No fixed deadlines — Notion reviews rolling and pulls listings once seats fill</t>
+          <t>Not open yet as of October 6, 2026: no US internships on Novartis's Workday board, and the Summer of Science portal still shows only last cycle's round (September 8 to December 8, 2025). Now expected late October 2026 through January 2027, varies by track (projected, lower confidence; the expected September opening did not happen)</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
@@ -13920,17 +13928,17 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>Digital &amp; Technology (DDIT)  (1 of 6 tracks)</t>
+          <t>Software Engineer (SWE)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>novartis.com/us-en/careers/early-talent</t>
+          <t>palantir.com/careers/open-positions/</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
@@ -13940,34 +13948,34 @@
       </c>
       <c r="G241" s="6" t="inlineStr">
         <is>
-          <t>Typically 4–5 stages over 6–10 weeks: a digital assessment via Pymetrics or HireVue (behavioral and cognitive, 60–90 minutes), a recruiter phone screen (20–30 minutes), a hiring manager interview (45–60 minutes, technical and behavioral), and a panel or assessment center (group exercises or back-to-</t>
+          <t>Palantir's interview funnel runs 4–5 stages over approximately 3–4 weeks from OA to offer. The process is technical but distinctive: the Decomposition round has no equivalent at other major tech companies. 1. Apply at palantir.com/careers or via the Lever job board . Upload a PDF resume and answer a</t>
         </is>
       </c>
       <c r="H241" s="6" t="inlineStr">
         <is>
-          <t>It depends on the program. The PRISM postbaccalaureate program explicitly requires US Citizenship or Green Card. The Summer of Science program requires eligibility to work in the United States, so CPT or OPT may qualify.</t>
+          <t>Yes. Palantir accepts CPT for internships and sponsors OPT/STEM OPT for new grad roles. However, some roles (especially USG and defense-focused positions) require US security clearance, which typically excludes visa hold</t>
         </is>
       </c>
       <c r="I241" s="6" t="inlineStr">
         <is>
-          <t>Yes for most tracks. Research programs (Summer of Science, PRISM) have hard deadlines in early December (December 8 in the last cycle). Rotational programs have</t>
+          <t>Yes. 70–80% of interview invitations go to applicants who submit by mid-October</t>
         </is>
       </c>
       <c r="J241" s="6" t="inlineStr">
         <is>
-          <t>$26–$47/hr depending on level and location; Reddit reports $35–$40/hr as typical for big pharma interns. Summer of Science adds housing, travel, and health insu</t>
+          <t>$60.58/hr + $2,500–$3,500/mo housing stipend + relocation</t>
         </is>
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>Not open yet as of October 6, 2026: no US internships on Novartis's Workday board, and the Summer of Science portal still shows only last cycle's round (September 8 to December 8, 2025). Now expected late October 2026 through January 2027, varies by track (projected, lower confidence; the expected September opening did not happen)</t>
+          <t>Open now for summer 2027: 30 US internship postings live on Palantir's Lever board on October 6, 2026 (rolling review, no published deadline; most interview invitations go to applicants who submit by mid-October)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
@@ -13977,17 +13985,17 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – June 2027</t>
         </is>
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer (SWE)  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Software Engineer Intern (Unit 42); Data Science / AI Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>palantir.com/careers/open-positions/</t>
+          <t>jobs.paloaltonetworks.com/en/early-in-career</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
@@ -13997,34 +14005,34 @@
       </c>
       <c r="G242" s="6" t="inlineStr">
         <is>
-          <t>Palantir's interview funnel runs 4–5 stages over approximately 3–4 weeks from OA to offer. The process is technical but distinctive: the Decomposition round has no equivalent at other major tech companies. 1. Apply at palantir.com/careers or via the Lever job board . Upload a PDF resume and answer a</t>
+          <t>You apply, do a 20 to 30 minute recruiter phone screen, take a 60 to 90 minute technical assessment on HackerRank or CodeSignal (2 to 3 LeetCode-medium problems with possible security twists), go through 1 to 2 technical interviews, then a 45 to 60 minute behavioral/hiring manager final. Average tim</t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
         <is>
-          <t>Yes. Palantir accepts CPT for internships and sponsors OPT/STEM OPT for new grad roles. However, some roles (especially USG and defense-focused positions) require US security clearance, which typically excludes visa hold</t>
+          <t>U.S. work authorization required. F-1 CPT available; OPT with STEM extension supported; H-1B for full-time transitions</t>
         </is>
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>Yes. 70–80% of interview invitations go to applicants who submit by mid-October</t>
+          <t>Yes, confirmed. Approximately 70% of positions are filled in the first 6 to 8 weeks. Apply within the first 2 to 3 weeks of a posting</t>
         </is>
       </c>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>$60.58/hr + $2,500–$3,500/mo housing stipend + relocation</t>
+          <t>SWE intern $35 to $45/hr ($43/hr verified on Levels.fyi); Security Research $52 to $55/hr. Housing/relocation stipend $8,000 lump sum</t>
         </is>
       </c>
       <c r="K242" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: 30 US internship postings live on Palantir's Lever board on October 6, 2026 (rolling review, no published deadline; most interview invitations go to applicants who submit by mid-October)</t>
+          <t>Not confirmed for summer 2027 as of October 11, 2026: 24 US intern postings were listed on Palo Alto Networks' Workday job board and accepting applications, but none names a summer 2027 term. All 24 show posting dates between January 24 and February 3, 2026. The earlier estimate of early August 2026 came from the prior cycle</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -14034,17 +14042,17 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – June 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Software Engineer Intern (Unit 42); Data Science / AI Intern  (3 of 6 tracks)</t>
+          <t>Digital / Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>jobs.paloaltonetworks.com/en/early-in-career</t>
+          <t>pfizer.com/en/about/careers/pfizer-futures</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
@@ -14054,34 +14062,30 @@
       </c>
       <c r="G243" s="6" t="inlineStr">
         <is>
-          <t>You apply, do a 20 to 30 minute recruiter phone screen, take a 60 to 90 minute technical assessment on HackerRank or CodeSignal (2 to 3 LeetCode-medium problems with possible security twists), go through 1 to 2 technical interviews, then a 45 to 60 minute behavioral/hiring manager final. Average tim</t>
-        </is>
-      </c>
-      <c r="H243" s="6" t="inlineStr">
-        <is>
-          <t>U.S. work authorization required. F-1 CPT available; OPT with STEM extension supported; H-1B for full-time transitions</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Pfizer's funnel has two to three interview levels, and the process typically runs 4 to 8 weeks from application to final decision: 1. Apply through the Pfizer Futures page , which links to the Atrium application portal (summer 2027 window: October 5 to November 8, 2026). Pfizer's Workday board does </t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr"/>
       <c r="I243" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Approximately 70% of positions are filled in the first 6 to 8 weeks. Apply within the first 2 to 3 weeks of a posting</t>
+          <t>Yes. "Applications reviewed on a rolling basis" (all JD postings). Community reports 70% of top-track slots go within first 45 days</t>
         </is>
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>SWE intern $35 to $45/hr ($43/hr verified on Levels.fyi); Security Research $52 to $55/hr. Housing/relocation stipend $8,000 lump sum</t>
+          <t>$26–$29/hr undergrad (official); $45–$52/hr PhD (community-reported). Housing stipend available for relocated interns</t>
         </is>
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed for summer 2027 as of October 11, 2026: 24 US intern postings were listed on Palo Alto Networks' Workday job board and accepting applications, but none names a summer 2027 term. All 24 show posting dates between January 24 and February 3, 2026. The earlier estimate of early August 2026 came from the prior cycle</t>
+          <t>Open now. Applications for summer 2027 opened October 5, 2026 and close November 8, 2026 (stated on the Pfizer Futures page and on every summer 2027 posting)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Physical Intelligence</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
@@ -14091,17 +14095,17 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>Digital / Technology  (1 of 6 tracks)</t>
+          <t>Research Intern (Robotics/AI); ML Infra Intern; Robotics SWE Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>pfizer.com/en/about/careers/pfizer-futures</t>
+          <t>jobs.ashbyhq.com/physicalintelligence</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
@@ -14111,30 +14115,34 @@
       </c>
       <c r="G244" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pfizer's funnel has two to three interview levels, and the process typically runs 4 to 8 weeks from application to final decision: 1. Apply through the Pfizer Futures page , which links to the Atrium application portal (summer 2027 window: October 5 to November 8, 2026). Pfizer's Workday board does </t>
-        </is>
-      </c>
-      <c r="H244" s="6" t="inlineStr"/>
+          <t>Physical Intelligence does not publish its interview process, but recruiter job descriptions mention structured interviewer calibration, and the loop for comparable robotics AI research roles follows a predictable pattern: 1. Apply on the Ashby ATS or pi.website/join-us . Upload your resume, publica</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>Likely supported for qualified candidates. CPT standard for F-1 students. Not explicitly confirmed on PI's website; verify during application</t>
+        </is>
+      </c>
       <c r="I244" s="6" t="inlineStr">
         <is>
-          <t>Yes. "Applications reviewed on a rolling basis" (all JD postings). Community reports 70% of top-track slots go within first 45 days</t>
+          <t>Yes (DEFAULT tier). No publicly documented rigid cycle. Positions are posted when research teams identify needs. Apply as soon as you see a listing</t>
         </is>
       </c>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>$26–$29/hr undergrad (official); $45–$52/hr PhD (community-reported). Housing stipend available for relocated interns</t>
+          <t>Estimated $8,000 to $12,000/month for PhD research interns; $5,000 to $7,000/month for MS. Robot Operator roles approximately $25/hr. Based on comparable SF rob</t>
         </is>
       </c>
       <c r="K244" s="6" t="inlineStr">
         <is>
-          <t>Open now. Applications for summer 2027 opened October 5, 2026 and close November 8, 2026 (stated on the Pfizer Futures page and on every summer 2027 posting)</t>
+          <t>Expected October to December 2026 for summer 2027 roles. Rolling review; likely closes January to February 2027. Projected from company growth trajectory and industry norms</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>Physical Intelligence</t>
+          <t>Pika</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
@@ -14149,12 +14157,12 @@
       </c>
       <c r="D245" s="6" t="inlineStr">
         <is>
-          <t>Research Intern (Robotics/AI); ML Infra Intern; Robotics SWE Intern  (3 of 5 tracks)</t>
+          <t>Summer Research Internship: Generative AI Features (prior cycle)  (1 of 4 tracks)</t>
         </is>
       </c>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/physicalintelligence</t>
+          <t>jobs.ashbyhq.com/pika</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
@@ -14164,34 +14172,34 @@
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>Physical Intelligence does not publish its interview process, but recruiter job descriptions mention structured interviewer calibration, and the loop for comparable robotics AI research roles follows a predictable pattern: 1. Apply on the Ashby ATS or pi.website/join-us . Upload your resume, publica</t>
+          <t>Based on TechPrep candidate reports, the process takes 3 to 5 weeks and includes a recruiter screen (15 to 30 minutes), a technical phone screen with live Python coding (about 60 minutes), and a virtual onsite with 4 to 5 rounds covering DSA, system design for GPU inference and video pipelines, a cr</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
         <is>
-          <t>Likely supported for qualified candidates. CPT standard for F-1 students. Not explicitly confirmed on PI's website; verify during application</t>
+          <t>Not explicitly confirmed. Likely supports OPT/CPT for F-1 students given Palo Alto location and funding level. Verify during recruiter screen</t>
         </is>
       </c>
       <c r="I245" s="6" t="inlineStr">
         <is>
-          <t>Yes (DEFAULT tier). No publicly documented rigid cycle. Positions are posted when research teams identify needs. Apply as soon as you see a listing</t>
+          <t>Yes. The current Research Intern listing offers flexible part-time and full-time terms with no fixed deadline, suggesting continuous hiring. Apply as soon as th</t>
         </is>
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
-          <t>Estimated $8,000 to $12,000/month for PhD research interns; $5,000 to $7,000/month for MS. Robot Operator roles approximately $25/hr. Based on comparable SF rob</t>
+          <t>$10,000/month (from prior BuiltInSF listing). Catered lunch and dinner in office. Weekly team events. Housing and transportation not included</t>
         </is>
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. Rolling review; likely closes January to February 2027. Projected from company growth trajectory and industry norms</t>
+          <t>Expected October to December 2026 for summer 2027 roles. Rolling intake; the previous summer listing was removed September 2025, suggesting a similar rhythm</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>Pika</t>
+          <t>Plaid</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
@@ -14201,17 +14209,17 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D246" s="6" t="inlineStr">
         <is>
-          <t>Summer Research Internship: Generative AI Features (prior cycle)  (1 of 4 tracks)</t>
+          <t>Software Engineering Intern; Data Science Intern; Security Engineering Intern  (3 of 5 tracks)</t>
         </is>
       </c>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/pika</t>
+          <t>plaid.com/careers/</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
@@ -14221,34 +14229,34 @@
       </c>
       <c r="G246" s="6" t="inlineStr">
         <is>
-          <t>Based on TechPrep candidate reports, the process takes 3 to 5 weeks and includes a recruiter screen (15 to 30 minutes), a technical phone screen with live Python coding (about 60 minutes), and a virtual onsite with 4 to 5 rounds covering DSA, system design for GPU inference and video pipelines, a cr</t>
+          <t>Four stages over 4 to 6 weeks: resume screening (15 to 20% advance), a 30-minute recruiter phone screen (non-technical), a 45- to 60-minute technical phone screen via CodeSignal or Karat (LeetCode Easy-Medium), and a 3- to 4-hour virtual onsite with two coding rounds, one behavioral round, sometimes</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed. Likely supports OPT/CPT for F-1 students given Palo Alto location and funding level. Verify during recruiter screen</t>
+          <t>F-1 CPT and OPT accepted (university-sponsored). Plaid does not directly sponsor visa status for interns. Full-time conversion supports OPT, STEM Extension, and H-1B</t>
         </is>
       </c>
       <c r="I246" s="6" t="inlineStr">
         <is>
-          <t>Yes. The current Research Intern listing offers flexible part-time and full-time terms with no fixed deadline, suggesting continuous hiring. Apply as soon as th</t>
+          <t>Yes, rolling with soft deadlines. Positions close by team as they fill. Applying in the first two weeks after a posting goes live yields the fastest responses (</t>
         </is>
       </c>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>$10,000/month (from prior BuiltInSF listing). Catered lunch and dinner in office. Weekly team events. Housing and transportation not included</t>
+          <t>$49 to $61 per hour ($8,500 to $10,500/month) depending on role and location. Housing stipend of $2,500 to $3,500/month. Sign-on/relocation of $9,000 to $10,000</t>
         </is>
       </c>
       <c r="K246" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. Rolling intake; the previous summer listing was removed September 2025, suggesting a similar rhythm</t>
+          <t>Not open as of October 6, 2026: no internship on Plaid's job board. The projected August 15, 2026 opening did not happen, and archived snapshots show no public intern posting in the summer 2026 cycle either, so no date can be projected with confidence</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
@@ -14263,12 +14271,12 @@
       </c>
       <c r="D247" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Data Science Intern; Security Engineering Intern  (3 of 5 tracks)</t>
+          <t>Cubist Quantitative Researcher; Cubist Quantitative Developer; Technology – Software Engineer; Data Engineer (Market Intelligence); AI Analyst  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>plaid.com/careers/</t>
+          <t>careers.point72.com/?experience=internships</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
@@ -14278,34 +14286,34 @@
       </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
-          <t>Four stages over 4 to 6 weeks: resume screening (15 to 20% advance), a 30-minute recruiter phone screen (non-technical), a 45- to 60-minute technical phone screen via CodeSignal or Karat (LeetCode Easy-Medium), and a 3- to 4-hour virtual onsite with two coding rounds, one behavioral round, sometimes</t>
+          <t>The summer 2028 US posting (live October 22, 2026) lists the order as application, essays and resume, then an invited case study, then an online assessment and virtual one-on-one interviews. It allows one Academy application globally and prohibits any GenAI use on the application. The five stages be</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT and OPT accepted (university-sponsored). Plaid does not directly sponsor visa status for interns. Full-time conversion supports OPT, STEM Extension, and H-1B</t>
+          <t>Yes. Point72 sponsors CPT, OPT, and H-1B visas. The firm had approximately 150 visa approvals in FY2025. That said, the process is selective, and third-party estimates suggest roughly 30 to 40% odds for Academy graduates</t>
         </is>
       </c>
       <c r="I247" s="6" t="inlineStr">
         <is>
-          <t>Yes, rolling with soft deadlines. Positions close by team as they fill. Applying in the first two weeks after a posting goes live yields the fastest responses (</t>
+          <t>Yes. No set deadline; candidates reviewed as they apply until the program is at capacity</t>
         </is>
       </c>
       <c r="J247" s="6" t="inlineStr">
         <is>
-          <t>$49 to $61 per hour ($8,500 to $10,500/month) depending on role and location. Housing stipend of $2,500 to $3,500/month. Sign-on/relocation of $9,000 to $10,000</t>
+          <t>Academy: $120K–$140K annual base, prorated (summer 2028 US posting, live October 22, 2026; no signing bonus listed); Cubist Summer 2027 Quantitative Research in</t>
         </is>
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>Not open as of October 6, 2026: no internship on Plaid's job board. The projected August 15, 2026 opening did not happen, and archived snapshots show no public intern posting in the summer 2026 cycle either, so no date can be projected with confidence</t>
+          <t>US Academy, summer 2028: open now, posted October 19, 2026, with no set deadline (the summer 2027 posting went live in early December 2025 and closed by early May 2026). Also open for summer 2027: Investment Services Internship (New York/Stamford), four New York roles posted October 14, 2026 (Fundamental Researcher, Canvas; Sector Analyst; Software Engineer; MS/PhD Data Scientist), Cubist and Poin</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>Raymond James</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -14320,12 +14328,12 @@
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>Cubist Quantitative Researcher; Cubist Quantitative Developer; Technology – Software Engineer; Data Engineer (Market Intelligence); AI Analyst  (5 of 6 tracks)</t>
+          <t>Information Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>careers.point72.com/?experience=internships</t>
+          <t>raymondjames.wd1.myworkdayjobs.com/RaymondJamesEarlyCareers</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
@@ -14335,34 +14343,34 @@
       </c>
       <c r="G248" s="6" t="inlineStr">
         <is>
-          <t>The summer 2028 US posting (live October 22, 2026) lists the order as application, essays and resume, then an invited case study, then an online assessment and virtual one-on-one interviews. It allows one Academy application globally and prohibits any GenAI use on the application. The five stages be</t>
+          <t>Raymond James runs a five-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through the Raymond James Workday portal with your resume, cover letter, and transcripts. Raymond James posts separate listings per division, so choose your strongest</t>
         </is>
       </c>
       <c r="H248" s="6" t="inlineStr">
         <is>
-          <t>Yes. Point72 sponsors CPT, OPT, and H-1B visas. The firm had approximately 150 visa approvals in FY2025. That said, the process is selective, and third-party estimates suggest roughly 30 to 40% odds for Academy graduates</t>
+          <t>No. Raymond James does not offer visa sponsorship for internships. Applicants must be legally authorized to work in the U.S. without visa sponsorship now or in the future, including beyond OPT/EAD. International students</t>
         </is>
       </c>
       <c r="I248" s="6" t="inlineStr">
         <is>
-          <t>Yes. No set deadline; candidates reviewed as they apply until the program is at capacity</t>
+          <t>Yes. Raymond James reviews applications on a rolling basis; apply within the first 2–3 weeks</t>
         </is>
       </c>
       <c r="J248" s="6" t="inlineStr">
         <is>
-          <t>Academy: $120K–$140K annual base, prorated (summer 2028 US posting, live October 22, 2026; no signing bonus listed); Cubist Summer 2027 Quantitative Research in</t>
+          <t>$72,000–$95,000 annualized by division (IB Summer Analyst ~$95,000; general intern ~$72,000)</t>
         </is>
       </c>
       <c r="K248" s="6" t="inlineStr">
         <is>
-          <t>US Academy, summer 2028: open now, posted October 19, 2026, with no set deadline (the summer 2027 posting went live in early December 2025 and closed by early May 2026). Also open for summer 2027: Investment Services Internship (New York/Stamford), four New York roles posted October 14, 2026 (Fundamental Researcher, Canvas; Sector Analyst; Software Engineer; MS/PhD Data Scientist), Cubist and Poin</t>
+          <t>Open now for summer 2027: IB Summer Analyst roles posting group by group on the Raymond James Early Careers Workday portal (Chicago Financial Services Oct 5, Charlotte Consumer Oct 12, McLean Diversified Industrials Oct 15, 2026; McLean closes Oct 22). The September 11 wave (St. Petersburg M&amp;A, Capital Markets, Equity Research) is already down. Summer 2028: Sophomore IB Bootcamp open since October</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>Raymond James</t>
+          <t>RBC Capital Markets</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
@@ -14372,17 +14380,17 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>Information Technology  (1 of 6 tracks)</t>
+          <t>QTS (Quantitative Technology &amp; Strategy)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>raymondjames.wd1.myworkdayjobs.com/RaymondJamesEarlyCareers</t>
+          <t>rbc.wd3.myworkdayjobs.com/RBCEARLYTALENT1</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
@@ -14392,34 +14400,34 @@
       </c>
       <c r="G249" s="6" t="inlineStr">
         <is>
-          <t>Raymond James runs a five-stage funnel, and the rolling timeline means each stage can start within days of the previous one: 1. Apply through the Raymond James Workday portal with your resume, cover letter, and transcripts. Raymond James posts separate listings per division, so choose your strongest</t>
+          <t>You apply, complete a HireVue video assessment (four to five questions, zero retakes, 15 to 25% pass rate), then a 60-minute first-round phone or video interview mixing behavioral and technical questions, and finally a Superday with VPs, Directors, and MDs. Candidates report offers within one to two</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
         <is>
-          <t>No. Raymond James does not offer visa sponsorship for internships. Applicants must be legally authorized to work in the U.S. without visa sponsorship now or in the future, including beyond OPT/EAD. International students</t>
+          <t>Strong track record: 273 H-1B filings with 100% approval rate. CPT supported for F-1 students</t>
         </is>
       </c>
       <c r="I249" s="6" t="inlineStr">
         <is>
-          <t>Yes. Raymond James reviews applications on a rolling basis; apply within the first 2–3 weeks</t>
+          <t>Yes. RBC reviews applications on a rolling basis and fills interview slots continuously. Apply in the first one to two weeks for the best odds</t>
         </is>
       </c>
       <c r="J249" s="6" t="inlineStr">
         <is>
-          <t>$72,000–$95,000 annualized by division (IB Summer Analyst ~$95,000; general intern ~$72,000)</t>
+          <t>$2,115/week (~$110,000 annualized) for U.S. IB/CM roles. $7,000 housing stipend, dinner stipend after 7 PM, car service after 9 PM, relocation up to $2,000 dome</t>
         </is>
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: IB Summer Analyst roles posting group by group on the Raymond James Early Careers Workday portal (Chicago Financial Services Oct 5, Charlotte Consumer Oct 12, McLean Diversified Industrials Oct 15, 2026; McLean closes Oct 22). The September 11 wave (St. Petersburg M&amp;A, Capital Markets, Equity Research) is already down. Summer 2028: Sophomore IB Bootcamp open since October</t>
+          <t>Summer 2028 IB Summer Analyst: NOT YET OPEN. Applications for summer 2028 expected to open around Oct to Nov 2026 and close around late Jan to early Mar 2027 (last two cycles: posted Sep 27, 2024 and Nov 3, 2025; closed Mar 3, 2025 and Jan 30, 2026). Still open for summer 2027: COO Operations, Quantitative Technology Services (Jersey City, Raleigh) and Global Markets Quantitative Trading Summer An</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>RBC Capital Markets</t>
+          <t>Regeneron</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
@@ -14429,17 +14437,17 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>QTS (Quantitative Technology &amp; Strategy)  (1 of 6 tracks)</t>
+          <t>Data Science &amp; Bioinformatics; Technology/IT (AI/ML); Supply Chain &amp; Engineering  (3 of 12 tracks)</t>
         </is>
       </c>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>rbc.wd3.myworkdayjobs.com/RBCEARLYTALENT1</t>
+          <t>careers.regeneron.com/en/career-pathways/early-careers/</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
@@ -14449,34 +14457,34 @@
       </c>
       <c r="G250" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a HireVue video assessment (four to five questions, zero retakes, 15 to 25% pass rate), then a 60-minute first-round phone or video interview mixing behavioral and technical questions, and finally a Superday with VPs, Directors, and MDs. Candidates report offers within one to two</t>
+          <t>The standard process is: ATS resume screen, recruiter phone screen (20 to 30 minutes), HireVue on-demand video interview (AI-scored on transcript alignment), then a live hiring manager interview via MS Teams (45 to 60 minutes). Select roles add an in-person final round at Tarrytown with 3 to 5 inter</t>
         </is>
       </c>
       <c r="H250" s="6" t="inlineStr">
         <is>
-          <t>Strong track record: 273 H-1B filings with 100% approval rate. CPT supported for F-1 students</t>
+          <t>No. Regeneron does not directly sponsor visas for interns. International students on F-1 visas must secure CPT (Curricular Practical Training) authorization through their university before the internship starts. You'll n</t>
         </is>
       </c>
       <c r="I250" s="6" t="inlineStr">
         <is>
-          <t>Yes. RBC reviews applications on a rolling basis and fills interview slots continuously. Apply in the first one to two weeks for the best odds</t>
+          <t>Yes. Positions filled as qualified candidates are identified within the window</t>
         </is>
       </c>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>$2,115/week (~$110,000 annualized) for U.S. IB/CM roles. $7,000 housing stipend, dinner stipend after 7 PM, car service after 9 PM, relocation up to $2,000 dome</t>
+          <t>$17.90–$50.90/hr by degree level + $1,400/mo housing stipend + free meals and gym</t>
         </is>
       </c>
       <c r="K250" s="6" t="inlineStr">
         <is>
-          <t>Summer 2028 IB Summer Analyst: NOT YET OPEN. Applications for summer 2028 expected to open around Oct to Nov 2026 and close around late Jan to early Mar 2027 (last two cycles: posted Sep 27, 2024 and Nov 3, 2025; closed Mar 3, 2025 and Jan 30, 2026). Still open for summer 2027: COO Operations, Quantitative Technology Services (Jersey City, Raleigh) and Global Markets Quantitative Trading Summer An</t>
+          <t>For summer 2027: 2027 Co-op (22 reqs) and MBA BuiLD postings open since October 1 to 2, 2026. Standard 10-week summer intern postings not yet live as of October 6, 2026; expected October to November 2026, later than last cycle</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>Regeneron</t>
+          <t>Relativity Space</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
@@ -14491,12 +14499,12 @@
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>Data Science &amp; Bioinformatics; Technology/IT (AI/ML); Supply Chain &amp; Engineering  (3 of 12 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Test Engineering; Robotics Software  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>careers.regeneron.com/en/career-pathways/early-careers/</t>
+          <t>relativityspace.com/internships</t>
         </is>
       </c>
       <c r="F251" s="7" t="inlineStr">
@@ -14506,34 +14514,34 @@
       </c>
       <c r="G251" s="6" t="inlineStr">
         <is>
-          <t>The standard process is: ATS resume screen, recruiter phone screen (20 to 30 minutes), HireVue on-demand video interview (AI-scored on transcript alignment), then a live hiring manager interview via MS Teams (45 to 60 minutes). Select roles add an in-person final round at Tarrytown with 3 to 5 inter</t>
+          <t>The standard process has 2–3 stages: a 30-minute recruiter phone screen covering background, projects, and career goals; a 45–60-minute technical interview specific to your role (coding for SWE, materials analysis for manufacturing, thermodynamics for propulsion); and a behavioral interview assessin</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
         <is>
-          <t>No. Regeneron does not directly sponsor visas for interns. International students on F-1 visas must secure CPT (Curricular Practical Training) authorization through their university before the internship starts. You'll n</t>
+          <t>Most engineering roles require U.S. Person status under ITAR regulations (U.S. citizen, permanent resident, refugee, or asylee). F-1 visa holders are generally ineligible for hardware roles involving flight software, pro</t>
         </is>
       </c>
       <c r="I251" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified within the window</t>
+          <t>Yes. Positions filled as qualified candidates are identified; earlier applications get more attention</t>
         </is>
       </c>
       <c r="J251" s="6" t="inlineStr">
         <is>
-          <t>$17.90–$50.90/hr by degree level + $1,400/mo housing stipend + free meals and gym</t>
+          <t>Posted ranges for current intern roles: $39 to $44/hr for software and data science, $34 to $42/hr for engineering, $27 to $30/hr for design and policy roles; i</t>
         </is>
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>For summer 2027: 2027 Co-op (22 reqs) and MBA BuiLD postings open since October 1 to 2, 2026. Standard 10-week summer intern postings not yet live as of October 6, 2026; expected October to November 2026, later than last cycle</t>
+          <t>Open now: 30 US intern postings live as of October 6, 2026 (first batch listed July 10, 2026, more added through October 5). Rolling review, no published deadline; peak interviews expected October 2026 to February 2027</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>Relativity Space</t>
+          <t>Replicate</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
@@ -14548,12 +14556,12 @@
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Test Engineering; Robotics Software  (4 of 6 tracks)</t>
+          <t>SWE Intern — Workers AI / AI Platform; SWE Intern — Cloudflare Workers; ML Engineering Intern; SWE Intern — Infrastructure / Systems</t>
         </is>
       </c>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>relativityspace.com/internships</t>
+          <t>cloudflare.com/careers/early-talent/</t>
         </is>
       </c>
       <c r="F252" s="7" t="inlineStr">
@@ -14563,34 +14571,34 @@
       </c>
       <c r="G252" s="6" t="inlineStr">
         <is>
-          <t>The standard process has 2–3 stages: a 30-minute recruiter phone screen covering background, projects, and career goals; a 45–60-minute technical interview specific to your role (coding for SWE, materials analysis for manufacturing, thermodynamics for propulsion); and a behavioral interview assessin</t>
+          <t xml:space="preserve">All applications go through Cloudflare's 1111 Interns program. The funnel spans 3 to 4 weeks from application to decision: 1. Apply on cloudflare.com/careers/early-talent . Search for internship roles mentioning Workers AI, AI Platform, or Machine Learning. Postings typically go live around October </t>
         </is>
       </c>
       <c r="H252" s="6" t="inlineStr">
         <is>
-          <t>Most engineering roles require U.S. Person status under ITAR regulations (U.S. citizen, permanent resident, refugee, or asylee). F-1 visa holders are generally ineligible for hardware roles involving flight software, pro</t>
+          <t>F-1 CPT supported for US intern positions. International hub offices in London, Lisbon, and Bengaluru available for non-US students</t>
         </is>
       </c>
       <c r="I252" s="6" t="inlineStr">
         <is>
-          <t>Yes. Positions filled as qualified candidates are identified; earlier applications get more attention</t>
+          <t>Yes. Cloudflare reviews applications on a rolling basis. Interviews run November through February with offers December through March. Apply as early as possible</t>
         </is>
       </c>
       <c r="J252" s="6" t="inlineStr">
         <is>
-          <t>Posted ranges for current intern roles: $39 to $44/hr for software and data science, $34 to $42/hr for engineering, $27 to $30/hr for design and policy roles; i</t>
+          <t>$45 to $53 per hour (~$7,800 to $9,200/month) for US engineering interns. $1,000/month housing stipend plus relocation support. No Replicate-specific data exist</t>
         </is>
       </c>
       <c r="K252" s="6" t="inlineStr">
         <is>
-          <t>Open now: 30 US intern postings live as of October 6, 2026 (first batch listed July 10, 2026, more added through October 5). Rolling review, no published deadline; peak interviews expected October 2026 to February 2027</t>
+          <t>Expected mid-October 2026 for summer 2027 roles. Rolling review through February 2027. Projected from the 2026 cycle</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>Replicate</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
@@ -14600,17 +14608,17 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–November 2026</t>
         </is>
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>SWE Intern — Workers AI / AI Platform; SWE Intern — Cloudflare Workers; ML Engineering Intern; SWE Intern — Infrastructure / Systems</t>
+          <t>Software Engineering Intern; Mechanical Engineering Intern; Manufacturing Engineering Intern; AI, ML &amp; Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>cloudflare.com/careers/early-talent/</t>
+          <t>careers.rivian.com/students</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
@@ -14620,34 +14628,34 @@
       </c>
       <c r="G253" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">All applications go through Cloudflare's 1111 Interns program. The funnel spans 3 to 4 weeks from application to decision: 1. Apply on cloudflare.com/careers/early-talent . Search for internship roles mentioning Workers AI, AI Platform, or Machine Learning. Postings typically go live around October </t>
+          <t>You apply online, complete a 30- to 45-minute recruiter phone screen, then face 1 to 2 technical interview rounds (coding on HackerRank for SWE or engineering fundamentals for hardware) plus a behavioral round and a hiring-manager chat. Glassdoor rates difficulty at 2.8 out of 5.</t>
         </is>
       </c>
       <c r="H253" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for US intern positions. International hub offices in London, Lisbon, and Bengaluru available for non-US students</t>
+          <t>Valid work authorization required. F-1 CPT supported; international students reviewed case-by-case. Some roles carry export-control restrictions</t>
         </is>
       </c>
       <c r="I253" s="6" t="inlineStr">
         <is>
-          <t>Yes. Cloudflare reviews applications on a rolling basis. Interviews run November through February with offers December through March. Apply as early as possible</t>
+          <t>Yes. Rivian reviews applications and schedules interviews on a rolling basis from October through March. Early applicants face the most open seats</t>
         </is>
       </c>
       <c r="J253" s="6" t="inlineStr">
         <is>
-          <t>$45 to $53 per hour (~$7,800 to $9,200/month) for US engineering interns. $1,000/month housing stipend plus relocation support. No Replicate-specific data exist</t>
+          <t>$25 to $51 per hour depending on role and location. Palo Alto SWE interns report $51/hr ($8,840/mo). Housing stipend of $2,000 to $2,500/mo plus relocation assi</t>
         </is>
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>Expected mid-October 2026 for summer 2027 roles. Rolling review through February 2027. Projected from the 2026 cycle</t>
+          <t>Summer 2027 is starting to post: the first role (Finance Analyst intern, Palo Alto) went live 2 October 2026, and most summer 2027 roles are expected later this fall (October to November 2026, projected from prior-cycle timing). Interviews run through March 2027</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Rockstar Games</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
@@ -14662,12 +14670,12 @@
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern; Mechanical Engineering Intern; Manufacturing Engineering Intern; AI, ML &amp; Data Science Intern  (4 of 6 tracks)</t>
+          <t>Data Analytics / Data Science; Hardware Engineering  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>careers.rivian.com/students</t>
+          <t>job-boards.greenhouse.io/rsgur</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
@@ -14677,34 +14685,34 @@
       </c>
       <c r="G254" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a 30- to 45-minute recruiter phone screen, then face 1 to 2 technical interview rounds (coding on HackerRank for SWE or engineering fundamentals for hardware) plus a behavioral round and a hiring-manager chat. Glassdoor rates difficulty at 2.8 out of 5.</t>
+          <t>The process varies by role but typically spans 3 to 5 rounds over approximately 60 days. For Data Science interns, expect an initial 30-minute Zoom screening, a multi-day take-home data analysis project, follow-up technical discussions, and a final 60-minute panel interview. Game Design roles includ</t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr">
         <is>
-          <t>Valid work authorization required. F-1 CPT supported; international students reviewed case-by-case. Some roles carry export-control restrictions</t>
+          <t>US-based listings require eligibility to work in the US, which typically means US citizens, permanent residents, or students with valid work authorization such as CPT or OPT for F-1 visa holders. Rockstar doesn't confirm</t>
         </is>
       </c>
       <c r="I254" s="6" t="inlineStr">
         <is>
-          <t>Yes. Rivian reviews applications and schedules interviews on a rolling basis from October through March. Early applicants face the most open seats</t>
+          <t>Not confirmed. Some roles close within weeks of posting; others stay open until spring. Early application is strongly recommended</t>
         </is>
       </c>
       <c r="J254" s="6" t="inlineStr">
         <is>
-          <t>$25 to $51 per hour depending on role and location. Palo Alto SWE interns report $51/hr ($8,840/mo). Housing stipend of $2,000 to $2,500/mo plus relocation assi</t>
+          <t>$34/hr confirmed for NYC Data Science (Greenhouse listing); Glassdoor range $26–$47/hr across roles</t>
         </is>
       </c>
       <c r="K254" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 is starting to post: the first role (Finance Analyst intern, Palo Alto) went live 2 October 2026, and most summer 2027 roles are expected later this fall (October to November 2026, projected from prior-cycle timing). Interviews run through March 2027</t>
+          <t>Expected October–November 2026 for summer 2027 (based on documented Summer 2026 cycle; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>Rockstar Games</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
@@ -14714,17 +14722,17 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>October–November 2026</t>
+          <t>October 2026 – June 2027</t>
         </is>
       </c>
       <c r="D255" s="6" t="inlineStr">
         <is>
-          <t>Data Analytics / Data Science; Hardware Engineering  (2 of 6 tracks)</t>
+          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical / Multi-Disciplined Engineer Intern; Systems Engineering Intern / Co-op; Digital Technology / Cyber, Finance &amp; Supply Chain</t>
         </is>
       </c>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/rsgur</t>
+          <t>careers.rtx.com/global/en/campus</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
@@ -14734,34 +14742,34 @@
       </c>
       <c r="G255" s="6" t="inlineStr">
         <is>
-          <t>The process varies by role but typically spans 3 to 5 rounds over approximately 60 days. For Data Science interns, expect an initial 30-minute Zoom screening, a multi-day take-home data analysis project, follow-up technical discussions, and a final 60-minute panel interview. Game Design roles includ</t>
+          <t>A recruiter screen, often a HireVue recorded video, then a behavioral hiring-manager or Zoom interview (sometimes a panel or a single director), a possible in-person step, and an offer. It is behavioral-heavy (conflict, leadership, teamwork, datasets) with no documented timed coding assessment. Turn</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr">
         <is>
-          <t>US-based listings require eligibility to work in the US, which typically means US citizens, permanent residents, or students with valid work authorization such as CPT or OPT for F-1 visa holders. Rockstar doesn't confirm</t>
+          <t>No. US citizenship is required for nearly all US roles (ITAR-controlled defense work); software reqs are tagged "No H1B Sponsorship." A minority of roles require an active SECRET clearance on day one</t>
         </is>
       </c>
       <c r="I255" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed. Some roles close within weeks of posting; others stay open until spring. Early application is strongly recommended</t>
+          <t>Yes, confirmed. Each req states the window closes "approximately 40 days from the date the notice was posted," subject to candidate flow and business need. In p</t>
         </is>
       </c>
       <c r="J255" s="6" t="inlineStr">
         <is>
-          <t>$34/hr confirmed for NYC Data Science (Greenhouse listing); Glassdoor range $26–$47/hr across roles</t>
+          <t>No single official hourly figure; Levels.fyi (community) shows roughly $27–43/hr by business unit, role, location, and class standing (RTX SWE interns average ~</t>
         </is>
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>Expected October–November 2026 for summer 2027 (based on documented Summer 2026 cycle; not yet posted)</t>
+          <t>OPEN NOW, short windows. 240 US intern and co-op reqs live on October 2, 2026 (195 titled 2027, 112 titled Summer 2027), about 150 of them posted September 28 to October 2 in a second wave after the first one of September 2 to 11; half of a 30-req September sample carried a Workday end date only 5 to 6 days after posting, and the new wave repeats that (end dates 4 to 33 days out in the reqs we ope</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
@@ -14771,17 +14779,17 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – June 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineering Intern (primary); Mechanical Engineering Intern; Software Engineer Intern; Electrical / Multi-Disciplined Engineer Intern; Systems Engineering Intern / Co-op; Digital Technology / Cyber, Finance &amp; Supply Chain</t>
+          <t>ML Research Intern; Software Engineering Intern (inferred); Applied ML / Computer Vision Intern (inferred)  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>careers.rtx.com/global/en/campus</t>
+          <t>runway.com/careers</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
@@ -14791,34 +14799,34 @@
       </c>
       <c r="G256" s="6" t="inlineStr">
         <is>
-          <t>A recruiter screen, often a HireVue recorded video, then a behavioral hiring-manager or Zoom interview (sometimes a panel or a single director), a possible in-person step, and an offer. It is behavioral-heavy (conflict, leadership, teamwork, datasets) with no documented timed coding assessment. Turn</t>
+          <t>The process typically takes 2 to 4 weeks (average 20 days on Glassdoor) and includes a recruiter screen (30 minutes), technical assessment (45 to 60 minutes of coding in Python and TypeScript), virtual onsite (pair programming, code review, systems design), and leadership meetings with senior leader</t>
         </is>
       </c>
       <c r="H256" s="6" t="inlineStr">
         <is>
-          <t>No. US citizenship is required for nearly all US roles (ITAR-controlled defense work); software reqs are tagged "No H1B Sponsorship." A minority of roles require an active SECRET clearance on day one</t>
+          <t>H-1B sponsorship confirmed for full-time roles. CPT/OPT likely supported for international students (standard for AI companies at this tier). No explicit visa restriction stated</t>
         </is>
       </c>
       <c r="I256" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Each req states the window closes "approximately 40 days from the date the notice was posted," subject to candidate flow and business need. In p</t>
+          <t>Likely yes. No fixed deadline exists. Glassdoor data (80 interviews) shows an average of 20 days from application to decision. Apply as soon as a posting appear</t>
         </is>
       </c>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>No single official hourly figure; Levels.fyi (community) shows roughly $27–43/hr by business unit, role, location, and class standing (RTX SWE interns average ~</t>
+          <t>Indeed estimates approximately $4,015/month ($3,734 to $4,497 range), though this is based on limited data. Full-time research roles pay $320K+ median, suggesti</t>
         </is>
       </c>
       <c r="K256" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW, short windows. 240 US intern and co-op reqs live on October 2, 2026 (195 titled 2027, 112 titled Summer 2027), about 150 of them posted September 28 to October 2 in a second wave after the first one of September 2 to 11; half of a 30-req September sample carried a Workday end date only 5 to 6 days after posting, and the new wave repeats that (end dates 4 to 33 days out in the reqs we ope</t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed public deadline; roles fill on a rolling basis. Projected from general AI startup hiring patterns</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
@@ -14828,17 +14836,17 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>ML Research Intern; Software Engineering Intern (inferred); Applied ML / Computer Vision Intern (inferred)  (3 of 4 tracks)</t>
+          <t>Software Engineer Intern; Hardware Engineering Intern; Data Science / ML (via SWE posting)  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>runway.com/careers</t>
+          <t>samsara.com/company/careers/emerging-talent</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
@@ -14848,34 +14856,30 @@
       </c>
       <c r="G257" s="6" t="inlineStr">
         <is>
-          <t>The process typically takes 2 to 4 weeks (average 20 days on Glassdoor) and includes a recruiter screen (30 minutes), technical assessment (45 to 60 minutes of coding in Python and TypeScript), virtual onsite (pair programming, code review, systems design), and leadership meetings with senior leader</t>
-        </is>
-      </c>
-      <c r="H257" s="6" t="inlineStr">
-        <is>
-          <t>H-1B sponsorship confirmed for full-time roles. CPT/OPT likely supported for international students (standard for AI companies at this tier). No explicit visa restriction stated</t>
-        </is>
-      </c>
+          <t>Four stages over about a month: an online assessment (CoderPad or Codility, four to five timed LeetCode-style DSA questions, roughly one hour), a live technical coding round (one question plus a follow-up, with a light behavioral warm-up), a final behavioral round with a senior engineer, then an off</t>
+        </is>
+      </c>
+      <c r="H257" s="6" t="inlineStr"/>
       <c r="I257" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No fixed deadline exists. Glassdoor data (80 interviews) shows an average of 20 days from application to decision. Apply as soon as a posting appear</t>
+          <t>Yes. Samsara hires on a rolling basis until positions are filled, with a firm November 26 backstop. Apply early: strong candidates interview before the deadline</t>
         </is>
       </c>
       <c r="J257" s="6" t="inlineStr">
         <is>
-          <t>Indeed estimates approximately $4,015/month ($3,734 to $4,497 range), though this is based on limited data. Full-time research roles pay $320K+ median, suggesti</t>
+          <t>$61.90/hr (official current SF SWE intern posting), with relocation assistance. The Account Development Representative Intern postings in Atlanta and Phoenix, l</t>
         </is>
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed public deadline; roles fill on a rolling basis. Projected from general AI startup hiring patterns</t>
+          <t>Open now and accepting applications (as of October 21, 2026). Applications officially close November 26 at 11:59pm ET (year inferred 2026); cohort finalized late November / early December.</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
@@ -14885,17 +14889,17 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – May 2027</t>
         </is>
       </c>
       <c r="D258" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Hardware Engineering Intern; Data Science / ML (via SWE posting)  (3 of 6 tracks)</t>
+          <t>SRA AI/ML Research Intern; SRA Software Engineering Intern; SAS Engineering Summer Intern; SDS Cloud/AI Intern  (4 of 7 tracks)</t>
         </is>
       </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>samsara.com/company/careers/emerging-talent</t>
+          <t>samsung.com/us/careers/internships/</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
@@ -14905,30 +14909,34 @@
       </c>
       <c r="G258" s="6" t="inlineStr">
         <is>
-          <t>Four stages over about a month: an online assessment (CoderPad or Codility, four to five timed LeetCode-style DSA questions, roughly one hour), a live technical coding round (one question plus a follow-up, with a light behavioral warm-up), a final behavioral round with a senior engineer, then an off</t>
-        </is>
-      </c>
-      <c r="H258" s="6" t="inlineStr"/>
+          <t>There is no standardized coding assessment across Samsung. Samsung Research America interviews focus on your research publications, design choices, and a project proposal with a potential mentor. Samsung Electronics America uses a short skills test plus two interviews covering behavioral and technic</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>SRA JDs state applicants need legal US work authorization or visa sponsorship eligibility. Samsung has a track record of H-1B sponsorship for full-time roles; F-1 CPT is the typical intern path</t>
+        </is>
+      </c>
       <c r="I258" s="6" t="inlineStr">
         <is>
-          <t>Yes. Samsara hires on a rolling basis until positions are filled, with a firm November 26 backstop. Apply early: strong candidates interview before the deadline</t>
+          <t xml:space="preserve">Semi-rolling. Samsung encourages checking year-round, but most positions fill during defined windows. SAS had a firm deadline (~late March) in the prior cycle; </t>
         </is>
       </c>
       <c r="J258" s="6" t="inlineStr">
         <is>
-          <t>$61.90/hr (official current SF SWE intern posting), with relocation assistance. The Account Development Representative Intern postings in Atlanta and Phoenix, l</t>
+          <t>$27 to $63/hr depending on division and role. SWE ~$62/hr (Levels.fyi); SRA research $48 to $63/hr (official JD); SAS engineering ~$30/hr. Housing stipend and r</t>
         </is>
       </c>
       <c r="K258" s="6" t="inlineStr">
         <is>
-          <t>Open now and accepting applications (as of October 21, 2026). Applications officially close November 26 at 11:59pm ET (year inferred 2026); cohort finalized late November / early December.</t>
+          <t>Partly open: on October 11, 2026, Samsung Austin Semiconductor (SAS) listed one 2027 Summer Internship posting, posted August 4, 2026, with a printed end date of May 31, 2027. Samsung Research America (SRA) and Samsung Electronics America (SEA) listed no intern roles that day; the SRA internship board carried only a general posting for sharing a resume. SRA research reqs ~Oct 2026 and SEA summer p</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
@@ -14938,17 +14946,17 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – May 2027</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D259" s="6" t="inlineStr">
         <is>
-          <t>SRA AI/ML Research Intern; SRA Software Engineering Intern; SAS Engineering Summer Intern; SDS Cloud/AI Intern  (4 of 7 tracks)</t>
+          <t>Digital / Technology; Data Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>samsung.com/us/careers/internships/</t>
+          <t>join.sephora.com/careers?query=intern</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
@@ -14958,34 +14966,34 @@
       </c>
       <c r="G259" s="6" t="inlineStr">
         <is>
-          <t>There is no standardized coding assessment across Samsung. Samsung Research America interviews focus on your research publications, design choices, and a project proposal with a potential mentor. Samsung Electronics America uses a short skills test plus two interviews covering behavioral and technic</t>
+          <t>Typically 3 to 4 stages over roughly 22 days: an on-demand video interview with behavioral and beauty-passion questions, a recruiter phone screen, a hiring manager interview, and for competitive tracks a final panel or Superday with senior leaders. Some roles include a 60 to 90 minute online assessm</t>
         </is>
       </c>
       <c r="H259" s="6" t="inlineStr">
         <is>
-          <t>SRA JDs state applicants need legal US work authorization or visa sponsorship eligibility. Samsung has a track record of H-1B sponsorship for full-time roles; F-1 CPT is the typical intern path</t>
+          <t>No. Sephora does not sponsor H-1B visas for internships. International students must have independent work authorization through CPT or OPT. You must be authorized to work in the U.S. without employer sponsorship.</t>
         </is>
       </c>
       <c r="I259" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Semi-rolling. Samsung encourages checking year-round, but most positions fill during defined windows. SAS had a firm deadline (~late March) in the prior cycle; </t>
+          <t>Yes. Applications reviewed on a rolling basis; last cycle gave priority consideration by mid-October</t>
         </is>
       </c>
       <c r="J259" s="6" t="inlineStr">
         <is>
-          <t>$27 to $63/hr depending on division and role. SWE ~$62/hr (Levels.fyi); SRA research $48 to $63/hr (official JD); SAS engineering ~$30/hr. Housing stipend and r</t>
+          <t>$22–$25/hr depending on role (~$9,000 total at top rate)</t>
         </is>
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>Partly open: on October 11, 2026, Samsung Austin Semiconductor (SAS) listed one 2027 Summer Internship posting, posted August 4, 2026, with a printed end date of May 31, 2027. Samsung Research America (SRA) and Samsung Electronics America (SEA) listed no intern roles that day; the SRA internship board carried only a general posting for sharing a resume. SRA research reqs ~Oct 2026 and SEA summer p</t>
+          <t>OPEN. Six US summer 2027 internships posted October 27, 2026 on join.sephora.com (San Francisco, Salt Lake City, Maryland and remote); program runs June 14 to August 20, 2027 for students graduating in 2027 or 2028. No closing date printed; last cycle closed by mid-November, and more tracks may post</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Sierra Space</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
@@ -14995,17 +15003,17 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D260" s="6" t="inlineStr">
         <is>
-          <t>Digital / Technology; Data Analytics  (2 of 6 tracks)</t>
+          <t>Aerospace Engineer Intern; Mechanical Engineer Intern; Propulsion Engineer Intern; Systems Engineer Intern; Electrical Engineer Intern; Software Engineer Intern</t>
         </is>
       </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>join.sephora.com/careers?query=intern</t>
+          <t>sierraspace.com/careers/internship/</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr">
@@ -15015,34 +15023,34 @@
       </c>
       <c r="G260" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 stages over roughly 22 days: an on-demand video interview with behavioral and beauty-passion questions, a recruiter phone screen, a hiring manager interview, and for competitive tracks a final panel or Superday with senior leaders. Some roles include a 60 to 90 minute online assessm</t>
+          <t>Sierra Space does not publish a formal, round-by-round intern interview structure, so the steps below combine the official application flow with community-reported interview signal (Reddit r/aerospace): treat the interview specifics as directional, not official: 1. Monitor the internship page (summe</t>
         </is>
       </c>
       <c r="H260" s="6" t="inlineStr">
         <is>
-          <t>No. Sephora does not sponsor H-1B visas for internships. International students must have independent work authorization through CPT or OPT. You must be authorized to work in the U.S. without employer sponsorship.</t>
+          <t>Not available. Because of ITAR / export-control work, F-1 visa sponsorship is not offered for internships, and non-US-persons are effectively screened out. Security-clearance eligibility is also required</t>
         </is>
       </c>
       <c r="I260" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis; last cycle gave priority consideration by mid-October</t>
+          <t xml:space="preserve">Partially. Individual postings state the deadline stays open "until a qualified pool of candidates is identified," so roles close once filled. Apply as soon as </t>
         </is>
       </c>
       <c r="J260" s="6" t="inlineStr">
         <is>
-          <t>$22–$25/hr depending on role (~$9,000 total at top rate)</t>
+          <t>$31.00/hour on the live 2027 Systems Engineer Intern posting ($30.00/hour on the 2026 Colorado Engineering Intern posting). Community sources vary: Glassdoor ~$</t>
         </is>
       </c>
       <c r="K260" s="6" t="inlineStr">
         <is>
-          <t>OPEN. Six US summer 2027 internships posted October 27, 2026 on join.sephora.com (San Francisco, Salt Lake City, Maryland and remote); program runs June 14 to August 20, 2027 for students graduating in 2027 or 2028. No closing date printed; last cycle closed by mid-November, and more tracks may post</t>
+          <t>Open for summer 2027: the first req (2027 Systems Engineer Intern, Colorado) posted October 1, 2026, about a month later than the September pattern. More function reqs expected through fall 2026, with a deadline expected around December 2026 (not confirmed)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>Sierra Space</t>
+          <t>Snap</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
@@ -15057,12 +15065,12 @@
       </c>
       <c r="D261" s="6" t="inlineStr">
         <is>
-          <t>Aerospace Engineer Intern; Mechanical Engineer Intern; Propulsion Engineer Intern; Systems Engineer Intern; Electrical Engineer Intern; Software Engineer Intern</t>
+          <t>Software Engineer Intern; Machine Learning Engineering Intern  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E261" s="7" t="inlineStr">
         <is>
-          <t>sierraspace.com/careers/internship/</t>
+          <t>careers.snap.com/emerging-talent</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr">
@@ -15072,34 +15080,34 @@
       </c>
       <c r="G261" s="6" t="inlineStr">
         <is>
-          <t>Sierra Space does not publish a formal, round-by-round intern interview structure, so the steps below combine the official application flow with community-reported interview signal (Reddit r/aerospace): treat the interview specifics as directional, not official: 1. Monitor the internship page (summe</t>
+          <t>You apply online, complete a recruiter phone screen (20 to 30 minutes), do 1 to 2 technical phone screens on CoderPad, then attend SnapFest, a full-day virtual onsite with 2 to 3 coding rounds, system design, and a behavioral round. Decisions typically come 1 to 2 weeks after SnapFest.</t>
         </is>
       </c>
       <c r="H261" s="6" t="inlineStr">
         <is>
-          <t>Not available. Because of ITAR / export-control work, F-1 visa sponsorship is not offered for internships, and non-US-persons are effectively screened out. Security-clearance eligibility is also required</t>
+          <t>CPT supported for F-1 students. OPT and 24-month STEM OPT extension available. H-1B sponsorship limited and lottery-dependent</t>
         </is>
       </c>
       <c r="I261" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially. Individual postings state the deadline stays open "until a qualified pool of candidates is identified," so roles close once filled. Apply as soon as </t>
+          <t>Yes. Snap reviews applications on a rolling basis, so apply the week a summer 2027 role posts. Last cycle, most seats were filled by mid-November</t>
         </is>
       </c>
       <c r="J261" s="6" t="inlineStr">
         <is>
-          <t>$31.00/hour on the live 2027 Systems Engineer Intern posting ($30.00/hour on the 2026 Colorado Engineering Intern posting). Community sources vary: Glassdoor ~$</t>
+          <t>$50 to $68 per hour depending on role and location. SWE median around $52/hr; Research interns around $58/hr. Housing stipend of $1,200 to $2,500/month (Levels.</t>
         </is>
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>Open for summer 2027: the first req (2027 Systems Engineer Intern, Colorado) posted October 1, 2026, about a month later than the September pattern. More function reqs expected through fall 2026, with a deadline expected around December 2026 (not confirmed)</t>
+          <t>Not yet posted for summer 2027 software, ML, PM or design roles as of Oct 22, 2026, later than last cycle's late August to early September opening and mid-October priority date. One 2027 Generative Media Research Intern (Los Angeles, graduate program, PhD preferred) posted Oct 14, 2026. Check the board weekly</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>Snap</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
@@ -15114,12 +15122,12 @@
       </c>
       <c r="D262" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Machine Learning Engineering Intern  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern; Software Engineer Intern (AI/ML); Data Engineer Intern; Data Science Intern  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E262" s="7" t="inlineStr">
         <is>
-          <t>careers.snap.com/emerging-talent</t>
+          <t>careers.snowflake.com/us/en/university</t>
         </is>
       </c>
       <c r="F262" s="7" t="inlineStr">
@@ -15129,34 +15137,34 @@
       </c>
       <c r="G262" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (20 to 30 minutes), do 1 to 2 technical phone screens on CoderPad, then attend SnapFest, a full-day virtual onsite with 2 to 3 coding rounds, system design, and a behavioral round. Decisions typically come 1 to 2 weeks after SnapFest.</t>
+          <t>You apply, complete a 30-minute recruiter phone screen, take a 90- to 120-minute HackerRank OA with 2 to 3 medium-to-hard problems, then two technical coding interviews plus a behavioral round. Offers come within 3 to 5 business days of the final interview. Total timeline: 6 to 10 weeks.</t>
         </is>
       </c>
       <c r="H262" s="6" t="inlineStr">
         <is>
-          <t>CPT supported for F-1 students. OPT and 24-month STEM OPT extension available. H-1B sponsorship limited and lottery-dependent</t>
+          <t>F-1 CPT supported for internships, OPT for new graduates. STEM-designated employer (24-month OPT extension eligible). No J-1 sponsorship</t>
         </is>
       </c>
       <c r="I262" s="6" t="inlineStr">
         <is>
-          <t>Yes. Snap reviews applications on a rolling basis, so apply the week a summer 2027 role posts. Last cycle, most seats were filled by mid-November</t>
+          <t>Yes. Snowflake reviews applications on a rolling basis and extends offers as seats fill. Apply in the first two weeks of a posting for the best response rates</t>
         </is>
       </c>
       <c r="J262" s="6" t="inlineStr">
         <is>
-          <t>$50 to $68 per hour depending on role and location. SWE median around $52/hr; Research interns around $58/hr. Housing stipend of $1,200 to $2,500/month (Levels.</t>
+          <t>$55 per hour ($9,533 per month) for SWE interns per Levels.fyi. Housing stipend of $2,000 to $2,500 per month. Some offers include a relocation bonus of $500 to</t>
         </is>
       </c>
       <c r="K262" s="6" t="inlineStr">
         <is>
-          <t>Not yet posted for summer 2027 software, ML, PM or design roles as of Oct 22, 2026, later than last cycle's late August to early September opening and mid-October priority date. One 2027 Generative Media Research Intern (Los Angeles, graduate program, PhD preferred) posted Oct 14, 2026. Check the board weekly</t>
+          <t>Not open yet: no US summer 2027 intern postings were live on 1 October 2026. Prior cycles opened in early September, so this cycle is running late. Once postings appear, expect priority screening within the first two to three weeks (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
@@ -15171,12 +15179,12 @@
       </c>
       <c r="D263" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Software Engineer Intern (AI/ML); Data Engineer Intern; Data Science Intern  (4 of 6 tracks)</t>
+          <t>Technology (SWE / Data Engineering); Technology Analyst  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E263" s="7" t="inlineStr">
         <is>
-          <t>careers.snowflake.com/us/en/university</t>
+          <t>careers.southwestair.com/us/en/campus-reach</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
@@ -15186,34 +15194,34 @@
       </c>
       <c r="G263" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a 30-minute recruiter phone screen, take a 90- to 120-minute HackerRank OA with 2 to 3 medium-to-hard problems, then two technical coding interviews plus a behavioral round. Offers come within 3 to 5 business days of the final interview. Total timeline: 6 to 10 weeks.</t>
+          <t>It is an on-demand video interview with pre-set behavioral prompts and timed responses. The focus is entirely on culture fit, not technical skills. Southwest assesses alignment with their three core values: Warrior Spirit (resilience), Servant's Heart (service), and Fun-LUVing Attitude (positivity).</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT supported for internships, OPT for new graduates. STEM-designated employer (24-month OPT extension eligible). No J-1 sponsorship</t>
+          <t>Effectively no. Southwest requires unrestricted US work authorization without sponsorship. International students on F-1 visas using CPT or OPT are generally ineligible unless they hold separate permanent work authorizat</t>
         </is>
       </c>
       <c r="I263" s="6" t="inlineStr">
         <is>
-          <t>Yes. Snowflake reviews applications on a rolling basis and extends offers as seats fill. Apply in the first two weeks of a posting for the best response rates</t>
+          <t>Semi-rolling inside each fixed window. Southwest reviews on a rolling basis and may close early once the candidate pool is full</t>
         </is>
       </c>
       <c r="J263" s="6" t="inlineStr">
         <is>
-          <t>$55 per hour ($9,533 per month) for SWE interns per Levels.fyi. Housing stipend of $2,000 to $2,500 per month. Some offers include a relocation bonus of $500 to</t>
+          <t>$20–$30/hr + up to $2,000 housing stipend + free unlimited standby flights on all Southwest routes</t>
         </is>
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>Not open yet: no US summer 2027 intern postings were live on 1 October 2026. Prior cycles opened in early September, so this cycle is running late. Once postings appear, expect priority screening within the first two to three weeks (projected from prior cycle)</t>
+          <t>Open now for summer 2027: about 32 internships across all departments posted October 1, 2026. No closing date is published; last cycle the Tech and Revenue Management window ran 8 days (October 7 to 15, 2025), so expect these to close within days</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
@@ -15228,12 +15236,12 @@
       </c>
       <c r="D264" s="6" t="inlineStr">
         <is>
-          <t>Technology (SWE / Data Engineering); Technology Analyst  (2 of 6 tracks)</t>
+          <t>Engineering Intern; Software Engineering Intern; Graduate Engineer Intern  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E264" s="7" t="inlineStr">
         <is>
-          <t>careers.southwestair.com/us/en/campus-reach</t>
+          <t>spacex.com/careers/jobs/?keyword=internship</t>
         </is>
       </c>
       <c r="F264" s="7" t="inlineStr">
@@ -15243,34 +15251,34 @@
       </c>
       <c r="G264" s="6" t="inlineStr">
         <is>
-          <t>It is an on-demand video interview with pre-set behavioral prompts and timed responses. The focus is entirely on culture fit, not technical skills. Southwest assesses alignment with their three core values: Warrior Spirit (resilience), Servant's Heart (service), and Fun-LUVing Attitude (positivity).</t>
+          <t>SpaceX's interview funnel is technically demanding and project-depth-driven. The total process runs 4 to 12 weeks from application to offer, with Glassdoor reporting an average of 17 days for intern roles: 1. Apply at spacex.com/careers within 48 to 72 hours of a posting going live. Submit your resu</t>
         </is>
       </c>
       <c r="H264" s="6" t="inlineStr">
         <is>
-          <t>Effectively no. Southwest requires unrestricted US work authorization without sponsorship. International students on F-1 visas using CPT or OPT are generally ineligible unless they hold separate permanent work authorizat</t>
+          <t>No. SpaceX requires U.S. Person status under ITAR regulations. F-1 visa holders are ineligible regardless of CPT or OPT work authorization. H-1B holders are generally ineligible. SpaceX does not sponsor work visas for in</t>
         </is>
       </c>
       <c r="I264" s="6" t="inlineStr">
         <is>
-          <t>Semi-rolling inside each fixed window. Southwest reviews on a rolling basis and may close early once the candidate pool is full</t>
+          <t>Yes. No fixed cohort deadlines. Apply within 48–72 hours of a posting going live for best odds</t>
         </is>
       </c>
       <c r="J264" s="6" t="inlineStr">
         <is>
-          <t>$20–$30/hr + up to $2,000 housing stipend + free unlimited standby flights on all Southwest routes</t>
+          <t>$24.50–$40/hr by posting and academic level, as printed in the Summer 2027 postings listed on October 11, 2026: Engineering and Civil Engineering $28.00 to $30.</t>
         </is>
       </c>
       <c r="K264" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: about 32 internships across all departments posted October 1, 2026. No closing date is published; last cycle the Tech and Revenue Management window ran 8 days (October 7 to 15, 2025), so expect these to close within days</t>
+          <t>Open now for summer 2027: six Summer 2027 internship postings were listed on SpaceX's job board on October 11, 2026, each first published August 3, 2026. No closing date is printed; rolling admissions, positions fill as qualified candidates found</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>SpaceX</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
@@ -15285,12 +15293,12 @@
       </c>
       <c r="D265" s="6" t="inlineStr">
         <is>
-          <t>Engineering Intern; Software Engineering Intern; Graduate Engineer Intern  (3 of 6 tracks)</t>
+          <t>Software Engineering Intern (Backend/Full-Stack); C++ Software Engineer Intern; Solutions Engineer Intern; Security Engineering Intern; Data Science Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E265" s="7" t="inlineStr">
         <is>
-          <t>spacex.com/careers/jobs/?keyword=internship</t>
+          <t>careers.cisco.com/global/en/splunk</t>
         </is>
       </c>
       <c r="F265" s="7" t="inlineStr">
@@ -15300,34 +15308,34 @@
       </c>
       <c r="G265" s="6" t="inlineStr">
         <is>
-          <t>SpaceX's interview funnel is technically demanding and project-depth-driven. The total process runs 4 to 12 weeks from application to offer, with Glassdoor reporting an average of 17 days for intern roles: 1. Apply at spacex.com/careers within 48 to 72 hours of a posting going live. Submit your resu</t>
+          <t>A recruiter phone screen (15 to 30 minutes), then a Karat technical assessment (15-minute MCQ quiz plus 60-minute live coding), then a hiring manager behavioral interview (45 to 60 minutes). Some roles add a virtual onsite with 2 to 4 additional rounds. Total timeline is 3 to 5 weeks from first cont</t>
         </is>
       </c>
       <c r="H265" s="6" t="inlineStr">
         <is>
-          <t>No. SpaceX requires U.S. Person status under ITAR regulations. F-1 visa holders are ineligible regardless of CPT or OPT work authorization. H-1B holders are generally ineligible. SpaceX does not sponsor work visas for in</t>
+          <t>Roles available in US, Canada, UK, Germany, Poland, Australia, Japan, Singapore. US roles likely require valid work authorization (CPT for F-1 students)</t>
         </is>
       </c>
       <c r="I265" s="6" t="inlineStr">
         <is>
-          <t>Yes. No fixed cohort deadlines. Apply within 48–72 hours of a posting going live for best odds</t>
+          <t>Yes, confirmed. In prior cycles Splunk posted roles in early September and filled them progressively through February. The US posting listed on October 11, 2026</t>
         </is>
       </c>
       <c r="J265" s="6" t="inlineStr">
         <is>
-          <t>$24.50–$40/hr by posting and academic level, as printed in the Summer 2027 postings listed on October 11, 2026: Engineering and Civil Engineering $28.00 to $30.</t>
+          <t>SWE intern $42 to $60/hr ($7,280 to $10,400/mo) depending on location. Housing stipends $2,000 to $6,000 for select offices</t>
         </is>
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: six Summer 2027 internship postings were listed on SpaceX's job board on October 11, 2026, each first published August 3, 2026. No closing date is printed; rolling admissions, positions fill as qualified candidates found</t>
+          <t>Partly open: on October 11, 2026, one US Splunk intern posting was accepting applications on careers.cisco.com, Splunk Solutions Engineer (Intern) - United States, posted October 7, 2026. It names no summer and no closing date, and says applications are accepted until further notice. No Splunk-branded software engineering intern posting was listed that day. The earlier estimate of an early Septemb</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
@@ -15337,17 +15345,17 @@
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D266" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Backend/Full-Stack); C++ Software Engineer Intern; Solutions Engineer Intern; Security Engineering Intern; Data Science Intern  (5 of 6 tracks)</t>
+          <t>Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E266" s="7" t="inlineStr">
         <is>
-          <t>careers.cisco.com/global/en/splunk</t>
+          <t>apply.starbucks.com/careers?query=intern</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
@@ -15357,34 +15365,34 @@
       </c>
       <c r="G266" s="6" t="inlineStr">
         <is>
-          <t>A recruiter phone screen (15 to 30 minutes), then a Karat technical assessment (15-minute MCQ quiz plus 60-minute live coding), then a hiring manager behavioral interview (45 to 60 minutes). Some roles add a virtual onsite with 2 to 4 additional rounds. Total timeline is 3 to 5 weeks from first cont</t>
+          <t>You apply, complete a recruiter phone screen (15 to 20 minutes), then 2 to 3 behavioral interview rounds (45 to 60 minutes each) using the STAR method. Technology roles add a coding assessment. The total process spans 6 to 10 weeks. Glassdoor rates difficulty at 2.2 out of 5.</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr">
         <is>
-          <t>Roles available in US, Canada, UK, Germany, Poland, Australia, Japan, Singapore. US roles likely require valid work authorization (CPT for F-1 students)</t>
+          <t>Limited. CPT may be supported for F-1 students on a case-by-case basis, but most postings state sponsorship is not provided. Check the work-authorization line on each specific role</t>
         </is>
       </c>
       <c r="I266" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. In prior cycles Splunk posted roles in early September and filled them progressively through February. The US posting listed on October 11, 2026</t>
+          <t>Partially. In the prior cycle Starbucks reviewed applications on a priority basis through October, then continued on a rolling basis until positions were filled</t>
         </is>
       </c>
       <c r="J266" s="6" t="inlineStr">
         <is>
-          <t>SWE intern $42 to $60/hr ($7,280 to $10,400/mo) depending on location. Housing stipends $2,000 to $6,000 for select offices</t>
+          <t>$25 to $45 per hour depending on role and level. Technology roles $28 to $45 per hour (Levels.fyi reports $28/hr for SWE interns, Summer 2023). Corporate housin</t>
         </is>
       </c>
       <c r="K266" s="6" t="inlineStr">
         <is>
-          <t>Partly open: on October 11, 2026, one US Splunk intern posting was accepting applications on careers.cisco.com, Splunk Solutions Engineer (Intern) - United States, posted October 7, 2026. It names no summer and no closing date, and says applications are accepted until further notice. No Splunk-branded software engineering intern posting was listed that day. The earlier estimate of an early Septemb</t>
+          <t>Not posted as of October 11, 2026: no US internship posting was listed on apply.starbucks.com that day. The earlier estimate (late August 2026 opening, priority review through October 2026, some postings open through December 2026) was projected from the prior cycle. Starbucks’s internships page says applications open around fall each year</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
@@ -15394,17 +15402,17 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>Technology Intern  (1 of 6 tracks)</t>
+          <t>AI / Self-Driving (Autopilot); Software Engineering (Vehicle); Battery / Cell Engineering; Supply Chain Analytics  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E267" s="7" t="inlineStr">
         <is>
-          <t>apply.starbucks.com/careers?query=intern</t>
+          <t>tesla.com/careers/internships</t>
         </is>
       </c>
       <c r="F267" s="7" t="inlineStr">
@@ -15414,34 +15422,34 @@
       </c>
       <c r="G267" s="6" t="inlineStr">
         <is>
-          <t>You apply, complete a recruiter phone screen (15 to 20 minutes), then 2 to 3 behavioral interview rounds (45 to 60 minutes each) using the STAR method. Technology roles add a coding assessment. The total process spans 6 to 10 weeks. Glassdoor rates difficulty at 2.2 out of 5.</t>
+          <t>Typically 3 to 4 rounds: a recruiter phone screen (15 to 30 minutes), an online coding assessment via Codility (about 85 minutes, 2 to 3 LeetCode-Medium problems), a live technical interview (45 to 60 minutes), and a manager or final round. Non-SWE roles may replace the coding assessment with a proj</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr">
         <is>
-          <t>Limited. CPT may be supported for F-1 students on a case-by-case basis, but most postings state sponsorship is not provided. Check the work-authorization line on each specific role</t>
+          <t>Tesla accepts F-1 CPT and OPT for internships. You'll need to verify 40-hour-per-week work authorization for the on-site requirement. H-1B sponsorship for full-time roles after internship conversion is handled case by ca</t>
         </is>
       </c>
       <c r="I267" s="6" t="inlineStr">
         <is>
-          <t>Partially. In the prior cycle Starbucks reviewed applications on a priority basis through October, then continued on a rolling basis until positions were filled</t>
+          <t>Yes. Tesla reviews applications immediately upon submission and may recruit up to 4 months after posting</t>
         </is>
       </c>
       <c r="J267" s="6" t="inlineStr">
         <is>
-          <t>$25 to $45 per hour depending on role and level. Technology roles $28 to $45 per hour (Levels.fyi reports $28/hr for SWE interns, Summer 2023). Corporate housin</t>
+          <t>SWE $58.80/hr (Levels.fyi); AI/Self-Driving $48–$72/hr; manufacturing $20–$50/hr + housing $700–$3,000/mo</t>
         </is>
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>Not posted as of October 11, 2026: no US internship posting was listed on apply.starbucks.com that day. The earlier estimate (late August 2026 opening, priority review through October 2026, some postings open through December 2026) was projected from the prior cycle. Starbucks’s internships page says applications open around fall each year</t>
+          <t>Winter/Spring 2027 cohort open now (about 280 US listings live 1 October 2026, January 2027 start, minimum 12 weeks full time); summer 2027 postings have started (7 US listings live 1 October 2026, May/June 2027 start), more expected through November 2026 with peak hiring November 2026 through February 2027 (projected from prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
@@ -15456,12 +15464,12 @@
       </c>
       <c r="D268" s="6" t="inlineStr">
         <is>
-          <t>AI / Self-Driving (Autopilot); Software Engineering (Vehicle); Battery / Cell Engineering; Supply Chain Analytics  (4 of 6 tracks)</t>
+          <t>Embedded Software Engineering; Digital IC Design; Product/Test Engineering; Manufacturing/Process Engineering; Applications Engineering  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E268" s="7" t="inlineStr">
         <is>
-          <t>tesla.com/careers/internships</t>
+          <t>careers.ti.com/en/sites/CX/jobs?keyword=intern</t>
         </is>
       </c>
       <c r="F268" s="7" t="inlineStr">
@@ -15471,34 +15479,34 @@
       </c>
       <c r="G268" s="6" t="inlineStr">
         <is>
-          <t>Typically 3 to 4 rounds: a recruiter phone screen (15 to 30 minutes), an online coding assessment via Codility (about 85 minutes, 2 to 3 LeetCode-Medium problems), a live technical interview (45 to 60 minutes), and a manager or final round. Non-SWE roles may replace the coding assessment with a proj</t>
+          <t xml:space="preserve">TI's interview funnel is shorter than most tech companies, averaging 22 days from application to offer. But the technical content is domain-specific rather than algorithm-focused, so generic LeetCode prep will not help you here: 1. Apply at careers.ti.com with a resume. No cover letter is required. </t>
         </is>
       </c>
       <c r="H268" s="6" t="inlineStr">
         <is>
-          <t>Tesla accepts F-1 CPT and OPT for internships. You'll need to verify 40-hour-per-week work authorization for the on-site requirement. H-1B sponsorship for full-time roles after internship conversion is handled case by ca</t>
+          <t xml:space="preserve">Yes. For internships: CPT authorization from your school is sufficient (no employer petition needed). For full-time: TI actively sponsors H-1B visas and filed 122 petitions with 122 approved in FY2025. TN visas are also </t>
         </is>
       </c>
       <c r="I268" s="6" t="inlineStr">
         <is>
-          <t>Yes. Tesla reviews applications immediately upon submission and may recruit up to 4 months after posting</t>
+          <t>Yes. Applications reviewed on a rolling basis. First-come advantage is real; positions may fill before the soft November close</t>
         </is>
       </c>
       <c r="J268" s="6" t="inlineStr">
         <is>
-          <t>SWE $58.80/hr (Levels.fyi); AI/Self-Driving $48–$72/hr; manufacturing $20–$50/hr + housing $700–$3,000/mo</t>
+          <t>$28 to $47/hr depending on degree, role, and location, plus $2,300–$8,000 housing stipend</t>
         </is>
       </c>
       <c r="K268" s="6" t="inlineStr">
         <is>
-          <t>Winter/Spring 2027 cohort open now (about 280 US listings live 1 October 2026, January 2027 start, minimum 12 weeks full time); summer 2027 postings have started (7 US listings live 1 October 2026, May/June 2027 start), more expected through November 2026 with peak hiring November 2026 through February 2027 (projected from prior cycle)</t>
+          <t>Open now: 65 US intern reqs live on October 2, 2026, all posted September 1 to 28, 2026. 63 are titled without a year and print no close date (mostly degree-track engineering, software and business roles that appear to be for summer 2027, plus one Encore returnship and three SkillBridge roles); the other two are 2027-titled Manufacturing Technician (AAS/certificate) roles with Apply Before Novembe</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
@@ -15508,17 +15516,17 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D269" s="6" t="inlineStr">
         <is>
-          <t>Embedded Software Engineering; Digital IC Design; Product/Test Engineering; Manufacturing/Process Engineering; Applications Engineering  (5 of 6 tracks)</t>
+          <t>Information Technology Internship  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E269" s="7" t="inlineStr">
         <is>
-          <t>careers.ti.com/en/sites/CX/jobs?keyword=intern</t>
+          <t>jobs.tjx.com/global/en/studentsus</t>
         </is>
       </c>
       <c r="F269" s="7" t="inlineStr">
@@ -15528,34 +15536,30 @@
       </c>
       <c r="G269" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TI's interview funnel is shorter than most tech companies, averaging 22 days from application to offer. But the technical content is domain-specific rather than algorithm-focused, so generic LeetCode prep will not help you here: 1. Apply at careers.ti.com with a resume. No cover letter is required. </t>
-        </is>
-      </c>
-      <c r="H269" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Yes. For internships: CPT authorization from your school is sufficient (no employer petition needed). For full-time: TI actively sponsors H-1B visas and filed 122 petitions with 122 approved in FY2025. TN visas are also </t>
-        </is>
-      </c>
+          <t>Officially: a HireVue one-way video interview, then a case study, then behavioral interviews. The HireVue is about five recorded questions with roughly a minute to prep each, including an allocate-the-product scenario. The case study tests retail math, and the final round is often two interviewers f</t>
+        </is>
+      </c>
+      <c r="H269" s="6" t="inlineStr"/>
       <c r="I269" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications reviewed on a rolling basis. First-come advantage is real; positions may fill before the soft November close</t>
+          <t>Yes (community-reported). TJX interviews merchandising interns as applications arrive, and many roles fill before the formal deadline. Apply the first week post</t>
         </is>
       </c>
       <c r="J269" s="6" t="inlineStr">
         <is>
-          <t>$28 to $47/hr depending on degree, role, and location, plus $2,300–$8,000 housing stipend</t>
+          <t>No official rate published. Community and Levels.fyi data: merchandising interns ~$21–$26/hr; software-engineer interns ~$22/hr. Housing and relocation are unre</t>
         </is>
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>Open now: 65 US intern reqs live on October 2, 2026, all posted September 1 to 28, 2026. 63 are titled without a year and print no close date (mostly degree-track engineering, software and business roles that appear to be for summer 2027, plus one Encore returnship and three SkillBridge roles); the other two are 2027-titled Manufacturing Technician (AAS/certificate) roles with Apply Before Novembe</t>
+          <t xml:space="preserve">PARTLY CLOSED for summer 2027 (verified October 6, 2026 on TJX's Workday board). Still live: the Merchandising Internship Program (posted September 1, 2026; listed through December 31), Logistics (Supply Chain), Distribution Operations (20 US sites, listed through November 2) and Retail Management (Stores) in Phoenix and Tucson. Closed: Financial Accounting and Financial Analyst (deadline October </t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Together AI</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
@@ -15565,17 +15569,17 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D270" s="6" t="inlineStr">
         <is>
-          <t>Information Technology Internship  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Security Engineer Intern  (2 of 7 tracks)</t>
         </is>
       </c>
       <c r="E270" s="7" t="inlineStr">
         <is>
-          <t>jobs.tjx.com/global/en/studentsus</t>
+          <t>job-boards.greenhouse.io/togetherai</t>
         </is>
       </c>
       <c r="F270" s="7" t="inlineStr">
@@ -15585,30 +15589,30 @@
       </c>
       <c r="G270" s="6" t="inlineStr">
         <is>
-          <t>Officially: a HireVue one-way video interview, then a case study, then behavioral interviews. The HireVue is about five recorded questions with roughly a minute to prep each, including an allocate-the-product scenario. The case study tests retail math, and the final round is often two interviewers f</t>
+          <t xml:space="preserve">For research interns, expect a PyTorch-based coding screen focused on ML-systems problems rather than traditional LeetCode. For engineering interns, expect coding interviews on distributed systems and full-stack development. The overall difficulty is rated 8 out of 10, comparable to Nvidia core GPU </t>
         </is>
       </c>
       <c r="H270" s="6" t="inlineStr"/>
       <c r="I270" s="6" t="inlineStr">
         <is>
-          <t>Yes (community-reported). TJX interviews merchandising interns as applications arrive, and many roles fill before the formal deadline. Apply the first week post</t>
+          <t>Not stated. Positions close once filled; no fixed deadline published for most roles</t>
         </is>
       </c>
       <c r="J270" s="6" t="inlineStr">
         <is>
-          <t>No official rate published. Community and Levels.fyi data: merchandising interns ~$21–$26/hr; software-engineer interns ~$22/hr. Housing and relocation are unre</t>
+          <t>$58–$70/hr across the six Summer 2027 postings listed on October 11, 2026: $58/hr for Software Engineer Intern and Software Development In Test Intern, $58 to $</t>
         </is>
       </c>
       <c r="K270" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTLY CLOSED for summer 2027 (verified October 6, 2026 on TJX's Workday board). Still live: the Merchandising Internship Program (posted September 1, 2026; listed through December 31), Logistics (Supply Chain), Distribution Operations (20 US sites, listed through November 2) and Retail Management (Stores) in Phoenix and Tucson. Closed: Financial Accounting and Financial Analyst (deadline October </t>
+          <t>Open now for summer 2027: Six Summer 2027 intern postings were listed on Together AI's Greenhouse board on October 11, 2026, all first published September 18, 2026. None of the six prints an application deadline.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>Together AI</t>
+          <t>TSMC</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
@@ -15618,17 +15622,17 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D271" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Security Engineer Intern  (2 of 7 tracks)</t>
+          <t>Software / IT (Phoenix)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E271" s="7" t="inlineStr">
         <is>
-          <t>job-boards.greenhouse.io/togetherai</t>
+          <t>careers.tsmc.com/en_US/</t>
         </is>
       </c>
       <c r="F271" s="7" t="inlineStr">
@@ -15638,30 +15642,34 @@
       </c>
       <c r="G271" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">For research interns, expect a PyTorch-based coding screen focused on ML-systems problems rather than traditional LeetCode. For engineering interns, expect coding interviews on distributed systems and full-stack development. The overall difficulty is rated 8 out of 10, comparable to Nvidia core GPU </t>
-        </is>
-      </c>
-      <c r="H271" s="6" t="inlineStr"/>
+          <t>TSMC's hiring funnel depends on whether you are applying for an engineering or software role, and the split matters: 1. Find your track at careers.tsmc.com and filter by US locations plus "intern." Arizona alone has 12+ engineering tracks, so read the specific JD carefully before applying. 2. Submit</t>
+        </is>
+      </c>
+      <c r="H271" s="6" t="inlineStr">
+        <is>
+          <t>No. TSMC explicitly excludes H-1B, OPT, O-1, and TN visa holders from US internship positions. Applicants must have long-term work authorization without any current or future employer sponsorship. Arizona postings use sl</t>
+        </is>
+      </c>
       <c r="I271" s="6" t="inlineStr">
         <is>
-          <t>Not stated. Positions close once filled; no fixed deadline published for most roles</t>
+          <t>Partially. Window is defined but review within it is rolling; apply early</t>
         </is>
       </c>
       <c r="J271" s="6" t="inlineStr">
         <is>
-          <t>$58–$70/hr across the six Summer 2027 postings listed on October 11, 2026: $58/hr for Software Engineer Intern and Software Development In Test Intern, $58 to $</t>
+          <t>$23 to $48/hr depending on location, role, and degree (Camas WA entry to San Jose PhD research)</t>
         </is>
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: Six Summer 2027 intern postings were listed on Together AI's Greenhouse board on October 11, 2026, all first published September 18, 2026. None of the six prints an application deadline.</t>
+          <t>Applications for summer 2027 expected to open October to December 2026 and close by March 2027 (earliest AZ postings live as of July 2026; projected from prior cycles)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>TSMC</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
@@ -15671,17 +15679,17 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D272" s="6" t="inlineStr">
         <is>
-          <t>Software / IT (Phoenix)  (1 of 6 tracks)</t>
+          <t>Software Engineering; Data Science  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E272" s="7" t="inlineStr">
         <is>
-          <t>careers.tsmc.com/en_US/</t>
+          <t>jobs.uber.com/en/teams/emerging-talent/</t>
         </is>
       </c>
       <c r="F272" s="7" t="inlineStr">
@@ -15691,34 +15699,34 @@
       </c>
       <c r="G272" s="6" t="inlineStr">
         <is>
-          <t>TSMC's hiring funnel depends on whether you are applying for an engineering or software role, and the split matters: 1. Find your track at careers.tsmc.com and filter by US locations plus "intern." Arizona alone has 12+ engineering tracks, so read the specific JD carefully before applying. 2. Submit</t>
+          <t>Uber’s SWE internship funnel runs 4 stages, averaging about 28 days from application to decision: 1. Submit your application at jobs.uber.com with a resume. List 3 to 5 city preferences in order. No cover letter required. 2. Complete the CodeSignal Online Assessment (70 minutes, 4 problems, threshol</t>
         </is>
       </c>
       <c r="H272" s="6" t="inlineStr">
         <is>
-          <t>No. TSMC explicitly excludes H-1B, OPT, O-1, and TN visa holders from US internship positions. Applicants must have long-term work authorization without any current or future employer sponsorship. Arizona postings use sl</t>
+          <t>Yes. Uber accepts CPT and OPT for interns. For full-time conversion, Uber filed 823 H-1B petitions in FY2025 (ranked #41 among US employers). STEM OPT 24-month extension eligible.</t>
         </is>
       </c>
       <c r="I272" s="6" t="inlineStr">
         <is>
-          <t>Partially. Window is defined but review within it is rolling; apply early</t>
+          <t>Yes. Offers extended continuously; early applicants see significantly higher response rates</t>
         </is>
       </c>
       <c r="J272" s="6" t="inlineStr">
         <is>
-          <t>$23 to $48/hr depending on location, role, and degree (Camas WA entry to San Jose PhD research)</t>
+          <t>$52/hr + housing stipend $1,000–$6,000/month + Uber credits, meals, benefits</t>
         </is>
       </c>
       <c r="K272" s="6" t="inlineStr">
         <is>
-          <t>Applications for summer 2027 expected to open October to December 2026 and close by March 2027 (earliest AZ postings live as of July 2026; projected from prior cycles)</t>
+          <t>Open now for software engineering: Uber posted 2027 Software Engineering Intern, US (San Francisco, Seattle, Sunnyvale) on October 20, 2026, with a scheduled end date of October 31, 2026. On October 22 it was the only US intern requisition on Uber’s careers board</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Ubisoft</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
@@ -15733,12 +15741,12 @@
       </c>
       <c r="D273" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Data Science  (2 of 6 tracks)</t>
+          <t>Data &amp; Analytics  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E273" s="7" t="inlineStr">
         <is>
-          <t>jobs.uber.com/en/teams/emerging-talent/</t>
+          <t>ubisoft.com/en-us/company/careers/search</t>
         </is>
       </c>
       <c r="F273" s="7" t="inlineStr">
@@ -15748,34 +15756,30 @@
       </c>
       <c r="G273" s="6" t="inlineStr">
         <is>
-          <t>Uber’s SWE internship funnel runs 4 stages, averaging about 28 days from application to decision: 1. Submit your application at jobs.uber.com with a resume. List 3 to 5 city preferences in order. No cover letter required. 2. Complete the CodeSignal Online Assessment (70 minutes, 4 problems, threshol</t>
-        </is>
-      </c>
-      <c r="H273" s="6" t="inlineStr">
-        <is>
-          <t>Yes. Uber accepts CPT and OPT for interns. For full-time conversion, Uber filed 823 H-1B petitions in FY2025 (ranked #41 among US employers). STEM OPT 24-month extension eligible.</t>
-        </is>
-      </c>
+          <t>For programming roles, expect 4 rounds: an online MCQ assessment covering OOP, OS, C++, and data structures; two technical interviews testing CS fundamentals and game-specific knowledge like 3D math and engine concepts; and a short HR round. For other roles, expect 2 to 3 rounds including a recruite</t>
+        </is>
+      </c>
+      <c r="H273" s="6" t="inlineStr"/>
       <c r="I273" s="6" t="inlineStr">
         <is>
-          <t>Yes. Offers extended continuously; early applicants see significantly higher response rates</t>
+          <t>Effectively yes. Each studio reviews applications as they come in; positions close once filled. Structured programs (Develop at Ubisoft, Graduate Program, NEXT)</t>
         </is>
       </c>
       <c r="J273" s="6" t="inlineStr">
         <is>
-          <t>$52/hr + housing stipend $1,000–$6,000/month + Uber credits, meals, benefits</t>
+          <t>$23 to $33/hr for US interns (Indeed and Glassdoor ranges); ~$18 to $22 CAD/hr for Montreal co-ops</t>
         </is>
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>Open now for software engineering: Uber posted 2027 Software Engineering Intern, US (San Francisco, Seattle, Sunnyvale) on October 20, 2026, with a scheduled end date of October 31, 2026. On October 22 it was the only US intern requisition on Uber’s careers board</t>
+          <t>Studio postings expected December 2026 through March 2027; Develop at Ubisoft mentorship opens October 2026</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>Ubisoft</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
@@ -15790,12 +15794,12 @@
       </c>
       <c r="D274" s="6" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics  (1 of 6 tracks)</t>
+          <t>See guide</t>
         </is>
       </c>
       <c r="E274" s="7" t="inlineStr">
         <is>
-          <t>ubisoft.com/en-us/company/careers/search</t>
+          <t>ubs.com/global/en/careers/early-careers.html</t>
         </is>
       </c>
       <c r="F274" s="7" t="inlineStr">
@@ -15805,30 +15809,34 @@
       </c>
       <c r="G274" s="6" t="inlineStr">
         <is>
-          <t>For programming roles, expect 4 rounds: an online MCQ assessment covering OOP, OS, C++, and data structures; two technical interviews testing CS fundamentals and game-specific knowledge like 3D math and engine concepts; and a short HR round. For other roles, expect 2 to 3 rounds including a recruite</t>
-        </is>
-      </c>
-      <c r="H274" s="6" t="inlineStr"/>
+          <t>Four to five back-to-back interviews, each roughly 30 minutes, with Associates, VPs, and Directors. The format mixes behavioral questions (resume walkthrough, teamwork, setback stories) with technical questions for front-office roles (DCF, three-statement linking, EV vs. equity value, LBO basics). S</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>Many US internship positions explicitly state they do not offer employment-based immigration sponsorship, including OPT and CPT. This is confirmed across Global Banking, Global Wealth Management, and Asset Management pos</t>
+        </is>
+      </c>
       <c r="I274" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Each studio reviews applications as they come in; positions close once filled. Structured programs (Develop at Ubisoft, Graduate Program, NEXT)</t>
+          <t>Yes. UBS reviews on a rolling basis; front-office US Summer 2027 seats filled by May 2026, so early-window seats go fast. Five US 2027 Summer Internship posting</t>
         </is>
       </c>
       <c r="J274" s="6" t="inlineStr">
         <is>
-          <t>$23 to $33/hr for US interns (Indeed and Glassdoor ranges); ~$18 to $22 CAD/hr for Montreal co-ops</t>
+          <t>$43–$55/hr depending on division (Global Banking $52.88; Global Wealth Management $43.27)</t>
         </is>
       </c>
       <c r="K274" s="6" t="inlineStr">
         <is>
-          <t>Studio postings expected December 2026 through March 2027; Develop at Ubisoft mentorship opens October 2026</t>
+          <t>Open now for summer 2027: US internships in Technology, Group Risk Control and Chief Operating Office (New York/New Jersey and Raleigh) were listed on UBS's early-careers job gateway on October 10, 2026. Front-office US tracks (Investment Banking, Global Markets, Wealth Management, Asset Management, Research) were not listed that day and are expected December 2026 to January 2027, rolling until fi</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>UBS</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
@@ -15843,12 +15851,12 @@
       </c>
       <c r="D275" s="6" t="inlineStr">
         <is>
-          <t>See guide</t>
+          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E275" s="7" t="inlineStr">
         <is>
-          <t>ubs.com/global/en/careers/early-careers.html</t>
+          <t>careers.ulta.com/internships</t>
         </is>
       </c>
       <c r="F275" s="7" t="inlineStr">
@@ -15858,34 +15866,30 @@
       </c>
       <c r="G275" s="6" t="inlineStr">
         <is>
-          <t>Four to five back-to-back interviews, each roughly 30 minutes, with Associates, VPs, and Directors. The format mixes behavioral questions (resume walkthrough, teamwork, setback stories) with technical questions for front-office roles (DCF, three-statement linking, EV vs. equity value, LBO basics). S</t>
-        </is>
-      </c>
-      <c r="H275" s="6" t="inlineStr">
-        <is>
-          <t>Many US internship positions explicitly state they do not offer employment-based immigration sponsorship, including OPT and CPT. This is confirmed across Global Banking, Global Wealth Management, and Asset Management pos</t>
-        </is>
-      </c>
+          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr"/>
       <c r="I275" s="6" t="inlineStr">
         <is>
-          <t>Yes. UBS reviews on a rolling basis; front-office US Summer 2027 seats filled by May 2026, so early-window seats go fast. Five US 2027 Summer Internship posting</t>
+          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
         </is>
       </c>
       <c r="J275" s="6" t="inlineStr">
         <is>
-          <t>$43–$55/hr depending on division (Global Banking $52.88; Global Wealth Management $43.27)</t>
+          <t>$25.00 per hour on the 2027-cycle corporate postings we checked (Corporate Strategy, Audit, Ecommerce) and $30.00 per hour on the distribution-center postings w</t>
         </is>
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: US internships in Technology, Group Risk Control and Chief Operating Office (New York/New Jersey and Raleigh) were listed on UBS's early-careers job gateway on October 10, 2026. Front-office US tracks (Investment Banking, Global Markets, Wealth Management, Asset Management, Research) were not listed that day and are expected December 2026 to January 2027, rolling until fi</t>
+          <t>Open now for Summer 2027: 22 US intern postings live on Oct 1, 2026 (15 corporate at Bolingbrook, 7 distribution center), posted Sept 14–23, 2026. No deadline printed on the postings we checked; the 2026 cycle closed January 1, so a deadline around January 1, 2027 is expected. Apply early for priority</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
@@ -15900,12 +15904,12 @@
       </c>
       <c r="D276" s="6" t="inlineStr">
         <is>
-          <t>IT / IT Engineering Intern  (1 of 6 tracks)</t>
+          <t>Global Solutions Technology; Cybersecurity / AI Risk; AI/ML Engineering; Data Science &amp; Analytics  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E276" s="7" t="inlineStr">
         <is>
-          <t>careers.ulta.com/internships</t>
+          <t>mycareer.verizon.com/life-at-verizon/students-internships/</t>
         </is>
       </c>
       <c r="F276" s="7" t="inlineStr">
@@ -15915,30 +15919,34 @@
       </c>
       <c r="G276" s="6" t="inlineStr">
         <is>
-          <t>Typically a resume/ATS screen, an on-demand digital video screen (reported to be HireVue), a recruiter phone screen, and one or two hiring-manager rounds on Microsoft Teams, sometimes with a final executive or business-case round. Glassdoor users report about three rounds of behavioral questions ove</t>
-        </is>
-      </c>
-      <c r="H276" s="6" t="inlineStr"/>
+          <t>After applying online, most candidates complete a Candidates Assessment on Workday (the ADEPT-15 personality test, about 25–30 minutes), followed by a self-recorded video interview with 6 behavioral questions and 2 attempts each. Strong candidates advance to a phone or virtual interview, and some ro</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>No. All Verizon internship postings require "authorization to work in the U.S. without restrictions or need for future sponsorship." The summer 2027 postings live October 22, 2026 print no CPT or OPT exception, so F-1 st</t>
+        </is>
+      </c>
       <c r="I276" s="6" t="inlineStr">
         <is>
-          <t>Partially. Postings open in the fall and are reviewed on a rolling basis, but there is a hard published cutoff (January 1 for the 2026 cycle). Competitive corpo</t>
+          <t>Effectively yes. Postings "may close before the stated closing date"; applicants encouraged to apply as soon as possible</t>
         </is>
       </c>
       <c r="J276" s="6" t="inlineStr">
         <is>
-          <t>$25.00 per hour on the 2027-cycle corporate postings we checked (Corporate Strategy, Audit, Ecommerce) and $30.00 per hour on the distribution-center postings w</t>
+          <t>$25.00 to $27.00/hr on the summer 2027 postings live October 22, 2026 (Data Science and Call Routing Optimization Engineering $27.00, Sales and Service Operatio</t>
         </is>
       </c>
       <c r="K276" s="6" t="inlineStr">
         <is>
-          <t>Open now for Summer 2027: 22 US intern postings live on Oct 1, 2026 (15 corporate at Bolingbrook, 7 distribution center), posted Sept 14–23, 2026. No deadline printed on the postings we checked; the 2026 cycle closed January 1, so a deadline around January 1, 2027 is expected. Apply early for priority</t>
+          <t>Open for summer 2027, one posting at a time: on October 30, 2026 Verizon's careers board listed one US summer 2027 internship, Verizon Consumer Group Customer Go To Channel Operations (Basking Ridge, NJ, R-1102390), posted October 23, 2026; its end date, first set as October 28, now reads November 3, 2026. The second wave of eight postings (October 19 and 20; Call Routing Optimization Engineering,</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
@@ -15953,12 +15961,12 @@
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>Global Solutions Technology; Cybersecurity / AI Risk; AI/ML Engineering; Data Science &amp; Analytics  (4 of 6 tracks)</t>
+          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E277" s="7" t="inlineStr">
         <is>
-          <t>mycareer.verizon.com/life-at-verizon/students-internships/</t>
+          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
         </is>
       </c>
       <c r="F277" s="7" t="inlineStr">
@@ -15968,34 +15976,34 @@
       </c>
       <c r="G277" s="6" t="inlineStr">
         <is>
-          <t>After applying online, most candidates complete a Candidates Assessment on Workday (the ADEPT-15 personality test, about 25–30 minutes), followed by a self-recorded video interview with 6 behavioral questions and 2 attempts each. Strong candidates advance to a phone or virtual interview, and some ro</t>
+          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
         </is>
       </c>
       <c r="H277" s="6" t="inlineStr">
         <is>
-          <t>No. All Verizon internship postings require "authorization to work in the U.S. without restrictions or need for future sponsorship." The summer 2027 postings live October 22, 2026 print no CPT or OPT exception, so F-1 st</t>
+          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
         </is>
       </c>
       <c r="I277" s="6" t="inlineStr">
         <is>
-          <t>Effectively yes. Postings "may close before the stated closing date"; applicants encouraged to apply as soon as possible</t>
+          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
         </is>
       </c>
       <c r="J277" s="6" t="inlineStr">
         <is>
-          <t>$25.00 to $27.00/hr on the summer 2027 postings live October 22, 2026 (Data Science and Call Routing Optimization Engineering $27.00, Sales and Service Operatio</t>
+          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
         </is>
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>Open for summer 2027, one posting at a time: on October 25, 2026 Verizon's careers board listed one US summer 2027 internship, Verizon Consumer Group Customer Go To Channel Operations (Basking Ridge, NJ), posted October 23, 2026 with an end date of October 28, 2026. The second wave of eight postings (October 19 and 20; Call Routing Optimization Engineering, Data Science, Sales and Service Operatio</t>
+          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
@@ -16005,17 +16013,17 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>October 2026 – August 2027</t>
         </is>
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>DTE (Data, Technology &amp; Engineering)  (1 of 6 tracks)</t>
+          <t>Software Engineering (Global Tech); Data Science &amp; Analytics  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E278" s="7" t="inlineStr">
         <is>
-          <t>vrtx.wd501.myworkdayjobs.com/Vertex_intern</t>
+          <t>careers.walmart.com/us/en/home/careers-areas/students</t>
         </is>
       </c>
       <c r="F278" s="7" t="inlineStr">
@@ -16025,34 +16033,34 @@
       </c>
       <c r="G278" s="6" t="inlineStr">
         <is>
-          <t>The process typically involves 2 to 3 rounds over about 19 days: a 30-minute phone screen with an HR recruiter, followed by 2 to 4 technical and behavioral interviews with team members and managers. R&amp;D roles skew 70% technical and may include a 10 to 15 minute research presentation. There is no Hir</t>
+          <t>Walmart runs two distinct funnels depending on whether you're applying for a corporate/business track or a Walmart Global Tech/SWE track: 1. Apply at careers.walmart.com . Summer 2027 postings started going live on August 25, 2026, and 17 US intern requisitions were listed on October 11, 2026. Ten p</t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr">
         <is>
-          <t>No. Vertex explicitly states across all internship and co-op postings that it doesn't provide sponsorship for internships, co-ops, or entry-level roles. You must have legal authorization to work in the United States. Som</t>
+          <t>No. Walmart doesn't provide visa sponsorship (H-1B, TN) for internship roles. International students on CPT or OPT are eligible, provided they have valid work authorization during the full internship period.</t>
         </is>
       </c>
       <c r="I278" s="6" t="inlineStr">
         <is>
-          <t>Yes. Applications are reviewed rolling; positions may close before the stated deadline once filled</t>
+          <t>Yes. Interviews begin rolling in September; ~60–70% of slots fill by mid-September</t>
         </is>
       </c>
       <c r="J278" s="6" t="inlineStr">
         <is>
-          <t>$20–$52/hr depending on degree level and track; ~$4,500 housing stipend for relocating candidates</t>
+          <t>$19–$55/hr depending on role and location; SWE at Sunnyvale up to $52/hr, plus housing and relocation</t>
         </is>
       </c>
       <c r="K278" s="6" t="inlineStr">
         <is>
-          <t>Expected ~October 2026 for summer 2027 (documented pattern; not yet posted)</t>
+          <t xml:space="preserve">Open now for summer 2027: 17 US Summer 2027 intern requisitions were listed on October 11, 2026 (first postings August 25, newest October 9, 2026). Ten print no close date; data science closes January 29, 2027, cybersecurity February 5, 2027, and three supply chain and transportation reqs March 1, 2027. The Accounting and Finance Development Program and Automation Engineer postings were no longer </t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Weaviate</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
@@ -16062,17 +16070,17 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – August 2027</t>
+          <t>October–December 2026</t>
         </is>
       </c>
       <c r="D279" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering (Global Tech); Data Science &amp; Analytics  (2 of 6 tracks)</t>
+          <t>Software Engineer Intern  (1 of 3 tracks)</t>
         </is>
       </c>
       <c r="E279" s="7" t="inlineStr">
         <is>
-          <t>careers.walmart.com/us/en/home/careers-areas/students</t>
+          <t>jobs.ashbyhq.com/weaviate</t>
         </is>
       </c>
       <c r="F279" s="7" t="inlineStr">
@@ -16082,34 +16090,34 @@
       </c>
       <c r="G279" s="6" t="inlineStr">
         <is>
-          <t>Walmart runs two distinct funnels depending on whether you're applying for a corporate/business track or a Walmart Global Tech/SWE track: 1. Apply at careers.walmart.com . Summer 2027 postings started going live on August 25, 2026, and 17 US intern requisitions were listed on October 11, 2026. Ten p</t>
+          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
         </is>
       </c>
       <c r="H279" s="6" t="inlineStr">
         <is>
-          <t>No. Walmart doesn't provide visa sponsorship (H-1B, TN) for internship roles. International students on CPT or OPT are eligible, provided they have valid work authorization during the full internship period.</t>
+          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
         </is>
       </c>
       <c r="I279" s="6" t="inlineStr">
         <is>
-          <t>Yes. Interviews begin rolling in September; ~60–70% of slots fill by mid-September</t>
+          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
         </is>
       </c>
       <c r="J279" s="6" t="inlineStr">
         <is>
-          <t>$19–$55/hr depending on role and location; SWE at Sunnyvale up to $52/hr, plus housing and relocation</t>
+          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
         </is>
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open now for summer 2027: 17 US Summer 2027 intern requisitions were listed on October 11, 2026 (first postings August 25, newest October 9, 2026). Ten print no close date; data science closes January 29, 2027, cybersecurity February 5, 2027, and three supply chain and transportation reqs March 1, 2027. The Accounting and Finance Development Program and Automation Engineer postings were no longer </t>
+          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>Weaviate</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
@@ -16119,17 +16127,17 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>October–December 2026</t>
+          <t>October 2026 – March 2027</t>
         </is>
       </c>
       <c r="D280" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern  (1 of 3 tracks)</t>
+          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
         </is>
       </c>
       <c r="E280" s="7" t="inlineStr">
         <is>
-          <t>jobs.ashbyhq.com/weaviate</t>
+          <t>coreweave.com/careers/weights-biases</t>
         </is>
       </c>
       <c r="F280" s="7" t="inlineStr">
@@ -16139,34 +16147,34 @@
       </c>
       <c r="G280" s="6" t="inlineStr">
         <is>
-          <t>Four steps over 4 to 7 weeks: a 30-minute introductory chat with People and Culture, a 1-hour technical screen with the hiring manager, a take-home challenge with a 1-hour review discussion, and a 45-minute cultural fit interview. There is no traditional algorithmic coding assessment.</t>
+          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
         </is>
       </c>
       <c r="H280" s="6" t="inlineStr">
         <is>
-          <t>Weaviate does not sponsor visas. F-1 students in the US must secure their own CPT/OPT. All candidates must have existing work authorization in their country of residence</t>
+          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
         </is>
       </c>
       <c r="I280" s="6" t="inlineStr">
         <is>
-          <t>Likely yes. No application deadlines are published on any Weaviate intern posting. Roles remain open until filled. Apply as soon as postings appear</t>
+          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
         </is>
       </c>
       <c r="J280" s="6" t="inlineStr">
         <is>
-          <t>Paid internship with competitive compensation (exact rate not publicly disclosed). Includes paid time off, equipment budget for home office, and potential compa</t>
+          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
         </is>
       </c>
       <c r="K280" s="6" t="inlineStr">
         <is>
-          <t>Expected October to December 2026 for summer 2027 roles. No fixed deadline published. Projected from prior cycle cadence</t>
+          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
@@ -16176,17 +16184,17 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – March 2027</t>
+          <t>October 2026 – February 2027</t>
         </is>
       </c>
       <c r="D281" s="6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer Intern; Software Engineer Intern; ML Infrastructure / Platform Intern  (3 of 4 tracks)</t>
+          <t>Technology  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E281" s="7" t="inlineStr">
         <is>
-          <t>coreweave.com/careers/weights-biases</t>
+          <t>wellsfargojobs.com/en/early-careers/</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
@@ -16196,34 +16204,34 @@
       </c>
       <c r="G281" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">W&amp;B's hiring process typically spans three to five weeks, faster than FAANG, and emphasizes product judgment alongside coding ability: 1. Monitor the CoreWeave/W&amp;B careers portal starting October 2026. Set a monthly calendar reminder and sign up for job alerts. Intern postings appear ad-hoc and can </t>
+          <t>Four stages. First, an online application with resume upload and motivation questions. Second, an online assessment with cognitive or situational judgment tests (coding challenges for tech roles). Third, a HireVue video interview with 3 to 7 behavioral questions and a 24 to 48 hour preparation windo</t>
         </is>
       </c>
       <c r="H281" s="6" t="inlineStr">
         <is>
-          <t>Not explicitly confirmed for interns. Historical listings required US-based applicants. Full-time visa sponsorship has been mentioned in past postings. International students should verify CPT/OPT eligibility directly</t>
+          <t>No. Wells Fargo explicitly requires authorization to work in the United States on a full-time basis and does not sponsor work visas for internships, post-graduation programs, or permanent employment. There is no assistan</t>
         </is>
       </c>
       <c r="I281" s="6" t="inlineStr">
         <is>
-          <t>Yes. Weights &amp; Biases posts internships on an as-needed, ad-hoc basis. No structured deadline or annual cycle has been publicly documented</t>
+          <t>Yes. Wells Fargo reviews and fills positions as qualified candidates are identified</t>
         </is>
       </c>
       <c r="J281" s="6" t="inlineStr">
         <is>
-          <t>No publicly verified intern salary data on Glassdoor or Levels.fyi. Full-time SWE median total compensation is approximately $313,000 per Levels.fyi, suggesting</t>
+          <t>$31–$53/hr ($64,500 to $110,000+ annualized); CIB IB at top with $2,500 housing stipend</t>
         </is>
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>No fixed dates. Intern postings have historically appeared in fall through winter for summer cohorts. Begin monitoring in October 2026 and check monthly through spring 2027</t>
+          <t xml:space="preserve">Mostly closed for summer 2027. As of October 6, 2026, Finance, HR, Audit, Commercial Banking, Consumer Banking and Lending, Global Payments, Wealth &amp; Investment Management, Corporate Risk, COO, Quantitative Analytics and Public Affairs have all come down. Still live for summer 2027: Technology Software Engineering (Posting End Date October 13, 2026) and the MBA Investment Banking Summer Associate </t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZS Associates</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
@@ -16233,17 +16241,17 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>October 2026 – February 2027</t>
+          <t>October 2026</t>
         </is>
       </c>
       <c r="D282" s="6" t="inlineStr">
         <is>
-          <t>Technology  (1 of 6 tracks)</t>
+          <t>Decision Analytics Associate (DAA); Business Technology Solutions Associate (BTSA)  (2 of 4 tracks)</t>
         </is>
       </c>
       <c r="E282" s="7" t="inlineStr">
         <is>
-          <t>wellsfargojobs.com/en/early-careers/</t>
+          <t>jobs.zs.com/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
         </is>
       </c>
       <c r="F282" s="7" t="inlineStr">
@@ -16253,34 +16261,34 @@
       </c>
       <c r="G282" s="6" t="inlineStr">
         <is>
-          <t>Four stages. First, an online application with resume upload and motivation questions. Second, an online assessment with cognitive or situational judgment tests (coding challenges for tech roles). Third, a HireVue video interview with 3 to 7 behavioral questions and a 24 to 48 hour preparation windo</t>
+          <t>The process runs two to four rounds: an online aptitude test covering logical, quantitative, and verbal reasoning, then case and behavioral interviews. ZS cases are candidate-led and often pharma or healthcare themed. Final rounds may include a written case presentation where you analyze a data pack</t>
         </is>
       </c>
       <c r="H282" s="6" t="inlineStr">
         <is>
-          <t>No. Wells Fargo explicitly requires authorization to work in the United States on a full-time basis and does not sponsor work visas for internships, post-graduation programs, or permanent employment. There is no assistan</t>
+          <t>Yes. ZS's official FAQ states the firm offers visa sponsorship for full-time employees and support for interns with a student visa. Sponsorship type and reimbursement may vary based on location, role, and status. ZS file</t>
         </is>
       </c>
       <c r="I282" s="6" t="inlineStr">
         <is>
-          <t>Yes. Wells Fargo reviews and fills positions as qualified candidates are identified</t>
+          <t>Yes. ZS recruits on a rolling basis during campus season; intern spots fill as strong candidates clear the rounds</t>
         </is>
       </c>
       <c r="J282" s="6" t="inlineStr">
         <is>
-          <t>$31–$53/hr ($64,500 to $110,000+ annualized); CIB IB at top with $2,500 housing stipend</t>
+          <t>~$34/hr general intern range ($25–$46); Strategy Insights &amp; Planning ~$50/hr; Business Technology Solutions ~$63/hr</t>
         </is>
       </c>
       <c r="K282" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mostly closed for summer 2027. As of October 6, 2026, Finance, HR, Audit, Commercial Banking, Consumer Banking and Lending, Global Payments, Wealth &amp; Investment Management, Corporate Risk, COO, Quantitative Analytics and Public Affairs have all come down. Still live for summer 2027: Technology Software Engineering (Posting End Date October 13, 2026) and the MBA Investment Banking Summer Associate </t>
+          <t>Open now for summer 2027: nine North America intern postings live on jobs.zs.com as of October 1, 2026 (posted September 1–2). Rolling review; no deadline printed in the postings we checked</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>ZS Associates</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
@@ -16290,17 +16298,17 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>October 2026</t>
+          <t>December 2026 – February 2027</t>
         </is>
       </c>
       <c r="D283" s="6" t="inlineStr">
         <is>
-          <t>Decision Analytics Associate (DAA); Business Technology Solutions Associate (BTSA)  (2 of 4 tracks)</t>
+          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
         </is>
       </c>
       <c r="E283" s="7" t="inlineStr">
         <is>
-          <t>jobs.zs.com/jobs?keywords=intern&amp;sortBy=relevance&amp;page=1</t>
+          <t>biibhr.wd3.myworkdayjobs.com/external</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -16310,34 +16318,34 @@
       </c>
       <c r="G283" s="6" t="inlineStr">
         <is>
-          <t>The process runs two to four rounds: an online aptitude test covering logical, quantitative, and verbal reasoning, then case and behavioral interviews. ZS cases are candidate-led and often pharma or healthcare themed. Final rounds may include a written case presentation where you analyze a data pack</t>
+          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
         </is>
       </c>
       <c r="H283" s="6" t="inlineStr">
         <is>
-          <t>Yes. ZS's official FAQ states the firm offers visa sponsorship for full-time employees and support for interns with a student visa. Sponsorship type and reimbursement may vary based on location, role, and status. ZS file</t>
+          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
         </is>
       </c>
       <c r="I283" s="6" t="inlineStr">
         <is>
-          <t>Yes. ZS recruits on a rolling basis during campus season; intern spots fill as strong candidates clear the rounds</t>
+          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
         </is>
       </c>
       <c r="J283" s="6" t="inlineStr">
         <is>
-          <t>~$34/hr general intern range ($25–$46); Strategy Insights &amp; Planning ~$50/hr; Business Technology Solutions ~$63/hr</t>
+          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>Open now for summer 2027: nine North America intern postings live on jobs.zs.com as of October 1, 2026 (posted September 1–2). Rolling review; no deadline printed in the postings we checked</t>
+          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted as of October 30, 2026). The MBA IMPACT summer 2027 posting and separate January to June 2027 co-ops are open now</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
@@ -16347,17 +16355,17 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>December 2026 – February 2027</t>
+          <t>February 2027</t>
         </is>
       </c>
       <c r="D284" s="6" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering; Information Technology  (2 of 6 tracks)</t>
+          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E284" s="7" t="inlineStr">
         <is>
-          <t>biibhr.wd3.myworkdayjobs.com/external</t>
+          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
         </is>
       </c>
       <c r="F284" s="7" t="inlineStr">
@@ -16367,34 +16375,30 @@
       </c>
       <c r="G284" s="6" t="inlineStr">
         <is>
-          <t>The typical process has two to three stages: a 20 to 30 minute recruiter phone screen, a 60 to 90 minute first-round virtual interview (behavioral plus technical), and for advanced candidates, a half-day final round with 3 to 5 interviewers. Biogen evaluates candidates against its six "Elements": Cu</t>
-        </is>
-      </c>
-      <c r="H284" s="6" t="inlineStr">
-        <is>
-          <t>Biogen requires applicants to be "legally authorized to work in the US" for internship and co-op roles. International students on CPT or OPT are eligible. The MBA IMPACT program specifically allows "Permanent US Work Aut</t>
-        </is>
-      </c>
+          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
+        </is>
+      </c>
+      <c r="H284" s="6" t="inlineStr"/>
       <c r="I284" s="6" t="inlineStr">
         <is>
-          <t>Yes. Biogen explicitly accepts applications "on a rolling basis" and encourages applying "sooner rather than later"</t>
+          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
         </is>
       </c>
       <c r="J284" s="6" t="inlineStr">
         <is>
-          <t>$25 to $55/hr by degree level; MBA IMPACT pays a flat $57/hr. Housing/relocation stipend ($3K to $5K, community-reported)</t>
+          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr">
         <is>
-          <t>Expected December 2026 to early February 2027 for summer 2027 (documented pattern; not yet posted as of October 1, 2026). Separate January to June 2027 co-ops are open now</t>
+          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
@@ -16404,17 +16408,17 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>February 2027</t>
+          <t>February–April 2027</t>
         </is>
       </c>
       <c r="D285" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Machine Learning &amp; AI; Hardware Engineering; Hardware Technologies (Silicon); Engineering Program Management  (5 of 6 tracks)</t>
+          <t>iXp Software Engineering; iXp AI Software Developer; iXp Data Engineering  (3 of 6 tracks)</t>
         </is>
       </c>
       <c r="E285" s="7" t="inlineStr">
         <is>
-          <t>jobs.apple.com/en-us/search?team=internships-STDNT-INTRN</t>
+          <t>jobs.sap.com/go/Intern-Jobs-in-the-United-States/872801/</t>
         </is>
       </c>
       <c r="F285" s="7" t="inlineStr">
@@ -16424,30 +16428,34 @@
       </c>
       <c r="G285" s="6" t="inlineStr">
         <is>
-          <t>Team-run and variable. You apply per posting at jobs.apple.com, take a recruiter phone screen if a team pulls your resume, then do roughly 2 to 4 interviews mixing behavioral and live technical questions. There's no standardized online assessment, and offers commonly arrive within 1 to 2 weeks.</t>
-        </is>
-      </c>
-      <c r="H285" s="6" t="inlineStr"/>
+          <t xml:space="preserve">Typically 3 to 4 stages: automated coding challenge via Codility or HackerRank (60 to 90 minutes, LeetCode Medium), recruiter phone screen (30 minutes), technical interview (60 to 75 minutes), and behavioral interview (45 to 60 minutes, STAR method). Select roles include an Assessment Center with a </t>
+        </is>
+      </c>
+      <c r="H285" s="6" t="inlineStr">
+        <is>
+          <t>F-1 CPT and OPT fully eligible. Some roles explicitly do not provide visa sponsorship; check individual JDs. H-1B available for full-time conversion</t>
+        </is>
+      </c>
       <c r="I285" s="6" t="inlineStr">
         <is>
-          <t>Yes. Official JD text: "Apple accepts applications to this posting on an ongoing basis"; teams hire as headcount opens</t>
+          <t>Yes, confirmed. Applications reviewed rolling; submissions in the first 2 weeks get higher visibility. Employee referrals advance at 3 to 5x the cold-applicatio</t>
         </is>
       </c>
       <c r="J285" s="6" t="inlineStr">
         <is>
-          <t>$38 to $60/hr by role (Levels.fyi, self-reported); corporate housing or a ~$3,300/mo stipend (community-reported)</t>
+          <t>SWE US $32 to $56/hr (~$5,500 to $8,500/month). Master's-level candidates earn 15 to 20% premiums. Full posted range $15 to $62/hr across all roles</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Summer 2027 intern roles are live at jobs.apple.com, including Applied Data Solutions 2027, IST 2027, and hardware/software engineering tracks. Rolling review through February 2027</t>
+          <t>Summer 2027 iXp roles: not posted yet on October 6, 2026; expected around February to April 2027, projected from the 1 to 3 month lead on current postings. Off-cycle US iXp roles (6 to 12 months, starting October 2026 to early 2027) are open now</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
@@ -16457,17 +16465,17 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>February–April 2027</t>
+          <t>March 2027</t>
         </is>
       </c>
       <c r="D286" s="6" t="inlineStr">
         <is>
-          <t>iXp Software Engineering; iXp AI Software Developer; iXp Data Engineering  (3 of 6 tracks)</t>
+          <t>GEICO TDP Software &amp; AI Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E286" s="7" t="inlineStr">
         <is>
-          <t>jobs.sap.com/go/Intern-Jobs-in-the-United-States/872801/</t>
+          <t>geico.wd1.myworkdayjobs.com/External</t>
         </is>
       </c>
       <c r="F286" s="7" t="inlineStr">
@@ -16477,34 +16485,34 @@
       </c>
       <c r="G286" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Typically 3 to 4 stages: automated coding challenge via Codility or HackerRank (60 to 90 minutes, LeetCode Medium), recruiter phone screen (30 minutes), technical interview (60 to 75 minutes), and behavioral interview (45 to 60 minutes, STAR method). Select roles include an Assessment Center with a </t>
+          <t>Most subsidiaries use 1 to 2 rounds: a recruiter phone screen followed by a hiring-manager interview. GEICO tech adds a technical skills assessment. Behavioral questions focus on integrity, problem-solving, teamwork, and long-term thinking using the STAR method.</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
         <is>
-          <t>F-1 CPT and OPT fully eligible. Some roles explicitly do not provide visa sponsorship; check individual JDs. H-1B available for full-time conversion</t>
+          <t>Generally no. GEICO explicitly does not sponsor employment authorization for intern roles. Other subsidiaries typically require existing U.S. work authorization</t>
         </is>
       </c>
       <c r="I286" s="6" t="inlineStr">
         <is>
-          <t>Yes, confirmed. Applications reviewed rolling; submissions in the first 2 weeks get higher visibility. Employee referrals advance at 3 to 5x the cold-applicatio</t>
+          <t>Not officially stated by any subsidiary. Most roles accept applications until filled. Apply as soon as postings appear for the best odds</t>
         </is>
       </c>
       <c r="J286" s="6" t="inlineStr">
         <is>
-          <t>SWE US $32 to $56/hr (~$5,500 to $8,500/month). Master's-level candidates earn 15 to 20% premiums. Full posted range $15 to $62/hr across all roles</t>
+          <t>Varies widely: GEICO tech $28 to $50+/hr (official JD), BHSI $24 to $43/hr, BH Energy IT $17.50 to $21.50/hr, BNSF ~$20/hr (community), BH GUARD $15 to $20/hr</t>
         </is>
       </c>
       <c r="K286" s="6" t="inlineStr">
         <is>
-          <t>Summer 2027 iXp roles: not posted yet on October 6, 2026; expected around February to April 2027, projected from the 1 to 3 month lead on current postings. Off-cycle US iXp roles (6 to 12 months, starting October 2026 to early 2027) are open now</t>
+          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
@@ -16519,12 +16527,12 @@
       </c>
       <c r="D287" s="6" t="inlineStr">
         <is>
-          <t>GEICO TDP Software &amp; AI Intern  (1 of 6 tracks)</t>
+          <t>Engineering / Developer  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E287" s="7" t="inlineStr">
         <is>
-          <t>geico.wd1.myworkdayjobs.com/External</t>
+          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
         </is>
       </c>
       <c r="F287" s="7" t="inlineStr">
@@ -16534,34 +16542,34 @@
       </c>
       <c r="G287" s="6" t="inlineStr">
         <is>
-          <t>Most subsidiaries use 1 to 2 rounds: a recruiter phone screen followed by a hiring-manager interview. GEICO tech adds a technical skills assessment. Behavioral questions focus on integrity, problem-solving, teamwork, and long-term thinking using the STAR method.</t>
+          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
         </is>
       </c>
       <c r="H287" s="6" t="inlineStr">
         <is>
-          <t>Generally no. GEICO explicitly does not sponsor employment authorization for intern roles. Other subsidiaries typically require existing U.S. work authorization</t>
+          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
         </is>
       </c>
       <c r="I287" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated by any subsidiary. Most roles accept applications until filled. Apply as soon as postings appear for the best odds</t>
+          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
         </is>
       </c>
       <c r="J287" s="6" t="inlineStr">
         <is>
-          <t>Varies widely: GEICO tech $28 to $50+/hr (official JD), BHSI $24 to $43/hr, BH Energy IT $17.50 to $21.50/hr, BNSF ~$20/hr (community), BH GUARD $15 to $20/hr</t>
+          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>Open now at the first movers: BNSF posted 17 Summer 2027 internships on September 4, 2026, and GEICO's summer 2027 Analyst Internship Program, Human Resources and Marketing internships went live between September 14 and 29. BHHC, BHSI, and BH GUARD are expected to post in spring 2027 (projected from the prior cycle)</t>
+          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
@@ -16571,17 +16579,17 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>March 2027</t>
+          <t>March–September 2027</t>
         </is>
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>Engineering / Developer  (1 of 6 tracks)</t>
+          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
         </is>
       </c>
       <c r="E288" s="7" t="inlineStr">
         <is>
-          <t>bny.com/corporate/global/en/about-us/careers/students/intern</t>
+          <t>careers.l3harris.com/en/new-grads-and-interns</t>
         </is>
       </c>
       <c r="F288" s="7" t="inlineStr">
@@ -16591,34 +16599,34 @@
       </c>
       <c r="G288" s="6" t="inlineStr">
         <is>
-          <t>The tech process has three stages after the application: a HackerRank coding assessment with 4 questions (1 easy, 2 medium, 1 hard) covering graphs, greedy algorithms, and data structures; a first-round technical interview focused on DSA and OOP concepts; and a second-round interview mixing technica</t>
+          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
         </is>
       </c>
       <c r="H288" s="6" t="inlineStr">
         <is>
-          <t>No. BNY explicitly states that candidates must not require visa sponsorship now or in the future. This applies to all internship tracks and the full-time Analyst Program. STEM degree holders who will have OPT authorizati</t>
+          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
         </is>
       </c>
       <c r="I288" s="6" t="inlineStr">
         <is>
-          <t>Not officially stated, but individual postings have varied closing dates and positions appear to fill within the window</t>
+          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
         </is>
       </c>
       <c r="J288" s="6" t="inlineStr">
         <is>
-          <t>Tech: ~$38–$48/hr + $3K sign-on; all-role avg: ~$29/hr (community data, not official)</t>
+          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. 2027 BNY Summer Internship Program is live across Engineering, Data Science, and Finance tracks (Lake Mary, Pittsburgh, New York). Rolling review</t>
+          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Rocket Lab</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
@@ -16633,12 +16641,12 @@
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>Software Engineer Intern; Electrical Engineer Intern; Mechanical Engineer Intern; Systems Engineer Intern; Manufacturing Engineer Intern  (5 of 6 tracks)</t>
+          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
         </is>
       </c>
       <c r="E289" s="7" t="inlineStr">
         <is>
-          <t>careers.l3harris.com/en/new-grads-and-interns</t>
+          <t>rocketlabcorp.com/careers/internships/</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
@@ -16648,34 +16656,34 @@
       </c>
       <c r="G289" s="6" t="inlineStr">
         <is>
-          <t>You apply online, complete a recruiter phone screen (15 to 30 minutes), then one to two technical or behavioral interviews (30 to 60 minutes each). Glassdoor rates interview difficulty at 2.5 out of 5, and 82% of candidates rated the experience as positive. Average time from application to hire is a</t>
+          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
         <is>
-          <t>Not available. US citizenship is required for most positions due to government security-clearance requirements. Dual citizenship may also disqualify candidates</t>
+          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
         </is>
       </c>
       <c r="I289" s="6" t="inlineStr">
         <is>
-          <t>Yes. L3Harris reviews applications on a rolling basis. Apply early in the posting window for the best response rates</t>
+          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
         </is>
       </c>
       <c r="J289" s="6" t="inlineStr">
         <is>
-          <t>Approximately $25 to $35 per hour depending on role, level, and location. Software engineering interns report around $28 to $32/hr. Housing and relocation stipe</t>
+          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
         </is>
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>OPEN NOW. Spring 2027, Summer 2027, and Fall 2027 engineering intern roles are live on careers.l3harris.com as of August 2026, including Mechanical, Electrical, and Software Engineering. Rolling review; apply early</t>
+          <t>Open now: about 30 Spring 2027 and Summer 2027 intern postings live on Rocket Lab's Greenhouse board since September 9 to 13, 2026 (Long Beach, CA); no published deadline. ITAR: US citizen, green card holder, or other US person status required</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
         <is>
-          <t>Rocket Lab</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
@@ -16685,17 +16693,17 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>March–September 2027</t>
+          <t>June–August 2027</t>
         </is>
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>Software Engineering; Propulsion Engineering; Mechanical Engineering; Manufacturing Engineering  (4 of 6 tracks)</t>
+          <t>IS/Technology Intern  (1 of 6 tracks)</t>
         </is>
       </c>
       <c r="E290" s="7" t="inlineStr">
         <is>
-          <t>rocketlabcorp.com/careers/internships/</t>
+          <t>careers.amgen.com/en/students-graduates</t>
         </is>
       </c>
       <c r="F290" s="7" t="inlineStr">
@@ -16705,34 +16713,34 @@
       </c>
       <c r="G290" s="6" t="inlineStr">
         <is>
-          <t>The typical process has 2 to 3 stages over about one month: a 30-minute recruiter phone screen covering motivation and fit, a 45 to 60-minute technical interview with an engineer on the team, and sometimes a behavioral interview. Software roles may include an online coding assessment or take-home pr</t>
+          <t>After applying, expect a recruiter phone screen lasting about 25 to 30 minutes, followed by a 45 to 90 minute hiring manager interview focused on technical skills and behavioral questions in the STAR format. Some roles add a final panel round with multiple stakeholders, which can run two to four hou</t>
         </is>
       </c>
       <c r="H290" s="6" t="inlineStr">
         <is>
-          <t>For U.S. locations, most roles require U.S. Person status under ITAR (citizen, permanent resident, refugee, or asylee). F-1 visa holders on CPT/OPT are generally ineligible for ITAR-restricted roles, which covers the maj</t>
+          <t>No. Every Amgen internship posting states that the company doesn't provide immigration sponsorship for intern roles. International students on CPT or OPT may be eligible to participate, but H-1B sponsorship isn't offered</t>
         </is>
       </c>
       <c r="I290" s="6" t="inlineStr">
         <is>
-          <t>Yes, effectively rolling. Positions close when filled; applying early matters</t>
+          <t>Yes. Applications reviewed on a rolling basis; positions may close once filled</t>
         </is>
       </c>
       <c r="J290" s="6" t="inlineStr">
         <is>
-          <t>$22–$30/hr by location (Fall 2026 postings); relocation stipend for CA and NZ sites</t>
+          <t>Undergrad $25–$32/hr; graduate $35–$45/hr; housing/relocation stipend for on-site roles</t>
         </is>
       </c>
       <c r="K290" s="6" t="inlineStr">
         <is>
-          <t>Open now: about 30 Spring